--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50D54063-48AF-4848-9D81-E9A2102BD797}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C914A8-9679-5A4E-9DF5-AD732CC65F33}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="893">
   <si>
     <t>Date</t>
   </si>
@@ -2332,148 +2332,373 @@
     <t>&lt;span style="display:none"&gt;row_2-Sex&lt;/span&gt;6</t>
   </si>
   <si>
-    <t>&lt;span style="display:none"&gt;row_3-Sex&lt;/span&gt;7</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_1-Sex&lt;/span&gt;8</t>
-  </si>
-  <si>
-    <t>Specify9</t>
-  </si>
-  <si>
     <t>Specify10</t>
   </si>
   <si>
-    <t>**Sex**11</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_2-Sex&lt;/span&gt;12</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_4-Sex&lt;/span&gt;13</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_3-Sex&lt;/span&gt;14</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_5-Sex&lt;/span&gt;15</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row-Sex&lt;/span&gt;16</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_1-Sex&lt;/span&gt;17</t>
-  </si>
-  <si>
-    <t>Specify18</t>
-  </si>
-  <si>
     <t>Specify19</t>
   </si>
   <si>
-    <t>**Male**20</t>
-  </si>
-  <si>
-    <t>**Female**21</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row-Male&lt;/span&gt;22</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row-Female&lt;/span&gt;23</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_1-Male&lt;/span&gt;24</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_1-Female&lt;/span&gt;25</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_2-Male&lt;/span&gt;26</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_2-Female&lt;/span&gt;27</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_3-Male&lt;/span&gt;28</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_3-Female&lt;/span&gt;29</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_4-Male&lt;/span&gt;30</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_4-Female&lt;/span&gt;31</t>
-  </si>
-  <si>
-    <t>**Sex**32</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row-Sex&lt;/span&gt;33</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_2-Sex&lt;/span&gt;34</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_1-Sex&lt;/span&gt;35</t>
-  </si>
-  <si>
-    <t>What specific campaign event, activity, chart, or discussion caused the shift?36</t>
-  </si>
-  <si>
-    <t>Practical Activity Delivered37</t>
-  </si>
-  <si>
-    <t>Practical Activity Delivered/Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat)38</t>
-  </si>
-  <si>
-    <t>Practical Activity Delivered/Climate-Smart Living: Firewood-saving cooking methods &amp; moving from 3-stone fires39</t>
-  </si>
-  <si>
-    <t>Practical Activity Delivered/Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing40</t>
-  </si>
-  <si>
-    <t>Practical Activity Delivered/Gender Chore Rebalancing: Boys sharing morning water/firewood chores41</t>
-  </si>
-  <si>
-    <t>Practical Activity Delivered/Peer Attendance Tracing: Checking and following up chronically absent classmates42</t>
-  </si>
-  <si>
-    <t>start43</t>
-  </si>
-  <si>
-    <t>end44</t>
-  </si>
-  <si>
-    <t>##### Learner 145</t>
-  </si>
-  <si>
-    <t>##### Learner 22</t>
-  </si>
-  <si>
-    <t>##### Adult 13</t>
-  </si>
-  <si>
-    <t>##### Adult 24</t>
-  </si>
-  <si>
-    <t>**Column**5</t>
-  </si>
-  <si>
-    <t>##### Caregiver 26</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row_1-Column&lt;/span&gt;7</t>
-  </si>
-  <si>
-    <t>##### Caregiver 18</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:none"&gt;row-Column&lt;/span&gt;9</t>
-  </si>
-  <si>
     <t>Specify11</t>
+  </si>
+  <si>
+    <t>##### Learner 4</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_5-Imagine you are at home tonight and your family is cooking plain porridge.  What local greens or food can you ask them to add to make it strong?&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_5-If morning chores are very heavy at home tomorrow, what should happen so you  and your siblings still arrive at school on time?&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_5-Record exact response/words spoken&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_5-Campaign Line Recall: What does 'Abas ikimorikinit kaapei' mean in your own words?&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_5-Record respondent's exact words on campaign line meaning&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any other comments or observations about that event to inform future activities </t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Opio John Fred and Okello Daniel Nimaro</t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>Orientation</t>
+  </si>
+  <si>
+    <t>KIRU P/S</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>2 sessions per week in school</t>
+  </si>
+  <si>
+    <t>Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>Enrich school/home porridge with obtainable local greens or cowpeas</t>
+  </si>
+  <si>
+    <t>10 Cooking demonstration in Communities, teachers roles of forming new or reactivating already existing Nutri school health clubs, elders dialogue etc</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Rebalancing morning water/firewood chores so girls stay in school</t>
+  </si>
+  <si>
+    <t>Mobilize boys/fathers to share water/wood chores so girls arrive on time Adopt firewood-saving practices in school kitchen / establish Nutri Club</t>
+  </si>
+  <si>
+    <t>Re activating school health clubs for Nutri bus campaign, 2 sessions per week</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Rebalancing morning water/firewood chores so girls stay in school Using improved cooking methods to consume less firewood</t>
+  </si>
+  <si>
+    <t>Mobilize boys/fathers to share water/wood chores so girls arrive on time</t>
+  </si>
+  <si>
+    <t>Conducting cooking demos in 10 villages neighbouring the school</t>
+  </si>
+  <si>
+    <t>Rebalancing morning water/firewood chores so girls stay in school Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>Involving children in games that will promote the 3 pillars of Nutri campaign</t>
+  </si>
+  <si>
+    <t>Fair and equal plate sharing between boys and girls at home Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>Enrich school/home porridge with obtainable local greens or cowpeas Adopt firewood-saving practices in school kitchen / establish Nutri Club</t>
+  </si>
+  <si>
+    <t>Preparation of school gardens to boost nutrition in school</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Using improved cooking methods to consume less firewood</t>
+  </si>
+  <si>
+    <t>The kind of food that boost Nutrion</t>
+  </si>
+  <si>
+    <t>Nutri calendar</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>26c18675-fe44-4639-aa5d-707df9618cac</t>
+  </si>
+  <si>
+    <t>submitted_via_web</t>
+  </si>
+  <si>
+    <t>vTpRFNprWBoePswXDqMv26</t>
+  </si>
+  <si>
+    <t>uuid:26c18675-fe44-4639-aa5d-707df9618cac</t>
+  </si>
+  <si>
+    <t>Amoo Sofia</t>
+  </si>
+  <si>
+    <t>Nutriclub session</t>
+  </si>
+  <si>
+    <t>KAKAMAR P/S</t>
+  </si>
+  <si>
+    <t>Session one of the week</t>
+  </si>
+  <si>
+    <t>Amera Francis</t>
+  </si>
+  <si>
+    <t>Under the tree</t>
+  </si>
+  <si>
+    <t>22:30:00.000+03:00</t>
+  </si>
+  <si>
+    <t>15:00:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing Gender Chore Rebalancing: Boys sharing morning water/firewood chores</t>
+  </si>
+  <si>
+    <t>They were asked to try kitchen gardens at home so that their parents could learn from them and adopt</t>
+  </si>
+  <si>
+    <t>The during the bus activation we realized that most students were not in school due to the less portion of food given in school and so gathering alarger number was a little hard because most upper classes were in class studying</t>
+  </si>
+  <si>
+    <t>fb96a303-ee5e-4eda-abb9-ed81ca611cae</t>
+  </si>
+  <si>
+    <t>vetneLvbBEoZyFMAftqN8K</t>
+  </si>
+  <si>
+    <t>uuid:fb96a303-ee5e-4eda-abb9-ed81ca611cae</t>
+  </si>
+  <si>
+    <t>Ogwang Sam</t>
+  </si>
+  <si>
+    <t>Three visit contact</t>
+  </si>
+  <si>
+    <t>Kotido mixed PS</t>
+  </si>
+  <si>
+    <t>Visit 2: NutriBus Big Activation Day</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>O4</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Fair food portions for all genders Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>Strongly Agree</t>
+  </si>
+  <si>
+    <t>Agree</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Explains a specific, actionable practice without prompting</t>
+  </si>
+  <si>
+    <t>States that boys and girls share water/wood chores equally before leaving</t>
+  </si>
+  <si>
+    <t>b8c26a07-d365-49a0-bd0d-6a08b184c590</t>
+  </si>
+  <si>
+    <t>vsQBB8MvohDpjHc8TbDv5G</t>
+  </si>
+  <si>
+    <t>uuid:b8c26a07-d365-49a0-bd0d-6a08b184c590</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_5-Sex&lt;/span&gt;7</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_3-Sex&lt;/span&gt;8</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_1-Sex&lt;/span&gt;9</t>
+  </si>
+  <si>
+    <t>**Sex**12</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_2-Sex&lt;/span&gt;13</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_4-Sex&lt;/span&gt;14</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_3-Sex&lt;/span&gt;15</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_5-Sex&lt;/span&gt;16</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row-Sex&lt;/span&gt;17</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_1-Sex&lt;/span&gt;18</t>
+  </si>
+  <si>
+    <t>Specify20</t>
+  </si>
+  <si>
+    <t>**Male**21</t>
+  </si>
+  <si>
+    <t>**Female**22</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row-Male&lt;/span&gt;23</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row-Female&lt;/span&gt;24</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_1-Male&lt;/span&gt;25</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_1-Female&lt;/span&gt;26</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_2-Male&lt;/span&gt;27</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_2-Female&lt;/span&gt;28</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_3-Male&lt;/span&gt;29</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_3-Female&lt;/span&gt;30</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_4-Male&lt;/span&gt;31</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_4-Female&lt;/span&gt;32</t>
+  </si>
+  <si>
+    <t>**Sex**33</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row-Sex&lt;/span&gt;34</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_2-Sex&lt;/span&gt;35</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_1-Sex&lt;/span&gt;36</t>
+  </si>
+  <si>
+    <t>What specific campaign event, activity, chart, or discussion caused the shift?37</t>
+  </si>
+  <si>
+    <t>Practical Activity Delivered38</t>
+  </si>
+  <si>
+    <t>Practical Activity Delivered/Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat)39</t>
+  </si>
+  <si>
+    <t>Practical Activity Delivered/Climate-Smart Living: Firewood-saving cooking methods &amp; moving from 3-stone fires40</t>
+  </si>
+  <si>
+    <t>Practical Activity Delivered/Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing41</t>
+  </si>
+  <si>
+    <t>Practical Activity Delivered/Gender Chore Rebalancing: Boys sharing morning water/firewood chores42</t>
+  </si>
+  <si>
+    <t>Practical Activity Delivered/Peer Attendance Tracing: Checking and following up chronically absent classmates43</t>
+  </si>
+  <si>
+    <t>start44</t>
+  </si>
+  <si>
+    <t>end45</t>
+  </si>
+  <si>
+    <t>##### Learner 146</t>
+  </si>
+  <si>
+    <t>##### Learner 247</t>
+  </si>
+  <si>
+    <t>##### Adult 148</t>
+  </si>
+  <si>
+    <t>##### Adult 249</t>
+  </si>
+  <si>
+    <t>**Column**50</t>
+  </si>
+  <si>
+    <t>##### Caregiver 251</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row_1-Column&lt;/span&gt;52</t>
+  </si>
+  <si>
+    <t>##### Caregiver 153</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:none"&gt;row-Column&lt;/span&gt;54</t>
+  </si>
+  <si>
+    <t>Specify55</t>
   </si>
 </sst>
 </file>
@@ -2519,7 +2744,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     </dxf>
@@ -2540,10 +2771,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AEL2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:AEL2" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
-  <tableColumns count="818">
-    <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET4" totalsRowShown="0">
+  <autoFilter ref="A1:AET4" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+  <tableColumns count="826">
+    <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
     <tableColumn id="3" xr3:uid="{1A468597-D831-D84D-804A-CED0115BE04C}" name="Specify"/>
     <tableColumn id="4" xr3:uid="{1393CF8E-733A-E140-A757-7249B3FBBBF5}" name="District"/>
@@ -2803,564 +3034,572 @@
     <tableColumn id="258" xr3:uid="{BDE008CB-3B19-C044-8253-C5D4E4F74E08}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Campaign Line Recall: What does 'Abas ikimorikinit kaapei' mean in your own words?&lt;/span&gt;"/>
     <tableColumn id="259" xr3:uid="{1A1FAECF-B2DD-F946-8AA6-6761392D23BA}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Record respondent's exact words on campaign line meaning&lt;/span&gt;"/>
     <tableColumn id="260" xr3:uid="{4BE98BF5-63DF-E044-93FD-D96B8FA6E6A0}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Sex&lt;/span&gt;6"/>
-    <tableColumn id="261" xr3:uid="{43D9CCC4-D82F-7340-BBE8-D62E0EA34A76}" name="##### Adult 2"/>
-    <tableColumn id="262" xr3:uid="{EAE4908E-5AED-E04E-995F-3BF1035D3294}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Imagine you are at home tonight and your family is cooking plain porridge.  What local greens or food can you ask them to add to make it strong?&lt;/span&gt;"/>
-    <tableColumn id="263" xr3:uid="{BE116813-C5F9-5C42-9F48-AF0B3F80D66B}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-If morning chores are very heavy at home tomorrow, what should happen so you  and your siblings still arrive at school on time?&lt;/span&gt;"/>
-    <tableColumn id="264" xr3:uid="{8BC6050E-157A-4A44-B35B-DD2834D33F43}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Record exact response/words spoken&lt;/span&gt;"/>
-    <tableColumn id="265" xr3:uid="{8403B00E-1708-824A-8D89-E3AAE644CDF5}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Campaign Line Recall: What does 'Abas ikimorikinit kaapei' mean in your own words?&lt;/span&gt;"/>
-    <tableColumn id="266" xr3:uid="{1C1F8BF9-88DE-DA4A-A47A-85186676CBD8}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Record respondent's exact words on campaign line meaning&lt;/span&gt;"/>
-    <tableColumn id="267" xr3:uid="{8E1F3396-44DC-E144-8987-360C0EBB7186}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Sex&lt;/span&gt;7"/>
-    <tableColumn id="268" xr3:uid="{A3FA371C-4726-5C48-A698-CD571D44F808}" name="##### Learner 2"/>
-    <tableColumn id="269" xr3:uid="{18E7DF93-EC71-0144-B25A-94835172FD36}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Imagine you are at home tonight and your family is cooking plain porridge.  What local greens or food can you ask them to add to make it strong?&lt;/span&gt;"/>
-    <tableColumn id="270" xr3:uid="{1B3FB524-39A7-6B44-95AC-4E5FEE7BAB8D}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-If morning chores are very heavy at home tomorrow, what should happen so you  and your siblings still arrive at school on time?&lt;/span&gt;"/>
-    <tableColumn id="271" xr3:uid="{4BCE93B3-8C05-644B-A093-9307ED67736E}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Record exact response/words spoken&lt;/span&gt;"/>
-    <tableColumn id="272" xr3:uid="{E6B6094D-C5A3-2840-9306-F73C4A9899FC}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Campaign Line Recall: What does 'Abas ikimorikinit kaapei' mean in your own words?&lt;/span&gt;"/>
-    <tableColumn id="273" xr3:uid="{1E1CD542-9A29-7541-B245-988B5B79FF18}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Record respondent's exact words on campaign line meaning&lt;/span&gt;"/>
-    <tableColumn id="274" xr3:uid="{7DBC2E33-4717-9045-8A5F-763CEA493324}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Sex&lt;/span&gt;8"/>
-    <tableColumn id="275" xr3:uid="{65B42868-A479-A445-89CF-6C521241EDF6}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?"/>
-    <tableColumn id="276" xr3:uid="{AFA86433-1905-294F-B08D-9879BFE402C1}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Lack of preparation confidence/skills"/>
-    <tableColumn id="277" xr3:uid="{5E008FC1-397B-2440-B42D-C0E8CBC120DB}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Taste preference barriers"/>
-    <tableColumn id="278" xr3:uid="{04BF44F0-ACA8-E941-978F-AAFA6ECA03E1}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Ingredients not prioritized at household level"/>
-    <tableColumn id="279" xr3:uid="{17778277-034B-6944-B494-8DE17E2A3F76}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Other"/>
-    <tableColumn id="280" xr3:uid="{43F27785-C9D9-884E-B2EB-DB50B1CD6CF7}" name="Specify9"/>
-    <tableColumn id="281" xr3:uid="{EA93520E-484C-0B40-A908-42683293F13D}" name="Key delivery issue or barrier observed during activation"/>
-    <tableColumn id="282" xr3:uid="{994E4838-ACD7-1C46-B650-CA970507849B}" name="Key success observed during activation"/>
-    <tableColumn id="283" xr3:uid="{34EE488B-B20F-174B-9D8C-AC75EDD1938E}" name="One adaptation to make before the next school"/>
-    <tableColumn id="284" xr3:uid="{FE86ECED-D077-7041-A3BA-EDA9346DCA90}" name="Record the written School Commitment in their exact words"/>
-    <tableColumn id="285" xr3:uid="{48CFFD15-4DAF-DD4E-856C-6F42554E1506}" name="Total NutriCharts Issued (Visit 1)"/>
-    <tableColumn id="286" xr3:uid="{0F8BA876-79F9-4744-9C26-E479D3AC757F}" name="Total NutriCharts Returned Today"/>
-    <tableColumn id="287" xr3:uid="{153A913C-EE52-224C-A3EF-1799F5AC75BF}" name="Returned charts showing joint household completion"/>
-    <tableColumn id="288" xr3:uid="{DFE8FE8A-D12C-C04A-A5D0-CB60F0909305}" name="Primary Feedback from Households"/>
-    <tableColumn id="289" xr3:uid="{CE5990EA-B876-3C48-9A10-8807B3EA385B}" name="Primary Barrier Reported"/>
-    <tableColumn id="290" xr3:uid="{C732E1A9-247C-7443-8A56-64016C5479AA}" name="Specify10"/>
-    <tableColumn id="291" xr3:uid="{BA6D171C-F2BC-EB4C-9E59-2BF6458162CC}" name="Status of Bus Day School Commitment"/>
-    <tableColumn id="292" xr3:uid="{FF8DBFED-E62C-0341-8596-7AE8F5EB833A}" name="If partly done or not done what got in the way?"/>
-    <tableColumn id="293" xr3:uid="{EB529DD2-CB63-4847-837E-8CCA298C3432}" name="Collective Chronic Absentee Tracing Active?"/>
-    <tableColumn id="294" xr3:uid="{43CC63A9-F91D-9144-AA81-3B48605894D0}" name="Explain how it has changed since the Nutribus activation"/>
-    <tableColumn id="295" xr3:uid="{61DE2B76-DD11-0D42-A35E-6811E236416D}" name="Did the school kitchen implement firewood-saving cooking practices/stoves?"/>
-    <tableColumn id="296" xr3:uid="{9F5842AA-825E-5B49-B116-045D7486DE9A}" name="Were school-level media highlights, photos, or student success stories captured for social media PR reporting today?"/>
-    <tableColumn id="297" xr3:uid="{4F57EBF9-3152-3D49-8F8F-DB6A8F91116E}" name="briefly describe the captured PR highlight/story:"/>
-    <tableColumn id="298" xr3:uid="{A204C349-4188-064F-A093-18AD26358FB4}" name="Did teachers or learners report hearing the Nutribus campaign radio spots this week?"/>
-    <tableColumn id="299" xr3:uid="{128D3A95-D2A2-4142-BE28-3A4350C17525}" name="**Household and learner interview**"/>
-    <tableColumn id="300" xr3:uid="{EA034228-1858-8645-BA56-AB7DAC43B393}" name="**Sex**11"/>
-    <tableColumn id="301" xr3:uid="{78651C36-CF91-A443-BA61-7B223248FF9C}" name="**Since taking the chart home which feasible actions was your family able to try?**"/>
-    <tableColumn id="302" xr3:uid="{14FBBFC7-B10D-DF43-8387-CC007AC1937C}" name="**What was difficult or got in the way of taking action?**"/>
-    <tableColumn id="303" xr3:uid="{90605ED0-952D-0C4D-B8B7-AD0F9E24E927}" name="**Has morning water/wood chore sharing shifted to help girls arrive at school on time?**"/>
-    <tableColumn id="304" xr3:uid="{5EC5AE34-E0A7-1443-8361-097529342012}" name="**Has food serving order shifted so the youngest child is served fairly?**"/>
-    <tableColumn id="305" xr3:uid="{345CB5A3-E0AB-2C46-9E05-32C146E52F4E}" name="**Record caregiver/learner verbatim comments on shifts at home**"/>
-    <tableColumn id="306" xr3:uid="{F3D355D8-B487-8F43-9721-06E4512073E8}" name="##### Learner III"/>
-    <tableColumn id="307" xr3:uid="{20CAD6E9-4B05-C242-9336-134F43158B6D}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Sex&lt;/span&gt;12"/>
-    <tableColumn id="308" xr3:uid="{35A2131E-2E45-8A41-8039-2900A72BC580}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
-    <tableColumn id="309" xr3:uid="{8CF4524E-0F4B-8041-89DD-E2D4103791DE}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
-    <tableColumn id="310" xr3:uid="{B93DA49F-883F-774D-8DB2-72798F7C0584}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
-    <tableColumn id="311" xr3:uid="{4C2AADB5-48E0-7B44-A320-E4206A9859BC}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
-    <tableColumn id="312" xr3:uid="{333EC2DC-7BF7-4045-A535-5AE0BC1855A3}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
-    <tableColumn id="313" xr3:uid="{F8A265DC-4541-A340-8E6C-366C8B45711B}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
-    <tableColumn id="314" xr3:uid="{94B09118-F3C2-EC41-82EB-707AFC280777}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
-    <tableColumn id="315" xr3:uid="{739D5E49-671A-1B49-B297-8A75E47BF9E0}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
-    <tableColumn id="316" xr3:uid="{AA849FF2-D1CA-FD4C-B716-BE5C76A5DD24}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
-    <tableColumn id="317" xr3:uid="{E9293D66-995D-8341-9265-36CC40B0ADEE}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
-    <tableColumn id="318" xr3:uid="{FF545F7B-4C99-754B-9464-8B936F61B1D6}" name="##### Caregiver II"/>
-    <tableColumn id="319" xr3:uid="{0C8AA7FF-BF9B-0F49-8DB2-70BF194E8C4B}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Sex&lt;/span&gt;13"/>
-    <tableColumn id="320" xr3:uid="{C415E0B2-4351-1C4E-8F7B-3B1DD980F7CC}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
-    <tableColumn id="321" xr3:uid="{701DA804-90DD-8148-8E6A-048F8E81762E}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
-    <tableColumn id="322" xr3:uid="{AFE3F5CA-313A-EE41-8FF7-9C9101EDA281}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
-    <tableColumn id="323" xr3:uid="{D9A87922-5534-2B4C-AE78-9DA2781B57F1}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
-    <tableColumn id="324" xr3:uid="{473DE0FE-0ED0-2242-9D48-46EC48F0E310}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
-    <tableColumn id="325" xr3:uid="{003049ED-3ED5-5E46-B664-EE3EBF2F62FD}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
-    <tableColumn id="326" xr3:uid="{95C84FEB-EA38-3445-937C-661FF0E00CE5}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
-    <tableColumn id="327" xr3:uid="{EE7A1C8B-F420-5E49-89B0-9A5AD2968DDD}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
-    <tableColumn id="328" xr3:uid="{F692C1F9-C81E-9E4E-9E70-F62EED6A8BBC}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
-    <tableColumn id="329" xr3:uid="{0035D1DF-2220-1541-B91F-7A38FEF088EB}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
-    <tableColumn id="330" xr3:uid="{A8E29F67-8667-8444-B1D5-24846E6A8080}" name="##### Caregiver I"/>
-    <tableColumn id="331" xr3:uid="{6B356D7D-C10C-194D-B24C-3F3F0C9A8435}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Sex&lt;/span&gt;14"/>
-    <tableColumn id="332" xr3:uid="{9DBA6618-1E25-774E-BA61-7B7282D63922}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
-    <tableColumn id="333" xr3:uid="{349EEF99-A5C5-D649-9E1B-90338715FA75}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
-    <tableColumn id="334" xr3:uid="{C4E377F4-E73C-1740-BDE3-7BA2CD2C721B}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
-    <tableColumn id="335" xr3:uid="{5D8CD3EF-BC71-E249-AEFD-DD17384D0E7B}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
-    <tableColumn id="336" xr3:uid="{89A67960-7967-414F-B194-37D5BDFAAED1}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
-    <tableColumn id="337" xr3:uid="{6CE9A9DA-6B2C-D240-B888-4FD5155D148A}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
-    <tableColumn id="338" xr3:uid="{62F5BDAA-208B-9144-8D33-219E219309DB}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
-    <tableColumn id="339" xr3:uid="{45921911-491A-6E41-9BB1-3DBBC116D143}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
-    <tableColumn id="340" xr3:uid="{EA925F27-9A47-0742-820C-E7F3339195CB}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
-    <tableColumn id="341" xr3:uid="{E3C47080-3917-F24D-A199-0EBCEC7BBE93}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
-    <tableColumn id="342" xr3:uid="{F887D173-39C9-1343-9BB8-4EF1F3061994}" name="##### Caregiver III"/>
-    <tableColumn id="343" xr3:uid="{1B82DD35-9172-E44C-A6EE-464D955B2C67}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Sex&lt;/span&gt;15"/>
-    <tableColumn id="344" xr3:uid="{A7134196-7729-D447-A65E-9D6A6ABA1C70}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
-    <tableColumn id="345" xr3:uid="{F09ACDE3-816B-A047-A148-0DB6BEE5ECF8}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
-    <tableColumn id="346" xr3:uid="{598DDA97-E8D8-D24D-B0E0-99ECE7FD2B6B}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
-    <tableColumn id="347" xr3:uid="{4DAB67E8-94A4-7742-B476-D13901AD1C3E}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
-    <tableColumn id="348" xr3:uid="{DA8F4236-7FB6-9F40-BC72-1FEC98D4D5EB}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
-    <tableColumn id="349" xr3:uid="{0B05B41B-1EA4-5E4A-B352-077B10E617F3}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
-    <tableColumn id="350" xr3:uid="{63F03AD1-467F-CE4E-B455-FEFE934738DB}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
-    <tableColumn id="351" xr3:uid="{6E7E0553-488C-A74D-B319-61B4BC3B696C}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
-    <tableColumn id="352" xr3:uid="{9FEA492B-198B-1746-A770-2C1E903F5221}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
-    <tableColumn id="353" xr3:uid="{D4E09853-73B0-7B4D-BBA9-5F77D51D8F98}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
-    <tableColumn id="354" xr3:uid="{88CE74F1-AD4E-F74F-A114-CA1A4A6835B1}" name="##### Learner I"/>
-    <tableColumn id="355" xr3:uid="{C1D57B73-2991-CE49-9188-71F474A54E7E}" name="&lt;span style=&quot;display:none&quot;&gt;row-Sex&lt;/span&gt;16"/>
-    <tableColumn id="356" xr3:uid="{E172E14D-F633-0345-B663-14C8F1A7CB33}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
-    <tableColumn id="357" xr3:uid="{01565C16-B614-5748-86AE-9D4C9A520762}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
-    <tableColumn id="358" xr3:uid="{5E52DE89-BFBA-3745-9D3A-6A7000DD68A1}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
-    <tableColumn id="359" xr3:uid="{62983F49-855D-2A49-BD04-AB968D9111D9}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
-    <tableColumn id="360" xr3:uid="{828B8790-88EB-944F-8C1E-3FD49B73331A}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
-    <tableColumn id="361" xr3:uid="{A0423107-9031-DA4A-8CC9-5981882E54BC}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
-    <tableColumn id="362" xr3:uid="{2CE877B4-61B9-EC41-9C62-5B30873DA633}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
-    <tableColumn id="363" xr3:uid="{0730FA3E-EC90-E847-90D2-E6E63F1AD405}" name="&lt;span style=&quot;display:none&quot;&gt;row-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
-    <tableColumn id="364" xr3:uid="{D3325582-C332-7144-B2DE-8C7ABB27374E}" name="&lt;span style=&quot;display:none&quot;&gt;row-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
-    <tableColumn id="365" xr3:uid="{3C5B2AF7-F558-1144-B0CA-C95CBB106249}" name="&lt;span style=&quot;display:none&quot;&gt;row-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
-    <tableColumn id="366" xr3:uid="{0CF05ECB-23F7-3D4A-AF0E-75C4724A5A78}" name="##### Learner II"/>
-    <tableColumn id="367" xr3:uid="{49826E7E-7D3A-264F-B794-7CD70B2F71C5}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Sex&lt;/span&gt;17"/>
-    <tableColumn id="368" xr3:uid="{9A9EED84-EFC4-874C-BDED-95F7B96DC22C}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
-    <tableColumn id="369" xr3:uid="{C807A5C3-3678-F64B-BE3E-C7AB4B79BF1B}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
-    <tableColumn id="370" xr3:uid="{A172AD87-A290-2D40-A801-E8604213DF8E}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
-    <tableColumn id="371" xr3:uid="{DBE23440-9743-3B4C-9663-0BB5317BA0BD}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
-    <tableColumn id="372" xr3:uid="{6BBCCC32-FB4E-264F-AC43-AA1B03701AB5}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
-    <tableColumn id="373" xr3:uid="{09AC9B81-F7A0-4D45-8495-15E1421AC760}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
-    <tableColumn id="374" xr3:uid="{3ADE6FF5-6693-C84C-A81B-7C3E61A39F00}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
-    <tableColumn id="375" xr3:uid="{E259EE65-6FF4-5D43-A857-C322D79D3123}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
-    <tableColumn id="376" xr3:uid="{21A195A8-6BEA-9F46-9055-7DBBB6E6A25C}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
-    <tableColumn id="377" xr3:uid="{DB02FAC4-CF66-A442-95B7-D8FC30574B97}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
-    <tableColumn id="378" xr3:uid="{F9BE2A69-021A-F942-B946-B082509B23B3}" name="Pillar 2: Did households report a shift in fair plate-sharing practices (specifically stopping the practice of young ones/girls eating last)?"/>
-    <tableColumn id="379" xr3:uid="{8B2D5118-585C-AA40-BEC5-D079FDB5D9E4}" name="Pillar 1: How directly did the school feeding protection and meal routines influence student presence this cycle?"/>
-    <tableColumn id="380" xr3:uid="{78F21182-27D2-2242-9D1F-5108494A0F8B}" name="**Registered Boys this week Attendance**"/>
-    <tableColumn id="381" xr3:uid="{E09AEFE2-CB8C-8443-9CE0-C81A787070A1}" name="**Boys**"/>
-    <tableColumn id="382" xr3:uid="{BF966A01-6781-1E42-ADBF-C257CEE2C185}" name="**Girls**"/>
-    <tableColumn id="383" xr3:uid="{1B3D9E94-C89E-2A4F-97EB-382B11FE4CB8}" name="##### Lower Primary (ECD-P2) Registered Boys this week Attendance"/>
-    <tableColumn id="384" xr3:uid="{058E9CD0-8604-3D44-BC30-848CC1A059C1}" name="&lt;span style=&quot;display:none&quot;&gt;row-Boys&lt;/span&gt;"/>
-    <tableColumn id="385" xr3:uid="{F4A0819C-7C73-E141-9F31-F4C8BE554A29}" name="&lt;span style=&quot;display:none&quot;&gt;row-Girls&lt;/span&gt;"/>
-    <tableColumn id="386" xr3:uid="{2BA1C280-71DE-374D-BB0F-BE200E5EA4F3}" name="##### Lower Primary (ECD-P2) Registered Girls this week Attendance"/>
-    <tableColumn id="387" xr3:uid="{85AD0BAA-A58C-1943-ACDF-B382D64C7435}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Boys&lt;/span&gt;"/>
-    <tableColumn id="388" xr3:uid="{F38DBA67-63F0-D340-B629-CD4F697E0994}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Girls&lt;/span&gt;"/>
-    <tableColumn id="389" xr3:uid="{730F0705-AF9A-624E-B7BB-DFE90B86FC36}" name="##### Middle Primary (P3-P4) Registered Boys this week Attendance"/>
-    <tableColumn id="390" xr3:uid="{4E6AEBCB-31FA-D94F-92C0-FF425E66086C}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Boys&lt;/span&gt;"/>
-    <tableColumn id="391" xr3:uid="{C3957CC4-B26D-B948-9703-E3B203534921}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Girls&lt;/span&gt;"/>
-    <tableColumn id="392" xr3:uid="{7FA60F63-45E8-B241-9BDF-D89E279CD65E}" name="##### Middle Primary (P3-P4) Registered Girls this week Attendance"/>
-    <tableColumn id="393" xr3:uid="{A6F3C32F-1A39-2443-A8B3-D06F16533ECB}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Boys&lt;/span&gt;"/>
-    <tableColumn id="394" xr3:uid="{8D24BC88-B0C8-DF45-ACF8-FF8BC017EEB4}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Girls&lt;/span&gt;"/>
-    <tableColumn id="395" xr3:uid="{B13958B2-AAE5-0843-B65E-F6E5437004A1}" name="##### Upper Primary (P5-P7) Registered Boys this week Attendance"/>
-    <tableColumn id="396" xr3:uid="{BEDDA644-A18D-474E-9A76-15279A340A35}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Boys&lt;/span&gt;"/>
-    <tableColumn id="397" xr3:uid="{0F4D7B18-68C6-4243-A30D-7473D8F961DE}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Girls&lt;/span&gt;"/>
-    <tableColumn id="398" xr3:uid="{3676DCF9-3886-5E45-BFF3-9C613386E171}" name="##### Upper Primary (P5-P7) Registered Girls this weekAttendance"/>
-    <tableColumn id="399" xr3:uid="{A402DC75-A472-B94E-9C5C-4220E9F7106A}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Boys&lt;/span&gt;"/>
-    <tableColumn id="400" xr3:uid="{1668E7FF-80F8-094B-8BC8-9579D4619992}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Girls&lt;/span&gt;"/>
-    <tableColumn id="401" xr3:uid="{DA12EF57-5DFE-4C44-9280-97E9E18B9B85}" name="Village / Catchment Demo Site"/>
-    <tableColumn id="402" xr3:uid="{DB2527D7-F091-B543-B8AA-F71B5F43C73E}" name="Who was on ground when this demo happened"/>
-    <tableColumn id="403" xr3:uid="{13903B93-C2A9-E94B-B8A1-1816DA8CFF07}" name="Name of VHT"/>
-    <tableColumn id="404" xr3:uid="{F0FAFC63-2740-DE4A-A814-17E08782CB57}" name="Were capacity-strengthening partners (e.g., UNAC, Afi) present and co-facilitating this community demonstration?"/>
-    <tableColumn id="405" xr3:uid="{FA77C2F1-33BD-0744-9BD7-59BB81C27FAD}" name="If yes, specify partner name"/>
-    <tableColumn id="406" xr3:uid="{C336E36E-59C2-254B-9D9D-F64D29AFB63A}" name="If yes, specify partner name/UNAC"/>
-    <tableColumn id="407" xr3:uid="{15799A46-940C-0843-9201-69BF361EFF74}" name="If yes, specify partner name/AFI"/>
-    <tableColumn id="408" xr3:uid="{65BC3A5B-459D-CE4B-ADF0-C56D930945B9}" name="If yes, specify partner name/Other"/>
-    <tableColumn id="409" xr3:uid="{880AA04D-D68C-2348-BBC7-8E811A52C8C6}" name="Specify18"/>
-    <tableColumn id="410" xr3:uid="{21B7F7F8-FEF6-2C46-B031-C71E1FD796AF}" name="Partner role observed"/>
-    <tableColumn id="411" xr3:uid="{E74E427E-E684-1D47-B9EA-5D85C9CF17F4}" name="Partner role observed/Co-facilitating clean cooking/gender dialogue"/>
-    <tableColumn id="412" xr3:uid="{60B9D2D0-573D-444A-A985-9352150C65EA}" name="Partner role observed/Mentoring local VHTs/Elders"/>
-    <tableColumn id="413" xr3:uid="{AB92E4B8-7C47-9D4C-8507-0B8555171D25}" name="Partner role observed/Observing for sustainability tracking"/>
-    <tableColumn id="414" xr3:uid="{D9D59B8D-05EC-084B-88CB-6C3800D5B5A0}" name="Partner role observed/Other "/>
-    <tableColumn id="415" xr3:uid="{B1A12E08-C2AF-634B-BEFA-A181F32772F5}" name="Specify19"/>
-    <tableColumn id="416" xr3:uid="{D7930498-2BB0-1E48-A505-57C5A328BB61}" name="**Participant headcount**"/>
-    <tableColumn id="417" xr3:uid="{DA6131C0-BCE6-3F44-87DF-E250003840A3}" name="**Male**20"/>
-    <tableColumn id="418" xr3:uid="{279900AA-FDA2-4D41-AB9F-EE53D47C7EF4}" name="**Female**21"/>
-    <tableColumn id="419" xr3:uid="{0E0857DB-5E90-1042-B0BF-E50335D03751}" name="##### Female Caregivers"/>
-    <tableColumn id="420" xr3:uid="{43BBA490-0EB0-4C41-9F1C-58E9072863BE}" name="&lt;span style=&quot;display:none&quot;&gt;row-Male&lt;/span&gt;22"/>
-    <tableColumn id="421" xr3:uid="{785A4C40-BE0B-5643-85E3-C31AA88BC1C3}" name="&lt;span style=&quot;display:none&quot;&gt;row-Female&lt;/span&gt;23"/>
-    <tableColumn id="422" xr3:uid="{AA1A44CC-E2FD-5E45-B26D-B8E2A6360399}" name="##### Male Fathers/Elders"/>
-    <tableColumn id="423" xr3:uid="{DC464029-05C3-4543-9E0D-BD2675859A12}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Male&lt;/span&gt;24"/>
-    <tableColumn id="424" xr3:uid="{CCE47534-63C2-5449-8689-1E777AF87C8D}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Female&lt;/span&gt;25"/>
-    <tableColumn id="425" xr3:uid="{7331296B-D0C9-CB40-97B9-0C4216F8B77E}" name="##### Male Children"/>
-    <tableColumn id="426" xr3:uid="{FE54AB76-D7B0-CA4C-AE83-1930E5387E75}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Male&lt;/span&gt;26"/>
-    <tableColumn id="427" xr3:uid="{603858D4-1699-BB41-8D95-4E01466F912D}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Female&lt;/span&gt;27"/>
-    <tableColumn id="428" xr3:uid="{6AC7EBED-B23E-2A45-A596-6794C8E029CD}" name="##### Female Children"/>
-    <tableColumn id="429" xr3:uid="{4F86605D-F406-0240-B3B7-59AACE0FCE2D}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Male&lt;/span&gt;28"/>
-    <tableColumn id="430" xr3:uid="{6A07A545-6A36-EE4C-8918-02202FF7A247}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Female&lt;/span&gt;29"/>
-    <tableColumn id="431" xr3:uid="{BA7F9846-1F81-334A-8009-7353383E9247}" name="##### Male PWDs"/>
-    <tableColumn id="432" xr3:uid="{02FE8884-7236-574E-8E3B-9858FB820E00}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Male&lt;/span&gt;30"/>
-    <tableColumn id="433" xr3:uid="{1EA4FFFB-E066-524C-A044-C76A33D6A672}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Female&lt;/span&gt;31"/>
-    <tableColumn id="434" xr3:uid="{115080D5-29E2-1847-BFBA-5AEC57F873C6}" name="##### Female PWDs"/>
-    <tableColumn id="435" xr3:uid="{B876A06B-428C-8041-BE1B-04EE97977FCA}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Male&lt;/span&gt;"/>
-    <tableColumn id="436" xr3:uid="{41B7CD24-A484-7D4D-87E9-281AC9258CB0}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Female&lt;/span&gt;"/>
-    <tableColumn id="437" xr3:uid="{4FFAA74D-F040-B146-AD41-B6906BBE3601}" name="Did caregivers cook and handle ingredients hands-on, or only observe?"/>
-    <tableColumn id="438" xr3:uid="{DEA7A9D4-3F42-4D47-9E2F-C1D9D71D81F3}" name="Was WFP Metu porridge demonstrated with additions of obtainable local staples      (e.g., wild greens like Eboo/Lokaka, cowpea leaves, roasted sesame/sorghum)?"/>
-    <tableColumn id="439" xr3:uid="{D6B22172-589F-B74E-BFCC-E637A8CF04CA}" name="What comments or reactions came from the spectators?"/>
-    <tableColumn id="440" xr3:uid="{41A75906-82BA-104E-8A18-4949879D1719}" name="Pilar 3: Was clean/smart cooking demonstrated to protect the environment and lead to better harvests?"/>
-    <tableColumn id="441" xr3:uid="{E7A5D097-9926-784C-A91A-DBC0D4E91DF7}" name="Observed community commitment to clean cooking practices:"/>
-    <tableColumn id="442" xr3:uid="{1F06DEA5-BC15-CF48-92A0-4DF88BB0E711}" name="Were all demonstrated foods sourced locally from seasonal gardens/markets?"/>
-    <tableColumn id="443" xr3:uid="{A381777E-0942-1D48-81EE-6A5E1521F2B1}" name="Which fuel-saving practices were demonstrated to the gathering?"/>
-    <tableColumn id="444" xr3:uid="{B79CB855-78C8-7746-ABA9-5760492E9753}" name="Which fuel-saving practices were demonstrated to the gathering?/Improved cookstove consuming less firewood"/>
-    <tableColumn id="445" xr3:uid="{D4CDC723-08FA-FC4B-A174-2DD9F1DF4073}" name="Which fuel-saving practices were demonstrated to the gathering?/Proper fuelwood pre-drying &amp; flame/airflow management"/>
-    <tableColumn id="446" xr3:uid="{61E394FC-5871-8449-8CA0-86AD48D10F9F}" name="Which fuel-saving practices were demonstrated to the gathering?/Retained heat cooking and pot covering to conserve fuel"/>
-    <tableColumn id="447" xr3:uid="{ACFFDA4C-0EFA-994F-919C-0E03BD2DEC93}" name="Which fuel-saving practices were demonstrated to the gathering?/Traditional 3-stone fire used (Non-compliant)"/>
-    <tableColumn id="448" xr3:uid="{9BD093DF-C4E6-DF47-8901-09596AAF57CF}" name="Conducted privately at the demo ground."/>
-    <tableColumn id="449" xr3:uid="{815002C0-4EA0-744C-8FBC-9EDB51F1AD02}" name="**Privately at the demonstration site.  Interview 2 to 3 attending caregivers right after the cooking demo**"/>
-    <tableColumn id="450" xr3:uid="{C85F57AD-F97F-D742-902C-92694DDD7DC6}" name="**What is most difficult or gets in the way of feeding your family well at home?**"/>
-    <tableColumn id="451" xr3:uid="{CED5106C-5C09-504A-9FEB-2D52BFCB5C19}" name="**Despite those difficulties, which feasible action can you realistically try at home?**"/>
-    <tableColumn id="452" xr3:uid="{FDFE6E50-D020-9D41-8388-048DB1754873}" name="**Caregiver Commitment Verdict**"/>
-    <tableColumn id="453" xr3:uid="{29E68C8B-E30A-6443-A530-FECA3531DE4B}" name="**Record their exact words; no personal names**"/>
-    <tableColumn id="454" xr3:uid="{91B0F36D-0CA7-DD46-9AB9-26E6E7632655}" name="**Sex**32"/>
-    <tableColumn id="455" xr3:uid="{4A1A6B41-FDA6-4042-9D62-828F1AD44498}" name="##### Caregiver 1"/>
-    <tableColumn id="456" xr3:uid="{057E634B-A5F1-A04A-AE26-4CB9A2024C1E}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;"/>
-    <tableColumn id="457" xr3:uid="{955A92BF-87C9-1F48-A96A-AB4A25ECCF96}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of cooking water"/>
-    <tableColumn id="458" xr3:uid="{025AED3A-4966-354B-AFD3-9113DF5BFB64}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of firewood"/>
-    <tableColumn id="459" xr3:uid="{52B170A6-2656-8549-8349-AE5DBE572605}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Food items missing in the local garden or market"/>
-    <tableColumn id="460" xr3:uid="{A972A0FE-632A-9949-95B6-2E38C95D7B54}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/lack of money"/>
-    <tableColumn id="461" xr3:uid="{A0D6B17D-2BE1-464D-841F-0F657551D0D6}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Heavy morning chores"/>
-    <tableColumn id="462" xr3:uid="{9FA729A8-F90F-A446-AE62-B54B5DE943DA}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Family or elder disagreement"/>
-    <tableColumn id="463" xr3:uid="{D73A05AF-F500-384C-B733-600425C720AB}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Nothing is difficult"/>
-    <tableColumn id="464" xr3:uid="{B700F713-9E91-5F45-B020-BFF5F7611337}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite those difficulties, which feasible action can you realistically try at home?&lt;/span&gt;"/>
-    <tableColumn id="465" xr3:uid="{421233FF-7586-C94E-9675-6804D00A57F1}" name="&lt;span style=&quot;display:none&quot;&gt;row-Caregiver Commitment Verdict&lt;/span&gt;"/>
-    <tableColumn id="466" xr3:uid="{0F0563D0-7970-054E-AE78-E1F6476EB33B}" name="&lt;span style=&quot;display:none&quot;&gt;row-Record their exact words; no personal names&lt;/span&gt;"/>
-    <tableColumn id="467" xr3:uid="{8CA55713-E371-3640-9066-DA10C0E5253D}" name="&lt;span style=&quot;display:none&quot;&gt;row-Sex&lt;/span&gt;33"/>
-    <tableColumn id="468" xr3:uid="{E94B6233-6C96-2441-91A1-6AA1C99149F9}" name="##### Caregiver 3"/>
-    <tableColumn id="469" xr3:uid="{8BA432C0-4D59-D64E-A4F0-3E429D1512F9}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;"/>
-    <tableColumn id="470" xr3:uid="{003482D1-190B-8F4D-A499-2D237C5E5632}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of cooking water"/>
-    <tableColumn id="471" xr3:uid="{C303CAB4-7FCE-A440-A788-DCBD81AFB8C4}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of firewood"/>
-    <tableColumn id="472" xr3:uid="{1AA1525D-3D94-394D-A324-BE0A9D602276}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Food items missing in the local garden or market"/>
-    <tableColumn id="473" xr3:uid="{8050423B-8ACC-1B40-BA0F-1A7E74F08BDB}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/lack of money"/>
-    <tableColumn id="474" xr3:uid="{6FD9B0D9-665F-2D48-8D94-46C988FBAFE9}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Heavy morning chores"/>
-    <tableColumn id="475" xr3:uid="{632D8D7B-B103-5749-A670-65B384BAE44D}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Family or elder disagreement"/>
-    <tableColumn id="476" xr3:uid="{DD2AFFDB-A39C-0344-8F3F-E3AD5327061D}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Nothing is difficult"/>
-    <tableColumn id="477" xr3:uid="{11BBBB2B-BF79-324E-AD57-6804FA9817ED}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Despite those difficulties, which feasible action can you realistically try at home?&lt;/span&gt;"/>
-    <tableColumn id="478" xr3:uid="{93A21771-3DED-BD49-B697-BCB423165A09}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Caregiver Commitment Verdict&lt;/span&gt;"/>
-    <tableColumn id="479" xr3:uid="{326862D2-FBF7-E946-8297-3C4E37C27F8C}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Record their exact words; no personal names&lt;/span&gt;"/>
-    <tableColumn id="480" xr3:uid="{73342FE1-3EF1-6C4D-A1D5-1AE16F51C8FE}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Sex&lt;/span&gt;34"/>
-    <tableColumn id="481" xr3:uid="{1A7EEFE4-769E-D546-8F2B-E08347B28785}" name="##### Caregiver 2"/>
-    <tableColumn id="482" xr3:uid="{A2154D6B-4567-0942-ACBF-FA7ED42E4E87}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;"/>
-    <tableColumn id="483" xr3:uid="{88704F69-295E-CA4B-A35F-D5F499B488A8}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of cooking water"/>
-    <tableColumn id="484" xr3:uid="{7A53BC7F-7408-A64A-9AB8-5A20DE86988D}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of firewood"/>
-    <tableColumn id="485" xr3:uid="{4E3A7430-164A-7B4C-AF65-04E20C2F1FEC}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Food items missing in the local garden or market"/>
-    <tableColumn id="486" xr3:uid="{553E992D-B3C6-D841-810E-1A872AD08680}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/lack of money"/>
-    <tableColumn id="487" xr3:uid="{19929B94-807C-FA4A-A8CC-06BE2F28BE61}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Heavy morning chores"/>
-    <tableColumn id="488" xr3:uid="{1070F61C-D5A9-824F-AC96-E26E71937EBB}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Family or elder disagreement"/>
-    <tableColumn id="489" xr3:uid="{91EE5EA6-12E9-B04F-BEAF-3AC1BE6C3C00}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Nothing is difficult"/>
-    <tableColumn id="490" xr3:uid="{72198C9D-597C-E846-B3CD-3B4A789018DB}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite those difficulties, which feasible action can you realistically try at home?&lt;/span&gt;"/>
-    <tableColumn id="491" xr3:uid="{EF60A24C-5D61-4647-97C2-C87883ABAB7F}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Caregiver Commitment Verdict&lt;/span&gt;"/>
-    <tableColumn id="492" xr3:uid="{E16D293E-70E4-B144-91EA-FA04E52B15A7}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Record their exact words; no personal names&lt;/span&gt;"/>
-    <tableColumn id="493" xr3:uid="{C7B8E81C-BB87-8547-98D3-B85927B0A925}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Sex&lt;/span&gt;35"/>
-    <tableColumn id="494" xr3:uid="{24252B5A-931B-2E45-8B68-6BA232326CEB}" name="Did the structured gender chore and fair-sharing discussion take place?"/>
-    <tableColumn id="495" xr3:uid="{68B5845F-8D3E-2443-89FD-779AA51C6980}" name="Were gender dialogues led by senior women, senior men, and VHTs successfully executed?"/>
-    <tableColumn id="496" xr3:uid="{FB56AF65-E271-2A46-94BC-9071226C9CC0}" name="Male Participation Level in Gender, Chore &amp; Resource Discussions"/>
-    <tableColumn id="497" xr3:uid="{F49466C0-F719-E344-9751-6ED4A3B8F9CA}" name="Community Accountability &amp; Grievance Promotion"/>
-    <tableColumn id="498" xr3:uid="{B921394E-D83F-5A42-AB33-0A93E92D1306}" name="Group response: In your household who is served first and who eats last?"/>
-    <tableColumn id="499" xr3:uid="{BAA1B846-EFE7-2B4F-A9DD-2DE58E2F1EBA}" name="Group response: What would need to change for the youngest child to be served first?"/>
-    <tableColumn id="500" xr3:uid="{A40C09EA-5F54-1F42-B126-6540599803CE}" name="Community Accountability &amp; WFP Hotline Feedback Promoted?"/>
-    <tableColumn id="501" xr3:uid="{6CF85ADA-7C9C-CD4D-AB1B-FD5860D24C71}" name="Community Agreement and Commitments made in their own words"/>
-    <tableColumn id="502" xr3:uid="{7920551A-DA20-C846-B6EE-39CD6A253911}" name="Named Community Body / Elders Responsible for Follow-Up"/>
-    <tableColumn id="503" xr3:uid="{0EB1926F-7718-5E4F-A1D0-FE198C626532}" name="Main debate point or objection raised before consensus was reached"/>
-    <tableColumn id="504" xr3:uid="{07AD3755-31F6-6B49-A96D-46A80E54847A}" name="Were community media highlights or clean cooking/gender dialogue photos captured for social media PR reporting?"/>
-    <tableColumn id="505" xr3:uid="{55F46251-0799-B243-BC04-E768222908E8}" name="Provide a short description of the captured community highlight"/>
-    <tableColumn id="506" xr3:uid="{FF44A4A5-ECB7-D44C-9F64-24A9ED0065B3}" name="Did community members mention or give feedback on the campaign radio broadcasts during the gathering?"/>
-    <tableColumn id="507" xr3:uid="{8F1FF92F-4578-8E4E-8069-1BA9EFBCD195}" name="Summary of community radio feedback (if any)"/>
-    <tableColumn id="508" xr3:uid="{DB134C52-623C-A84C-AF72-ED73D77427F8}" name="Storyteller names and age"/>
-    <tableColumn id="509" xr3:uid="{6B45C29B-2C7A-594B-AB33-6D9E0DCF3479}" name="Storyteller Role"/>
-    <tableColumn id="510" xr3:uid="{6BE1328F-A764-8347-9E63-E6A48448D877}" name="Record the storyteller's actual words; do not reinterpret "/>
-    <tableColumn id="511" xr3:uid="{EAC6B0D0-B8C3-D44D-B3BF-4D51BA60889A}" name="Describe the situation before the campaign:    What was the normal household diet, daily chore burden (water/firewood),    or school attendance pattern?"/>
-    <tableColumn id="512" xr3:uid="{2B076E9D-6CFC-EB49-99E9-5B5C9C4E217D}" name="What specific campaign event, activity, chart, or discussion caused the shift?"/>
-    <tableColumn id="513" xr3:uid="{A37FA151-486C-1743-A146-4A795E7F3E83}" name="What specific campaign event, activity, chart, or discussion caused the shift?36"/>
-    <tableColumn id="514" xr3:uid="{E58E5509-0937-B24E-88F7-EB4381AF1CC6}" name="What was physically done differently at home, class, or community after attending?"/>
-    <tableColumn id="515" xr3:uid="{8DD023AD-C893-754B-A6C0-BC567A488883}" name="What was physically done differently at home, class, or community after attending the nutribus activitiies"/>
-    <tableColumn id="516" xr3:uid="{9468CFF2-C9DA-D948-B0E5-E1F7D5703041}" name="Why is this change significant to you?"/>
-    <tableColumn id="517" xr3:uid="{D72E9639-2B18-9D49-A3A0-83E5DAC85FEE}" name="Verifiable Physical Evidence Sighted by Collector"/>
-    <tableColumn id="518" xr3:uid="{14D0F5C7-0C13-184D-8626-51FCB274E2E2}" name="Verifiable Physical Evidence Sighted by Collector/Completed NutriChart sighted"/>
-    <tableColumn id="519" xr3:uid="{BCE2308A-05D0-3A45-9A9E-CA4A2BBFABDE}" name="Verifiable Physical Evidence Sighted by Collector/School register shows consistent female attendance"/>
-    <tableColumn id="520" xr3:uid="{59271F7A-AB24-5A40-9A42-EBA982D09C5D}" name="Verifiable Physical Evidence Sighted by Collector/Cooking pot shows Metu fortified with obtainable local greens"/>
-    <tableColumn id="521" xr3:uid="{35FEACEE-AD1E-E74A-A7CF-F83706A90798}" name="Verifiable Physical Evidence Sighted by Collector/Kitchen displays improved cookstove using less firewood"/>
-    <tableColumn id="522" xr3:uid="{2369C0D8-C8E4-5B40-9EB4-38085468F31B}" name="Verifiable Physical Evidence Sighted by Collector/None sighted"/>
-    <tableColumn id="523" xr3:uid="{6AA2836A-0F3F-4B4C-A4C5-5ED68BE80613}" name="What session of the week is this"/>
-    <tableColumn id="524" xr3:uid="{834BAA6E-DE77-9343-BCB9-45DD7B2CEAC8}" name="What session of the week is this/Session one of the week"/>
-    <tableColumn id="525" xr3:uid="{E028087A-6DC0-DB4E-AE34-646C309E9E59}" name="What session of the week is this/Session two of the week"/>
-    <tableColumn id="526" xr3:uid="{629A021E-0B51-9B43-A0BD-45CA1257AF8E}" name="Club Patron Name"/>
-    <tableColumn id="527" xr3:uid="{F00578AB-D87C-5B4F-BD26-C58D9BC0FCA5}" name="Total  male membership of the nutriclub"/>
-    <tableColumn id="528" xr3:uid="{1BC05A79-896F-2A48-8D3A-F63A39834E57}" name="Total  female membership of the nutriclub"/>
-    <tableColumn id="529" xr3:uid="{75757D2A-E180-844A-8CB4-E748F09A770E}" name="Designated Meeting Place on Compound"/>
-    <tableColumn id="530" xr3:uid="{0AA50A64-CB53-434E-8F59-D52B591324F0}" name="Date session was conducted"/>
-    <tableColumn id="531" xr3:uid="{7F239D4A-99B5-C44C-87D2-C59720D08C7D}" name="start time"/>
-    <tableColumn id="532" xr3:uid="{1B98F0A5-C08A-9B47-9AD3-0636D44356D1}" name="End time"/>
-    <tableColumn id="533" xr3:uid="{751016E5-D836-2D4E-90F4-4C0CA8022DF4}" name="Boys Present"/>
-    <tableColumn id="534" xr3:uid="{75F70004-603C-BE45-BCFB-7F3C8CC0A0D3}" name="Girls Present"/>
-    <tableColumn id="535" xr3:uid="{2F85AD79-072B-834B-B567-EEDDED08169D}" name="Male learners with Disabilities"/>
-    <tableColumn id="536" xr3:uid="{7AC55962-C969-964A-BDC5-3D5E2B93FC64}" name="Female learners with Disabilities"/>
-    <tableColumn id="537" xr3:uid="{118DC67C-7127-644F-BBD6-DB61C5E17358}" name="Practical Activity Delivered"/>
-    <tableColumn id="538" xr3:uid="{2B0695AC-0DC7-1148-8EB0-D6C5A766C08B}" name="Practical Activity Delivered/Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat)"/>
-    <tableColumn id="539" xr3:uid="{638A3AC0-5CD8-214B-B76B-E8F5B3D168E3}" name="Practical Activity Delivered/Climate-Smart Living: Firewood-saving cooking methods &amp; moving from 3-stone fires"/>
-    <tableColumn id="540" xr3:uid="{670067AA-D264-2845-93B4-24F548DCE600}" name="Practical Activity Delivered/Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing"/>
-    <tableColumn id="541" xr3:uid="{383AE4E3-A0D1-2B48-897F-7F129026E2B8}" name="Practical Activity Delivered/Gender Chore Rebalancing: Boys sharing morning water/firewood chores"/>
-    <tableColumn id="542" xr3:uid="{E54C44B2-8AD7-774A-8DCE-AC4160CA3FEA}" name="Practical Activity Delivered/Peer Attendance Tracing: Checking and following up chronically absent classmates"/>
-    <tableColumn id="543" xr3:uid="{83A90B45-47C7-2448-B686-A6DD81F6B984}" name="What specific feasible food or chore action were members asked to try at home?"/>
-    <tableColumn id="544" xr3:uid="{027969E6-322C-9943-B553-8E4448BAE68F}" name="Date session II was conducted"/>
-    <tableColumn id="545" xr3:uid="{83AE75FD-0EF3-7948-8E61-DC15EE2872C3}" name="Start"/>
-    <tableColumn id="546" xr3:uid="{B581CEE0-3B42-894A-837C-1BCAF41E4EAC}" name="End"/>
-    <tableColumn id="547" xr3:uid="{78FEBA50-A5C5-C74A-A7D1-719282D23B5E}" name="Boys"/>
-    <tableColumn id="548" xr3:uid="{322CD615-AE2C-ED45-B439-6976CB0B61A0}" name="Girls"/>
-    <tableColumn id="549" xr3:uid="{90F02817-FD5A-4647-8F82-083ECAC4AC3A}" name="female learners PWDs"/>
-    <tableColumn id="550" xr3:uid="{FF32D2FD-5E3B-5C47-87C9-4CA787635002}" name="male leaders with PWDs"/>
-    <tableColumn id="551" xr3:uid="{7BAE1B5A-8469-7D43-B159-42091A454B50}" name="Practical Activity Delivered37"/>
-    <tableColumn id="552" xr3:uid="{71978859-A044-B54D-B4C5-2393922645EF}" name="Practical Activity Delivered/Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat)38"/>
-    <tableColumn id="553" xr3:uid="{BED07455-4303-7248-85C6-7970DDBF90EA}" name="Practical Activity Delivered/Climate-Smart Living: Firewood-saving cooking methods &amp; moving from 3-stone fires39"/>
-    <tableColumn id="554" xr3:uid="{01BFBDED-A4A5-3549-A338-770E3C6600D5}" name="Practical Activity Delivered/Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing40"/>
-    <tableColumn id="555" xr3:uid="{2DB9BA5B-36EF-6046-9A6A-A892CBBE2111}" name="Practical Activity Delivered/Gender Chore Rebalancing: Boys sharing morning water/firewood chores41"/>
-    <tableColumn id="556" xr3:uid="{1DE27230-0304-A543-9A5E-0AE34B6C9AEC}" name="Practical Activity Delivered/Peer Attendance Tracing: Checking and following up chronically absent classmates42"/>
-    <tableColumn id="557" xr3:uid="{B95F7A22-A310-A149-AA91-67FA9FF1FB80}" name="Did members report trying the home action with parents?"/>
-    <tableColumn id="558" xr3:uid="{0CD7FCBC-65C2-E74C-B644-40023719B931}" name="Date Assembly Nutri-Moment was delivered"/>
-    <tableColumn id="559" xr3:uid="{376B4AA3-8D04-3549-8D7D-9F6C1DEB6D35}" name="Core Message Shared with Whole School"/>
-    <tableColumn id="560" xr3:uid="{8C2E6001-F27B-DC4D-8AB9-2813C9D217C1}" name="Delivered By"/>
-    <tableColumn id="561" xr3:uid="{571716CC-4C2F-3D47-A7D9-821D65514320}" name="start43"/>
-    <tableColumn id="562" xr3:uid="{EF1A69D8-D509-7341-82D5-A322254404CC}" name="end44"/>
-    <tableColumn id="563" xr3:uid="{BE9BB600-9D57-FE47-88E3-31D7909B141F}" name="Activity type"/>
-    <tableColumn id="564" xr3:uid="{E8CA202C-A529-344E-829C-BC135AAA86F7}" name="Type of session"/>
-    <tableColumn id="565" xr3:uid="{D0522797-89F6-634D-A75C-5AD538F3713C}" name="Which visit is this?"/>
-    <tableColumn id="566" xr3:uid="{137DF9A7-2CF7-8843-9655-D41636890B50}" name="Headteacher or Deputy Present"/>
-    <tableColumn id="567" xr3:uid="{E4F21ACA-A745-114F-B387-8E4D6F4305B9}" name="Which planned contact is being conducted today?"/>
-    <tableColumn id="568" xr3:uid="{98DFD8AF-8A1A-9F49-8538-A071EFA423D9}" name="Which age group was in this session?"/>
-    <tableColumn id="569" xr3:uid="{B2E10632-C61F-814C-B9D4-AA6BE40F2B85}" name="Number of designated Club Patrons oriented"/>
-    <tableColumn id="570" xr3:uid="{8DA0ACD3-7A79-AA42-ABFB-18B7090A610A}" name="Administered by the District Coordinator immediately after each age-band session observed. Each session observed is submitted as its own flat record"/>
-    <tableColumn id="571" xr3:uid="{CDA317BF-63D3-F345-A6A4-4B186B562DF8}" name="Which learner age band is participating in this specific session?"/>
-    <tableColumn id="572" xr3:uid="{BE92FC42-97E0-504A-BDB1-C2A8FCC1BD29}" name="Number of boys present"/>
-    <tableColumn id="573" xr3:uid="{3CA394CE-3F4E-6F4C-BE97-3B3DDD7B8DC2}" name="Did the school team and catchment VHTs sit together to agree on the schedule?"/>
-    <tableColumn id="574" xr3:uid="{D2E9C5EE-82F8-3147-9F28-314B11B70B5C}" name="Number of girls present"/>
-    <tableColumn id="575" xr3:uid="{15713FF4-64D5-004D-A46A-46640FB9DBAD}" name="Is a formal Nutri Club established with a named patron?"/>
-    <tableColumn id="576" xr3:uid="{7C437AF8-BDA3-EE48-8963-F1BE7AD90ACE}" name="Number of parents or adult community members present"/>
-    <tableColumn id="577" xr3:uid="{726C697A-3400-8848-AD63-BB91B0D2CE53}" name="Tick all activities that were delivered during this session"/>
-    <tableColumn id="578" xr3:uid="{758E388B-610E-8C42-BBB1-4118B327E518}" name="Tick all activities that were delivered during this session/Song and movement activity led"/>
-    <tableColumn id="579" xr3:uid="{3CFD5536-4224-564D-92F2-6A63DAE75E2E}" name="Tick all activities that were delivered during this session/Food sorting or matching game practiced"/>
-    <tableColumn id="580" xr3:uid="{37C4D8A8-C4BD-F541-B6A5-F88FAB6090BC}" name="Tick all activities that were delivered during this session/Adere calabash built together with the group"/>
-    <tableColumn id="581" xr3:uid="{276B28C8-BF2F-6147-B9C9-D96EAFCA91FB}" name="Tick all activities that were delivered during this session/Substitution game played (alternative food offered every time)"/>
-    <tableColumn id="582" xr3:uid="{C77D1A68-E7ED-F846-B466-E37B7C4E7C6D}" name="Tick all activities that were delivered during this session/Fair sharing round discussed (sharing meals and chores fairly)"/>
-    <tableColumn id="583" xr3:uid="{E475154B-3D13-3E45-8E92-FB17D9B91099}" name="Tick all activities that were delivered during this session/Learners actively moved, sorted, touched materials, or spoke (not just watching)"/>
-    <tableColumn id="584" xr3:uid="{CDBBF927-5153-7443-AD29-08D38CA798EB}" name="Designated Club Meeting Day(s) each week"/>
-    <tableColumn id="585" xr3:uid="{4C434B0B-FA46-6C4A-A2A8-C26A4F0DAF06}" name="Designated Club Meeting Day(s) each week/Monday"/>
-    <tableColumn id="586" xr3:uid="{162CD29C-160A-2444-B344-5F37813363C1}" name="Designated Club Meeting Day(s) each week/Tuesday"/>
-    <tableColumn id="587" xr3:uid="{4E7452C7-7158-EF42-8972-247AEDA314B2}" name="Designated Club Meeting Day(s) each week/Wednesday"/>
-    <tableColumn id="588" xr3:uid="{116FE33E-B3AB-AA43-AB3B-8F1232682C7B}" name="Designated Club Meeting Day(s) each week/Thursday"/>
-    <tableColumn id="589" xr3:uid="{0EC2DB8C-8AD9-6548-A6C1-646C51CE79D8}" name="Designated Club Meeting Day(s) each week/Friday"/>
-    <tableColumn id="590" xr3:uid="{DD57A600-0EFD-954F-B384-903217DD77A3}" name="Number of children with identified disabilities present"/>
-    <tableColumn id="591" xr3:uid="{26B2C48F-691D-054B-A301-231F4895318D}" name="Designated Weekly Meeting Time"/>
-    <tableColumn id="592" xr3:uid="{953A2301-6632-9247-ADB0-705458861BD0}" name="Designated Weekly Meeting Time/Morning before class"/>
-    <tableColumn id="593" xr3:uid="{EF052011-0566-1A45-AE90-5507686737F0}" name="Designated Weekly Meeting Time/Lunch / Midday break"/>
-    <tableColumn id="594" xr3:uid="{78E4947B-EE2F-A349-BA47-4BC0B2A52026}" name="Designated Weekly Meeting Time/After school hours"/>
-    <tableColumn id="595" xr3:uid="{5543139B-0188-204A-AA14-81D08D3D6981}" name="Did learners complete the food sorting or matching activity?"/>
-    <tableColumn id="596" xr3:uid="{030860A2-01FD-8948-9472-F9AAD44FD74F}" name="Stand at the side. Tick each activity delivered by the facilitator"/>
-    <tableColumn id="597" xr3:uid="{F31638B0-87D2-4440-A9E5-121E620BC4F5}" name="Did the headteacher commit to a weekly whole-school assembly nutrition message?"/>
-    <tableColumn id="598" xr3:uid="{546FBEDA-3F44-C647-9108-3855ADA1E67D}" name="Was the Adere calabash built hands-on with the participants?"/>
-    <tableColumn id="599" xr3:uid="{C12E2F1F-854C-8947-AA82-5E5F3AA4565F}" name="Fixed day for the weekly Nutri-Moment"/>
-    <tableColumn id="600" xr3:uid="{853D5995-011A-974F-9AF6-B56A945F64BE}" name="Was the substitution round completed with a feasible local substitute offered?"/>
-    <tableColumn id="601" xr3:uid="{0C0D4EA8-319B-8449-BB98-D6600D531209}" name="Pull aside 5 individual participants (aim for 3 Teachers and 2 VHTs, balanced by gender)"/>
-    <tableColumn id="602" xr3:uid="{DE60BEDB-2F12-7A46-871B-085A0D300B81}" name="Was a signed 4-week school work plan completed and submitted?"/>
-    <tableColumn id="603" xr3:uid="{8652E2E9-7956-C741-86FC-A83CD84C7E42}" name="Was the fair sharing round delivered (fair meal serving and morning chores)?"/>
-    <tableColumn id="604" xr3:uid="{B65B3105-903F-0143-9E9B-60F3A5E2A538}" name="To be filled by Teacher Patron twice every week after each club activity"/>
-    <tableColumn id="605" xr3:uid="{98470653-1BF4-CD4E-B191-127D88464C2C}" name="Did the school teacher lead this session without the road crew?"/>
-    <tableColumn id="606" xr3:uid="{FD3BF3D7-0C64-454E-BA0F-41726B9ACF95}" name="**iNDIVIDUAL TEACH-BACK CHECKS**"/>
-    <tableColumn id="607" xr3:uid="{FCC66418-968A-A241-94CA-4896A0551A58}" name="Contact Number"/>
-    <tableColumn id="608" xr3:uid="{9E0CFAAF-5A56-C64F-B101-9AF4E37F30E8}" name="**Participant**"/>
-    <tableColumn id="609" xr3:uid="{EDF8BB68-6FA2-6E49-B391-E68AEB1C06DE}" name="**Quoted phrase used by the participants during teach-back**"/>
-    <tableColumn id="610" xr3:uid="{F7A812D0-D33B-934C-BFF4-3E8CC3C4C905}" name="##### First Learner (Child 1) "/>
-    <tableColumn id="611" xr3:uid="{20B259C0-F3B0-4741-83D5-1A524CAC4349}" name="&lt;span style=&quot;display:none&quot;&gt;row-Participant&lt;/span&gt;"/>
-    <tableColumn id="612" xr3:uid="{62DE719B-D7DB-B14A-AAEA-E6E7FD565803}" name="Learners with disabilities participating"/>
-    <tableColumn id="613" xr3:uid="{1855E198-D5DB-3D4B-83F2-3A915D308D5D}" name="&lt;span style=&quot;display:none&quot;&gt;row-Quoted phrase used by the participants during teach-back&lt;/span&gt;"/>
-    <tableColumn id="614" xr3:uid="{43B8B546-AAE1-B545-9EE4-962CF8ED8D50}" name="Session Theme / Activity Completed"/>
-    <tableColumn id="615" xr3:uid="{35ACA737-4775-8247-BB6F-A11868F1936A}" name="Session Theme / Activity Completed/Food sorting &amp; matching game using local foods"/>
-    <tableColumn id="616" xr3:uid="{7F965FE0-B2AC-6541-85B7-1D6C1EC1EBC4}" name="Session Theme / Activity Completed/Adere calabash balanced meal discussion"/>
-    <tableColumn id="617" xr3:uid="{4759CB57-4B1A-594C-B74B-C65567FE1B07}" name="Session Theme / Activity Completed/Local recipe substitution challenge"/>
-    <tableColumn id="618" xr3:uid="{1A3A3408-0E14-FC46-9020-364F5FDA24B8}" name="Session Theme / Activity Completed/Fair food serving &amp; morning chore balance dialogue"/>
-    <tableColumn id="619" xr3:uid="{CBA78BFC-ED90-1C4E-A220-52714F311AF9}" name="Session Theme / Activity Completed/Peer-to-peer tracing for absent learners"/>
-    <tableColumn id="620" xr3:uid="{7860089A-31F2-EC4D-A443-8FED7285A463}" name="##### Second Learner (Child 2)"/>
-    <tableColumn id="621" xr3:uid="{38868145-6FF0-3C40-8F47-B62B144C9D2B}" name="What specific food or chore action were members asked to try at home?"/>
-    <tableColumn id="622" xr3:uid="{49B2464E-C141-9E46-9011-7C9A0E595E82}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Participant&lt;/span&gt;"/>
-    <tableColumn id="623" xr3:uid="{315529F9-4676-764A-9577-C6DAF84B3D75}" name="Did learners report back on their home trials?"/>
-    <tableColumn id="624" xr3:uid="{2136C4C8-236B-DD42-A6C8-018DFE738FA4}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Quoted phrase used by the participants during teach-back&lt;/span&gt;"/>
-    <tableColumn id="625" xr3:uid="{3806B439-C6BE-E248-A448-5B7EB7409F3A}" name="More detailed explanation about home trials"/>
-    <tableColumn id="626" xr3:uid="{FA70251D-C9AD-B64A-9F53-67771537833D}" name="##### First Adult (Caregiver 1)"/>
-    <tableColumn id="627" xr3:uid="{76295D21-49B5-6D4E-9DFC-136B9DDB5B78}" name="Did the school hold a nutri-moment "/>
-    <tableColumn id="628" xr3:uid="{21E53DC4-20F5-B141-A4EF-F6F7FE650FA6}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Participant&lt;/span&gt;"/>
-    <tableColumn id="629" xr3:uid="{AAD7B705-7DA0-4C41-834D-0C1436549E5A}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Quoted phrase used by the participants during teach-back&lt;/span&gt;"/>
-    <tableColumn id="630" xr3:uid="{96B4E005-5C0A-F64D-BF9D-EEAFB15903B3}" name="Core message delivered to whole school"/>
-    <tableColumn id="631" xr3:uid="{F8BF78BC-614E-534C-B06E-4901ACDEE9A3}" name="##### Second Adult (Caregiver 2)"/>
-    <tableColumn id="632" xr3:uid="{59331D85-F8F5-7746-B173-38E3563CC4E3}" name="It was delivered by"/>
-    <tableColumn id="633" xr3:uid="{C9C854C7-DF3B-A242-BDC0-2A78228E5AFB}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Participant&lt;/span&gt;"/>
-    <tableColumn id="634" xr3:uid="{8CB20AB5-8A42-DA45-A02F-F3DF7A41C1B1}" name="Which planned visit is being conducted today?"/>
-    <tableColumn id="635" xr3:uid="{91EC0102-EEFF-A943-B726-AB6A5A36745B}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Quoted phrase used by the participants during teach-back&lt;/span&gt;"/>
-    <tableColumn id="636" xr3:uid="{F896D22B-C9E8-934C-90FC-A307038369C4}" name="Has the school formally set up the Nutri Club?"/>
-    <tableColumn id="637" xr3:uid="{AB7DEDA5-E9C1-3046-AFB4-482966BE5D46}" name="One key success or operational issue observed in this session"/>
-    <tableColumn id="638" xr3:uid="{8DF0716F-5FCE-834E-BA8C-B2F56C5E4666}" name="Is there a designated teacher patron active on the compound?"/>
-    <tableColumn id="639" xr3:uid="{E3E50B7E-62AD-F14A-97A0-2C1F61645874}" name="Total Nutri charts handed out"/>
-    <tableColumn id="640" xr3:uid="{60076818-9C04-774D-B41B-5A032A497AA8}" name="Agreed meeting place on compound"/>
-    <tableColumn id="641" xr3:uid="{179CF4E4-8D2D-6D43-B038-30F0A5A80AC5}" name="Total Nutri charts returned by learners"/>
-    <tableColumn id="642" xr3:uid="{2E2B84E1-5FA2-A640-B3F2-9601420CB455}" name="Total take-home NutriCharts / cards handed over"/>
-    <tableColumn id="643" xr3:uid="{6D15D65C-0023-7C4F-AD22-0178BCC7E1F6}" name="How many returned charts were completed together with an adult?"/>
-    <tableColumn id="644" xr3:uid="{7B2F5774-BC54-F845-B40D-A3C1609FBB79}" name="Did the coordinator demonstrate how learners should use them at home with parents?"/>
-    <tableColumn id="645" xr3:uid="{46FB4AEA-6AC7-0B46-BA02-10BB96F22793}" name="What did most families report about trying the home action?"/>
-    <tableColumn id="646" xr3:uid="{FCC9CFCA-2978-E840-A948-DE478BE01292}" name="Classes receiving materials today"/>
-    <tableColumn id="647" xr3:uid="{A73F34A0-1B83-184D-9D2C-67BECBCFEF25}" name="What was the biggest reason reported by families who struggled?"/>
-    <tableColumn id="648" xr3:uid="{6BB251DA-0F1B-3F48-89FD-53CC15A9C59C}" name="Age Band Participating in this Session"/>
-    <tableColumn id="649" xr3:uid="{E9676F68-4711-2F4A-9B9E-20D56E888571}" name="Does the school Nutri Club have an active teacher in charge and a meeting place?"/>
-    <tableColumn id="650" xr3:uid="{D50A340B-D7FA-9D40-BFCB-262CEAEBFBEC}" name="The action the school promised in their own words"/>
-    <tableColumn id="651" xr3:uid="{40BDD23B-F1FD-FC47-8204-B752293450E8}" name="male teachers present"/>
-    <tableColumn id="652" xr3:uid="{EF54FD03-C8DC-AB4B-B546-C775A156622E}" name="Tick every quality standard met by this commitment"/>
-    <tableColumn id="653" xr3:uid="{EC8DE3AB-0FF9-D64F-9814-63AD8B3FEA4E}" name="Tick every quality standard met by this commitment/The action is clear and specific"/>
-    <tableColumn id="654" xr3:uid="{561F1A56-8B54-1643-811C-C9CC29217B27}" name="Tick every quality standard met by this commitment/A specific teacher or staff member is named to lead it"/>
-    <tableColumn id="655" xr3:uid="{D00DB10D-254D-2649-B5FB-767EB82B1595}" name="Tick every quality standard met by this commitment/It can be finished within four weeks"/>
-    <tableColumn id="656" xr3:uid="{2FEBF22F-E3D9-5E4A-BE2C-56752B66B2D2}" name="Tick every quality standard met by this commitment/It mentions food, school snacks, or local crops"/>
-    <tableColumn id="657" xr3:uid="{ADC74742-FD10-2B47-9D66-BED86F8D0A83}" name="Tick every quality standard met by this commitment/It includes an action to keep children in school"/>
-    <tableColumn id="658" xr3:uid="{0D8F4936-76F6-4648-BD13-E3949B9CCA93}" name="Tick every quality standard met by this commitment/It includes fair sharing for both boys and girls"/>
-    <tableColumn id="659" xr3:uid="{CB0E7422-2264-4345-A25D-687A07755686}" name="Tick every quality standard met by this commitment/It states what the school will do if a child stops coming"/>
-    <tableColumn id="660" xr3:uid="{D9883FBE-B21F-A542-B9C8-2C75C078F0DC}" name="female teachers present"/>
-    <tableColumn id="661" xr3:uid="{B7E406CF-518D-524D-9D0A-695411453763}" name="Status of the school commitment made on Bus Day"/>
-    <tableColumn id="662" xr3:uid="{C564E6F9-DE6B-9E41-8071-C3ABC65536D0}" name="male caregivers present"/>
-    <tableColumn id="663" xr3:uid="{1F9D69D7-FA60-8E4B-AEB9-BD5EA7B7A444}" name="Is a practice active to follow up when a child stops coming to school?"/>
-    <tableColumn id="664" xr3:uid="{857E7112-01FF-D84F-AFAD-9D89D2118401}" name="female caregivers present"/>
-    <tableColumn id="665" xr3:uid="{04E817BD-2488-8D47-8105-D9C51F2691F7}" name="What physical evidence was seen to verify this commitment status?"/>
-    <tableColumn id="666" xr3:uid="{D47EBB08-3418-9D40-A3CD-EA8AE805A16F}" name="male PWDs"/>
-    <tableColumn id="667" xr3:uid="{108BB1AF-D9C7-224B-BF5B-5FBABD0A7E82}" name="Child Food Recognitio"/>
-    <tableColumn id="668" xr3:uid="{355CE0B1-F95C-7342-9B48-E0F7B12C575C}" name="female PWDs"/>
-    <tableColumn id="669" xr3:uid="{435EEE56-2202-404F-B637-948B9534F9D0}" name="The Adere Symbol"/>
-    <tableColumn id="670" xr3:uid="{EAB3FC27-A0D1-B04C-B60C-1040DA286F54}" name="Activity Delivery Checklist (Tick what was observed)"/>
-    <tableColumn id="671" xr3:uid="{586E25C4-03E2-4B49-A37F-219B7C7C3594}" name="Activity Delivery Checklist (Tick what was observed)/Energizer song &amp; movement completed"/>
-    <tableColumn id="672" xr3:uid="{E59A7291-D48A-2B4B-AAE4-1E2CE2444704}" name="Activity Delivery Checklist (Tick what was observed)/Food sorting / matching game completed"/>
-    <tableColumn id="673" xr3:uid="{C42DBA75-5543-F747-9196-9977C24CEF10}" name="Activity Delivery Checklist (Tick what was observed)/Adere calabash built hands-on with learners"/>
-    <tableColumn id="674" xr3:uid="{0926C518-A0E1-CF42-895D-D7CAC6DA4B75}" name="Activity Delivery Checklist (Tick what was observed)/local food replacement offered"/>
-    <tableColumn id="675" xr3:uid="{2ADBF1F9-3667-A846-9531-7F5C8683B7C7}" name="Activity Delivery Checklist (Tick what was observed)/equal plate portions &amp; chore balance"/>
-    <tableColumn id="676" xr3:uid="{A487F836-1A36-2F4C-B51B-3AFF14473129}" name="Activity Delivery Checklist (Tick what was observed)/Learners actively participated not just watching"/>
-    <tableColumn id="677" xr3:uid="{387BB9C2-55FA-AC4B-A54A-138C8385FE5E}" name="Working Together at Home"/>
-    <tableColumn id="678" xr3:uid="{4A70BA1F-D5D9-8947-A14D-8D2C024B3C89}" name="Did community members actually practice cooking/preparing, or only stand and watch?"/>
-    <tableColumn id="679" xr3:uid="{82D91847-044C-1A4E-8D2D-19A230F9A781}" name="Who facilitated the session"/>
-    <tableColumn id="680" xr3:uid="{EA31D18A-3D0D-0B4F-B1FA-7AE4D2F38715}" name="Help at School"/>
-    <tableColumn id="681" xr3:uid="{B640175B-B0E7-0149-AA9E-786CF5DB1850}" name="Explain"/>
-    <tableColumn id="682" xr3:uid="{C659E17E-70F8-F84C-821C-370163873884}" name="**Two-Minute Teach-Back Check**"/>
-    <tableColumn id="683" xr3:uid="{509F4318-7B2E-5644-AB20-6B63BB4B2278}" name="Names of Village Health Team (VHT) members interviewed"/>
-    <tableColumn id="684" xr3:uid="{B1F66958-3D43-B94B-9C16-74192AC24756}" name="**Can they recall activities from the session**"/>
-    <tableColumn id="685" xr3:uid="{29E0C23A-62D1-074E-9672-94000C9952EF}" name="Total females present"/>
-    <tableColumn id="686" xr3:uid="{7184D4B5-497E-8B42-BA7E-93956BB75536}" name="**Explain in their own words**"/>
-    <tableColumn id="687" xr3:uid="{A87F9C28-2C9B-7947-8188-2708D92754AA}" name="Number of women present" dataDxfId="1"/>
-    <tableColumn id="688" xr3:uid="{163F27DD-60AE-B546-BC3D-EDFB40B458B1}" name="##### Learner 145"/>
-    <tableColumn id="689" xr3:uid="{01F5B0BF-E941-BA4E-B9DC-B55C53601615}" name="Did community members actually practice cooking/preparing, or only stood and watched?"/>
-    <tableColumn id="690" xr3:uid="{07527EF8-6756-3E4F-A4FB-9C7CAA3A1F1C}" name="&lt;span style=&quot;display:none&quot;&gt;row-Can they recall activities from the session&lt;/span&gt;"/>
-    <tableColumn id="691" xr3:uid="{8412A573-8C3A-B64D-BB70-3E54E0E77DF5}" name="Explain your response above"/>
-    <tableColumn id="692" xr3:uid="{EEC467A9-4B19-344F-A617-55191F0EC7F9}" name="&lt;span style=&quot;display:none&quot;&gt;row-Explain in their own words&lt;/span&gt;"/>
-    <tableColumn id="693" xr3:uid="{2733BB94-DE8C-5040-B2BB-C7F0DEBDFC8E}" name="Were the foods used in the demonstration available in the local market/garden today?"/>
-    <tableColumn id="694" xr3:uid="{63D37C42-AAB6-CF44-8DDD-A9A0F858EBEA}" name="##### Learner 22"/>
-    <tableColumn id="695" xr3:uid="{8A0BA82A-4402-E44E-9AAA-5A0B7374DE94}" name="Did the demonstration show an alternative replacement food?"/>
-    <tableColumn id="696" xr3:uid="{FDF16B0D-EA27-6540-9904-6AC99B9660F5}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Can they recall activities from the session&lt;/span&gt;"/>
-    <tableColumn id="697" xr3:uid="{385B0F35-71C8-774F-9CD8-596E0E512C8D}" name="Mention the foods"/>
-    <tableColumn id="698" xr3:uid="{DBB14AD5-209E-F641-8321-1EDB20A6B5AF}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Explain in their own words&lt;/span&gt;"/>
-    <tableColumn id="699" xr3:uid="{D4083379-2AF2-C447-8476-FF511728FC5E}" name="**New Question**"/>
-    <tableColumn id="700" xr3:uid="{B7BBA52B-9D91-D643-A196-D64CE2AB0F18}" name="Campaign collaterla handed over to participants"/>
-    <tableColumn id="701" xr3:uid="{6BEB7DA1-A0C4-8649-A157-5F3300633E92}" name="Campaign collaterla handed over to participants/Printed Nutri Club Session forms"/>
-    <tableColumn id="702" xr3:uid="{F74E2256-15E1-C242-968A-75E265005521}" name="Campaign collaterla handed over to participants/Metu Nutrition Posters"/>
-    <tableColumn id="703" xr3:uid="{27CBC350-4B62-8B4F-A6D2-7F74A140B43A}" name="Campaign collaterla handed over to participants/Climate-Smart Cooking One-Pager Manuals"/>
-    <tableColumn id="704" xr3:uid="{4177F5F2-E47A-B54A-9530-A3C8286597D8}" name="Campaign collaterla handed over to participants/Game for the school"/>
-    <tableColumn id="705" xr3:uid="{47FD61BE-2C35-8645-A3F3-45046BD19624}" name="Campaign collaterla handed over to participants/WFP Toll-Free Feedback Display Board"/>
-    <tableColumn id="706" xr3:uid="{AEACA448-388F-4C47-9AED-8C205FF114F1}" name="Campaign collaterla handed over to participants/Nutri calendar"/>
-    <tableColumn id="707" xr3:uid="{B3088102-1078-394A-A49C-BBB17FD955B0}" name="Campaign collaterla handed over to participants/Metu handbook"/>
-    <tableColumn id="708" xr3:uid="{597CBB58-42AE-B344-A1A2-C829B6F410D6}" name="Campaign collaterla handed over to participants/Cooking manual"/>
-    <tableColumn id="709" xr3:uid="{130D8294-4EEE-F64D-9E20-82F696BD9329}" name="Campaign collaterla handed over to participants/Pledge / Commitment card"/>
-    <tableColumn id="710" xr3:uid="{A34BD4E5-9FCB-6D4C-823B-885E0450DCB6}" name="Lower Primary (ECD-P2) Registered Boys Weekly Attendance"/>
-    <tableColumn id="711" xr3:uid="{CC254387-7BFE-BB4A-9F7B-1408036A7587}" name="##### Adult 13"/>
-    <tableColumn id="712" xr3:uid="{CCF1C133-2602-DB42-8C08-BCB9CA9F1D71}" name="**What was hard or stood in the way first?**"/>
-    <tableColumn id="713" xr3:uid="{88324E33-3F77-8146-AF85-A19A0F05E75F}" name="Lower Primary (ECD-P2) Registered Girls Weekly Attendance"/>
-    <tableColumn id="714" xr3:uid="{B30E6D49-4602-7444-ABAF-5C807FFB0372}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Can they recall activities from the session&lt;/span&gt;"/>
-    <tableColumn id="715" xr3:uid="{B1746862-4D1E-8D48-9BB2-018537C55CA0}" name="**Despite that, what action was tried?**"/>
-    <tableColumn id="716" xr3:uid="{7104F4F2-1E48-2443-BAFD-8C6FB783ED7E}" name="Middle Primary (P3-P4) Registered Boys Weekly Attendance"/>
-    <tableColumn id="717" xr3:uid="{B8C71583-A7C8-EB4E-88CF-38B24E203E91}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Explain in their own words&lt;/span&gt;"/>
-    <tableColumn id="718" xr3:uid="{4BAB0ED3-EF06-E347-90B4-7D860644C850}" name="**Final verdict for Family**"/>
-    <tableColumn id="719" xr3:uid="{70B16144-4E33-B843-AAE3-AE38AA7CEE8D}" name="Middle Primary (P3-P4) Registered Girls Weekly Attendance"/>
-    <tableColumn id="720" xr3:uid="{E55B8C80-37C5-534B-B41A-A54D3FB0AD7D}" name="##### Adult 24"/>
-    <tableColumn id="721" xr3:uid="{7B751F4F-FD8D-EA46-9737-C9AF52D802F5}" name="##### Family 1"/>
-    <tableColumn id="722" xr3:uid="{6E4238B7-964D-8C41-B7A7-A523A61D20A2}" name="Upper Primary (P5-P7) Registered Boys Weekly Attendance"/>
-    <tableColumn id="723" xr3:uid="{7099E7A6-D5BF-0E49-AB65-99344934845B}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Can they recall activities from the session&lt;/span&gt;"/>
-    <tableColumn id="724" xr3:uid="{FE75FB72-162D-8C4B-81A9-64F256ED9478}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;"/>
-    <tableColumn id="725" xr3:uid="{997CA327-C301-344A-A4BE-95D6E8C2493D}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/No food or money"/>
-    <tableColumn id="726" xr3:uid="{101B3DB7-189B-7541-9CC2-D1A363B267E3}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/No water or firewood"/>
-    <tableColumn id="727" xr3:uid="{591B0310-48BF-F648-9300-7BC6E2AA16C8}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/No time to cook differently"/>
-    <tableColumn id="728" xr3:uid="{B469D3F5-2FFE-254B-8AF5-584F2B5F2E7C}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/Family did not agree"/>
-    <tableColumn id="729" xr3:uid="{8C199700-36CE-A74F-8ED8-0418A2D0E16B}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/Nothing was hard"/>
-    <tableColumn id="730" xr3:uid="{9AB24CED-EB29-AF40-8B86-CDB67AAE85A5}" name="Upper Primary (P5-P7) Registered Girls Weekly Attendance"/>
-    <tableColumn id="731" xr3:uid="{ABF065E0-F474-684F-8A94-5C3C66D71470}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Explain in their own words&lt;/span&gt;"/>
-    <tableColumn id="732" xr3:uid="{777B762B-9BCA-FD40-940D-7758D61DE6D8}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;"/>
-    <tableColumn id="733" xr3:uid="{FBDEE666-EB70-AF42-A92D-0C0EBDE40EE7}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;/Added a different local food"/>
-    <tableColumn id="734" xr3:uid="{A8EC39A0-9B71-C94B-BDDC-4CF91B969DC9}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;/Shared food portions fairly"/>
-    <tableColumn id="735" xr3:uid="{B30F34AB-5F2E-934F-8A56-7339ABF5071F}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;/Reduced morning chores so child gets to school"/>
-    <tableColumn id="736" xr3:uid="{D2108EF4-7348-F543-8678-658636AE53C9}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;/Nothing was possible"/>
-    <tableColumn id="737" xr3:uid="{CE8D9AD4-606B-3C4F-9B88-06935EAFC315}" name="What commitment did the school promise to put into action"/>
-    <tableColumn id="738" xr3:uid="{FE4D5BFE-FB61-144D-B69E-8DE01A429397}" name="&lt;span style=&quot;display:none&quot;&gt;row-Final verdict for Family&lt;/span&gt;"/>
-    <tableColumn id="739" xr3:uid="{A99ECD1A-BFC9-D746-85DE-31AB3DF9FC14}" name="Quality control of the commitment"/>
-    <tableColumn id="740" xr3:uid="{047EA7A5-598B-2C46-B290-3B2E1C34C931}" name="Quality control of the commitment/Commitment is clear and specific action"/>
-    <tableColumn id="741" xr3:uid="{2B951409-9F4E-D940-90DC-EAA52D95D3F6}" name="Quality control of the commitment/Named teacher/staff member responsible"/>
-    <tableColumn id="742" xr3:uid="{0F00B47B-A853-D049-955E-977C7ABFBDE6}" name="Quality control of the commitment/Realistic to finish within 4 weeks"/>
-    <tableColumn id="743" xr3:uid="{4B50D91E-47D8-334C-BAEC-91722DD37AE3}" name="Quality control of the commitment/Includes local food, snacks, or diet action"/>
-    <tableColumn id="744" xr3:uid="{6C23FB16-E4FD-1747-A513-4B02B2C796B7}" name="Quality control of the commitment/Includes step to keep children in class"/>
-    <tableColumn id="745" xr3:uid="{59835CE8-79B9-6646-B457-B16B8EA1ADF4}" name="Quality control of the commitment/Includes fair meal sharing for boys and girls"/>
-    <tableColumn id="746" xr3:uid="{DEDA9F62-BC0A-CB43-B9B9-F20DB3F4B72C}" name="Quality control of the commitment/Names action taken if a child drops out / stops attending"/>
-    <tableColumn id="747" xr3:uid="{B4F456E7-AC42-C34D-B6B6-C69CBBDCAE95}" name="##### Family 2"/>
-    <tableColumn id="748" xr3:uid="{CD065669-A2ED-C144-A833-F7878A6BB2DC}" name="Revised commitment"/>
-    <tableColumn id="749" xr3:uid="{68BAF242-C936-374D-A705-65E18F531272}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;"/>
-    <tableColumn id="750" xr3:uid="{98272EDF-2CB0-4F42-805E-D2231DED85B0}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/No food or money"/>
-    <tableColumn id="751" xr3:uid="{D182582F-6EC8-EB4B-8890-758B851F6B40}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/No water or firewood"/>
-    <tableColumn id="752" xr3:uid="{CB8A7C50-6AF7-1E47-B00B-2A99F594455C}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/No time to cook differently"/>
-    <tableColumn id="753" xr3:uid="{AFDC6B5D-5F22-1840-A265-2A20CCE6598D}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/Family did not agree"/>
-    <tableColumn id="754" xr3:uid="{615F089D-D785-B947-A995-FFC48F614EFC}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/Nothing was hard"/>
-    <tableColumn id="755" xr3:uid="{5DE2DCD7-CD26-AA49-BEA0-DA0D9B7D1A5D}" name="Total NutriCharts issued during Visit 1"/>
-    <tableColumn id="756" xr3:uid="{370A91CF-BB2C-9F46-83A1-E00AFC6FB3BD}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;"/>
-    <tableColumn id="757" xr3:uid="{DCDC3913-802B-A649-91E2-23C9A652D356}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;/Added a different local food"/>
-    <tableColumn id="758" xr3:uid="{318BF6D3-2669-2042-BD6F-052240B98B8A}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;/Shared food portions fairly"/>
-    <tableColumn id="759" xr3:uid="{B171E2A0-DB66-6C49-9329-979EF229267D}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;/Reduced morning chores so child gets to school"/>
-    <tableColumn id="760" xr3:uid="{3AAF9BF7-9C3B-9943-A857-6C921E231148}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;/Nothing was possible"/>
-    <tableColumn id="761" xr3:uid="{1585DE51-6917-584E-9422-BCA074FBB79C}" name="Total NutriCharts collected back today"/>
-    <tableColumn id="762" xr3:uid="{B09AFAA1-2D92-4E46-84EF-1E0F3E2DE8DB}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Final verdict for Family&lt;/span&gt;"/>
-    <tableColumn id="763" xr3:uid="{48276CBD-7DDA-364C-9D6C-E0AF0CAD10E8}" name="How many returned charts show joint completion by child AND adult?"/>
-    <tableColumn id="764" xr3:uid="{CFF9BF87-F43A-9449-8F86-94A5429055DC}" name="Number of male elders present"/>
-    <tableColumn id="765" xr3:uid="{431BAE0F-E642-0A48-BD07-3E9580E8C96A}" name="What did most families report about trying the home food/chore tasks?"/>
-    <tableColumn id="766" xr3:uid="{0A6A4D42-AB80-8242-9318-06D8C4390D46}" name="Number of female elders present"/>
-    <tableColumn id="767" xr3:uid="{D42ABD03-4340-D04F-901B-0B5B8180CED5}" name="What was the primary obstacle reported?"/>
-    <tableColumn id="768" xr3:uid="{26AD5A03-FC70-9D41-982B-72CA490451C0}" name="How did the men take part in the dialogue?"/>
-    <tableColumn id="769" xr3:uid="{155BF6B3-C6EA-4445-A5B3-CF059F8590F0}" name="What solution did the elders agree on in their exact words?"/>
-    <tableColumn id="770" xr3:uid="{F26C02C2-EC51-9D48-977D-7AD8F55210D1}" name="Status of the commitment written on Bus Day (Visit 2)"/>
-    <tableColumn id="771" xr3:uid="{68F7B305-3CE9-E144-A01C-F735282461AB}" name="Name of the elder or community leader responsible for this action"/>
-    <tableColumn id="772" xr3:uid="{6B33630A-603E-994B-959A-5D859ADCAE93}" name="Physical evidence sighted"/>
-    <tableColumn id="773" xr3:uid="{C92D874B-7C7F-3141-8B64-D855FAEF0AD6}" name="Does the school have an active, verified register to trace chronic absentees?"/>
-    <tableColumn id="774" xr3:uid="{C2DE2EC9-4B79-004A-865E-A512D6C157C9}" name="Women present"/>
-    <tableColumn id="775" xr3:uid="{5D231FFF-8084-BD47-964B-DE0823404037}" name="Men present"/>
-    <tableColumn id="776" xr3:uid="{F5BE35E7-087B-B04E-B4B8-C33752B67958}" name="Male children"/>
-    <tableColumn id="777" xr3:uid="{B21B4590-B540-F841-875B-7EC8F1575065}" name="Female children"/>
-    <tableColumn id="778" xr3:uid="{FFA72694-835A-F34E-93AF-53E9B39965DF}" name="Were demonstrated foods sourced locally from the area?"/>
-    <tableColumn id="779" xr3:uid="{1D0BD040-FFA8-FB42-B192-F8A3D37C1F4C}" name="Was an affordable, feasible local food substitute demonstrated?"/>
-    <tableColumn id="780" xr3:uid="{812B7757-55A7-B845-A76E-280187F1C3C3}" name="Total recipe cards distributed"/>
-    <tableColumn id="781" xr3:uid="{14173C5B-8AC6-6B4E-BEA6-46A9B87800F7}" name="**Interview 2 to 3 attending caregivers privately at the demo ground. Do not go to their homes.**"/>
-    <tableColumn id="782" xr3:uid="{22A6ACAA-ED83-D243-A15A-4F07E87942EA}" name="**What is most difficult or gets in the way of preparing balanced meals at home?**"/>
-    <tableColumn id="783" xr3:uid="{683F53F5-C55D-944F-AE80-04B259FE7F60}" name="**Despite those difficulties, which action can they realistically try at home?**"/>
-    <tableColumn id="784" xr3:uid="{9F55CD67-6EE1-A54D-B274-FB6EE1B55E8F}" name="**Column**5"/>
-    <tableColumn id="785" xr3:uid="{C9D810BF-8748-6D4F-B87F-C96ECFFEB9C1}" name="##### Caregiver 26"/>
-    <tableColumn id="786" xr3:uid="{CB7C7F37-E2EB-3E46-BF53-CB427BF7BA04}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of preparing balanced meals at home?&lt;/span&gt;"/>
-    <tableColumn id="787" xr3:uid="{64044F33-FEC3-AF48-8645-AC7FE992941E}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite those difficulties, which action can they realistically try at home?&lt;/span&gt;"/>
-    <tableColumn id="788" xr3:uid="{FE2A9B3C-A2E3-FA42-A6F4-F9B079C3DF23}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Column&lt;/span&gt;7"/>
-    <tableColumn id="789" xr3:uid="{A754D96F-5D5E-5642-80DE-3963122FCB45}" name="##### Caregiver 18"/>
-    <tableColumn id="790" xr3:uid="{70E4ADEC-2E02-C24A-BAC5-611619FBC7B0}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of preparing balanced meals at home?&lt;/span&gt;"/>
-    <tableColumn id="791" xr3:uid="{4C0A5DF5-86B2-D849-95A5-CB71300B7CB0}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite those difficulties, which action can they realistically try at home?&lt;/span&gt;"/>
-    <tableColumn id="792" xr3:uid="{E5325280-A774-3B4A-9ED8-84FA8A8874F1}" name="&lt;span style=&quot;display:none&quot;&gt;row-Column&lt;/span&gt;9"/>
-    <tableColumn id="793" xr3:uid="{DB727688-D385-C245-8A2D-AF7B898277DE}" name="Male Elders Present"/>
-    <tableColumn id="794" xr3:uid="{250149CA-1640-2040-8485-513B1F14F7BC}" name="Female Elders Present"/>
-    <tableColumn id="795" xr3:uid="{2D8627C1-C63D-B947-B59B-912D1C5CA4F6}" name="Young Men / Fathers"/>
-    <tableColumn id="796" xr3:uid="{7E068712-10C1-7E45-82C2-547C0A0C71FB}" name="ale Participation Level in Gender &amp; Feeding Discussions"/>
-    <tableColumn id="797" xr3:uid="{7DFD7878-2F3F-3643-A2BD-5E4E0BE589AC}" name="Community Agreement (Record in their exact words with NO personal names)"/>
-    <tableColumn id="798" xr3:uid="{1499A095-5303-6442-A268-48DD8C119850}" name="Named community body or structure responsible for follow-up"/>
-    <tableColumn id="799" xr3:uid="{001CD147-E387-1F47-BE40-9AC957C013CD}" name="Story Collector Name &amp; Role"/>
-    <tableColumn id="800" xr3:uid="{D8A7EC63-50BC-274A-86D2-668C7D822872}" name="Storyteller Category"/>
-    <tableColumn id="801" xr3:uid="{0C08E4AF-A66A-0546-AA7A-E85453EA2AAA}" name="Record the storyteller's actual words and dont try to re-interprete them"/>
-    <tableColumn id="802" xr3:uid="{804E32AA-4C22-9C4A-89AD-8565D5E43A3F}" name="What specific nutribus event, activity, chart, or discussion caused the shift"/>
-    <tableColumn id="803" xr3:uid="{0B2A7644-1219-7F45-BD58-C140D0F9A9F1}" name="What was physically done differently at home, class, or community after attending nutribus activities"/>
-    <tableColumn id="804" xr3:uid="{C6C34708-06EA-6C4E-96CF-F8A94B96848E}" name="what comments from the spectators"/>
-    <tableColumn id="805" xr3:uid="{38679512-AF49-9741-99A0-3E49B75219C7}" name="Were all demonstrated foods sourced locally"/>
-    <tableColumn id="806" xr3:uid="{7948810D-68E4-9042-97FB-D505C399CD49}" name="Specify11"/>
-    <tableColumn id="807" xr3:uid="{5184A4C6-CB6E-BE4F-A410-850CD982E8DA}" name="Community Agreement and commitments"/>
-    <tableColumn id="808" xr3:uid="{8DFC507D-7250-144D-B9FC-922148269969}" name="Learners with Disabilities"/>
-    <tableColumn id="809" xr3:uid="{17AD863D-022A-334A-90F9-10B02B02B72E}" name="PWDs"/>
-    <tableColumn id="810" xr3:uid="{6E77CEB2-09A1-A64E-9C2F-066C012C88A5}" name="_id"/>
-    <tableColumn id="811" xr3:uid="{A125A5B7-6729-2F4D-A89E-57182780722A}" name="_uuid"/>
-    <tableColumn id="812" xr3:uid="{CBDA2636-18B3-8342-8FDA-9DC4985989C4}" name="_submission_time" dataDxfId="0"/>
-    <tableColumn id="813" xr3:uid="{9DDB1991-893A-9E49-8798-D37329B1BE84}" name="_validation_status"/>
-    <tableColumn id="814" xr3:uid="{57F7BE9C-7FF0-8943-BD94-043F22383037}" name="_status"/>
-    <tableColumn id="815" xr3:uid="{DCB58F26-5678-8640-83A1-3038E9E1F7CE}" name="_submitted_by"/>
-    <tableColumn id="816" xr3:uid="{C13820D4-7E5D-934C-815D-78E13E6DF482}" name="__version__"/>
-    <tableColumn id="817" xr3:uid="{531BF569-E52C-3B47-AC2D-BD84FCFB1A61}" name="meta/rootUuid"/>
-    <tableColumn id="818" xr3:uid="{644122ED-CCCD-7042-ACA5-DF926883BF3D}" name="_index"/>
+    <tableColumn id="261" xr3:uid="{43D9CCC4-D82F-7340-BBE8-D62E0EA34A76}" name="##### Learner 4"/>
+    <tableColumn id="262" xr3:uid="{EAE4908E-5AED-E04E-995F-3BF1035D3294}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Imagine you are at home tonight and your family is cooking plain porridge.  What local greens or food can you ask them to add to make it strong?&lt;/span&gt;"/>
+    <tableColumn id="263" xr3:uid="{BE116813-C5F9-5C42-9F48-AF0B3F80D66B}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-If morning chores are very heavy at home tomorrow, what should happen so you  and your siblings still arrive at school on time?&lt;/span&gt;"/>
+    <tableColumn id="264" xr3:uid="{8BC6050E-157A-4A44-B35B-DD2834D33F43}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Record exact response/words spoken&lt;/span&gt;"/>
+    <tableColumn id="265" xr3:uid="{8403B00E-1708-824A-8D89-E3AAE644CDF5}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Campaign Line Recall: What does 'Abas ikimorikinit kaapei' mean in your own words?&lt;/span&gt;"/>
+    <tableColumn id="266" xr3:uid="{1C1F8BF9-88DE-DA4A-A47A-85186676CBD8}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Record respondent's exact words on campaign line meaning&lt;/span&gt;"/>
+    <tableColumn id="267" xr3:uid="{8E1F3396-44DC-E144-8987-360C0EBB7186}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Sex&lt;/span&gt;7"/>
+    <tableColumn id="268" xr3:uid="{A3FA371C-4726-5C48-A698-CD571D44F808}" name="##### Adult 2"/>
+    <tableColumn id="269" xr3:uid="{18E7DF93-EC71-0144-B25A-94835172FD36}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Imagine you are at home tonight and your family is cooking plain porridge.  What local greens or food can you ask them to add to make it strong?&lt;/span&gt;"/>
+    <tableColumn id="270" xr3:uid="{1B3FB524-39A7-6B44-95AC-4E5FEE7BAB8D}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-If morning chores are very heavy at home tomorrow, what should happen so you  and your siblings still arrive at school on time?&lt;/span&gt;"/>
+    <tableColumn id="271" xr3:uid="{4BCE93B3-8C05-644B-A093-9307ED67736E}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Record exact response/words spoken&lt;/span&gt;"/>
+    <tableColumn id="272" xr3:uid="{E6B6094D-C5A3-2840-9306-F73C4A9899FC}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Campaign Line Recall: What does 'Abas ikimorikinit kaapei' mean in your own words?&lt;/span&gt;"/>
+    <tableColumn id="273" xr3:uid="{1E1CD542-9A29-7541-B245-988B5B79FF18}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Record respondent's exact words on campaign line meaning&lt;/span&gt;"/>
+    <tableColumn id="274" xr3:uid="{7DBC2E33-4717-9045-8A5F-763CEA493324}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Sex&lt;/span&gt;8"/>
+    <tableColumn id="275" xr3:uid="{65B42868-A479-A445-89CF-6C521241EDF6}" name="##### Learner 2"/>
+    <tableColumn id="276" xr3:uid="{AFA86433-1905-294F-B08D-9879BFE402C1}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Imagine you are at home tonight and your family is cooking plain porridge.  What local greens or food can you ask them to add to make it strong?&lt;/span&gt;"/>
+    <tableColumn id="277" xr3:uid="{5E008FC1-397B-2440-B42D-C0E8CBC120DB}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-If morning chores are very heavy at home tomorrow, what should happen so you  and your siblings still arrive at school on time?&lt;/span&gt;"/>
+    <tableColumn id="278" xr3:uid="{04BF44F0-ACA8-E941-978F-AAFA6ECA03E1}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Record exact response/words spoken&lt;/span&gt;"/>
+    <tableColumn id="279" xr3:uid="{17778277-034B-6944-B494-8DE17E2A3F76}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Campaign Line Recall: What does 'Abas ikimorikinit kaapei' mean in your own words?&lt;/span&gt;"/>
+    <tableColumn id="280" xr3:uid="{43F27785-C9D9-884E-B2EB-DB50B1CD6CF7}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Record respondent's exact words on campaign line meaning&lt;/span&gt;"/>
+    <tableColumn id="281" xr3:uid="{EA93520E-484C-0B40-A908-42683293F13D}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Sex&lt;/span&gt;9"/>
+    <tableColumn id="282" xr3:uid="{994E4838-ACD7-1C46-B650-CA970507849B}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?"/>
+    <tableColumn id="283" xr3:uid="{34EE488B-B20F-174B-9D8C-AC75EDD1938E}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Lack of preparation confidence/skills"/>
+    <tableColumn id="284" xr3:uid="{FE86ECED-D077-7041-A3BA-EDA9346DCA90}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Taste preference barriers"/>
+    <tableColumn id="285" xr3:uid="{48CFFD15-4DAF-DD4E-856C-6F42554E1506}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Ingredients not prioritized at household level"/>
+    <tableColumn id="286" xr3:uid="{0F8BA876-79F9-4744-9C26-E479D3AC757F}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Other"/>
+    <tableColumn id="287" xr3:uid="{153A913C-EE52-224C-A3EF-1799F5AC75BF}" name="Specify10"/>
+    <tableColumn id="288" xr3:uid="{DFE8FE8A-D12C-C04A-A5D0-CB60F0909305}" name="Key delivery issue or barrier observed during activation"/>
+    <tableColumn id="289" xr3:uid="{CE5990EA-B876-3C48-9A10-8807B3EA385B}" name="Key success observed during activation"/>
+    <tableColumn id="290" xr3:uid="{C732E1A9-247C-7443-8A56-64016C5479AA}" name="One adaptation to make before the next school"/>
+    <tableColumn id="291" xr3:uid="{BA6D171C-F2BC-EB4C-9E59-2BF6458162CC}" name="Record the written School Commitment in their exact words"/>
+    <tableColumn id="292" xr3:uid="{FF8DBFED-E62C-0341-8596-7AE8F5EB833A}" name="Total NutriCharts Issued (Visit 1)"/>
+    <tableColumn id="293" xr3:uid="{EB529DD2-CB63-4847-837E-8CCA298C3432}" name="Total NutriCharts Returned Today"/>
+    <tableColumn id="294" xr3:uid="{43CC63A9-F91D-9144-AA81-3B48605894D0}" name="Returned charts showing joint household completion"/>
+    <tableColumn id="295" xr3:uid="{61DE2B76-DD11-0D42-A35E-6811E236416D}" name="Primary Feedback from Households"/>
+    <tableColumn id="296" xr3:uid="{9F5842AA-825E-5B49-B116-045D7486DE9A}" name="Primary Barrier Reported"/>
+    <tableColumn id="297" xr3:uid="{4F57EBF9-3152-3D49-8F8F-DB6A8F91116E}" name="Specify11"/>
+    <tableColumn id="298" xr3:uid="{A204C349-4188-064F-A093-18AD26358FB4}" name="Status of Bus Day School Commitment"/>
+    <tableColumn id="299" xr3:uid="{128D3A95-D2A2-4142-BE28-3A4350C17525}" name="If partly done or not done what got in the way?"/>
+    <tableColumn id="300" xr3:uid="{EA034228-1858-8645-BA56-AB7DAC43B393}" name="Collective Chronic Absentee Tracing Active?"/>
+    <tableColumn id="301" xr3:uid="{78651C36-CF91-A443-BA61-7B223248FF9C}" name="Explain how it has changed since the Nutribus activation"/>
+    <tableColumn id="302" xr3:uid="{14FBBFC7-B10D-DF43-8387-CC007AC1937C}" name="Did the school kitchen implement firewood-saving cooking practices/stoves?"/>
+    <tableColumn id="303" xr3:uid="{90605ED0-952D-0C4D-B8B7-AD0F9E24E927}" name="Were school-level media highlights, photos, or student success stories captured for social media PR reporting today?"/>
+    <tableColumn id="304" xr3:uid="{5EC5AE34-E0A7-1443-8361-097529342012}" name="briefly describe the captured PR highlight/story:"/>
+    <tableColumn id="305" xr3:uid="{345CB5A3-E0AB-2C46-9E05-32C146E52F4E}" name="Did teachers or learners report hearing the Nutribus campaign radio spots this week?"/>
+    <tableColumn id="306" xr3:uid="{F3D355D8-B487-8F43-9721-06E4512073E8}" name="**Household and learner interview**"/>
+    <tableColumn id="307" xr3:uid="{20CAD6E9-4B05-C242-9336-134F43158B6D}" name="**Sex**12"/>
+    <tableColumn id="308" xr3:uid="{35A2131E-2E45-8A41-8039-2900A72BC580}" name="**Since taking the chart home which feasible actions was your family able to try?**"/>
+    <tableColumn id="309" xr3:uid="{8CF4524E-0F4B-8041-89DD-E2D4103791DE}" name="**What was difficult or got in the way of taking action?**"/>
+    <tableColumn id="310" xr3:uid="{B93DA49F-883F-774D-8DB2-72798F7C0584}" name="**Has morning water/wood chore sharing shifted to help girls arrive at school on time?**"/>
+    <tableColumn id="311" xr3:uid="{4C2AADB5-48E0-7B44-A320-E4206A9859BC}" name="**Has food serving order shifted so the youngest child is served fairly?**"/>
+    <tableColumn id="312" xr3:uid="{333EC2DC-7BF7-4045-A535-5AE0BC1855A3}" name="**Record caregiver/learner verbatim comments on shifts at home**"/>
+    <tableColumn id="313" xr3:uid="{F8A265DC-4541-A340-8E6C-366C8B45711B}" name="##### Learner III"/>
+    <tableColumn id="314" xr3:uid="{94B09118-F3C2-EC41-82EB-707AFC280777}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Sex&lt;/span&gt;13"/>
+    <tableColumn id="315" xr3:uid="{739D5E49-671A-1B49-B297-8A75E47BF9E0}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
+    <tableColumn id="316" xr3:uid="{AA849FF2-D1CA-FD4C-B716-BE5C76A5DD24}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
+    <tableColumn id="317" xr3:uid="{E9293D66-995D-8341-9265-36CC40B0ADEE}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
+    <tableColumn id="318" xr3:uid="{FF545F7B-4C99-754B-9464-8B936F61B1D6}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
+    <tableColumn id="319" xr3:uid="{0C8AA7FF-BF9B-0F49-8DB2-70BF194E8C4B}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
+    <tableColumn id="320" xr3:uid="{C415E0B2-4351-1C4E-8F7B-3B1DD980F7CC}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
+    <tableColumn id="321" xr3:uid="{701DA804-90DD-8148-8E6A-048F8E81762E}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
+    <tableColumn id="322" xr3:uid="{AFE3F5CA-313A-EE41-8FF7-9C9101EDA281}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
+    <tableColumn id="323" xr3:uid="{D9A87922-5534-2B4C-AE78-9DA2781B57F1}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
+    <tableColumn id="324" xr3:uid="{473DE0FE-0ED0-2242-9D48-46EC48F0E310}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
+    <tableColumn id="325" xr3:uid="{003049ED-3ED5-5E46-B664-EE3EBF2F62FD}" name="##### Caregiver II"/>
+    <tableColumn id="326" xr3:uid="{95C84FEB-EA38-3445-937C-661FF0E00CE5}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Sex&lt;/span&gt;14"/>
+    <tableColumn id="327" xr3:uid="{EE7A1C8B-F420-5E49-89B0-9A5AD2968DDD}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
+    <tableColumn id="328" xr3:uid="{F692C1F9-C81E-9E4E-9E70-F62EED6A8BBC}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
+    <tableColumn id="329" xr3:uid="{0035D1DF-2220-1541-B91F-7A38FEF088EB}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
+    <tableColumn id="330" xr3:uid="{A8E29F67-8667-8444-B1D5-24846E6A8080}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
+    <tableColumn id="331" xr3:uid="{6B356D7D-C10C-194D-B24C-3F3F0C9A8435}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
+    <tableColumn id="332" xr3:uid="{9DBA6618-1E25-774E-BA61-7B7282D63922}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
+    <tableColumn id="333" xr3:uid="{349EEF99-A5C5-D649-9E1B-90338715FA75}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
+    <tableColumn id="334" xr3:uid="{C4E377F4-E73C-1740-BDE3-7BA2CD2C721B}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
+    <tableColumn id="335" xr3:uid="{5D8CD3EF-BC71-E249-AEFD-DD17384D0E7B}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
+    <tableColumn id="336" xr3:uid="{89A67960-7967-414F-B194-37D5BDFAAED1}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
+    <tableColumn id="337" xr3:uid="{6CE9A9DA-6B2C-D240-B888-4FD5155D148A}" name="##### Caregiver I"/>
+    <tableColumn id="338" xr3:uid="{62F5BDAA-208B-9144-8D33-219E219309DB}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Sex&lt;/span&gt;15"/>
+    <tableColumn id="339" xr3:uid="{45921911-491A-6E41-9BB1-3DBBC116D143}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
+    <tableColumn id="340" xr3:uid="{EA925F27-9A47-0742-820C-E7F3339195CB}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
+    <tableColumn id="341" xr3:uid="{E3C47080-3917-F24D-A199-0EBCEC7BBE93}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
+    <tableColumn id="342" xr3:uid="{F887D173-39C9-1343-9BB8-4EF1F3061994}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
+    <tableColumn id="343" xr3:uid="{1B82DD35-9172-E44C-A6EE-464D955B2C67}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
+    <tableColumn id="344" xr3:uid="{A7134196-7729-D447-A65E-9D6A6ABA1C70}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
+    <tableColumn id="345" xr3:uid="{F09ACDE3-816B-A047-A148-0DB6BEE5ECF8}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
+    <tableColumn id="346" xr3:uid="{598DDA97-E8D8-D24D-B0E0-99ECE7FD2B6B}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
+    <tableColumn id="347" xr3:uid="{4DAB67E8-94A4-7742-B476-D13901AD1C3E}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
+    <tableColumn id="348" xr3:uid="{DA8F4236-7FB6-9F40-BC72-1FEC98D4D5EB}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
+    <tableColumn id="349" xr3:uid="{0B05B41B-1EA4-5E4A-B352-077B10E617F3}" name="##### Caregiver III"/>
+    <tableColumn id="350" xr3:uid="{63F03AD1-467F-CE4E-B455-FEFE934738DB}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Sex&lt;/span&gt;16"/>
+    <tableColumn id="351" xr3:uid="{6E7E0553-488C-A74D-B319-61B4BC3B696C}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
+    <tableColumn id="352" xr3:uid="{9FEA492B-198B-1746-A770-2C1E903F5221}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
+    <tableColumn id="353" xr3:uid="{D4E09853-73B0-7B4D-BBA9-5F77D51D8F98}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
+    <tableColumn id="354" xr3:uid="{88CE74F1-AD4E-F74F-A114-CA1A4A6835B1}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
+    <tableColumn id="355" xr3:uid="{C1D57B73-2991-CE49-9188-71F474A54E7E}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
+    <tableColumn id="356" xr3:uid="{E172E14D-F633-0345-B663-14C8F1A7CB33}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
+    <tableColumn id="357" xr3:uid="{01565C16-B614-5748-86AE-9D4C9A520762}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
+    <tableColumn id="358" xr3:uid="{5E52DE89-BFBA-3745-9D3A-6A7000DD68A1}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
+    <tableColumn id="359" xr3:uid="{62983F49-855D-2A49-BD04-AB968D9111D9}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
+    <tableColumn id="360" xr3:uid="{828B8790-88EB-944F-8C1E-3FD49B73331A}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
+    <tableColumn id="361" xr3:uid="{A0423107-9031-DA4A-8CC9-5981882E54BC}" name="##### Learner I"/>
+    <tableColumn id="362" xr3:uid="{2CE877B4-61B9-EC41-9C62-5B30873DA633}" name="&lt;span style=&quot;display:none&quot;&gt;row-Sex&lt;/span&gt;17"/>
+    <tableColumn id="363" xr3:uid="{0730FA3E-EC90-E847-90D2-E6E63F1AD405}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
+    <tableColumn id="364" xr3:uid="{D3325582-C332-7144-B2DE-8C7ABB27374E}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
+    <tableColumn id="365" xr3:uid="{3C5B2AF7-F558-1144-B0CA-C95CBB106249}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
+    <tableColumn id="366" xr3:uid="{0CF05ECB-23F7-3D4A-AF0E-75C4724A5A78}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
+    <tableColumn id="367" xr3:uid="{49826E7E-7D3A-264F-B794-7CD70B2F71C5}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
+    <tableColumn id="368" xr3:uid="{9A9EED84-EFC4-874C-BDED-95F7B96DC22C}" name="&lt;span style=&quot;display:none&quot;&gt;row-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
+    <tableColumn id="369" xr3:uid="{C807A5C3-3678-F64B-BE3E-C7AB4B79BF1B}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
+    <tableColumn id="370" xr3:uid="{A172AD87-A290-2D40-A801-E8604213DF8E}" name="&lt;span style=&quot;display:none&quot;&gt;row-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
+    <tableColumn id="371" xr3:uid="{DBE23440-9743-3B4C-9663-0BB5317BA0BD}" name="&lt;span style=&quot;display:none&quot;&gt;row-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
+    <tableColumn id="372" xr3:uid="{6BBCCC32-FB4E-264F-AC43-AA1B03701AB5}" name="&lt;span style=&quot;display:none&quot;&gt;row-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
+    <tableColumn id="373" xr3:uid="{09AC9B81-F7A0-4D45-8495-15E1421AC760}" name="##### Learner II"/>
+    <tableColumn id="374" xr3:uid="{3ADE6FF5-6693-C84C-A81B-7C3E61A39F00}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Sex&lt;/span&gt;18"/>
+    <tableColumn id="375" xr3:uid="{E259EE65-6FF4-5D43-A857-C322D79D3123}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;"/>
+    <tableColumn id="376" xr3:uid="{21A195A8-6BEA-9F46-9055-7DBBB6E6A25C}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Boys took over/shared morning water and firewood chores"/>
+    <tableColumn id="377" xr3:uid="{DB02FAC4-CF66-A442-95B7-D8FC30574B97}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Supplemented Metu porridge with local wild greens or cowpeas"/>
+    <tableColumn id="378" xr3:uid="{F9BE2A69-021A-F942-B946-B082509B23B3}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/None possible right now"/>
+    <tableColumn id="379" xr3:uid="{8B2D5118-585C-AA40-BEC5-D079FDB5D9E4}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Practiced firewood-saving cooking methods (covered pot, smaller wood)"/>
+    <tableColumn id="380" xr3:uid="{78F21182-27D2-2242-9D1F-5108494A0F8B}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Since taking the chart home which feasible actions was your family able to try?&lt;/span&gt;/Served fair and equal food portions to boys and girls"/>
+    <tableColumn id="381" xr3:uid="{E09AEFE2-CB8C-8443-9CE0-C81A787070A1}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was difficult or got in the way of taking action?&lt;/span&gt;"/>
+    <tableColumn id="382" xr3:uid="{BF966A01-6781-1E42-ADBF-C257CEE2C185}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Has morning water/wood chore sharing shifted to help girls arrive at school on time?&lt;/span&gt;"/>
+    <tableColumn id="383" xr3:uid="{1B3D9E94-C89E-2A4F-97EB-382B11FE4CB8}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Has food serving order shifted so the youngest child is served fairly?&lt;/span&gt;"/>
+    <tableColumn id="384" xr3:uid="{058E9CD0-8604-3D44-BC30-848CC1A059C1}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Record caregiver/learner verbatim comments on shifts at home&lt;/span&gt;"/>
+    <tableColumn id="385" xr3:uid="{F4A0819C-7C73-E141-9F31-F4C8BE554A29}" name="Pillar 2: Did households report a shift in fair plate-sharing practices (specifically stopping the practice of young ones/girls eating last)?"/>
+    <tableColumn id="386" xr3:uid="{2BA1C280-71DE-374D-BB0F-BE200E5EA4F3}" name="Pillar 1: How directly did the school feeding protection and meal routines influence student presence this cycle?"/>
+    <tableColumn id="387" xr3:uid="{85AD0BAA-A58C-1943-ACDF-B382D64C7435}" name="**Registered Boys this week Attendance**"/>
+    <tableColumn id="388" xr3:uid="{F38DBA67-63F0-D340-B629-CD4F697E0994}" name="**Boys**"/>
+    <tableColumn id="389" xr3:uid="{730F0705-AF9A-624E-B7BB-DFE90B86FC36}" name="**Girls**"/>
+    <tableColumn id="390" xr3:uid="{4E6AEBCB-31FA-D94F-92C0-FF425E66086C}" name="##### Lower Primary (ECD-P2) Registered Boys this week Attendance"/>
+    <tableColumn id="391" xr3:uid="{C3957CC4-B26D-B948-9703-E3B203534921}" name="&lt;span style=&quot;display:none&quot;&gt;row-Boys&lt;/span&gt;"/>
+    <tableColumn id="392" xr3:uid="{7FA60F63-45E8-B241-9BDF-D89E279CD65E}" name="&lt;span style=&quot;display:none&quot;&gt;row-Girls&lt;/span&gt;"/>
+    <tableColumn id="393" xr3:uid="{A6F3C32F-1A39-2443-A8B3-D06F16533ECB}" name="##### Lower Primary (ECD-P2) Registered Girls this week Attendance"/>
+    <tableColumn id="394" xr3:uid="{8D24BC88-B0C8-DF45-ACF8-FF8BC017EEB4}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Boys&lt;/span&gt;"/>
+    <tableColumn id="395" xr3:uid="{B13958B2-AAE5-0843-B65E-F6E5437004A1}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Girls&lt;/span&gt;"/>
+    <tableColumn id="396" xr3:uid="{BEDDA644-A18D-474E-9A76-15279A340A35}" name="##### Middle Primary (P3-P4) Registered Boys this week Attendance"/>
+    <tableColumn id="397" xr3:uid="{0F4D7B18-68C6-4243-A30D-7473D8F961DE}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Boys&lt;/span&gt;"/>
+    <tableColumn id="398" xr3:uid="{3676DCF9-3886-5E45-BFF3-9C613386E171}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Girls&lt;/span&gt;"/>
+    <tableColumn id="399" xr3:uid="{A402DC75-A472-B94E-9C5C-4220E9F7106A}" name="##### Middle Primary (P3-P4) Registered Girls this week Attendance"/>
+    <tableColumn id="400" xr3:uid="{1668E7FF-80F8-094B-8BC8-9579D4619992}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Boys&lt;/span&gt;"/>
+    <tableColumn id="401" xr3:uid="{DA12EF57-5DFE-4C44-9280-97E9E18B9B85}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Girls&lt;/span&gt;"/>
+    <tableColumn id="402" xr3:uid="{DB2527D7-F091-B543-B8AA-F71B5F43C73E}" name="##### Upper Primary (P5-P7) Registered Boys this week Attendance"/>
+    <tableColumn id="403" xr3:uid="{13903B93-C2A9-E94B-B8A1-1816DA8CFF07}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Boys&lt;/span&gt;"/>
+    <tableColumn id="404" xr3:uid="{F0FAFC63-2740-DE4A-A814-17E08782CB57}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Girls&lt;/span&gt;"/>
+    <tableColumn id="405" xr3:uid="{FA77C2F1-33BD-0744-9BD7-59BB81C27FAD}" name="##### Upper Primary (P5-P7) Registered Girls this weekAttendance"/>
+    <tableColumn id="406" xr3:uid="{C336E36E-59C2-254B-9D9D-F64D29AFB63A}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Boys&lt;/span&gt;"/>
+    <tableColumn id="407" xr3:uid="{15799A46-940C-0843-9201-69BF361EFF74}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Girls&lt;/span&gt;"/>
+    <tableColumn id="408" xr3:uid="{65BC3A5B-459D-CE4B-ADF0-C56D930945B9}" name="Village / Catchment Demo Site"/>
+    <tableColumn id="409" xr3:uid="{880AA04D-D68C-2348-BBC7-8E811A52C8C6}" name="Who was on ground when this demo happened"/>
+    <tableColumn id="410" xr3:uid="{21B7F7F8-FEF6-2C46-B031-C71E1FD796AF}" name="Name of VHT"/>
+    <tableColumn id="411" xr3:uid="{E74E427E-E684-1D47-B9EA-5D85C9CF17F4}" name="Were capacity-strengthening partners (e.g., UNAC, Afi) present and co-facilitating this community demonstration?"/>
+    <tableColumn id="412" xr3:uid="{60B9D2D0-573D-444A-A985-9352150C65EA}" name="If yes, specify partner name"/>
+    <tableColumn id="413" xr3:uid="{AB92E4B8-7C47-9D4C-8507-0B8555171D25}" name="If yes, specify partner name/UNAC"/>
+    <tableColumn id="414" xr3:uid="{D9D59B8D-05EC-084B-88CB-6C3800D5B5A0}" name="If yes, specify partner name/AFI"/>
+    <tableColumn id="415" xr3:uid="{B1A12E08-C2AF-634B-BEFA-A181F32772F5}" name="If yes, specify partner name/Other"/>
+    <tableColumn id="416" xr3:uid="{D7930498-2BB0-1E48-A505-57C5A328BB61}" name="Specify19"/>
+    <tableColumn id="417" xr3:uid="{DA6131C0-BCE6-3F44-87DF-E250003840A3}" name="Partner role observed"/>
+    <tableColumn id="418" xr3:uid="{279900AA-FDA2-4D41-AB9F-EE53D47C7EF4}" name="Partner role observed/Co-facilitating clean cooking/gender dialogue"/>
+    <tableColumn id="419" xr3:uid="{0E0857DB-5E90-1042-B0BF-E50335D03751}" name="Partner role observed/Mentoring local VHTs/Elders"/>
+    <tableColumn id="420" xr3:uid="{43BBA490-0EB0-4C41-9F1C-58E9072863BE}" name="Partner role observed/Observing for sustainability tracking"/>
+    <tableColumn id="421" xr3:uid="{785A4C40-BE0B-5643-85E3-C31AA88BC1C3}" name="Partner role observed/Other "/>
+    <tableColumn id="422" xr3:uid="{AA1A44CC-E2FD-5E45-B26D-B8E2A6360399}" name="Specify20"/>
+    <tableColumn id="423" xr3:uid="{DC464029-05C3-4543-9E0D-BD2675859A12}" name="**Participant headcount**"/>
+    <tableColumn id="424" xr3:uid="{CCE47534-63C2-5449-8689-1E777AF87C8D}" name="**Male**21"/>
+    <tableColumn id="425" xr3:uid="{7331296B-D0C9-CB40-97B9-0C4216F8B77E}" name="**Female**22"/>
+    <tableColumn id="426" xr3:uid="{FE54AB76-D7B0-CA4C-AE83-1930E5387E75}" name="##### Female Caregivers"/>
+    <tableColumn id="427" xr3:uid="{603858D4-1699-BB41-8D95-4E01466F912D}" name="&lt;span style=&quot;display:none&quot;&gt;row-Male&lt;/span&gt;23"/>
+    <tableColumn id="428" xr3:uid="{6AC7EBED-B23E-2A45-A596-6794C8E029CD}" name="&lt;span style=&quot;display:none&quot;&gt;row-Female&lt;/span&gt;24"/>
+    <tableColumn id="429" xr3:uid="{4F86605D-F406-0240-B3B7-59AACE0FCE2D}" name="##### Male Fathers/Elders"/>
+    <tableColumn id="430" xr3:uid="{6A07A545-6A36-EE4C-8918-02202FF7A247}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Male&lt;/span&gt;25"/>
+    <tableColumn id="431" xr3:uid="{BA7F9846-1F81-334A-8009-7353383E9247}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Female&lt;/span&gt;26"/>
+    <tableColumn id="432" xr3:uid="{02FE8884-7236-574E-8E3B-9858FB820E00}" name="##### Male Children"/>
+    <tableColumn id="433" xr3:uid="{1EA4FFFB-E066-524C-A044-C76A33D6A672}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Male&lt;/span&gt;27"/>
+    <tableColumn id="434" xr3:uid="{115080D5-29E2-1847-BFBA-5AEC57F873C6}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Female&lt;/span&gt;28"/>
+    <tableColumn id="435" xr3:uid="{B876A06B-428C-8041-BE1B-04EE97977FCA}" name="##### Female Children"/>
+    <tableColumn id="436" xr3:uid="{41B7CD24-A484-7D4D-87E9-281AC9258CB0}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Male&lt;/span&gt;29"/>
+    <tableColumn id="437" xr3:uid="{4FFAA74D-F040-B146-AD41-B6906BBE3601}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Female&lt;/span&gt;30"/>
+    <tableColumn id="438" xr3:uid="{DEA7A9D4-3F42-4D47-9E2F-C1D9D71D81F3}" name="##### Male PWDs"/>
+    <tableColumn id="439" xr3:uid="{D6B22172-589F-B74E-BFCC-E637A8CF04CA}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Male&lt;/span&gt;31"/>
+    <tableColumn id="440" xr3:uid="{41A75906-82BA-104E-8A18-4949879D1719}" name="&lt;span style=&quot;display:none&quot;&gt;row_4-Female&lt;/span&gt;32"/>
+    <tableColumn id="441" xr3:uid="{E7A5D097-9926-784C-A91A-DBC0D4E91DF7}" name="##### Female PWDs"/>
+    <tableColumn id="442" xr3:uid="{1F06DEA5-BC15-CF48-92A0-4DF88BB0E711}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Male&lt;/span&gt;"/>
+    <tableColumn id="443" xr3:uid="{A381777E-0942-1D48-81EE-6A5E1521F2B1}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Female&lt;/span&gt;"/>
+    <tableColumn id="444" xr3:uid="{B79CB855-78C8-7746-ABA9-5760492E9753}" name="Did caregivers cook and handle ingredients hands-on, or only observe?"/>
+    <tableColumn id="445" xr3:uid="{D4CDC723-08FA-FC4B-A174-2DD9F1DF4073}" name="Was WFP Metu porridge demonstrated with additions of obtainable local staples      (e.g., wild greens like Eboo/Lokaka, cowpea leaves, roasted sesame/sorghum)?"/>
+    <tableColumn id="446" xr3:uid="{61E394FC-5871-8449-8CA0-86AD48D10F9F}" name="What comments or reactions came from the spectators?"/>
+    <tableColumn id="447" xr3:uid="{ACFFDA4C-0EFA-994F-919C-0E03BD2DEC93}" name="Pilar 3: Was clean/smart cooking demonstrated to protect the environment and lead to better harvests?"/>
+    <tableColumn id="448" xr3:uid="{9BD093DF-C4E6-DF47-8901-09596AAF57CF}" name="Observed community commitment to clean cooking practices:"/>
+    <tableColumn id="449" xr3:uid="{815002C0-4EA0-744C-8FBC-9EDB51F1AD02}" name="Were all demonstrated foods sourced locally from seasonal gardens/markets?"/>
+    <tableColumn id="450" xr3:uid="{C85F57AD-F97F-D742-902C-92694DDD7DC6}" name="Which fuel-saving practices were demonstrated to the gathering?"/>
+    <tableColumn id="451" xr3:uid="{CED5106C-5C09-504A-9FEB-2D52BFCB5C19}" name="Which fuel-saving practices were demonstrated to the gathering?/Improved cookstove consuming less firewood"/>
+    <tableColumn id="452" xr3:uid="{FDFE6E50-D020-9D41-8388-048DB1754873}" name="Which fuel-saving practices were demonstrated to the gathering?/Proper fuelwood pre-drying &amp; flame/airflow management"/>
+    <tableColumn id="453" xr3:uid="{29E68C8B-E30A-6443-A530-FECA3531DE4B}" name="Which fuel-saving practices were demonstrated to the gathering?/Retained heat cooking and pot covering to conserve fuel"/>
+    <tableColumn id="454" xr3:uid="{91B0F36D-0CA7-DD46-9AB9-26E6E7632655}" name="Which fuel-saving practices were demonstrated to the gathering?/Traditional 3-stone fire used (Non-compliant)"/>
+    <tableColumn id="455" xr3:uid="{4A1A6B41-FDA6-4042-9D62-828F1AD44498}" name="Conducted privately at the demo ground."/>
+    <tableColumn id="456" xr3:uid="{057E634B-A5F1-A04A-AE26-4CB9A2024C1E}" name="**Privately at the demonstration site.  Interview 2 to 3 attending caregivers right after the cooking demo**"/>
+    <tableColumn id="457" xr3:uid="{955A92BF-87C9-1F48-A96A-AB4A25ECCF96}" name="**What is most difficult or gets in the way of feeding your family well at home?**"/>
+    <tableColumn id="458" xr3:uid="{025AED3A-4966-354B-AFD3-9113DF5BFB64}" name="**Despite those difficulties, which feasible action can you realistically try at home?**"/>
+    <tableColumn id="459" xr3:uid="{52B170A6-2656-8549-8349-AE5DBE572605}" name="**Caregiver Commitment Verdict**"/>
+    <tableColumn id="460" xr3:uid="{A972A0FE-632A-9949-95B6-2E38C95D7B54}" name="**Record their exact words; no personal names**"/>
+    <tableColumn id="461" xr3:uid="{A0D6B17D-2BE1-464D-841F-0F657551D0D6}" name="**Sex**33"/>
+    <tableColumn id="462" xr3:uid="{9FA729A8-F90F-A446-AE62-B54B5DE943DA}" name="##### Caregiver 1"/>
+    <tableColumn id="463" xr3:uid="{D73A05AF-F500-384C-B733-600425C720AB}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;"/>
+    <tableColumn id="464" xr3:uid="{B700F713-9E91-5F45-B020-BFF5F7611337}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of cooking water"/>
+    <tableColumn id="465" xr3:uid="{421233FF-7586-C94E-9675-6804D00A57F1}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of firewood"/>
+    <tableColumn id="466" xr3:uid="{0F0563D0-7970-054E-AE78-E1F6476EB33B}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Food items missing in the local garden or market"/>
+    <tableColumn id="467" xr3:uid="{8CA55713-E371-3640-9066-DA10C0E5253D}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/lack of money"/>
+    <tableColumn id="468" xr3:uid="{E94B6233-6C96-2441-91A1-6AA1C99149F9}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Heavy morning chores"/>
+    <tableColumn id="469" xr3:uid="{8BA432C0-4D59-D64E-A4F0-3E429D1512F9}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Family or elder disagreement"/>
+    <tableColumn id="470" xr3:uid="{003482D1-190B-8F4D-A499-2D237C5E5632}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Nothing is difficult"/>
+    <tableColumn id="471" xr3:uid="{C303CAB4-7FCE-A440-A788-DCBD81AFB8C4}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite those difficulties, which feasible action can you realistically try at home?&lt;/span&gt;"/>
+    <tableColumn id="472" xr3:uid="{1AA1525D-3D94-394D-A324-BE0A9D602276}" name="&lt;span style=&quot;display:none&quot;&gt;row-Caregiver Commitment Verdict&lt;/span&gt;"/>
+    <tableColumn id="473" xr3:uid="{8050423B-8ACC-1B40-BA0F-1A7E74F08BDB}" name="&lt;span style=&quot;display:none&quot;&gt;row-Record their exact words; no personal names&lt;/span&gt;"/>
+    <tableColumn id="474" xr3:uid="{6FD9B0D9-665F-2D48-8D94-46C988FBAFE9}" name="&lt;span style=&quot;display:none&quot;&gt;row-Sex&lt;/span&gt;34"/>
+    <tableColumn id="475" xr3:uid="{632D8D7B-B103-5749-A670-65B384BAE44D}" name="##### Caregiver 3"/>
+    <tableColumn id="476" xr3:uid="{DD2AFFDB-A39C-0344-8F3F-E3AD5327061D}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;"/>
+    <tableColumn id="477" xr3:uid="{11BBBB2B-BF79-324E-AD57-6804FA9817ED}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of cooking water"/>
+    <tableColumn id="478" xr3:uid="{93A21771-3DED-BD49-B697-BCB423165A09}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of firewood"/>
+    <tableColumn id="479" xr3:uid="{326862D2-FBF7-E946-8297-3C4E37C27F8C}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Food items missing in the local garden or market"/>
+    <tableColumn id="480" xr3:uid="{73342FE1-3EF1-6C4D-A1D5-1AE16F51C8FE}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/lack of money"/>
+    <tableColumn id="481" xr3:uid="{1A7EEFE4-769E-D546-8F2B-E08347B28785}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Heavy morning chores"/>
+    <tableColumn id="482" xr3:uid="{A2154D6B-4567-0942-ACBF-FA7ED42E4E87}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Family or elder disagreement"/>
+    <tableColumn id="483" xr3:uid="{88704F69-295E-CA4B-A35F-D5F499B488A8}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Nothing is difficult"/>
+    <tableColumn id="484" xr3:uid="{7A53BC7F-7408-A64A-9AB8-5A20DE86988D}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Despite those difficulties, which feasible action can you realistically try at home?&lt;/span&gt;"/>
+    <tableColumn id="485" xr3:uid="{4E3A7430-164A-7B4C-AF65-04E20C2F1FEC}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Caregiver Commitment Verdict&lt;/span&gt;"/>
+    <tableColumn id="486" xr3:uid="{553E992D-B3C6-D841-810E-1A872AD08680}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Record their exact words; no personal names&lt;/span&gt;"/>
+    <tableColumn id="487" xr3:uid="{19929B94-807C-FA4A-A8CC-06BE2F28BE61}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Sex&lt;/span&gt;35"/>
+    <tableColumn id="488" xr3:uid="{1070F61C-D5A9-824F-AC96-E26E71937EBB}" name="##### Caregiver 2"/>
+    <tableColumn id="489" xr3:uid="{91EE5EA6-12E9-B04F-BEAF-3AC1BE6C3C00}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;"/>
+    <tableColumn id="490" xr3:uid="{72198C9D-597C-E846-B3CD-3B4A789018DB}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of cooking water"/>
+    <tableColumn id="491" xr3:uid="{EF60A24C-5D61-4647-97C2-C87883ABAB7F}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Scarcity of firewood"/>
+    <tableColumn id="492" xr3:uid="{E16D293E-70E4-B144-91EA-FA04E52B15A7}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Food items missing in the local garden or market"/>
+    <tableColumn id="493" xr3:uid="{C7B8E81C-BB87-8547-98D3-B85927B0A925}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/lack of money"/>
+    <tableColumn id="494" xr3:uid="{24252B5A-931B-2E45-8B68-6BA232326CEB}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Heavy morning chores"/>
+    <tableColumn id="495" xr3:uid="{68B5845F-8D3E-2443-89FD-779AA51C6980}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Family or elder disagreement"/>
+    <tableColumn id="496" xr3:uid="{FB56AF65-E271-2A46-94BC-9071226C9CC0}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of feeding your family well at home?&lt;/span&gt;/Nothing is difficult"/>
+    <tableColumn id="497" xr3:uid="{F49466C0-F719-E344-9751-6ED4A3B8F9CA}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite those difficulties, which feasible action can you realistically try at home?&lt;/span&gt;"/>
+    <tableColumn id="498" xr3:uid="{B921394E-D83F-5A42-AB33-0A93E92D1306}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Caregiver Commitment Verdict&lt;/span&gt;"/>
+    <tableColumn id="499" xr3:uid="{BAA1B846-EFE7-2B4F-A9DD-2DE58E2F1EBA}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Record their exact words; no personal names&lt;/span&gt;"/>
+    <tableColumn id="500" xr3:uid="{A40C09EA-5F54-1F42-B126-6540599803CE}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Sex&lt;/span&gt;36"/>
+    <tableColumn id="501" xr3:uid="{6CF85ADA-7C9C-CD4D-AB1B-FD5860D24C71}" name="Did the structured gender chore and fair-sharing discussion take place?"/>
+    <tableColumn id="502" xr3:uid="{7920551A-DA20-C846-B6EE-39CD6A253911}" name="Were gender dialogues led by senior women, senior men, and VHTs successfully executed?"/>
+    <tableColumn id="503" xr3:uid="{0EB1926F-7718-5E4F-A1D0-FE198C626532}" name="Male Participation Level in Gender, Chore &amp; Resource Discussions"/>
+    <tableColumn id="504" xr3:uid="{07AD3755-31F6-6B49-A96D-46A80E54847A}" name="Community Accountability &amp; Grievance Promotion"/>
+    <tableColumn id="505" xr3:uid="{55F46251-0799-B243-BC04-E768222908E8}" name="Group response: In your household who is served first and who eats last?"/>
+    <tableColumn id="506" xr3:uid="{FF44A4A5-ECB7-D44C-9F64-24A9ED0065B3}" name="Group response: What would need to change for the youngest child to be served first?"/>
+    <tableColumn id="507" xr3:uid="{8F1FF92F-4578-8E4E-8069-1BA9EFBCD195}" name="Community Accountability &amp; WFP Hotline Feedback Promoted?"/>
+    <tableColumn id="508" xr3:uid="{DB134C52-623C-A84C-AF72-ED73D77427F8}" name="Community Agreement and Commitments made in their own words"/>
+    <tableColumn id="509" xr3:uid="{6B45C29B-2C7A-594B-AB33-6D9E0DCF3479}" name="Named Community Body / Elders Responsible for Follow-Up"/>
+    <tableColumn id="510" xr3:uid="{6BE1328F-A764-8347-9E63-E6A48448D877}" name="Main debate point or objection raised before consensus was reached"/>
+    <tableColumn id="511" xr3:uid="{EAC6B0D0-B8C3-D44D-B3BF-4D51BA60889A}" name="Were community media highlights or clean cooking/gender dialogue photos captured for social media PR reporting?"/>
+    <tableColumn id="512" xr3:uid="{2B076E9D-6CFC-EB49-99E9-5B5C9C4E217D}" name="Provide a short description of the captured community highlight"/>
+    <tableColumn id="513" xr3:uid="{A37FA151-486C-1743-A146-4A795E7F3E83}" name="Did community members mention or give feedback on the campaign radio broadcasts during the gathering?"/>
+    <tableColumn id="514" xr3:uid="{E58E5509-0937-B24E-88F7-EB4381AF1CC6}" name="Summary of community radio feedback (if any)"/>
+    <tableColumn id="515" xr3:uid="{8DD023AD-C893-754B-A6C0-BC567A488883}" name="Storyteller names and age"/>
+    <tableColumn id="516" xr3:uid="{9468CFF2-C9DA-D948-B0E5-E1F7D5703041}" name="Storyteller Role"/>
+    <tableColumn id="517" xr3:uid="{D72E9639-2B18-9D49-A3A0-83E5DAC85FEE}" name="Record the storyteller's actual words; do not reinterpret "/>
+    <tableColumn id="518" xr3:uid="{14D0F5C7-0C13-184D-8626-51FCB274E2E2}" name="Describe the situation before the campaign:    What was the normal household diet, daily chore burden (water/firewood),    or school attendance pattern?"/>
+    <tableColumn id="519" xr3:uid="{BCE2308A-05D0-3A45-9A9E-CA4A2BBFABDE}" name="What specific campaign event, activity, chart, or discussion caused the shift?"/>
+    <tableColumn id="520" xr3:uid="{59271F7A-AB24-5A40-9A42-EBA982D09C5D}" name="What specific campaign event, activity, chart, or discussion caused the shift?37"/>
+    <tableColumn id="521" xr3:uid="{35FEACEE-AD1E-E74A-A7CF-F83706A90798}" name="What was physically done differently at home, class, or community after attending?"/>
+    <tableColumn id="522" xr3:uid="{2369C0D8-C8E4-5B40-9EB4-38085468F31B}" name="What was physically done differently at home, class, or community after attending the nutribus activitiies"/>
+    <tableColumn id="523" xr3:uid="{6AA2836A-0F3F-4B4C-A4C5-5ED68BE80613}" name="Why is this change significant to you?"/>
+    <tableColumn id="524" xr3:uid="{834BAA6E-DE77-9343-BCB9-45DD7B2CEAC8}" name="Verifiable Physical Evidence Sighted by Collector"/>
+    <tableColumn id="525" xr3:uid="{E028087A-6DC0-DB4E-AE34-646C309E9E59}" name="Verifiable Physical Evidence Sighted by Collector/Completed NutriChart sighted"/>
+    <tableColumn id="526" xr3:uid="{629A021E-0B51-9B43-A0BD-45CA1257AF8E}" name="Verifiable Physical Evidence Sighted by Collector/School register shows consistent female attendance"/>
+    <tableColumn id="527" xr3:uid="{F00578AB-D87C-5B4F-BD26-C58D9BC0FCA5}" name="Verifiable Physical Evidence Sighted by Collector/Cooking pot shows Metu fortified with obtainable local greens"/>
+    <tableColumn id="528" xr3:uid="{1BC05A79-896F-2A48-8D3A-F63A39834E57}" name="Verifiable Physical Evidence Sighted by Collector/Kitchen displays improved cookstove using less firewood"/>
+    <tableColumn id="529" xr3:uid="{75757D2A-E180-844A-8CB4-E748F09A770E}" name="Verifiable Physical Evidence Sighted by Collector/None sighted"/>
+    <tableColumn id="530" xr3:uid="{0AA50A64-CB53-434E-8F59-D52B591324F0}" name="What session of the week is this"/>
+    <tableColumn id="531" xr3:uid="{7F239D4A-99B5-C44C-87D2-C59720D08C7D}" name="What session of the week is this/Session one of the week"/>
+    <tableColumn id="532" xr3:uid="{1B98F0A5-C08A-9B47-9AD3-0636D44356D1}" name="What session of the week is this/Session two of the week"/>
+    <tableColumn id="533" xr3:uid="{751016E5-D836-2D4E-90F4-4C0CA8022DF4}" name="Club Patron Name"/>
+    <tableColumn id="534" xr3:uid="{75F70004-603C-BE45-BCFB-7F3C8CC0A0D3}" name="Total  male membership of the nutriclub"/>
+    <tableColumn id="535" xr3:uid="{2F85AD79-072B-834B-B567-EEDDED08169D}" name="Total  female membership of the nutriclub"/>
+    <tableColumn id="536" xr3:uid="{7AC55962-C969-964A-BDC5-3D5E2B93FC64}" name="Designated Meeting Place on Compound"/>
+    <tableColumn id="537" xr3:uid="{118DC67C-7127-644F-BBD6-DB61C5E17358}" name="Date session was conducted"/>
+    <tableColumn id="538" xr3:uid="{2B0695AC-0DC7-1148-8EB0-D6C5A766C08B}" name="start time"/>
+    <tableColumn id="539" xr3:uid="{638A3AC0-5CD8-214B-B76B-E8F5B3D168E3}" name="End time"/>
+    <tableColumn id="540" xr3:uid="{670067AA-D264-2845-93B4-24F548DCE600}" name="Boys Present"/>
+    <tableColumn id="541" xr3:uid="{383AE4E3-A0D1-2B48-897F-7F129026E2B8}" name="Girls Present"/>
+    <tableColumn id="542" xr3:uid="{E54C44B2-8AD7-774A-8DCE-AC4160CA3FEA}" name="Male learners with Disabilities"/>
+    <tableColumn id="543" xr3:uid="{83A90B45-47C7-2448-B686-A6DD81F6B984}" name="Female learners with Disabilities"/>
+    <tableColumn id="544" xr3:uid="{027969E6-322C-9943-B553-8E4448BAE68F}" name="Practical Activity Delivered"/>
+    <tableColumn id="545" xr3:uid="{83AE75FD-0EF3-7948-8E61-DC15EE2872C3}" name="Practical Activity Delivered/Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat)"/>
+    <tableColumn id="546" xr3:uid="{B581CEE0-3B42-894A-837C-1BCAF41E4EAC}" name="Practical Activity Delivered/Climate-Smart Living: Firewood-saving cooking methods &amp; moving from 3-stone fires"/>
+    <tableColumn id="547" xr3:uid="{78FEBA50-A5C5-C74A-A7D1-719282D23B5E}" name="Practical Activity Delivered/Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing"/>
+    <tableColumn id="548" xr3:uid="{322CD615-AE2C-ED45-B439-6976CB0B61A0}" name="Practical Activity Delivered/Gender Chore Rebalancing: Boys sharing morning water/firewood chores"/>
+    <tableColumn id="549" xr3:uid="{90F02817-FD5A-4647-8F82-083ECAC4AC3A}" name="Practical Activity Delivered/Peer Attendance Tracing: Checking and following up chronically absent classmates"/>
+    <tableColumn id="550" xr3:uid="{FF32D2FD-5E3B-5C47-87C9-4CA787635002}" name="What specific feasible food or chore action were members asked to try at home?"/>
+    <tableColumn id="551" xr3:uid="{7BAE1B5A-8469-7D43-B159-42091A454B50}" name="Date session II was conducted"/>
+    <tableColumn id="552" xr3:uid="{71978859-A044-B54D-B4C5-2393922645EF}" name="Start"/>
+    <tableColumn id="553" xr3:uid="{BED07455-4303-7248-85C6-7970DDBF90EA}" name="End"/>
+    <tableColumn id="554" xr3:uid="{01BFBDED-A4A5-3549-A338-770E3C6600D5}" name="Boys"/>
+    <tableColumn id="555" xr3:uid="{2DB9BA5B-36EF-6046-9A6A-A892CBBE2111}" name="Girls"/>
+    <tableColumn id="556" xr3:uid="{1DE27230-0304-A543-9A5E-0AE34B6C9AEC}" name="female learners PWDs"/>
+    <tableColumn id="557" xr3:uid="{B95F7A22-A310-A149-AA91-67FA9FF1FB80}" name="male leaders with PWDs"/>
+    <tableColumn id="558" xr3:uid="{0CD7FCBC-65C2-E74C-B644-40023719B931}" name="Practical Activity Delivered38"/>
+    <tableColumn id="559" xr3:uid="{376B4AA3-8D04-3549-8D7D-9F6C1DEB6D35}" name="Practical Activity Delivered/Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat)39"/>
+    <tableColumn id="560" xr3:uid="{8C2E6001-F27B-DC4D-8AB9-2813C9D217C1}" name="Practical Activity Delivered/Climate-Smart Living: Firewood-saving cooking methods &amp; moving from 3-stone fires40"/>
+    <tableColumn id="561" xr3:uid="{571716CC-4C2F-3D47-A7D9-821D65514320}" name="Practical Activity Delivered/Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing41"/>
+    <tableColumn id="562" xr3:uid="{EF1A69D8-D509-7341-82D5-A322254404CC}" name="Practical Activity Delivered/Gender Chore Rebalancing: Boys sharing morning water/firewood chores42"/>
+    <tableColumn id="563" xr3:uid="{BE9BB600-9D57-FE47-88E3-31D7909B141F}" name="Practical Activity Delivered/Peer Attendance Tracing: Checking and following up chronically absent classmates43"/>
+    <tableColumn id="564" xr3:uid="{E8CA202C-A529-344E-829C-BC135AAA86F7}" name="Did members report trying the home action with parents?"/>
+    <tableColumn id="565" xr3:uid="{D0522797-89F6-634D-A75C-5AD538F3713C}" name="Date Assembly Nutri-Moment was delivered"/>
+    <tableColumn id="566" xr3:uid="{137DF9A7-2CF7-8843-9655-D41636890B50}" name="Core Message Shared with Whole School"/>
+    <tableColumn id="567" xr3:uid="{E4F21ACA-A745-114F-B387-8E4D6F4305B9}" name="Delivered By"/>
+    <tableColumn id="568" xr3:uid="{98DFD8AF-8A1A-9F49-8538-A071EFA423D9}" name="Any other comments or observations about that event to inform future activities "/>
+    <tableColumn id="569" xr3:uid="{B2E10632-C61F-814C-B9D4-AA6BE40F2B85}" name="start44"/>
+    <tableColumn id="570" xr3:uid="{8DA0ACD3-7A79-AA42-ABFB-18B7090A610A}" name="end45"/>
+    <tableColumn id="571" xr3:uid="{CDA317BF-63D3-F345-A6A4-4B186B562DF8}" name="Activity type"/>
+    <tableColumn id="572" xr3:uid="{BE92FC42-97E0-504A-BDB1-C2A8FCC1BD29}" name="Type of session"/>
+    <tableColumn id="573" xr3:uid="{3CA394CE-3F4E-6F4C-BE97-3B3DDD7B8DC2}" name="Which visit is this?"/>
+    <tableColumn id="574" xr3:uid="{D2E9C5EE-82F8-3147-9F28-314B11B70B5C}" name="Headteacher or Deputy Present"/>
+    <tableColumn id="575" xr3:uid="{15713FF4-64D5-004D-A46A-46640FB9DBAD}" name="Which planned contact is being conducted today?"/>
+    <tableColumn id="576" xr3:uid="{7C437AF8-BDA3-EE48-8963-F1BE7AD90ACE}" name="Which age group was in this session?"/>
+    <tableColumn id="577" xr3:uid="{726C697A-3400-8848-AD63-BB91B0D2CE53}" name="Number of designated Club Patrons oriented"/>
+    <tableColumn id="578" xr3:uid="{758E388B-610E-8C42-BBB1-4118B327E518}" name="Administered by the District Coordinator immediately after each age-band session observed. Each session observed is submitted as its own flat record"/>
+    <tableColumn id="579" xr3:uid="{3CFD5536-4224-564D-92F2-6A63DAE75E2E}" name="Which learner age band is participating in this specific session?"/>
+    <tableColumn id="580" xr3:uid="{37C4D8A8-C4BD-F541-B6A5-F88FAB6090BC}" name="Number of boys present"/>
+    <tableColumn id="581" xr3:uid="{276B28C8-BF2F-6147-B9C9-D96EAFCA91FB}" name="Did the school team and catchment VHTs sit together to agree on the schedule?"/>
+    <tableColumn id="582" xr3:uid="{C77D1A68-E7ED-F846-B466-E37B7C4E7C6D}" name="Number of girls present"/>
+    <tableColumn id="583" xr3:uid="{E475154B-3D13-3E45-8E92-FB17D9B91099}" name="Is a formal Nutri Club established with a named patron?"/>
+    <tableColumn id="584" xr3:uid="{CDBBF927-5153-7443-AD29-08D38CA798EB}" name="Number of parents or adult community members present"/>
+    <tableColumn id="585" xr3:uid="{4C434B0B-FA46-6C4A-A2A8-C26A4F0DAF06}" name="Tick all activities that were delivered during this session"/>
+    <tableColumn id="586" xr3:uid="{162CD29C-160A-2444-B344-5F37813363C1}" name="Tick all activities that were delivered during this session/Song and movement activity led"/>
+    <tableColumn id="587" xr3:uid="{4E7452C7-7158-EF42-8972-247AEDA314B2}" name="Tick all activities that were delivered during this session/Food sorting or matching game practiced"/>
+    <tableColumn id="588" xr3:uid="{116FE33E-B3AB-AA43-AB3B-8F1232682C7B}" name="Tick all activities that were delivered during this session/Adere calabash built together with the group"/>
+    <tableColumn id="589" xr3:uid="{0EC2DB8C-8AD9-6548-A6C1-646C51CE79D8}" name="Tick all activities that were delivered during this session/Substitution game played (alternative food offered every time)"/>
+    <tableColumn id="590" xr3:uid="{DD57A600-0EFD-954F-B384-903217DD77A3}" name="Tick all activities that were delivered during this session/Fair sharing round discussed (sharing meals and chores fairly)"/>
+    <tableColumn id="591" xr3:uid="{26B2C48F-691D-054B-A301-231F4895318D}" name="Tick all activities that were delivered during this session/Learners actively moved, sorted, touched materials, or spoke (not just watching)"/>
+    <tableColumn id="592" xr3:uid="{953A2301-6632-9247-ADB0-705458861BD0}" name="Designated Club Meeting Day(s) each week"/>
+    <tableColumn id="593" xr3:uid="{EF052011-0566-1A45-AE90-5507686737F0}" name="Designated Club Meeting Day(s) each week/Monday"/>
+    <tableColumn id="594" xr3:uid="{78E4947B-EE2F-A349-BA47-4BC0B2A52026}" name="Designated Club Meeting Day(s) each week/Tuesday"/>
+    <tableColumn id="595" xr3:uid="{5543139B-0188-204A-AA14-81D08D3D6981}" name="Designated Club Meeting Day(s) each week/Wednesday"/>
+    <tableColumn id="596" xr3:uid="{030860A2-01FD-8948-9472-F9AAD44FD74F}" name="Designated Club Meeting Day(s) each week/Thursday"/>
+    <tableColumn id="597" xr3:uid="{F31638B0-87D2-4440-A9E5-121E620BC4F5}" name="Designated Club Meeting Day(s) each week/Friday"/>
+    <tableColumn id="598" xr3:uid="{546FBEDA-3F44-C647-9108-3855ADA1E67D}" name="Number of children with identified disabilities present"/>
+    <tableColumn id="599" xr3:uid="{C12E2F1F-854C-8947-AA82-5E5F3AA4565F}" name="Designated Weekly Meeting Time"/>
+    <tableColumn id="600" xr3:uid="{853D5995-011A-974F-9AF6-B56A945F64BE}" name="Designated Weekly Meeting Time/Morning before class"/>
+    <tableColumn id="601" xr3:uid="{0C0D4EA8-319B-8449-BB98-D6600D531209}" name="Designated Weekly Meeting Time/Lunch / Midday break"/>
+    <tableColumn id="602" xr3:uid="{DE60BEDB-2F12-7A46-871B-085A0D300B81}" name="Designated Weekly Meeting Time/After school hours"/>
+    <tableColumn id="603" xr3:uid="{8652E2E9-7956-C741-86FC-A83CD84C7E42}" name="Did learners complete the food sorting or matching activity?"/>
+    <tableColumn id="604" xr3:uid="{B65B3105-903F-0143-9E9B-60F3A5E2A538}" name="Stand at the side. Tick each activity delivered by the facilitator"/>
+    <tableColumn id="605" xr3:uid="{98470653-1BF4-CD4E-B191-127D88464C2C}" name="Did the headteacher commit to a weekly whole-school assembly nutrition message?"/>
+    <tableColumn id="606" xr3:uid="{FD3BF3D7-0C64-454E-BA0F-41726B9ACF95}" name="Was the Adere calabash built hands-on with the participants?"/>
+    <tableColumn id="607" xr3:uid="{FCC66418-968A-A241-94CA-4896A0551A58}" name="Fixed day for the weekly Nutri-Moment"/>
+    <tableColumn id="608" xr3:uid="{9E0CFAAF-5A56-C64F-B101-9AF4E37F30E8}" name="Was the substitution round completed with a feasible local substitute offered?"/>
+    <tableColumn id="609" xr3:uid="{EDF8BB68-6FA2-6E49-B391-E68AEB1C06DE}" name="Pull aside 5 individual participants (aim for 3 Teachers and 2 VHTs, balanced by gender)"/>
+    <tableColumn id="610" xr3:uid="{F7A812D0-D33B-934C-BFF4-3E8CC3C4C905}" name="Was a signed 4-week school work plan completed and submitted?"/>
+    <tableColumn id="611" xr3:uid="{20B259C0-F3B0-4741-83D5-1A524CAC4349}" name="Was the fair sharing round delivered (fair meal serving and morning chores)?"/>
+    <tableColumn id="612" xr3:uid="{62DE719B-D7DB-B14A-AAEA-E6E7FD565803}" name="To be filled by Teacher Patron twice every week after each club activity"/>
+    <tableColumn id="613" xr3:uid="{1855E198-D5DB-3D4B-83F2-3A915D308D5D}" name="Did the school teacher lead this session without the road crew?"/>
+    <tableColumn id="614" xr3:uid="{43B8B546-AAE1-B545-9EE4-962CF8ED8D50}" name="**iNDIVIDUAL TEACH-BACK CHECKS**"/>
+    <tableColumn id="615" xr3:uid="{35ACA737-4775-8247-BB6F-A11868F1936A}" name="Contact Number"/>
+    <tableColumn id="616" xr3:uid="{7F965FE0-B2AC-6541-85B7-1D6C1EC1EBC4}" name="**Participant**"/>
+    <tableColumn id="617" xr3:uid="{4759CB57-4B1A-594C-B74B-C65567FE1B07}" name="**Quoted phrase used by the participants during teach-back**"/>
+    <tableColumn id="618" xr3:uid="{1A3A3408-0E14-FC46-9020-364F5FDA24B8}" name="##### First Learner (Child 1) "/>
+    <tableColumn id="619" xr3:uid="{CBA78BFC-ED90-1C4E-A220-52714F311AF9}" name="&lt;span style=&quot;display:none&quot;&gt;row-Participant&lt;/span&gt;"/>
+    <tableColumn id="620" xr3:uid="{7860089A-31F2-EC4D-A443-8FED7285A463}" name="Learners with disabilities participating"/>
+    <tableColumn id="621" xr3:uid="{38868145-6FF0-3C40-8F47-B62B144C9D2B}" name="&lt;span style=&quot;display:none&quot;&gt;row-Quoted phrase used by the participants during teach-back&lt;/span&gt;"/>
+    <tableColumn id="622" xr3:uid="{49B2464E-C141-9E46-9011-7C9A0E595E82}" name="Session Theme / Activity Completed"/>
+    <tableColumn id="623" xr3:uid="{315529F9-4676-764A-9577-C6DAF84B3D75}" name="Session Theme / Activity Completed/Food sorting &amp; matching game using local foods"/>
+    <tableColumn id="624" xr3:uid="{2136C4C8-236B-DD42-A6C8-018DFE738FA4}" name="Session Theme / Activity Completed/Adere calabash balanced meal discussion"/>
+    <tableColumn id="625" xr3:uid="{3806B439-C6BE-E248-A448-5B7EB7409F3A}" name="Session Theme / Activity Completed/Local recipe substitution challenge"/>
+    <tableColumn id="626" xr3:uid="{FA70251D-C9AD-B64A-9F53-67771537833D}" name="Session Theme / Activity Completed/Fair food serving &amp; morning chore balance dialogue"/>
+    <tableColumn id="627" xr3:uid="{76295D21-49B5-6D4E-9DFC-136B9DDB5B78}" name="Session Theme / Activity Completed/Peer-to-peer tracing for absent learners"/>
+    <tableColumn id="628" xr3:uid="{21E53DC4-20F5-B141-A4EF-F6F7FE650FA6}" name="##### Second Learner (Child 2)"/>
+    <tableColumn id="629" xr3:uid="{AAD7B705-7DA0-4C41-834D-0C1436549E5A}" name="What specific food or chore action were members asked to try at home?"/>
+    <tableColumn id="630" xr3:uid="{96B4E005-5C0A-F64D-BF9D-EEAFB15903B3}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Participant&lt;/span&gt;"/>
+    <tableColumn id="631" xr3:uid="{F8BF78BC-614E-534C-B06E-4901ACDEE9A3}" name="Did learners report back on their home trials?"/>
+    <tableColumn id="632" xr3:uid="{59331D85-F8F5-7746-B173-38E3563CC4E3}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Quoted phrase used by the participants during teach-back&lt;/span&gt;"/>
+    <tableColumn id="633" xr3:uid="{C9C854C7-DF3B-A242-BDC0-2A78228E5AFB}" name="More detailed explanation about home trials"/>
+    <tableColumn id="634" xr3:uid="{8CB20AB5-8A42-DA45-A02F-F3DF7A41C1B1}" name="##### First Adult (Caregiver 1)"/>
+    <tableColumn id="635" xr3:uid="{91EC0102-EEFF-A943-B726-AB6A5A36745B}" name="Did the school hold a nutri-moment "/>
+    <tableColumn id="636" xr3:uid="{F896D22B-C9E8-934C-90FC-A307038369C4}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Participant&lt;/span&gt;"/>
+    <tableColumn id="637" xr3:uid="{AB7DEDA5-E9C1-3046-AFB4-482966BE5D46}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Quoted phrase used by the participants during teach-back&lt;/span&gt;"/>
+    <tableColumn id="638" xr3:uid="{8DF0716F-5FCE-834E-BA8C-B2F56C5E4666}" name="Core message delivered to whole school"/>
+    <tableColumn id="639" xr3:uid="{E3E50B7E-62AD-F14A-97A0-2C1F61645874}" name="##### Second Adult (Caregiver 2)"/>
+    <tableColumn id="640" xr3:uid="{60076818-9C04-774D-B41B-5A032A497AA8}" name="It was delivered by"/>
+    <tableColumn id="641" xr3:uid="{179CF4E4-8D2D-6D43-B038-30F0A5A80AC5}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Participant&lt;/span&gt;"/>
+    <tableColumn id="642" xr3:uid="{2E2B84E1-5FA2-A640-B3F2-9601420CB455}" name="Which planned visit is being conducted today?"/>
+    <tableColumn id="643" xr3:uid="{6D15D65C-0023-7C4F-AD22-0178BCC7E1F6}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Quoted phrase used by the participants during teach-back&lt;/span&gt;"/>
+    <tableColumn id="644" xr3:uid="{7B2F5774-BC54-F845-B40D-A3C1609FBB79}" name="Has the school formally set up the Nutri Club?"/>
+    <tableColumn id="645" xr3:uid="{46FB4AEA-6AC7-0B46-BA02-10BB96F22793}" name="One key success or operational issue observed in this session"/>
+    <tableColumn id="646" xr3:uid="{FCC9CFCA-2978-E840-A948-DE478BE01292}" name="Is there a designated teacher patron active on the compound?"/>
+    <tableColumn id="647" xr3:uid="{A73F34A0-1B83-184D-9D2C-67BECBCFEF25}" name="Total Nutri charts handed out"/>
+    <tableColumn id="648" xr3:uid="{6BB251DA-0F1B-3F48-89FD-53CC15A9C59C}" name="Agreed meeting place on compound"/>
+    <tableColumn id="649" xr3:uid="{E9676F68-4711-2F4A-9B9E-20D56E888571}" name="Total Nutri charts returned by learners"/>
+    <tableColumn id="650" xr3:uid="{D50A340B-D7FA-9D40-BFCB-262CEAEBFBEC}" name="Total take-home NutriCharts / cards handed over"/>
+    <tableColumn id="651" xr3:uid="{40BDD23B-F1FD-FC47-8204-B752293450E8}" name="How many returned charts were completed together with an adult?"/>
+    <tableColumn id="652" xr3:uid="{EF54FD03-C8DC-AB4B-B546-C775A156622E}" name="Did the coordinator demonstrate how learners should use them at home with parents?"/>
+    <tableColumn id="653" xr3:uid="{EC8DE3AB-0FF9-D64F-9814-63AD8B3FEA4E}" name="What did most families report about trying the home action?"/>
+    <tableColumn id="654" xr3:uid="{561F1A56-8B54-1643-811C-C9CC29217B27}" name="Classes receiving materials today"/>
+    <tableColumn id="655" xr3:uid="{D00DB10D-254D-2649-B5FB-767EB82B1595}" name="What was the biggest reason reported by families who struggled?"/>
+    <tableColumn id="656" xr3:uid="{2FEBF22F-E3D9-5E4A-BE2C-56752B66B2D2}" name="Age Band Participating in this Session"/>
+    <tableColumn id="657" xr3:uid="{ADC74742-FD10-2B47-9D66-BED86F8D0A83}" name="Does the school Nutri Club have an active teacher in charge and a meeting place?"/>
+    <tableColumn id="658" xr3:uid="{0D8F4936-76F6-4648-BD13-E3949B9CCA93}" name="The action the school promised in their own words"/>
+    <tableColumn id="659" xr3:uid="{CB0E7422-2264-4345-A25D-687A07755686}" name="male teachers present"/>
+    <tableColumn id="660" xr3:uid="{D9883FBE-B21F-A542-B9C8-2C75C078F0DC}" name="Tick every quality standard met by this commitment"/>
+    <tableColumn id="661" xr3:uid="{B7E406CF-518D-524D-9D0A-695411453763}" name="Tick every quality standard met by this commitment/The action is clear and specific"/>
+    <tableColumn id="662" xr3:uid="{C564E6F9-DE6B-9E41-8071-C3ABC65536D0}" name="Tick every quality standard met by this commitment/A specific teacher or staff member is named to lead it"/>
+    <tableColumn id="663" xr3:uid="{1F9D69D7-FA60-8E4B-AEB9-BD5EA7B7A444}" name="Tick every quality standard met by this commitment/It can be finished within four weeks"/>
+    <tableColumn id="664" xr3:uid="{857E7112-01FF-D84F-AFAD-9D89D2118401}" name="Tick every quality standard met by this commitment/It mentions food, school snacks, or local crops"/>
+    <tableColumn id="665" xr3:uid="{04E817BD-2488-8D47-8105-D9C51F2691F7}" name="Tick every quality standard met by this commitment/It includes an action to keep children in school"/>
+    <tableColumn id="666" xr3:uid="{D47EBB08-3418-9D40-A3CD-EA8AE805A16F}" name="Tick every quality standard met by this commitment/It includes fair sharing for both boys and girls"/>
+    <tableColumn id="667" xr3:uid="{108BB1AF-D9C7-224B-BF5B-5FBABD0A7E82}" name="Tick every quality standard met by this commitment/It states what the school will do if a child stops coming"/>
+    <tableColumn id="668" xr3:uid="{355CE0B1-F95C-7342-9B48-E0F7B12C575C}" name="female teachers present"/>
+    <tableColumn id="669" xr3:uid="{435EEE56-2202-404F-B637-948B9534F9D0}" name="Status of the school commitment made on Bus Day"/>
+    <tableColumn id="670" xr3:uid="{EAB3FC27-A0D1-B04C-B60C-1040DA286F54}" name="male caregivers present"/>
+    <tableColumn id="671" xr3:uid="{586E25C4-03E2-4B49-A37F-219B7C7C3594}" name="Is a practice active to follow up when a child stops coming to school?"/>
+    <tableColumn id="672" xr3:uid="{E59A7291-D48A-2B4B-AAE4-1E2CE2444704}" name="female caregivers present"/>
+    <tableColumn id="673" xr3:uid="{C42DBA75-5543-F747-9196-9977C24CEF10}" name="What physical evidence was seen to verify this commitment status?"/>
+    <tableColumn id="674" xr3:uid="{0926C518-A0E1-CF42-895D-D7CAC6DA4B75}" name="male PWDs"/>
+    <tableColumn id="675" xr3:uid="{2ADBF1F9-3667-A846-9531-7F5C8683B7C7}" name="Child Food Recognitio"/>
+    <tableColumn id="676" xr3:uid="{A487F836-1A36-2F4C-B51B-3AFF14473129}" name="female PWDs"/>
+    <tableColumn id="677" xr3:uid="{387BB9C2-55FA-AC4B-A54A-138C8385FE5E}" name="The Adere Symbol"/>
+    <tableColumn id="678" xr3:uid="{4A70BA1F-D5D9-8947-A14D-8D2C024B3C89}" name="Activity Delivery Checklist (Tick what was observed)"/>
+    <tableColumn id="679" xr3:uid="{82D91847-044C-1A4E-8D2D-19A230F9A781}" name="Activity Delivery Checklist (Tick what was observed)/Energizer song &amp; movement completed"/>
+    <tableColumn id="680" xr3:uid="{EA31D18A-3D0D-0B4F-B1FA-7AE4D2F38715}" name="Activity Delivery Checklist (Tick what was observed)/Food sorting / matching game completed"/>
+    <tableColumn id="681" xr3:uid="{B640175B-B0E7-0149-AA9E-786CF5DB1850}" name="Activity Delivery Checklist (Tick what was observed)/Adere calabash built hands-on with learners"/>
+    <tableColumn id="682" xr3:uid="{C659E17E-70F8-F84C-821C-370163873884}" name="Activity Delivery Checklist (Tick what was observed)/local food replacement offered"/>
+    <tableColumn id="683" xr3:uid="{509F4318-7B2E-5644-AB20-6B63BB4B2278}" name="Activity Delivery Checklist (Tick what was observed)/equal plate portions &amp; chore balance"/>
+    <tableColumn id="684" xr3:uid="{B1F66958-3D43-B94B-9C16-74192AC24756}" name="Activity Delivery Checklist (Tick what was observed)/Learners actively participated not just watching"/>
+    <tableColumn id="685" xr3:uid="{29E0C23A-62D1-074E-9672-94000C9952EF}" name="Working Together at Home"/>
+    <tableColumn id="686" xr3:uid="{7184D4B5-497E-8B42-BA7E-93956BB75536}" name="Did community members actually practice cooking/preparing, or only stand and watch?"/>
+    <tableColumn id="687" xr3:uid="{A87F9C28-2C9B-7947-8188-2708D92754AA}" name="Who facilitated the session" dataDxfId="2"/>
+    <tableColumn id="688" xr3:uid="{163F27DD-60AE-B546-BC3D-EDFB40B458B1}" name="Help at School"/>
+    <tableColumn id="689" xr3:uid="{01F5B0BF-E941-BA4E-B9DC-B55C53601615}" name="Explain"/>
+    <tableColumn id="690" xr3:uid="{07527EF8-6756-3E4F-A4FB-9C7CAA3A1F1C}" name="**Two-Minute Teach-Back Check**"/>
+    <tableColumn id="691" xr3:uid="{8412A573-8C3A-B64D-BB70-3E54E0E77DF5}" name="Names of Village Health Team (VHT) members interviewed"/>
+    <tableColumn id="692" xr3:uid="{EEC467A9-4B19-344F-A617-55191F0EC7F9}" name="**Can they recall activities from the session**"/>
+    <tableColumn id="693" xr3:uid="{2733BB94-DE8C-5040-B2BB-C7F0DEBDFC8E}" name="Total females present"/>
+    <tableColumn id="694" xr3:uid="{63D37C42-AAB6-CF44-8DDD-A9A0F858EBEA}" name="**Explain in their own words**"/>
+    <tableColumn id="695" xr3:uid="{8A0BA82A-4402-E44E-9AAA-5A0B7374DE94}" name="Number of women present"/>
+    <tableColumn id="696" xr3:uid="{FDF16B0D-EA27-6540-9904-6AC99B9660F5}" name="##### Learner 146"/>
+    <tableColumn id="697" xr3:uid="{385B0F35-71C8-774F-9CD8-596E0E512C8D}" name="Did community members actually practice cooking/preparing, or only stood and watched?"/>
+    <tableColumn id="698" xr3:uid="{DBB14AD5-209E-F641-8321-1EDB20A6B5AF}" name="&lt;span style=&quot;display:none&quot;&gt;row-Can they recall activities from the session&lt;/span&gt;"/>
+    <tableColumn id="699" xr3:uid="{D4083379-2AF2-C447-8476-FF511728FC5E}" name="Explain your response above"/>
+    <tableColumn id="700" xr3:uid="{B7BBA52B-9D91-D643-A196-D64CE2AB0F18}" name="&lt;span style=&quot;display:none&quot;&gt;row-Explain in their own words&lt;/span&gt;"/>
+    <tableColumn id="701" xr3:uid="{6BEB7DA1-A0C4-8649-A157-5F3300633E92}" name="Were the foods used in the demonstration available in the local market/garden today?"/>
+    <tableColumn id="702" xr3:uid="{F74E2256-15E1-C242-968A-75E265005521}" name="##### Learner 247"/>
+    <tableColumn id="703" xr3:uid="{27CBC350-4B62-8B4F-A6D2-7F74A140B43A}" name="Did the demonstration show an alternative replacement food?"/>
+    <tableColumn id="704" xr3:uid="{4177F5F2-E47A-B54A-9530-A3C8286597D8}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Can they recall activities from the session&lt;/span&gt;"/>
+    <tableColumn id="705" xr3:uid="{47FD61BE-2C35-8645-A3F3-45046BD19624}" name="Mention the foods"/>
+    <tableColumn id="706" xr3:uid="{AEACA448-388F-4C47-9AED-8C205FF114F1}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Explain in their own words&lt;/span&gt;"/>
+    <tableColumn id="707" xr3:uid="{B3088102-1078-394A-A49C-BBB17FD955B0}" name="**New Question**"/>
+    <tableColumn id="708" xr3:uid="{597CBB58-42AE-B344-A1A2-C829B6F410D6}" name="Campaign collaterla handed over to participants"/>
+    <tableColumn id="709" xr3:uid="{130D8294-4EEE-F64D-9E20-82F696BD9329}" name="Campaign collaterla handed over to participants/Printed Nutri Club Session forms"/>
+    <tableColumn id="710" xr3:uid="{A34BD4E5-9FCB-6D4C-823B-885E0450DCB6}" name="Campaign collaterla handed over to participants/Metu Nutrition Posters"/>
+    <tableColumn id="711" xr3:uid="{CC254387-7BFE-BB4A-9F7B-1408036A7587}" name="Campaign collaterla handed over to participants/Climate-Smart Cooking One-Pager Manuals"/>
+    <tableColumn id="712" xr3:uid="{CCF1C133-2602-DB42-8C08-BCB9CA9F1D71}" name="Campaign collaterla handed over to participants/Game for the school"/>
+    <tableColumn id="713" xr3:uid="{88324E33-3F77-8146-AF85-A19A0F05E75F}" name="Campaign collaterla handed over to participants/WFP Toll-Free Feedback Display Board"/>
+    <tableColumn id="714" xr3:uid="{B30E6D49-4602-7444-ABAF-5C807FFB0372}" name="Campaign collaterla handed over to participants/Nutri calendar"/>
+    <tableColumn id="715" xr3:uid="{B1746862-4D1E-8D48-9BB2-018537C55CA0}" name="Campaign collaterla handed over to participants/Metu handbook"/>
+    <tableColumn id="716" xr3:uid="{7104F4F2-1E48-2443-BAFD-8C6FB783ED7E}" name="Campaign collaterla handed over to participants/Cooking manual"/>
+    <tableColumn id="717" xr3:uid="{B8C71583-A7C8-EB4E-88CF-38B24E203E91}" name="Campaign collaterla handed over to participants/Pledge / Commitment card"/>
+    <tableColumn id="718" xr3:uid="{4BAB0ED3-EF06-E347-90B4-7D860644C850}" name="Lower Primary (ECD-P2) Registered Boys Weekly Attendance"/>
+    <tableColumn id="719" xr3:uid="{70B16144-4E33-B843-AAE3-AE38AA7CEE8D}" name="##### Adult 148"/>
+    <tableColumn id="720" xr3:uid="{E55B8C80-37C5-534B-B41A-A54D3FB0AD7D}" name="**What was hard or stood in the way first?**"/>
+    <tableColumn id="721" xr3:uid="{7B751F4F-FD8D-EA46-9737-C9AF52D802F5}" name="Lower Primary (ECD-P2) Registered Girls Weekly Attendance"/>
+    <tableColumn id="722" xr3:uid="{6E4238B7-964D-8C41-B7A7-A523A61D20A2}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Can they recall activities from the session&lt;/span&gt;"/>
+    <tableColumn id="723" xr3:uid="{7099E7A6-D5BF-0E49-AB65-99344934845B}" name="**Despite that, what action was tried?**"/>
+    <tableColumn id="724" xr3:uid="{FE75FB72-162D-8C4B-81A9-64F256ED9478}" name="Middle Primary (P3-P4) Registered Boys Weekly Attendance"/>
+    <tableColumn id="725" xr3:uid="{997CA327-C301-344A-A4BE-95D6E8C2493D}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Explain in their own words&lt;/span&gt;"/>
+    <tableColumn id="726" xr3:uid="{101B3DB7-189B-7541-9CC2-D1A363B267E3}" name="**Final verdict for Family**"/>
+    <tableColumn id="727" xr3:uid="{591B0310-48BF-F648-9300-7BC6E2AA16C8}" name="Middle Primary (P3-P4) Registered Girls Weekly Attendance"/>
+    <tableColumn id="728" xr3:uid="{B469D3F5-2FFE-254B-8AF5-584F2B5F2E7C}" name="##### Adult 249"/>
+    <tableColumn id="729" xr3:uid="{8C199700-36CE-A74F-8ED8-0418A2D0E16B}" name="##### Family 1"/>
+    <tableColumn id="730" xr3:uid="{9AB24CED-EB29-AF40-8B86-CDB67AAE85A5}" name="Upper Primary (P5-P7) Registered Boys Weekly Attendance"/>
+    <tableColumn id="731" xr3:uid="{ABF065E0-F474-684F-8A94-5C3C66D71470}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Can they recall activities from the session&lt;/span&gt;"/>
+    <tableColumn id="732" xr3:uid="{777B762B-9BCA-FD40-940D-7758D61DE6D8}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;"/>
+    <tableColumn id="733" xr3:uid="{FBDEE666-EB70-AF42-A92D-0C0EBDE40EE7}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/No food or money"/>
+    <tableColumn id="734" xr3:uid="{A8EC39A0-9B71-C94B-BDDC-4CF91B969DC9}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/No water or firewood"/>
+    <tableColumn id="735" xr3:uid="{B30F34AB-5F2E-934F-8A56-7339ABF5071F}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/No time to cook differently"/>
+    <tableColumn id="736" xr3:uid="{D2108EF4-7348-F543-8678-658636AE53C9}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/Family did not agree"/>
+    <tableColumn id="737" xr3:uid="{CE8D9AD4-606B-3C4F-9B88-06935EAFC315}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;/Nothing was hard"/>
+    <tableColumn id="738" xr3:uid="{FE4D5BFE-FB61-144D-B69E-8DE01A429397}" name="Upper Primary (P5-P7) Registered Girls Weekly Attendance"/>
+    <tableColumn id="739" xr3:uid="{A99ECD1A-BFC9-D746-85DE-31AB3DF9FC14}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Explain in their own words&lt;/span&gt;"/>
+    <tableColumn id="740" xr3:uid="{047EA7A5-598B-2C46-B290-3B2E1C34C931}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;"/>
+    <tableColumn id="741" xr3:uid="{2B951409-9F4E-D940-90DC-EAA52D95D3F6}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;/Added a different local food"/>
+    <tableColumn id="742" xr3:uid="{0F00B47B-A853-D049-955E-977C7ABFBDE6}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;/Shared food portions fairly"/>
+    <tableColumn id="743" xr3:uid="{4B50D91E-47D8-334C-BAEC-91722DD37AE3}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;/Reduced morning chores so child gets to school"/>
+    <tableColumn id="744" xr3:uid="{6C23FB16-E4FD-1747-A513-4B02B2C796B7}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite that, what action was tried?&lt;/span&gt;/Nothing was possible"/>
+    <tableColumn id="745" xr3:uid="{59835CE8-79B9-6646-B457-B16B8EA1ADF4}" name="What commitment did the school promise to put into action"/>
+    <tableColumn id="746" xr3:uid="{DEDA9F62-BC0A-CB43-B9B9-F20DB3F4B72C}" name="&lt;span style=&quot;display:none&quot;&gt;row-Final verdict for Family&lt;/span&gt;"/>
+    <tableColumn id="747" xr3:uid="{B4F456E7-AC42-C34D-B6B6-C69CBBDCAE95}" name="Quality control of the commitment"/>
+    <tableColumn id="748" xr3:uid="{CD065669-A2ED-C144-A833-F7878A6BB2DC}" name="Quality control of the commitment/Commitment is clear and specific action"/>
+    <tableColumn id="749" xr3:uid="{68BAF242-C936-374D-A705-65E18F531272}" name="Quality control of the commitment/Named teacher/staff member responsible"/>
+    <tableColumn id="750" xr3:uid="{98272EDF-2CB0-4F42-805E-D2231DED85B0}" name="Quality control of the commitment/Realistic to finish within 4 weeks"/>
+    <tableColumn id="751" xr3:uid="{D182582F-6EC8-EB4B-8890-758B851F6B40}" name="Quality control of the commitment/Includes local food, snacks, or diet action"/>
+    <tableColumn id="752" xr3:uid="{CB8A7C50-6AF7-1E47-B00B-2A99F594455C}" name="Quality control of the commitment/Includes step to keep children in class"/>
+    <tableColumn id="753" xr3:uid="{AFDC6B5D-5F22-1840-A265-2A20CCE6598D}" name="Quality control of the commitment/Includes fair meal sharing for boys and girls"/>
+    <tableColumn id="754" xr3:uid="{615F089D-D785-B947-A995-FFC48F614EFC}" name="Quality control of the commitment/Names action taken if a child drops out / stops attending"/>
+    <tableColumn id="755" xr3:uid="{5DE2DCD7-CD26-AA49-BEA0-DA0D9B7D1A5D}" name="##### Family 2"/>
+    <tableColumn id="756" xr3:uid="{370A91CF-BB2C-9F46-83A1-E00AFC6FB3BD}" name="Revised commitment"/>
+    <tableColumn id="757" xr3:uid="{DCDC3913-802B-A649-91E2-23C9A652D356}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;"/>
+    <tableColumn id="758" xr3:uid="{318BF6D3-2669-2042-BD6F-052240B98B8A}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/No food or money"/>
+    <tableColumn id="759" xr3:uid="{B171E2A0-DB66-6C49-9329-979EF229267D}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/No water or firewood"/>
+    <tableColumn id="760" xr3:uid="{3AAF9BF7-9C3B-9943-A857-6C921E231148}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/No time to cook differently"/>
+    <tableColumn id="761" xr3:uid="{1585DE51-6917-584E-9422-BCA074FBB79C}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/Family did not agree"/>
+    <tableColumn id="762" xr3:uid="{B09AFAA1-2D92-4E46-84EF-1E0F3E2DE8DB}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What was hard or stood in the way first?&lt;/span&gt;/Nothing was hard"/>
+    <tableColumn id="763" xr3:uid="{48276CBD-7DDA-364C-9D6C-E0AF0CAD10E8}" name="Total NutriCharts issued during Visit 1"/>
+    <tableColumn id="764" xr3:uid="{CFF9BF87-F43A-9449-8F86-94A5429055DC}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;"/>
+    <tableColumn id="765" xr3:uid="{431BAE0F-E642-0A48-BD07-3E9580E8C96A}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;/Added a different local food"/>
+    <tableColumn id="766" xr3:uid="{0A6A4D42-AB80-8242-9318-06D8C4390D46}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;/Shared food portions fairly"/>
+    <tableColumn id="767" xr3:uid="{D42ABD03-4340-D04F-901B-0B5B8180CED5}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;/Reduced morning chores so child gets to school"/>
+    <tableColumn id="768" xr3:uid="{26AD5A03-FC70-9D41-982B-72CA490451C0}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite that, what action was tried?&lt;/span&gt;/Nothing was possible"/>
+    <tableColumn id="769" xr3:uid="{155BF6B3-C6EA-4445-A5B3-CF059F8590F0}" name="Total NutriCharts collected back today"/>
+    <tableColumn id="770" xr3:uid="{F26C02C2-EC51-9D48-977D-7AD8F55210D1}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Final verdict for Family&lt;/span&gt;"/>
+    <tableColumn id="771" xr3:uid="{68F7B305-3CE9-E144-A01C-F735282461AB}" name="How many returned charts show joint completion by child AND adult?"/>
+    <tableColumn id="772" xr3:uid="{6B33630A-603E-994B-959A-5D859ADCAE93}" name="Number of male elders present"/>
+    <tableColumn id="773" xr3:uid="{C92D874B-7C7F-3141-8B64-D855FAEF0AD6}" name="What did most families report about trying the home food/chore tasks?"/>
+    <tableColumn id="774" xr3:uid="{C2DE2EC9-4B79-004A-865E-A512D6C157C9}" name="Number of female elders present"/>
+    <tableColumn id="775" xr3:uid="{5D231FFF-8084-BD47-964B-DE0823404037}" name="What was the primary obstacle reported?"/>
+    <tableColumn id="776" xr3:uid="{F5BE35E7-087B-B04E-B4B8-C33752B67958}" name="How did the men take part in the dialogue?"/>
+    <tableColumn id="777" xr3:uid="{B21B4590-B540-F841-875B-7EC8F1575065}" name="What solution did the elders agree on in their exact words?"/>
+    <tableColumn id="778" xr3:uid="{FFA72694-835A-F34E-93AF-53E9B39965DF}" name="Status of the commitment written on Bus Day (Visit 2)"/>
+    <tableColumn id="779" xr3:uid="{1D0BD040-FFA8-FB42-B192-F8A3D37C1F4C}" name="Name of the elder or community leader responsible for this action"/>
+    <tableColumn id="780" xr3:uid="{812B7757-55A7-B845-A76E-280187F1C3C3}" name="Physical evidence sighted"/>
+    <tableColumn id="781" xr3:uid="{14173C5B-8AC6-6B4E-BEA6-46A9B87800F7}" name="Does the school have an active, verified register to trace chronic absentees?"/>
+    <tableColumn id="782" xr3:uid="{22A6ACAA-ED83-D243-A15A-4F07E87942EA}" name="Women present"/>
+    <tableColumn id="783" xr3:uid="{683F53F5-C55D-944F-AE80-04B259FE7F60}" name="Men present"/>
+    <tableColumn id="784" xr3:uid="{9F55CD67-6EE1-A54D-B274-FB6EE1B55E8F}" name="Male children"/>
+    <tableColumn id="785" xr3:uid="{C9D810BF-8748-6D4F-B87F-C96ECFFEB9C1}" name="Female children"/>
+    <tableColumn id="786" xr3:uid="{CB7C7F37-E2EB-3E46-BF53-CB427BF7BA04}" name="Were demonstrated foods sourced locally from the area?"/>
+    <tableColumn id="787" xr3:uid="{64044F33-FEC3-AF48-8645-AC7FE992941E}" name="Was an affordable, feasible local food substitute demonstrated?"/>
+    <tableColumn id="788" xr3:uid="{FE2A9B3C-A2E3-FA42-A6F4-F9B079C3DF23}" name="Total recipe cards distributed"/>
+    <tableColumn id="789" xr3:uid="{A754D96F-5D5E-5642-80DE-3963122FCB45}" name="**Interview 2 to 3 attending caregivers privately at the demo ground. Do not go to their homes.**"/>
+    <tableColumn id="790" xr3:uid="{70E4ADEC-2E02-C24A-BAC5-611619FBC7B0}" name="**What is most difficult or gets in the way of preparing balanced meals at home?**"/>
+    <tableColumn id="791" xr3:uid="{4C0A5DF5-86B2-D849-95A5-CB71300B7CB0}" name="**Despite those difficulties, which action can they realistically try at home?**"/>
+    <tableColumn id="792" xr3:uid="{E5325280-A774-3B4A-9ED8-84FA8A8874F1}" name="**Column**50"/>
+    <tableColumn id="793" xr3:uid="{DB727688-D385-C245-8A2D-AF7B898277DE}" name="##### Caregiver 251"/>
+    <tableColumn id="794" xr3:uid="{250149CA-1640-2040-8485-513B1F14F7BC}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is most difficult or gets in the way of preparing balanced meals at home?&lt;/span&gt;"/>
+    <tableColumn id="795" xr3:uid="{2D8627C1-C63D-B947-B59B-912D1C5CA4F6}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Despite those difficulties, which action can they realistically try at home?&lt;/span&gt;"/>
+    <tableColumn id="796" xr3:uid="{7E068712-10C1-7E45-82C2-547C0A0C71FB}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Column&lt;/span&gt;52"/>
+    <tableColumn id="797" xr3:uid="{7DFD7878-2F3F-3643-A2BD-5E4E0BE589AC}" name="##### Caregiver 153"/>
+    <tableColumn id="798" xr3:uid="{1499A095-5303-6442-A268-48DD8C119850}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of preparing balanced meals at home?&lt;/span&gt;"/>
+    <tableColumn id="799" xr3:uid="{001CD147-E387-1F47-BE40-9AC957C013CD}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite those difficulties, which action can they realistically try at home?&lt;/span&gt;"/>
+    <tableColumn id="800" xr3:uid="{D8A7EC63-50BC-274A-86D2-668C7D822872}" name="&lt;span style=&quot;display:none&quot;&gt;row-Column&lt;/span&gt;54"/>
+    <tableColumn id="801" xr3:uid="{0C08E4AF-A66A-0546-AA7A-E85453EA2AAA}" name="Male Elders Present"/>
+    <tableColumn id="802" xr3:uid="{804E32AA-4C22-9C4A-89AD-8565D5E43A3F}" name="Female Elders Present"/>
+    <tableColumn id="803" xr3:uid="{0B2A7644-1219-7F45-BD58-C140D0F9A9F1}" name="Young Men / Fathers"/>
+    <tableColumn id="804" xr3:uid="{C6C34708-06EA-6C4E-96CF-F8A94B96848E}" name="ale Participation Level in Gender &amp; Feeding Discussions"/>
+    <tableColumn id="805" xr3:uid="{38679512-AF49-9741-99A0-3E49B75219C7}" name="Community Agreement (Record in their exact words with NO personal names)"/>
+    <tableColumn id="806" xr3:uid="{7948810D-68E4-9042-97FB-D505C399CD49}" name="Named community body or structure responsible for follow-up"/>
+    <tableColumn id="807" xr3:uid="{5184A4C6-CB6E-BE4F-A410-850CD982E8DA}" name="Story Collector Name &amp; Role"/>
+    <tableColumn id="808" xr3:uid="{8DFC507D-7250-144D-B9FC-922148269969}" name="Storyteller Category"/>
+    <tableColumn id="809" xr3:uid="{17AD863D-022A-334A-90F9-10B02B02B72E}" name="Record the storyteller's actual words and dont try to re-interprete them"/>
+    <tableColumn id="810" xr3:uid="{6E77CEB2-09A1-A64E-9C2F-066C012C88A5}" name="What specific nutribus event, activity, chart, or discussion caused the shift"/>
+    <tableColumn id="811" xr3:uid="{A125A5B7-6729-2F4D-A89E-57182780722A}" name="What was physically done differently at home, class, or community after attending nutribus activities"/>
+    <tableColumn id="812" xr3:uid="{CBDA2636-18B3-8342-8FDA-9DC4985989C4}" name="what comments from the spectators" dataDxfId="1"/>
+    <tableColumn id="813" xr3:uid="{9DDB1991-893A-9E49-8798-D37329B1BE84}" name="Were all demonstrated foods sourced locally"/>
+    <tableColumn id="814" xr3:uid="{57F7BE9C-7FF0-8943-BD94-043F22383037}" name="Specify55"/>
+    <tableColumn id="815" xr3:uid="{DCB58F26-5678-8640-83A1-3038E9E1F7CE}" name="Community Agreement and commitments"/>
+    <tableColumn id="816" xr3:uid="{C13820D4-7E5D-934C-815D-78E13E6DF482}" name="Learners with Disabilities"/>
+    <tableColumn id="817" xr3:uid="{531BF569-E52C-3B47-AC2D-BD84FCFB1A61}" name="PWDs"/>
+    <tableColumn id="818" xr3:uid="{644122ED-CCCD-7042-ACA5-DF926883BF3D}" name="_id"/>
+    <tableColumn id="819" xr3:uid="{44BA26A3-9884-A247-8CA4-CC60A58C2858}" name="_uuid"/>
+    <tableColumn id="820" xr3:uid="{57BC694F-1C38-484A-9288-ACCA88D7D177}" name="_submission_time" dataDxfId="0"/>
+    <tableColumn id="821" xr3:uid="{2C14184A-443F-F746-8E63-144B3BBDC063}" name="_validation_status"/>
+    <tableColumn id="822" xr3:uid="{95BE97BC-A42E-D545-8BC1-C31F87E6BC0D}" name="_status"/>
+    <tableColumn id="823" xr3:uid="{0807B666-BF5A-1B4E-ABA5-D6C0A17FC7B1}" name="_submitted_by"/>
+    <tableColumn id="824" xr3:uid="{380FC912-43B5-EC40-A672-C95FFDDFC648}" name="__version__"/>
+    <tableColumn id="825" xr3:uid="{42C4B0F2-07A2-8A47-A91C-12D4838A9C8F}" name="meta/rootUuid"/>
+    <tableColumn id="826" xr3:uid="{1A8E1F56-2F11-3144-AB87-13304B50D1CA}" name="_index"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3653,14 +3892,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AEL2"/>
+  <dimension ref="A1:AET4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="43" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
     <col min="8" max="8" width="85.6640625" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" customWidth="1"/>
@@ -4227,7 +4467,7 @@
     <col min="692" max="692" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:818" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:826" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5009,1685 +5249,2336 @@
         <v>769</v>
       </c>
       <c r="JA1" t="s">
+        <v>773</v>
+      </c>
+      <c r="JB1" t="s">
+        <v>774</v>
+      </c>
+      <c r="JC1" t="s">
+        <v>775</v>
+      </c>
+      <c r="JD1" t="s">
+        <v>776</v>
+      </c>
+      <c r="JE1" t="s">
+        <v>777</v>
+      </c>
+      <c r="JF1" t="s">
+        <v>778</v>
+      </c>
+      <c r="JG1" t="s">
+        <v>847</v>
+      </c>
+      <c r="JH1" t="s">
         <v>210</v>
       </c>
-      <c r="JB1" t="s">
+      <c r="JI1" t="s">
         <v>211</v>
       </c>
-      <c r="JC1" t="s">
+      <c r="JJ1" t="s">
         <v>212</v>
       </c>
-      <c r="JD1" t="s">
+      <c r="JK1" t="s">
         <v>213</v>
       </c>
-      <c r="JE1" t="s">
+      <c r="JL1" t="s">
         <v>214</v>
       </c>
-      <c r="JF1" t="s">
+      <c r="JM1" t="s">
         <v>215</v>
       </c>
-      <c r="JG1" t="s">
+      <c r="JN1" t="s">
+        <v>848</v>
+      </c>
+      <c r="JO1" t="s">
+        <v>216</v>
+      </c>
+      <c r="JP1" t="s">
+        <v>217</v>
+      </c>
+      <c r="JQ1" t="s">
+        <v>218</v>
+      </c>
+      <c r="JR1" t="s">
+        <v>219</v>
+      </c>
+      <c r="JS1" t="s">
+        <v>220</v>
+      </c>
+      <c r="JT1" t="s">
+        <v>221</v>
+      </c>
+      <c r="JU1" t="s">
+        <v>849</v>
+      </c>
+      <c r="JV1" t="s">
+        <v>699</v>
+      </c>
+      <c r="JW1" t="s">
+        <v>700</v>
+      </c>
+      <c r="JX1" t="s">
+        <v>701</v>
+      </c>
+      <c r="JY1" t="s">
+        <v>702</v>
+      </c>
+      <c r="JZ1" t="s">
+        <v>703</v>
+      </c>
+      <c r="KA1" t="s">
         <v>770</v>
       </c>
-      <c r="JH1" t="s">
-        <v>216</v>
-      </c>
-      <c r="JI1" t="s">
-        <v>217</v>
-      </c>
-      <c r="JJ1" t="s">
-        <v>218</v>
-      </c>
-      <c r="JK1" t="s">
-        <v>219</v>
-      </c>
-      <c r="JL1" t="s">
-        <v>220</v>
-      </c>
-      <c r="JM1" t="s">
-        <v>221</v>
-      </c>
-      <c r="JN1" t="s">
+      <c r="KB1" t="s">
+        <v>222</v>
+      </c>
+      <c r="KC1" t="s">
+        <v>223</v>
+      </c>
+      <c r="KD1" t="s">
+        <v>224</v>
+      </c>
+      <c r="KE1" t="s">
+        <v>225</v>
+      </c>
+      <c r="KF1" t="s">
+        <v>226</v>
+      </c>
+      <c r="KG1" t="s">
+        <v>227</v>
+      </c>
+      <c r="KH1" t="s">
+        <v>228</v>
+      </c>
+      <c r="KI1" t="s">
+        <v>229</v>
+      </c>
+      <c r="KJ1" t="s">
+        <v>230</v>
+      </c>
+      <c r="KK1" t="s">
+        <v>772</v>
+      </c>
+      <c r="KL1" t="s">
+        <v>231</v>
+      </c>
+      <c r="KM1" t="s">
+        <v>232</v>
+      </c>
+      <c r="KN1" t="s">
+        <v>233</v>
+      </c>
+      <c r="KO1" t="s">
+        <v>234</v>
+      </c>
+      <c r="KP1" t="s">
+        <v>235</v>
+      </c>
+      <c r="KQ1" t="s">
+        <v>704</v>
+      </c>
+      <c r="KR1" t="s">
+        <v>705</v>
+      </c>
+      <c r="KS1" t="s">
+        <v>706</v>
+      </c>
+      <c r="KT1" t="s">
+        <v>236</v>
+      </c>
+      <c r="KU1" t="s">
+        <v>850</v>
+      </c>
+      <c r="KV1" t="s">
+        <v>237</v>
+      </c>
+      <c r="KW1" t="s">
+        <v>238</v>
+      </c>
+      <c r="KX1" t="s">
+        <v>239</v>
+      </c>
+      <c r="KY1" t="s">
+        <v>240</v>
+      </c>
+      <c r="KZ1" t="s">
+        <v>241</v>
+      </c>
+      <c r="LA1" t="s">
+        <v>242</v>
+      </c>
+      <c r="LB1" t="s">
+        <v>851</v>
+      </c>
+      <c r="LC1" t="s">
+        <v>243</v>
+      </c>
+      <c r="LD1" t="s">
+        <v>244</v>
+      </c>
+      <c r="LE1" t="s">
+        <v>245</v>
+      </c>
+      <c r="LF1" t="s">
+        <v>246</v>
+      </c>
+      <c r="LG1" t="s">
+        <v>247</v>
+      </c>
+      <c r="LH1" t="s">
+        <v>248</v>
+      </c>
+      <c r="LI1" t="s">
+        <v>249</v>
+      </c>
+      <c r="LJ1" t="s">
+        <v>250</v>
+      </c>
+      <c r="LK1" t="s">
+        <v>251</v>
+      </c>
+      <c r="LL1" t="s">
+        <v>252</v>
+      </c>
+      <c r="LM1" t="s">
+        <v>253</v>
+      </c>
+      <c r="LN1" t="s">
+        <v>852</v>
+      </c>
+      <c r="LO1" t="s">
+        <v>254</v>
+      </c>
+      <c r="LP1" t="s">
+        <v>255</v>
+      </c>
+      <c r="LQ1" t="s">
+        <v>256</v>
+      </c>
+      <c r="LR1" t="s">
+        <v>257</v>
+      </c>
+      <c r="LS1" t="s">
+        <v>258</v>
+      </c>
+      <c r="LT1" t="s">
+        <v>259</v>
+      </c>
+      <c r="LU1" t="s">
+        <v>260</v>
+      </c>
+      <c r="LV1" t="s">
+        <v>261</v>
+      </c>
+      <c r="LW1" t="s">
+        <v>262</v>
+      </c>
+      <c r="LX1" t="s">
+        <v>263</v>
+      </c>
+      <c r="LY1" t="s">
+        <v>264</v>
+      </c>
+      <c r="LZ1" t="s">
+        <v>853</v>
+      </c>
+      <c r="MA1" t="s">
+        <v>265</v>
+      </c>
+      <c r="MB1" t="s">
+        <v>266</v>
+      </c>
+      <c r="MC1" t="s">
+        <v>267</v>
+      </c>
+      <c r="MD1" t="s">
+        <v>268</v>
+      </c>
+      <c r="ME1" t="s">
+        <v>269</v>
+      </c>
+      <c r="MF1" t="s">
+        <v>270</v>
+      </c>
+      <c r="MG1" t="s">
+        <v>271</v>
+      </c>
+      <c r="MH1" t="s">
+        <v>272</v>
+      </c>
+      <c r="MI1" t="s">
+        <v>273</v>
+      </c>
+      <c r="MJ1" t="s">
+        <v>274</v>
+      </c>
+      <c r="MK1" t="s">
+        <v>707</v>
+      </c>
+      <c r="ML1" t="s">
+        <v>854</v>
+      </c>
+      <c r="MM1" t="s">
+        <v>708</v>
+      </c>
+      <c r="MN1" t="s">
+        <v>709</v>
+      </c>
+      <c r="MO1" t="s">
+        <v>710</v>
+      </c>
+      <c r="MP1" t="s">
+        <v>711</v>
+      </c>
+      <c r="MQ1" t="s">
+        <v>712</v>
+      </c>
+      <c r="MR1" t="s">
+        <v>713</v>
+      </c>
+      <c r="MS1" t="s">
+        <v>714</v>
+      </c>
+      <c r="MT1" t="s">
+        <v>715</v>
+      </c>
+      <c r="MU1" t="s">
+        <v>716</v>
+      </c>
+      <c r="MV1" t="s">
+        <v>717</v>
+      </c>
+      <c r="MW1" t="s">
+        <v>718</v>
+      </c>
+      <c r="MX1" t="s">
+        <v>855</v>
+      </c>
+      <c r="MY1" t="s">
+        <v>275</v>
+      </c>
+      <c r="MZ1" t="s">
+        <v>276</v>
+      </c>
+      <c r="NA1" t="s">
+        <v>277</v>
+      </c>
+      <c r="NB1" t="s">
+        <v>278</v>
+      </c>
+      <c r="NC1" t="s">
+        <v>279</v>
+      </c>
+      <c r="ND1" t="s">
+        <v>280</v>
+      </c>
+      <c r="NE1" t="s">
+        <v>281</v>
+      </c>
+      <c r="NF1" t="s">
+        <v>282</v>
+      </c>
+      <c r="NG1" t="s">
+        <v>283</v>
+      </c>
+      <c r="NH1" t="s">
+        <v>284</v>
+      </c>
+      <c r="NI1" t="s">
+        <v>285</v>
+      </c>
+      <c r="NJ1" t="s">
+        <v>856</v>
+      </c>
+      <c r="NK1" t="s">
+        <v>286</v>
+      </c>
+      <c r="NL1" t="s">
+        <v>287</v>
+      </c>
+      <c r="NM1" t="s">
+        <v>288</v>
+      </c>
+      <c r="NN1" t="s">
+        <v>289</v>
+      </c>
+      <c r="NO1" t="s">
+        <v>290</v>
+      </c>
+      <c r="NP1" t="s">
+        <v>291</v>
+      </c>
+      <c r="NQ1" t="s">
+        <v>292</v>
+      </c>
+      <c r="NR1" t="s">
+        <v>293</v>
+      </c>
+      <c r="NS1" t="s">
+        <v>294</v>
+      </c>
+      <c r="NT1" t="s">
+        <v>295</v>
+      </c>
+      <c r="NU1" t="s">
+        <v>719</v>
+      </c>
+      <c r="NV1" t="s">
+        <v>720</v>
+      </c>
+      <c r="NW1" t="s">
+        <v>721</v>
+      </c>
+      <c r="NX1" t="s">
+        <v>722</v>
+      </c>
+      <c r="NY1" t="s">
+        <v>723</v>
+      </c>
+      <c r="NZ1" t="s">
+        <v>724</v>
+      </c>
+      <c r="OA1" t="s">
+        <v>725</v>
+      </c>
+      <c r="OB1" t="s">
+        <v>726</v>
+      </c>
+      <c r="OC1" t="s">
+        <v>727</v>
+      </c>
+      <c r="OD1" t="s">
+        <v>728</v>
+      </c>
+      <c r="OE1" t="s">
+        <v>729</v>
+      </c>
+      <c r="OF1" t="s">
+        <v>730</v>
+      </c>
+      <c r="OG1" t="s">
+        <v>731</v>
+      </c>
+      <c r="OH1" t="s">
+        <v>732</v>
+      </c>
+      <c r="OI1" t="s">
+        <v>733</v>
+      </c>
+      <c r="OJ1" t="s">
+        <v>734</v>
+      </c>
+      <c r="OK1" t="s">
+        <v>735</v>
+      </c>
+      <c r="OL1" t="s">
+        <v>736</v>
+      </c>
+      <c r="OM1" t="s">
+        <v>737</v>
+      </c>
+      <c r="ON1" t="s">
+        <v>738</v>
+      </c>
+      <c r="OO1" t="s">
+        <v>739</v>
+      </c>
+      <c r="OP1" t="s">
+        <v>740</v>
+      </c>
+      <c r="OQ1" t="s">
+        <v>741</v>
+      </c>
+      <c r="OR1" t="s">
+        <v>296</v>
+      </c>
+      <c r="OS1" t="s">
+        <v>742</v>
+      </c>
+      <c r="OT1" t="s">
+        <v>297</v>
+      </c>
+      <c r="OU1" t="s">
+        <v>743</v>
+      </c>
+      <c r="OV1" t="s">
+        <v>744</v>
+      </c>
+      <c r="OW1" t="s">
+        <v>745</v>
+      </c>
+      <c r="OX1" t="s">
+        <v>746</v>
+      </c>
+      <c r="OY1" t="s">
+        <v>747</v>
+      </c>
+      <c r="OZ1" t="s">
         <v>771</v>
       </c>
-      <c r="JO1" t="s">
-        <v>699</v>
-      </c>
-      <c r="JP1" t="s">
-        <v>700</v>
-      </c>
-      <c r="JQ1" t="s">
-        <v>701</v>
-      </c>
-      <c r="JR1" t="s">
-        <v>702</v>
-      </c>
-      <c r="JS1" t="s">
-        <v>703</v>
-      </c>
-      <c r="JT1" t="s">
-        <v>772</v>
-      </c>
-      <c r="JU1" t="s">
-        <v>222</v>
-      </c>
-      <c r="JV1" t="s">
-        <v>223</v>
-      </c>
-      <c r="JW1" t="s">
-        <v>224</v>
-      </c>
-      <c r="JX1" t="s">
-        <v>225</v>
-      </c>
-      <c r="JY1" t="s">
-        <v>226</v>
-      </c>
-      <c r="JZ1" t="s">
-        <v>227</v>
-      </c>
-      <c r="KA1" t="s">
-        <v>228</v>
-      </c>
-      <c r="KB1" t="s">
-        <v>229</v>
-      </c>
-      <c r="KC1" t="s">
-        <v>230</v>
-      </c>
-      <c r="KD1" t="s">
-        <v>773</v>
-      </c>
-      <c r="KE1" t="s">
-        <v>231</v>
-      </c>
-      <c r="KF1" t="s">
-        <v>232</v>
-      </c>
-      <c r="KG1" t="s">
-        <v>233</v>
-      </c>
-      <c r="KH1" t="s">
-        <v>234</v>
-      </c>
-      <c r="KI1" t="s">
-        <v>235</v>
-      </c>
-      <c r="KJ1" t="s">
-        <v>704</v>
-      </c>
-      <c r="KK1" t="s">
-        <v>705</v>
-      </c>
-      <c r="KL1" t="s">
-        <v>706</v>
-      </c>
-      <c r="KM1" t="s">
-        <v>236</v>
-      </c>
-      <c r="KN1" t="s">
-        <v>774</v>
-      </c>
-      <c r="KO1" t="s">
-        <v>237</v>
-      </c>
-      <c r="KP1" t="s">
-        <v>238</v>
-      </c>
-      <c r="KQ1" t="s">
-        <v>239</v>
-      </c>
-      <c r="KR1" t="s">
-        <v>240</v>
-      </c>
-      <c r="KS1" t="s">
-        <v>241</v>
-      </c>
-      <c r="KT1" t="s">
-        <v>242</v>
-      </c>
-      <c r="KU1" t="s">
-        <v>775</v>
-      </c>
-      <c r="KV1" t="s">
-        <v>243</v>
-      </c>
-      <c r="KW1" t="s">
-        <v>244</v>
-      </c>
-      <c r="KX1" t="s">
-        <v>245</v>
-      </c>
-      <c r="KY1" t="s">
-        <v>246</v>
-      </c>
-      <c r="KZ1" t="s">
-        <v>247</v>
-      </c>
-      <c r="LA1" t="s">
-        <v>248</v>
-      </c>
-      <c r="LB1" t="s">
-        <v>249</v>
-      </c>
-      <c r="LC1" t="s">
-        <v>250</v>
-      </c>
-      <c r="LD1" t="s">
-        <v>251</v>
-      </c>
-      <c r="LE1" t="s">
-        <v>252</v>
-      </c>
-      <c r="LF1" t="s">
-        <v>253</v>
-      </c>
-      <c r="LG1" t="s">
-        <v>776</v>
-      </c>
-      <c r="LH1" t="s">
-        <v>254</v>
-      </c>
-      <c r="LI1" t="s">
-        <v>255</v>
-      </c>
-      <c r="LJ1" t="s">
-        <v>256</v>
-      </c>
-      <c r="LK1" t="s">
-        <v>257</v>
-      </c>
-      <c r="LL1" t="s">
-        <v>258</v>
-      </c>
-      <c r="LM1" t="s">
-        <v>259</v>
-      </c>
-      <c r="LN1" t="s">
-        <v>260</v>
-      </c>
-      <c r="LO1" t="s">
-        <v>261</v>
-      </c>
-      <c r="LP1" t="s">
-        <v>262</v>
-      </c>
-      <c r="LQ1" t="s">
-        <v>263</v>
-      </c>
-      <c r="LR1" t="s">
-        <v>264</v>
-      </c>
-      <c r="LS1" t="s">
-        <v>777</v>
-      </c>
-      <c r="LT1" t="s">
-        <v>265</v>
-      </c>
-      <c r="LU1" t="s">
-        <v>266</v>
-      </c>
-      <c r="LV1" t="s">
-        <v>267</v>
-      </c>
-      <c r="LW1" t="s">
-        <v>268</v>
-      </c>
-      <c r="LX1" t="s">
-        <v>269</v>
-      </c>
-      <c r="LY1" t="s">
-        <v>270</v>
-      </c>
-      <c r="LZ1" t="s">
-        <v>271</v>
-      </c>
-      <c r="MA1" t="s">
-        <v>272</v>
-      </c>
-      <c r="MB1" t="s">
-        <v>273</v>
-      </c>
-      <c r="MC1" t="s">
-        <v>274</v>
-      </c>
-      <c r="MD1" t="s">
-        <v>707</v>
-      </c>
-      <c r="ME1" t="s">
-        <v>778</v>
-      </c>
-      <c r="MF1" t="s">
-        <v>708</v>
-      </c>
-      <c r="MG1" t="s">
-        <v>709</v>
-      </c>
-      <c r="MH1" t="s">
-        <v>710</v>
-      </c>
-      <c r="MI1" t="s">
-        <v>711</v>
-      </c>
-      <c r="MJ1" t="s">
-        <v>712</v>
-      </c>
-      <c r="MK1" t="s">
-        <v>713</v>
-      </c>
-      <c r="ML1" t="s">
-        <v>714</v>
-      </c>
-      <c r="MM1" t="s">
-        <v>715</v>
-      </c>
-      <c r="MN1" t="s">
-        <v>716</v>
-      </c>
-      <c r="MO1" t="s">
-        <v>717</v>
-      </c>
-      <c r="MP1" t="s">
-        <v>718</v>
-      </c>
-      <c r="MQ1" t="s">
+      <c r="PA1" t="s">
+        <v>748</v>
+      </c>
+      <c r="PB1" t="s">
+        <v>749</v>
+      </c>
+      <c r="PC1" t="s">
+        <v>750</v>
+      </c>
+      <c r="PD1" t="s">
+        <v>751</v>
+      </c>
+      <c r="PE1" t="s">
+        <v>752</v>
+      </c>
+      <c r="PF1" t="s">
+        <v>857</v>
+      </c>
+      <c r="PG1" t="s">
+        <v>298</v>
+      </c>
+      <c r="PH1" t="s">
+        <v>858</v>
+      </c>
+      <c r="PI1" t="s">
+        <v>859</v>
+      </c>
+      <c r="PJ1" t="s">
+        <v>299</v>
+      </c>
+      <c r="PK1" t="s">
+        <v>860</v>
+      </c>
+      <c r="PL1" t="s">
+        <v>861</v>
+      </c>
+      <c r="PM1" t="s">
+        <v>300</v>
+      </c>
+      <c r="PN1" t="s">
+        <v>862</v>
+      </c>
+      <c r="PO1" t="s">
+        <v>863</v>
+      </c>
+      <c r="PP1" t="s">
+        <v>301</v>
+      </c>
+      <c r="PQ1" t="s">
+        <v>864</v>
+      </c>
+      <c r="PR1" t="s">
+        <v>865</v>
+      </c>
+      <c r="PS1" t="s">
+        <v>302</v>
+      </c>
+      <c r="PT1" t="s">
+        <v>866</v>
+      </c>
+      <c r="PU1" t="s">
+        <v>867</v>
+      </c>
+      <c r="PV1" t="s">
+        <v>303</v>
+      </c>
+      <c r="PW1" t="s">
+        <v>868</v>
+      </c>
+      <c r="PX1" t="s">
+        <v>869</v>
+      </c>
+      <c r="PY1" t="s">
+        <v>304</v>
+      </c>
+      <c r="PZ1" t="s">
+        <v>305</v>
+      </c>
+      <c r="QA1" t="s">
+        <v>306</v>
+      </c>
+      <c r="QB1" t="s">
+        <v>307</v>
+      </c>
+      <c r="QC1" t="s">
+        <v>308</v>
+      </c>
+      <c r="QD1" t="s">
+        <v>309</v>
+      </c>
+      <c r="QE1" t="s">
+        <v>753</v>
+      </c>
+      <c r="QF1" t="s">
+        <v>754</v>
+      </c>
+      <c r="QG1" t="s">
+        <v>310</v>
+      </c>
+      <c r="QH1" t="s">
+        <v>311</v>
+      </c>
+      <c r="QI1" t="s">
+        <v>312</v>
+      </c>
+      <c r="QJ1" t="s">
+        <v>313</v>
+      </c>
+      <c r="QK1" t="s">
+        <v>314</v>
+      </c>
+      <c r="QL1" t="s">
+        <v>315</v>
+      </c>
+      <c r="QM1" t="s">
+        <v>316</v>
+      </c>
+      <c r="QN1" t="s">
+        <v>317</v>
+      </c>
+      <c r="QO1" t="s">
+        <v>318</v>
+      </c>
+      <c r="QP1" t="s">
+        <v>319</v>
+      </c>
+      <c r="QQ1" t="s">
+        <v>320</v>
+      </c>
+      <c r="QR1" t="s">
+        <v>321</v>
+      </c>
+      <c r="QS1" t="s">
+        <v>870</v>
+      </c>
+      <c r="QT1" t="s">
+        <v>322</v>
+      </c>
+      <c r="QU1" t="s">
+        <v>323</v>
+      </c>
+      <c r="QV1" t="s">
+        <v>324</v>
+      </c>
+      <c r="QW1" t="s">
+        <v>325</v>
+      </c>
+      <c r="QX1" t="s">
+        <v>326</v>
+      </c>
+      <c r="QY1" t="s">
+        <v>327</v>
+      </c>
+      <c r="QZ1" t="s">
+        <v>328</v>
+      </c>
+      <c r="RA1" t="s">
+        <v>329</v>
+      </c>
+      <c r="RB1" t="s">
+        <v>330</v>
+      </c>
+      <c r="RC1" t="s">
+        <v>331</v>
+      </c>
+      <c r="RD1" t="s">
+        <v>332</v>
+      </c>
+      <c r="RE1" t="s">
+        <v>333</v>
+      </c>
+      <c r="RF1" t="s">
+        <v>871</v>
+      </c>
+      <c r="RG1" t="s">
+        <v>334</v>
+      </c>
+      <c r="RH1" t="s">
+        <v>335</v>
+      </c>
+      <c r="RI1" t="s">
+        <v>336</v>
+      </c>
+      <c r="RJ1" t="s">
+        <v>337</v>
+      </c>
+      <c r="RK1" t="s">
+        <v>338</v>
+      </c>
+      <c r="RL1" t="s">
+        <v>339</v>
+      </c>
+      <c r="RM1" t="s">
+        <v>340</v>
+      </c>
+      <c r="RN1" t="s">
+        <v>341</v>
+      </c>
+      <c r="RO1" t="s">
+        <v>342</v>
+      </c>
+      <c r="RP1" t="s">
+        <v>343</v>
+      </c>
+      <c r="RQ1" t="s">
+        <v>344</v>
+      </c>
+      <c r="RR1" t="s">
+        <v>345</v>
+      </c>
+      <c r="RS1" t="s">
+        <v>872</v>
+      </c>
+      <c r="RT1" t="s">
+        <v>346</v>
+      </c>
+      <c r="RU1" t="s">
+        <v>347</v>
+      </c>
+      <c r="RV1" t="s">
+        <v>348</v>
+      </c>
+      <c r="RW1" t="s">
+        <v>349</v>
+      </c>
+      <c r="RX1" t="s">
+        <v>350</v>
+      </c>
+      <c r="RY1" t="s">
+        <v>351</v>
+      </c>
+      <c r="RZ1" t="s">
+        <v>352</v>
+      </c>
+      <c r="SA1" t="s">
+        <v>353</v>
+      </c>
+      <c r="SB1" t="s">
+        <v>354</v>
+      </c>
+      <c r="SC1" t="s">
+        <v>355</v>
+      </c>
+      <c r="SD1" t="s">
+        <v>356</v>
+      </c>
+      <c r="SE1" t="s">
+        <v>357</v>
+      </c>
+      <c r="SF1" t="s">
+        <v>873</v>
+      </c>
+      <c r="SG1" t="s">
+        <v>358</v>
+      </c>
+      <c r="SH1" t="s">
+        <v>755</v>
+      </c>
+      <c r="SI1" t="s">
+        <v>359</v>
+      </c>
+      <c r="SJ1" t="s">
+        <v>360</v>
+      </c>
+      <c r="SK1" t="s">
+        <v>361</v>
+      </c>
+      <c r="SL1" t="s">
+        <v>362</v>
+      </c>
+      <c r="SM1" t="s">
+        <v>363</v>
+      </c>
+      <c r="SN1" t="s">
+        <v>364</v>
+      </c>
+      <c r="SO1" t="s">
+        <v>365</v>
+      </c>
+      <c r="SP1" t="s">
+        <v>366</v>
+      </c>
+      <c r="SQ1" t="s">
+        <v>756</v>
+      </c>
+      <c r="SR1" t="s">
+        <v>757</v>
+      </c>
+      <c r="SS1" t="s">
+        <v>758</v>
+      </c>
+      <c r="ST1" t="s">
+        <v>759</v>
+      </c>
+      <c r="SU1" t="s">
+        <v>367</v>
+      </c>
+      <c r="SV1" t="s">
+        <v>368</v>
+      </c>
+      <c r="SW1" t="s">
+        <v>369</v>
+      </c>
+      <c r="SX1" t="s">
+        <v>370</v>
+      </c>
+      <c r="SY1" t="s">
+        <v>371</v>
+      </c>
+      <c r="SZ1" t="s">
+        <v>874</v>
+      </c>
+      <c r="TA1" t="s">
+        <v>372</v>
+      </c>
+      <c r="TB1" t="s">
+        <v>373</v>
+      </c>
+      <c r="TC1" t="s">
+        <v>374</v>
+      </c>
+      <c r="TD1" t="s">
+        <v>375</v>
+      </c>
+      <c r="TE1" t="s">
+        <v>376</v>
+      </c>
+      <c r="TF1" t="s">
+        <v>377</v>
+      </c>
+      <c r="TG1" t="s">
+        <v>378</v>
+      </c>
+      <c r="TH1" t="s">
+        <v>379</v>
+      </c>
+      <c r="TI1" t="s">
+        <v>380</v>
+      </c>
+      <c r="TJ1" t="s">
+        <v>381</v>
+      </c>
+      <c r="TK1" t="s">
+        <v>382</v>
+      </c>
+      <c r="TL1" t="s">
+        <v>383</v>
+      </c>
+      <c r="TM1" t="s">
+        <v>384</v>
+      </c>
+      <c r="TN1" t="s">
+        <v>385</v>
+      </c>
+      <c r="TO1" t="s">
+        <v>386</v>
+      </c>
+      <c r="TP1" t="s">
+        <v>387</v>
+      </c>
+      <c r="TQ1" t="s">
+        <v>388</v>
+      </c>
+      <c r="TR1" t="s">
+        <v>389</v>
+      </c>
+      <c r="TS1" t="s">
+        <v>390</v>
+      </c>
+      <c r="TT1" t="s">
+        <v>391</v>
+      </c>
+      <c r="TU1" t="s">
+        <v>392</v>
+      </c>
+      <c r="TV1" t="s">
+        <v>393</v>
+      </c>
+      <c r="TW1" t="s">
+        <v>394</v>
+      </c>
+      <c r="TX1" t="s">
+        <v>395</v>
+      </c>
+      <c r="TY1" t="s">
+        <v>396</v>
+      </c>
+      <c r="TZ1" t="s">
+        <v>397</v>
+      </c>
+      <c r="UA1" t="s">
+        <v>398</v>
+      </c>
+      <c r="UB1" t="s">
+        <v>399</v>
+      </c>
+      <c r="UC1" t="s">
+        <v>400</v>
+      </c>
+      <c r="UD1" t="s">
+        <v>401</v>
+      </c>
+      <c r="UE1" t="s">
+        <v>402</v>
+      </c>
+      <c r="UF1" t="s">
+        <v>403</v>
+      </c>
+      <c r="UG1" t="s">
+        <v>404</v>
+      </c>
+      <c r="UH1" t="s">
+        <v>405</v>
+      </c>
+      <c r="UI1" t="s">
+        <v>406</v>
+      </c>
+      <c r="UJ1" t="s">
+        <v>407</v>
+      </c>
+      <c r="UK1" t="s">
+        <v>408</v>
+      </c>
+      <c r="UL1" t="s">
+        <v>875</v>
+      </c>
+      <c r="UM1" t="s">
+        <v>876</v>
+      </c>
+      <c r="UN1" t="s">
+        <v>877</v>
+      </c>
+      <c r="UO1" t="s">
+        <v>878</v>
+      </c>
+      <c r="UP1" t="s">
+        <v>879</v>
+      </c>
+      <c r="UQ1" t="s">
+        <v>880</v>
+      </c>
+      <c r="UR1" t="s">
+        <v>409</v>
+      </c>
+      <c r="US1" t="s">
+        <v>410</v>
+      </c>
+      <c r="UT1" t="s">
+        <v>411</v>
+      </c>
+      <c r="UU1" t="s">
+        <v>412</v>
+      </c>
+      <c r="UV1" t="s">
         <v>779</v>
       </c>
-      <c r="MR1" t="s">
-        <v>275</v>
-      </c>
-      <c r="MS1" t="s">
-        <v>276</v>
-      </c>
-      <c r="MT1" t="s">
-        <v>277</v>
-      </c>
-      <c r="MU1" t="s">
-        <v>278</v>
-      </c>
-      <c r="MV1" t="s">
-        <v>279</v>
-      </c>
-      <c r="MW1" t="s">
-        <v>280</v>
-      </c>
-      <c r="MX1" t="s">
-        <v>281</v>
-      </c>
-      <c r="MY1" t="s">
-        <v>282</v>
-      </c>
-      <c r="MZ1" t="s">
-        <v>283</v>
-      </c>
-      <c r="NA1" t="s">
-        <v>284</v>
-      </c>
-      <c r="NB1" t="s">
-        <v>285</v>
-      </c>
-      <c r="NC1" t="s">
+      <c r="UW1" t="s">
+        <v>881</v>
+      </c>
+      <c r="UX1" t="s">
+        <v>882</v>
+      </c>
+      <c r="UY1" t="s">
+        <v>413</v>
+      </c>
+      <c r="UZ1" t="s">
+        <v>414</v>
+      </c>
+      <c r="VA1" t="s">
+        <v>415</v>
+      </c>
+      <c r="VB1" t="s">
+        <v>416</v>
+      </c>
+      <c r="VC1" t="s">
+        <v>417</v>
+      </c>
+      <c r="VD1" t="s">
+        <v>418</v>
+      </c>
+      <c r="VE1" t="s">
+        <v>419</v>
+      </c>
+      <c r="VF1" t="s">
+        <v>420</v>
+      </c>
+      <c r="VG1" t="s">
+        <v>421</v>
+      </c>
+      <c r="VH1" t="s">
+        <v>422</v>
+      </c>
+      <c r="VI1" t="s">
+        <v>423</v>
+      </c>
+      <c r="VJ1" t="s">
+        <v>424</v>
+      </c>
+      <c r="VK1" t="s">
+        <v>425</v>
+      </c>
+      <c r="VL1" t="s">
+        <v>426</v>
+      </c>
+      <c r="VM1" t="s">
+        <v>427</v>
+      </c>
+      <c r="VN1" t="s">
+        <v>428</v>
+      </c>
+      <c r="VO1" t="s">
+        <v>429</v>
+      </c>
+      <c r="VP1" t="s">
+        <v>430</v>
+      </c>
+      <c r="VQ1" t="s">
+        <v>431</v>
+      </c>
+      <c r="VR1" t="s">
+        <v>432</v>
+      </c>
+      <c r="VS1" t="s">
+        <v>433</v>
+      </c>
+      <c r="VT1" t="s">
+        <v>434</v>
+      </c>
+      <c r="VU1" t="s">
+        <v>435</v>
+      </c>
+      <c r="VV1" t="s">
+        <v>436</v>
+      </c>
+      <c r="VW1" t="s">
+        <v>437</v>
+      </c>
+      <c r="VX1" t="s">
+        <v>438</v>
+      </c>
+      <c r="VY1" t="s">
+        <v>439</v>
+      </c>
+      <c r="VZ1" t="s">
+        <v>440</v>
+      </c>
+      <c r="WA1" t="s">
+        <v>441</v>
+      </c>
+      <c r="WB1" t="s">
+        <v>442</v>
+      </c>
+      <c r="WC1" t="s">
+        <v>443</v>
+      </c>
+      <c r="WD1" t="s">
+        <v>444</v>
+      </c>
+      <c r="WE1" t="s">
+        <v>445</v>
+      </c>
+      <c r="WF1" t="s">
+        <v>446</v>
+      </c>
+      <c r="WG1" t="s">
+        <v>447</v>
+      </c>
+      <c r="WH1" t="s">
+        <v>448</v>
+      </c>
+      <c r="WI1" t="s">
+        <v>449</v>
+      </c>
+      <c r="WJ1" t="s">
+        <v>450</v>
+      </c>
+      <c r="WK1" t="s">
+        <v>17</v>
+      </c>
+      <c r="WL1" t="s">
+        <v>451</v>
+      </c>
+      <c r="WM1" t="s">
+        <v>452</v>
+      </c>
+      <c r="WN1" t="s">
+        <v>453</v>
+      </c>
+      <c r="WO1" t="s">
+        <v>454</v>
+      </c>
+      <c r="WP1" t="s">
+        <v>455</v>
+      </c>
+      <c r="WQ1" t="s">
+        <v>456</v>
+      </c>
+      <c r="WR1" t="s">
+        <v>457</v>
+      </c>
+      <c r="WS1" t="s">
+        <v>458</v>
+      </c>
+      <c r="WT1" t="s">
+        <v>459</v>
+      </c>
+      <c r="WU1" t="s">
+        <v>460</v>
+      </c>
+      <c r="WV1" t="s">
+        <v>461</v>
+      </c>
+      <c r="WW1" t="s">
+        <v>462</v>
+      </c>
+      <c r="WX1" t="s">
+        <v>463</v>
+      </c>
+      <c r="WY1" t="s">
+        <v>464</v>
+      </c>
+      <c r="WZ1" t="s">
+        <v>465</v>
+      </c>
+      <c r="XA1" t="s">
+        <v>466</v>
+      </c>
+      <c r="XB1" t="s">
+        <v>467</v>
+      </c>
+      <c r="XC1" t="s">
+        <v>468</v>
+      </c>
+      <c r="XD1" t="s">
+        <v>469</v>
+      </c>
+      <c r="XE1" t="s">
+        <v>470</v>
+      </c>
+      <c r="XF1" t="s">
+        <v>471</v>
+      </c>
+      <c r="XG1" t="s">
+        <v>472</v>
+      </c>
+      <c r="XH1" t="s">
+        <v>473</v>
+      </c>
+      <c r="XI1" t="s">
+        <v>474</v>
+      </c>
+      <c r="XJ1" t="s">
+        <v>475</v>
+      </c>
+      <c r="XK1" t="s">
+        <v>476</v>
+      </c>
+      <c r="XL1" t="s">
+        <v>477</v>
+      </c>
+      <c r="XM1" t="s">
+        <v>478</v>
+      </c>
+      <c r="XN1" t="s">
+        <v>479</v>
+      </c>
+      <c r="XO1" t="s">
+        <v>480</v>
+      </c>
+      <c r="XP1" t="s">
+        <v>481</v>
+      </c>
+      <c r="XQ1" t="s">
+        <v>482</v>
+      </c>
+      <c r="XR1" t="s">
+        <v>483</v>
+      </c>
+      <c r="XS1" t="s">
+        <v>484</v>
+      </c>
+      <c r="XT1" t="s">
+        <v>485</v>
+      </c>
+      <c r="XU1" t="s">
+        <v>486</v>
+      </c>
+      <c r="XV1" t="s">
+        <v>487</v>
+      </c>
+      <c r="XW1" t="s">
+        <v>488</v>
+      </c>
+      <c r="XX1" t="s">
+        <v>489</v>
+      </c>
+      <c r="XY1" t="s">
+        <v>490</v>
+      </c>
+      <c r="XZ1" t="s">
+        <v>491</v>
+      </c>
+      <c r="YA1" t="s">
+        <v>492</v>
+      </c>
+      <c r="YB1" t="s">
+        <v>493</v>
+      </c>
+      <c r="YC1" t="s">
+        <v>494</v>
+      </c>
+      <c r="YD1" t="s">
+        <v>495</v>
+      </c>
+      <c r="YE1" t="s">
+        <v>496</v>
+      </c>
+      <c r="YF1" t="s">
+        <v>497</v>
+      </c>
+      <c r="YG1" t="s">
+        <v>498</v>
+      </c>
+      <c r="YH1" t="s">
+        <v>499</v>
+      </c>
+      <c r="YI1" t="s">
+        <v>500</v>
+      </c>
+      <c r="YJ1" t="s">
+        <v>501</v>
+      </c>
+      <c r="YK1" t="s">
+        <v>502</v>
+      </c>
+      <c r="YL1" t="s">
+        <v>503</v>
+      </c>
+      <c r="YM1" t="s">
+        <v>504</v>
+      </c>
+      <c r="YN1" t="s">
+        <v>505</v>
+      </c>
+      <c r="YO1" t="s">
+        <v>506</v>
+      </c>
+      <c r="YP1" t="s">
+        <v>507</v>
+      </c>
+      <c r="YQ1" t="s">
+        <v>508</v>
+      </c>
+      <c r="YR1" t="s">
+        <v>509</v>
+      </c>
+      <c r="YS1" t="s">
+        <v>510</v>
+      </c>
+      <c r="YT1" t="s">
+        <v>511</v>
+      </c>
+      <c r="YU1" t="s">
+        <v>512</v>
+      </c>
+      <c r="YV1" t="s">
+        <v>513</v>
+      </c>
+      <c r="YW1" t="s">
+        <v>514</v>
+      </c>
+      <c r="YX1" t="s">
+        <v>515</v>
+      </c>
+      <c r="YY1" t="s">
+        <v>516</v>
+      </c>
+      <c r="YZ1" t="s">
+        <v>517</v>
+      </c>
+      <c r="ZA1" t="s">
+        <v>518</v>
+      </c>
+      <c r="ZB1" t="s">
+        <v>519</v>
+      </c>
+      <c r="ZC1" t="s">
+        <v>520</v>
+      </c>
+      <c r="ZD1" t="s">
+        <v>521</v>
+      </c>
+      <c r="ZE1" t="s">
+        <v>522</v>
+      </c>
+      <c r="ZF1" t="s">
+        <v>523</v>
+      </c>
+      <c r="ZG1" t="s">
+        <v>524</v>
+      </c>
+      <c r="ZH1" t="s">
+        <v>525</v>
+      </c>
+      <c r="ZI1" t="s">
+        <v>526</v>
+      </c>
+      <c r="ZJ1" t="s">
+        <v>527</v>
+      </c>
+      <c r="ZK1" t="s">
+        <v>528</v>
+      </c>
+      <c r="ZL1" t="s">
+        <v>529</v>
+      </c>
+      <c r="ZM1" t="s">
+        <v>530</v>
+      </c>
+      <c r="ZN1" t="s">
+        <v>531</v>
+      </c>
+      <c r="ZO1" t="s">
+        <v>532</v>
+      </c>
+      <c r="ZP1" t="s">
+        <v>533</v>
+      </c>
+      <c r="ZQ1" t="s">
+        <v>534</v>
+      </c>
+      <c r="ZR1" t="s">
+        <v>535</v>
+      </c>
+      <c r="ZS1" t="s">
+        <v>536</v>
+      </c>
+      <c r="ZT1" t="s">
+        <v>883</v>
+      </c>
+      <c r="ZU1" t="s">
+        <v>537</v>
+      </c>
+      <c r="ZV1" t="s">
+        <v>538</v>
+      </c>
+      <c r="ZW1" t="s">
+        <v>539</v>
+      </c>
+      <c r="ZX1" t="s">
+        <v>540</v>
+      </c>
+      <c r="ZY1" t="s">
+        <v>541</v>
+      </c>
+      <c r="ZZ1" t="s">
+        <v>884</v>
+      </c>
+      <c r="AAA1" t="s">
+        <v>542</v>
+      </c>
+      <c r="AAB1" t="s">
+        <v>543</v>
+      </c>
+      <c r="AAC1" t="s">
+        <v>544</v>
+      </c>
+      <c r="AAD1" t="s">
+        <v>545</v>
+      </c>
+      <c r="AAE1" t="s">
+        <v>546</v>
+      </c>
+      <c r="AAF1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AAG1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AAH1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AAI1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AAJ1" t="s">
+        <v>760</v>
+      </c>
+      <c r="AAK1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AAL1" t="s">
+        <v>761</v>
+      </c>
+      <c r="AAM1" t="s">
+        <v>762</v>
+      </c>
+      <c r="AAN1" t="s">
+        <v>763</v>
+      </c>
+      <c r="AAO1" t="s">
+        <v>764</v>
+      </c>
+      <c r="AAP1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AAQ1" t="s">
+        <v>885</v>
+      </c>
+      <c r="AAR1" t="s">
+        <v>547</v>
+      </c>
+      <c r="AAS1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AAT1" t="s">
+        <v>548</v>
+      </c>
+      <c r="AAU1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AAV1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AAW1" t="s">
+        <v>550</v>
+      </c>
+      <c r="AAX1" t="s">
+        <v>551</v>
+      </c>
+      <c r="AAY1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AAZ1" t="s">
+        <v>886</v>
+      </c>
+      <c r="ABA1" t="s">
+        <v>552</v>
+      </c>
+      <c r="ABB1" t="s">
+        <v>115</v>
+      </c>
+      <c r="ABC1" t="s">
+        <v>553</v>
+      </c>
+      <c r="ABD1" t="s">
+        <v>554</v>
+      </c>
+      <c r="ABE1" t="s">
+        <v>555</v>
+      </c>
+      <c r="ABF1" t="s">
+        <v>556</v>
+      </c>
+      <c r="ABG1" t="s">
+        <v>557</v>
+      </c>
+      <c r="ABH1" t="s">
+        <v>558</v>
+      </c>
+      <c r="ABI1" t="s">
+        <v>559</v>
+      </c>
+      <c r="ABJ1" t="s">
+        <v>116</v>
+      </c>
+      <c r="ABK1" t="s">
+        <v>560</v>
+      </c>
+      <c r="ABL1" t="s">
+        <v>561</v>
+      </c>
+      <c r="ABM1" t="s">
+        <v>562</v>
+      </c>
+      <c r="ABN1" t="s">
+        <v>563</v>
+      </c>
+      <c r="ABO1" t="s">
+        <v>564</v>
+      </c>
+      <c r="ABP1" t="s">
+        <v>565</v>
+      </c>
+      <c r="ABQ1" t="s">
+        <v>566</v>
+      </c>
+      <c r="ABR1" t="s">
+        <v>567</v>
+      </c>
+      <c r="ABS1" t="s">
+        <v>568</v>
+      </c>
+      <c r="ABT1" t="s">
+        <v>569</v>
+      </c>
+      <c r="ABU1" t="s">
+        <v>570</v>
+      </c>
+      <c r="ABV1" t="s">
+        <v>571</v>
+      </c>
+      <c r="ABW1" t="s">
+        <v>572</v>
+      </c>
+      <c r="ABX1" t="s">
+        <v>573</v>
+      </c>
+      <c r="ABY1" t="s">
+        <v>574</v>
+      </c>
+      <c r="ABZ1" t="s">
+        <v>575</v>
+      </c>
+      <c r="ACA1" t="s">
+        <v>576</v>
+      </c>
+      <c r="ACB1" t="s">
+        <v>577</v>
+      </c>
+      <c r="ACC1" t="s">
+        <v>578</v>
+      </c>
+      <c r="ACD1" t="s">
+        <v>579</v>
+      </c>
+      <c r="ACE1" t="s">
+        <v>580</v>
+      </c>
+      <c r="ACF1" t="s">
+        <v>581</v>
+      </c>
+      <c r="ACG1" t="s">
+        <v>582</v>
+      </c>
+      <c r="ACH1" t="s">
+        <v>583</v>
+      </c>
+      <c r="ACI1" t="s">
+        <v>584</v>
+      </c>
+      <c r="ACJ1" t="s">
+        <v>585</v>
+      </c>
+      <c r="ACK1" t="s">
+        <v>586</v>
+      </c>
+      <c r="ACL1" t="s">
+        <v>587</v>
+      </c>
+      <c r="ACM1" t="s">
+        <v>588</v>
+      </c>
+      <c r="ACN1" t="s">
+        <v>589</v>
+      </c>
+      <c r="ACO1" t="s">
+        <v>590</v>
+      </c>
+      <c r="ACP1" t="s">
+        <v>591</v>
+      </c>
+      <c r="ACQ1" t="s">
+        <v>592</v>
+      </c>
+      <c r="ACR1" t="s">
+        <v>593</v>
+      </c>
+      <c r="ACS1" t="s">
+        <v>594</v>
+      </c>
+      <c r="ACT1" t="s">
+        <v>595</v>
+      </c>
+      <c r="ACU1" t="s">
+        <v>596</v>
+      </c>
+      <c r="ACV1" t="s">
+        <v>597</v>
+      </c>
+      <c r="ACW1" t="s">
+        <v>598</v>
+      </c>
+      <c r="ACX1" t="s">
+        <v>599</v>
+      </c>
+      <c r="ACY1" t="s">
+        <v>600</v>
+      </c>
+      <c r="ACZ1" t="s">
+        <v>601</v>
+      </c>
+      <c r="ADA1" t="s">
+        <v>602</v>
+      </c>
+      <c r="ADB1" t="s">
+        <v>603</v>
+      </c>
+      <c r="ADC1" t="s">
+        <v>604</v>
+      </c>
+      <c r="ADD1" t="s">
+        <v>605</v>
+      </c>
+      <c r="ADE1" t="s">
+        <v>606</v>
+      </c>
+      <c r="ADF1" t="s">
+        <v>607</v>
+      </c>
+      <c r="ADG1" t="s">
+        <v>608</v>
+      </c>
+      <c r="ADH1" t="s">
+        <v>609</v>
+      </c>
+      <c r="ADI1" t="s">
+        <v>610</v>
+      </c>
+      <c r="ADJ1" t="s">
+        <v>611</v>
+      </c>
+      <c r="ADK1" t="s">
+        <v>612</v>
+      </c>
+      <c r="ADL1" t="s">
+        <v>887</v>
+      </c>
+      <c r="ADM1" t="s">
+        <v>888</v>
+      </c>
+      <c r="ADN1" t="s">
+        <v>614</v>
+      </c>
+      <c r="ADO1" t="s">
+        <v>615</v>
+      </c>
+      <c r="ADP1" t="s">
+        <v>889</v>
+      </c>
+      <c r="ADQ1" t="s">
+        <v>890</v>
+      </c>
+      <c r="ADR1" t="s">
+        <v>617</v>
+      </c>
+      <c r="ADS1" t="s">
+        <v>618</v>
+      </c>
+      <c r="ADT1" t="s">
+        <v>891</v>
+      </c>
+      <c r="ADU1" t="s">
+        <v>620</v>
+      </c>
+      <c r="ADV1" t="s">
+        <v>621</v>
+      </c>
+      <c r="ADW1" t="s">
+        <v>622</v>
+      </c>
+      <c r="ADX1" t="s">
+        <v>623</v>
+      </c>
+      <c r="ADY1" t="s">
+        <v>624</v>
+      </c>
+      <c r="ADZ1" t="s">
+        <v>625</v>
+      </c>
+      <c r="AEA1" t="s">
+        <v>626</v>
+      </c>
+      <c r="AEB1" t="s">
+        <v>627</v>
+      </c>
+      <c r="AEC1" t="s">
+        <v>628</v>
+      </c>
+      <c r="AED1" t="s">
+        <v>629</v>
+      </c>
+      <c r="AEE1" t="s">
+        <v>630</v>
+      </c>
+      <c r="AEF1" t="s">
+        <v>631</v>
+      </c>
+      <c r="AEG1" t="s">
+        <v>632</v>
+      </c>
+      <c r="AEH1" t="s">
+        <v>892</v>
+      </c>
+      <c r="AEI1" t="s">
+        <v>633</v>
+      </c>
+      <c r="AEJ1" t="s">
+        <v>634</v>
+      </c>
+      <c r="AEK1" t="s">
+        <v>635</v>
+      </c>
+      <c r="AEL1" t="s">
+        <v>636</v>
+      </c>
+      <c r="AEM1" t="s">
+        <v>637</v>
+      </c>
+      <c r="AEN1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AEO1" t="s">
+        <v>639</v>
+      </c>
+      <c r="AEP1" t="s">
+        <v>640</v>
+      </c>
+      <c r="AEQ1" t="s">
+        <v>641</v>
+      </c>
+      <c r="AER1" t="s">
+        <v>642</v>
+      </c>
+      <c r="AES1" t="s">
+        <v>643</v>
+      </c>
+      <c r="AET1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="2" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B2" t="s">
         <v>780</v>
       </c>
-      <c r="ND1" t="s">
-        <v>286</v>
-      </c>
-      <c r="NE1" t="s">
-        <v>287</v>
-      </c>
-      <c r="NF1" t="s">
-        <v>288</v>
-      </c>
-      <c r="NG1" t="s">
-        <v>289</v>
-      </c>
-      <c r="NH1" t="s">
-        <v>290</v>
-      </c>
-      <c r="NI1" t="s">
-        <v>291</v>
-      </c>
-      <c r="NJ1" t="s">
-        <v>292</v>
-      </c>
-      <c r="NK1" t="s">
-        <v>293</v>
-      </c>
-      <c r="NL1" t="s">
-        <v>294</v>
-      </c>
-      <c r="NM1" t="s">
-        <v>295</v>
-      </c>
-      <c r="NN1" t="s">
-        <v>719</v>
-      </c>
-      <c r="NO1" t="s">
-        <v>720</v>
-      </c>
-      <c r="NP1" t="s">
-        <v>721</v>
-      </c>
-      <c r="NQ1" t="s">
-        <v>722</v>
-      </c>
-      <c r="NR1" t="s">
-        <v>723</v>
-      </c>
-      <c r="NS1" t="s">
-        <v>724</v>
-      </c>
-      <c r="NT1" t="s">
-        <v>725</v>
-      </c>
-      <c r="NU1" t="s">
-        <v>726</v>
-      </c>
-      <c r="NV1" t="s">
-        <v>727</v>
-      </c>
-      <c r="NW1" t="s">
-        <v>728</v>
-      </c>
-      <c r="NX1" t="s">
-        <v>729</v>
-      </c>
-      <c r="NY1" t="s">
-        <v>730</v>
-      </c>
-      <c r="NZ1" t="s">
-        <v>731</v>
-      </c>
-      <c r="OA1" t="s">
-        <v>732</v>
-      </c>
-      <c r="OB1" t="s">
-        <v>733</v>
-      </c>
-      <c r="OC1" t="s">
-        <v>734</v>
-      </c>
-      <c r="OD1" t="s">
-        <v>735</v>
-      </c>
-      <c r="OE1" t="s">
-        <v>736</v>
-      </c>
-      <c r="OF1" t="s">
-        <v>737</v>
-      </c>
-      <c r="OG1" t="s">
-        <v>738</v>
-      </c>
-      <c r="OH1" t="s">
-        <v>739</v>
-      </c>
-      <c r="OI1" t="s">
-        <v>740</v>
-      </c>
-      <c r="OJ1" t="s">
-        <v>741</v>
-      </c>
-      <c r="OK1" t="s">
-        <v>296</v>
-      </c>
-      <c r="OL1" t="s">
-        <v>742</v>
-      </c>
-      <c r="OM1" t="s">
-        <v>297</v>
-      </c>
-      <c r="ON1" t="s">
-        <v>743</v>
-      </c>
-      <c r="OO1" t="s">
-        <v>744</v>
-      </c>
-      <c r="OP1" t="s">
-        <v>745</v>
-      </c>
-      <c r="OQ1" t="s">
-        <v>746</v>
-      </c>
-      <c r="OR1" t="s">
-        <v>747</v>
-      </c>
-      <c r="OS1" t="s">
+      <c r="C2" t="s">
         <v>781</v>
       </c>
-      <c r="OT1" t="s">
-        <v>748</v>
-      </c>
-      <c r="OU1" t="s">
-        <v>749</v>
-      </c>
-      <c r="OV1" t="s">
-        <v>750</v>
-      </c>
-      <c r="OW1" t="s">
-        <v>751</v>
-      </c>
-      <c r="OX1" t="s">
-        <v>752</v>
-      </c>
-      <c r="OY1" t="s">
+      <c r="D2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E2" t="s">
         <v>782</v>
       </c>
-      <c r="OZ1" t="s">
-        <v>298</v>
-      </c>
-      <c r="PA1" t="s">
+      <c r="F2" t="s">
         <v>783</v>
       </c>
-      <c r="PB1" t="s">
+      <c r="G2" t="s">
         <v>784</v>
       </c>
-      <c r="PC1" t="s">
-        <v>299</v>
-      </c>
-      <c r="PD1" t="s">
+      <c r="Q2">
+        <v>9</v>
+      </c>
+      <c r="R2">
+        <v>9</v>
+      </c>
+      <c r="S2" t="s">
         <v>785</v>
       </c>
-      <c r="PE1" t="s">
+      <c r="T2">
+        <v>9</v>
+      </c>
+      <c r="U2">
+        <v>11</v>
+      </c>
+      <c r="V2">
+        <v>12</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>785</v>
+      </c>
+      <c r="Z2" t="s">
         <v>786</v>
       </c>
-      <c r="PF1" t="s">
-        <v>300</v>
-      </c>
-      <c r="PG1" t="s">
+      <c r="AH2" t="s">
         <v>787</v>
       </c>
-      <c r="PH1" t="s">
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="s">
         <v>788</v>
       </c>
-      <c r="PI1" t="s">
-        <v>301</v>
-      </c>
-      <c r="PJ1" t="s">
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="s">
         <v>789</v>
       </c>
-      <c r="PK1" t="s">
+      <c r="AS2" t="s">
         <v>790</v>
       </c>
-      <c r="PL1" t="s">
-        <v>302</v>
-      </c>
-      <c r="PM1" t="s">
+      <c r="AU2" t="s">
         <v>791</v>
       </c>
-      <c r="PN1" t="s">
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="s">
         <v>792</v>
       </c>
-      <c r="PO1" t="s">
-        <v>303</v>
-      </c>
-      <c r="PP1" t="s">
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>1</v>
+      </c>
+      <c r="BD2">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="s">
         <v>793</v>
       </c>
-      <c r="PQ1" t="s">
+      <c r="BF2" t="s">
         <v>794</v>
       </c>
-      <c r="PR1" t="s">
-        <v>304</v>
-      </c>
-      <c r="PS1" t="s">
-        <v>305</v>
-      </c>
-      <c r="PT1" t="s">
-        <v>306</v>
-      </c>
-      <c r="PU1" t="s">
-        <v>307</v>
-      </c>
-      <c r="PV1" t="s">
-        <v>308</v>
-      </c>
-      <c r="PW1" t="s">
-        <v>309</v>
-      </c>
-      <c r="PX1" t="s">
-        <v>753</v>
-      </c>
-      <c r="PY1" t="s">
-        <v>754</v>
-      </c>
-      <c r="PZ1" t="s">
-        <v>310</v>
-      </c>
-      <c r="QA1" t="s">
-        <v>311</v>
-      </c>
-      <c r="QB1" t="s">
-        <v>312</v>
-      </c>
-      <c r="QC1" t="s">
-        <v>313</v>
-      </c>
-      <c r="QD1" t="s">
-        <v>314</v>
-      </c>
-      <c r="QE1" t="s">
-        <v>315</v>
-      </c>
-      <c r="QF1" t="s">
-        <v>316</v>
-      </c>
-      <c r="QG1" t="s">
-        <v>317</v>
-      </c>
-      <c r="QH1" t="s">
-        <v>318</v>
-      </c>
-      <c r="QI1" t="s">
-        <v>319</v>
-      </c>
-      <c r="QJ1" t="s">
-        <v>320</v>
-      </c>
-      <c r="QK1" t="s">
-        <v>321</v>
-      </c>
-      <c r="QL1" t="s">
+      <c r="BH2" t="s">
         <v>795</v>
       </c>
-      <c r="QM1" t="s">
-        <v>322</v>
-      </c>
-      <c r="QN1" t="s">
-        <v>323</v>
-      </c>
-      <c r="QO1" t="s">
-        <v>324</v>
-      </c>
-      <c r="QP1" t="s">
-        <v>325</v>
-      </c>
-      <c r="QQ1" t="s">
-        <v>326</v>
-      </c>
-      <c r="QR1" t="s">
-        <v>327</v>
-      </c>
-      <c r="QS1" t="s">
-        <v>328</v>
-      </c>
-      <c r="QT1" t="s">
-        <v>329</v>
-      </c>
-      <c r="QU1" t="s">
-        <v>330</v>
-      </c>
-      <c r="QV1" t="s">
-        <v>331</v>
-      </c>
-      <c r="QW1" t="s">
-        <v>332</v>
-      </c>
-      <c r="QX1" t="s">
-        <v>333</v>
-      </c>
-      <c r="QY1" t="s">
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>1</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>1</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="s">
         <v>796</v>
       </c>
-      <c r="QZ1" t="s">
-        <v>334</v>
-      </c>
-      <c r="RA1" t="s">
-        <v>335</v>
-      </c>
-      <c r="RB1" t="s">
-        <v>336</v>
-      </c>
-      <c r="RC1" t="s">
-        <v>337</v>
-      </c>
-      <c r="RD1" t="s">
-        <v>338</v>
-      </c>
-      <c r="RE1" t="s">
-        <v>339</v>
-      </c>
-      <c r="RF1" t="s">
-        <v>340</v>
-      </c>
-      <c r="RG1" t="s">
-        <v>341</v>
-      </c>
-      <c r="RH1" t="s">
-        <v>342</v>
-      </c>
-      <c r="RI1" t="s">
-        <v>343</v>
-      </c>
-      <c r="RJ1" t="s">
-        <v>344</v>
-      </c>
-      <c r="RK1" t="s">
-        <v>345</v>
-      </c>
-      <c r="RL1" t="s">
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>1</v>
+      </c>
+      <c r="BQ2">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="s">
         <v>797</v>
       </c>
-      <c r="RM1" t="s">
-        <v>346</v>
-      </c>
-      <c r="RN1" t="s">
-        <v>347</v>
-      </c>
-      <c r="RO1" t="s">
-        <v>348</v>
-      </c>
-      <c r="RP1" t="s">
-        <v>349</v>
-      </c>
-      <c r="RQ1" t="s">
-        <v>350</v>
-      </c>
-      <c r="RR1" t="s">
-        <v>351</v>
-      </c>
-      <c r="RS1" t="s">
-        <v>352</v>
-      </c>
-      <c r="RT1" t="s">
-        <v>353</v>
-      </c>
-      <c r="RU1" t="s">
-        <v>354</v>
-      </c>
-      <c r="RV1" t="s">
-        <v>355</v>
-      </c>
-      <c r="RW1" t="s">
-        <v>356</v>
-      </c>
-      <c r="RX1" t="s">
-        <v>357</v>
-      </c>
-      <c r="RY1" t="s">
+      <c r="BS2" t="s">
+        <v>790</v>
+      </c>
+      <c r="BU2" t="s">
         <v>798</v>
       </c>
-      <c r="RZ1" t="s">
-        <v>358</v>
-      </c>
-      <c r="SA1" t="s">
-        <v>755</v>
-      </c>
-      <c r="SB1" t="s">
-        <v>359</v>
-      </c>
-      <c r="SC1" t="s">
-        <v>360</v>
-      </c>
-      <c r="SD1" t="s">
-        <v>361</v>
-      </c>
-      <c r="SE1" t="s">
-        <v>362</v>
-      </c>
-      <c r="SF1" t="s">
-        <v>363</v>
-      </c>
-      <c r="SG1" t="s">
-        <v>364</v>
-      </c>
-      <c r="SH1" t="s">
-        <v>365</v>
-      </c>
-      <c r="SI1" t="s">
-        <v>366</v>
-      </c>
-      <c r="SJ1" t="s">
-        <v>756</v>
-      </c>
-      <c r="SK1" t="s">
-        <v>757</v>
-      </c>
-      <c r="SL1" t="s">
-        <v>758</v>
-      </c>
-      <c r="SM1" t="s">
-        <v>759</v>
-      </c>
-      <c r="SN1" t="s">
-        <v>367</v>
-      </c>
-      <c r="SO1" t="s">
-        <v>368</v>
-      </c>
-      <c r="SP1" t="s">
-        <v>369</v>
-      </c>
-      <c r="SQ1" t="s">
-        <v>370</v>
-      </c>
-      <c r="SR1" t="s">
-        <v>371</v>
-      </c>
-      <c r="SS1" t="s">
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>0</v>
+      </c>
+      <c r="BX2">
+        <v>1</v>
+      </c>
+      <c r="BY2">
+        <v>1</v>
+      </c>
+      <c r="BZ2">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>788</v>
+      </c>
+      <c r="CB2">
+        <v>1</v>
+      </c>
+      <c r="CC2">
+        <v>0</v>
+      </c>
+      <c r="CD2">
+        <v>0</v>
+      </c>
+      <c r="CE2" t="s">
         <v>799</v>
       </c>
-      <c r="ST1" t="s">
-        <v>372</v>
-      </c>
-      <c r="SU1" t="s">
-        <v>373</v>
-      </c>
-      <c r="SV1" t="s">
-        <v>374</v>
-      </c>
-      <c r="SW1" t="s">
-        <v>375</v>
-      </c>
-      <c r="SX1" t="s">
-        <v>376</v>
-      </c>
-      <c r="SY1" t="s">
-        <v>377</v>
-      </c>
-      <c r="SZ1" t="s">
-        <v>378</v>
-      </c>
-      <c r="TA1" t="s">
-        <v>379</v>
-      </c>
-      <c r="TB1" t="s">
-        <v>380</v>
-      </c>
-      <c r="TC1" t="s">
-        <v>381</v>
-      </c>
-      <c r="TD1" t="s">
-        <v>382</v>
-      </c>
-      <c r="TE1" t="s">
-        <v>383</v>
-      </c>
-      <c r="TF1" t="s">
-        <v>384</v>
-      </c>
-      <c r="TG1" t="s">
-        <v>385</v>
-      </c>
-      <c r="TH1" t="s">
-        <v>386</v>
-      </c>
-      <c r="TI1" t="s">
-        <v>387</v>
-      </c>
-      <c r="TJ1" t="s">
-        <v>388</v>
-      </c>
-      <c r="TK1" t="s">
-        <v>389</v>
-      </c>
-      <c r="TL1" t="s">
-        <v>390</v>
-      </c>
-      <c r="TM1" t="s">
-        <v>391</v>
-      </c>
-      <c r="TN1" t="s">
-        <v>392</v>
-      </c>
-      <c r="TO1" t="s">
-        <v>393</v>
-      </c>
-      <c r="TP1" t="s">
-        <v>394</v>
-      </c>
-      <c r="TQ1" t="s">
-        <v>395</v>
-      </c>
-      <c r="TR1" t="s">
-        <v>396</v>
-      </c>
-      <c r="TS1" t="s">
-        <v>397</v>
-      </c>
-      <c r="TT1" t="s">
-        <v>398</v>
-      </c>
-      <c r="TU1" t="s">
-        <v>399</v>
-      </c>
-      <c r="TV1" t="s">
-        <v>400</v>
-      </c>
-      <c r="TW1" t="s">
-        <v>401</v>
-      </c>
-      <c r="TX1" t="s">
-        <v>402</v>
-      </c>
-      <c r="TY1" t="s">
-        <v>403</v>
-      </c>
-      <c r="TZ1" t="s">
-        <v>404</v>
-      </c>
-      <c r="UA1" t="s">
-        <v>405</v>
-      </c>
-      <c r="UB1" t="s">
-        <v>406</v>
-      </c>
-      <c r="UC1" t="s">
-        <v>407</v>
-      </c>
-      <c r="UD1" t="s">
-        <v>408</v>
-      </c>
-      <c r="UE1" t="s">
+      <c r="CF2" t="s">
+        <v>790</v>
+      </c>
+      <c r="CH2" t="s">
         <v>800</v>
       </c>
-      <c r="UF1" t="s">
+      <c r="CI2">
+        <v>0</v>
+      </c>
+      <c r="CJ2">
+        <v>0</v>
+      </c>
+      <c r="CK2">
+        <v>1</v>
+      </c>
+      <c r="CL2">
+        <v>0</v>
+      </c>
+      <c r="CM2">
+        <v>1</v>
+      </c>
+      <c r="CN2" t="s">
         <v>801</v>
       </c>
-      <c r="UG1" t="s">
+      <c r="CO2">
+        <v>1</v>
+      </c>
+      <c r="CP2">
+        <v>0</v>
+      </c>
+      <c r="CQ2">
+        <v>1</v>
+      </c>
+      <c r="CR2" t="s">
         <v>802</v>
       </c>
-      <c r="UH1" t="s">
+      <c r="CS2" t="s">
+        <v>794</v>
+      </c>
+      <c r="CU2" t="s">
         <v>803</v>
       </c>
-      <c r="UI1" t="s">
+      <c r="CV2">
+        <v>1</v>
+      </c>
+      <c r="CW2">
+        <v>1</v>
+      </c>
+      <c r="CX2">
+        <v>0</v>
+      </c>
+      <c r="CY2">
+        <v>0</v>
+      </c>
+      <c r="CZ2">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>796</v>
+      </c>
+      <c r="DB2">
+        <v>0</v>
+      </c>
+      <c r="DC2">
+        <v>1</v>
+      </c>
+      <c r="DD2">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="s">
         <v>804</v>
       </c>
-      <c r="UJ1" t="s">
+      <c r="DF2" t="s">
+        <v>790</v>
+      </c>
+      <c r="DG2" t="s">
         <v>805</v>
       </c>
-      <c r="UK1" t="s">
-        <v>409</v>
-      </c>
-      <c r="UL1" t="s">
-        <v>410</v>
-      </c>
-      <c r="UM1" t="s">
-        <v>411</v>
-      </c>
-      <c r="UN1" t="s">
-        <v>412</v>
-      </c>
-      <c r="UO1" t="s">
+      <c r="DH2">
+        <v>0</v>
+      </c>
+      <c r="DI2">
+        <v>0</v>
+      </c>
+      <c r="DJ2">
+        <v>0</v>
+      </c>
+      <c r="DK2">
+        <v>0</v>
+      </c>
+      <c r="DL2">
+        <v>0</v>
+      </c>
+      <c r="DM2">
+        <v>1</v>
+      </c>
+      <c r="DN2">
+        <v>0</v>
+      </c>
+      <c r="DO2">
+        <v>0</v>
+      </c>
+      <c r="DP2">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="s">
         <v>806</v>
       </c>
-      <c r="UP1" t="s">
+      <c r="EG2">
+        <v>6</v>
+      </c>
+      <c r="EI2">
+        <v>2</v>
+      </c>
+      <c r="EK2">
+        <v>1</v>
+      </c>
+      <c r="AEL2">
+        <v>884394036</v>
+      </c>
+      <c r="AEM2" t="s">
         <v>807</v>
       </c>
-      <c r="UQ1" t="s">
-        <v>413</v>
-      </c>
-      <c r="UR1" t="s">
-        <v>414</v>
-      </c>
-      <c r="US1" t="s">
-        <v>415</v>
-      </c>
-      <c r="UT1" t="s">
-        <v>416</v>
-      </c>
-      <c r="UU1" t="s">
-        <v>417</v>
-      </c>
-      <c r="UV1" t="s">
-        <v>418</v>
-      </c>
-      <c r="UW1" t="s">
-        <v>419</v>
-      </c>
-      <c r="UX1" t="s">
-        <v>420</v>
-      </c>
-      <c r="UY1" t="s">
-        <v>421</v>
-      </c>
-      <c r="UZ1" t="s">
-        <v>422</v>
-      </c>
-      <c r="VA1" t="s">
-        <v>423</v>
-      </c>
-      <c r="VB1" t="s">
-        <v>424</v>
-      </c>
-      <c r="VC1" t="s">
-        <v>425</v>
-      </c>
-      <c r="VD1" t="s">
-        <v>426</v>
-      </c>
-      <c r="VE1" t="s">
-        <v>427</v>
-      </c>
-      <c r="VF1" t="s">
-        <v>428</v>
-      </c>
-      <c r="VG1" t="s">
-        <v>429</v>
-      </c>
-      <c r="VH1" t="s">
-        <v>430</v>
-      </c>
-      <c r="VI1" t="s">
-        <v>431</v>
-      </c>
-      <c r="VJ1" t="s">
-        <v>432</v>
-      </c>
-      <c r="VK1" t="s">
-        <v>433</v>
-      </c>
-      <c r="VL1" t="s">
-        <v>434</v>
-      </c>
-      <c r="VM1" t="s">
-        <v>435</v>
-      </c>
-      <c r="VN1" t="s">
-        <v>436</v>
-      </c>
-      <c r="VO1" t="s">
-        <v>437</v>
-      </c>
-      <c r="VP1" t="s">
-        <v>438</v>
-      </c>
-      <c r="VQ1" t="s">
-        <v>439</v>
-      </c>
-      <c r="VR1" t="s">
-        <v>440</v>
-      </c>
-      <c r="VS1" t="s">
-        <v>441</v>
-      </c>
-      <c r="VT1" t="s">
-        <v>442</v>
-      </c>
-      <c r="VU1" t="s">
-        <v>443</v>
-      </c>
-      <c r="VV1" t="s">
-        <v>444</v>
-      </c>
-      <c r="VW1" t="s">
-        <v>445</v>
-      </c>
-      <c r="VX1" t="s">
-        <v>446</v>
-      </c>
-      <c r="VY1" t="s">
-        <v>447</v>
-      </c>
-      <c r="VZ1" t="s">
-        <v>448</v>
-      </c>
-      <c r="WA1" t="s">
-        <v>449</v>
-      </c>
-      <c r="WB1" t="s">
-        <v>450</v>
-      </c>
-      <c r="WC1" t="s">
-        <v>17</v>
-      </c>
-      <c r="WD1" t="s">
-        <v>451</v>
-      </c>
-      <c r="WE1" t="s">
-        <v>452</v>
-      </c>
-      <c r="WF1" t="s">
-        <v>453</v>
-      </c>
-      <c r="WG1" t="s">
-        <v>454</v>
-      </c>
-      <c r="WH1" t="s">
-        <v>455</v>
-      </c>
-      <c r="WI1" t="s">
-        <v>456</v>
-      </c>
-      <c r="WJ1" t="s">
-        <v>457</v>
-      </c>
-      <c r="WK1" t="s">
-        <v>458</v>
-      </c>
-      <c r="WL1" t="s">
-        <v>459</v>
-      </c>
-      <c r="WM1" t="s">
-        <v>460</v>
-      </c>
-      <c r="WN1" t="s">
-        <v>461</v>
-      </c>
-      <c r="WO1" t="s">
-        <v>462</v>
-      </c>
-      <c r="WP1" t="s">
-        <v>463</v>
-      </c>
-      <c r="WQ1" t="s">
-        <v>464</v>
-      </c>
-      <c r="WR1" t="s">
-        <v>465</v>
-      </c>
-      <c r="WS1" t="s">
-        <v>466</v>
-      </c>
-      <c r="WT1" t="s">
-        <v>467</v>
-      </c>
-      <c r="WU1" t="s">
-        <v>468</v>
-      </c>
-      <c r="WV1" t="s">
-        <v>469</v>
-      </c>
-      <c r="WW1" t="s">
-        <v>470</v>
-      </c>
-      <c r="WX1" t="s">
-        <v>471</v>
-      </c>
-      <c r="WY1" t="s">
-        <v>472</v>
-      </c>
-      <c r="WZ1" t="s">
-        <v>473</v>
-      </c>
-      <c r="XA1" t="s">
-        <v>474</v>
-      </c>
-      <c r="XB1" t="s">
-        <v>475</v>
-      </c>
-      <c r="XC1" t="s">
-        <v>476</v>
-      </c>
-      <c r="XD1" t="s">
-        <v>477</v>
-      </c>
-      <c r="XE1" t="s">
-        <v>478</v>
-      </c>
-      <c r="XF1" t="s">
-        <v>479</v>
-      </c>
-      <c r="XG1" t="s">
-        <v>480</v>
-      </c>
-      <c r="XH1" t="s">
-        <v>481</v>
-      </c>
-      <c r="XI1" t="s">
-        <v>482</v>
-      </c>
-      <c r="XJ1" t="s">
-        <v>483</v>
-      </c>
-      <c r="XK1" t="s">
-        <v>484</v>
-      </c>
-      <c r="XL1" t="s">
-        <v>485</v>
-      </c>
-      <c r="XM1" t="s">
-        <v>486</v>
-      </c>
-      <c r="XN1" t="s">
-        <v>487</v>
-      </c>
-      <c r="XO1" t="s">
-        <v>488</v>
-      </c>
-      <c r="XP1" t="s">
-        <v>489</v>
-      </c>
-      <c r="XQ1" t="s">
-        <v>490</v>
-      </c>
-      <c r="XR1" t="s">
-        <v>491</v>
-      </c>
-      <c r="XS1" t="s">
-        <v>492</v>
-      </c>
-      <c r="XT1" t="s">
-        <v>493</v>
-      </c>
-      <c r="XU1" t="s">
-        <v>494</v>
-      </c>
-      <c r="XV1" t="s">
-        <v>495</v>
-      </c>
-      <c r="XW1" t="s">
-        <v>496</v>
-      </c>
-      <c r="XX1" t="s">
-        <v>497</v>
-      </c>
-      <c r="XY1" t="s">
-        <v>498</v>
-      </c>
-      <c r="XZ1" t="s">
-        <v>499</v>
-      </c>
-      <c r="YA1" t="s">
-        <v>500</v>
-      </c>
-      <c r="YB1" t="s">
-        <v>501</v>
-      </c>
-      <c r="YC1" t="s">
-        <v>502</v>
-      </c>
-      <c r="YD1" t="s">
-        <v>503</v>
-      </c>
-      <c r="YE1" t="s">
-        <v>504</v>
-      </c>
-      <c r="YF1" t="s">
-        <v>505</v>
-      </c>
-      <c r="YG1" t="s">
-        <v>506</v>
-      </c>
-      <c r="YH1" t="s">
-        <v>507</v>
-      </c>
-      <c r="YI1" t="s">
-        <v>508</v>
-      </c>
-      <c r="YJ1" t="s">
-        <v>509</v>
-      </c>
-      <c r="YK1" t="s">
-        <v>510</v>
-      </c>
-      <c r="YL1" t="s">
-        <v>511</v>
-      </c>
-      <c r="YM1" t="s">
-        <v>512</v>
-      </c>
-      <c r="YN1" t="s">
-        <v>513</v>
-      </c>
-      <c r="YO1" t="s">
-        <v>514</v>
-      </c>
-      <c r="YP1" t="s">
-        <v>515</v>
-      </c>
-      <c r="YQ1" t="s">
-        <v>516</v>
-      </c>
-      <c r="YR1" t="s">
-        <v>517</v>
-      </c>
-      <c r="YS1" t="s">
-        <v>518</v>
-      </c>
-      <c r="YT1" t="s">
-        <v>519</v>
-      </c>
-      <c r="YU1" t="s">
-        <v>520</v>
-      </c>
-      <c r="YV1" t="s">
-        <v>521</v>
-      </c>
-      <c r="YW1" t="s">
-        <v>522</v>
-      </c>
-      <c r="YX1" t="s">
-        <v>523</v>
-      </c>
-      <c r="YY1" t="s">
-        <v>524</v>
-      </c>
-      <c r="YZ1" t="s">
-        <v>525</v>
-      </c>
-      <c r="ZA1" t="s">
-        <v>526</v>
-      </c>
-      <c r="ZB1" t="s">
-        <v>527</v>
-      </c>
-      <c r="ZC1" t="s">
-        <v>528</v>
-      </c>
-      <c r="ZD1" t="s">
-        <v>529</v>
-      </c>
-      <c r="ZE1" t="s">
-        <v>530</v>
-      </c>
-      <c r="ZF1" t="s">
-        <v>531</v>
-      </c>
-      <c r="ZG1" t="s">
-        <v>532</v>
-      </c>
-      <c r="ZH1" t="s">
-        <v>533</v>
-      </c>
-      <c r="ZI1" t="s">
-        <v>534</v>
-      </c>
-      <c r="ZJ1" t="s">
-        <v>535</v>
-      </c>
-      <c r="ZK1" t="s">
-        <v>536</v>
-      </c>
-      <c r="ZL1" t="s">
+      <c r="AEN2" s="1">
+        <v>46297.550879629627</v>
+      </c>
+      <c r="AEP2" t="s">
         <v>808</v>
       </c>
-      <c r="ZM1" t="s">
-        <v>537</v>
-      </c>
-      <c r="ZN1" t="s">
-        <v>538</v>
-      </c>
-      <c r="ZO1" t="s">
-        <v>539</v>
-      </c>
-      <c r="ZP1" t="s">
-        <v>540</v>
-      </c>
-      <c r="ZQ1" t="s">
-        <v>541</v>
-      </c>
-      <c r="ZR1" t="s">
+      <c r="AER2" t="s">
         <v>809</v>
       </c>
-      <c r="ZS1" t="s">
-        <v>542</v>
-      </c>
-      <c r="ZT1" t="s">
-        <v>543</v>
-      </c>
-      <c r="ZU1" t="s">
-        <v>544</v>
-      </c>
-      <c r="ZV1" t="s">
-        <v>545</v>
-      </c>
-      <c r="ZW1" t="s">
-        <v>546</v>
-      </c>
-      <c r="ZX1" t="s">
-        <v>88</v>
-      </c>
-      <c r="ZY1" t="s">
-        <v>89</v>
-      </c>
-      <c r="ZZ1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AAA1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AAB1" t="s">
-        <v>760</v>
-      </c>
-      <c r="AAC1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AAD1" t="s">
-        <v>761</v>
-      </c>
-      <c r="AAE1" t="s">
-        <v>762</v>
-      </c>
-      <c r="AAF1" t="s">
-        <v>763</v>
-      </c>
-      <c r="AAG1" t="s">
-        <v>764</v>
-      </c>
-      <c r="AAH1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AAI1" t="s">
+      <c r="AES2" t="s">
         <v>810</v>
       </c>
-      <c r="AAJ1" t="s">
-        <v>547</v>
-      </c>
-      <c r="AAK1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AAL1" t="s">
-        <v>548</v>
-      </c>
-      <c r="AAM1" t="s">
-        <v>549</v>
-      </c>
-      <c r="AAN1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AAO1" t="s">
-        <v>550</v>
-      </c>
-      <c r="AAP1" t="s">
-        <v>551</v>
-      </c>
-      <c r="AAQ1" t="s">
-        <v>114</v>
-      </c>
-      <c r="AAR1" t="s">
+      <c r="AET2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B3" t="s">
+        <v>780</v>
+      </c>
+      <c r="C3" t="s">
         <v>811</v>
       </c>
-      <c r="AAS1" t="s">
-        <v>552</v>
-      </c>
-      <c r="AAT1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AAU1" t="s">
-        <v>553</v>
-      </c>
-      <c r="AAV1" t="s">
-        <v>554</v>
-      </c>
-      <c r="AAW1" t="s">
-        <v>555</v>
-      </c>
-      <c r="AAX1" t="s">
-        <v>556</v>
-      </c>
-      <c r="AAY1" t="s">
-        <v>557</v>
-      </c>
-      <c r="AAZ1" t="s">
-        <v>558</v>
-      </c>
-      <c r="ABA1" t="s">
-        <v>559</v>
-      </c>
-      <c r="ABB1" t="s">
-        <v>116</v>
-      </c>
-      <c r="ABC1" t="s">
-        <v>560</v>
-      </c>
-      <c r="ABD1" t="s">
-        <v>561</v>
-      </c>
-      <c r="ABE1" t="s">
-        <v>562</v>
-      </c>
-      <c r="ABF1" t="s">
-        <v>563</v>
-      </c>
-      <c r="ABG1" t="s">
-        <v>564</v>
-      </c>
-      <c r="ABH1" t="s">
-        <v>565</v>
-      </c>
-      <c r="ABI1" t="s">
-        <v>566</v>
-      </c>
-      <c r="ABJ1" t="s">
-        <v>567</v>
-      </c>
-      <c r="ABK1" t="s">
-        <v>568</v>
-      </c>
-      <c r="ABL1" t="s">
-        <v>569</v>
-      </c>
-      <c r="ABM1" t="s">
-        <v>570</v>
-      </c>
-      <c r="ABN1" t="s">
-        <v>571</v>
-      </c>
-      <c r="ABO1" t="s">
-        <v>572</v>
-      </c>
-      <c r="ABP1" t="s">
-        <v>573</v>
-      </c>
-      <c r="ABQ1" t="s">
-        <v>574</v>
-      </c>
-      <c r="ABR1" t="s">
-        <v>575</v>
-      </c>
-      <c r="ABS1" t="s">
-        <v>576</v>
-      </c>
-      <c r="ABT1" t="s">
-        <v>577</v>
-      </c>
-      <c r="ABU1" t="s">
-        <v>578</v>
-      </c>
-      <c r="ABV1" t="s">
-        <v>579</v>
-      </c>
-      <c r="ABW1" t="s">
-        <v>580</v>
-      </c>
-      <c r="ABX1" t="s">
-        <v>581</v>
-      </c>
-      <c r="ABY1" t="s">
-        <v>582</v>
-      </c>
-      <c r="ABZ1" t="s">
-        <v>583</v>
-      </c>
-      <c r="ACA1" t="s">
-        <v>584</v>
-      </c>
-      <c r="ACB1" t="s">
-        <v>585</v>
-      </c>
-      <c r="ACC1" t="s">
-        <v>586</v>
-      </c>
-      <c r="ACD1" t="s">
-        <v>587</v>
-      </c>
-      <c r="ACE1" t="s">
-        <v>588</v>
-      </c>
-      <c r="ACF1" t="s">
-        <v>589</v>
-      </c>
-      <c r="ACG1" t="s">
-        <v>590</v>
-      </c>
-      <c r="ACH1" t="s">
-        <v>591</v>
-      </c>
-      <c r="ACI1" t="s">
-        <v>592</v>
-      </c>
-      <c r="ACJ1" t="s">
-        <v>593</v>
-      </c>
-      <c r="ACK1" t="s">
-        <v>594</v>
-      </c>
-      <c r="ACL1" t="s">
-        <v>595</v>
-      </c>
-      <c r="ACM1" t="s">
-        <v>596</v>
-      </c>
-      <c r="ACN1" t="s">
-        <v>597</v>
-      </c>
-      <c r="ACO1" t="s">
-        <v>598</v>
-      </c>
-      <c r="ACP1" t="s">
-        <v>599</v>
-      </c>
-      <c r="ACQ1" t="s">
-        <v>600</v>
-      </c>
-      <c r="ACR1" t="s">
-        <v>601</v>
-      </c>
-      <c r="ACS1" t="s">
-        <v>602</v>
-      </c>
-      <c r="ACT1" t="s">
-        <v>603</v>
-      </c>
-      <c r="ACU1" t="s">
-        <v>604</v>
-      </c>
-      <c r="ACV1" t="s">
-        <v>605</v>
-      </c>
-      <c r="ACW1" t="s">
-        <v>606</v>
-      </c>
-      <c r="ACX1" t="s">
-        <v>607</v>
-      </c>
-      <c r="ACY1" t="s">
-        <v>608</v>
-      </c>
-      <c r="ACZ1" t="s">
-        <v>609</v>
-      </c>
-      <c r="ADA1" t="s">
-        <v>610</v>
-      </c>
-      <c r="ADB1" t="s">
-        <v>611</v>
-      </c>
-      <c r="ADC1" t="s">
-        <v>612</v>
-      </c>
-      <c r="ADD1" t="s">
+      <c r="D3" t="s">
+        <v>648</v>
+      </c>
+      <c r="E3" t="s">
+        <v>782</v>
+      </c>
+      <c r="F3" t="s">
         <v>812</v>
       </c>
-      <c r="ADE1" t="s">
+      <c r="H3" t="s">
         <v>813</v>
       </c>
-      <c r="ADF1" t="s">
-        <v>614</v>
-      </c>
-      <c r="ADG1" t="s">
-        <v>615</v>
-      </c>
-      <c r="ADH1" t="s">
+      <c r="TJ3" t="s">
         <v>814</v>
       </c>
-      <c r="ADI1" t="s">
+      <c r="TK3">
+        <v>1</v>
+      </c>
+      <c r="TL3">
+        <v>0</v>
+      </c>
+      <c r="TM3" t="s">
         <v>815</v>
       </c>
-      <c r="ADJ1" t="s">
-        <v>617</v>
-      </c>
-      <c r="ADK1" t="s">
-        <v>618</v>
-      </c>
-      <c r="ADL1" t="s">
+      <c r="TN3">
+        <v>16</v>
+      </c>
+      <c r="TO3">
+        <v>25</v>
+      </c>
+      <c r="TP3" t="s">
         <v>816</v>
       </c>
-      <c r="ADM1" t="s">
-        <v>620</v>
-      </c>
-      <c r="ADN1" t="s">
-        <v>621</v>
-      </c>
-      <c r="ADO1" t="s">
-        <v>622</v>
-      </c>
-      <c r="ADP1" t="s">
-        <v>623</v>
-      </c>
-      <c r="ADQ1" t="s">
-        <v>624</v>
-      </c>
-      <c r="ADR1" t="s">
-        <v>625</v>
-      </c>
-      <c r="ADS1" t="s">
-        <v>626</v>
-      </c>
-      <c r="ADT1" t="s">
-        <v>627</v>
-      </c>
-      <c r="ADU1" t="s">
-        <v>628</v>
-      </c>
-      <c r="ADV1" t="s">
-        <v>629</v>
-      </c>
-      <c r="ADW1" t="s">
-        <v>630</v>
-      </c>
-      <c r="ADX1" t="s">
-        <v>631</v>
-      </c>
-      <c r="ADY1" t="s">
-        <v>632</v>
-      </c>
-      <c r="ADZ1" t="s">
+      <c r="TQ3" s="1">
+        <v>46297</v>
+      </c>
+      <c r="TR3" t="s">
         <v>817</v>
       </c>
-      <c r="AEA1" t="s">
-        <v>633</v>
-      </c>
-      <c r="AEB1" t="s">
-        <v>634</v>
-      </c>
-      <c r="AEC1" t="s">
-        <v>635</v>
-      </c>
-      <c r="AED1" t="s">
-        <v>636</v>
-      </c>
-      <c r="AEE1" t="s">
-        <v>637</v>
-      </c>
-      <c r="AEF1" t="s">
-        <v>638</v>
-      </c>
-      <c r="AEG1" t="s">
-        <v>639</v>
-      </c>
-      <c r="AEH1" t="s">
-        <v>640</v>
-      </c>
-      <c r="AEI1" t="s">
-        <v>641</v>
-      </c>
-      <c r="AEJ1" t="s">
-        <v>642</v>
-      </c>
-      <c r="AEK1" t="s">
-        <v>643</v>
-      </c>
-      <c r="AEL1" t="s">
-        <v>644</v>
+      <c r="TS3" t="s">
+        <v>818</v>
+      </c>
+      <c r="TT3">
+        <v>12</v>
+      </c>
+      <c r="TU3">
+        <v>24</v>
+      </c>
+      <c r="TV3">
+        <v>0</v>
+      </c>
+      <c r="TW3">
+        <v>0</v>
+      </c>
+      <c r="TX3" t="s">
+        <v>819</v>
+      </c>
+      <c r="TY3">
+        <v>0</v>
+      </c>
+      <c r="TZ3">
+        <v>0</v>
+      </c>
+      <c r="UA3">
+        <v>1</v>
+      </c>
+      <c r="UB3">
+        <v>1</v>
+      </c>
+      <c r="UC3">
+        <v>0</v>
+      </c>
+      <c r="UD3" t="s">
+        <v>820</v>
+      </c>
+      <c r="UV3" t="s">
+        <v>821</v>
+      </c>
+      <c r="AEL3">
+        <v>884613428</v>
+      </c>
+      <c r="AEM3" t="s">
+        <v>822</v>
+      </c>
+      <c r="AEN3" s="1">
+        <v>46297.744189814817</v>
+      </c>
+      <c r="AEP3" t="s">
+        <v>808</v>
+      </c>
+      <c r="AER3" t="s">
+        <v>823</v>
+      </c>
+      <c r="AES3" t="s">
+        <v>824</v>
+      </c>
+      <c r="AET3">
+        <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:818" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="UO2" s="1"/>
-      <c r="UP2" s="1"/>
-      <c r="AEF2" s="1"/>
+    <row r="4" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C4" t="s">
+        <v>825</v>
+      </c>
+      <c r="D4" t="s">
+        <v>650</v>
+      </c>
+      <c r="E4" t="s">
+        <v>782</v>
+      </c>
+      <c r="F4" t="s">
+        <v>826</v>
+      </c>
+      <c r="G4" t="s">
+        <v>827</v>
+      </c>
+      <c r="EL4" t="s">
+        <v>828</v>
+      </c>
+      <c r="FN4" t="s">
+        <v>829</v>
+      </c>
+      <c r="FO4" t="s">
+        <v>829</v>
+      </c>
+      <c r="FP4" t="s">
+        <v>829</v>
+      </c>
+      <c r="FS4" t="s">
+        <v>830</v>
+      </c>
+      <c r="FT4" t="s">
+        <v>831</v>
+      </c>
+      <c r="FU4" t="s">
+        <v>832</v>
+      </c>
+      <c r="FX4" t="s">
+        <v>833</v>
+      </c>
+      <c r="FY4" t="s">
+        <v>834</v>
+      </c>
+      <c r="FZ4" t="s">
+        <v>835</v>
+      </c>
+      <c r="GC4" t="s">
+        <v>836</v>
+      </c>
+      <c r="GD4" t="s">
+        <v>833</v>
+      </c>
+      <c r="GE4" t="s">
+        <v>832</v>
+      </c>
+      <c r="GH4" t="s">
+        <v>837</v>
+      </c>
+      <c r="GI4" t="s">
+        <v>835</v>
+      </c>
+      <c r="GJ4" t="s">
+        <v>829</v>
+      </c>
+      <c r="GL4" t="s">
+        <v>838</v>
+      </c>
+      <c r="GM4">
+        <v>1</v>
+      </c>
+      <c r="GN4">
+        <v>0</v>
+      </c>
+      <c r="GO4">
+        <v>0</v>
+      </c>
+      <c r="GP4">
+        <v>0</v>
+      </c>
+      <c r="GQ4">
+        <v>1</v>
+      </c>
+      <c r="GR4">
+        <v>0</v>
+      </c>
+      <c r="GS4">
+        <v>1</v>
+      </c>
+      <c r="HE4" t="s">
+        <v>839</v>
+      </c>
+      <c r="HF4">
+        <v>8</v>
+      </c>
+      <c r="HG4" t="s">
+        <v>833</v>
+      </c>
+      <c r="HI4" t="s">
+        <v>840</v>
+      </c>
+      <c r="HJ4">
+        <v>10</v>
+      </c>
+      <c r="HK4" t="s">
+        <v>841</v>
+      </c>
+      <c r="HM4" t="s">
+        <v>839</v>
+      </c>
+      <c r="HN4">
+        <v>8</v>
+      </c>
+      <c r="HO4" t="s">
+        <v>836</v>
+      </c>
+      <c r="HQ4" t="s">
+        <v>840</v>
+      </c>
+      <c r="HR4">
+        <v>8</v>
+      </c>
+      <c r="HS4" t="s">
+        <v>833</v>
+      </c>
+      <c r="HU4" t="s">
+        <v>839</v>
+      </c>
+      <c r="HV4">
+        <v>8</v>
+      </c>
+      <c r="HW4" t="s">
+        <v>841</v>
+      </c>
+      <c r="IG4" t="s">
+        <v>842</v>
+      </c>
+      <c r="IH4" t="s">
+        <v>843</v>
+      </c>
+      <c r="IN4" t="s">
+        <v>842</v>
+      </c>
+      <c r="IO4" t="s">
+        <v>843</v>
+      </c>
+      <c r="IU4" t="s">
+        <v>842</v>
+      </c>
+      <c r="IV4" t="s">
+        <v>843</v>
+      </c>
+      <c r="JI4" t="s">
+        <v>842</v>
+      </c>
+      <c r="JJ4" t="s">
+        <v>843</v>
+      </c>
+      <c r="JP4" t="s">
+        <v>842</v>
+      </c>
+      <c r="JQ4" t="s">
+        <v>843</v>
+      </c>
+      <c r="AEL4">
+        <v>884667912</v>
+      </c>
+      <c r="AEM4" t="s">
+        <v>844</v>
+      </c>
+      <c r="AEN4" s="1">
+        <v>46297.806550925918</v>
+      </c>
+      <c r="AEP4" t="s">
+        <v>808</v>
+      </c>
+      <c r="AER4" t="s">
+        <v>845</v>
+      </c>
+      <c r="AES4" t="s">
+        <v>846</v>
+      </c>
+      <c r="AET4">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C914A8-9679-5A4E-9DF5-AD732CC65F33}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3986BB43-46E3-6942-B0E0-1963076D7C66}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="982">
   <si>
     <t>Date</t>
   </si>
@@ -2699,6 +2699,273 @@
   </si>
   <si>
     <t>Specify55</t>
+  </si>
+  <si>
+    <t>Lopeyok Martin</t>
+  </si>
+  <si>
+    <t>KARENGA BOYS P/S</t>
+  </si>
+  <si>
+    <t>They agreed they will be reporting the activities done on weekly basis</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Fair and equal plate sharing between boys and girls at home Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>He is appreciating the program and promises to give the full support</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Fair and equal plate sharing between boys and girls at home Using improved cooking methods to consume less firewood</t>
+  </si>
+  <si>
+    <t>Mobilize boys/fathers to share water/wood chores so girls arrive on time Enrich school/home porridge with obtainable local greens or cowpeas</t>
+  </si>
+  <si>
+    <t>She is willing to give the best results</t>
+  </si>
+  <si>
+    <t>She only words of thanks</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Rebalancing morning water/firewood chores so girls stay in school Fair and equal plate sharing between boys and girls at home Using improved cooking methods to consume less firewood Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>Mobilize boys/fathers to share water/wood chores so girls arrive on time Enrich school/home porridge with obtainable local greens or cowpeas Adopt firewood-saving practices in school kitchen / establish Nutri Club</t>
+  </si>
+  <si>
+    <t>She said she wants to work to start</t>
+  </si>
+  <si>
+    <t>Only gave words of thanks</t>
+  </si>
+  <si>
+    <t>Printed Nutri Club Session forms Metu Nutrition Posters Pledge / Commitment card</t>
+  </si>
+  <si>
+    <t>Timely supply of materials can help for effectiveness of work by most VHT s</t>
+  </si>
+  <si>
+    <t>d923dd3c-c197-427d-9182-0e14e5ea8d7f</t>
+  </si>
+  <si>
+    <t>uuid:d923dd3c-c197-427d-9182-0e14e5ea8d7f</t>
+  </si>
+  <si>
+    <t>AWAS FRANCIS</t>
+  </si>
+  <si>
+    <t>NABILATUK TOWNSHIP P/S</t>
+  </si>
+  <si>
+    <t>The patrons and VHTs have agreed to start their activities next week starting on Monday except for teachers who have teachers day celebration</t>
+  </si>
+  <si>
+    <t>Developing activities workplan and teaching children nutrition messages,gender and education</t>
+  </si>
+  <si>
+    <t>Developing workplan and doing cooking demonstrations</t>
+  </si>
+  <si>
+    <t>Doing cooking demonstrations,hold elders dialogue and reporting</t>
+  </si>
+  <si>
+    <t>Have classroom nutrition sessions, doing school activation activity, Do learner to learner interactive sessions and sending weekly reports</t>
+  </si>
+  <si>
+    <t>Do school day bus activation, engaging learners on nutrition,gender and education while updating district coordinator</t>
+  </si>
+  <si>
+    <t>Doing community cooking food demonstrations, liase withdistrict coordinator to followup the households</t>
+  </si>
+  <si>
+    <t>Printed Nutri Club Session forms Game for the school WFP Toll-Free Feedback Display Board Cooking manual</t>
+  </si>
+  <si>
+    <t>The orientation went on well with emphasis from the DIS that this activity should be rolled to other schools as well since issues of nutrition not only affect these five schools but schools as a whole</t>
+  </si>
+  <si>
+    <t>37cc56fd-9bcf-4a65-8e1e-8bd43ce11dc8</t>
+  </si>
+  <si>
+    <t>uuid:37cc56fd-9bcf-4a65-8e1e-8bd43ce11dc8</t>
+  </si>
+  <si>
+    <t>Ochen moses tom</t>
+  </si>
+  <si>
+    <t>KOTIDO MIXED P/S</t>
+  </si>
+  <si>
+    <t>When afi brings the food for cooking demonstration</t>
+  </si>
+  <si>
+    <t>Rebalancing morning water/firewood chores so girls stay in school</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Using improved cooking methods to consume less firewood</t>
+  </si>
+  <si>
+    <t>Rebalancing morning water/firewood chores so girls stay in school Fair and equal plate sharing between boys and girls at home Using improved cooking methods to consume less firewood</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Rebalancing morning water/firewood chores so girls stay in school Fair and equal plate sharing between boys and girls at home Using improved cooking methods to consume less firewood Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Printed Nutri Club Session forms Metu Nutrition Posters Game for the school WFP Toll-Free Feedback Display Board Nutri calendar</t>
+  </si>
+  <si>
+    <t>District Education Offices Health Centre Parish Focal Persons</t>
+  </si>
+  <si>
+    <t>Joint facilitation</t>
+  </si>
+  <si>
+    <t>Inbolvung the community and launch at every district</t>
+  </si>
+  <si>
+    <t>b4e4f1ed-ce12-46b1-af95-c3af56846dd1</t>
+  </si>
+  <si>
+    <t>uuid:b4e4f1ed-ce12-46b1-af95-c3af56846dd1</t>
+  </si>
+  <si>
+    <t>Evaline</t>
+  </si>
+  <si>
+    <t>KASIMERI P/S</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Food sorting &amp; matching game Fair food portions for all genders</t>
+  </si>
+  <si>
+    <t>Pictures describing the messages</t>
+  </si>
+  <si>
+    <t>Disagree</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Undecided</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Gives a general/vague idea; lacks a concrete action</t>
+  </si>
+  <si>
+    <t>Demonstrated (explained clearly and accurately without prompting)</t>
+  </si>
+  <si>
+    <t>Incorrect, silences, or names unavailable foods</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Partly demonstrated (vague or needed prompting)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Lack of preparation confidence/skills Ingredients not prioritized at household level Other</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Children learnt with excitement</t>
+  </si>
+  <si>
+    <t>More time for reading stiry books and quizzes</t>
+  </si>
+  <si>
+    <t>We pledge to male meals available for both boys and girls</t>
+  </si>
+  <si>
+    <t>Teachers participation encouraged</t>
+  </si>
+  <si>
+    <t>99e32c91-6126-40c2-a595-3b567e9f578c</t>
+  </si>
+  <si>
+    <t>uuid:99e32c91-6126-40c2-a595-3b567e9f578c</t>
+  </si>
+  <si>
+    <t>Evalyne</t>
+  </si>
+  <si>
+    <t>Rebalancing morning water/firewood chores so girls stay in school Fair and equal plate sharing between boys and girls at home Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Fair and equal plate sharing between boys and girls at home</t>
+  </si>
+  <si>
+    <t>Adopt firewood-saving practices in school kitchen / establish Nutri Club</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Using improved cooking methods to consume less firewood Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Rebalancing morning water/firewood chores so girls stay in school Fair and equal plate sharing between boys and girls at home</t>
+  </si>
+  <si>
+    <t>WFP Toll-Free Feedback Display Board Pledge / Commitment card</t>
+  </si>
+  <si>
+    <t>Need capacity building on all cooking demonstration</t>
+  </si>
+  <si>
+    <t>d626f565-e3e3-4557-8a2f-301c66e57a6f</t>
+  </si>
+  <si>
+    <t>uuid:d626f565-e3e3-4557-8a2f-301c66e57a6f</t>
   </si>
 </sst>
 </file>
@@ -2771,8 +3038,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET4" totalsRowShown="0">
-  <autoFilter ref="A1:AET4" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET9" totalsRowShown="0">
+  <autoFilter ref="A1:AET9" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="826">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -3892,7 +4159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AET4"/>
+  <dimension ref="A1:AET9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -7580,6 +7847,1754 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B5" t="s">
+        <v>780</v>
+      </c>
+      <c r="C5" t="s">
+        <v>893</v>
+      </c>
+      <c r="D5" t="s">
+        <v>649</v>
+      </c>
+      <c r="E5" t="s">
+        <v>782</v>
+      </c>
+      <c r="F5" t="s">
+        <v>783</v>
+      </c>
+      <c r="I5" t="s">
+        <v>894</v>
+      </c>
+      <c r="Q5">
+        <v>6</v>
+      </c>
+      <c r="R5">
+        <v>4</v>
+      </c>
+      <c r="S5" t="s">
+        <v>806</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>5</v>
+      </c>
+      <c r="V5">
+        <v>9</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>785</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>895</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>896</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>801</v>
+      </c>
+      <c r="AO5">
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>897</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>794</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>898</v>
+      </c>
+      <c r="AV5">
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>899</v>
+      </c>
+      <c r="BB5">
+        <v>1</v>
+      </c>
+      <c r="BC5">
+        <v>1</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>900</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>790</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>898</v>
+      </c>
+      <c r="BI5">
+        <v>1</v>
+      </c>
+      <c r="BJ5">
+        <v>1</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>1</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>899</v>
+      </c>
+      <c r="BO5">
+        <v>1</v>
+      </c>
+      <c r="BP5">
+        <v>1</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>901</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>790</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>902</v>
+      </c>
+      <c r="BV5">
+        <v>1</v>
+      </c>
+      <c r="BW5">
+        <v>1</v>
+      </c>
+      <c r="BX5">
+        <v>1</v>
+      </c>
+      <c r="BY5">
+        <v>1</v>
+      </c>
+      <c r="BZ5">
+        <v>1</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>903</v>
+      </c>
+      <c r="CB5">
+        <v>1</v>
+      </c>
+      <c r="CC5">
+        <v>1</v>
+      </c>
+      <c r="CD5">
+        <v>1</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>904</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>790</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>902</v>
+      </c>
+      <c r="CI5">
+        <v>1</v>
+      </c>
+      <c r="CJ5">
+        <v>1</v>
+      </c>
+      <c r="CK5">
+        <v>1</v>
+      </c>
+      <c r="CL5">
+        <v>1</v>
+      </c>
+      <c r="CM5">
+        <v>1</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>903</v>
+      </c>
+      <c r="CO5">
+        <v>1</v>
+      </c>
+      <c r="CP5">
+        <v>1</v>
+      </c>
+      <c r="CQ5">
+        <v>1</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>905</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>794</v>
+      </c>
+      <c r="CU5" t="s">
+        <v>902</v>
+      </c>
+      <c r="CV5">
+        <v>1</v>
+      </c>
+      <c r="CW5">
+        <v>1</v>
+      </c>
+      <c r="CX5">
+        <v>1</v>
+      </c>
+      <c r="CY5">
+        <v>1</v>
+      </c>
+      <c r="CZ5">
+        <v>1</v>
+      </c>
+      <c r="DA5" t="s">
+        <v>903</v>
+      </c>
+      <c r="DB5">
+        <v>1</v>
+      </c>
+      <c r="DC5">
+        <v>1</v>
+      </c>
+      <c r="DD5">
+        <v>1</v>
+      </c>
+      <c r="DE5" t="s">
+        <v>905</v>
+      </c>
+      <c r="DF5" t="s">
+        <v>794</v>
+      </c>
+      <c r="DG5" t="s">
+        <v>906</v>
+      </c>
+      <c r="DH5">
+        <v>1</v>
+      </c>
+      <c r="DI5">
+        <v>1</v>
+      </c>
+      <c r="DJ5">
+        <v>0</v>
+      </c>
+      <c r="DK5">
+        <v>0</v>
+      </c>
+      <c r="DL5">
+        <v>0</v>
+      </c>
+      <c r="DM5">
+        <v>0</v>
+      </c>
+      <c r="DN5">
+        <v>0</v>
+      </c>
+      <c r="DO5">
+        <v>0</v>
+      </c>
+      <c r="DP5">
+        <v>1</v>
+      </c>
+      <c r="DQ5" t="s">
+        <v>806</v>
+      </c>
+      <c r="EG5">
+        <v>0</v>
+      </c>
+      <c r="EI5">
+        <v>0</v>
+      </c>
+      <c r="EK5">
+        <v>0</v>
+      </c>
+      <c r="UV5" t="s">
+        <v>907</v>
+      </c>
+      <c r="ZK5" s="1"/>
+      <c r="AEF5" s="1"/>
+      <c r="AEL5">
+        <v>885064065</v>
+      </c>
+      <c r="AEM5" t="s">
+        <v>908</v>
+      </c>
+      <c r="AEN5" s="1">
+        <v>46298.597939814812</v>
+      </c>
+      <c r="AEP5" t="s">
+        <v>808</v>
+      </c>
+      <c r="AER5" t="s">
+        <v>823</v>
+      </c>
+      <c r="AES5" t="s">
+        <v>909</v>
+      </c>
+      <c r="AET5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B6" t="s">
+        <v>780</v>
+      </c>
+      <c r="C6" t="s">
+        <v>910</v>
+      </c>
+      <c r="D6" t="s">
+        <v>646</v>
+      </c>
+      <c r="E6" t="s">
+        <v>782</v>
+      </c>
+      <c r="F6" t="s">
+        <v>783</v>
+      </c>
+      <c r="M6" t="s">
+        <v>911</v>
+      </c>
+      <c r="Q6">
+        <v>6</v>
+      </c>
+      <c r="R6">
+        <v>4</v>
+      </c>
+      <c r="S6" t="s">
+        <v>785</v>
+      </c>
+      <c r="T6">
+        <v>10</v>
+      </c>
+      <c r="U6">
+        <v>11</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>785</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>912</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>902</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>903</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>913</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>794</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>902</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>903</v>
+      </c>
+      <c r="BB6">
+        <v>1</v>
+      </c>
+      <c r="BC6">
+        <v>1</v>
+      </c>
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>914</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>790</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>902</v>
+      </c>
+      <c r="BI6">
+        <v>1</v>
+      </c>
+      <c r="BJ6">
+        <v>1</v>
+      </c>
+      <c r="BK6">
+        <v>1</v>
+      </c>
+      <c r="BL6">
+        <v>1</v>
+      </c>
+      <c r="BM6">
+        <v>1</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>903</v>
+      </c>
+      <c r="BO6">
+        <v>1</v>
+      </c>
+      <c r="BP6">
+        <v>1</v>
+      </c>
+      <c r="BQ6">
+        <v>1</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>915</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>794</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>902</v>
+      </c>
+      <c r="BV6">
+        <v>1</v>
+      </c>
+      <c r="BW6">
+        <v>1</v>
+      </c>
+      <c r="BX6">
+        <v>1</v>
+      </c>
+      <c r="BY6">
+        <v>1</v>
+      </c>
+      <c r="BZ6">
+        <v>1</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>903</v>
+      </c>
+      <c r="CB6">
+        <v>1</v>
+      </c>
+      <c r="CC6">
+        <v>1</v>
+      </c>
+      <c r="CD6">
+        <v>1</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>916</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>794</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>902</v>
+      </c>
+      <c r="CI6">
+        <v>1</v>
+      </c>
+      <c r="CJ6">
+        <v>1</v>
+      </c>
+      <c r="CK6">
+        <v>1</v>
+      </c>
+      <c r="CL6">
+        <v>1</v>
+      </c>
+      <c r="CM6">
+        <v>1</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>903</v>
+      </c>
+      <c r="CO6">
+        <v>1</v>
+      </c>
+      <c r="CP6">
+        <v>1</v>
+      </c>
+      <c r="CQ6">
+        <v>1</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>917</v>
+      </c>
+      <c r="CS6" t="s">
+        <v>794</v>
+      </c>
+      <c r="CU6" t="s">
+        <v>902</v>
+      </c>
+      <c r="CV6">
+        <v>1</v>
+      </c>
+      <c r="CW6">
+        <v>1</v>
+      </c>
+      <c r="CX6">
+        <v>1</v>
+      </c>
+      <c r="CY6">
+        <v>1</v>
+      </c>
+      <c r="CZ6">
+        <v>1</v>
+      </c>
+      <c r="DA6" t="s">
+        <v>899</v>
+      </c>
+      <c r="DB6">
+        <v>1</v>
+      </c>
+      <c r="DC6">
+        <v>1</v>
+      </c>
+      <c r="DD6">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="s">
+        <v>918</v>
+      </c>
+      <c r="DF6" t="s">
+        <v>794</v>
+      </c>
+      <c r="DG6" t="s">
+        <v>919</v>
+      </c>
+      <c r="DH6">
+        <v>1</v>
+      </c>
+      <c r="DI6">
+        <v>0</v>
+      </c>
+      <c r="DJ6">
+        <v>0</v>
+      </c>
+      <c r="DK6">
+        <v>1</v>
+      </c>
+      <c r="DL6">
+        <v>1</v>
+      </c>
+      <c r="DM6">
+        <v>0</v>
+      </c>
+      <c r="DN6">
+        <v>0</v>
+      </c>
+      <c r="DO6">
+        <v>1</v>
+      </c>
+      <c r="DP6">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="s">
+        <v>806</v>
+      </c>
+      <c r="EG6">
+        <v>0</v>
+      </c>
+      <c r="EI6">
+        <v>0</v>
+      </c>
+      <c r="EK6">
+        <v>5</v>
+      </c>
+      <c r="UV6" t="s">
+        <v>920</v>
+      </c>
+      <c r="ZK6" s="1"/>
+      <c r="AEF6" s="1"/>
+      <c r="AEL6">
+        <v>885072414</v>
+      </c>
+      <c r="AEM6" t="s">
+        <v>921</v>
+      </c>
+      <c r="AEN6" s="1">
+        <v>46298.609120370369</v>
+      </c>
+      <c r="AEP6" t="s">
+        <v>808</v>
+      </c>
+      <c r="AER6" t="s">
+        <v>823</v>
+      </c>
+      <c r="AES6" t="s">
+        <v>922</v>
+      </c>
+      <c r="AET6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B7" t="s">
+        <v>780</v>
+      </c>
+      <c r="C7" t="s">
+        <v>923</v>
+      </c>
+      <c r="D7" t="s">
+        <v>650</v>
+      </c>
+      <c r="E7" t="s">
+        <v>782</v>
+      </c>
+      <c r="F7" t="s">
+        <v>783</v>
+      </c>
+      <c r="J7" t="s">
+        <v>924</v>
+      </c>
+      <c r="Q7">
+        <v>17</v>
+      </c>
+      <c r="R7">
+        <v>7</v>
+      </c>
+      <c r="S7" t="s">
+        <v>785</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>28</v>
+      </c>
+      <c r="V7">
+        <v>8</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>785</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>925</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>926</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>796</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>927</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>790</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>928</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>796</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>1</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>927</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>794</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>929</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>1</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>1</v>
+      </c>
+      <c r="BM7">
+        <v>1</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>903</v>
+      </c>
+      <c r="BO7">
+        <v>1</v>
+      </c>
+      <c r="BP7">
+        <v>1</v>
+      </c>
+      <c r="BQ7">
+        <v>1</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>930</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>790</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>931</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>1</v>
+      </c>
+      <c r="BX7">
+        <v>1</v>
+      </c>
+      <c r="BY7">
+        <v>1</v>
+      </c>
+      <c r="BZ7">
+        <v>1</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>903</v>
+      </c>
+      <c r="CB7">
+        <v>1</v>
+      </c>
+      <c r="CC7">
+        <v>1</v>
+      </c>
+      <c r="CD7">
+        <v>1</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>932</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>790</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>902</v>
+      </c>
+      <c r="CI7">
+        <v>1</v>
+      </c>
+      <c r="CJ7">
+        <v>1</v>
+      </c>
+      <c r="CK7">
+        <v>1</v>
+      </c>
+      <c r="CL7">
+        <v>1</v>
+      </c>
+      <c r="CM7">
+        <v>1</v>
+      </c>
+      <c r="CN7" t="s">
+        <v>903</v>
+      </c>
+      <c r="CO7">
+        <v>1</v>
+      </c>
+      <c r="CP7">
+        <v>1</v>
+      </c>
+      <c r="CQ7">
+        <v>1</v>
+      </c>
+      <c r="CR7" t="s">
+        <v>933</v>
+      </c>
+      <c r="CS7" t="s">
+        <v>794</v>
+      </c>
+      <c r="CU7" t="s">
+        <v>931</v>
+      </c>
+      <c r="CV7">
+        <v>0</v>
+      </c>
+      <c r="CW7">
+        <v>1</v>
+      </c>
+      <c r="CX7">
+        <v>1</v>
+      </c>
+      <c r="CY7">
+        <v>1</v>
+      </c>
+      <c r="CZ7">
+        <v>1</v>
+      </c>
+      <c r="DA7" t="s">
+        <v>903</v>
+      </c>
+      <c r="DB7">
+        <v>1</v>
+      </c>
+      <c r="DC7">
+        <v>1</v>
+      </c>
+      <c r="DD7">
+        <v>1</v>
+      </c>
+      <c r="DE7" t="s">
+        <v>932</v>
+      </c>
+      <c r="DF7" t="s">
+        <v>790</v>
+      </c>
+      <c r="DG7" t="s">
+        <v>934</v>
+      </c>
+      <c r="DH7">
+        <v>1</v>
+      </c>
+      <c r="DI7">
+        <v>1</v>
+      </c>
+      <c r="DJ7">
+        <v>0</v>
+      </c>
+      <c r="DK7">
+        <v>1</v>
+      </c>
+      <c r="DL7">
+        <v>1</v>
+      </c>
+      <c r="DM7">
+        <v>1</v>
+      </c>
+      <c r="DN7">
+        <v>0</v>
+      </c>
+      <c r="DO7">
+        <v>0</v>
+      </c>
+      <c r="DP7">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="s">
+        <v>785</v>
+      </c>
+      <c r="DR7" t="s">
+        <v>935</v>
+      </c>
+      <c r="DS7">
+        <v>0</v>
+      </c>
+      <c r="DT7">
+        <v>0</v>
+      </c>
+      <c r="DU7">
+        <v>1</v>
+      </c>
+      <c r="DV7">
+        <v>1</v>
+      </c>
+      <c r="DW7">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="s">
+        <v>936</v>
+      </c>
+      <c r="DY7">
+        <v>1</v>
+      </c>
+      <c r="DZ7">
+        <v>0</v>
+      </c>
+      <c r="EA7">
+        <v>0</v>
+      </c>
+      <c r="EB7">
+        <v>0</v>
+      </c>
+      <c r="EG7">
+        <v>0</v>
+      </c>
+      <c r="EI7">
+        <v>0</v>
+      </c>
+      <c r="EK7">
+        <v>1</v>
+      </c>
+      <c r="UV7" t="s">
+        <v>937</v>
+      </c>
+      <c r="ZK7" s="1"/>
+      <c r="AEF7" s="1"/>
+      <c r="AEL7">
+        <v>885187630</v>
+      </c>
+      <c r="AEM7" t="s">
+        <v>938</v>
+      </c>
+      <c r="AEN7" s="1">
+        <v>46298.763460648152</v>
+      </c>
+      <c r="AEP7" t="s">
+        <v>808</v>
+      </c>
+      <c r="AER7" t="s">
+        <v>823</v>
+      </c>
+      <c r="AES7" t="s">
+        <v>939</v>
+      </c>
+      <c r="AET7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B8" t="s">
+        <v>780</v>
+      </c>
+      <c r="C8" t="s">
+        <v>940</v>
+      </c>
+      <c r="D8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E8" t="s">
+        <v>782</v>
+      </c>
+      <c r="F8" t="s">
+        <v>826</v>
+      </c>
+      <c r="K8" t="s">
+        <v>941</v>
+      </c>
+      <c r="EL8" t="s">
+        <v>828</v>
+      </c>
+      <c r="FN8" t="s">
+        <v>942</v>
+      </c>
+      <c r="FO8" t="s">
+        <v>942</v>
+      </c>
+      <c r="FP8" t="s">
+        <v>942</v>
+      </c>
+      <c r="FQ8">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="s">
+        <v>943</v>
+      </c>
+      <c r="FT8" t="s">
+        <v>944</v>
+      </c>
+      <c r="FU8" t="s">
+        <v>945</v>
+      </c>
+      <c r="FV8">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="s">
+        <v>946</v>
+      </c>
+      <c r="FY8" t="s">
+        <v>947</v>
+      </c>
+      <c r="FZ8" t="s">
+        <v>942</v>
+      </c>
+      <c r="GA8">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="s">
+        <v>841</v>
+      </c>
+      <c r="GD8" t="s">
+        <v>948</v>
+      </c>
+      <c r="GE8" t="s">
+        <v>942</v>
+      </c>
+      <c r="GF8">
+        <v>0</v>
+      </c>
+      <c r="GH8" t="s">
+        <v>949</v>
+      </c>
+      <c r="GI8" t="s">
+        <v>950</v>
+      </c>
+      <c r="GJ8" t="s">
+        <v>942</v>
+      </c>
+      <c r="GK8">
+        <v>2</v>
+      </c>
+      <c r="GL8" t="s">
+        <v>951</v>
+      </c>
+      <c r="GM8">
+        <v>1</v>
+      </c>
+      <c r="GN8">
+        <v>1</v>
+      </c>
+      <c r="GO8">
+        <v>0</v>
+      </c>
+      <c r="GP8">
+        <v>0</v>
+      </c>
+      <c r="GQ8">
+        <v>1</v>
+      </c>
+      <c r="GR8">
+        <v>0</v>
+      </c>
+      <c r="GS8">
+        <v>0</v>
+      </c>
+      <c r="GT8" t="s">
+        <v>785</v>
+      </c>
+      <c r="GU8" t="s">
+        <v>785</v>
+      </c>
+      <c r="GV8" t="s">
+        <v>785</v>
+      </c>
+      <c r="GW8" t="s">
+        <v>785</v>
+      </c>
+      <c r="GX8" t="s">
+        <v>952</v>
+      </c>
+      <c r="HE8" t="s">
+        <v>953</v>
+      </c>
+      <c r="HF8">
+        <v>2</v>
+      </c>
+      <c r="HG8" t="s">
+        <v>954</v>
+      </c>
+      <c r="HI8" t="s">
+        <v>840</v>
+      </c>
+      <c r="HJ8">
+        <v>10</v>
+      </c>
+      <c r="HK8" t="s">
+        <v>955</v>
+      </c>
+      <c r="HM8" t="s">
+        <v>840</v>
+      </c>
+      <c r="HN8">
+        <v>6</v>
+      </c>
+      <c r="HO8" t="s">
+        <v>927</v>
+      </c>
+      <c r="HQ8" t="s">
+        <v>956</v>
+      </c>
+      <c r="HR8">
+        <v>1</v>
+      </c>
+      <c r="HS8" t="s">
+        <v>954</v>
+      </c>
+      <c r="HU8" t="s">
+        <v>840</v>
+      </c>
+      <c r="HV8">
+        <v>8</v>
+      </c>
+      <c r="HW8" t="s">
+        <v>957</v>
+      </c>
+      <c r="IG8" t="s">
+        <v>958</v>
+      </c>
+      <c r="IH8" t="s">
+        <v>843</v>
+      </c>
+      <c r="II8" t="s">
+        <v>955</v>
+      </c>
+      <c r="IJ8" t="s">
+        <v>959</v>
+      </c>
+      <c r="IK8" t="s">
+        <v>841</v>
+      </c>
+      <c r="IL8" t="s">
+        <v>790</v>
+      </c>
+      <c r="IN8" t="s">
+        <v>842</v>
+      </c>
+      <c r="IO8" t="s">
+        <v>843</v>
+      </c>
+      <c r="IP8" t="s">
+        <v>927</v>
+      </c>
+      <c r="IQ8" t="s">
+        <v>959</v>
+      </c>
+      <c r="IR8" t="s">
+        <v>930</v>
+      </c>
+      <c r="IS8" t="s">
+        <v>794</v>
+      </c>
+      <c r="IU8" t="s">
+        <v>960</v>
+      </c>
+      <c r="IV8" t="s">
+        <v>843</v>
+      </c>
+      <c r="IW8" t="s">
+        <v>961</v>
+      </c>
+      <c r="IX8" t="s">
+        <v>962</v>
+      </c>
+      <c r="IY8" t="s">
+        <v>933</v>
+      </c>
+      <c r="IZ8" t="s">
+        <v>790</v>
+      </c>
+      <c r="JB8" t="s">
+        <v>960</v>
+      </c>
+      <c r="JC8" t="s">
+        <v>843</v>
+      </c>
+      <c r="JD8" t="s">
+        <v>963</v>
+      </c>
+      <c r="JE8" t="s">
+        <v>959</v>
+      </c>
+      <c r="JF8" t="s">
+        <v>957</v>
+      </c>
+      <c r="JG8" t="s">
+        <v>790</v>
+      </c>
+      <c r="JI8" t="s">
+        <v>960</v>
+      </c>
+      <c r="JJ8" t="s">
+        <v>843</v>
+      </c>
+      <c r="JK8" t="s">
+        <v>963</v>
+      </c>
+      <c r="JL8" t="s">
+        <v>962</v>
+      </c>
+      <c r="JM8" t="s">
+        <v>963</v>
+      </c>
+      <c r="JN8" t="s">
+        <v>790</v>
+      </c>
+      <c r="JP8" t="s">
+        <v>960</v>
+      </c>
+      <c r="JQ8" t="s">
+        <v>843</v>
+      </c>
+      <c r="JR8" t="s">
+        <v>927</v>
+      </c>
+      <c r="JS8" t="s">
+        <v>962</v>
+      </c>
+      <c r="JT8" t="s">
+        <v>927</v>
+      </c>
+      <c r="JU8" t="s">
+        <v>794</v>
+      </c>
+      <c r="JV8" t="s">
+        <v>964</v>
+      </c>
+      <c r="JW8">
+        <v>1</v>
+      </c>
+      <c r="JX8">
+        <v>0</v>
+      </c>
+      <c r="JY8">
+        <v>1</v>
+      </c>
+      <c r="JZ8">
+        <v>1</v>
+      </c>
+      <c r="KA8" t="s">
+        <v>806</v>
+      </c>
+      <c r="KB8" t="s">
+        <v>965</v>
+      </c>
+      <c r="KC8" t="s">
+        <v>966</v>
+      </c>
+      <c r="KD8" t="s">
+        <v>967</v>
+      </c>
+      <c r="KE8" t="s">
+        <v>968</v>
+      </c>
+      <c r="OA8">
+        <v>0</v>
+      </c>
+      <c r="OB8">
+        <v>0</v>
+      </c>
+      <c r="OD8">
+        <v>0</v>
+      </c>
+      <c r="OE8">
+        <v>0</v>
+      </c>
+      <c r="OG8">
+        <v>650</v>
+      </c>
+      <c r="OH8">
+        <v>375</v>
+      </c>
+      <c r="OJ8">
+        <v>254</v>
+      </c>
+      <c r="OK8">
+        <v>125</v>
+      </c>
+      <c r="OM8">
+        <v>86</v>
+      </c>
+      <c r="ON8">
+        <v>91</v>
+      </c>
+      <c r="OP8">
+        <v>44</v>
+      </c>
+      <c r="OQ8">
+        <v>67</v>
+      </c>
+      <c r="UV8" t="s">
+        <v>969</v>
+      </c>
+      <c r="ZK8" s="1"/>
+      <c r="AEF8" s="1"/>
+      <c r="AEL8">
+        <v>885200260</v>
+      </c>
+      <c r="AEM8" t="s">
+        <v>970</v>
+      </c>
+      <c r="AEN8" s="1">
+        <v>46298.788032407407</v>
+      </c>
+      <c r="AEP8" t="s">
+        <v>808</v>
+      </c>
+      <c r="AER8" t="s">
+        <v>823</v>
+      </c>
+      <c r="AES8" t="s">
+        <v>971</v>
+      </c>
+      <c r="AET8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B9" t="s">
+        <v>780</v>
+      </c>
+      <c r="C9" t="s">
+        <v>972</v>
+      </c>
+      <c r="D9" t="s">
+        <v>651</v>
+      </c>
+      <c r="E9" t="s">
+        <v>782</v>
+      </c>
+      <c r="F9" t="s">
+        <v>783</v>
+      </c>
+      <c r="K9" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q9">
+        <v>5</v>
+      </c>
+      <c r="R9">
+        <v>6</v>
+      </c>
+      <c r="S9" t="s">
+        <v>785</v>
+      </c>
+      <c r="T9">
+        <v>10</v>
+      </c>
+      <c r="U9">
+        <v>5</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>806</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>973</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+      <c r="AM9">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>801</v>
+      </c>
+      <c r="AO9">
+        <v>1</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>833</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>790</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>974</v>
+      </c>
+      <c r="AV9">
+        <v>1</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>975</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>833</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>794</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>976</v>
+      </c>
+      <c r="BI9">
+        <v>1</v>
+      </c>
+      <c r="BJ9">
+        <v>1</v>
+      </c>
+      <c r="BK9">
+        <v>1</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>903</v>
+      </c>
+      <c r="BO9">
+        <v>1</v>
+      </c>
+      <c r="BP9">
+        <v>1</v>
+      </c>
+      <c r="BQ9">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>945</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>794</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>977</v>
+      </c>
+      <c r="BV9">
+        <v>1</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>1</v>
+      </c>
+      <c r="BZ9">
+        <v>1</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>792</v>
+      </c>
+      <c r="CB9">
+        <v>0</v>
+      </c>
+      <c r="CC9">
+        <v>1</v>
+      </c>
+      <c r="CD9">
+        <v>1</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>833</v>
+      </c>
+      <c r="CF9" t="s">
+        <v>794</v>
+      </c>
+      <c r="CH9" t="s">
+        <v>931</v>
+      </c>
+      <c r="CI9">
+        <v>0</v>
+      </c>
+      <c r="CJ9">
+        <v>1</v>
+      </c>
+      <c r="CK9">
+        <v>1</v>
+      </c>
+      <c r="CL9">
+        <v>1</v>
+      </c>
+      <c r="CM9">
+        <v>1</v>
+      </c>
+      <c r="CN9" t="s">
+        <v>903</v>
+      </c>
+      <c r="CO9">
+        <v>1</v>
+      </c>
+      <c r="CP9">
+        <v>1</v>
+      </c>
+      <c r="CQ9">
+        <v>1</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>833</v>
+      </c>
+      <c r="CS9" t="s">
+        <v>790</v>
+      </c>
+      <c r="CU9" t="s">
+        <v>803</v>
+      </c>
+      <c r="CV9">
+        <v>1</v>
+      </c>
+      <c r="CW9">
+        <v>1</v>
+      </c>
+      <c r="CX9">
+        <v>0</v>
+      </c>
+      <c r="CY9">
+        <v>0</v>
+      </c>
+      <c r="CZ9">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="s">
+        <v>801</v>
+      </c>
+      <c r="DB9">
+        <v>1</v>
+      </c>
+      <c r="DC9">
+        <v>0</v>
+      </c>
+      <c r="DD9">
+        <v>1</v>
+      </c>
+      <c r="DE9" t="s">
+        <v>945</v>
+      </c>
+      <c r="DF9" t="s">
+        <v>790</v>
+      </c>
+      <c r="DG9" t="s">
+        <v>978</v>
+      </c>
+      <c r="DH9">
+        <v>0</v>
+      </c>
+      <c r="DI9">
+        <v>0</v>
+      </c>
+      <c r="DJ9">
+        <v>0</v>
+      </c>
+      <c r="DK9">
+        <v>0</v>
+      </c>
+      <c r="DL9">
+        <v>1</v>
+      </c>
+      <c r="DM9">
+        <v>0</v>
+      </c>
+      <c r="DN9">
+        <v>0</v>
+      </c>
+      <c r="DO9">
+        <v>0</v>
+      </c>
+      <c r="DP9">
+        <v>1</v>
+      </c>
+      <c r="DQ9" t="s">
+        <v>806</v>
+      </c>
+      <c r="EG9">
+        <v>0</v>
+      </c>
+      <c r="EI9">
+        <v>0</v>
+      </c>
+      <c r="EK9">
+        <v>0</v>
+      </c>
+      <c r="UV9" t="s">
+        <v>979</v>
+      </c>
+      <c r="ZK9" s="1"/>
+      <c r="AEF9" s="1"/>
+      <c r="AEL9">
+        <v>885201939</v>
+      </c>
+      <c r="AEM9" t="s">
+        <v>980</v>
+      </c>
+      <c r="AEN9" s="1">
+        <v>46298.791562500002</v>
+      </c>
+      <c r="AEP9" t="s">
+        <v>808</v>
+      </c>
+      <c r="AER9" t="s">
+        <v>823</v>
+      </c>
+      <c r="AES9" t="s">
+        <v>981</v>
+      </c>
+      <c r="AET9">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3986BB43-46E3-6942-B0E0-1963076D7C66}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FF9D525-E66B-8F40-AD3B-2A5C8586E827}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="1038">
   <si>
     <t>Date</t>
   </si>
@@ -2966,6 +2966,174 @@
   </si>
   <si>
     <t>uuid:d626f565-e3e3-4557-8a2f-301c66e57a6f</t>
+  </si>
+  <si>
+    <t>Lobur stephen</t>
+  </si>
+  <si>
+    <t>ST MARYS P/S</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Patrons</t>
+  </si>
+  <si>
+    <t>Class teachers</t>
+  </si>
+  <si>
+    <t>All staff</t>
+  </si>
+  <si>
+    <t>L C1</t>
+  </si>
+  <si>
+    <t>Caregivers</t>
+  </si>
+  <si>
+    <t>Community members</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Structured dialogue on rebalancing chores Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>Locally available materials</t>
+  </si>
+  <si>
+    <t>The girl may not concentrate like aboy</t>
+  </si>
+  <si>
+    <t>To make work easy</t>
+  </si>
+  <si>
+    <t>To offer campany to and security to girls from rapiest</t>
+  </si>
+  <si>
+    <t>Share work with my sister</t>
+  </si>
+  <si>
+    <t>Girls are not to look after animas while boys go to school</t>
+  </si>
+  <si>
+    <t>Nutrition is important for concentration</t>
+  </si>
+  <si>
+    <t>Says "hurry up" or "wake up early" without mentioning sharing the work</t>
+  </si>
+  <si>
+    <t>Do not know</t>
+  </si>
+  <si>
+    <t>Am in P1</t>
+  </si>
+  <si>
+    <t>Equal rights</t>
+  </si>
+  <si>
+    <t>Blessings xan come from anybody as God plans, so never leave one child behind</t>
+  </si>
+  <si>
+    <t>Everyone knows what to do</t>
+  </si>
+  <si>
+    <t>Am not sure</t>
+  </si>
+  <si>
+    <t>To make everyone active</t>
+  </si>
+  <si>
+    <t>When you leave one he /she will be lazy</t>
+  </si>
+  <si>
+    <t>I dont know</t>
+  </si>
+  <si>
+    <t>Was shy</t>
+  </si>
+  <si>
+    <t>Lack of preparation confidence/skills</t>
+  </si>
+  <si>
+    <t>We dont know what to put how to make it</t>
+  </si>
+  <si>
+    <t>Little time</t>
+  </si>
+  <si>
+    <t>Massive attendence and participation</t>
+  </si>
+  <si>
+    <t>Mobilise with the school patron early</t>
+  </si>
+  <si>
+    <t>We will continue to support the nurtition club and see that it grows to be the major club in our school</t>
+  </si>
+  <si>
+    <t>Support them with vegetable seeds to boost their kitchen gardens and do more demonstrations to equip them with skills to do it at home</t>
+  </si>
+  <si>
+    <t>8ba868d6-3a41-4da4-bd58-8a10962b05b2</t>
+  </si>
+  <si>
+    <t>uuid:8ba868d6-3a41-4da4-bd58-8a10962b05b2</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>NAPIANANYA P/S</t>
+  </si>
+  <si>
+    <t>Strengthen the nutrition club in school</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Rebalancing morning water/firewood chores so girls stay in school Using improved cooking methods to consume less firewood Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>Going to sensitise communities to embrace this knowledge they have recieved</t>
+  </si>
+  <si>
+    <t>Im ready to do it in my community</t>
+  </si>
+  <si>
+    <t>Rebalancing morning water/firewood chores so girls stay in school Fair and equal plate sharing between boys and girls at home</t>
+  </si>
+  <si>
+    <t>Mobilise learners for the bus visit</t>
+  </si>
+  <si>
+    <t>Support nutrition club</t>
+  </si>
+  <si>
+    <t>This materials are locally available</t>
+  </si>
+  <si>
+    <t>Metu Nutrition Posters Game for the school WFP Toll-Free Feedback Display Board Nutri calendar Pledge / Commitment card</t>
+  </si>
+  <si>
+    <t>All club patrons and VHT embraced the campegein idea and said it is going to help when this idea is implemented. They requested for material to be availed early to ease the implimentation of campegien well</t>
+  </si>
+  <si>
+    <t>57d74563-4421-4576-b15b-856571694a91</t>
+  </si>
+  <si>
+    <t>uuid:57d74563-4421-4576-b15b-856571694a91</t>
+  </si>
+  <si>
+    <t>Tuesday and thursday every week activity</t>
   </si>
 </sst>
 </file>
@@ -3038,8 +3206,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET9" totalsRowShown="0">
-  <autoFilter ref="A1:AET9" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET11" totalsRowShown="0">
+  <autoFilter ref="A1:AET11" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="826">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -4159,7 +4327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AET9"/>
+  <dimension ref="A1:AET11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -8603,9 +8771,6 @@
       <c r="AQ7">
         <v>0</v>
       </c>
-      <c r="AR7" t="s">
-        <v>927</v>
-      </c>
       <c r="AS7" t="s">
         <v>790</v>
       </c>
@@ -8675,9 +8840,6 @@
       <c r="BQ7">
         <v>1</v>
       </c>
-      <c r="BR7" t="s">
-        <v>930</v>
-      </c>
       <c r="BS7" t="s">
         <v>790</v>
       </c>
@@ -8710,9 +8872,6 @@
       </c>
       <c r="CD7">
         <v>1</v>
-      </c>
-      <c r="CE7" t="s">
-        <v>932</v>
       </c>
       <c r="CF7" t="s">
         <v>790</v>
@@ -9340,9 +9499,6 @@
       <c r="AQ9">
         <v>1</v>
       </c>
-      <c r="AR9" t="s">
-        <v>833</v>
-      </c>
       <c r="AS9" t="s">
         <v>790</v>
       </c>
@@ -9412,9 +9568,6 @@
       <c r="BQ9">
         <v>1</v>
       </c>
-      <c r="BR9" t="s">
-        <v>945</v>
-      </c>
       <c r="BS9" t="s">
         <v>794</v>
       </c>
@@ -9447,9 +9600,6 @@
       </c>
       <c r="CD9">
         <v>1</v>
-      </c>
-      <c r="CE9" t="s">
-        <v>833</v>
       </c>
       <c r="CF9" t="s">
         <v>794</v>
@@ -9593,6 +9743,695 @@
       </c>
       <c r="AET9">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B10" t="s">
+        <v>780</v>
+      </c>
+      <c r="C10" t="s">
+        <v>982</v>
+      </c>
+      <c r="D10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E10" t="s">
+        <v>782</v>
+      </c>
+      <c r="F10" t="s">
+        <v>826</v>
+      </c>
+      <c r="N10" t="s">
+        <v>983</v>
+      </c>
+      <c r="EL10" t="s">
+        <v>828</v>
+      </c>
+      <c r="FN10" t="s">
+        <v>829</v>
+      </c>
+      <c r="FO10" t="s">
+        <v>984</v>
+      </c>
+      <c r="FP10" t="s">
+        <v>985</v>
+      </c>
+      <c r="FS10" t="s">
+        <v>984</v>
+      </c>
+      <c r="FT10" t="s">
+        <v>984</v>
+      </c>
+      <c r="FU10" t="s">
+        <v>986</v>
+      </c>
+      <c r="FX10" t="s">
+        <v>949</v>
+      </c>
+      <c r="FY10" t="s">
+        <v>987</v>
+      </c>
+      <c r="FZ10" t="s">
+        <v>988</v>
+      </c>
+      <c r="GC10" t="s">
+        <v>989</v>
+      </c>
+      <c r="GD10" t="s">
+        <v>990</v>
+      </c>
+      <c r="GE10" t="s">
+        <v>991</v>
+      </c>
+      <c r="GH10" t="s">
+        <v>992</v>
+      </c>
+      <c r="GI10" t="s">
+        <v>993</v>
+      </c>
+      <c r="GJ10" t="s">
+        <v>994</v>
+      </c>
+      <c r="GL10" t="s">
+        <v>995</v>
+      </c>
+      <c r="GM10">
+        <v>1</v>
+      </c>
+      <c r="GN10">
+        <v>0</v>
+      </c>
+      <c r="GO10">
+        <v>0</v>
+      </c>
+      <c r="GP10">
+        <v>1</v>
+      </c>
+      <c r="GQ10">
+        <v>0</v>
+      </c>
+      <c r="GR10">
+        <v>0</v>
+      </c>
+      <c r="GS10">
+        <v>1</v>
+      </c>
+      <c r="GT10" t="s">
+        <v>785</v>
+      </c>
+      <c r="GU10" t="s">
+        <v>785</v>
+      </c>
+      <c r="GV10" t="s">
+        <v>806</v>
+      </c>
+      <c r="GW10" t="s">
+        <v>785</v>
+      </c>
+      <c r="GX10" t="s">
+        <v>996</v>
+      </c>
+      <c r="HE10" t="s">
+        <v>840</v>
+      </c>
+      <c r="HF10">
+        <v>80</v>
+      </c>
+      <c r="HG10" t="s">
+        <v>997</v>
+      </c>
+      <c r="HI10" t="s">
+        <v>840</v>
+      </c>
+      <c r="HJ10">
+        <v>90</v>
+      </c>
+      <c r="HK10" t="s">
+        <v>998</v>
+      </c>
+      <c r="HM10" t="s">
+        <v>840</v>
+      </c>
+      <c r="HN10">
+        <v>105</v>
+      </c>
+      <c r="HO10" t="s">
+        <v>999</v>
+      </c>
+      <c r="HQ10" t="s">
+        <v>840</v>
+      </c>
+      <c r="HR10">
+        <v>50</v>
+      </c>
+      <c r="HS10" t="s">
+        <v>1000</v>
+      </c>
+      <c r="HU10" t="s">
+        <v>839</v>
+      </c>
+      <c r="HV10">
+        <v>120</v>
+      </c>
+      <c r="HW10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="IG10" t="s">
+        <v>842</v>
+      </c>
+      <c r="IH10" t="s">
+        <v>843</v>
+      </c>
+      <c r="II10" t="s">
+        <v>998</v>
+      </c>
+      <c r="IJ10" t="s">
+        <v>959</v>
+      </c>
+      <c r="IK10" t="s">
+        <v>1002</v>
+      </c>
+      <c r="IL10" t="s">
+        <v>794</v>
+      </c>
+      <c r="IN10" t="s">
+        <v>958</v>
+      </c>
+      <c r="IO10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="IP10" t="s">
+        <v>1004</v>
+      </c>
+      <c r="IQ10" t="s">
+        <v>962</v>
+      </c>
+      <c r="IR10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="IS10" t="s">
+        <v>790</v>
+      </c>
+      <c r="IU10" t="s">
+        <v>842</v>
+      </c>
+      <c r="IV10" t="s">
+        <v>843</v>
+      </c>
+      <c r="IW10" t="s">
+        <v>1006</v>
+      </c>
+      <c r="IX10" t="s">
+        <v>959</v>
+      </c>
+      <c r="IY10" t="s">
+        <v>1007</v>
+      </c>
+      <c r="IZ10" t="s">
+        <v>794</v>
+      </c>
+      <c r="JB10" t="s">
+        <v>958</v>
+      </c>
+      <c r="JC10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="JD10" t="s">
+        <v>1008</v>
+      </c>
+      <c r="JE10" t="s">
+        <v>962</v>
+      </c>
+      <c r="JF10" t="s">
+        <v>1009</v>
+      </c>
+      <c r="JG10" t="s">
+        <v>790</v>
+      </c>
+      <c r="JI10" t="s">
+        <v>842</v>
+      </c>
+      <c r="JJ10" t="s">
+        <v>843</v>
+      </c>
+      <c r="JK10" t="s">
+        <v>1010</v>
+      </c>
+      <c r="JL10" t="s">
+        <v>959</v>
+      </c>
+      <c r="JM10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="JN10" t="s">
+        <v>794</v>
+      </c>
+      <c r="JP10" t="s">
+        <v>960</v>
+      </c>
+      <c r="JR10" t="s">
+        <v>1012</v>
+      </c>
+      <c r="JS10" t="s">
+        <v>962</v>
+      </c>
+      <c r="JT10" t="s">
+        <v>1013</v>
+      </c>
+      <c r="JU10" t="s">
+        <v>790</v>
+      </c>
+      <c r="JV10" t="s">
+        <v>1014</v>
+      </c>
+      <c r="JW10">
+        <v>1</v>
+      </c>
+      <c r="JX10">
+        <v>0</v>
+      </c>
+      <c r="JY10">
+        <v>0</v>
+      </c>
+      <c r="JZ10">
+        <v>0</v>
+      </c>
+      <c r="KA10" t="s">
+        <v>1015</v>
+      </c>
+      <c r="KB10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="KC10" t="s">
+        <v>1017</v>
+      </c>
+      <c r="KD10" t="s">
+        <v>1018</v>
+      </c>
+      <c r="KE10" t="s">
+        <v>1019</v>
+      </c>
+      <c r="OA10">
+        <v>90</v>
+      </c>
+      <c r="OB10">
+        <v>105</v>
+      </c>
+      <c r="OD10">
+        <v>90</v>
+      </c>
+      <c r="OE10">
+        <v>140</v>
+      </c>
+      <c r="OG10">
+        <v>150</v>
+      </c>
+      <c r="OH10">
+        <v>180</v>
+      </c>
+      <c r="OJ10">
+        <v>150</v>
+      </c>
+      <c r="OK10">
+        <v>200</v>
+      </c>
+      <c r="OM10">
+        <v>118</v>
+      </c>
+      <c r="ON10">
+        <v>105</v>
+      </c>
+      <c r="OP10">
+        <v>100</v>
+      </c>
+      <c r="OQ10">
+        <v>90</v>
+      </c>
+      <c r="UV10" t="s">
+        <v>1020</v>
+      </c>
+      <c r="ZK10" s="1"/>
+      <c r="AEF10" s="1"/>
+      <c r="AEL10">
+        <v>885374147</v>
+      </c>
+      <c r="AEM10" t="s">
+        <v>1021</v>
+      </c>
+      <c r="AEN10" s="1">
+        <v>46299.338842592602</v>
+      </c>
+      <c r="AEP10" t="s">
+        <v>808</v>
+      </c>
+      <c r="AER10" t="s">
+        <v>823</v>
+      </c>
+      <c r="AES10" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AET10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B11" t="s">
+        <v>780</v>
+      </c>
+      <c r="C11" t="s">
+        <v>982</v>
+      </c>
+      <c r="D11" t="s">
+        <v>653</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F11" t="s">
+        <v>783</v>
+      </c>
+      <c r="N11" t="s">
+        <v>1024</v>
+      </c>
+      <c r="Q11">
+        <v>6</v>
+      </c>
+      <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11" t="s">
+        <v>806</v>
+      </c>
+      <c r="T11">
+        <v>2</v>
+      </c>
+      <c r="U11">
+        <v>6</v>
+      </c>
+      <c r="V11">
+        <v>3</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>785</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>973</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+      <c r="AM11">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>796</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>1</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>790</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>1026</v>
+      </c>
+      <c r="AV11">
+        <v>1</v>
+      </c>
+      <c r="AW11">
+        <v>1</v>
+      </c>
+      <c r="AX11">
+        <v>1</v>
+      </c>
+      <c r="AY11">
+        <v>1</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>801</v>
+      </c>
+      <c r="BB11">
+        <v>1</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>1027</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>794</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>974</v>
+      </c>
+      <c r="BI11">
+        <v>1</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>1</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>792</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>1</v>
+      </c>
+      <c r="BQ11">
+        <v>1</v>
+      </c>
+      <c r="BR11" t="s">
+        <v>1028</v>
+      </c>
+      <c r="BS11" t="s">
+        <v>794</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>1029</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>1</v>
+      </c>
+      <c r="BZ11">
+        <v>1</v>
+      </c>
+      <c r="CA11" t="s">
+        <v>792</v>
+      </c>
+      <c r="CB11">
+        <v>0</v>
+      </c>
+      <c r="CC11">
+        <v>1</v>
+      </c>
+      <c r="CD11">
+        <v>1</v>
+      </c>
+      <c r="CE11" t="s">
+        <v>1030</v>
+      </c>
+      <c r="CF11" t="s">
+        <v>790</v>
+      </c>
+      <c r="CH11" t="s">
+        <v>798</v>
+      </c>
+      <c r="CI11">
+        <v>0</v>
+      </c>
+      <c r="CJ11">
+        <v>0</v>
+      </c>
+      <c r="CK11">
+        <v>1</v>
+      </c>
+      <c r="CL11">
+        <v>1</v>
+      </c>
+      <c r="CM11">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="s">
+        <v>796</v>
+      </c>
+      <c r="CO11">
+        <v>0</v>
+      </c>
+      <c r="CP11">
+        <v>1</v>
+      </c>
+      <c r="CQ11">
+        <v>0</v>
+      </c>
+      <c r="CR11" t="s">
+        <v>1031</v>
+      </c>
+      <c r="CS11" t="s">
+        <v>790</v>
+      </c>
+      <c r="CU11" t="s">
+        <v>803</v>
+      </c>
+      <c r="CV11">
+        <v>1</v>
+      </c>
+      <c r="CW11">
+        <v>1</v>
+      </c>
+      <c r="CX11">
+        <v>0</v>
+      </c>
+      <c r="CY11">
+        <v>0</v>
+      </c>
+      <c r="CZ11">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="s">
+        <v>796</v>
+      </c>
+      <c r="DB11">
+        <v>0</v>
+      </c>
+      <c r="DC11">
+        <v>1</v>
+      </c>
+      <c r="DD11">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="s">
+        <v>1032</v>
+      </c>
+      <c r="DF11" t="s">
+        <v>794</v>
+      </c>
+      <c r="DG11" t="s">
+        <v>1033</v>
+      </c>
+      <c r="DH11">
+        <v>0</v>
+      </c>
+      <c r="DI11">
+        <v>1</v>
+      </c>
+      <c r="DJ11">
+        <v>0</v>
+      </c>
+      <c r="DK11">
+        <v>1</v>
+      </c>
+      <c r="DL11">
+        <v>1</v>
+      </c>
+      <c r="DM11">
+        <v>1</v>
+      </c>
+      <c r="DN11">
+        <v>0</v>
+      </c>
+      <c r="DO11">
+        <v>0</v>
+      </c>
+      <c r="DP11">
+        <v>1</v>
+      </c>
+      <c r="DQ11" t="s">
+        <v>806</v>
+      </c>
+      <c r="EG11">
+        <v>0</v>
+      </c>
+      <c r="EI11">
+        <v>0</v>
+      </c>
+      <c r="EK11">
+        <v>1</v>
+      </c>
+      <c r="UV11" t="s">
+        <v>1034</v>
+      </c>
+      <c r="ZK11" s="1"/>
+      <c r="AEF11" s="1"/>
+      <c r="AEL11">
+        <v>885381637</v>
+      </c>
+      <c r="AEM11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="AEN11" s="1">
+        <v>46299.352372685193</v>
+      </c>
+      <c r="AEP11" t="s">
+        <v>808</v>
+      </c>
+      <c r="AER11" t="s">
+        <v>823</v>
+      </c>
+      <c r="AES11" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AET11">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FF9D525-E66B-8F40-AD3B-2A5C8586E827}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AD62BCC-96A1-3F4D-B093-9902A68B5F89}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="1037">
   <si>
     <t>Date</t>
   </si>
@@ -2816,9 +2816,6 @@
   </si>
   <si>
     <t>Rebalancing morning water/firewood chores so girls stay in school Fair and equal plate sharing between boys and girls at home Using improved cooking methods to consume less firewood Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>8</t>
@@ -3207,7 +3204,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET11" totalsRowShown="0">
-  <autoFilter ref="A1:AET11" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+  <autoFilter ref="A1:AET11" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Orientation"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="826">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -7714,7 +7717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:826" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>46297</v>
       </c>
@@ -7824,7 +7827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:826" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>46297</v>
       </c>
@@ -8804,9 +8807,6 @@
       <c r="BD7">
         <v>0</v>
       </c>
-      <c r="BE7" t="s">
-        <v>927</v>
-      </c>
       <c r="BF7" t="s">
         <v>794</v>
       </c>
@@ -8906,9 +8906,6 @@
       <c r="CQ7">
         <v>1</v>
       </c>
-      <c r="CR7" t="s">
-        <v>933</v>
-      </c>
       <c r="CS7" t="s">
         <v>794</v>
       </c>
@@ -8942,14 +8939,11 @@
       <c r="DD7">
         <v>1</v>
       </c>
-      <c r="DE7" t="s">
-        <v>932</v>
-      </c>
       <c r="DF7" t="s">
         <v>790</v>
       </c>
       <c r="DG7" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="DH7">
         <v>1</v>
@@ -8982,49 +8976,49 @@
         <v>785</v>
       </c>
       <c r="DR7" t="s">
+        <v>934</v>
+      </c>
+      <c r="DS7">
+        <v>0</v>
+      </c>
+      <c r="DT7">
+        <v>0</v>
+      </c>
+      <c r="DU7">
+        <v>1</v>
+      </c>
+      <c r="DV7">
+        <v>1</v>
+      </c>
+      <c r="DW7">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="s">
         <v>935</v>
       </c>
-      <c r="DS7">
-        <v>0</v>
-      </c>
-      <c r="DT7">
-        <v>0</v>
-      </c>
-      <c r="DU7">
-        <v>1</v>
-      </c>
-      <c r="DV7">
-        <v>1</v>
-      </c>
-      <c r="DW7">
-        <v>0</v>
-      </c>
-      <c r="DX7" t="s">
+      <c r="DY7">
+        <v>1</v>
+      </c>
+      <c r="DZ7">
+        <v>0</v>
+      </c>
+      <c r="EA7">
+        <v>0</v>
+      </c>
+      <c r="EB7">
+        <v>0</v>
+      </c>
+      <c r="EG7">
+        <v>0</v>
+      </c>
+      <c r="EI7">
+        <v>0</v>
+      </c>
+      <c r="EK7">
+        <v>1</v>
+      </c>
+      <c r="UV7" t="s">
         <v>936</v>
-      </c>
-      <c r="DY7">
-        <v>1</v>
-      </c>
-      <c r="DZ7">
-        <v>0</v>
-      </c>
-      <c r="EA7">
-        <v>0</v>
-      </c>
-      <c r="EB7">
-        <v>0</v>
-      </c>
-      <c r="EG7">
-        <v>0</v>
-      </c>
-      <c r="EI7">
-        <v>0</v>
-      </c>
-      <c r="EK7">
-        <v>1</v>
-      </c>
-      <c r="UV7" t="s">
-        <v>937</v>
       </c>
       <c r="ZK7" s="1"/>
       <c r="AEF7" s="1"/>
@@ -9032,7 +9026,7 @@
         <v>885187630</v>
       </c>
       <c r="AEM7" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AEN7" s="1">
         <v>46298.763460648152</v>
@@ -9044,13 +9038,13 @@
         <v>823</v>
       </c>
       <c r="AES7" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AET7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:826" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>46295</v>
       </c>
@@ -9058,7 +9052,7 @@
         <v>780</v>
       </c>
       <c r="C8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D8" t="s">
         <v>651</v>
@@ -9070,43 +9064,43 @@
         <v>826</v>
       </c>
       <c r="K8" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="EL8" t="s">
         <v>828</v>
       </c>
       <c r="FN8" t="s">
+        <v>941</v>
+      </c>
+      <c r="FO8" t="s">
+        <v>941</v>
+      </c>
+      <c r="FP8" t="s">
+        <v>941</v>
+      </c>
+      <c r="FQ8">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="s">
         <v>942</v>
       </c>
-      <c r="FO8" t="s">
-        <v>942</v>
-      </c>
-      <c r="FP8" t="s">
-        <v>942</v>
-      </c>
-      <c r="FQ8">
-        <v>0</v>
-      </c>
-      <c r="FS8" t="s">
+      <c r="FT8" t="s">
         <v>943</v>
       </c>
-      <c r="FT8" t="s">
+      <c r="FU8" t="s">
         <v>944</v>
       </c>
-      <c r="FU8" t="s">
+      <c r="FV8">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="s">
         <v>945</v>
       </c>
-      <c r="FV8">
-        <v>0</v>
-      </c>
-      <c r="FX8" t="s">
+      <c r="FY8" t="s">
         <v>946</v>
       </c>
-      <c r="FY8" t="s">
-        <v>947</v>
-      </c>
       <c r="FZ8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="GA8">
         <v>0</v>
@@ -9115,28 +9109,28 @@
         <v>841</v>
       </c>
       <c r="GD8" t="s">
+        <v>947</v>
+      </c>
+      <c r="GE8" t="s">
+        <v>941</v>
+      </c>
+      <c r="GF8">
+        <v>0</v>
+      </c>
+      <c r="GH8" t="s">
         <v>948</v>
       </c>
-      <c r="GE8" t="s">
-        <v>942</v>
-      </c>
-      <c r="GF8">
-        <v>0</v>
-      </c>
-      <c r="GH8" t="s">
+      <c r="GI8" t="s">
         <v>949</v>
       </c>
-      <c r="GI8" t="s">
-        <v>950</v>
-      </c>
       <c r="GJ8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="GK8">
         <v>2</v>
       </c>
       <c r="GL8" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="GM8">
         <v>1</v>
@@ -9172,16 +9166,16 @@
         <v>785</v>
       </c>
       <c r="GX8" t="s">
+        <v>951</v>
+      </c>
+      <c r="HE8" t="s">
         <v>952</v>
-      </c>
-      <c r="HE8" t="s">
-        <v>953</v>
       </c>
       <c r="HF8">
         <v>2</v>
       </c>
       <c r="HG8" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="HI8" t="s">
         <v>840</v>
@@ -9190,7 +9184,7 @@
         <v>10</v>
       </c>
       <c r="HK8" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="HM8" t="s">
         <v>840</v>
@@ -9202,13 +9196,13 @@
         <v>927</v>
       </c>
       <c r="HQ8" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="HR8">
         <v>1</v>
       </c>
       <c r="HS8" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="HU8" t="s">
         <v>840</v>
@@ -9217,19 +9211,19 @@
         <v>8</v>
       </c>
       <c r="HW8" t="s">
+        <v>956</v>
+      </c>
+      <c r="IG8" t="s">
         <v>957</v>
-      </c>
-      <c r="IG8" t="s">
-        <v>958</v>
       </c>
       <c r="IH8" t="s">
         <v>843</v>
       </c>
       <c r="II8" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="IJ8" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="IK8" t="s">
         <v>841</v>
@@ -9247,7 +9241,7 @@
         <v>927</v>
       </c>
       <c r="IQ8" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="IR8" t="s">
         <v>930</v>
@@ -9256,61 +9250,61 @@
         <v>794</v>
       </c>
       <c r="IU8" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="IV8" t="s">
         <v>843</v>
       </c>
       <c r="IW8" t="s">
+        <v>960</v>
+      </c>
+      <c r="IX8" t="s">
         <v>961</v>
       </c>
-      <c r="IX8" t="s">
-        <v>962</v>
-      </c>
       <c r="IY8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="IZ8" t="s">
         <v>790</v>
       </c>
       <c r="JB8" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="JC8" t="s">
         <v>843</v>
       </c>
       <c r="JD8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="JE8" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="JF8" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="JG8" t="s">
         <v>790</v>
       </c>
       <c r="JI8" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="JJ8" t="s">
         <v>843</v>
       </c>
       <c r="JK8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="JL8" t="s">
+        <v>961</v>
+      </c>
+      <c r="JM8" t="s">
         <v>962</v>
-      </c>
-      <c r="JM8" t="s">
-        <v>963</v>
       </c>
       <c r="JN8" t="s">
         <v>790</v>
       </c>
       <c r="JP8" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="JQ8" t="s">
         <v>843</v>
@@ -9319,7 +9313,7 @@
         <v>927</v>
       </c>
       <c r="JS8" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="JT8" t="s">
         <v>927</v>
@@ -9328,7 +9322,7 @@
         <v>794</v>
       </c>
       <c r="JV8" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="JW8">
         <v>1</v>
@@ -9346,16 +9340,16 @@
         <v>806</v>
       </c>
       <c r="KB8" t="s">
+        <v>964</v>
+      </c>
+      <c r="KC8" t="s">
         <v>965</v>
       </c>
-      <c r="KC8" t="s">
+      <c r="KD8" t="s">
         <v>966</v>
       </c>
-      <c r="KD8" t="s">
+      <c r="KE8" t="s">
         <v>967</v>
-      </c>
-      <c r="KE8" t="s">
-        <v>968</v>
       </c>
       <c r="OA8">
         <v>0</v>
@@ -9394,7 +9388,7 @@
         <v>67</v>
       </c>
       <c r="UV8" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="ZK8" s="1"/>
       <c r="AEF8" s="1"/>
@@ -9402,7 +9396,7 @@
         <v>885200260</v>
       </c>
       <c r="AEM8" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="AEN8" s="1">
         <v>46298.788032407407</v>
@@ -9414,7 +9408,7 @@
         <v>823</v>
       </c>
       <c r="AES8" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AET8">
         <v>7</v>
@@ -9428,7 +9422,7 @@
         <v>780</v>
       </c>
       <c r="C9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D9" t="s">
         <v>651</v>
@@ -9440,7 +9434,7 @@
         <v>783</v>
       </c>
       <c r="K9" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -9470,7 +9464,7 @@
         <v>806</v>
       </c>
       <c r="AH9" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="AI9">
         <v>0</v>
@@ -9503,26 +9497,26 @@
         <v>790</v>
       </c>
       <c r="AU9" t="s">
+        <v>973</v>
+      </c>
+      <c r="AV9">
+        <v>1</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="s">
         <v>974</v>
       </c>
-      <c r="AV9">
-        <v>1</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>1</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>975</v>
-      </c>
       <c r="BB9">
         <v>0</v>
       </c>
@@ -9531,15 +9525,12 @@
       </c>
       <c r="BD9">
         <v>1</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>833</v>
       </c>
       <c r="BF9" t="s">
         <v>794</v>
       </c>
       <c r="BH9" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="BI9">
         <v>1</v>
@@ -9572,7 +9563,7 @@
         <v>794</v>
       </c>
       <c r="BU9" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="BV9">
         <v>1</v>
@@ -9634,9 +9625,6 @@
       <c r="CQ9">
         <v>1</v>
       </c>
-      <c r="CR9" t="s">
-        <v>833</v>
-      </c>
       <c r="CS9" t="s">
         <v>790</v>
       </c>
@@ -9670,14 +9658,11 @@
       <c r="DD9">
         <v>1</v>
       </c>
-      <c r="DE9" t="s">
-        <v>945</v>
-      </c>
       <c r="DF9" t="s">
         <v>790</v>
       </c>
       <c r="DG9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="DH9">
         <v>0</v>
@@ -9719,7 +9704,7 @@
         <v>0</v>
       </c>
       <c r="UV9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="ZK9" s="1"/>
       <c r="AEF9" s="1"/>
@@ -9727,7 +9712,7 @@
         <v>885201939</v>
       </c>
       <c r="AEM9" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AEN9" s="1">
         <v>46298.791562500002</v>
@@ -9739,13 +9724,13 @@
         <v>823</v>
       </c>
       <c r="AES9" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="AET9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:826" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46296</v>
       </c>
@@ -9753,7 +9738,7 @@
         <v>780</v>
       </c>
       <c r="C10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D10" t="s">
         <v>653</v>
@@ -9765,7 +9750,7 @@
         <v>826</v>
       </c>
       <c r="N10" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="EL10" t="s">
         <v>828</v>
@@ -9774,49 +9759,49 @@
         <v>829</v>
       </c>
       <c r="FO10" t="s">
+        <v>983</v>
+      </c>
+      <c r="FP10" t="s">
         <v>984</v>
       </c>
-      <c r="FP10" t="s">
+      <c r="FS10" t="s">
+        <v>983</v>
+      </c>
+      <c r="FT10" t="s">
+        <v>983</v>
+      </c>
+      <c r="FU10" t="s">
         <v>985</v>
       </c>
-      <c r="FS10" t="s">
-        <v>984</v>
-      </c>
-      <c r="FT10" t="s">
-        <v>984</v>
-      </c>
-      <c r="FU10" t="s">
+      <c r="FX10" t="s">
+        <v>948</v>
+      </c>
+      <c r="FY10" t="s">
         <v>986</v>
       </c>
-      <c r="FX10" t="s">
-        <v>949</v>
-      </c>
-      <c r="FY10" t="s">
+      <c r="FZ10" t="s">
         <v>987</v>
       </c>
-      <c r="FZ10" t="s">
+      <c r="GC10" t="s">
         <v>988</v>
       </c>
-      <c r="GC10" t="s">
+      <c r="GD10" t="s">
         <v>989</v>
       </c>
-      <c r="GD10" t="s">
+      <c r="GE10" t="s">
         <v>990</v>
       </c>
-      <c r="GE10" t="s">
+      <c r="GH10" t="s">
         <v>991</v>
       </c>
-      <c r="GH10" t="s">
+      <c r="GI10" t="s">
         <v>992</v>
       </c>
-      <c r="GI10" t="s">
+      <c r="GJ10" t="s">
         <v>993</v>
       </c>
-      <c r="GJ10" t="s">
+      <c r="GL10" t="s">
         <v>994</v>
-      </c>
-      <c r="GL10" t="s">
-        <v>995</v>
       </c>
       <c r="GM10">
         <v>1</v>
@@ -9852,7 +9837,7 @@
         <v>785</v>
       </c>
       <c r="GX10" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="HE10" t="s">
         <v>840</v>
@@ -9861,7 +9846,7 @@
         <v>80</v>
       </c>
       <c r="HG10" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="HI10" t="s">
         <v>840</v>
@@ -9870,7 +9855,7 @@
         <v>90</v>
       </c>
       <c r="HK10" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="HM10" t="s">
         <v>840</v>
@@ -9879,7 +9864,7 @@
         <v>105</v>
       </c>
       <c r="HO10" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="HQ10" t="s">
         <v>840</v>
@@ -9888,7 +9873,7 @@
         <v>50</v>
       </c>
       <c r="HS10" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="HU10" t="s">
         <v>839</v>
@@ -9897,7 +9882,7 @@
         <v>120</v>
       </c>
       <c r="HW10" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="IG10" t="s">
         <v>842</v>
@@ -9906,31 +9891,31 @@
         <v>843</v>
       </c>
       <c r="II10" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="IJ10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="IK10" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="IL10" t="s">
         <v>794</v>
       </c>
       <c r="IN10" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="IO10" t="s">
+        <v>1002</v>
+      </c>
+      <c r="IP10" t="s">
         <v>1003</v>
       </c>
-      <c r="IP10" t="s">
+      <c r="IQ10" t="s">
+        <v>961</v>
+      </c>
+      <c r="IR10" t="s">
         <v>1004</v>
-      </c>
-      <c r="IQ10" t="s">
-        <v>962</v>
-      </c>
-      <c r="IR10" t="s">
-        <v>1005</v>
       </c>
       <c r="IS10" t="s">
         <v>790</v>
@@ -9942,31 +9927,31 @@
         <v>843</v>
       </c>
       <c r="IW10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="IX10" t="s">
+        <v>958</v>
+      </c>
+      <c r="IY10" t="s">
         <v>1006</v>
-      </c>
-      <c r="IX10" t="s">
-        <v>959</v>
-      </c>
-      <c r="IY10" t="s">
-        <v>1007</v>
       </c>
       <c r="IZ10" t="s">
         <v>794</v>
       </c>
       <c r="JB10" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="JC10" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="JD10" t="s">
+        <v>1007</v>
+      </c>
+      <c r="JE10" t="s">
+        <v>961</v>
+      </c>
+      <c r="JF10" t="s">
         <v>1008</v>
-      </c>
-      <c r="JE10" t="s">
-        <v>962</v>
-      </c>
-      <c r="JF10" t="s">
-        <v>1009</v>
       </c>
       <c r="JG10" t="s">
         <v>790</v>
@@ -9978,61 +9963,61 @@
         <v>843</v>
       </c>
       <c r="JK10" t="s">
+        <v>1009</v>
+      </c>
+      <c r="JL10" t="s">
+        <v>958</v>
+      </c>
+      <c r="JM10" t="s">
         <v>1010</v>
-      </c>
-      <c r="JL10" t="s">
-        <v>959</v>
-      </c>
-      <c r="JM10" t="s">
-        <v>1011</v>
       </c>
       <c r="JN10" t="s">
         <v>794</v>
       </c>
       <c r="JP10" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="JR10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="JS10" t="s">
+        <v>961</v>
+      </c>
+      <c r="JT10" t="s">
         <v>1012</v>
-      </c>
-      <c r="JS10" t="s">
-        <v>962</v>
-      </c>
-      <c r="JT10" t="s">
-        <v>1013</v>
       </c>
       <c r="JU10" t="s">
         <v>790</v>
       </c>
       <c r="JV10" t="s">
+        <v>1013</v>
+      </c>
+      <c r="JW10">
+        <v>1</v>
+      </c>
+      <c r="JX10">
+        <v>0</v>
+      </c>
+      <c r="JY10">
+        <v>0</v>
+      </c>
+      <c r="JZ10">
+        <v>0</v>
+      </c>
+      <c r="KA10" t="s">
         <v>1014</v>
       </c>
-      <c r="JW10">
-        <v>1</v>
-      </c>
-      <c r="JX10">
-        <v>0</v>
-      </c>
-      <c r="JY10">
-        <v>0</v>
-      </c>
-      <c r="JZ10">
-        <v>0</v>
-      </c>
-      <c r="KA10" t="s">
+      <c r="KB10" t="s">
         <v>1015</v>
       </c>
-      <c r="KB10" t="s">
+      <c r="KC10" t="s">
         <v>1016</v>
       </c>
-      <c r="KC10" t="s">
+      <c r="KD10" t="s">
         <v>1017</v>
       </c>
-      <c r="KD10" t="s">
+      <c r="KE10" t="s">
         <v>1018</v>
-      </c>
-      <c r="KE10" t="s">
-        <v>1019</v>
       </c>
       <c r="OA10">
         <v>90</v>
@@ -10071,7 +10056,7 @@
         <v>90</v>
       </c>
       <c r="UV10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="ZK10" s="1"/>
       <c r="AEF10" s="1"/>
@@ -10079,7 +10064,7 @@
         <v>885374147</v>
       </c>
       <c r="AEM10" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="AEN10" s="1">
         <v>46299.338842592602</v>
@@ -10091,7 +10076,7 @@
         <v>823</v>
       </c>
       <c r="AES10" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AET10">
         <v>9</v>
@@ -10105,19 +10090,19 @@
         <v>780</v>
       </c>
       <c r="C11" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D11" t="s">
         <v>653</v>
       </c>
       <c r="E11" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F11" t="s">
         <v>783</v>
       </c>
       <c r="N11" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="Q11">
         <v>6</v>
@@ -10147,10 +10132,10 @@
         <v>785</v>
       </c>
       <c r="Z11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="AH11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="AI11">
         <v>0</v>
@@ -10180,13 +10165,13 @@
         <v>0</v>
       </c>
       <c r="AR11" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="AS11" t="s">
         <v>790</v>
       </c>
       <c r="AU11" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="AV11">
         <v>1</v>
@@ -10216,13 +10201,13 @@
         <v>1</v>
       </c>
       <c r="BE11" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="BF11" t="s">
         <v>794</v>
       </c>
       <c r="BH11" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="BI11">
         <v>1</v>
@@ -10252,13 +10237,13 @@
         <v>1</v>
       </c>
       <c r="BR11" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="BS11" t="s">
         <v>794</v>
       </c>
       <c r="BU11" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="BV11">
         <v>0</v>
@@ -10288,7 +10273,7 @@
         <v>1</v>
       </c>
       <c r="CE11" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="CF11" t="s">
         <v>790</v>
@@ -10324,7 +10309,7 @@
         <v>0</v>
       </c>
       <c r="CR11" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="CS11" t="s">
         <v>790</v>
@@ -10360,13 +10345,13 @@
         <v>0</v>
       </c>
       <c r="DE11" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="DF11" t="s">
         <v>794</v>
       </c>
       <c r="DG11" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="DH11">
         <v>0</v>
@@ -10408,7 +10393,7 @@
         <v>1</v>
       </c>
       <c r="UV11" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="ZK11" s="1"/>
       <c r="AEF11" s="1"/>
@@ -10416,7 +10401,7 @@
         <v>885381637</v>
       </c>
       <c r="AEM11" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="AEN11" s="1">
         <v>46299.352372685193</v>
@@ -10428,7 +10413,7 @@
         <v>823</v>
       </c>
       <c r="AES11" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="AET11">
         <v>10</v>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AD62BCC-96A1-3F4D-B093-9902A68B5F89}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA52B80F-B50B-8841-A6BA-39E3C7B0000F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3204,13 +3204,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET11" totalsRowShown="0">
-  <autoFilter ref="A1:AET11" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Orientation"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AET11" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="826">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -7717,7 +7711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:826" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:826" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>46297</v>
       </c>
@@ -7827,7 +7821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:826" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:826" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>46297</v>
       </c>
@@ -9044,7 +9038,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:826" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:826" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>46295</v>
       </c>
@@ -9730,7 +9724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:826" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:826" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46296</v>
       </c>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54EEC68-01D8-4640-9D6C-1B047C752CC0}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{711D1655-250B-E247-A9F1-C0ECA8990ED8}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="1070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="1079">
   <si>
     <t>Date</t>
   </si>
@@ -3230,6 +3230,33 @@
   </si>
   <si>
     <t>Did learners actively handle materials and practice rather than listen passively?55</t>
+  </si>
+  <si>
+    <t>Lopeyok Paul pax</t>
+  </si>
+  <si>
+    <t>School compound</t>
+  </si>
+  <si>
+    <t>12:30:00.000+03:00</t>
+  </si>
+  <si>
+    <t>14:00:00.000+03:00</t>
+  </si>
+  <si>
+    <t>We informed them to go and try eating a full balanced diet meal at home and list for us the type of food they eat and mark the food calenders given to themthey should mark in the d ca</t>
+  </si>
+  <si>
+    <t>The children are excited for the activity because it a wards them gifts after answering questions</t>
+  </si>
+  <si>
+    <t>885f2eb2-24d0-4967-9096-3b782883963f</t>
+  </si>
+  <si>
+    <t>v8tceXwuSJPeM95LoTz6Gv</t>
+  </si>
+  <si>
+    <t>uuid:885f2eb2-24d0-4967-9096-3b782883963f</t>
   </si>
 </sst>
 </file>
@@ -3308,8 +3335,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET14" totalsRowShown="0">
-  <autoFilter ref="A1:AET14" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET15" totalsRowShown="0">
+  <autoFilter ref="A1:AET15" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="826">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -4429,7 +4456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AET14"/>
+  <dimension ref="A1:AET15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -8973,6 +9000,9 @@
       <c r="AP7">
         <v>0</v>
       </c>
+      <c r="AQ7" t="s">
+        <v>810</v>
+      </c>
       <c r="AR7" t="s">
         <v>718</v>
       </c>
@@ -9006,6 +9036,9 @@
       <c r="BC7">
         <v>0</v>
       </c>
+      <c r="BD7" t="s">
+        <v>810</v>
+      </c>
       <c r="BE7" t="s">
         <v>722</v>
       </c>
@@ -9038,6 +9071,9 @@
       </c>
       <c r="BP7">
         <v>1</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>813</v>
       </c>
       <c r="BR7" t="s">
         <v>718</v>
@@ -9732,6 +9768,9 @@
       <c r="AP9">
         <v>1</v>
       </c>
+      <c r="AQ9" t="s">
+        <v>761</v>
+      </c>
       <c r="AR9" t="s">
         <v>718</v>
       </c>
@@ -9765,6 +9804,9 @@
       <c r="BC9">
         <v>1</v>
       </c>
+      <c r="BD9" t="s">
+        <v>761</v>
+      </c>
       <c r="BE9" t="s">
         <v>722</v>
       </c>
@@ -9797,6 +9839,9 @@
       </c>
       <c r="BP9">
         <v>1</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>827</v>
       </c>
       <c r="BR9" t="s">
         <v>722</v>
@@ -11317,6 +11362,115 @@
       </c>
       <c r="AEF14" s="1"/>
       <c r="AEN14" s="1"/>
+    </row>
+    <row r="15" spans="1:826" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B15" t="s">
+        <v>708</v>
+      </c>
+      <c r="C15" t="s">
+        <v>776</v>
+      </c>
+      <c r="D15" t="s">
+        <v>593</v>
+      </c>
+      <c r="E15" t="s">
+        <v>740</v>
+      </c>
+      <c r="H15" t="s">
+        <v>777</v>
+      </c>
+      <c r="RS15" t="s">
+        <v>742</v>
+      </c>
+      <c r="RT15">
+        <v>1</v>
+      </c>
+      <c r="RU15">
+        <v>0</v>
+      </c>
+      <c r="RV15" t="s">
+        <v>1070</v>
+      </c>
+      <c r="RW15">
+        <v>30</v>
+      </c>
+      <c r="RX15">
+        <v>30</v>
+      </c>
+      <c r="RY15" t="s">
+        <v>1071</v>
+      </c>
+      <c r="RZ15" s="1">
+        <v>46301</v>
+      </c>
+      <c r="SA15" t="s">
+        <v>1072</v>
+      </c>
+      <c r="SB15" t="s">
+        <v>1073</v>
+      </c>
+      <c r="SC15">
+        <v>112</v>
+      </c>
+      <c r="SD15">
+        <v>104</v>
+      </c>
+      <c r="SE15">
+        <v>0</v>
+      </c>
+      <c r="SF15">
+        <v>0</v>
+      </c>
+      <c r="SG15" t="s">
+        <v>1016</v>
+      </c>
+      <c r="SH15">
+        <v>0</v>
+      </c>
+      <c r="SI15">
+        <v>1</v>
+      </c>
+      <c r="SJ15">
+        <v>1</v>
+      </c>
+      <c r="SK15">
+        <v>1</v>
+      </c>
+      <c r="SL15">
+        <v>1</v>
+      </c>
+      <c r="SM15" t="s">
+        <v>1074</v>
+      </c>
+      <c r="TE15" t="s">
+        <v>1075</v>
+      </c>
+      <c r="ADT15">
+        <v>886940645</v>
+      </c>
+      <c r="ADU15" t="s">
+        <v>1076</v>
+      </c>
+      <c r="ADV15" s="1">
+        <v>46301.473958333343</v>
+      </c>
+      <c r="ADX15" t="s">
+        <v>736</v>
+      </c>
+      <c r="ADZ15" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AEA15" t="s">
+        <v>1078</v>
+      </c>
+      <c r="AEB15">
+        <v>14</v>
+      </c>
+      <c r="AEF15" s="1"/>
+      <c r="AEN15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{711D1655-250B-E247-A9F1-C0ECA8990ED8}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{386EFE74-4BD8-8341-BDD5-6691401BE939}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="1079">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="1113">
   <si>
     <t>Date</t>
   </si>
@@ -2347,9 +2347,6 @@
     <t>uuid:b8c26a07-d365-49a0-bd0d-6a08b184c590</t>
   </si>
   <si>
-    <t>Specify55</t>
-  </si>
-  <si>
     <t>Lopeyok Martin</t>
   </si>
   <si>
@@ -2479,12 +2476,6 @@
     <t>Joint facilitation</t>
   </si>
   <si>
-    <t>Inbolvung the community and launch at every district</t>
-  </si>
-  <si>
-    <t>b4e4f1ed-ce12-46b1-af95-c3af56846dd1</t>
-  </si>
-  <si>
     <t>uuid:b4e4f1ed-ce12-46b1-af95-c3af56846dd1</t>
   </si>
   <si>
@@ -2608,9 +2599,6 @@
     <t>Need capacity building on all cooking demonstration</t>
   </si>
   <si>
-    <t>d626f565-e3e3-4557-8a2f-301c66e57a6f</t>
-  </si>
-  <si>
     <t>uuid:d626f565-e3e3-4557-8a2f-301c66e57a6f</t>
   </si>
   <si>
@@ -2932,9 +2920,6 @@
     <t>The teachers are wel informed of the nutribus programme</t>
   </si>
   <si>
-    <t>0ad3d30f-610b-46fb-82c8-62f71d2df9b4</t>
-  </si>
-  <si>
     <t>vEzEfWt86sJoHTbN86HtUK</t>
   </si>
   <si>
@@ -2983,57 +2968,6 @@
     <t>Observed community commitment to clean cooking practices:58</t>
   </si>
   <si>
-    <t>Record the storyteller's actual words and dont try to re-interprete them67</t>
-  </si>
-  <si>
-    <t>What specific nutribus event, activity, chart, or discussion caused the shift68</t>
-  </si>
-  <si>
-    <t>What was physically done differently at home, class, or community after attending nutribus activities69</t>
-  </si>
-  <si>
-    <t>what comments from the spectators70</t>
-  </si>
-  <si>
-    <t>Were all demonstrated foods sourced locally71</t>
-  </si>
-  <si>
-    <t>Community Agreement and commitments72</t>
-  </si>
-  <si>
-    <t>Learners with Disabilities73</t>
-  </si>
-  <si>
-    <t>PWDs74</t>
-  </si>
-  <si>
-    <t>_id75</t>
-  </si>
-  <si>
-    <t>_uuid76</t>
-  </si>
-  <si>
-    <t>_submission_time77</t>
-  </si>
-  <si>
-    <t>_validation_status78</t>
-  </si>
-  <si>
-    <t>_status79</t>
-  </si>
-  <si>
-    <t>_submitted_by80</t>
-  </si>
-  <si>
-    <t>__version__81</t>
-  </si>
-  <si>
-    <t>meta/rootUuid82</t>
-  </si>
-  <si>
-    <t>_index83</t>
-  </si>
-  <si>
     <t>What the query was about</t>
   </si>
   <si>
@@ -3257,6 +3191,174 @@
   </si>
   <si>
     <t>uuid:885f2eb2-24d0-4967-9096-3b782883963f</t>
+  </si>
+  <si>
+    <t>mobilise fathers to share chores</t>
+  </si>
+  <si>
+    <t>mobilise fathers to share</t>
+  </si>
+  <si>
+    <t>mobilise fathers to share, enrich school porridge and adopt energy saving practices</t>
+  </si>
+  <si>
+    <t>Inolving the community and launch at every district</t>
+  </si>
+  <si>
+    <t>ed67b768-82ad-4bc8-a8b3-4654ea71f70c</t>
+  </si>
+  <si>
+    <t>Enrish school porridge and adopt firewood saving practices</t>
+  </si>
+  <si>
+    <t>adopt firewood saving practices</t>
+  </si>
+  <si>
+    <t>Mobilise fathers to share chores, enrish school porridge and adopt wood saving practices</t>
+  </si>
+  <si>
+    <t>Mobilise fathers to share chores and adopt energy saving practices</t>
+  </si>
+  <si>
+    <t>Mobilise fathers to share chores, enrich porridge and adopt firewood saving practices</t>
+  </si>
+  <si>
+    <t>enrich school porridge and adopt firewood saving practices</t>
+  </si>
+  <si>
+    <t>d91fd75a-fcd7-466d-b61c-3e019f506aea</t>
+  </si>
+  <si>
+    <t>Forming Nutri clubs</t>
+  </si>
+  <si>
+    <t>e7a62c2f-5838-4021-8ce8-8ae3262b2291</t>
+  </si>
+  <si>
+    <t>Priscilla</t>
+  </si>
+  <si>
+    <t>LONGALOM P/S</t>
+  </si>
+  <si>
+    <t>Twice weekly</t>
+  </si>
+  <si>
+    <t>Willing to do support the nutri bus campaign</t>
+  </si>
+  <si>
+    <t>Will integrate nutr bus in all their daily activities.</t>
+  </si>
+  <si>
+    <t>Will sensitive the community on gender and equal responsibility.</t>
+  </si>
+  <si>
+    <t>Will engage all learners to participate in nutri bus sessions.</t>
+  </si>
+  <si>
+    <t>Will make sure gender is uplifted and also integrate children with disability</t>
+  </si>
+  <si>
+    <t>Will make sure all the community to embrace smart cooking energy</t>
+  </si>
+  <si>
+    <t>Game for the school WFP Toll-Free Feedback Display Board Pledge / Commitment card</t>
+  </si>
+  <si>
+    <t>The teachers should also be taught how to make metu porridge,wfp to continue supporting the community.</t>
+  </si>
+  <si>
+    <t>d3c59386-b1fd-4e40-a818-f756ca5e3331</t>
+  </si>
+  <si>
+    <t>v3e4bDVXCcP2PfJrrj52U4</t>
+  </si>
+  <si>
+    <t>uuid:d3c59386-b1fd-4e40-a818-f756ca5e3331</t>
+  </si>
+  <si>
+    <t>LOBALANGIT P/S</t>
+  </si>
+  <si>
+    <t>Adoto simon peter and adeno fiona okot</t>
+  </si>
+  <si>
+    <t>School main hall</t>
+  </si>
+  <si>
+    <t>15:45:00.000+03:00</t>
+  </si>
+  <si>
+    <t>17:00:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat) Climate-Smart Living: Firewood-saving cooking methods &amp; moving from 3-stone fires Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing Gender Chore Rebalancing: Boys sharing morning water/firewood chores Peer Attendance Tracing: Checking and following up chronically absent classmates</t>
+  </si>
+  <si>
+    <t>Food calendars were given for them to mark at home on what they will eat and return them to the teachers</t>
+  </si>
+  <si>
+    <t>The activity was okay but needed a radio for children to be hearing what we are telling out because most children were excited but the audience of the one responding questions was low</t>
+  </si>
+  <si>
+    <t>7eb5fb6e-b62d-441e-b7bb-82e5ea6ad12e</t>
+  </si>
+  <si>
+    <t>uuid:7eb5fb6e-b62d-441e-b7bb-82e5ea6ad12e</t>
+  </si>
+  <si>
+    <t>LOOKOROK P/S</t>
+  </si>
+  <si>
+    <t>Angura samuel</t>
+  </si>
+  <si>
+    <t>Both compound and in class</t>
+  </si>
+  <si>
+    <t>21:25:00.000+03:00</t>
+  </si>
+  <si>
+    <t>23:30:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Making of kitchen garden and watering</t>
+  </si>
+  <si>
+    <t>Projector needes for proper observation of video</t>
+  </si>
+  <si>
+    <t>4540053f-8433-459f-8cde-162347014a4b</t>
+  </si>
+  <si>
+    <t>uuid:4540053f-8433-459f-8cde-162347014a4b</t>
+  </si>
+  <si>
+    <t>NAKAPELIMORU P/S</t>
+  </si>
+  <si>
+    <t>Aural Simon Peter</t>
+  </si>
+  <si>
+    <t>In class</t>
+  </si>
+  <si>
+    <t>12:10:00.000+03:00</t>
+  </si>
+  <si>
+    <t>13:55:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Growing vegetables through kitchen garden</t>
+  </si>
+  <si>
+    <t>Projector needed</t>
+  </si>
+  <si>
+    <t>bf431d41-7bc7-4dd0-b12a-28f79f7a4c42</t>
+  </si>
+  <si>
+    <t>uuid:bf431d41-7bc7-4dd0-b12a-28f79f7a4c42</t>
   </si>
 </sst>
 </file>
@@ -3302,13 +3404,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     </dxf>
@@ -3335,9 +3431,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AET15" totalsRowShown="0">
-  <autoFilter ref="A1:AET15" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
-  <tableColumns count="826">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AEB19" totalsRowShown="0">
+  <autoFilter ref="A1:AEB19" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+  <tableColumns count="808">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
     <tableColumn id="3" xr3:uid="{1A468597-D831-D84D-804A-CED0115BE04C}" name="Specify"/>
@@ -4024,7 +4120,7 @@
     <tableColumn id="684" xr3:uid="{B1F66958-3D43-B94B-9C16-74192AC24756}" name="**Final verdict for Family**"/>
     <tableColumn id="685" xr3:uid="{29E0C23A-62D1-074E-9672-94000C9952EF}" name="Middle Primary (P3-P4) Registered Girls Weekly Attendance"/>
     <tableColumn id="686" xr3:uid="{7184D4B5-497E-8B42-BA7E-93956BB75536}" name="##### Adult 2"/>
-    <tableColumn id="687" xr3:uid="{A87F9C28-2C9B-7947-8188-2708D92754AA}" name="##### Family 1" dataDxfId="5"/>
+    <tableColumn id="687" xr3:uid="{A87F9C28-2C9B-7947-8188-2708D92754AA}" name="##### Family 1" dataDxfId="3"/>
     <tableColumn id="688" xr3:uid="{163F27DD-60AE-B546-BC3D-EDFB40B458B1}" name="Upper Primary (P5-P7) Registered Boys Weekly Attendance"/>
     <tableColumn id="689" xr3:uid="{01F5B0BF-E941-BA4E-B9DC-B55C53601615}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Can they recall activities from the session&lt;/span&gt;"/>
     <tableColumn id="690" xr3:uid="{07527EF8-6756-3E4F-A4FB-9C7CAA3A1F1C}" name="&lt;span style=&quot;display:none&quot;&gt;row-What was hard or stood in the way first?&lt;/span&gt;"/>
@@ -4131,7 +4227,7 @@
     <tableColumn id="791" xr3:uid="{4C0A5DF5-86B2-D849-95A5-CB71300B7CB0}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Boys&lt;/span&gt;"/>
     <tableColumn id="792" xr3:uid="{E5325280-A774-3B4A-9ED8-84FA8A8874F1}" name="&lt;span style=&quot;display:none&quot;&gt;row_3-Girls&lt;/span&gt;"/>
     <tableColumn id="793" xr3:uid="{DB727688-D385-C245-8A2D-AF7B898277DE}" name="##### Upper Primary (P5-P7) Registered Girls this weekAttendance"/>
-    <tableColumn id="794" xr3:uid="{250149CA-1640-2040-8485-513B1F14F7BC}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Boys&lt;/span&gt;" dataDxfId="4"/>
+    <tableColumn id="794" xr3:uid="{250149CA-1640-2040-8485-513B1F14F7BC}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Boys&lt;/span&gt;" dataDxfId="2"/>
     <tableColumn id="795" xr3:uid="{2D8627C1-C63D-B947-B59B-912D1C5CA4F6}" name="&lt;span style=&quot;display:none&quot;&gt;row_5-Girls&lt;/span&gt;"/>
     <tableColumn id="796" xr3:uid="{7E068712-10C1-7E45-82C2-547C0A0C71FB}" name="Did caregivers cook and handle ingredients hands-on, or only observe?57"/>
     <tableColumn id="797" xr3:uid="{7DFD7878-2F3F-3643-A2BD-5E4E0BE589AC}" name="Observed community commitment to clean cooking practices:58"/>
@@ -4146,24 +4242,6 @@
     <tableColumn id="806" xr3:uid="{7948810D-68E4-9042-97FB-D505C399CD49}" name="__version__"/>
     <tableColumn id="807" xr3:uid="{5184A4C6-CB6E-BE4F-A410-850CD982E8DA}" name="meta/rootUuid"/>
     <tableColumn id="808" xr3:uid="{8DFC507D-7250-144D-B9FC-922148269969}" name="_index"/>
-    <tableColumn id="809" xr3:uid="{17AD863D-022A-334A-90F9-10B02B02B72E}" name="Record the storyteller's actual words and dont try to re-interprete them67"/>
-    <tableColumn id="810" xr3:uid="{6E77CEB2-09A1-A64E-9C2F-066C012C88A5}" name="What specific nutribus event, activity, chart, or discussion caused the shift68"/>
-    <tableColumn id="811" xr3:uid="{A125A5B7-6729-2F4D-A89E-57182780722A}" name="What was physically done differently at home, class, or community after attending nutribus activities69"/>
-    <tableColumn id="812" xr3:uid="{CBDA2636-18B3-8342-8FDA-9DC4985989C4}" name="what comments from the spectators70" dataDxfId="3"/>
-    <tableColumn id="813" xr3:uid="{9DDB1991-893A-9E49-8798-D37329B1BE84}" name="Were all demonstrated foods sourced locally71"/>
-    <tableColumn id="814" xr3:uid="{57F7BE9C-7FF0-8943-BD94-043F22383037}" name="Specify55"/>
-    <tableColumn id="815" xr3:uid="{DCB58F26-5678-8640-83A1-3038E9E1F7CE}" name="Community Agreement and commitments72"/>
-    <tableColumn id="816" xr3:uid="{C13820D4-7E5D-934C-815D-78E13E6DF482}" name="Learners with Disabilities73"/>
-    <tableColumn id="817" xr3:uid="{531BF569-E52C-3B47-AC2D-BD84FCFB1A61}" name="PWDs74"/>
-    <tableColumn id="818" xr3:uid="{644122ED-CCCD-7042-ACA5-DF926883BF3D}" name="_id75"/>
-    <tableColumn id="819" xr3:uid="{44BA26A3-9884-A247-8CA4-CC60A58C2858}" name="_uuid76"/>
-    <tableColumn id="820" xr3:uid="{57BC694F-1C38-484A-9288-ACCA88D7D177}" name="_submission_time77" dataDxfId="2"/>
-    <tableColumn id="821" xr3:uid="{2C14184A-443F-F746-8E63-144B3BBDC063}" name="_validation_status78"/>
-    <tableColumn id="822" xr3:uid="{95BE97BC-A42E-D545-8BC1-C31F87E6BC0D}" name="_status79"/>
-    <tableColumn id="823" xr3:uid="{0807B666-BF5A-1B4E-ABA5-D6C0A17FC7B1}" name="_submitted_by80"/>
-    <tableColumn id="824" xr3:uid="{380FC912-43B5-EC40-A672-C95FFDDFC648}" name="__version__81"/>
-    <tableColumn id="825" xr3:uid="{42C4B0F2-07A2-8A47-A91C-12D4838A9C8F}" name="meta/rootUuid82"/>
-    <tableColumn id="826" xr3:uid="{1A8E1F56-2F11-3144-AB87-13304B50D1CA}" name="_index83"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4456,7 +4534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AET15"/>
+  <dimension ref="A1:AEB19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -5031,7 +5109,7 @@
     <col min="692" max="692" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5411,13 +5489,13 @@
         <v>628</v>
       </c>
       <c r="DW1" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="DX1" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="DY1" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="DZ1" t="s">
         <v>629</v>
@@ -5441,25 +5519,25 @@
         <v>634</v>
       </c>
       <c r="EG1" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="EH1" t="s">
         <v>635</v>
       </c>
       <c r="EI1" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="EJ1" t="s">
         <v>636</v>
       </c>
       <c r="EK1" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="EL1" t="s">
         <v>637</v>
       </c>
       <c r="EM1" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="EN1" t="s">
         <v>93</v>
@@ -5474,31 +5552,31 @@
         <v>94</v>
       </c>
       <c r="ER1" t="s">
+        <v>922</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>923</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>924</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>925</v>
+      </c>
+      <c r="EV1" t="s">
         <v>926</v>
       </c>
-      <c r="ES1" t="s">
+      <c r="EW1" t="s">
         <v>927</v>
       </c>
-      <c r="ET1" t="s">
+      <c r="EX1" t="s">
         <v>928</v>
-      </c>
-      <c r="EU1" t="s">
-        <v>929</v>
-      </c>
-      <c r="EV1" t="s">
-        <v>930</v>
-      </c>
-      <c r="EW1" t="s">
-        <v>931</v>
-      </c>
-      <c r="EX1" t="s">
-        <v>932</v>
       </c>
       <c r="EY1" t="s">
         <v>102</v>
       </c>
       <c r="EZ1" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="FA1" t="s">
         <v>104</v>
@@ -5525,10 +5603,10 @@
         <v>640</v>
       </c>
       <c r="FI1" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="FJ1" t="s">
-        <v>1004</v>
+        <v>982</v>
       </c>
       <c r="FK1" t="s">
         <v>117</v>
@@ -5645,43 +5723,43 @@
         <v>154</v>
       </c>
       <c r="GW1" t="s">
-        <v>1005</v>
+        <v>983</v>
       </c>
       <c r="GX1" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="GY1" t="s">
-        <v>1007</v>
+        <v>985</v>
       </c>
       <c r="GZ1" t="s">
-        <v>1008</v>
+        <v>986</v>
       </c>
       <c r="HA1" t="s">
-        <v>1009</v>
+        <v>987</v>
       </c>
       <c r="HB1" t="s">
-        <v>1010</v>
+        <v>988</v>
       </c>
       <c r="HC1" t="s">
-        <v>1021</v>
+        <v>999</v>
       </c>
       <c r="HD1" t="s">
         <v>155</v>
       </c>
       <c r="HE1" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="HF1" t="s">
         <v>156</v>
       </c>
       <c r="HG1" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="HH1" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="HI1" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="HJ1" t="s">
         <v>158</v>
@@ -5690,7 +5768,7 @@
         <v>159</v>
       </c>
       <c r="HL1" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="HM1" t="s">
         <v>160</v>
@@ -5699,7 +5777,7 @@
         <v>161</v>
       </c>
       <c r="HO1" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="HP1" t="s">
         <v>162</v>
@@ -5711,7 +5789,7 @@
         <v>164</v>
       </c>
       <c r="HS1" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="HT1" t="s">
         <v>165</v>
@@ -5723,7 +5801,7 @@
         <v>167</v>
       </c>
       <c r="HW1" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="HX1" t="s">
         <v>168</v>
@@ -5735,7 +5813,7 @@
         <v>170</v>
       </c>
       <c r="IA1" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="IB1" t="s">
         <v>171</v>
@@ -5747,7 +5825,7 @@
         <v>173</v>
       </c>
       <c r="IE1" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="IF1" t="s">
         <v>174</v>
@@ -5759,13 +5837,13 @@
         <v>176</v>
       </c>
       <c r="II1" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="IJ1" t="s">
         <v>177</v>
       </c>
       <c r="IK1" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="IL1" t="s">
         <v>178</v>
@@ -5783,10 +5861,10 @@
         <v>182</v>
       </c>
       <c r="IQ1" t="s">
-        <v>1022</v>
+        <v>1000</v>
       </c>
       <c r="IR1" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="IS1" t="s">
         <v>183</v>
@@ -5804,7 +5882,7 @@
         <v>187</v>
       </c>
       <c r="IX1" t="s">
-        <v>1023</v>
+        <v>1001</v>
       </c>
       <c r="IY1" t="s">
         <v>188</v>
@@ -5825,7 +5903,7 @@
         <v>193</v>
       </c>
       <c r="JE1" t="s">
-        <v>1024</v>
+        <v>1002</v>
       </c>
       <c r="JF1" t="s">
         <v>232</v>
@@ -5846,10 +5924,10 @@
         <v>199</v>
       </c>
       <c r="JL1" t="s">
-        <v>1025</v>
+        <v>1003</v>
       </c>
       <c r="JM1" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="JN1" t="s">
         <v>702</v>
@@ -5867,7 +5945,7 @@
         <v>706</v>
       </c>
       <c r="JS1" t="s">
-        <v>1026</v>
+        <v>1004</v>
       </c>
       <c r="JT1" t="s">
         <v>701</v>
@@ -5888,7 +5966,7 @@
         <v>205</v>
       </c>
       <c r="JZ1" t="s">
-        <v>1027</v>
+        <v>1005</v>
       </c>
       <c r="KA1" t="s">
         <v>206</v>
@@ -5909,7 +5987,7 @@
         <v>211</v>
       </c>
       <c r="KG1" t="s">
-        <v>1028</v>
+        <v>1006</v>
       </c>
       <c r="KH1" t="s">
         <v>641</v>
@@ -5936,7 +6014,7 @@
         <v>213</v>
       </c>
       <c r="KP1" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="KQ1" t="s">
         <v>215</v>
@@ -5954,13 +6032,13 @@
         <v>219</v>
       </c>
       <c r="KV1" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="KW1" t="s">
         <v>220</v>
       </c>
       <c r="KX1" t="s">
-        <v>1029</v>
+        <v>1007</v>
       </c>
       <c r="KY1" t="s">
         <v>221</v>
@@ -5990,7 +6068,7 @@
         <v>226</v>
       </c>
       <c r="LH1" t="s">
-        <v>1030</v>
+        <v>1008</v>
       </c>
       <c r="LI1" t="s">
         <v>227</v>
@@ -6008,10 +6086,10 @@
         <v>231</v>
       </c>
       <c r="LN1" t="s">
-        <v>1031</v>
+        <v>1009</v>
       </c>
       <c r="LO1" t="s">
-        <v>1032</v>
+        <v>1010</v>
       </c>
       <c r="LP1" t="s">
         <v>233</v>
@@ -6032,7 +6110,7 @@
         <v>238</v>
       </c>
       <c r="LV1" t="s">
-        <v>1033</v>
+        <v>1011</v>
       </c>
       <c r="LW1" t="s">
         <v>239</v>
@@ -6053,7 +6131,7 @@
         <v>244</v>
       </c>
       <c r="MC1" t="s">
-        <v>1034</v>
+        <v>1012</v>
       </c>
       <c r="MD1" t="s">
         <v>245</v>
@@ -6074,7 +6152,7 @@
         <v>649</v>
       </c>
       <c r="MJ1" t="s">
-        <v>1035</v>
+        <v>1013</v>
       </c>
       <c r="MK1" t="s">
         <v>650</v>
@@ -6095,7 +6173,7 @@
         <v>655</v>
       </c>
       <c r="MQ1" t="s">
-        <v>1036</v>
+        <v>1014</v>
       </c>
       <c r="MR1" t="s">
         <v>250</v>
@@ -6116,7 +6194,7 @@
         <v>255</v>
       </c>
       <c r="MX1" t="s">
-        <v>1037</v>
+        <v>1015</v>
       </c>
       <c r="MY1" t="s">
         <v>256</v>
@@ -6149,7 +6227,7 @@
         <v>660</v>
       </c>
       <c r="NI1" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="NJ1" t="s">
         <v>661</v>
@@ -6158,7 +6236,7 @@
         <v>662</v>
       </c>
       <c r="NL1" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="NM1" t="s">
         <v>666</v>
@@ -6167,7 +6245,7 @@
         <v>667</v>
       </c>
       <c r="NO1" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="NP1" t="s">
         <v>671</v>
@@ -6200,13 +6278,13 @@
         <v>681</v>
       </c>
       <c r="NZ1" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="OA1" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="OB1" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="OC1" t="s">
         <v>682</v>
@@ -6224,61 +6302,61 @@
         <v>686</v>
       </c>
       <c r="OH1" t="s">
-        <v>1038</v>
+        <v>1016</v>
       </c>
       <c r="OI1" t="s">
         <v>263</v>
       </c>
       <c r="OJ1" t="s">
-        <v>1039</v>
+        <v>1017</v>
       </c>
       <c r="OK1" t="s">
-        <v>1040</v>
+        <v>1018</v>
       </c>
       <c r="OL1" t="s">
         <v>264</v>
       </c>
       <c r="OM1" t="s">
-        <v>1041</v>
+        <v>1019</v>
       </c>
       <c r="ON1" t="s">
-        <v>1042</v>
+        <v>1020</v>
       </c>
       <c r="OO1" t="s">
         <v>265</v>
       </c>
       <c r="OP1" t="s">
-        <v>1043</v>
+        <v>1021</v>
       </c>
       <c r="OQ1" t="s">
-        <v>1044</v>
+        <v>1022</v>
       </c>
       <c r="OR1" t="s">
         <v>266</v>
       </c>
       <c r="OS1" t="s">
-        <v>1045</v>
+        <v>1023</v>
       </c>
       <c r="OT1" t="s">
-        <v>1046</v>
+        <v>1024</v>
       </c>
       <c r="OU1" t="s">
         <v>267</v>
       </c>
       <c r="OV1" t="s">
-        <v>1047</v>
+        <v>1025</v>
       </c>
       <c r="OW1" t="s">
-        <v>1048</v>
+        <v>1026</v>
       </c>
       <c r="OX1" t="s">
         <v>268</v>
       </c>
       <c r="OY1" t="s">
-        <v>1049</v>
+        <v>1027</v>
       </c>
       <c r="OZ1" t="s">
-        <v>1050</v>
+        <v>1028</v>
       </c>
       <c r="PA1" t="s">
         <v>269</v>
@@ -6293,7 +6371,7 @@
         <v>272</v>
       </c>
       <c r="PE1" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="PF1" t="s">
         <v>273</v>
@@ -6308,7 +6386,7 @@
         <v>688</v>
       </c>
       <c r="PJ1" t="s">
-        <v>1051</v>
+        <v>1029</v>
       </c>
       <c r="PK1" t="s">
         <v>275</v>
@@ -6347,7 +6425,7 @@
         <v>286</v>
       </c>
       <c r="PW1" t="s">
-        <v>1052</v>
+        <v>1030</v>
       </c>
       <c r="PX1" t="s">
         <v>287</v>
@@ -6365,7 +6443,7 @@
         <v>291</v>
       </c>
       <c r="QC1" t="s">
-        <v>1053</v>
+        <v>1031</v>
       </c>
       <c r="QD1" t="s">
         <v>292</v>
@@ -6383,7 +6461,7 @@
         <v>296</v>
       </c>
       <c r="QI1" t="s">
-        <v>1054</v>
+        <v>1032</v>
       </c>
       <c r="QJ1" t="s">
         <v>297</v>
@@ -6401,7 +6479,7 @@
         <v>301</v>
       </c>
       <c r="QO1" t="s">
-        <v>1055</v>
+        <v>1033</v>
       </c>
       <c r="QP1" t="s">
         <v>302</v>
@@ -6428,10 +6506,10 @@
         <v>308</v>
       </c>
       <c r="QX1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="QY1" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="QZ1" t="s">
         <v>690</v>
@@ -6461,7 +6539,7 @@
         <v>315</v>
       </c>
       <c r="RI1" t="s">
-        <v>1056</v>
+        <v>1034</v>
       </c>
       <c r="RJ1" t="s">
         <v>316</v>
@@ -6575,22 +6653,22 @@
         <v>352</v>
       </c>
       <c r="SU1" t="s">
-        <v>1057</v>
+        <v>1035</v>
       </c>
       <c r="SV1" t="s">
-        <v>1058</v>
+        <v>1036</v>
       </c>
       <c r="SW1" t="s">
-        <v>1059</v>
+        <v>1037</v>
       </c>
       <c r="SX1" t="s">
-        <v>1060</v>
+        <v>1038</v>
       </c>
       <c r="SY1" t="s">
-        <v>1061</v>
+        <v>1039</v>
       </c>
       <c r="SZ1" t="s">
-        <v>1062</v>
+        <v>1040</v>
       </c>
       <c r="TA1" t="s">
         <v>353</v>
@@ -6608,10 +6686,10 @@
         <v>707</v>
       </c>
       <c r="TF1" t="s">
-        <v>1063</v>
+        <v>1041</v>
       </c>
       <c r="TG1" t="s">
-        <v>1064</v>
+        <v>1042</v>
       </c>
       <c r="TH1" t="s">
         <v>4</v>
@@ -6992,7 +7070,7 @@
         <v>480</v>
       </c>
       <c r="YD1" t="s">
-        <v>1065</v>
+        <v>1043</v>
       </c>
       <c r="YE1" t="s">
         <v>481</v>
@@ -7010,7 +7088,7 @@
         <v>485</v>
       </c>
       <c r="YJ1" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
       <c r="YK1" t="s">
         <v>486</v>
@@ -7307,7 +7385,7 @@
         <v>557</v>
       </c>
       <c r="ACE1" t="s">
-        <v>1067</v>
+        <v>1045</v>
       </c>
       <c r="ACF1" t="s">
         <v>558</v>
@@ -7319,7 +7397,7 @@
         <v>560</v>
       </c>
       <c r="ACI1" t="s">
-        <v>1068</v>
+        <v>1046</v>
       </c>
       <c r="ACJ1" t="s">
         <v>561</v>
@@ -7364,7 +7442,7 @@
         <v>574</v>
       </c>
       <c r="ACX1" t="s">
-        <v>1069</v>
+        <v>1047</v>
       </c>
       <c r="ACY1" t="s">
         <v>157</v>
@@ -7376,7 +7454,7 @@
         <v>576</v>
       </c>
       <c r="ADB1" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="ADC1" t="s">
         <v>577</v>
@@ -7418,10 +7496,10 @@
         <v>675</v>
       </c>
       <c r="ADP1" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="ADQ1" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="ADR1" t="s">
         <v>309</v>
@@ -7456,62 +7534,8 @@
       <c r="AEB1" t="s">
         <v>588</v>
       </c>
-      <c r="AEC1" t="s">
-        <v>987</v>
-      </c>
-      <c r="AED1" t="s">
-        <v>988</v>
-      </c>
-      <c r="AEE1" t="s">
-        <v>989</v>
-      </c>
-      <c r="AEF1" t="s">
-        <v>990</v>
-      </c>
-      <c r="AEG1" t="s">
-        <v>991</v>
-      </c>
-      <c r="AEH1" t="s">
-        <v>775</v>
-      </c>
-      <c r="AEI1" t="s">
-        <v>992</v>
-      </c>
-      <c r="AEJ1" t="s">
-        <v>993</v>
-      </c>
-      <c r="AEK1" t="s">
-        <v>994</v>
-      </c>
-      <c r="AEL1" t="s">
-        <v>995</v>
-      </c>
-      <c r="AEM1" t="s">
-        <v>996</v>
-      </c>
-      <c r="AEN1" t="s">
-        <v>997</v>
-      </c>
-      <c r="AEO1" t="s">
-        <v>998</v>
-      </c>
-      <c r="AEP1" t="s">
-        <v>999</v>
-      </c>
-      <c r="AEQ1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="AER1" t="s">
-        <v>1001</v>
-      </c>
-      <c r="AES1" t="s">
-        <v>1002</v>
-      </c>
-      <c r="AET1" t="s">
-        <v>1003</v>
-      </c>
     </row>
-    <row r="2" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>46297</v>
       </c>
@@ -7842,29 +7866,8 @@
       <c r="AEB2">
         <v>1</v>
       </c>
-      <c r="AEL2">
-        <v>884394036</v>
-      </c>
-      <c r="AEM2" t="s">
-        <v>735</v>
-      </c>
-      <c r="AEN2" s="1">
-        <v>46297.550879629627</v>
-      </c>
-      <c r="AEP2" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER2" t="s">
-        <v>737</v>
-      </c>
-      <c r="AES2" t="s">
-        <v>738</v>
-      </c>
-      <c r="AET2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>46297</v>
       </c>
@@ -7973,29 +7976,8 @@
       <c r="AEB3">
         <v>2</v>
       </c>
-      <c r="AEL3">
-        <v>884613428</v>
-      </c>
-      <c r="AEM3" t="s">
-        <v>750</v>
-      </c>
-      <c r="AEN3" s="1">
-        <v>46297.744189814817</v>
-      </c>
-      <c r="AEP3" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER3" t="s">
-        <v>751</v>
-      </c>
-      <c r="AES3" t="s">
-        <v>752</v>
-      </c>
-      <c r="AET3">
-        <v>2</v>
-      </c>
     </row>
-    <row r="4" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>46297</v>
       </c>
@@ -8185,29 +8167,8 @@
       <c r="AEB4">
         <v>3</v>
       </c>
-      <c r="AEL4">
-        <v>884667912</v>
-      </c>
-      <c r="AEM4" t="s">
-        <v>772</v>
-      </c>
-      <c r="AEN4" s="1">
-        <v>46297.806550925918</v>
-      </c>
-      <c r="AEP4" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER4" t="s">
-        <v>773</v>
-      </c>
-      <c r="AES4" t="s">
-        <v>774</v>
-      </c>
-      <c r="AET4">
-        <v>3</v>
-      </c>
     </row>
-    <row r="5" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>46298</v>
       </c>
@@ -8215,7 +8176,7 @@
         <v>708</v>
       </c>
       <c r="C5" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D5" t="s">
         <v>593</v>
@@ -8224,7 +8185,7 @@
         <v>711</v>
       </c>
       <c r="H5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -8254,10 +8215,10 @@
         <v>713</v>
       </c>
       <c r="Y5" t="s">
+        <v>777</v>
+      </c>
+      <c r="AG5" t="s">
         <v>778</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>779</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -8287,68 +8248,68 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AR5" t="s">
         <v>722</v>
       </c>
       <c r="AT5" t="s">
+        <v>780</v>
+      </c>
+      <c r="AU5">
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>1</v>
+      </c>
+      <c r="AZ5" t="s">
         <v>781</v>
       </c>
-      <c r="AU5">
-        <v>1</v>
-      </c>
-      <c r="AV5">
-        <v>1</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>1</v>
-      </c>
-      <c r="AZ5" t="s">
+      <c r="BA5">
+        <v>1</v>
+      </c>
+      <c r="BB5">
+        <v>1</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="s">
         <v>782</v>
-      </c>
-      <c r="BA5">
-        <v>1</v>
-      </c>
-      <c r="BB5">
-        <v>1</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>783</v>
       </c>
       <c r="BE5" t="s">
         <v>718</v>
       </c>
       <c r="BG5" t="s">
+        <v>780</v>
+      </c>
+      <c r="BH5">
+        <v>1</v>
+      </c>
+      <c r="BI5">
+        <v>1</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>1</v>
+      </c>
+      <c r="BM5" t="s">
         <v>781</v>
       </c>
-      <c r="BH5">
-        <v>1</v>
-      </c>
-      <c r="BI5">
-        <v>1</v>
-      </c>
-      <c r="BJ5">
-        <v>0</v>
-      </c>
-      <c r="BK5">
-        <v>0</v>
-      </c>
-      <c r="BL5">
-        <v>1</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>782</v>
-      </c>
       <c r="BN5">
         <v>1</v>
       </c>
@@ -8359,68 +8320,68 @@
         <v>0</v>
       </c>
       <c r="BQ5" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="BR5" t="s">
         <v>718</v>
       </c>
       <c r="BT5" t="s">
+        <v>784</v>
+      </c>
+      <c r="BU5">
+        <v>1</v>
+      </c>
+      <c r="BV5">
+        <v>1</v>
+      </c>
+      <c r="BW5">
+        <v>1</v>
+      </c>
+      <c r="BX5">
+        <v>1</v>
+      </c>
+      <c r="BY5">
+        <v>1</v>
+      </c>
+      <c r="BZ5" t="s">
         <v>785</v>
       </c>
-      <c r="BU5">
-        <v>1</v>
-      </c>
-      <c r="BV5">
-        <v>1</v>
-      </c>
-      <c r="BW5">
-        <v>1</v>
-      </c>
-      <c r="BX5">
-        <v>1</v>
-      </c>
-      <c r="BY5">
-        <v>1</v>
-      </c>
-      <c r="BZ5" t="s">
+      <c r="CA5">
+        <v>1</v>
+      </c>
+      <c r="CB5">
+        <v>1</v>
+      </c>
+      <c r="CC5">
+        <v>1</v>
+      </c>
+      <c r="CD5" t="s">
         <v>786</v>
-      </c>
-      <c r="CA5">
-        <v>1</v>
-      </c>
-      <c r="CB5">
-        <v>1</v>
-      </c>
-      <c r="CC5">
-        <v>1</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>787</v>
       </c>
       <c r="CE5" t="s">
         <v>718</v>
       </c>
       <c r="CG5" t="s">
+        <v>784</v>
+      </c>
+      <c r="CH5">
+        <v>1</v>
+      </c>
+      <c r="CI5">
+        <v>1</v>
+      </c>
+      <c r="CJ5">
+        <v>1</v>
+      </c>
+      <c r="CK5">
+        <v>1</v>
+      </c>
+      <c r="CL5">
+        <v>1</v>
+      </c>
+      <c r="CM5" t="s">
         <v>785</v>
       </c>
-      <c r="CH5">
-        <v>1</v>
-      </c>
-      <c r="CI5">
-        <v>1</v>
-      </c>
-      <c r="CJ5">
-        <v>1</v>
-      </c>
-      <c r="CK5">
-        <v>1</v>
-      </c>
-      <c r="CL5">
-        <v>1</v>
-      </c>
-      <c r="CM5" t="s">
-        <v>786</v>
-      </c>
       <c r="CN5">
         <v>1</v>
       </c>
@@ -8431,32 +8392,32 @@
         <v>1</v>
       </c>
       <c r="CQ5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="CR5" t="s">
         <v>722</v>
       </c>
       <c r="CT5" t="s">
+        <v>784</v>
+      </c>
+      <c r="CU5">
+        <v>1</v>
+      </c>
+      <c r="CV5">
+        <v>1</v>
+      </c>
+      <c r="CW5">
+        <v>1</v>
+      </c>
+      <c r="CX5">
+        <v>1</v>
+      </c>
+      <c r="CY5">
+        <v>1</v>
+      </c>
+      <c r="CZ5" t="s">
         <v>785</v>
       </c>
-      <c r="CU5">
-        <v>1</v>
-      </c>
-      <c r="CV5">
-        <v>1</v>
-      </c>
-      <c r="CW5">
-        <v>1</v>
-      </c>
-      <c r="CX5">
-        <v>1</v>
-      </c>
-      <c r="CY5">
-        <v>1</v>
-      </c>
-      <c r="CZ5" t="s">
-        <v>786</v>
-      </c>
       <c r="DA5">
         <v>1</v>
       </c>
@@ -8467,13 +8428,13 @@
         <v>1</v>
       </c>
       <c r="DD5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="DE5" t="s">
         <v>722</v>
       </c>
       <c r="DF5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="DG5">
         <v>1</v>
@@ -8515,7 +8476,7 @@
         <v>0</v>
       </c>
       <c r="TE5" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="TH5" t="s">
         <v>710</v>
@@ -8524,7 +8485,7 @@
         <v>885064065</v>
       </c>
       <c r="ADU5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="ADV5" s="1">
         <v>46298.597939814812</v>
@@ -8536,35 +8497,13 @@
         <v>751</v>
       </c>
       <c r="AEA5" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AEB5">
         <v>4</v>
       </c>
-      <c r="AEF5" s="1"/>
-      <c r="AEL5">
-        <v>885064065</v>
-      </c>
-      <c r="AEM5" t="s">
-        <v>791</v>
-      </c>
-      <c r="AEN5" s="1">
-        <v>46298.597939814812</v>
-      </c>
-      <c r="AEP5" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER5" t="s">
-        <v>751</v>
-      </c>
-      <c r="AES5" t="s">
-        <v>792</v>
-      </c>
-      <c r="AET5">
-        <v>4</v>
-      </c>
     </row>
-    <row r="6" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>46298</v>
       </c>
@@ -8572,7 +8511,7 @@
         <v>708</v>
       </c>
       <c r="C6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D6" t="s">
         <v>590</v>
@@ -8581,7 +8520,7 @@
         <v>711</v>
       </c>
       <c r="L6" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -8611,65 +8550,65 @@
         <v>713</v>
       </c>
       <c r="Y6" t="s">
+        <v>794</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>784</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>785</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>795</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>785</v>
-      </c>
-      <c r="AH6">
-        <v>1</v>
-      </c>
-      <c r="AI6">
-        <v>1</v>
-      </c>
-      <c r="AJ6">
-        <v>1</v>
-      </c>
-      <c r="AK6">
-        <v>1</v>
-      </c>
-      <c r="AL6">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>786</v>
-      </c>
-      <c r="AN6">
-        <v>1</v>
-      </c>
-      <c r="AO6">
-        <v>1</v>
-      </c>
-      <c r="AP6">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>796</v>
       </c>
       <c r="AR6" t="s">
         <v>722</v>
       </c>
       <c r="AT6" t="s">
+        <v>784</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6" t="s">
         <v>785</v>
       </c>
-      <c r="AU6">
-        <v>1</v>
-      </c>
-      <c r="AV6">
-        <v>1</v>
-      </c>
-      <c r="AW6">
-        <v>1</v>
-      </c>
-      <c r="AX6">
-        <v>1</v>
-      </c>
-      <c r="AY6">
-        <v>1</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>786</v>
-      </c>
       <c r="BA6">
         <v>1</v>
       </c>
@@ -8680,32 +8619,32 @@
         <v>1</v>
       </c>
       <c r="BD6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="BE6" t="s">
         <v>718</v>
       </c>
       <c r="BG6" t="s">
+        <v>784</v>
+      </c>
+      <c r="BH6">
+        <v>1</v>
+      </c>
+      <c r="BI6">
+        <v>1</v>
+      </c>
+      <c r="BJ6">
+        <v>1</v>
+      </c>
+      <c r="BK6">
+        <v>1</v>
+      </c>
+      <c r="BL6">
+        <v>1</v>
+      </c>
+      <c r="BM6" t="s">
         <v>785</v>
       </c>
-      <c r="BH6">
-        <v>1</v>
-      </c>
-      <c r="BI6">
-        <v>1</v>
-      </c>
-      <c r="BJ6">
-        <v>1</v>
-      </c>
-      <c r="BK6">
-        <v>1</v>
-      </c>
-      <c r="BL6">
-        <v>1</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>786</v>
-      </c>
       <c r="BN6">
         <v>1</v>
       </c>
@@ -8716,32 +8655,32 @@
         <v>1</v>
       </c>
       <c r="BQ6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="BR6" t="s">
         <v>722</v>
       </c>
       <c r="BT6" t="s">
+        <v>784</v>
+      </c>
+      <c r="BU6">
+        <v>1</v>
+      </c>
+      <c r="BV6">
+        <v>1</v>
+      </c>
+      <c r="BW6">
+        <v>1</v>
+      </c>
+      <c r="BX6">
+        <v>1</v>
+      </c>
+      <c r="BY6">
+        <v>1</v>
+      </c>
+      <c r="BZ6" t="s">
         <v>785</v>
       </c>
-      <c r="BU6">
-        <v>1</v>
-      </c>
-      <c r="BV6">
-        <v>1</v>
-      </c>
-      <c r="BW6">
-        <v>1</v>
-      </c>
-      <c r="BX6">
-        <v>1</v>
-      </c>
-      <c r="BY6">
-        <v>1</v>
-      </c>
-      <c r="BZ6" t="s">
-        <v>786</v>
-      </c>
       <c r="CA6">
         <v>1</v>
       </c>
@@ -8752,32 +8691,32 @@
         <v>1</v>
       </c>
       <c r="CD6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="CE6" t="s">
         <v>722</v>
       </c>
       <c r="CG6" t="s">
+        <v>784</v>
+      </c>
+      <c r="CH6">
+        <v>1</v>
+      </c>
+      <c r="CI6">
+        <v>1</v>
+      </c>
+      <c r="CJ6">
+        <v>1</v>
+      </c>
+      <c r="CK6">
+        <v>1</v>
+      </c>
+      <c r="CL6">
+        <v>1</v>
+      </c>
+      <c r="CM6" t="s">
         <v>785</v>
       </c>
-      <c r="CH6">
-        <v>1</v>
-      </c>
-      <c r="CI6">
-        <v>1</v>
-      </c>
-      <c r="CJ6">
-        <v>1</v>
-      </c>
-      <c r="CK6">
-        <v>1</v>
-      </c>
-      <c r="CL6">
-        <v>1</v>
-      </c>
-      <c r="CM6" t="s">
-        <v>786</v>
-      </c>
       <c r="CN6">
         <v>1</v>
       </c>
@@ -8788,13 +8727,13 @@
         <v>1</v>
       </c>
       <c r="CQ6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="CR6" t="s">
         <v>722</v>
       </c>
       <c r="CT6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="CU6">
         <v>1</v>
@@ -8812,7 +8751,7 @@
         <v>1</v>
       </c>
       <c r="CZ6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="DA6">
         <v>1</v>
@@ -8824,13 +8763,13 @@
         <v>0</v>
       </c>
       <c r="DD6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="DE6" t="s">
         <v>722</v>
       </c>
       <c r="DF6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="DG6">
         <v>1</v>
@@ -8872,7 +8811,7 @@
         <v>5</v>
       </c>
       <c r="TE6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="TH6" t="s">
         <v>710</v>
@@ -8881,7 +8820,7 @@
         <v>885072414</v>
       </c>
       <c r="ADU6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="ADV6" s="1">
         <v>46298.609120370369</v>
@@ -8893,35 +8832,13 @@
         <v>751</v>
       </c>
       <c r="AEA6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AEB6">
         <v>5</v>
       </c>
-      <c r="AEF6" s="1"/>
-      <c r="AEL6">
-        <v>885072414</v>
-      </c>
-      <c r="AEM6" t="s">
-        <v>804</v>
-      </c>
-      <c r="AEN6" s="1">
-        <v>46298.609120370369</v>
-      </c>
-      <c r="AEP6" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER6" t="s">
-        <v>751</v>
-      </c>
-      <c r="AES6" t="s">
-        <v>805</v>
-      </c>
-      <c r="AET6">
-        <v>5</v>
-      </c>
     </row>
-    <row r="7" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>46297</v>
       </c>
@@ -8929,7 +8846,7 @@
         <v>708</v>
       </c>
       <c r="C7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D7" t="s">
         <v>594</v>
@@ -8938,7 +8855,7 @@
         <v>711</v>
       </c>
       <c r="I7" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="P7">
         <v>17</v>
@@ -8968,10 +8885,10 @@
         <v>713</v>
       </c>
       <c r="Y7" t="s">
+        <v>807</v>
+      </c>
+      <c r="AG7" t="s">
         <v>808</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>809</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -9001,13 +8918,13 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="s">
-        <v>810</v>
+        <v>1057</v>
       </c>
       <c r="AR7" t="s">
         <v>718</v>
       </c>
       <c r="AT7" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AU7">
         <v>0</v>
@@ -9037,13 +8954,13 @@
         <v>0</v>
       </c>
       <c r="BD7" t="s">
-        <v>810</v>
+        <v>1058</v>
       </c>
       <c r="BE7" t="s">
         <v>722</v>
       </c>
       <c r="BG7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="BH7">
         <v>0</v>
@@ -9061,7 +8978,7 @@
         <v>1</v>
       </c>
       <c r="BM7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="BN7">
         <v>1</v>
@@ -9073,13 +8990,13 @@
         <v>1</v>
       </c>
       <c r="BQ7" t="s">
-        <v>813</v>
+        <v>1059</v>
       </c>
       <c r="BR7" t="s">
         <v>718</v>
       </c>
       <c r="BT7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="BU7">
         <v>0</v>
@@ -9097,7 +9014,7 @@
         <v>1</v>
       </c>
       <c r="BZ7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="CA7">
         <v>1</v>
@@ -9107,31 +9024,34 @@
       </c>
       <c r="CC7">
         <v>1</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>1059</v>
       </c>
       <c r="CE7" t="s">
         <v>718</v>
       </c>
       <c r="CG7" t="s">
+        <v>784</v>
+      </c>
+      <c r="CH7">
+        <v>1</v>
+      </c>
+      <c r="CI7">
+        <v>1</v>
+      </c>
+      <c r="CJ7">
+        <v>1</v>
+      </c>
+      <c r="CK7">
+        <v>1</v>
+      </c>
+      <c r="CL7">
+        <v>1</v>
+      </c>
+      <c r="CM7" t="s">
         <v>785</v>
       </c>
-      <c r="CH7">
-        <v>1</v>
-      </c>
-      <c r="CI7">
-        <v>1</v>
-      </c>
-      <c r="CJ7">
-        <v>1</v>
-      </c>
-      <c r="CK7">
-        <v>1</v>
-      </c>
-      <c r="CL7">
-        <v>1</v>
-      </c>
-      <c r="CM7" t="s">
-        <v>786</v>
-      </c>
       <c r="CN7">
         <v>1</v>
       </c>
@@ -9140,12 +9060,15 @@
       </c>
       <c r="CP7">
         <v>1</v>
+      </c>
+      <c r="CQ7" t="s">
+        <v>1059</v>
       </c>
       <c r="CR7" t="s">
         <v>722</v>
       </c>
       <c r="CT7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="CU7">
         <v>0</v>
@@ -9163,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="CZ7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="DA7">
         <v>1</v>
@@ -9173,12 +9096,15 @@
       </c>
       <c r="DC7">
         <v>1</v>
+      </c>
+      <c r="DD7" t="s">
+        <v>1059</v>
       </c>
       <c r="DE7" t="s">
         <v>718</v>
       </c>
       <c r="DF7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="DG7">
         <v>1</v>
@@ -9211,26 +9137,26 @@
         <v>713</v>
       </c>
       <c r="DQ7" t="s">
+        <v>816</v>
+      </c>
+      <c r="DR7">
+        <v>0</v>
+      </c>
+      <c r="DS7">
+        <v>0</v>
+      </c>
+      <c r="DT7">
+        <v>1</v>
+      </c>
+      <c r="DU7">
+        <v>1</v>
+      </c>
+      <c r="DV7">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="s">
         <v>817</v>
       </c>
-      <c r="DR7">
-        <v>0</v>
-      </c>
-      <c r="DS7">
-        <v>0</v>
-      </c>
-      <c r="DT7">
-        <v>1</v>
-      </c>
-      <c r="DU7">
-        <v>1</v>
-      </c>
-      <c r="DV7">
-        <v>0</v>
-      </c>
-      <c r="DZ7" t="s">
-        <v>818</v>
-      </c>
       <c r="EA7">
         <v>1</v>
       </c>
@@ -9253,7 +9179,7 @@
         <v>1</v>
       </c>
       <c r="TE7" t="s">
-        <v>819</v>
+        <v>1060</v>
       </c>
       <c r="TH7" t="s">
         <v>710</v>
@@ -9262,7 +9188,7 @@
         <v>885187630</v>
       </c>
       <c r="ADU7" t="s">
-        <v>820</v>
+        <v>1061</v>
       </c>
       <c r="ADV7" s="1">
         <v>46298.763460648152</v>
@@ -9274,35 +9200,13 @@
         <v>751</v>
       </c>
       <c r="AEA7" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="AEB7">
         <v>6</v>
       </c>
-      <c r="AEF7" s="1"/>
-      <c r="AEL7">
-        <v>885187630</v>
-      </c>
-      <c r="AEM7" t="s">
-        <v>820</v>
-      </c>
-      <c r="AEN7" s="1">
-        <v>46298.763460648152</v>
-      </c>
-      <c r="AEP7" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER7" t="s">
-        <v>751</v>
-      </c>
-      <c r="AES7" t="s">
-        <v>821</v>
-      </c>
-      <c r="AET7">
-        <v>6</v>
-      </c>
     </row>
-    <row r="8" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>46295</v>
       </c>
@@ -9310,7 +9214,7 @@
         <v>708</v>
       </c>
       <c r="C8" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D8" t="s">
         <v>595</v>
@@ -9319,43 +9223,43 @@
         <v>754</v>
       </c>
       <c r="J8" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="EN8" t="s">
         <v>756</v>
       </c>
       <c r="FQ8" t="s">
+        <v>821</v>
+      </c>
+      <c r="FR8" t="s">
+        <v>821</v>
+      </c>
+      <c r="FS8" t="s">
+        <v>821</v>
+      </c>
+      <c r="FT8">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="s">
+        <v>822</v>
+      </c>
+      <c r="FW8" t="s">
+        <v>823</v>
+      </c>
+      <c r="FX8" t="s">
         <v>824</v>
       </c>
-      <c r="FR8" t="s">
-        <v>824</v>
-      </c>
-      <c r="FS8" t="s">
-        <v>824</v>
-      </c>
-      <c r="FT8">
-        <v>0</v>
-      </c>
-      <c r="FV8" t="s">
+      <c r="FY8">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="s">
         <v>825</v>
       </c>
-      <c r="FW8" t="s">
+      <c r="GB8" t="s">
         <v>826</v>
       </c>
-      <c r="FX8" t="s">
-        <v>827</v>
-      </c>
-      <c r="FY8">
-        <v>0</v>
-      </c>
-      <c r="GA8" t="s">
-        <v>828</v>
-      </c>
-      <c r="GB8" t="s">
-        <v>829</v>
-      </c>
       <c r="GC8" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="GD8">
         <v>0</v>
@@ -9364,28 +9268,28 @@
         <v>769</v>
       </c>
       <c r="GG8" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="GH8" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="GI8">
         <v>0</v>
       </c>
       <c r="GK8" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="GL8" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="GM8" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="GN8">
         <v>2</v>
       </c>
       <c r="GO8" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="GP8">
         <v>1</v>
@@ -9418,16 +9322,16 @@
         <v>713</v>
       </c>
       <c r="HJ8" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="HQ8" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="HR8">
         <v>2</v>
       </c>
       <c r="HS8" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="HU8" t="s">
         <v>768</v>
@@ -9436,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="HW8" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="HY8" t="s">
         <v>768</v>
@@ -9445,16 +9349,16 @@
         <v>6</v>
       </c>
       <c r="IA8" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="IC8" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="ID8">
         <v>1</v>
       </c>
       <c r="IE8" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="IG8" t="s">
         <v>768</v>
@@ -9463,19 +9367,19 @@
         <v>8</v>
       </c>
       <c r="II8" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="IS8" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="IT8" t="s">
         <v>771</v>
       </c>
       <c r="IU8" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="IV8" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="IW8" t="s">
         <v>769</v>
@@ -9490,91 +9394,91 @@
         <v>771</v>
       </c>
       <c r="JB8" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="JC8" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="JD8" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="JE8" t="s">
         <v>722</v>
       </c>
       <c r="JG8" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="JH8" t="s">
         <v>771</v>
       </c>
       <c r="JI8" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="JJ8" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="JK8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="JL8" t="s">
         <v>718</v>
       </c>
       <c r="JN8" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="JO8" t="s">
         <v>771</v>
       </c>
       <c r="JP8" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="JQ8" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="JR8" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="JS8" t="s">
         <v>718</v>
       </c>
       <c r="JU8" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="JV8" t="s">
         <v>771</v>
       </c>
       <c r="JW8" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="JX8" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="JY8" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="JZ8" t="s">
         <v>718</v>
       </c>
       <c r="KB8" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="KC8" t="s">
         <v>771</v>
       </c>
       <c r="KD8" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="KE8" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="KF8" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="KG8" t="s">
         <v>722</v>
       </c>
       <c r="KH8" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="KI8">
         <v>1</v>
@@ -9589,13 +9493,13 @@
         <v>1</v>
       </c>
       <c r="KN8" t="s">
+        <v>844</v>
+      </c>
+      <c r="KO8" t="s">
+        <v>845</v>
+      </c>
+      <c r="KQ8" t="s">
         <v>847</v>
-      </c>
-      <c r="KO8" t="s">
-        <v>848</v>
-      </c>
-      <c r="KQ8" t="s">
-        <v>850</v>
       </c>
       <c r="NJ8">
         <v>0</v>
@@ -9616,7 +9520,7 @@
         <v>91</v>
       </c>
       <c r="TE8" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="TH8" t="s">
         <v>710</v>
@@ -9628,7 +9532,7 @@
         <v>713</v>
       </c>
       <c r="ADD8" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="ADH8">
         <v>0</v>
@@ -9652,7 +9556,7 @@
         <v>885200260</v>
       </c>
       <c r="ADU8" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="ADV8" s="1">
         <v>46298.788032407407</v>
@@ -9664,35 +9568,13 @@
         <v>751</v>
       </c>
       <c r="AEA8" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="AEB8">
         <v>7</v>
       </c>
-      <c r="AEF8" s="1"/>
-      <c r="AEL8">
-        <v>885200260</v>
-      </c>
-      <c r="AEM8" t="s">
-        <v>852</v>
-      </c>
-      <c r="AEN8" s="1">
-        <v>46298.788032407407</v>
-      </c>
-      <c r="AEP8" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER8" t="s">
-        <v>751</v>
-      </c>
-      <c r="AES8" t="s">
-        <v>853</v>
-      </c>
-      <c r="AET8">
-        <v>7</v>
-      </c>
     </row>
-    <row r="9" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>46298</v>
       </c>
@@ -9700,7 +9582,7 @@
         <v>708</v>
       </c>
       <c r="C9" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D9" t="s">
         <v>595</v>
@@ -9709,7 +9591,7 @@
         <v>711</v>
       </c>
       <c r="J9" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="P9">
         <v>5</v>
@@ -9739,7 +9621,7 @@
         <v>734</v>
       </c>
       <c r="AG9" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -9769,13 +9651,13 @@
         <v>1</v>
       </c>
       <c r="AQ9" t="s">
-        <v>761</v>
+        <v>1062</v>
       </c>
       <c r="AR9" t="s">
         <v>718</v>
       </c>
       <c r="AT9" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="AU9">
         <v>1</v>
@@ -9793,7 +9675,7 @@
         <v>1</v>
       </c>
       <c r="AZ9" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="BA9">
         <v>0</v>
@@ -9805,13 +9687,13 @@
         <v>1</v>
       </c>
       <c r="BD9" t="s">
-        <v>761</v>
+        <v>1063</v>
       </c>
       <c r="BE9" t="s">
         <v>722</v>
       </c>
       <c r="BG9" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="BH9">
         <v>1</v>
@@ -9829,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="BM9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="BN9">
         <v>1</v>
@@ -9841,13 +9723,13 @@
         <v>1</v>
       </c>
       <c r="BQ9" t="s">
-        <v>827</v>
+        <v>1064</v>
       </c>
       <c r="BR9" t="s">
         <v>722</v>
       </c>
       <c r="BT9" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="BU9">
         <v>1</v>
@@ -9876,11 +9758,14 @@
       <c r="CC9">
         <v>1</v>
       </c>
+      <c r="CD9" t="s">
+        <v>1065</v>
+      </c>
       <c r="CE9" t="s">
         <v>722</v>
       </c>
       <c r="CG9" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="CH9">
         <v>0</v>
@@ -9898,7 +9783,7 @@
         <v>1</v>
       </c>
       <c r="CM9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="CN9">
         <v>1</v>
@@ -9908,6 +9793,9 @@
       </c>
       <c r="CP9">
         <v>1</v>
+      </c>
+      <c r="CQ9" t="s">
+        <v>1066</v>
       </c>
       <c r="CR9" t="s">
         <v>718</v>
@@ -9942,11 +9830,14 @@
       <c r="DC9">
         <v>1</v>
       </c>
+      <c r="DD9" t="s">
+        <v>1067</v>
+      </c>
       <c r="DE9" t="s">
         <v>718</v>
       </c>
       <c r="DF9" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="DG9">
         <v>0</v>
@@ -9988,7 +9879,7 @@
         <v>0</v>
       </c>
       <c r="TE9" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="TH9" t="s">
         <v>710</v>
@@ -9997,7 +9888,7 @@
         <v>885201939</v>
       </c>
       <c r="ADU9" t="s">
-        <v>862</v>
+        <v>1068</v>
       </c>
       <c r="ADV9" s="1">
         <v>46298.791562500002</v>
@@ -10009,35 +9900,13 @@
         <v>751</v>
       </c>
       <c r="AEA9" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="AEB9">
         <v>8</v>
       </c>
-      <c r="AEF9" s="1"/>
-      <c r="AEL9">
-        <v>885201939</v>
-      </c>
-      <c r="AEM9" t="s">
-        <v>862</v>
-      </c>
-      <c r="AEN9" s="1">
-        <v>46298.791562500002</v>
-      </c>
-      <c r="AEP9" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER9" t="s">
-        <v>751</v>
-      </c>
-      <c r="AES9" t="s">
-        <v>863</v>
-      </c>
-      <c r="AET9">
-        <v>8</v>
-      </c>
     </row>
-    <row r="10" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46296</v>
       </c>
@@ -10045,7 +9914,7 @@
         <v>708</v>
       </c>
       <c r="C10" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="D10" t="s">
         <v>597</v>
@@ -10054,7 +9923,7 @@
         <v>754</v>
       </c>
       <c r="M10" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="EN10" t="s">
         <v>756</v>
@@ -10063,50 +9932,50 @@
         <v>757</v>
       </c>
       <c r="FR10" t="s">
+        <v>862</v>
+      </c>
+      <c r="FS10" t="s">
+        <v>863</v>
+      </c>
+      <c r="FV10" t="s">
+        <v>862</v>
+      </c>
+      <c r="FW10" t="s">
+        <v>862</v>
+      </c>
+      <c r="FX10" t="s">
+        <v>864</v>
+      </c>
+      <c r="GA10" t="s">
+        <v>828</v>
+      </c>
+      <c r="GB10" t="s">
+        <v>865</v>
+      </c>
+      <c r="GC10" t="s">
         <v>866</v>
       </c>
-      <c r="FS10" t="s">
+      <c r="GF10" t="s">
         <v>867</v>
       </c>
-      <c r="FV10" t="s">
-        <v>866</v>
-      </c>
-      <c r="FW10" t="s">
-        <v>866</v>
-      </c>
-      <c r="FX10" t="s">
+      <c r="GG10" t="s">
         <v>868</v>
       </c>
-      <c r="GA10" t="s">
-        <v>831</v>
-      </c>
-      <c r="GB10" t="s">
+      <c r="GH10" t="s">
         <v>869</v>
       </c>
-      <c r="GC10" t="s">
+      <c r="GK10" t="s">
         <v>870</v>
       </c>
-      <c r="GF10" t="s">
+      <c r="GL10" t="s">
         <v>871</v>
       </c>
-      <c r="GG10" t="s">
+      <c r="GM10" t="s">
         <v>872</v>
       </c>
-      <c r="GH10" t="s">
+      <c r="GO10" t="s">
         <v>873</v>
       </c>
-      <c r="GK10" t="s">
-        <v>874</v>
-      </c>
-      <c r="GL10" t="s">
-        <v>875</v>
-      </c>
-      <c r="GM10" t="s">
-        <v>876</v>
-      </c>
-      <c r="GO10" t="s">
-        <v>877</v>
-      </c>
       <c r="GP10">
         <v>1</v>
       </c>
@@ -10129,7 +9998,7 @@
         <v>1</v>
       </c>
       <c r="HC10" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="HF10" t="s">
         <v>713</v>
@@ -10138,7 +10007,7 @@
         <v>713</v>
       </c>
       <c r="HJ10" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="HQ10" t="s">
         <v>768</v>
@@ -10147,7 +10016,7 @@
         <v>80</v>
       </c>
       <c r="HS10" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="HU10" t="s">
         <v>768</v>
@@ -10156,7 +10025,7 @@
         <v>90</v>
       </c>
       <c r="HW10" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="HY10" t="s">
         <v>768</v>
@@ -10165,7 +10034,7 @@
         <v>105</v>
       </c>
       <c r="IA10" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="IC10" t="s">
         <v>768</v>
@@ -10174,7 +10043,7 @@
         <v>50</v>
       </c>
       <c r="IE10" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="IG10" t="s">
         <v>767</v>
@@ -10183,7 +10052,7 @@
         <v>120</v>
       </c>
       <c r="II10" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="IS10" t="s">
         <v>770</v>
@@ -10192,31 +10061,31 @@
         <v>771</v>
       </c>
       <c r="IU10" t="s">
+        <v>876</v>
+      </c>
+      <c r="IV10" t="s">
+        <v>838</v>
+      </c>
+      <c r="IW10" t="s">
         <v>880</v>
-      </c>
-      <c r="IV10" t="s">
-        <v>841</v>
-      </c>
-      <c r="IW10" t="s">
-        <v>884</v>
       </c>
       <c r="IX10" t="s">
         <v>722</v>
       </c>
       <c r="IZ10" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="JA10" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="JB10" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="JC10" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="JD10" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="JE10" t="s">
         <v>718</v>
@@ -10228,31 +10097,31 @@
         <v>771</v>
       </c>
       <c r="JI10" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="JJ10" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="JK10" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="JL10" t="s">
         <v>722</v>
       </c>
       <c r="JN10" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="JO10" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="JP10" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="JQ10" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="JR10" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="JS10" t="s">
         <v>718</v>
@@ -10264,34 +10133,34 @@
         <v>771</v>
       </c>
       <c r="JW10" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="JX10" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="JY10" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="JZ10" t="s">
         <v>722</v>
       </c>
       <c r="KB10" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="KD10" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="KE10" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="KF10" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="KG10" t="s">
         <v>718</v>
       </c>
       <c r="KH10" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="KI10">
         <v>1</v>
@@ -10306,13 +10175,13 @@
         <v>0</v>
       </c>
       <c r="KN10" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="KO10" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="KQ10" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="NJ10">
         <v>90</v>
@@ -10333,7 +10202,7 @@
         <v>105</v>
       </c>
       <c r="TE10" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="TH10" t="s">
         <v>710</v>
@@ -10345,7 +10214,7 @@
         <v>734</v>
       </c>
       <c r="ADD10" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="ADH10">
         <v>90</v>
@@ -10369,7 +10238,7 @@
         <v>885374147</v>
       </c>
       <c r="ADU10" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="ADV10" s="1">
         <v>46299.338842592602</v>
@@ -10381,35 +10250,13 @@
         <v>751</v>
       </c>
       <c r="AEA10" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="AEB10">
         <v>9</v>
       </c>
-      <c r="AEF10" s="1"/>
-      <c r="AEL10">
-        <v>885374147</v>
-      </c>
-      <c r="AEM10" t="s">
-        <v>903</v>
-      </c>
-      <c r="AEN10" s="1">
-        <v>46299.338842592602</v>
-      </c>
-      <c r="AEP10" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER10" t="s">
-        <v>751</v>
-      </c>
-      <c r="AES10" t="s">
-        <v>904</v>
-      </c>
-      <c r="AET10">
-        <v>9</v>
-      </c>
     </row>
-    <row r="11" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46298</v>
       </c>
@@ -10417,7 +10264,7 @@
         <v>708</v>
       </c>
       <c r="C11" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="D11" t="s">
         <v>597</v>
@@ -10426,7 +10273,7 @@
         <v>711</v>
       </c>
       <c r="M11" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -10456,10 +10303,10 @@
         <v>713</v>
       </c>
       <c r="Y11" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="AG11" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -10489,13 +10336,13 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="AR11" t="s">
         <v>718</v>
       </c>
       <c r="AT11" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="AU11">
         <v>1</v>
@@ -10525,13 +10372,13 @@
         <v>1</v>
       </c>
       <c r="BD11" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="BE11" t="s">
         <v>722</v>
       </c>
       <c r="BG11" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="BH11">
         <v>1</v>
@@ -10561,13 +10408,13 @@
         <v>1</v>
       </c>
       <c r="BQ11" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="BR11" t="s">
         <v>722</v>
       </c>
       <c r="BT11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="BU11">
         <v>0</v>
@@ -10597,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="CD11" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="CE11" t="s">
         <v>718</v>
@@ -10633,7 +10480,7 @@
         <v>0</v>
       </c>
       <c r="CQ11" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="CR11" t="s">
         <v>718</v>
@@ -10669,13 +10516,13 @@
         <v>0</v>
       </c>
       <c r="DD11" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="DE11" t="s">
         <v>722</v>
       </c>
       <c r="DF11" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="DG11">
         <v>0</v>
@@ -10717,16 +10564,16 @@
         <v>1</v>
       </c>
       <c r="TE11" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="TH11" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="ADT11">
         <v>885381637</v>
       </c>
       <c r="ADU11" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="ADV11" s="1">
         <v>46299.352372685193</v>
@@ -10738,35 +10585,13 @@
         <v>751</v>
       </c>
       <c r="AEA11" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="AEB11">
         <v>10</v>
       </c>
-      <c r="AEF11" s="1"/>
-      <c r="AEL11">
-        <v>885381637</v>
-      </c>
-      <c r="AEM11" t="s">
-        <v>917</v>
-      </c>
-      <c r="AEN11" s="1">
-        <v>46299.352372685193</v>
-      </c>
-      <c r="AEP11" t="s">
-        <v>736</v>
-      </c>
-      <c r="AER11" t="s">
-        <v>751</v>
-      </c>
-      <c r="AES11" t="s">
-        <v>918</v>
-      </c>
-      <c r="AET11">
-        <v>10</v>
-      </c>
     </row>
-    <row r="12" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46298</v>
       </c>
@@ -10774,7 +10599,7 @@
         <v>708</v>
       </c>
       <c r="C12" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="D12" t="s">
         <v>589</v>
@@ -10783,7 +10608,7 @@
         <v>711</v>
       </c>
       <c r="N12" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -10812,6 +10637,9 @@
       <c r="X12" t="s">
         <v>713</v>
       </c>
+      <c r="Y12" t="s">
+        <v>1069</v>
+      </c>
       <c r="AG12" t="s">
         <v>715</v>
       </c>
@@ -10843,13 +10671,13 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="AR12" t="s">
         <v>722</v>
       </c>
       <c r="AT12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AU12">
         <v>0</v>
@@ -10879,13 +10707,13 @@
         <v>0</v>
       </c>
       <c r="BD12" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="BE12" t="s">
         <v>718</v>
       </c>
       <c r="BG12" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="BH12">
         <v>0</v>
@@ -10915,13 +10743,13 @@
         <v>0</v>
       </c>
       <c r="BQ12" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="BR12" t="s">
         <v>718</v>
       </c>
       <c r="BT12" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="BU12">
         <v>0</v>
@@ -10951,13 +10779,13 @@
         <v>1</v>
       </c>
       <c r="CD12" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="CE12" t="s">
         <v>722</v>
       </c>
       <c r="CG12" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="CH12">
         <v>0</v>
@@ -10987,13 +10815,13 @@
         <v>0</v>
       </c>
       <c r="CQ12" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="CR12" t="s">
         <v>718</v>
       </c>
       <c r="CT12" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="CU12">
         <v>1</v>
@@ -11011,7 +10839,7 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="DA12">
         <v>0</v>
@@ -11023,13 +10851,13 @@
         <v>1</v>
       </c>
       <c r="DD12" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="DE12" t="s">
         <v>718</v>
       </c>
       <c r="DF12" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="DG12">
         <v>1</v>
@@ -11071,7 +10899,7 @@
         <v>40</v>
       </c>
       <c r="TE12" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="TH12" t="s">
         <v>710</v>
@@ -11080,7 +10908,7 @@
         <v>886644705</v>
       </c>
       <c r="ADU12" t="s">
-        <v>970</v>
+        <v>1070</v>
       </c>
       <c r="ADV12" s="1">
         <v>46301.235891203702</v>
@@ -11089,18 +10917,16 @@
         <v>736</v>
       </c>
       <c r="ADZ12" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="AEA12" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="AEB12">
         <v>11</v>
       </c>
-      <c r="AEF12" s="1"/>
-      <c r="AEN12" s="1"/>
     </row>
-    <row r="13" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46298</v>
       </c>
@@ -11108,7 +10934,7 @@
         <v>708</v>
       </c>
       <c r="C13" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="D13" t="s">
         <v>589</v>
@@ -11117,10 +10943,10 @@
         <v>754</v>
       </c>
       <c r="N13" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="EN13" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="EO13">
         <v>676</v>
@@ -11138,7 +10964,7 @@
         <v>19</v>
       </c>
       <c r="FB13" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="FC13">
         <v>1</v>
@@ -11153,7 +10979,7 @@
         <v>713</v>
       </c>
       <c r="FG13" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="FH13" t="s">
         <v>713</v>
@@ -11180,13 +11006,13 @@
         <v>33</v>
       </c>
       <c r="TE13" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="TH13" t="s">
         <v>710</v>
       </c>
       <c r="ABK13" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="ABL13">
         <v>0</v>
@@ -11231,7 +11057,7 @@
         <v>886659275</v>
       </c>
       <c r="ADU13" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="ADV13" s="1">
         <v>46301.252986111111</v>
@@ -11240,18 +11066,16 @@
         <v>736</v>
       </c>
       <c r="ADZ13" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="AEA13" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="AEB13">
         <v>12</v>
       </c>
-      <c r="AEF13" s="1"/>
-      <c r="AEN13" s="1"/>
     </row>
-    <row r="14" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>46301</v>
       </c>
@@ -11259,7 +11083,7 @@
         <v>708</v>
       </c>
       <c r="C14" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D14" t="s">
         <v>593</v>
@@ -11268,7 +11092,7 @@
         <v>740</v>
       </c>
       <c r="H14" t="s">
-        <v>1011</v>
+        <v>989</v>
       </c>
       <c r="RS14" t="s">
         <v>742</v>
@@ -11280,7 +11104,7 @@
         <v>0</v>
       </c>
       <c r="RV14" t="s">
-        <v>1012</v>
+        <v>990</v>
       </c>
       <c r="RW14">
         <v>26</v>
@@ -11289,16 +11113,16 @@
         <v>34</v>
       </c>
       <c r="RY14" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="RZ14" s="1">
         <v>46301</v>
       </c>
       <c r="SA14" t="s">
-        <v>1014</v>
+        <v>992</v>
       </c>
       <c r="SB14" t="s">
-        <v>1015</v>
+        <v>993</v>
       </c>
       <c r="SC14">
         <v>51</v>
@@ -11313,7 +11137,7 @@
         <v>0</v>
       </c>
       <c r="SG14" t="s">
-        <v>1016</v>
+        <v>994</v>
       </c>
       <c r="SH14">
         <v>0</v>
@@ -11331,10 +11155,10 @@
         <v>1</v>
       </c>
       <c r="SM14" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="TE14" t="s">
-        <v>1018</v>
+        <v>996</v>
       </c>
       <c r="TH14" t="s">
         <v>710</v>
@@ -11343,7 +11167,7 @@
         <v>886820155</v>
       </c>
       <c r="ADU14" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="ADV14" s="1">
         <v>46301.379594907397</v>
@@ -11355,15 +11179,13 @@
         <v>751</v>
       </c>
       <c r="AEA14" t="s">
-        <v>1020</v>
+        <v>998</v>
       </c>
       <c r="AEB14">
         <v>13</v>
       </c>
-      <c r="AEF14" s="1"/>
-      <c r="AEN14" s="1"/>
     </row>
-    <row r="15" spans="1:826" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:808" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>46301</v>
       </c>
@@ -11371,7 +11193,7 @@
         <v>708</v>
       </c>
       <c r="C15" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D15" t="s">
         <v>593</v>
@@ -11380,7 +11202,7 @@
         <v>740</v>
       </c>
       <c r="H15" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="RS15" t="s">
         <v>742</v>
@@ -11392,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="RV15" t="s">
-        <v>1070</v>
+        <v>1048</v>
       </c>
       <c r="RW15">
         <v>30</v>
@@ -11401,16 +11223,16 @@
         <v>30</v>
       </c>
       <c r="RY15" t="s">
-        <v>1071</v>
+        <v>1049</v>
       </c>
       <c r="RZ15" s="1">
         <v>46301</v>
       </c>
       <c r="SA15" t="s">
-        <v>1072</v>
+        <v>1050</v>
       </c>
       <c r="SB15" t="s">
-        <v>1073</v>
+        <v>1051</v>
       </c>
       <c r="SC15">
         <v>112</v>
@@ -11425,7 +11247,7 @@
         <v>0</v>
       </c>
       <c r="SG15" t="s">
-        <v>1016</v>
+        <v>994</v>
       </c>
       <c r="SH15">
         <v>0</v>
@@ -11443,16 +11265,16 @@
         <v>1</v>
       </c>
       <c r="SM15" t="s">
-        <v>1074</v>
+        <v>1052</v>
       </c>
       <c r="TE15" t="s">
-        <v>1075</v>
+        <v>1053</v>
       </c>
       <c r="ADT15">
         <v>886940645</v>
       </c>
       <c r="ADU15" t="s">
-        <v>1076</v>
+        <v>1054</v>
       </c>
       <c r="ADV15" s="1">
         <v>46301.473958333343</v>
@@ -11461,16 +11283,670 @@
         <v>736</v>
       </c>
       <c r="ADZ15" t="s">
-        <v>1077</v>
+        <v>1055</v>
       </c>
       <c r="AEA15" t="s">
-        <v>1078</v>
+        <v>1056</v>
       </c>
       <c r="AEB15">
         <v>14</v>
       </c>
-      <c r="AEF15" s="1"/>
-      <c r="AEN15" s="1"/>
+    </row>
+    <row r="16" spans="1:808" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B16" t="s">
+        <v>708</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D16" t="s">
+        <v>596</v>
+      </c>
+      <c r="E16" t="s">
+        <v>711</v>
+      </c>
+      <c r="K16" t="s">
+        <v>1072</v>
+      </c>
+      <c r="P16">
+        <v>10</v>
+      </c>
+      <c r="Q16">
+        <v>5</v>
+      </c>
+      <c r="R16" t="s">
+        <v>713</v>
+      </c>
+      <c r="S16">
+        <v>10</v>
+      </c>
+      <c r="T16">
+        <v>5</v>
+      </c>
+      <c r="U16">
+        <v>5</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16" t="s">
+        <v>713</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>1073</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>813</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>1</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>1</v>
+      </c>
+      <c r="AL16">
+        <v>1</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>785</v>
+      </c>
+      <c r="AN16">
+        <v>1</v>
+      </c>
+      <c r="AO16">
+        <v>1</v>
+      </c>
+      <c r="AP16">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>718</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>784</v>
+      </c>
+      <c r="AU16">
+        <v>1</v>
+      </c>
+      <c r="AV16">
+        <v>1</v>
+      </c>
+      <c r="AW16">
+        <v>1</v>
+      </c>
+      <c r="AX16">
+        <v>1</v>
+      </c>
+      <c r="AY16">
+        <v>1</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>785</v>
+      </c>
+      <c r="BA16">
+        <v>1</v>
+      </c>
+      <c r="BB16">
+        <v>1</v>
+      </c>
+      <c r="BC16">
+        <v>1</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>1075</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>718</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>855</v>
+      </c>
+      <c r="BH16">
+        <v>1</v>
+      </c>
+      <c r="BI16">
+        <v>1</v>
+      </c>
+      <c r="BJ16">
+        <v>1</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>785</v>
+      </c>
+      <c r="BN16">
+        <v>1</v>
+      </c>
+      <c r="BO16">
+        <v>1</v>
+      </c>
+      <c r="BP16">
+        <v>1</v>
+      </c>
+      <c r="BQ16" t="s">
+        <v>1076</v>
+      </c>
+      <c r="BR16" t="s">
+        <v>718</v>
+      </c>
+      <c r="BT16" t="s">
+        <v>813</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>1</v>
+      </c>
+      <c r="BW16">
+        <v>1</v>
+      </c>
+      <c r="BX16">
+        <v>1</v>
+      </c>
+      <c r="BY16">
+        <v>1</v>
+      </c>
+      <c r="BZ16" t="s">
+        <v>785</v>
+      </c>
+      <c r="CA16">
+        <v>1</v>
+      </c>
+      <c r="CB16">
+        <v>1</v>
+      </c>
+      <c r="CC16">
+        <v>1</v>
+      </c>
+      <c r="CD16" t="s">
+        <v>1077</v>
+      </c>
+      <c r="CE16" t="s">
+        <v>722</v>
+      </c>
+      <c r="CG16" t="s">
+        <v>904</v>
+      </c>
+      <c r="CH16">
+        <v>1</v>
+      </c>
+      <c r="CI16">
+        <v>1</v>
+      </c>
+      <c r="CJ16">
+        <v>1</v>
+      </c>
+      <c r="CK16">
+        <v>1</v>
+      </c>
+      <c r="CL16">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="s">
+        <v>785</v>
+      </c>
+      <c r="CN16">
+        <v>1</v>
+      </c>
+      <c r="CO16">
+        <v>1</v>
+      </c>
+      <c r="CP16">
+        <v>1</v>
+      </c>
+      <c r="CQ16" t="s">
+        <v>1078</v>
+      </c>
+      <c r="CR16" t="s">
+        <v>718</v>
+      </c>
+      <c r="CT16" t="s">
+        <v>784</v>
+      </c>
+      <c r="CU16">
+        <v>1</v>
+      </c>
+      <c r="CV16">
+        <v>1</v>
+      </c>
+      <c r="CW16">
+        <v>1</v>
+      </c>
+      <c r="CX16">
+        <v>1</v>
+      </c>
+      <c r="CY16">
+        <v>1</v>
+      </c>
+      <c r="CZ16" t="s">
+        <v>785</v>
+      </c>
+      <c r="DA16">
+        <v>1</v>
+      </c>
+      <c r="DB16">
+        <v>1</v>
+      </c>
+      <c r="DC16">
+        <v>1</v>
+      </c>
+      <c r="DD16" t="s">
+        <v>1079</v>
+      </c>
+      <c r="DE16" t="s">
+        <v>722</v>
+      </c>
+      <c r="DF16" t="s">
+        <v>1080</v>
+      </c>
+      <c r="DG16">
+        <v>0</v>
+      </c>
+      <c r="DH16">
+        <v>0</v>
+      </c>
+      <c r="DI16">
+        <v>0</v>
+      </c>
+      <c r="DJ16">
+        <v>1</v>
+      </c>
+      <c r="DK16">
+        <v>1</v>
+      </c>
+      <c r="DL16">
+        <v>0</v>
+      </c>
+      <c r="DM16">
+        <v>0</v>
+      </c>
+      <c r="DN16">
+        <v>0</v>
+      </c>
+      <c r="DO16">
+        <v>1</v>
+      </c>
+      <c r="DP16" t="s">
+        <v>734</v>
+      </c>
+      <c r="EI16">
+        <v>0</v>
+      </c>
+      <c r="EK16">
+        <v>0</v>
+      </c>
+      <c r="EM16">
+        <v>0</v>
+      </c>
+      <c r="TE16" t="s">
+        <v>1081</v>
+      </c>
+      <c r="ADT16">
+        <v>887139498</v>
+      </c>
+      <c r="ADU16" t="s">
+        <v>1082</v>
+      </c>
+      <c r="ADV16" s="1">
+        <v>46301.599861111114</v>
+      </c>
+      <c r="ADX16" t="s">
+        <v>736</v>
+      </c>
+      <c r="ADZ16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AEA16" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AEB16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:808" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B17" t="s">
+        <v>708</v>
+      </c>
+      <c r="C17" t="s">
+        <v>775</v>
+      </c>
+      <c r="D17" t="s">
+        <v>593</v>
+      </c>
+      <c r="E17" t="s">
+        <v>740</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1085</v>
+      </c>
+      <c r="RS17" t="s">
+        <v>742</v>
+      </c>
+      <c r="RT17">
+        <v>1</v>
+      </c>
+      <c r="RU17">
+        <v>0</v>
+      </c>
+      <c r="RV17" t="s">
+        <v>1086</v>
+      </c>
+      <c r="RW17">
+        <v>24</v>
+      </c>
+      <c r="RX17">
+        <v>36</v>
+      </c>
+      <c r="RY17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="RZ17" s="1">
+        <v>46301</v>
+      </c>
+      <c r="SA17" t="s">
+        <v>1088</v>
+      </c>
+      <c r="SB17" t="s">
+        <v>1089</v>
+      </c>
+      <c r="SC17">
+        <v>63</v>
+      </c>
+      <c r="SD17">
+        <v>54</v>
+      </c>
+      <c r="SE17">
+        <v>0</v>
+      </c>
+      <c r="SF17">
+        <v>0</v>
+      </c>
+      <c r="SG17" t="s">
+        <v>1090</v>
+      </c>
+      <c r="SH17">
+        <v>1</v>
+      </c>
+      <c r="SI17">
+        <v>1</v>
+      </c>
+      <c r="SJ17">
+        <v>1</v>
+      </c>
+      <c r="SK17">
+        <v>1</v>
+      </c>
+      <c r="SL17">
+        <v>1</v>
+      </c>
+      <c r="SM17" t="s">
+        <v>1091</v>
+      </c>
+      <c r="TE17" t="s">
+        <v>1092</v>
+      </c>
+      <c r="ADT17">
+        <v>887285852</v>
+      </c>
+      <c r="ADU17" t="s">
+        <v>1093</v>
+      </c>
+      <c r="ADV17" s="1">
+        <v>46301.698564814818</v>
+      </c>
+      <c r="ADX17" t="s">
+        <v>736</v>
+      </c>
+      <c r="ADZ17" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AEA17" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AEB17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:808" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B18" t="s">
+        <v>708</v>
+      </c>
+      <c r="C18" t="s">
+        <v>805</v>
+      </c>
+      <c r="D18" t="s">
+        <v>594</v>
+      </c>
+      <c r="E18" t="s">
+        <v>740</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1095</v>
+      </c>
+      <c r="RS18" t="s">
+        <v>742</v>
+      </c>
+      <c r="RT18">
+        <v>1</v>
+      </c>
+      <c r="RU18">
+        <v>0</v>
+      </c>
+      <c r="RV18" t="s">
+        <v>1096</v>
+      </c>
+      <c r="RW18">
+        <v>2</v>
+      </c>
+      <c r="RX18">
+        <v>1</v>
+      </c>
+      <c r="RY18" t="s">
+        <v>1097</v>
+      </c>
+      <c r="RZ18" s="1">
+        <v>46301</v>
+      </c>
+      <c r="SA18" t="s">
+        <v>1098</v>
+      </c>
+      <c r="SB18" t="s">
+        <v>1099</v>
+      </c>
+      <c r="SC18">
+        <v>31</v>
+      </c>
+      <c r="SD18">
+        <v>26</v>
+      </c>
+      <c r="SE18">
+        <v>2</v>
+      </c>
+      <c r="SF18">
+        <v>1</v>
+      </c>
+      <c r="SG18" t="s">
+        <v>747</v>
+      </c>
+      <c r="SH18">
+        <v>0</v>
+      </c>
+      <c r="SI18">
+        <v>0</v>
+      </c>
+      <c r="SJ18">
+        <v>1</v>
+      </c>
+      <c r="SK18">
+        <v>1</v>
+      </c>
+      <c r="SL18">
+        <v>0</v>
+      </c>
+      <c r="SM18" t="s">
+        <v>1100</v>
+      </c>
+      <c r="TE18" t="s">
+        <v>1101</v>
+      </c>
+      <c r="TH18" t="s">
+        <v>710</v>
+      </c>
+      <c r="ADT18">
+        <v>887314303</v>
+      </c>
+      <c r="ADU18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="ADV18" s="1">
+        <v>46301.718159722222</v>
+      </c>
+      <c r="ADX18" t="s">
+        <v>736</v>
+      </c>
+      <c r="ADZ18" t="s">
+        <v>966</v>
+      </c>
+      <c r="AEA18" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AEB18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:808" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B19" t="s">
+        <v>708</v>
+      </c>
+      <c r="C19" t="s">
+        <v>805</v>
+      </c>
+      <c r="D19" t="s">
+        <v>594</v>
+      </c>
+      <c r="E19" t="s">
+        <v>740</v>
+      </c>
+      <c r="I19" t="s">
+        <v>1104</v>
+      </c>
+      <c r="RS19" t="s">
+        <v>742</v>
+      </c>
+      <c r="RT19">
+        <v>1</v>
+      </c>
+      <c r="RU19">
+        <v>0</v>
+      </c>
+      <c r="RV19" t="s">
+        <v>1105</v>
+      </c>
+      <c r="RW19">
+        <v>2</v>
+      </c>
+      <c r="RX19">
+        <v>2</v>
+      </c>
+      <c r="RY19" t="s">
+        <v>1106</v>
+      </c>
+      <c r="RZ19" s="1">
+        <v>46301</v>
+      </c>
+      <c r="SA19" t="s">
+        <v>1107</v>
+      </c>
+      <c r="SB19" t="s">
+        <v>1108</v>
+      </c>
+      <c r="SC19">
+        <v>39</v>
+      </c>
+      <c r="SD19">
+        <v>23</v>
+      </c>
+      <c r="SE19">
+        <v>0</v>
+      </c>
+      <c r="SF19">
+        <v>1</v>
+      </c>
+      <c r="SG19" t="s">
+        <v>747</v>
+      </c>
+      <c r="SH19">
+        <v>0</v>
+      </c>
+      <c r="SI19">
+        <v>0</v>
+      </c>
+      <c r="SJ19">
+        <v>1</v>
+      </c>
+      <c r="SK19">
+        <v>1</v>
+      </c>
+      <c r="SL19">
+        <v>0</v>
+      </c>
+      <c r="SM19" t="s">
+        <v>1109</v>
+      </c>
+      <c r="TE19" t="s">
+        <v>1110</v>
+      </c>
+      <c r="ADT19">
+        <v>887319690</v>
+      </c>
+      <c r="ADU19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="ADV19" s="1">
+        <v>46301.722268518519</v>
+      </c>
+      <c r="ADX19" t="s">
+        <v>736</v>
+      </c>
+      <c r="ADZ19" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AEA19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AEB19">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82B3ADAC-3BB3-2140-A591-35AC89166E19}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E72712D2-6E2D-E04E-B5FD-6C85726D6250}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="1348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="1488">
   <si>
     <t>Date</t>
   </si>
@@ -2701,9 +2701,6 @@
     <t>Lack of preparation confidence/skills</t>
   </si>
   <si>
-    <t>We dont know what to put how to make it</t>
-  </si>
-  <si>
     <t>Little time</t>
   </si>
   <si>
@@ -4064,6 +4061,429 @@
   </si>
   <si>
     <t>uuid:0a34d02e-4c95-40eb-bb84-b145b0b6f0aa</t>
+  </si>
+  <si>
+    <t>Nutri Club patron Nutri Club member District cordinator</t>
+  </si>
+  <si>
+    <t>through drama and role plays on how to process food from garden to kitchen</t>
+  </si>
+  <si>
+    <t>over population of the learners crowing the bus activation sessions</t>
+  </si>
+  <si>
+    <t>the learners can read well and understand especially the story books</t>
+  </si>
+  <si>
+    <t>girls must also be at school</t>
+  </si>
+  <si>
+    <t>girls dont like porriage</t>
+  </si>
+  <si>
+    <t>we use charcoal for cooking at home</t>
+  </si>
+  <si>
+    <t>but my mother pays someone who can collect water from the borehole</t>
+  </si>
+  <si>
+    <t>my mother may punish me</t>
+  </si>
+  <si>
+    <t>you can not add green in the porriage</t>
+  </si>
+  <si>
+    <t>nutrition scholl bus</t>
+  </si>
+  <si>
+    <t>waking up early will help boys and girls to attand class early</t>
+  </si>
+  <si>
+    <t>we all work at home</t>
+  </si>
+  <si>
+    <t>sharing work will help us all attned school early</t>
+  </si>
+  <si>
+    <t>because i can read</t>
+  </si>
+  <si>
+    <t>it is good to work for boys and girls at home and at school</t>
+  </si>
+  <si>
+    <t>dont know</t>
+  </si>
+  <si>
+    <t>idont know</t>
+  </si>
+  <si>
+    <t>crowds of children make the activation difficult until we separated per section which took long hours than expected</t>
+  </si>
+  <si>
+    <t>the learners discussed about gender roles and in terms of school feeding. recognised WFP support in feeding the children at school.</t>
+  </si>
+  <si>
+    <t>due to the large number of learners in school, conduct activation for two separate sessions for differnt classes.</t>
+  </si>
+  <si>
+    <t>this is a good activity for engaging the learners</t>
+  </si>
+  <si>
+    <t>engage the learners in two sessions to manage the numbers but also enagage all</t>
+  </si>
+  <si>
+    <t>8edbe0a5-ddc5-453e-b070-955bf2f8ba1d</t>
+  </si>
+  <si>
+    <t>uuid:8edbe0a5-ddc5-453e-b070-955bf2f8ba1d</t>
+  </si>
+  <si>
+    <t>NADUNGET P/S</t>
+  </si>
+  <si>
+    <t>more vulnerable children who need support</t>
+  </si>
+  <si>
+    <t>8af8d1e8-5712-49a6-9743-e97d5a0e83c0</t>
+  </si>
+  <si>
+    <t>uuid:8af8d1e8-5712-49a6-9743-e97d5a0e83c0</t>
+  </si>
+  <si>
+    <t>Nutri Club patron Another teacher District cordinator</t>
+  </si>
+  <si>
+    <t>by reading story books and quizzes and games</t>
+  </si>
+  <si>
+    <t>facilitators used simple word and also local language to make other learners understand</t>
+  </si>
+  <si>
+    <t>if my parents decide who remians at home, you cannot refuse</t>
+  </si>
+  <si>
+    <t>if there is available food to eat or porriage</t>
+  </si>
+  <si>
+    <t>it is good for all children to help at home work</t>
+  </si>
+  <si>
+    <t>i have to help my brother</t>
+  </si>
+  <si>
+    <t>herding cattle is not good work for girls</t>
+  </si>
+  <si>
+    <t>its good to wake up early</t>
+  </si>
+  <si>
+    <t>long distance to schhol you reach late</t>
+  </si>
+  <si>
+    <t>the mother says remain at home to work</t>
+  </si>
+  <si>
+    <t>both can fetch water</t>
+  </si>
+  <si>
+    <t>school bus for nutrition</t>
+  </si>
+  <si>
+    <t>its good to eat good food</t>
+  </si>
+  <si>
+    <t>nutrition</t>
+  </si>
+  <si>
+    <t>to look for food and cook for family</t>
+  </si>
+  <si>
+    <t>nutritional food</t>
+  </si>
+  <si>
+    <t>we help each other and eat same meals at school</t>
+  </si>
+  <si>
+    <t>nutri school bus in school</t>
+  </si>
+  <si>
+    <t>learners needed more time for enagemnet in groups</t>
+  </si>
+  <si>
+    <t>demonstration and games helped the learners to</t>
+  </si>
+  <si>
+    <t>prior planning with patrons and whole nutrition club</t>
+  </si>
+  <si>
+    <t>thank you for enaging the learners in the different sessions. we home to see the school ntribus coming again rto our school becasue it is educative and children have enjoyed today amnd may impove attendance in school</t>
+  </si>
+  <si>
+    <t>0abcaf97-9db0-463d-ac42-73f0d31b8bb5</t>
+  </si>
+  <si>
+    <t>uuid:0abcaf97-9db0-463d-ac42-73f0d31b8bb5</t>
+  </si>
+  <si>
+    <t>evaline</t>
+  </si>
+  <si>
+    <t>Nutri Club patron Another teacher Nutri Club member District cordinator</t>
+  </si>
+  <si>
+    <t>through a game</t>
+  </si>
+  <si>
+    <t>to control the crowd of children in one session</t>
+  </si>
+  <si>
+    <t>the video was shown and projected for learners to see</t>
+  </si>
+  <si>
+    <t>it is good to share roles at home and school</t>
+  </si>
+  <si>
+    <t>i agree to help my sister to cook and eat together</t>
+  </si>
+  <si>
+    <t>but girls are the ones who fetch forewood always</t>
+  </si>
+  <si>
+    <t>if my sister also is doing another work i can help to fetch water</t>
+  </si>
+  <si>
+    <t>all children must be at school not to take care of animals</t>
+  </si>
+  <si>
+    <t>no flour for porriage</t>
+  </si>
+  <si>
+    <t>no need to add green in food</t>
+  </si>
+  <si>
+    <t>we need to learn hpw to prepare together</t>
+  </si>
+  <si>
+    <t>i dont know</t>
+  </si>
+  <si>
+    <t>waking upo early to cook and fethc water</t>
+  </si>
+  <si>
+    <t>nutri bus</t>
+  </si>
+  <si>
+    <t>eat simiular meals at schools and home</t>
+  </si>
+  <si>
+    <t>both boys and gurls share roles</t>
+  </si>
+  <si>
+    <t>kasimeri school bus</t>
+  </si>
+  <si>
+    <t>there was no prior orientation of teachers on materials for nutrui bus activity</t>
+  </si>
+  <si>
+    <t>the activation was conducted alongside the campaign launch and children enjoyed session including the games, quize and answer sessions and reading inside the bus.</t>
+  </si>
+  <si>
+    <t>prior preparation and delivery of materials</t>
+  </si>
+  <si>
+    <t>Thank you for launching the nutri school bus campaign in Kasimeri school. as model school, we pledge to strengthen the learners ability to perform and excel in theor study.</t>
+  </si>
+  <si>
+    <t>70c45f08-47bc-4575-9f5b-671f212df395</t>
+  </si>
+  <si>
+    <t>uuid:70c45f08-47bc-4575-9f5b-671f212df395</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Metu porridge supplementation demonstrated Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>They were able to participate in the playing outdoor games of nutrition, education, and gender and my dreams</t>
+  </si>
+  <si>
+    <t>Strongly Disagree</t>
+  </si>
+  <si>
+    <t>Girls will not be able to catch up with the early morning lessons</t>
+  </si>
+  <si>
+    <t>It makes work very easy</t>
+  </si>
+  <si>
+    <t>It helps protect the other incase something happens on the way, shows respect to the girl child</t>
+  </si>
+  <si>
+    <t>Shows love to my sister, promoting gender equality</t>
+  </si>
+  <si>
+    <t>Because girls should also be given an opportunity to be in school, educating a girl child is like educating anation so they should not be left behind</t>
+  </si>
+  <si>
+    <t>Everyone is entitled to do house work at home</t>
+  </si>
+  <si>
+    <t>Everyone at home should be able to do house chores that includes boys and girls</t>
+  </si>
+  <si>
+    <t>Was not sure</t>
+  </si>
+  <si>
+    <t>Taste preference barriers Ingredients not prioritized at household level</t>
+  </si>
+  <si>
+    <t>Poor mobilisation by the school administrators</t>
+  </si>
+  <si>
+    <t>Active participation by all the learners</t>
+  </si>
+  <si>
+    <t>Early communication and early preparation</t>
+  </si>
+  <si>
+    <t>We the pupils and teachers of kamacharikol commit to work hand in hand with S4P AND WFP to make the campaign successful</t>
+  </si>
+  <si>
+    <t>Parents were not informed about the school activation and so it was hard to get information from any adult, the pupils should be given at least two days of bus activation that's the comment from one of them</t>
+  </si>
+  <si>
+    <t>76e9883a-d79a-4a54-b6c7-5aafe3619ffb</t>
+  </si>
+  <si>
+    <t>uuid:76e9883a-d79a-4a54-b6c7-5aafe3619ffb</t>
+  </si>
+  <si>
+    <t>KALAPATA P/S</t>
+  </si>
+  <si>
+    <t>Tuesday Friday</t>
+  </si>
+  <si>
+    <t>Next to the headteacher office</t>
+  </si>
+  <si>
+    <t>Early mobilisations for easy preparation of pupils</t>
+  </si>
+  <si>
+    <t>b3957f6e-cca2-4f03-886f-9d38e1773115</t>
+  </si>
+  <si>
+    <t>uuid:b3957f6e-cca2-4f03-886f-9d38e1773115</t>
+  </si>
+  <si>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t>PAJAR P/S</t>
+  </si>
+  <si>
+    <t>Monday Friday</t>
+  </si>
+  <si>
+    <t>On the wall of headteachers office</t>
+  </si>
+  <si>
+    <t>The school has an established garden that helps in supplementing the available food provided by wfp</t>
+  </si>
+  <si>
+    <t>c5b2ed38-95a4-42b6-b7bf-c863930fd956</t>
+  </si>
+  <si>
+    <t>uuid:c5b2ed38-95a4-42b6-b7bf-c863930fd956</t>
+  </si>
+  <si>
+    <t>Ngole Paula</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Food sorting &amp; matching game Metu porridge supplementation demonstrated Structured dialogue on rebalancing chores Fair food portions for all genders Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>The learners read the METU Porridge manual and they recited the cooking procedure</t>
+  </si>
+  <si>
+    <t>The questions were asked and learners were able to respond , they also practiced hands on</t>
+  </si>
+  <si>
+    <t>Because we want equal education for all, we all need to work together and leave for school early so that we get equal chances of better performance for all, to promote girl child education</t>
+  </si>
+  <si>
+    <t>It is very bad to leave your sister alone at home while you go to school, to promote love between boys and girls, to ensure equal performance</t>
+  </si>
+  <si>
+    <t>We should move or work together for security and protection purposes, to promote peace at home, to promote equal responsibilities at home, promotes equal treatment among boys and girls</t>
+  </si>
+  <si>
+    <t>For girls not to be punished, to show love to our sisters, to show respect to our sisters, to promote togetherness</t>
+  </si>
+  <si>
+    <t>To reduce the rates of school dropouts, to control early pregnancies, to reduce early marriages</t>
+  </si>
+  <si>
+    <t>While making porridge I will ensure that groundnut paste and milk is added, as a mother I will make sure that my children go to school early as I remain to do morning chores</t>
+  </si>
+  <si>
+    <t>A bus that brings people together</t>
+  </si>
+  <si>
+    <t>I will tell the person cooking to add BOO in the porridge, in the morning when we wake up I will make sure I help my sister to sweep the compound as she's doing other chores so that we all go to school at the same time</t>
+  </si>
+  <si>
+    <t>A bus that binds people together</t>
+  </si>
+  <si>
+    <t>While making porridge I ensure that they add sugar to make it tasty, if I wake up in the morning and the chores are heavy,  I will first rush to school and later come back to do them</t>
+  </si>
+  <si>
+    <t>A bus that brings us together</t>
+  </si>
+  <si>
+    <t>It's important to encourage workload sharing among boys and girls both at home and in school</t>
+  </si>
+  <si>
+    <t>When porridge is being made, I will make sure tammarine is added</t>
+  </si>
+  <si>
+    <t>While making porridge I will ensure that there is sorghum flour, cooking oil, groundnut paste and cooking oil, girls and boys should work together to make work easy</t>
+  </si>
+  <si>
+    <t>There were no community members involved in the activation since the school is enclosed.and outsiders are not allowed to enter</t>
+  </si>
+  <si>
+    <t>The school feeding program is such appreciated because the school attributes it to high enrolment</t>
+  </si>
+  <si>
+    <t>Early mobilization</t>
+  </si>
+  <si>
+    <t>We commit to make sure that our school garden is viable to support the learners nutrition because it supplies us with various vegetables</t>
+  </si>
+  <si>
+    <t>Data collection and entry should be done independently from the activation day</t>
+  </si>
+  <si>
+    <t>ef92283e-c179-49a0-a48c-bc86d4e40b83</t>
+  </si>
+  <si>
+    <t>uuid:ef92283e-c179-49a0-a48c-bc86d4e40b83</t>
+  </si>
+  <si>
+    <t>KACHIKOL P/S</t>
+  </si>
+  <si>
+    <t>Next to the headteachers office</t>
+  </si>
+  <si>
+    <t>The activation was scheduled for afternoon but due to delays in the first school it affected the amount of time allocated for this particular school, the learners  were few at the time of activation</t>
+  </si>
+  <si>
+    <t>b6f9aed8-98db-4211-a78e-32a0a844f14b</t>
+  </si>
+  <si>
+    <t>uuid:b6f9aed8-98db-4211-a78e-32a0a844f14b</t>
   </si>
 </sst>
 </file>
@@ -4142,8 +4562,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AEF35" totalsRowShown="0">
-  <autoFilter ref="A1:AEF35" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AEF44" totalsRowShown="0">
+  <autoFilter ref="A1:AEF44" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="812">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -5249,7 +5669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AEF35"/>
+  <dimension ref="A1:AEF44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -6207,13 +6627,13 @@
         <v>628</v>
       </c>
       <c r="DW1" t="s">
+        <v>914</v>
+      </c>
+      <c r="DX1" t="s">
         <v>915</v>
       </c>
-      <c r="DX1" t="s">
+      <c r="DY1" t="s">
         <v>916</v>
-      </c>
-      <c r="DY1" t="s">
-        <v>917</v>
       </c>
       <c r="DZ1" t="s">
         <v>629</v>
@@ -6237,25 +6657,25 @@
         <v>634</v>
       </c>
       <c r="EG1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="EH1" t="s">
         <v>635</v>
       </c>
       <c r="EI1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="EJ1" t="s">
         <v>636</v>
       </c>
       <c r="EK1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="EL1" t="s">
         <v>637</v>
       </c>
       <c r="EM1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="EN1" t="s">
         <v>93</v>
@@ -6270,31 +6690,31 @@
         <v>94</v>
       </c>
       <c r="ER1" t="s">
+        <v>921</v>
+      </c>
+      <c r="ES1" t="s">
         <v>922</v>
       </c>
-      <c r="ES1" t="s">
+      <c r="ET1" t="s">
         <v>923</v>
       </c>
-      <c r="ET1" t="s">
+      <c r="EU1" t="s">
         <v>924</v>
       </c>
-      <c r="EU1" t="s">
+      <c r="EV1" t="s">
         <v>925</v>
       </c>
-      <c r="EV1" t="s">
+      <c r="EW1" t="s">
         <v>926</v>
       </c>
-      <c r="EW1" t="s">
+      <c r="EX1" t="s">
         <v>927</v>
-      </c>
-      <c r="EX1" t="s">
-        <v>928</v>
       </c>
       <c r="EY1" t="s">
         <v>102</v>
       </c>
       <c r="EZ1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="FA1" t="s">
         <v>104</v>
@@ -6321,10 +6741,10 @@
         <v>640</v>
       </c>
       <c r="FI1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="FJ1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FK1" t="s">
         <v>117</v>
@@ -6441,43 +6861,43 @@
         <v>154</v>
       </c>
       <c r="GW1" t="s">
+        <v>980</v>
+      </c>
+      <c r="GX1" t="s">
         <v>981</v>
       </c>
-      <c r="GX1" t="s">
+      <c r="GY1" t="s">
         <v>982</v>
       </c>
-      <c r="GY1" t="s">
+      <c r="GZ1" t="s">
         <v>983</v>
       </c>
-      <c r="GZ1" t="s">
+      <c r="HA1" t="s">
         <v>984</v>
       </c>
-      <c r="HA1" t="s">
+      <c r="HB1" t="s">
         <v>985</v>
       </c>
-      <c r="HB1" t="s">
-        <v>986</v>
-      </c>
       <c r="HC1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="HD1" t="s">
         <v>155</v>
       </c>
       <c r="HE1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="HF1" t="s">
         <v>156</v>
       </c>
       <c r="HG1" t="s">
+        <v>931</v>
+      </c>
+      <c r="HH1" t="s">
         <v>932</v>
       </c>
-      <c r="HH1" t="s">
+      <c r="HI1" t="s">
         <v>933</v>
-      </c>
-      <c r="HI1" t="s">
-        <v>934</v>
       </c>
       <c r="HJ1" t="s">
         <v>158</v>
@@ -6486,7 +6906,7 @@
         <v>159</v>
       </c>
       <c r="HL1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="HM1" t="s">
         <v>160</v>
@@ -6495,7 +6915,7 @@
         <v>161</v>
       </c>
       <c r="HO1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="HP1" t="s">
         <v>162</v>
@@ -6507,7 +6927,7 @@
         <v>164</v>
       </c>
       <c r="HS1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="HT1" t="s">
         <v>165</v>
@@ -6519,7 +6939,7 @@
         <v>167</v>
       </c>
       <c r="HW1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="HX1" t="s">
         <v>168</v>
@@ -6531,7 +6951,7 @@
         <v>170</v>
       </c>
       <c r="IA1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="IB1" t="s">
         <v>171</v>
@@ -6543,7 +6963,7 @@
         <v>173</v>
       </c>
       <c r="IE1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="IF1" t="s">
         <v>174</v>
@@ -6555,13 +6975,13 @@
         <v>176</v>
       </c>
       <c r="II1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="IJ1" t="s">
         <v>177</v>
       </c>
       <c r="IK1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="IL1" t="s">
         <v>178</v>
@@ -6579,10 +6999,10 @@
         <v>182</v>
       </c>
       <c r="IQ1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="IR1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="IS1" t="s">
         <v>183</v>
@@ -6600,7 +7020,7 @@
         <v>187</v>
       </c>
       <c r="IX1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="IY1" t="s">
         <v>188</v>
@@ -6621,7 +7041,7 @@
         <v>193</v>
       </c>
       <c r="JE1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="JF1" t="s">
         <v>232</v>
@@ -6642,10 +7062,10 @@
         <v>199</v>
       </c>
       <c r="JL1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="JM1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="JN1" t="s">
         <v>702</v>
@@ -6663,7 +7083,7 @@
         <v>706</v>
       </c>
       <c r="JS1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="JT1" t="s">
         <v>701</v>
@@ -6684,7 +7104,7 @@
         <v>205</v>
       </c>
       <c r="JZ1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="KA1" t="s">
         <v>206</v>
@@ -6705,7 +7125,7 @@
         <v>211</v>
       </c>
       <c r="KG1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="KH1" t="s">
         <v>641</v>
@@ -6732,7 +7152,7 @@
         <v>213</v>
       </c>
       <c r="KP1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="KQ1" t="s">
         <v>215</v>
@@ -6750,13 +7170,13 @@
         <v>219</v>
       </c>
       <c r="KV1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="KW1" t="s">
         <v>220</v>
       </c>
       <c r="KX1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="KY1" t="s">
         <v>221</v>
@@ -6783,16 +7203,16 @@
         <v>648</v>
       </c>
       <c r="LG1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="LH1" t="s">
         <v>1126</v>
-      </c>
-      <c r="LH1" t="s">
-        <v>1127</v>
       </c>
       <c r="LI1" t="s">
         <v>226</v>
       </c>
       <c r="LJ1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="LK1" t="s">
         <v>227</v>
@@ -6810,10 +7230,10 @@
         <v>231</v>
       </c>
       <c r="LP1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="LQ1" t="s">
         <v>1007</v>
-      </c>
-      <c r="LQ1" t="s">
-        <v>1008</v>
       </c>
       <c r="LR1" t="s">
         <v>233</v>
@@ -6834,7 +7254,7 @@
         <v>238</v>
       </c>
       <c r="LX1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="LY1" t="s">
         <v>239</v>
@@ -6855,7 +7275,7 @@
         <v>244</v>
       </c>
       <c r="ME1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="MF1" t="s">
         <v>245</v>
@@ -6876,7 +7296,7 @@
         <v>649</v>
       </c>
       <c r="ML1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="MM1" t="s">
         <v>650</v>
@@ -6897,7 +7317,7 @@
         <v>655</v>
       </c>
       <c r="MS1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="MT1" t="s">
         <v>250</v>
@@ -6918,7 +7338,7 @@
         <v>255</v>
       </c>
       <c r="MZ1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="NA1" t="s">
         <v>256</v>
@@ -6951,7 +7371,7 @@
         <v>660</v>
       </c>
       <c r="NK1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="NL1" t="s">
         <v>661</v>
@@ -6960,7 +7380,7 @@
         <v>662</v>
       </c>
       <c r="NN1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="NO1" t="s">
         <v>666</v>
@@ -6969,7 +7389,7 @@
         <v>667</v>
       </c>
       <c r="NQ1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="NR1" t="s">
         <v>671</v>
@@ -7002,13 +7422,13 @@
         <v>681</v>
       </c>
       <c r="OB1" t="s">
+        <v>948</v>
+      </c>
+      <c r="OC1" t="s">
         <v>949</v>
       </c>
-      <c r="OC1" t="s">
-        <v>950</v>
-      </c>
       <c r="OD1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="OE1" t="s">
         <v>682</v>
@@ -7026,61 +7446,61 @@
         <v>686</v>
       </c>
       <c r="OJ1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="OK1" t="s">
         <v>263</v>
       </c>
       <c r="OL1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="OM1" t="s">
         <v>1015</v>
-      </c>
-      <c r="OM1" t="s">
-        <v>1016</v>
       </c>
       <c r="ON1" t="s">
         <v>264</v>
       </c>
       <c r="OO1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="OP1" t="s">
         <v>1017</v>
-      </c>
-      <c r="OP1" t="s">
-        <v>1018</v>
       </c>
       <c r="OQ1" t="s">
         <v>265</v>
       </c>
       <c r="OR1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="OS1" t="s">
         <v>1019</v>
-      </c>
-      <c r="OS1" t="s">
-        <v>1020</v>
       </c>
       <c r="OT1" t="s">
         <v>266</v>
       </c>
       <c r="OU1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="OV1" t="s">
         <v>1021</v>
-      </c>
-      <c r="OV1" t="s">
-        <v>1022</v>
       </c>
       <c r="OW1" t="s">
         <v>267</v>
       </c>
       <c r="OX1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="OY1" t="s">
         <v>1023</v>
-      </c>
-      <c r="OY1" t="s">
-        <v>1024</v>
       </c>
       <c r="OZ1" t="s">
         <v>268</v>
       </c>
       <c r="PA1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="PB1" t="s">
         <v>1025</v>
-      </c>
-      <c r="PB1" t="s">
-        <v>1026</v>
       </c>
       <c r="PC1" t="s">
         <v>269</v>
@@ -7095,7 +7515,7 @@
         <v>272</v>
       </c>
       <c r="PG1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="PH1" t="s">
         <v>273</v>
@@ -7110,7 +7530,7 @@
         <v>688</v>
       </c>
       <c r="PL1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="PM1" t="s">
         <v>275</v>
@@ -7149,7 +7569,7 @@
         <v>286</v>
       </c>
       <c r="PY1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="PZ1" t="s">
         <v>287</v>
@@ -7167,7 +7587,7 @@
         <v>291</v>
       </c>
       <c r="QE1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="QF1" t="s">
         <v>292</v>
@@ -7185,7 +7605,7 @@
         <v>296</v>
       </c>
       <c r="QK1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="QL1" t="s">
         <v>297</v>
@@ -7203,7 +7623,7 @@
         <v>301</v>
       </c>
       <c r="QQ1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="QR1" t="s">
         <v>302</v>
@@ -7230,10 +7650,10 @@
         <v>308</v>
       </c>
       <c r="QZ1" t="s">
+        <v>950</v>
+      </c>
+      <c r="RA1" t="s">
         <v>951</v>
-      </c>
-      <c r="RA1" t="s">
-        <v>952</v>
       </c>
       <c r="RB1" t="s">
         <v>690</v>
@@ -7245,7 +7665,7 @@
         <v>692</v>
       </c>
       <c r="RE1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="RF1" t="s">
         <v>693</v>
@@ -7266,7 +7686,7 @@
         <v>315</v>
       </c>
       <c r="RL1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="RM1" t="s">
         <v>316</v>
@@ -7380,22 +7800,22 @@
         <v>352</v>
       </c>
       <c r="SX1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="SY1" t="s">
         <v>1033</v>
       </c>
-      <c r="SY1" t="s">
+      <c r="SZ1" t="s">
         <v>1034</v>
       </c>
-      <c r="SZ1" t="s">
+      <c r="TA1" t="s">
         <v>1035</v>
       </c>
-      <c r="TA1" t="s">
+      <c r="TB1" t="s">
         <v>1036</v>
       </c>
-      <c r="TB1" t="s">
+      <c r="TC1" t="s">
         <v>1037</v>
-      </c>
-      <c r="TC1" t="s">
-        <v>1038</v>
       </c>
       <c r="TD1" t="s">
         <v>353</v>
@@ -7413,10 +7833,10 @@
         <v>707</v>
       </c>
       <c r="TI1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="TJ1" t="s">
         <v>1039</v>
-      </c>
-      <c r="TJ1" t="s">
-        <v>1040</v>
       </c>
       <c r="TK1" t="s">
         <v>4</v>
@@ -7797,7 +8217,7 @@
         <v>480</v>
       </c>
       <c r="YG1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="YH1" t="s">
         <v>481</v>
@@ -7815,7 +8235,7 @@
         <v>485</v>
       </c>
       <c r="YM1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="YN1" t="s">
         <v>486</v>
@@ -8112,7 +8532,7 @@
         <v>557</v>
       </c>
       <c r="ACH1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="ACI1" t="s">
         <v>558</v>
@@ -8124,7 +8544,7 @@
         <v>560</v>
       </c>
       <c r="ACL1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="ACM1" t="s">
         <v>561</v>
@@ -8169,7 +8589,7 @@
         <v>574</v>
       </c>
       <c r="ADA1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="ADB1" t="s">
         <v>157</v>
@@ -8181,7 +8601,7 @@
         <v>576</v>
       </c>
       <c r="ADE1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="ADF1" t="s">
         <v>577</v>
@@ -8196,7 +8616,7 @@
         <v>579</v>
       </c>
       <c r="ADJ1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="ADK1" t="s">
         <v>663</v>
@@ -8226,10 +8646,10 @@
         <v>675</v>
       </c>
       <c r="ADT1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="ADU1" t="s">
         <v>1248</v>
-      </c>
-      <c r="ADU1" t="s">
-        <v>1249</v>
       </c>
       <c r="ADV1" t="s">
         <v>309</v>
@@ -9648,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="AR7" t="s">
         <v>718</v>
@@ -9684,7 +10104,7 @@
         <v>0</v>
       </c>
       <c r="BD7" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="BE7" t="s">
         <v>722</v>
@@ -9720,7 +10140,7 @@
         <v>1</v>
       </c>
       <c r="BQ7" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="BR7" t="s">
         <v>718</v>
@@ -9756,7 +10176,7 @@
         <v>1</v>
       </c>
       <c r="CD7" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="CE7" t="s">
         <v>718</v>
@@ -9792,7 +10212,7 @@
         <v>1</v>
       </c>
       <c r="CQ7" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="CR7" t="s">
         <v>722</v>
@@ -9828,7 +10248,7 @@
         <v>1</v>
       </c>
       <c r="DD7" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="DE7" t="s">
         <v>718</v>
@@ -9909,7 +10329,7 @@
         <v>1</v>
       </c>
       <c r="TH7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="TK7" t="s">
         <v>710</v>
@@ -9918,7 +10338,7 @@
         <v>885187630</v>
       </c>
       <c r="ADY7" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="ADZ7" s="1">
         <v>46298.763460648152</v>
@@ -10381,7 +10801,7 @@
         <v>1</v>
       </c>
       <c r="AQ9" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="AR9" t="s">
         <v>718</v>
@@ -10417,7 +10837,7 @@
         <v>1</v>
       </c>
       <c r="BD9" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="BE9" t="s">
         <v>722</v>
@@ -10453,7 +10873,7 @@
         <v>1</v>
       </c>
       <c r="BQ9" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="BR9" t="s">
         <v>722</v>
@@ -10489,7 +10909,7 @@
         <v>1</v>
       </c>
       <c r="CD9" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="CE9" t="s">
         <v>722</v>
@@ -10525,7 +10945,7 @@
         <v>1</v>
       </c>
       <c r="CQ9" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="CR9" t="s">
         <v>718</v>
@@ -10561,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="DD9" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="DE9" t="s">
         <v>718</v>
@@ -10618,7 +11038,7 @@
         <v>885201939</v>
       </c>
       <c r="ADY9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="ADZ9" s="1">
         <v>46298.791562500002</v>
@@ -10727,9 +11147,6 @@
       <c r="GV10">
         <v>1</v>
       </c>
-      <c r="HC10" t="s">
-        <v>893</v>
-      </c>
       <c r="HF10" t="s">
         <v>713</v>
       </c>
@@ -10905,13 +11322,13 @@
         <v>0</v>
       </c>
       <c r="KN10" t="s">
+        <v>893</v>
+      </c>
+      <c r="KO10" t="s">
         <v>894</v>
       </c>
-      <c r="KO10" t="s">
-        <v>895</v>
-      </c>
       <c r="KQ10" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="NL10">
         <v>90</v>
@@ -10932,7 +11349,7 @@
         <v>105</v>
       </c>
       <c r="TH10" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="TK10" t="s">
         <v>710</v>
@@ -10944,7 +11361,7 @@
         <v>734</v>
       </c>
       <c r="ADG10" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="ADL10">
         <v>90</v>
@@ -10968,7 +11385,7 @@
         <v>885374147</v>
       </c>
       <c r="ADY10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="ADZ10" s="1">
         <v>46299.338842592602</v>
@@ -10980,7 +11397,7 @@
         <v>751</v>
       </c>
       <c r="AEE10" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AEF10">
         <v>9</v>
@@ -11003,7 +11420,7 @@
         <v>711</v>
       </c>
       <c r="M11" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -11033,7 +11450,7 @@
         <v>713</v>
       </c>
       <c r="Y11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AG11" t="s">
         <v>852</v>
@@ -11066,13 +11483,13 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AR11" t="s">
         <v>718</v>
       </c>
       <c r="AT11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="AU11">
         <v>1</v>
@@ -11102,7 +11519,7 @@
         <v>1</v>
       </c>
       <c r="BD11" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="BE11" t="s">
         <v>722</v>
@@ -11138,13 +11555,13 @@
         <v>1</v>
       </c>
       <c r="BQ11" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="BR11" t="s">
         <v>722</v>
       </c>
       <c r="BT11" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="BU11">
         <v>0</v>
@@ -11174,7 +11591,7 @@
         <v>1</v>
       </c>
       <c r="CD11" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="CE11" t="s">
         <v>718</v>
@@ -11210,7 +11627,7 @@
         <v>0</v>
       </c>
       <c r="CQ11" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="CR11" t="s">
         <v>718</v>
@@ -11246,13 +11663,13 @@
         <v>0</v>
       </c>
       <c r="DD11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="DE11" t="s">
         <v>722</v>
       </c>
       <c r="DF11" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="DG11">
         <v>0</v>
@@ -11294,16 +11711,16 @@
         <v>1</v>
       </c>
       <c r="TH11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="TK11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="ADX11">
         <v>885381637</v>
       </c>
       <c r="ADY11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="ADZ11" s="1">
         <v>46299.352372685193</v>
@@ -11315,7 +11732,7 @@
         <v>751</v>
       </c>
       <c r="AEE11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="AEF11">
         <v>10</v>
@@ -11329,7 +11746,7 @@
         <v>708</v>
       </c>
       <c r="C12" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D12" t="s">
         <v>589</v>
@@ -11338,7 +11755,7 @@
         <v>711</v>
       </c>
       <c r="N12" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -11368,7 +11785,7 @@
         <v>713</v>
       </c>
       <c r="Y12" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="AG12" t="s">
         <v>715</v>
@@ -11401,7 +11818,7 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AR12" t="s">
         <v>722</v>
@@ -11437,13 +11854,13 @@
         <v>0</v>
       </c>
       <c r="BD12" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="BE12" t="s">
         <v>718</v>
       </c>
       <c r="BG12" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="BH12">
         <v>0</v>
@@ -11473,13 +11890,13 @@
         <v>0</v>
       </c>
       <c r="BQ12" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="BR12" t="s">
         <v>718</v>
       </c>
       <c r="BT12" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="BU12">
         <v>0</v>
@@ -11509,13 +11926,13 @@
         <v>1</v>
       </c>
       <c r="CD12" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="CE12" t="s">
         <v>722</v>
       </c>
       <c r="CG12" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="CH12">
         <v>0</v>
@@ -11545,13 +11962,13 @@
         <v>0</v>
       </c>
       <c r="CQ12" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="CR12" t="s">
         <v>718</v>
       </c>
       <c r="CT12" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="CU12">
         <v>1</v>
@@ -11581,13 +11998,13 @@
         <v>1</v>
       </c>
       <c r="DD12" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="DE12" t="s">
         <v>718</v>
       </c>
       <c r="DF12" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="DG12">
         <v>1</v>
@@ -11629,7 +12046,7 @@
         <v>40</v>
       </c>
       <c r="TH12" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="TK12" t="s">
         <v>710</v>
@@ -11638,7 +12055,7 @@
         <v>886644705</v>
       </c>
       <c r="ADY12" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="ADZ12" s="1">
         <v>46301.235891203702</v>
@@ -11647,10 +12064,10 @@
         <v>736</v>
       </c>
       <c r="AED12" t="s">
+        <v>965</v>
+      </c>
+      <c r="AEE12" t="s">
         <v>966</v>
-      </c>
-      <c r="AEE12" t="s">
-        <v>967</v>
       </c>
       <c r="AEF12">
         <v>11</v>
@@ -11664,7 +12081,7 @@
         <v>708</v>
       </c>
       <c r="C13" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D13" t="s">
         <v>589</v>
@@ -11673,10 +12090,10 @@
         <v>754</v>
       </c>
       <c r="N13" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="EN13" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="EO13">
         <v>676</v>
@@ -11694,7 +12111,7 @@
         <v>19</v>
       </c>
       <c r="FB13" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FC13">
         <v>1</v>
@@ -11709,7 +12126,7 @@
         <v>713</v>
       </c>
       <c r="FG13" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="FH13" t="s">
         <v>713</v>
@@ -11736,13 +12153,13 @@
         <v>33</v>
       </c>
       <c r="TH13" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="TK13" t="s">
         <v>710</v>
       </c>
       <c r="ABN13" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="ABO13">
         <v>0</v>
@@ -11787,7 +12204,7 @@
         <v>886659275</v>
       </c>
       <c r="ADY13" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="ADZ13" s="1">
         <v>46301.252986111111</v>
@@ -11796,10 +12213,10 @@
         <v>736</v>
       </c>
       <c r="AED13" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE13" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="AEF13">
         <v>12</v>
@@ -11822,7 +12239,7 @@
         <v>740</v>
       </c>
       <c r="H14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="RV14" t="s">
         <v>742</v>
@@ -11834,7 +12251,7 @@
         <v>0</v>
       </c>
       <c r="RY14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="RZ14">
         <v>26</v>
@@ -11843,16 +12260,16 @@
         <v>34</v>
       </c>
       <c r="SB14" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="SC14" s="1">
         <v>46301</v>
       </c>
       <c r="SD14" t="s">
+        <v>989</v>
+      </c>
+      <c r="SE14" t="s">
         <v>990</v>
-      </c>
-      <c r="SE14" t="s">
-        <v>991</v>
       </c>
       <c r="SF14">
         <v>51</v>
@@ -11867,28 +12284,28 @@
         <v>0</v>
       </c>
       <c r="SJ14" t="s">
+        <v>991</v>
+      </c>
+      <c r="SK14">
+        <v>0</v>
+      </c>
+      <c r="SL14">
+        <v>1</v>
+      </c>
+      <c r="SM14">
+        <v>1</v>
+      </c>
+      <c r="SN14">
+        <v>1</v>
+      </c>
+      <c r="SO14">
+        <v>1</v>
+      </c>
+      <c r="SP14" t="s">
         <v>992</v>
       </c>
-      <c r="SK14">
-        <v>0</v>
-      </c>
-      <c r="SL14">
-        <v>1</v>
-      </c>
-      <c r="SM14">
-        <v>1</v>
-      </c>
-      <c r="SN14">
-        <v>1</v>
-      </c>
-      <c r="SO14">
-        <v>1</v>
-      </c>
-      <c r="SP14" t="s">
+      <c r="TH14" t="s">
         <v>993</v>
-      </c>
-      <c r="TH14" t="s">
-        <v>994</v>
       </c>
       <c r="TK14" t="s">
         <v>710</v>
@@ -11897,7 +12314,7 @@
         <v>886820155</v>
       </c>
       <c r="ADY14" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="ADZ14" s="1">
         <v>46301.379594907397</v>
@@ -11909,7 +12326,7 @@
         <v>751</v>
       </c>
       <c r="AEE14" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="AEF14">
         <v>13</v>
@@ -11944,7 +12361,7 @@
         <v>0</v>
       </c>
       <c r="RY15" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="RZ15">
         <v>30</v>
@@ -11953,16 +12370,16 @@
         <v>30</v>
       </c>
       <c r="SB15" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="SC15" s="1">
         <v>46301</v>
       </c>
       <c r="SD15" t="s">
+        <v>1047</v>
+      </c>
+      <c r="SE15" t="s">
         <v>1048</v>
-      </c>
-      <c r="SE15" t="s">
-        <v>1049</v>
       </c>
       <c r="SF15">
         <v>112</v>
@@ -11977,7 +12394,7 @@
         <v>0</v>
       </c>
       <c r="SJ15" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="SK15">
         <v>0</v>
@@ -11995,16 +12412,16 @@
         <v>1</v>
       </c>
       <c r="SP15" t="s">
+        <v>1049</v>
+      </c>
+      <c r="TH15" t="s">
         <v>1050</v>
-      </c>
-      <c r="TH15" t="s">
-        <v>1051</v>
       </c>
       <c r="ADX15">
         <v>886940645</v>
       </c>
       <c r="ADY15" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="ADZ15" s="1">
         <v>46301.473958333343</v>
@@ -12013,10 +12430,10 @@
         <v>736</v>
       </c>
       <c r="AED15" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AEE15" t="s">
         <v>1053</v>
-      </c>
-      <c r="AEE15" t="s">
-        <v>1054</v>
       </c>
       <c r="AEF15">
         <v>14</v>
@@ -12030,7 +12447,7 @@
         <v>708</v>
       </c>
       <c r="C16" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D16" t="s">
         <v>596</v>
@@ -12039,7 +12456,7 @@
         <v>711</v>
       </c>
       <c r="K16" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P16">
         <v>10</v>
@@ -12069,7 +12486,7 @@
         <v>713</v>
       </c>
       <c r="Y16" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="AG16" t="s">
         <v>813</v>
@@ -12102,7 +12519,7 @@
         <v>1</v>
       </c>
       <c r="AQ16" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AR16" t="s">
         <v>718</v>
@@ -12138,7 +12555,7 @@
         <v>1</v>
       </c>
       <c r="BD16" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="BE16" t="s">
         <v>718</v>
@@ -12174,7 +12591,7 @@
         <v>1</v>
       </c>
       <c r="BQ16" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="BR16" t="s">
         <v>718</v>
@@ -12210,13 +12627,13 @@
         <v>1</v>
       </c>
       <c r="CD16" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="CE16" t="s">
         <v>722</v>
       </c>
       <c r="CG16" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="CH16">
         <v>1</v>
@@ -12246,7 +12663,7 @@
         <v>1</v>
       </c>
       <c r="CQ16" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="CR16" t="s">
         <v>718</v>
@@ -12282,13 +12699,13 @@
         <v>1</v>
       </c>
       <c r="DD16" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="DE16" t="s">
         <v>722</v>
       </c>
       <c r="DF16" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="DG16">
         <v>0</v>
@@ -12330,13 +12747,13 @@
         <v>0</v>
       </c>
       <c r="TH16" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="ADX16">
         <v>887139498</v>
       </c>
       <c r="ADY16" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="ADZ16" s="1">
         <v>46301.599861111114</v>
@@ -12345,10 +12762,10 @@
         <v>736</v>
       </c>
       <c r="AED16" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AEE16" t="s">
         <v>1081</v>
-      </c>
-      <c r="AEE16" t="s">
-        <v>1082</v>
       </c>
       <c r="AEF16">
         <v>15</v>
@@ -12371,7 +12788,7 @@
         <v>740</v>
       </c>
       <c r="H17" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="RV17" t="s">
         <v>742</v>
@@ -12383,7 +12800,7 @@
         <v>0</v>
       </c>
       <c r="RY17" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="RZ17">
         <v>24</v>
@@ -12392,16 +12809,16 @@
         <v>36</v>
       </c>
       <c r="SB17" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="SC17" s="1">
         <v>46301</v>
       </c>
       <c r="SD17" t="s">
+        <v>1085</v>
+      </c>
+      <c r="SE17" t="s">
         <v>1086</v>
-      </c>
-      <c r="SE17" t="s">
-        <v>1087</v>
       </c>
       <c r="SF17">
         <v>63</v>
@@ -12416,34 +12833,34 @@
         <v>0</v>
       </c>
       <c r="SJ17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="SK17">
+        <v>1</v>
+      </c>
+      <c r="SL17">
+        <v>1</v>
+      </c>
+      <c r="SM17">
+        <v>1</v>
+      </c>
+      <c r="SN17">
+        <v>1</v>
+      </c>
+      <c r="SO17">
+        <v>1</v>
+      </c>
+      <c r="SP17" t="s">
         <v>1088</v>
       </c>
-      <c r="SK17">
-        <v>1</v>
-      </c>
-      <c r="SL17">
-        <v>1</v>
-      </c>
-      <c r="SM17">
-        <v>1</v>
-      </c>
-      <c r="SN17">
-        <v>1</v>
-      </c>
-      <c r="SO17">
-        <v>1</v>
-      </c>
-      <c r="SP17" t="s">
+      <c r="TH17" t="s">
         <v>1089</v>
-      </c>
-      <c r="TH17" t="s">
-        <v>1090</v>
       </c>
       <c r="ADX17">
         <v>887285852</v>
       </c>
       <c r="ADY17" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="ADZ17" s="1">
         <v>46301.698564814818</v>
@@ -12452,10 +12869,10 @@
         <v>736</v>
       </c>
       <c r="AED17" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AEE17" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="AEF17">
         <v>16</v>
@@ -12478,7 +12895,7 @@
         <v>740</v>
       </c>
       <c r="I18" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="RV18" t="s">
         <v>742</v>
@@ -12490,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="RY18" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="RZ18">
         <v>2</v>
@@ -12499,16 +12916,16 @@
         <v>1</v>
       </c>
       <c r="SB18" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="SC18" s="1">
         <v>46301</v>
       </c>
       <c r="SD18" t="s">
+        <v>1095</v>
+      </c>
+      <c r="SE18" t="s">
         <v>1096</v>
-      </c>
-      <c r="SE18" t="s">
-        <v>1097</v>
       </c>
       <c r="SF18">
         <v>31</v>
@@ -12541,10 +12958,10 @@
         <v>0</v>
       </c>
       <c r="SP18" t="s">
+        <v>1097</v>
+      </c>
+      <c r="TH18" t="s">
         <v>1098</v>
-      </c>
-      <c r="TH18" t="s">
-        <v>1099</v>
       </c>
       <c r="TK18" t="s">
         <v>710</v>
@@ -12553,7 +12970,7 @@
         <v>887314303</v>
       </c>
       <c r="ADY18" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="ADZ18" s="1">
         <v>46301.718159722222</v>
@@ -12562,10 +12979,10 @@
         <v>736</v>
       </c>
       <c r="AED18" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE18" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="AEF18">
         <v>17</v>
@@ -12588,7 +13005,7 @@
         <v>740</v>
       </c>
       <c r="I19" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="RV19" t="s">
         <v>742</v>
@@ -12600,7 +13017,7 @@
         <v>0</v>
       </c>
       <c r="RY19" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="RZ19">
         <v>2</v>
@@ -12609,16 +13026,16 @@
         <v>2</v>
       </c>
       <c r="SB19" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="SC19" s="1">
         <v>46301</v>
       </c>
       <c r="SD19" t="s">
+        <v>1104</v>
+      </c>
+      <c r="SE19" t="s">
         <v>1105</v>
-      </c>
-      <c r="SE19" t="s">
-        <v>1106</v>
       </c>
       <c r="SF19">
         <v>39</v>
@@ -12651,16 +13068,16 @@
         <v>0</v>
       </c>
       <c r="SP19" t="s">
+        <v>1106</v>
+      </c>
+      <c r="TH19" t="s">
         <v>1107</v>
-      </c>
-      <c r="TH19" t="s">
-        <v>1108</v>
       </c>
       <c r="ADX19">
         <v>887319690</v>
       </c>
       <c r="ADY19" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="ADZ19" s="1">
         <v>46301.722268518519</v>
@@ -12669,10 +13086,10 @@
         <v>736</v>
       </c>
       <c r="AED19" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AEE19" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="AEF19">
         <v>18</v>
@@ -12695,7 +13112,7 @@
         <v>740</v>
       </c>
       <c r="H20" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="RV20" t="s">
         <v>742</v>
@@ -12707,7 +13124,7 @@
         <v>0</v>
       </c>
       <c r="RY20" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="RZ20">
         <v>30</v>
@@ -12716,16 +13133,16 @@
         <v>30</v>
       </c>
       <c r="SB20" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="SC20" s="1">
         <v>46302</v>
       </c>
       <c r="SD20" t="s">
+        <v>1112</v>
+      </c>
+      <c r="SE20" t="s">
         <v>1113</v>
-      </c>
-      <c r="SE20" t="s">
-        <v>1114</v>
       </c>
       <c r="SF20">
         <v>81</v>
@@ -12740,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="SJ20" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="SK20">
         <v>0</v>
@@ -12758,16 +13175,16 @@
         <v>1</v>
       </c>
       <c r="SP20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="TH20" t="s">
         <v>1115</v>
-      </c>
-      <c r="TH20" t="s">
-        <v>1116</v>
       </c>
       <c r="ADX20">
         <v>887710163</v>
       </c>
       <c r="ADY20" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="ADZ20" s="1">
         <v>46302.307881944442</v>
@@ -12776,10 +13193,10 @@
         <v>736</v>
       </c>
       <c r="AED20" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AEE20" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AEF20">
         <v>19</v>
@@ -12802,10 +13219,10 @@
         <v>754</v>
       </c>
       <c r="G21" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="EN21" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="EO21">
         <v>922</v>
@@ -12823,7 +13240,7 @@
         <v>26</v>
       </c>
       <c r="FB21" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="FC21">
         <v>0</v>
@@ -12838,7 +13255,7 @@
         <v>713</v>
       </c>
       <c r="FG21" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="FH21" t="s">
         <v>734</v>
@@ -12862,13 +13279,13 @@
         <v>85</v>
       </c>
       <c r="TH21" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="TK21" t="s">
         <v>710</v>
       </c>
       <c r="ABN21" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="ABO21">
         <v>1</v>
@@ -12913,7 +13330,7 @@
         <v>887751145</v>
       </c>
       <c r="ADY21" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="ADZ21" s="1">
         <v>46302.341898148137</v>
@@ -12922,10 +13339,10 @@
         <v>736</v>
       </c>
       <c r="AED21" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE21" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="AEF21">
         <v>20</v>
@@ -12948,7 +13365,7 @@
         <v>740</v>
       </c>
       <c r="H22" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="RV22" t="s">
         <v>742</v>
@@ -12960,7 +13377,7 @@
         <v>0</v>
       </c>
       <c r="RY22" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="RZ22">
         <v>25</v>
@@ -12969,16 +13386,16 @@
         <v>30</v>
       </c>
       <c r="SB22" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="SC22" s="1">
         <v>46302</v>
       </c>
       <c r="SD22" t="s">
+        <v>1130</v>
+      </c>
+      <c r="SE22" t="s">
         <v>1131</v>
-      </c>
-      <c r="SE22" t="s">
-        <v>1132</v>
       </c>
       <c r="SF22">
         <v>71</v>
@@ -12993,7 +13410,7 @@
         <v>0</v>
       </c>
       <c r="SJ22" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="SK22">
         <v>0</v>
@@ -13011,16 +13428,16 @@
         <v>1</v>
       </c>
       <c r="SP22" t="s">
+        <v>1132</v>
+      </c>
+      <c r="TH22" t="s">
         <v>1133</v>
-      </c>
-      <c r="TH22" t="s">
-        <v>1134</v>
       </c>
       <c r="ADX22">
         <v>887875691</v>
       </c>
       <c r="ADY22" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="ADZ22" s="1">
         <v>46302.434293981481</v>
@@ -13029,10 +13446,10 @@
         <v>736</v>
       </c>
       <c r="AED22" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE22" t="s">
         <v>1136</v>
-      </c>
-      <c r="AEE22" t="s">
-        <v>1137</v>
       </c>
       <c r="AEF22">
         <v>21</v>
@@ -13046,7 +13463,7 @@
         <v>708</v>
       </c>
       <c r="C23" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D23" t="s">
         <v>594</v>
@@ -13055,7 +13472,7 @@
         <v>740</v>
       </c>
       <c r="I23" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="RV23" t="s">
         <v>742</v>
@@ -13067,7 +13484,7 @@
         <v>0</v>
       </c>
       <c r="RY23" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="RZ23">
         <v>5</v>
@@ -13076,16 +13493,16 @@
         <v>23</v>
       </c>
       <c r="SB23" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="SC23" s="1">
         <v>46301</v>
       </c>
       <c r="SD23" t="s">
+        <v>1141</v>
+      </c>
+      <c r="SE23" t="s">
         <v>1142</v>
-      </c>
-      <c r="SE23" t="s">
-        <v>1143</v>
       </c>
       <c r="SF23">
         <v>5</v>
@@ -13118,16 +13535,16 @@
         <v>0</v>
       </c>
       <c r="SP23" t="s">
+        <v>1143</v>
+      </c>
+      <c r="TH23" t="s">
         <v>1144</v>
-      </c>
-      <c r="TH23" t="s">
-        <v>1145</v>
       </c>
       <c r="ADX23">
         <v>887914294</v>
       </c>
       <c r="ADY23" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="ADZ23" s="1">
         <v>46302.464733796303</v>
@@ -13136,10 +13553,10 @@
         <v>736</v>
       </c>
       <c r="AED23" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AEE23" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AEF23">
         <v>22</v>
@@ -13162,10 +13579,10 @@
         <v>754</v>
       </c>
       <c r="J24" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="EN24" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="EO24">
         <v>321</v>
@@ -13177,7 +13594,7 @@
         <v>713</v>
       </c>
       <c r="ER24" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="ES24">
         <v>0</v>
@@ -13204,7 +13621,7 @@
         <v>30</v>
       </c>
       <c r="FB24" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="FC24">
         <v>0</v>
@@ -13240,13 +13657,13 @@
         <v>27</v>
       </c>
       <c r="TH24" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="ADX24">
         <v>887959840</v>
       </c>
       <c r="ADY24" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="ADZ24" s="1">
         <v>46302.49622685185</v>
@@ -13255,10 +13672,10 @@
         <v>736</v>
       </c>
       <c r="AED24" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AEE24" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="AEF24">
         <v>23</v>
@@ -13272,7 +13689,7 @@
         <v>708</v>
       </c>
       <c r="C25" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D25" t="s">
         <v>589</v>
@@ -13281,7 +13698,7 @@
         <v>754</v>
       </c>
       <c r="N25" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="EN25" t="s">
         <v>756</v>
@@ -13347,7 +13764,7 @@
         <v>0</v>
       </c>
       <c r="GO25" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="GP25">
         <v>1</v>
@@ -13377,7 +13794,7 @@
         <v>713</v>
       </c>
       <c r="HJ25" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="HQ25" t="s">
         <v>768</v>
@@ -13386,7 +13803,7 @@
         <v>2</v>
       </c>
       <c r="HS25" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="HU25" t="s">
         <v>768</v>
@@ -13395,7 +13812,7 @@
         <v>2</v>
       </c>
       <c r="HW25" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="HY25" t="s">
         <v>768</v>
@@ -13404,7 +13821,7 @@
         <v>2</v>
       </c>
       <c r="IA25" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="IC25" t="s">
         <v>768</v>
@@ -13413,7 +13830,7 @@
         <v>2</v>
       </c>
       <c r="IE25" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="IG25" t="s">
         <v>768</v>
@@ -13422,7 +13839,7 @@
         <v>2</v>
       </c>
       <c r="II25" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="IS25" t="s">
         <v>837</v>
@@ -13431,13 +13848,13 @@
         <v>771</v>
       </c>
       <c r="IU25" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="IV25" t="s">
         <v>838</v>
       </c>
       <c r="IW25" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="IX25" t="s">
         <v>718</v>
@@ -13449,13 +13866,13 @@
         <v>771</v>
       </c>
       <c r="JB25" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="JC25" t="s">
         <v>838</v>
       </c>
       <c r="JD25" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="JE25" t="s">
         <v>722</v>
@@ -13467,13 +13884,13 @@
         <v>771</v>
       </c>
       <c r="JI25" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="JJ25" t="s">
         <v>838</v>
       </c>
       <c r="JK25" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="JL25" t="s">
         <v>718</v>
@@ -13485,13 +13902,13 @@
         <v>771</v>
       </c>
       <c r="JP25" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="JQ25" t="s">
         <v>838</v>
       </c>
       <c r="JR25" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="JS25" t="s">
         <v>722</v>
@@ -13503,13 +13920,13 @@
         <v>771</v>
       </c>
       <c r="JW25" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="JX25" t="s">
         <v>838</v>
       </c>
       <c r="JY25" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="JZ25" t="s">
         <v>718</v>
@@ -13521,40 +13938,40 @@
         <v>771</v>
       </c>
       <c r="KD25" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="KE25" t="s">
         <v>838</v>
       </c>
       <c r="KF25" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="KG25" t="s">
         <v>722</v>
       </c>
       <c r="KH25" t="s">
+        <v>1172</v>
+      </c>
+      <c r="KI25">
+        <v>0</v>
+      </c>
+      <c r="KJ25">
+        <v>1</v>
+      </c>
+      <c r="KK25">
+        <v>0</v>
+      </c>
+      <c r="KL25">
+        <v>1</v>
+      </c>
+      <c r="KN25" t="s">
         <v>1173</v>
       </c>
-      <c r="KI25">
-        <v>0</v>
-      </c>
-      <c r="KJ25">
-        <v>1</v>
-      </c>
-      <c r="KK25">
-        <v>0</v>
-      </c>
-      <c r="KL25">
-        <v>1</v>
-      </c>
-      <c r="KN25" t="s">
+      <c r="KO25" t="s">
+        <v>1173</v>
+      </c>
+      <c r="KQ25" t="s">
         <v>1174</v>
-      </c>
-      <c r="KO25" t="s">
-        <v>1174</v>
-      </c>
-      <c r="KQ25" t="s">
-        <v>1175</v>
       </c>
       <c r="NL25">
         <v>62</v>
@@ -13575,7 +13992,7 @@
         <v>50</v>
       </c>
       <c r="TH25" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="TK25" t="s">
         <v>710</v>
@@ -13587,7 +14004,7 @@
         <v>734</v>
       </c>
       <c r="ADG25" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="ADL25">
         <v>65</v>
@@ -13611,7 +14028,7 @@
         <v>887974567</v>
       </c>
       <c r="ADY25" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="ADZ25" s="1">
         <v>46302.506296296298</v>
@@ -13620,10 +14037,10 @@
         <v>736</v>
       </c>
       <c r="AED25" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="AEF25">
         <v>24</v>
@@ -13637,7 +14054,7 @@
         <v>708</v>
       </c>
       <c r="C26" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D26" t="s">
         <v>589</v>
@@ -13646,7 +14063,7 @@
         <v>754</v>
       </c>
       <c r="N26" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="EN26" t="s">
         <v>756</v>
@@ -13712,7 +14129,7 @@
         <v>0</v>
       </c>
       <c r="GO26" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="GP26">
         <v>1</v>
@@ -13742,7 +14159,7 @@
         <v>713</v>
       </c>
       <c r="HJ26" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="HQ26" t="s">
         <v>768</v>
@@ -13751,7 +14168,7 @@
         <v>2</v>
       </c>
       <c r="HS26" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="HU26" t="s">
         <v>768</v>
@@ -13760,7 +14177,7 @@
         <v>4</v>
       </c>
       <c r="HW26" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="HY26" t="s">
         <v>768</v>
@@ -13769,7 +14186,7 @@
         <v>2</v>
       </c>
       <c r="IA26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="IC26" t="s">
         <v>768</v>
@@ -13778,7 +14195,7 @@
         <v>1</v>
       </c>
       <c r="IE26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="IG26" t="s">
         <v>768</v>
@@ -13787,7 +14204,7 @@
         <v>2</v>
       </c>
       <c r="II26" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="IS26" t="s">
         <v>837</v>
@@ -13796,13 +14213,13 @@
         <v>771</v>
       </c>
       <c r="IU26" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="IV26" t="s">
         <v>838</v>
       </c>
       <c r="IW26" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="IX26" t="s">
         <v>722</v>
@@ -13814,13 +14231,13 @@
         <v>771</v>
       </c>
       <c r="JB26" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="JC26" t="s">
         <v>838</v>
       </c>
       <c r="JD26" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="JE26" t="s">
         <v>718</v>
@@ -13832,13 +14249,13 @@
         <v>771</v>
       </c>
       <c r="JI26" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="JJ26" t="s">
         <v>838</v>
       </c>
       <c r="JK26" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="JL26" t="s">
         <v>718</v>
@@ -13850,13 +14267,13 @@
         <v>771</v>
       </c>
       <c r="JP26" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="JQ26" t="s">
         <v>838</v>
       </c>
       <c r="JR26" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="JS26" t="s">
         <v>722</v>
@@ -13865,16 +14282,16 @@
         <v>837</v>
       </c>
       <c r="JV26" t="s">
+        <v>1193</v>
+      </c>
+      <c r="JW26" t="s">
         <v>1194</v>
-      </c>
-      <c r="JW26" t="s">
-        <v>1195</v>
       </c>
       <c r="JX26" t="s">
         <v>838</v>
       </c>
       <c r="JY26" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="JZ26" t="s">
         <v>718</v>
@@ -13886,40 +14303,40 @@
         <v>771</v>
       </c>
       <c r="KD26" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="KE26" t="s">
         <v>838</v>
       </c>
       <c r="KF26" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="KG26" t="s">
         <v>718</v>
       </c>
       <c r="KH26" t="s">
+        <v>1198</v>
+      </c>
+      <c r="KI26">
+        <v>0</v>
+      </c>
+      <c r="KJ26">
+        <v>0</v>
+      </c>
+      <c r="KK26">
+        <v>1</v>
+      </c>
+      <c r="KL26">
+        <v>0</v>
+      </c>
+      <c r="KN26" t="s">
         <v>1199</v>
       </c>
-      <c r="KI26">
-        <v>0</v>
-      </c>
-      <c r="KJ26">
-        <v>0</v>
-      </c>
-      <c r="KK26">
-        <v>1</v>
-      </c>
-      <c r="KL26">
-        <v>0</v>
-      </c>
-      <c r="KN26" t="s">
+      <c r="KO26" t="s">
         <v>1200</v>
       </c>
-      <c r="KO26" t="s">
+      <c r="KQ26" t="s">
         <v>1201</v>
-      </c>
-      <c r="KQ26" t="s">
-        <v>1202</v>
       </c>
       <c r="NL26">
         <v>319</v>
@@ -13940,7 +14357,7 @@
         <v>67</v>
       </c>
       <c r="TH26" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="TK26" t="s">
         <v>710</v>
@@ -13952,7 +14369,7 @@
         <v>734</v>
       </c>
       <c r="ADG26" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="ADL26">
         <v>319</v>
@@ -13976,7 +14393,7 @@
         <v>887974580</v>
       </c>
       <c r="ADY26" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="ADZ26" s="1">
         <v>46302.506296296298</v>
@@ -13985,10 +14402,10 @@
         <v>736</v>
       </c>
       <c r="AED26" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE26" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="AEF26">
         <v>25</v>
@@ -14002,7 +14419,7 @@
         <v>708</v>
       </c>
       <c r="C27" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D27" t="s">
         <v>589</v>
@@ -14011,10 +14428,10 @@
         <v>754</v>
       </c>
       <c r="N27" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="EN27" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="EO27">
         <v>559</v>
@@ -14032,7 +14449,7 @@
         <v>3</v>
       </c>
       <c r="FB27" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FC27">
         <v>1</v>
@@ -14050,7 +14467,7 @@
         <v>713</v>
       </c>
       <c r="FI27">
-        <v>333</v>
+        <v>33</v>
       </c>
       <c r="NL27">
         <v>319</v>
@@ -14071,13 +14488,13 @@
         <v>84</v>
       </c>
       <c r="TH27" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="TK27" t="s">
         <v>710</v>
       </c>
       <c r="ABN27" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="ABO27">
         <v>0</v>
@@ -14122,7 +14539,7 @@
         <v>887974595</v>
       </c>
       <c r="ADY27" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="ADZ27" s="1">
         <v>46302.506307870368</v>
@@ -14131,10 +14548,10 @@
         <v>736</v>
       </c>
       <c r="AED27" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE27" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="AEF27">
         <v>26</v>
@@ -14148,7 +14565,7 @@
         <v>708</v>
       </c>
       <c r="C28" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D28" t="s">
         <v>589</v>
@@ -14157,7 +14574,7 @@
         <v>711</v>
       </c>
       <c r="N28" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="P28">
         <v>1</v>
@@ -14217,7 +14634,7 @@
         <v>1</v>
       </c>
       <c r="AQ28" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="AR28" t="s">
         <v>718</v>
@@ -14253,7 +14670,7 @@
         <v>1</v>
       </c>
       <c r="BD28" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="BE28" t="s">
         <v>722</v>
@@ -14289,7 +14706,7 @@
         <v>1</v>
       </c>
       <c r="BQ28" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="BR28" t="s">
         <v>722</v>
@@ -14325,7 +14742,7 @@
         <v>1</v>
       </c>
       <c r="CD28" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="CE28" t="s">
         <v>718</v>
@@ -14361,7 +14778,7 @@
         <v>1</v>
       </c>
       <c r="CQ28" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="CR28" t="s">
         <v>722</v>
@@ -14397,13 +14814,13 @@
         <v>1</v>
       </c>
       <c r="DD28" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="DE28" t="s">
         <v>722</v>
       </c>
       <c r="DF28" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="DG28">
         <v>1</v>
@@ -14445,7 +14862,7 @@
         <v>3</v>
       </c>
       <c r="TH28" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="TK28" t="s">
         <v>710</v>
@@ -14454,7 +14871,7 @@
         <v>887974610</v>
       </c>
       <c r="ADY28" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="ADZ28" s="1">
         <v>46302.506307870368</v>
@@ -14463,10 +14880,10 @@
         <v>736</v>
       </c>
       <c r="AED28" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE28" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="AEF28">
         <v>27</v>
@@ -14480,7 +14897,7 @@
         <v>708</v>
       </c>
       <c r="C29" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D29" t="s">
         <v>589</v>
@@ -14489,7 +14906,7 @@
         <v>754</v>
       </c>
       <c r="N29" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="EN29" t="s">
         <v>756</v>
@@ -14555,7 +14972,7 @@
         <v>0</v>
       </c>
       <c r="GO29" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="GP29">
         <v>1</v>
@@ -14585,7 +15002,7 @@
         <v>713</v>
       </c>
       <c r="HJ29" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="HQ29" t="s">
         <v>768</v>
@@ -14594,7 +15011,7 @@
         <v>32</v>
       </c>
       <c r="HS29" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="HU29" t="s">
         <v>768</v>
@@ -14603,7 +15020,7 @@
         <v>83</v>
       </c>
       <c r="HW29" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="HY29" t="s">
         <v>768</v>
@@ -14612,7 +15029,7 @@
         <v>78</v>
       </c>
       <c r="IA29" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="IC29" t="s">
         <v>768</v>
@@ -14621,7 +15038,7 @@
         <v>65</v>
       </c>
       <c r="IE29" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="IG29" t="s">
         <v>768</v>
@@ -14630,7 +15047,7 @@
         <v>89</v>
       </c>
       <c r="II29" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="IS29" t="s">
         <v>837</v>
@@ -14639,13 +15056,13 @@
         <v>771</v>
       </c>
       <c r="IU29" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="IV29" t="s">
         <v>838</v>
       </c>
       <c r="IW29" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="IX29" t="s">
         <v>722</v>
@@ -14657,13 +15074,13 @@
         <v>771</v>
       </c>
       <c r="JB29" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="JC29" t="s">
         <v>838</v>
       </c>
       <c r="JD29" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="JE29" t="s">
         <v>718</v>
@@ -14675,13 +15092,13 @@
         <v>881</v>
       </c>
       <c r="JI29" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="JJ29" t="s">
         <v>838</v>
       </c>
       <c r="JK29" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="JL29" t="s">
         <v>718</v>
@@ -14693,13 +15110,13 @@
         <v>771</v>
       </c>
       <c r="JP29" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="JQ29" t="s">
         <v>838</v>
       </c>
       <c r="JR29" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="JS29" t="s">
         <v>722</v>
@@ -14711,13 +15128,13 @@
         <v>771</v>
       </c>
       <c r="JW29" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="JX29" t="s">
         <v>838</v>
       </c>
       <c r="JY29" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="JZ29" t="s">
         <v>722</v>
@@ -14729,19 +15146,19 @@
         <v>771</v>
       </c>
       <c r="KD29" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="KE29" t="s">
         <v>838</v>
       </c>
       <c r="KF29" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="KG29" t="s">
         <v>718</v>
       </c>
       <c r="KH29" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="KI29">
         <v>0</v>
@@ -14756,13 +15173,13 @@
         <v>0</v>
       </c>
       <c r="KN29" t="s">
+        <v>1239</v>
+      </c>
+      <c r="KO29" t="s">
         <v>1240</v>
       </c>
-      <c r="KO29" t="s">
+      <c r="KQ29" t="s">
         <v>1241</v>
-      </c>
-      <c r="KQ29" t="s">
-        <v>1242</v>
       </c>
       <c r="NL29">
         <v>253</v>
@@ -14783,7 +15200,7 @@
         <v>133</v>
       </c>
       <c r="TH29" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="TK29" t="s">
         <v>710</v>
@@ -14795,7 +15212,7 @@
         <v>713</v>
       </c>
       <c r="ADG29" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="ADL29">
         <v>253</v>
@@ -14819,7 +15236,7 @@
         <v>887974623</v>
       </c>
       <c r="ADY29" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="ADZ29" s="1">
         <v>46302.506319444437</v>
@@ -14828,10 +15245,10 @@
         <v>736</v>
       </c>
       <c r="AED29" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE29" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="AEF29">
         <v>28</v>
@@ -14854,7 +15271,7 @@
         <v>754</v>
       </c>
       <c r="J30" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="EN30" t="s">
         <v>756</v>
@@ -14920,31 +15337,31 @@
         <v>0</v>
       </c>
       <c r="GO30" t="s">
+        <v>1249</v>
+      </c>
+      <c r="GP30">
+        <v>1</v>
+      </c>
+      <c r="GQ30">
+        <v>0</v>
+      </c>
+      <c r="GR30">
+        <v>0</v>
+      </c>
+      <c r="GS30">
+        <v>1</v>
+      </c>
+      <c r="GT30">
+        <v>1</v>
+      </c>
+      <c r="GU30">
+        <v>0</v>
+      </c>
+      <c r="GV30">
+        <v>1</v>
+      </c>
+      <c r="GW30" t="s">
         <v>1250</v>
-      </c>
-      <c r="GP30">
-        <v>1</v>
-      </c>
-      <c r="GQ30">
-        <v>0</v>
-      </c>
-      <c r="GR30">
-        <v>0</v>
-      </c>
-      <c r="GS30">
-        <v>1</v>
-      </c>
-      <c r="GT30">
-        <v>1</v>
-      </c>
-      <c r="GU30">
-        <v>0</v>
-      </c>
-      <c r="GV30">
-        <v>1</v>
-      </c>
-      <c r="GW30" t="s">
-        <v>1251</v>
       </c>
       <c r="GX30">
         <v>0</v>
@@ -14965,7 +15382,7 @@
         <v>713</v>
       </c>
       <c r="HE30" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="HF30" t="s">
         <v>713</v>
@@ -14983,7 +15400,7 @@
         <v>4</v>
       </c>
       <c r="HS30" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="HU30" t="s">
         <v>832</v>
@@ -14992,7 +15409,7 @@
         <v>6</v>
       </c>
       <c r="HW30" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="HY30" t="s">
         <v>768</v>
@@ -15001,7 +15418,7 @@
         <v>11</v>
       </c>
       <c r="IA30" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="IC30" t="s">
         <v>768</v>
@@ -15010,7 +15427,7 @@
         <v>3</v>
       </c>
       <c r="IE30" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="IG30" t="s">
         <v>768</v>
@@ -15019,7 +15436,7 @@
         <v>13</v>
       </c>
       <c r="II30" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="IS30" t="s">
         <v>839</v>
@@ -15028,13 +15445,13 @@
         <v>771</v>
       </c>
       <c r="IU30" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="IV30" t="s">
         <v>841</v>
       </c>
       <c r="IW30" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="IX30" t="s">
         <v>718</v>
@@ -15046,13 +15463,13 @@
         <v>771</v>
       </c>
       <c r="JB30" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="JC30" t="s">
         <v>841</v>
       </c>
       <c r="JD30" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="JE30" t="s">
         <v>718</v>
@@ -15064,13 +15481,13 @@
         <v>881</v>
       </c>
       <c r="JI30" t="s">
+        <v>1261</v>
+      </c>
+      <c r="JJ30" t="s">
         <v>1262</v>
       </c>
-      <c r="JJ30" t="s">
+      <c r="JK30" t="s">
         <v>1263</v>
-      </c>
-      <c r="JK30" t="s">
-        <v>1264</v>
       </c>
       <c r="JL30" t="s">
         <v>722</v>
@@ -15082,13 +15499,13 @@
         <v>771</v>
       </c>
       <c r="JP30" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="JQ30" t="s">
         <v>841</v>
       </c>
       <c r="JR30" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="JS30" t="s">
         <v>722</v>
@@ -15100,13 +15517,13 @@
         <v>771</v>
       </c>
       <c r="JW30" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="JX30" t="s">
         <v>838</v>
       </c>
       <c r="JY30" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="JZ30" t="s">
         <v>722</v>
@@ -15121,7 +15538,7 @@
         <v>890</v>
       </c>
       <c r="KE30" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="KF30" t="s">
         <v>890</v>
@@ -15145,16 +15562,16 @@
         <v>1</v>
       </c>
       <c r="KN30" t="s">
+        <v>1267</v>
+      </c>
+      <c r="KO30" t="s">
         <v>1268</v>
       </c>
-      <c r="KO30" t="s">
+      <c r="KP30" t="s">
         <v>1269</v>
       </c>
-      <c r="KP30" t="s">
+      <c r="KQ30" t="s">
         <v>1270</v>
-      </c>
-      <c r="KQ30" t="s">
-        <v>1271</v>
       </c>
       <c r="NL30">
         <v>194</v>
@@ -15176,7 +15593,7 @@
       </c>
       <c r="SC30" s="1"/>
       <c r="TH30" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="ZK30" s="1"/>
       <c r="ADN30" s="1"/>
@@ -15185,7 +15602,7 @@
         <v>887985732</v>
       </c>
       <c r="ADY30" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="ADZ30" s="1">
         <v>46302.513831018521</v>
@@ -15194,10 +15611,10 @@
         <v>736</v>
       </c>
       <c r="AED30" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AEE30" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="AEF30">
         <v>29</v>
@@ -15211,7 +15628,7 @@
         <v>708</v>
       </c>
       <c r="C31" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D31" t="s">
         <v>589</v>
@@ -15220,7 +15637,7 @@
         <v>711</v>
       </c>
       <c r="N31" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="P31">
         <v>11</v>
@@ -15253,7 +15670,7 @@
         <v>821</v>
       </c>
       <c r="AG31" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="AH31">
         <v>1</v>
@@ -15283,7 +15700,7 @@
         <v>1</v>
       </c>
       <c r="AQ31" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="AR31" t="s">
         <v>722</v>
@@ -15319,13 +15736,13 @@
         <v>1</v>
       </c>
       <c r="BD31" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="BE31" t="s">
         <v>718</v>
       </c>
       <c r="BG31" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="BH31">
         <v>1</v>
@@ -15355,7 +15772,7 @@
         <v>1</v>
       </c>
       <c r="BQ31" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="BR31" t="s">
         <v>718</v>
@@ -15391,7 +15808,7 @@
         <v>0</v>
       </c>
       <c r="CD31" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="CE31" t="s">
         <v>722</v>
@@ -15427,7 +15844,7 @@
         <v>0</v>
       </c>
       <c r="CQ31" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="CR31" t="s">
         <v>718</v>
@@ -15463,13 +15880,13 @@
         <v>1</v>
       </c>
       <c r="DD31" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="DE31" t="s">
         <v>718</v>
       </c>
       <c r="DF31" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="DG31">
         <v>1</v>
@@ -15502,34 +15919,34 @@
         <v>713</v>
       </c>
       <c r="DQ31" t="s">
+        <v>1284</v>
+      </c>
+      <c r="DR31">
+        <v>1</v>
+      </c>
+      <c r="DS31">
+        <v>1</v>
+      </c>
+      <c r="DT31">
+        <v>1</v>
+      </c>
+      <c r="DU31">
+        <v>0</v>
+      </c>
+      <c r="DV31">
+        <v>0</v>
+      </c>
+      <c r="DW31">
+        <v>1</v>
+      </c>
+      <c r="DX31">
+        <v>1</v>
+      </c>
+      <c r="DY31">
+        <v>0</v>
+      </c>
+      <c r="DZ31" t="s">
         <v>1285</v>
-      </c>
-      <c r="DR31">
-        <v>1</v>
-      </c>
-      <c r="DS31">
-        <v>1</v>
-      </c>
-      <c r="DT31">
-        <v>1</v>
-      </c>
-      <c r="DU31">
-        <v>0</v>
-      </c>
-      <c r="DV31">
-        <v>0</v>
-      </c>
-      <c r="DW31">
-        <v>1</v>
-      </c>
-      <c r="DX31">
-        <v>1</v>
-      </c>
-      <c r="DY31">
-        <v>0</v>
-      </c>
-      <c r="DZ31" t="s">
-        <v>1286</v>
       </c>
       <c r="EA31">
         <v>1</v>
@@ -15554,7 +15971,7 @@
       </c>
       <c r="SC31" s="1"/>
       <c r="TH31" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="TK31" t="s">
         <v>710</v>
@@ -15566,7 +15983,7 @@
         <v>887990407</v>
       </c>
       <c r="ADY31" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="ADZ31" s="1">
         <v>46302.516724537039</v>
@@ -15575,10 +15992,10 @@
         <v>736</v>
       </c>
       <c r="AED31" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE31" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="AEF31">
         <v>30</v>
@@ -15601,10 +16018,10 @@
         <v>754</v>
       </c>
       <c r="J32" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="EN32" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="EO32">
         <v>430</v>
@@ -15616,7 +16033,7 @@
         <v>713</v>
       </c>
       <c r="ER32" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="ES32">
         <v>0</v>
@@ -15643,7 +16060,7 @@
         <v>30</v>
       </c>
       <c r="FB32" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="FC32">
         <v>0</v>
@@ -15680,7 +16097,7 @@
       </c>
       <c r="SC32" s="1"/>
       <c r="TH32" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="ZK32" s="1"/>
       <c r="ADN32" s="1"/>
@@ -15689,7 +16106,7 @@
         <v>887992049</v>
       </c>
       <c r="ADY32" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="ADZ32" s="1">
         <v>46302.517812500002</v>
@@ -15698,10 +16115,10 @@
         <v>736</v>
       </c>
       <c r="AED32" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AEE32" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="AEF32">
         <v>31</v>
@@ -15724,7 +16141,7 @@
         <v>754</v>
       </c>
       <c r="J33" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="EN33" t="s">
         <v>756</v>
@@ -15814,7 +16231,7 @@
         <v>1</v>
       </c>
       <c r="GW33" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="GX33">
         <v>1</v>
@@ -15832,7 +16249,7 @@
         <v>0</v>
       </c>
       <c r="HD33" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="HF33" t="s">
         <v>713</v>
@@ -15844,7 +16261,7 @@
         <v>713</v>
       </c>
       <c r="HJ33" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="HQ33" t="s">
         <v>768</v>
@@ -15853,7 +16270,7 @@
         <v>8</v>
       </c>
       <c r="HS33" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="HU33" t="s">
         <v>768</v>
@@ -15862,7 +16279,7 @@
         <v>10</v>
       </c>
       <c r="HW33" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="HY33" t="s">
         <v>832</v>
@@ -15871,7 +16288,7 @@
         <v>4</v>
       </c>
       <c r="IA33" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="IC33" t="s">
         <v>835</v>
@@ -15880,7 +16297,7 @@
         <v>2</v>
       </c>
       <c r="IE33" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="IG33" t="s">
         <v>832</v>
@@ -15889,7 +16306,7 @@
         <v>5</v>
       </c>
       <c r="II33" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="IS33" t="s">
         <v>839</v>
@@ -15898,13 +16315,13 @@
         <v>771</v>
       </c>
       <c r="IU33" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="IV33" t="s">
         <v>841</v>
       </c>
       <c r="IW33" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="IX33" t="s">
         <v>722</v>
@@ -15916,13 +16333,13 @@
         <v>881</v>
       </c>
       <c r="JB33" t="s">
+        <v>1302</v>
+      </c>
+      <c r="JC33" t="s">
+        <v>1262</v>
+      </c>
+      <c r="JD33" t="s">
         <v>1303</v>
-      </c>
-      <c r="JC33" t="s">
-        <v>1263</v>
-      </c>
-      <c r="JD33" t="s">
-        <v>1304</v>
       </c>
       <c r="JE33" t="s">
         <v>722</v>
@@ -15934,13 +16351,13 @@
         <v>771</v>
       </c>
       <c r="JI33" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="JJ33" t="s">
         <v>838</v>
       </c>
       <c r="JK33" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="JL33" t="s">
         <v>718</v>
@@ -15952,13 +16369,13 @@
         <v>881</v>
       </c>
       <c r="JP33" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="JQ33" t="s">
         <v>841</v>
       </c>
       <c r="JR33" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="JS33" t="s">
         <v>718</v>
@@ -15970,13 +16387,13 @@
         <v>771</v>
       </c>
       <c r="JW33" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="JX33" t="s">
         <v>838</v>
       </c>
       <c r="JY33" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="JZ33" t="s">
         <v>718</v>
@@ -15985,16 +16402,16 @@
         <v>770</v>
       </c>
       <c r="KC33" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="KD33" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="KE33" t="s">
         <v>841</v>
       </c>
       <c r="KF33" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="KG33" t="s">
         <v>722</v>
@@ -16015,16 +16432,16 @@
         <v>1</v>
       </c>
       <c r="KN33" t="s">
+        <v>1312</v>
+      </c>
+      <c r="KO33" t="s">
         <v>1313</v>
       </c>
-      <c r="KO33" t="s">
+      <c r="KP33" t="s">
         <v>1314</v>
       </c>
-      <c r="KP33" t="s">
+      <c r="KQ33" t="s">
         <v>1315</v>
-      </c>
-      <c r="KQ33" t="s">
-        <v>1316</v>
       </c>
       <c r="NL33">
         <v>124</v>
@@ -16046,7 +16463,7 @@
       </c>
       <c r="SC33" s="1"/>
       <c r="TH33" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="ZK33" s="1"/>
       <c r="ADN33" s="1"/>
@@ -16055,7 +16472,7 @@
         <v>888012107</v>
       </c>
       <c r="ADY33" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="ADZ33" s="1">
         <v>46302.531006944453</v>
@@ -16064,10 +16481,10 @@
         <v>736</v>
       </c>
       <c r="AED33" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AEE33" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="AEF33">
         <v>32</v>
@@ -16081,7 +16498,7 @@
         <v>708</v>
       </c>
       <c r="C34" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="D34" t="s">
         <v>589</v>
@@ -16090,7 +16507,7 @@
         <v>754</v>
       </c>
       <c r="N34" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="EN34" t="s">
         <v>756</v>
@@ -16156,7 +16573,7 @@
         <v>2</v>
       </c>
       <c r="GO34" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="GP34">
         <v>1</v>
@@ -16180,7 +16597,7 @@
         <v>1</v>
       </c>
       <c r="HC34" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="HF34" t="s">
         <v>713</v>
@@ -16189,7 +16606,7 @@
         <v>713</v>
       </c>
       <c r="HJ34" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="HQ34" t="s">
         <v>768</v>
@@ -16198,7 +16615,7 @@
         <v>34</v>
       </c>
       <c r="HS34" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="HU34" t="s">
         <v>768</v>
@@ -16207,7 +16624,7 @@
         <v>53</v>
       </c>
       <c r="HW34" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="HY34" t="s">
         <v>768</v>
@@ -16216,7 +16633,7 @@
         <v>81</v>
       </c>
       <c r="IA34" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="IC34" t="s">
         <v>768</v>
@@ -16225,7 +16642,7 @@
         <v>62</v>
       </c>
       <c r="IE34" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="IG34" t="s">
         <v>835</v>
@@ -16234,7 +16651,7 @@
         <v>76</v>
       </c>
       <c r="II34" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="IS34" t="s">
         <v>837</v>
@@ -16243,13 +16660,13 @@
         <v>771</v>
       </c>
       <c r="IU34" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="IV34" t="s">
         <v>838</v>
       </c>
       <c r="IW34" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="IX34" t="s">
         <v>718</v>
@@ -16261,13 +16678,13 @@
         <v>771</v>
       </c>
       <c r="JB34" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="JC34" t="s">
         <v>838</v>
       </c>
       <c r="JD34" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="JE34" t="s">
         <v>718</v>
@@ -16279,13 +16696,13 @@
         <v>771</v>
       </c>
       <c r="JI34" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="JJ34" t="s">
         <v>838</v>
       </c>
       <c r="JK34" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="JL34" t="s">
         <v>722</v>
@@ -16297,13 +16714,13 @@
         <v>771</v>
       </c>
       <c r="JP34" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="JQ34" t="s">
         <v>838</v>
       </c>
       <c r="JR34" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="JS34" t="s">
         <v>718</v>
@@ -16312,16 +16729,16 @@
         <v>837</v>
       </c>
       <c r="JV34" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="JW34" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="JX34" t="s">
         <v>838</v>
       </c>
       <c r="JY34" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="JZ34" t="s">
         <v>722</v>
@@ -16333,13 +16750,13 @@
         <v>771</v>
       </c>
       <c r="KD34" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="KE34" t="s">
         <v>838</v>
       </c>
       <c r="KF34" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="KG34" t="s">
         <v>718</v>
@@ -16360,13 +16777,13 @@
         <v>1</v>
       </c>
       <c r="KN34" t="s">
+        <v>1338</v>
+      </c>
+      <c r="KO34" t="s">
         <v>1339</v>
       </c>
-      <c r="KO34" t="s">
-        <v>1340</v>
-      </c>
       <c r="KQ34" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="NL34">
         <v>209</v>
@@ -16388,7 +16805,7 @@
       </c>
       <c r="SC34" s="1"/>
       <c r="TH34" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="TK34" t="s">
         <v>710</v>
@@ -16401,7 +16818,7 @@
         <v>734</v>
       </c>
       <c r="ADG34" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="ADL34">
         <v>209</v>
@@ -16427,7 +16844,7 @@
         <v>888016271</v>
       </c>
       <c r="ADY34" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="ADZ34" s="1">
         <v>46302.533784722233</v>
@@ -16436,10 +16853,10 @@
         <v>736</v>
       </c>
       <c r="AED34" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AEE34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="AEF34">
         <v>33</v>
@@ -16462,10 +16879,10 @@
         <v>754</v>
       </c>
       <c r="J35" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="EN35" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="EO35">
         <v>699</v>
@@ -16477,7 +16894,7 @@
         <v>713</v>
       </c>
       <c r="ER35" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="ES35">
         <v>0</v>
@@ -16504,7 +16921,7 @@
         <v>30</v>
       </c>
       <c r="FB35" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FC35">
         <v>1</v>
@@ -16541,7 +16958,7 @@
       </c>
       <c r="SC35" s="1"/>
       <c r="TH35" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="ZK35" s="1"/>
       <c r="ADN35" s="1"/>
@@ -16550,7 +16967,7 @@
         <v>888043285</v>
       </c>
       <c r="ADY35" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="ADZ35" s="1">
         <v>46302.553067129629</v>
@@ -16559,13 +16976,2371 @@
         <v>736</v>
       </c>
       <c r="AED35" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AEE35" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="AEF35">
         <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:812" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B36" t="s">
+        <v>708</v>
+      </c>
+      <c r="C36" t="s">
+        <v>819</v>
+      </c>
+      <c r="D36" t="s">
+        <v>595</v>
+      </c>
+      <c r="E36" t="s">
+        <v>754</v>
+      </c>
+      <c r="J36" t="s">
+        <v>1342</v>
+      </c>
+      <c r="EN36" t="s">
+        <v>756</v>
+      </c>
+      <c r="FQ36">
+        <v>253</v>
+      </c>
+      <c r="FR36">
+        <v>231</v>
+      </c>
+      <c r="FS36">
+        <v>2</v>
+      </c>
+      <c r="FT36">
+        <v>4</v>
+      </c>
+      <c r="FV36">
+        <v>205</v>
+      </c>
+      <c r="FW36">
+        <v>187</v>
+      </c>
+      <c r="FX36">
+        <v>1</v>
+      </c>
+      <c r="FY36">
+        <v>0</v>
+      </c>
+      <c r="GA36">
+        <v>237</v>
+      </c>
+      <c r="GB36">
+        <v>245</v>
+      </c>
+      <c r="GC36">
+        <v>0</v>
+      </c>
+      <c r="GD36">
+        <v>0</v>
+      </c>
+      <c r="GF36">
+        <v>5</v>
+      </c>
+      <c r="GG36">
+        <v>4</v>
+      </c>
+      <c r="GH36">
+        <v>0</v>
+      </c>
+      <c r="GI36">
+        <v>0</v>
+      </c>
+      <c r="GK36">
+        <v>0</v>
+      </c>
+      <c r="GL36">
+        <v>0</v>
+      </c>
+      <c r="GM36">
+        <v>0</v>
+      </c>
+      <c r="GN36">
+        <v>0</v>
+      </c>
+      <c r="GO36" t="s">
+        <v>1249</v>
+      </c>
+      <c r="GP36">
+        <v>1</v>
+      </c>
+      <c r="GQ36">
+        <v>0</v>
+      </c>
+      <c r="GR36">
+        <v>0</v>
+      </c>
+      <c r="GS36">
+        <v>1</v>
+      </c>
+      <c r="GT36">
+        <v>1</v>
+      </c>
+      <c r="GU36">
+        <v>0</v>
+      </c>
+      <c r="GV36">
+        <v>1</v>
+      </c>
+      <c r="GW36" t="s">
+        <v>1347</v>
+      </c>
+      <c r="GX36">
+        <v>1</v>
+      </c>
+      <c r="GY36">
+        <v>0</v>
+      </c>
+      <c r="GZ36">
+        <v>1</v>
+      </c>
+      <c r="HA36">
+        <v>1</v>
+      </c>
+      <c r="HB36">
+        <v>0</v>
+      </c>
+      <c r="HD36" t="s">
+        <v>713</v>
+      </c>
+      <c r="HE36" t="s">
+        <v>1348</v>
+      </c>
+      <c r="HF36" t="s">
+        <v>713</v>
+      </c>
+      <c r="HG36" t="s">
+        <v>713</v>
+      </c>
+      <c r="HH36" t="s">
+        <v>1349</v>
+      </c>
+      <c r="HI36" t="s">
+        <v>713</v>
+      </c>
+      <c r="HJ36" t="s">
+        <v>1350</v>
+      </c>
+      <c r="HQ36" t="s">
+        <v>768</v>
+      </c>
+      <c r="HR36">
+        <v>4</v>
+      </c>
+      <c r="HS36" t="s">
+        <v>1351</v>
+      </c>
+      <c r="HU36" t="s">
+        <v>832</v>
+      </c>
+      <c r="HV36">
+        <v>2</v>
+      </c>
+      <c r="HW36" t="s">
+        <v>1352</v>
+      </c>
+      <c r="HY36" t="s">
+        <v>832</v>
+      </c>
+      <c r="HZ36">
+        <v>2</v>
+      </c>
+      <c r="IA36" t="s">
+        <v>1353</v>
+      </c>
+      <c r="IC36" t="s">
+        <v>768</v>
+      </c>
+      <c r="ID36">
+        <v>1</v>
+      </c>
+      <c r="IE36" t="s">
+        <v>1354</v>
+      </c>
+      <c r="IG36" t="s">
+        <v>835</v>
+      </c>
+      <c r="IH36">
+        <v>2</v>
+      </c>
+      <c r="II36" t="s">
+        <v>1355</v>
+      </c>
+      <c r="IS36" t="s">
+        <v>839</v>
+      </c>
+      <c r="IT36" t="s">
+        <v>771</v>
+      </c>
+      <c r="IU36" t="s">
+        <v>1356</v>
+      </c>
+      <c r="IV36" t="s">
+        <v>838</v>
+      </c>
+      <c r="IW36" t="s">
+        <v>1357</v>
+      </c>
+      <c r="IX36" t="s">
+        <v>718</v>
+      </c>
+      <c r="IZ36" t="s">
+        <v>837</v>
+      </c>
+      <c r="JA36" t="s">
+        <v>881</v>
+      </c>
+      <c r="JB36" t="s">
+        <v>1358</v>
+      </c>
+      <c r="JC36" t="s">
+        <v>838</v>
+      </c>
+      <c r="JD36" t="s">
+        <v>1311</v>
+      </c>
+      <c r="JE36" t="s">
+        <v>718</v>
+      </c>
+      <c r="JG36" t="s">
+        <v>837</v>
+      </c>
+      <c r="JH36" t="s">
+        <v>1193</v>
+      </c>
+      <c r="JI36" t="s">
+        <v>1359</v>
+      </c>
+      <c r="JJ36" t="s">
+        <v>838</v>
+      </c>
+      <c r="JK36" t="s">
+        <v>1309</v>
+      </c>
+      <c r="JL36" t="s">
+        <v>722</v>
+      </c>
+      <c r="JN36" t="s">
+        <v>770</v>
+      </c>
+      <c r="JO36" t="s">
+        <v>771</v>
+      </c>
+      <c r="JP36" t="s">
+        <v>1360</v>
+      </c>
+      <c r="JQ36" t="s">
+        <v>838</v>
+      </c>
+      <c r="JR36" t="s">
+        <v>1361</v>
+      </c>
+      <c r="JS36" t="s">
+        <v>718</v>
+      </c>
+      <c r="JU36" t="s">
+        <v>770</v>
+      </c>
+      <c r="JV36" t="s">
+        <v>771</v>
+      </c>
+      <c r="JW36" t="s">
+        <v>1362</v>
+      </c>
+      <c r="JX36" t="s">
+        <v>838</v>
+      </c>
+      <c r="JY36" t="s">
+        <v>1303</v>
+      </c>
+      <c r="JZ36" t="s">
+        <v>718</v>
+      </c>
+      <c r="KB36" t="s">
+        <v>837</v>
+      </c>
+      <c r="KC36" t="s">
+        <v>881</v>
+      </c>
+      <c r="KD36" t="s">
+        <v>1363</v>
+      </c>
+      <c r="KE36" t="s">
+        <v>1262</v>
+      </c>
+      <c r="KF36" t="s">
+        <v>1364</v>
+      </c>
+      <c r="KG36" t="s">
+        <v>722</v>
+      </c>
+      <c r="KH36" t="s">
+        <v>708</v>
+      </c>
+      <c r="KI36">
+        <v>0</v>
+      </c>
+      <c r="KJ36">
+        <v>0</v>
+      </c>
+      <c r="KK36">
+        <v>0</v>
+      </c>
+      <c r="KL36">
+        <v>1</v>
+      </c>
+      <c r="KN36" t="s">
+        <v>1365</v>
+      </c>
+      <c r="KO36" t="s">
+        <v>1366</v>
+      </c>
+      <c r="KP36" t="s">
+        <v>1367</v>
+      </c>
+      <c r="KQ36" t="s">
+        <v>1368</v>
+      </c>
+      <c r="NL36">
+        <v>254</v>
+      </c>
+      <c r="NM36">
+        <v>231</v>
+      </c>
+      <c r="NO36">
+        <v>205</v>
+      </c>
+      <c r="NP36">
+        <v>187</v>
+      </c>
+      <c r="NR36">
+        <v>237</v>
+      </c>
+      <c r="NS36">
+        <v>482</v>
+      </c>
+      <c r="SC36" s="1"/>
+      <c r="TH36" t="s">
+        <v>1369</v>
+      </c>
+      <c r="ZK36" s="1"/>
+      <c r="ADN36" s="1"/>
+      <c r="ADV36" s="1"/>
+      <c r="ADX36">
+        <v>888059430</v>
+      </c>
+      <c r="ADY36" t="s">
+        <v>1370</v>
+      </c>
+      <c r="ADZ36" s="1">
+        <v>46302.564606481479</v>
+      </c>
+      <c r="AEB36" t="s">
+        <v>736</v>
+      </c>
+      <c r="AED36" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE36" t="s">
+        <v>1371</v>
+      </c>
+      <c r="AEF36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:812" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B37" t="s">
+        <v>708</v>
+      </c>
+      <c r="C37" t="s">
+        <v>819</v>
+      </c>
+      <c r="D37" t="s">
+        <v>595</v>
+      </c>
+      <c r="E37" t="s">
+        <v>754</v>
+      </c>
+      <c r="J37" t="s">
+        <v>1372</v>
+      </c>
+      <c r="EN37" t="s">
+        <v>968</v>
+      </c>
+      <c r="EO37">
+        <v>651</v>
+      </c>
+      <c r="EP37">
+        <v>556</v>
+      </c>
+      <c r="EQ37" t="s">
+        <v>713</v>
+      </c>
+      <c r="ER37" t="s">
+        <v>1343</v>
+      </c>
+      <c r="ES37">
+        <v>0</v>
+      </c>
+      <c r="ET37">
+        <v>1</v>
+      </c>
+      <c r="EU37">
+        <v>0</v>
+      </c>
+      <c r="EV37">
+        <v>0</v>
+      </c>
+      <c r="EW37">
+        <v>0</v>
+      </c>
+      <c r="EX37">
+        <v>0</v>
+      </c>
+      <c r="EZ37" t="s">
+        <v>713</v>
+      </c>
+      <c r="FA37">
+        <v>30</v>
+      </c>
+      <c r="FB37" t="s">
+        <v>969</v>
+      </c>
+      <c r="FC37">
+        <v>1</v>
+      </c>
+      <c r="FD37">
+        <v>1</v>
+      </c>
+      <c r="FE37">
+        <v>1</v>
+      </c>
+      <c r="FF37" t="s">
+        <v>734</v>
+      </c>
+      <c r="FH37" t="s">
+        <v>734</v>
+      </c>
+      <c r="NL37">
+        <v>170</v>
+      </c>
+      <c r="NM37">
+        <v>102</v>
+      </c>
+      <c r="NO37">
+        <v>203</v>
+      </c>
+      <c r="NP37">
+        <v>161</v>
+      </c>
+      <c r="NR37">
+        <v>645</v>
+      </c>
+      <c r="NS37">
+        <v>275</v>
+      </c>
+      <c r="SC37" s="1"/>
+      <c r="TH37" t="s">
+        <v>1373</v>
+      </c>
+      <c r="ZK37" s="1"/>
+      <c r="ADN37" s="1"/>
+      <c r="ADV37" s="1"/>
+      <c r="ADX37">
+        <v>888068959</v>
+      </c>
+      <c r="ADY37" t="s">
+        <v>1374</v>
+      </c>
+      <c r="ADZ37" s="1">
+        <v>46302.571493055562</v>
+      </c>
+      <c r="AEB37" t="s">
+        <v>736</v>
+      </c>
+      <c r="AED37" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE37" t="s">
+        <v>1375</v>
+      </c>
+      <c r="AEF37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:812" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B38" t="s">
+        <v>708</v>
+      </c>
+      <c r="C38" t="s">
+        <v>819</v>
+      </c>
+      <c r="D38" t="s">
+        <v>595</v>
+      </c>
+      <c r="E38" t="s">
+        <v>754</v>
+      </c>
+      <c r="J38" t="s">
+        <v>1372</v>
+      </c>
+      <c r="EN38" t="s">
+        <v>756</v>
+      </c>
+      <c r="FQ38">
+        <v>170</v>
+      </c>
+      <c r="FR38">
+        <v>106</v>
+      </c>
+      <c r="FS38">
+        <v>2</v>
+      </c>
+      <c r="FT38">
+        <v>3</v>
+      </c>
+      <c r="FV38">
+        <v>207</v>
+      </c>
+      <c r="FW38">
+        <v>167</v>
+      </c>
+      <c r="FX38">
+        <v>1</v>
+      </c>
+      <c r="FY38">
+        <v>2</v>
+      </c>
+      <c r="GA38">
+        <v>270</v>
+      </c>
+      <c r="GB38">
+        <v>276</v>
+      </c>
+      <c r="GC38">
+        <v>1</v>
+      </c>
+      <c r="GD38">
+        <v>3</v>
+      </c>
+      <c r="GF38">
+        <v>2</v>
+      </c>
+      <c r="GG38">
+        <v>3</v>
+      </c>
+      <c r="GH38">
+        <v>0</v>
+      </c>
+      <c r="GI38">
+        <v>0</v>
+      </c>
+      <c r="GK38">
+        <v>0</v>
+      </c>
+      <c r="GL38">
+        <v>0</v>
+      </c>
+      <c r="GM38">
+        <v>0</v>
+      </c>
+      <c r="GN38">
+        <v>0</v>
+      </c>
+      <c r="GO38" t="s">
+        <v>1249</v>
+      </c>
+      <c r="GP38">
+        <v>1</v>
+      </c>
+      <c r="GQ38">
+        <v>0</v>
+      </c>
+      <c r="GR38">
+        <v>0</v>
+      </c>
+      <c r="GS38">
+        <v>1</v>
+      </c>
+      <c r="GT38">
+        <v>1</v>
+      </c>
+      <c r="GU38">
+        <v>0</v>
+      </c>
+      <c r="GV38">
+        <v>1</v>
+      </c>
+      <c r="GW38" t="s">
+        <v>1376</v>
+      </c>
+      <c r="GX38">
+        <v>1</v>
+      </c>
+      <c r="GY38">
+        <v>1</v>
+      </c>
+      <c r="GZ38">
+        <v>0</v>
+      </c>
+      <c r="HA38">
+        <v>1</v>
+      </c>
+      <c r="HB38">
+        <v>0</v>
+      </c>
+      <c r="HD38" t="s">
+        <v>713</v>
+      </c>
+      <c r="HE38" t="s">
+        <v>1377</v>
+      </c>
+      <c r="HF38" t="s">
+        <v>713</v>
+      </c>
+      <c r="HG38" t="s">
+        <v>734</v>
+      </c>
+      <c r="HI38" t="s">
+        <v>713</v>
+      </c>
+      <c r="HJ38" t="s">
+        <v>1378</v>
+      </c>
+      <c r="HQ38" t="s">
+        <v>835</v>
+      </c>
+      <c r="HR38">
+        <v>2</v>
+      </c>
+      <c r="HS38" t="s">
+        <v>1379</v>
+      </c>
+      <c r="HU38" t="s">
+        <v>835</v>
+      </c>
+      <c r="HV38">
+        <v>1</v>
+      </c>
+      <c r="HW38" t="s">
+        <v>1380</v>
+      </c>
+      <c r="HY38" t="s">
+        <v>768</v>
+      </c>
+      <c r="HZ38">
+        <v>4</v>
+      </c>
+      <c r="IA38" t="s">
+        <v>1381</v>
+      </c>
+      <c r="IC38" t="s">
+        <v>768</v>
+      </c>
+      <c r="ID38">
+        <v>2</v>
+      </c>
+      <c r="IE38" t="s">
+        <v>1382</v>
+      </c>
+      <c r="IG38" t="s">
+        <v>768</v>
+      </c>
+      <c r="IH38">
+        <v>1</v>
+      </c>
+      <c r="II38" t="s">
+        <v>1383</v>
+      </c>
+      <c r="IS38" t="s">
+        <v>837</v>
+      </c>
+      <c r="IT38" t="s">
+        <v>881</v>
+      </c>
+      <c r="IU38" t="s">
+        <v>1384</v>
+      </c>
+      <c r="IV38" t="s">
+        <v>838</v>
+      </c>
+      <c r="IW38" t="s">
+        <v>1385</v>
+      </c>
+      <c r="IX38" t="s">
+        <v>722</v>
+      </c>
+      <c r="IZ38" t="s">
+        <v>839</v>
+      </c>
+      <c r="JA38" t="s">
+        <v>1193</v>
+      </c>
+      <c r="JB38" t="s">
+        <v>1386</v>
+      </c>
+      <c r="JC38" t="s">
+        <v>841</v>
+      </c>
+      <c r="JD38" t="s">
+        <v>1302</v>
+      </c>
+      <c r="JE38" t="s">
+        <v>722</v>
+      </c>
+      <c r="JG38" t="s">
+        <v>770</v>
+      </c>
+      <c r="JH38" t="s">
+        <v>771</v>
+      </c>
+      <c r="JI38" t="s">
+        <v>1387</v>
+      </c>
+      <c r="JJ38" t="s">
+        <v>838</v>
+      </c>
+      <c r="JK38" t="s">
+        <v>1388</v>
+      </c>
+      <c r="JL38" t="s">
+        <v>718</v>
+      </c>
+      <c r="JN38" t="s">
+        <v>770</v>
+      </c>
+      <c r="JO38" t="s">
+        <v>771</v>
+      </c>
+      <c r="JP38" t="s">
+        <v>1389</v>
+      </c>
+      <c r="JQ38" t="s">
+        <v>838</v>
+      </c>
+      <c r="JR38" t="s">
+        <v>1390</v>
+      </c>
+      <c r="JS38" t="s">
+        <v>718</v>
+      </c>
+      <c r="JU38" t="s">
+        <v>837</v>
+      </c>
+      <c r="JV38" t="s">
+        <v>1193</v>
+      </c>
+      <c r="JW38" t="s">
+        <v>1391</v>
+      </c>
+      <c r="JX38" t="s">
+        <v>841</v>
+      </c>
+      <c r="JY38" t="s">
+        <v>1392</v>
+      </c>
+      <c r="JZ38" t="s">
+        <v>718</v>
+      </c>
+      <c r="KB38" t="s">
+        <v>770</v>
+      </c>
+      <c r="KC38" t="s">
+        <v>771</v>
+      </c>
+      <c r="KD38" t="s">
+        <v>1393</v>
+      </c>
+      <c r="KE38" t="s">
+        <v>838</v>
+      </c>
+      <c r="KF38" t="s">
+        <v>1394</v>
+      </c>
+      <c r="KG38" t="s">
+        <v>722</v>
+      </c>
+      <c r="KH38" t="s">
+        <v>708</v>
+      </c>
+      <c r="KI38">
+        <v>0</v>
+      </c>
+      <c r="KJ38">
+        <v>0</v>
+      </c>
+      <c r="KK38">
+        <v>0</v>
+      </c>
+      <c r="KL38">
+        <v>1</v>
+      </c>
+      <c r="KN38" t="s">
+        <v>1395</v>
+      </c>
+      <c r="KO38" t="s">
+        <v>1396</v>
+      </c>
+      <c r="KP38" t="s">
+        <v>1397</v>
+      </c>
+      <c r="KQ38" t="s">
+        <v>1398</v>
+      </c>
+      <c r="NL38">
+        <v>170</v>
+      </c>
+      <c r="NM38">
+        <v>106</v>
+      </c>
+      <c r="NO38">
+        <v>207</v>
+      </c>
+      <c r="NP38">
+        <v>167</v>
+      </c>
+      <c r="NR38">
+        <v>270</v>
+      </c>
+      <c r="NS38">
+        <v>276</v>
+      </c>
+      <c r="SC38" s="1"/>
+      <c r="TH38" t="s">
+        <v>1199</v>
+      </c>
+      <c r="ZK38" s="1"/>
+      <c r="ADN38" s="1"/>
+      <c r="ADV38" s="1"/>
+      <c r="ADX38">
+        <v>888115900</v>
+      </c>
+      <c r="ADY38" t="s">
+        <v>1399</v>
+      </c>
+      <c r="ADZ38" s="1">
+        <v>46302.604409722233</v>
+      </c>
+      <c r="AEB38" t="s">
+        <v>736</v>
+      </c>
+      <c r="AED38" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE38" t="s">
+        <v>1400</v>
+      </c>
+      <c r="AEF38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:812" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B39" t="s">
+        <v>708</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D39" t="s">
+        <v>595</v>
+      </c>
+      <c r="E39" t="s">
+        <v>754</v>
+      </c>
+      <c r="J39" t="s">
+        <v>820</v>
+      </c>
+      <c r="EN39" t="s">
+        <v>756</v>
+      </c>
+      <c r="FQ39">
+        <v>67</v>
+      </c>
+      <c r="FR39">
+        <v>128</v>
+      </c>
+      <c r="FS39">
+        <v>0</v>
+      </c>
+      <c r="FT39">
+        <v>0</v>
+      </c>
+      <c r="FV39">
+        <v>159</v>
+      </c>
+      <c r="FW39">
+        <v>295</v>
+      </c>
+      <c r="FX39">
+        <v>0</v>
+      </c>
+      <c r="FY39">
+        <v>2</v>
+      </c>
+      <c r="GA39">
+        <v>323</v>
+      </c>
+      <c r="GB39">
+        <v>591</v>
+      </c>
+      <c r="GC39">
+        <v>1</v>
+      </c>
+      <c r="GD39">
+        <v>0</v>
+      </c>
+      <c r="GF39">
+        <v>9</v>
+      </c>
+      <c r="GG39">
+        <v>11</v>
+      </c>
+      <c r="GH39">
+        <v>0</v>
+      </c>
+      <c r="GI39">
+        <v>0</v>
+      </c>
+      <c r="GK39">
+        <v>12</v>
+      </c>
+      <c r="GL39">
+        <v>16</v>
+      </c>
+      <c r="GM39">
+        <v>1</v>
+      </c>
+      <c r="GN39">
+        <v>0</v>
+      </c>
+      <c r="GO39" t="s">
+        <v>1249</v>
+      </c>
+      <c r="GP39">
+        <v>1</v>
+      </c>
+      <c r="GQ39">
+        <v>0</v>
+      </c>
+      <c r="GR39">
+        <v>0</v>
+      </c>
+      <c r="GS39">
+        <v>1</v>
+      </c>
+      <c r="GT39">
+        <v>1</v>
+      </c>
+      <c r="GU39">
+        <v>0</v>
+      </c>
+      <c r="GV39">
+        <v>1</v>
+      </c>
+      <c r="GW39" t="s">
+        <v>1402</v>
+      </c>
+      <c r="GX39">
+        <v>1</v>
+      </c>
+      <c r="GY39">
+        <v>1</v>
+      </c>
+      <c r="GZ39">
+        <v>1</v>
+      </c>
+      <c r="HA39">
+        <v>1</v>
+      </c>
+      <c r="HB39">
+        <v>0</v>
+      </c>
+      <c r="HD39" t="s">
+        <v>713</v>
+      </c>
+      <c r="HE39" t="s">
+        <v>1403</v>
+      </c>
+      <c r="HF39" t="s">
+        <v>713</v>
+      </c>
+      <c r="HG39" t="s">
+        <v>713</v>
+      </c>
+      <c r="HH39" t="s">
+        <v>1404</v>
+      </c>
+      <c r="HI39" t="s">
+        <v>713</v>
+      </c>
+      <c r="HJ39" t="s">
+        <v>1405</v>
+      </c>
+      <c r="HQ39" t="s">
+        <v>768</v>
+      </c>
+      <c r="HR39">
+        <v>1</v>
+      </c>
+      <c r="HS39" t="s">
+        <v>1406</v>
+      </c>
+      <c r="HU39" t="s">
+        <v>768</v>
+      </c>
+      <c r="HV39">
+        <v>2</v>
+      </c>
+      <c r="HW39" t="s">
+        <v>1407</v>
+      </c>
+      <c r="HY39" t="s">
+        <v>768</v>
+      </c>
+      <c r="HZ39">
+        <v>2</v>
+      </c>
+      <c r="IA39" t="s">
+        <v>1408</v>
+      </c>
+      <c r="IC39" t="s">
+        <v>835</v>
+      </c>
+      <c r="ID39">
+        <v>1</v>
+      </c>
+      <c r="IE39" t="s">
+        <v>1409</v>
+      </c>
+      <c r="IG39" t="s">
+        <v>767</v>
+      </c>
+      <c r="IH39">
+        <v>3</v>
+      </c>
+      <c r="II39" t="s">
+        <v>1410</v>
+      </c>
+      <c r="IS39" t="s">
+        <v>837</v>
+      </c>
+      <c r="IT39" t="s">
+        <v>771</v>
+      </c>
+      <c r="IU39" t="s">
+        <v>1411</v>
+      </c>
+      <c r="IV39" t="s">
+        <v>838</v>
+      </c>
+      <c r="IW39" t="s">
+        <v>1309</v>
+      </c>
+      <c r="IX39" t="s">
+        <v>718</v>
+      </c>
+      <c r="IZ39" t="s">
+        <v>770</v>
+      </c>
+      <c r="JA39" t="s">
+        <v>771</v>
+      </c>
+      <c r="JB39" t="s">
+        <v>1412</v>
+      </c>
+      <c r="JC39" t="s">
+        <v>838</v>
+      </c>
+      <c r="JD39" t="s">
+        <v>1413</v>
+      </c>
+      <c r="JE39" t="s">
+        <v>718</v>
+      </c>
+      <c r="JG39" t="s">
+        <v>770</v>
+      </c>
+      <c r="JH39" t="s">
+        <v>1193</v>
+      </c>
+      <c r="JI39" t="s">
+        <v>1414</v>
+      </c>
+      <c r="JJ39" t="s">
+        <v>1262</v>
+      </c>
+      <c r="JK39" t="s">
+        <v>1264</v>
+      </c>
+      <c r="JL39" t="s">
+        <v>722</v>
+      </c>
+      <c r="JN39" t="s">
+        <v>837</v>
+      </c>
+      <c r="JO39" t="s">
+        <v>881</v>
+      </c>
+      <c r="JP39" t="s">
+        <v>1415</v>
+      </c>
+      <c r="JQ39" t="s">
+        <v>841</v>
+      </c>
+      <c r="JR39" t="s">
+        <v>1416</v>
+      </c>
+      <c r="JS39" t="s">
+        <v>718</v>
+      </c>
+      <c r="JU39" t="s">
+        <v>770</v>
+      </c>
+      <c r="JV39" t="s">
+        <v>771</v>
+      </c>
+      <c r="JW39" t="s">
+        <v>1417</v>
+      </c>
+      <c r="JX39" t="s">
+        <v>838</v>
+      </c>
+      <c r="JY39" t="s">
+        <v>1309</v>
+      </c>
+      <c r="JZ39" t="s">
+        <v>718</v>
+      </c>
+      <c r="KB39" t="s">
+        <v>837</v>
+      </c>
+      <c r="KC39" t="s">
+        <v>771</v>
+      </c>
+      <c r="KD39" t="s">
+        <v>1418</v>
+      </c>
+      <c r="KE39" t="s">
+        <v>841</v>
+      </c>
+      <c r="KF39" t="s">
+        <v>1419</v>
+      </c>
+      <c r="KG39" t="s">
+        <v>722</v>
+      </c>
+      <c r="KH39" t="s">
+        <v>708</v>
+      </c>
+      <c r="KI39">
+        <v>0</v>
+      </c>
+      <c r="KJ39">
+        <v>0</v>
+      </c>
+      <c r="KK39">
+        <v>0</v>
+      </c>
+      <c r="KL39">
+        <v>1</v>
+      </c>
+      <c r="KN39" t="s">
+        <v>1420</v>
+      </c>
+      <c r="KO39" t="s">
+        <v>1421</v>
+      </c>
+      <c r="KP39" t="s">
+        <v>1422</v>
+      </c>
+      <c r="KQ39" t="s">
+        <v>1423</v>
+      </c>
+      <c r="NL39">
+        <v>67</v>
+      </c>
+      <c r="NM39">
+        <v>128</v>
+      </c>
+      <c r="NO39">
+        <v>159</v>
+      </c>
+      <c r="NP39">
+        <v>295</v>
+      </c>
+      <c r="NR39">
+        <v>323</v>
+      </c>
+      <c r="NS39">
+        <v>591</v>
+      </c>
+      <c r="SC39" s="1"/>
+      <c r="TH39" t="s">
+        <v>1199</v>
+      </c>
+      <c r="ZK39" s="1"/>
+      <c r="ADN39" s="1"/>
+      <c r="ADV39" s="1"/>
+      <c r="ADX39">
+        <v>888139197</v>
+      </c>
+      <c r="ADY39" t="s">
+        <v>1424</v>
+      </c>
+      <c r="ADZ39" s="1">
+        <v>46302.620891203696</v>
+      </c>
+      <c r="AEB39" t="s">
+        <v>736</v>
+      </c>
+      <c r="AED39" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE39" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AEF39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:812" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B40" t="s">
+        <v>708</v>
+      </c>
+      <c r="C40" t="s">
+        <v>739</v>
+      </c>
+      <c r="D40" t="s">
+        <v>592</v>
+      </c>
+      <c r="E40" t="s">
+        <v>754</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1118</v>
+      </c>
+      <c r="EN40" t="s">
+        <v>756</v>
+      </c>
+      <c r="FQ40">
+        <v>156</v>
+      </c>
+      <c r="FR40">
+        <v>215</v>
+      </c>
+      <c r="FS40">
+        <v>0</v>
+      </c>
+      <c r="FT40">
+        <v>0</v>
+      </c>
+      <c r="FV40">
+        <v>56</v>
+      </c>
+      <c r="FW40">
+        <v>102</v>
+      </c>
+      <c r="FX40">
+        <v>0</v>
+      </c>
+      <c r="FY40">
+        <v>0</v>
+      </c>
+      <c r="GA40">
+        <v>40</v>
+      </c>
+      <c r="GB40">
+        <v>56</v>
+      </c>
+      <c r="GC40">
+        <v>0</v>
+      </c>
+      <c r="GD40">
+        <v>0</v>
+      </c>
+      <c r="GF40">
+        <v>3</v>
+      </c>
+      <c r="GG40">
+        <v>1</v>
+      </c>
+      <c r="GH40">
+        <v>0</v>
+      </c>
+      <c r="GI40">
+        <v>0</v>
+      </c>
+      <c r="GK40">
+        <v>0</v>
+      </c>
+      <c r="GL40">
+        <v>0</v>
+      </c>
+      <c r="GM40">
+        <v>0</v>
+      </c>
+      <c r="GN40">
+        <v>0</v>
+      </c>
+      <c r="GO40" t="s">
+        <v>1426</v>
+      </c>
+      <c r="GP40">
+        <v>1</v>
+      </c>
+      <c r="GQ40">
+        <v>0</v>
+      </c>
+      <c r="GR40">
+        <v>1</v>
+      </c>
+      <c r="GS40">
+        <v>0</v>
+      </c>
+      <c r="GT40">
+        <v>0</v>
+      </c>
+      <c r="GU40">
+        <v>0</v>
+      </c>
+      <c r="GV40">
+        <v>1</v>
+      </c>
+      <c r="GW40" t="s">
+        <v>1293</v>
+      </c>
+      <c r="GX40">
+        <v>1</v>
+      </c>
+      <c r="GY40">
+        <v>0</v>
+      </c>
+      <c r="GZ40">
+        <v>0</v>
+      </c>
+      <c r="HA40">
+        <v>1</v>
+      </c>
+      <c r="HB40">
+        <v>0</v>
+      </c>
+      <c r="HD40" t="s">
+        <v>713</v>
+      </c>
+      <c r="HE40" t="s">
+        <v>1427</v>
+      </c>
+      <c r="HF40" t="s">
+        <v>713</v>
+      </c>
+      <c r="HG40" t="s">
+        <v>734</v>
+      </c>
+      <c r="HI40" t="s">
+        <v>734</v>
+      </c>
+      <c r="HQ40" t="s">
+        <v>1428</v>
+      </c>
+      <c r="HR40">
+        <v>40</v>
+      </c>
+      <c r="HS40" t="s">
+        <v>1429</v>
+      </c>
+      <c r="HU40" t="s">
+        <v>767</v>
+      </c>
+      <c r="HV40">
+        <v>35</v>
+      </c>
+      <c r="HW40" t="s">
+        <v>1430</v>
+      </c>
+      <c r="HY40" t="s">
+        <v>767</v>
+      </c>
+      <c r="HZ40">
+        <v>35</v>
+      </c>
+      <c r="IA40" t="s">
+        <v>1431</v>
+      </c>
+      <c r="IC40" t="s">
+        <v>767</v>
+      </c>
+      <c r="ID40">
+        <v>30</v>
+      </c>
+      <c r="IE40" t="s">
+        <v>1432</v>
+      </c>
+      <c r="IG40" t="s">
+        <v>767</v>
+      </c>
+      <c r="IH40">
+        <v>40</v>
+      </c>
+      <c r="II40" t="s">
+        <v>1433</v>
+      </c>
+      <c r="IS40" t="s">
+        <v>837</v>
+      </c>
+      <c r="IT40" t="s">
+        <v>771</v>
+      </c>
+      <c r="IU40" t="s">
+        <v>844</v>
+      </c>
+      <c r="IV40" t="s">
+        <v>1262</v>
+      </c>
+      <c r="IW40" t="s">
+        <v>844</v>
+      </c>
+      <c r="IX40" t="s">
+        <v>722</v>
+      </c>
+      <c r="IZ40" t="s">
+        <v>770</v>
+      </c>
+      <c r="JA40" t="s">
+        <v>881</v>
+      </c>
+      <c r="JB40" t="s">
+        <v>1434</v>
+      </c>
+      <c r="JC40" t="s">
+        <v>1262</v>
+      </c>
+      <c r="JD40" t="s">
+        <v>844</v>
+      </c>
+      <c r="JE40" t="s">
+        <v>718</v>
+      </c>
+      <c r="JG40" t="s">
+        <v>839</v>
+      </c>
+      <c r="JH40" t="s">
+        <v>881</v>
+      </c>
+      <c r="JI40" t="s">
+        <v>844</v>
+      </c>
+      <c r="JJ40" t="s">
+        <v>1262</v>
+      </c>
+      <c r="JK40" t="s">
+        <v>844</v>
+      </c>
+      <c r="JL40" t="s">
+        <v>722</v>
+      </c>
+      <c r="JN40" t="s">
+        <v>839</v>
+      </c>
+      <c r="JO40" t="s">
+        <v>881</v>
+      </c>
+      <c r="JP40" t="s">
+        <v>844</v>
+      </c>
+      <c r="JQ40" t="s">
+        <v>1262</v>
+      </c>
+      <c r="JR40" t="s">
+        <v>844</v>
+      </c>
+      <c r="JS40" t="s">
+        <v>722</v>
+      </c>
+      <c r="JU40" t="s">
+        <v>839</v>
+      </c>
+      <c r="JV40" t="s">
+        <v>881</v>
+      </c>
+      <c r="JW40" t="s">
+        <v>844</v>
+      </c>
+      <c r="JX40" t="s">
+        <v>1262</v>
+      </c>
+      <c r="JY40" t="s">
+        <v>844</v>
+      </c>
+      <c r="JZ40" t="s">
+        <v>718</v>
+      </c>
+      <c r="KB40" t="s">
+        <v>770</v>
+      </c>
+      <c r="KC40" t="s">
+        <v>771</v>
+      </c>
+      <c r="KD40" t="s">
+        <v>1435</v>
+      </c>
+      <c r="KE40" t="s">
+        <v>841</v>
+      </c>
+      <c r="KF40" t="s">
+        <v>1436</v>
+      </c>
+      <c r="KG40" t="s">
+        <v>718</v>
+      </c>
+      <c r="KH40" t="s">
+        <v>1437</v>
+      </c>
+      <c r="KI40">
+        <v>0</v>
+      </c>
+      <c r="KJ40">
+        <v>1</v>
+      </c>
+      <c r="KK40">
+        <v>1</v>
+      </c>
+      <c r="KL40">
+        <v>0</v>
+      </c>
+      <c r="KN40" t="s">
+        <v>1438</v>
+      </c>
+      <c r="KO40" t="s">
+        <v>1439</v>
+      </c>
+      <c r="KP40" t="s">
+        <v>1440</v>
+      </c>
+      <c r="KQ40" t="s">
+        <v>1441</v>
+      </c>
+      <c r="NL40">
+        <v>276</v>
+      </c>
+      <c r="NM40">
+        <v>304</v>
+      </c>
+      <c r="NO40">
+        <v>201</v>
+      </c>
+      <c r="NP40">
+        <v>269</v>
+      </c>
+      <c r="NR40">
+        <v>85</v>
+      </c>
+      <c r="NS40">
+        <v>67</v>
+      </c>
+      <c r="SC40" s="1"/>
+      <c r="TH40" t="s">
+        <v>1442</v>
+      </c>
+      <c r="ZK40" s="1"/>
+      <c r="ADN40" s="1"/>
+      <c r="ADV40" s="1"/>
+      <c r="ADX40">
+        <v>888162934</v>
+      </c>
+      <c r="ADY40" t="s">
+        <v>1443</v>
+      </c>
+      <c r="ADZ40" s="1">
+        <v>46302.638159722221</v>
+      </c>
+      <c r="AEB40" t="s">
+        <v>736</v>
+      </c>
+      <c r="AED40" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE40" t="s">
+        <v>1444</v>
+      </c>
+      <c r="AEF40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:812" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B41" t="s">
+        <v>708</v>
+      </c>
+      <c r="C41" t="s">
+        <v>739</v>
+      </c>
+      <c r="D41" t="s">
+        <v>592</v>
+      </c>
+      <c r="E41" t="s">
+        <v>754</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1445</v>
+      </c>
+      <c r="EN41" t="s">
+        <v>968</v>
+      </c>
+      <c r="EO41">
+        <v>738</v>
+      </c>
+      <c r="EP41">
+        <v>618</v>
+      </c>
+      <c r="EQ41" t="s">
+        <v>713</v>
+      </c>
+      <c r="ER41" t="s">
+        <v>1446</v>
+      </c>
+      <c r="ES41">
+        <v>0</v>
+      </c>
+      <c r="ET41">
+        <v>1</v>
+      </c>
+      <c r="EU41">
+        <v>0</v>
+      </c>
+      <c r="EV41">
+        <v>0</v>
+      </c>
+      <c r="EW41">
+        <v>1</v>
+      </c>
+      <c r="EX41">
+        <v>0</v>
+      </c>
+      <c r="EZ41" t="s">
+        <v>713</v>
+      </c>
+      <c r="FA41">
+        <v>30</v>
+      </c>
+      <c r="FB41" t="s">
+        <v>969</v>
+      </c>
+      <c r="FC41">
+        <v>1</v>
+      </c>
+      <c r="FD41">
+        <v>1</v>
+      </c>
+      <c r="FE41">
+        <v>1</v>
+      </c>
+      <c r="FF41" t="s">
+        <v>713</v>
+      </c>
+      <c r="FG41" t="s">
+        <v>1447</v>
+      </c>
+      <c r="FH41" t="s">
+        <v>713</v>
+      </c>
+      <c r="FI41">
+        <v>0</v>
+      </c>
+      <c r="FJ41" t="s">
+        <v>844</v>
+      </c>
+      <c r="NL41">
+        <v>492</v>
+      </c>
+      <c r="NM41">
+        <v>465</v>
+      </c>
+      <c r="NO41">
+        <v>233</v>
+      </c>
+      <c r="NP41">
+        <v>173</v>
+      </c>
+      <c r="NR41">
+        <v>113</v>
+      </c>
+      <c r="NS41">
+        <v>80</v>
+      </c>
+      <c r="SC41" s="1"/>
+      <c r="TH41" t="s">
+        <v>1448</v>
+      </c>
+      <c r="ZK41" s="1"/>
+      <c r="ADN41" s="1"/>
+      <c r="ADV41" s="1"/>
+      <c r="ADX41">
+        <v>888172725</v>
+      </c>
+      <c r="ADY41" t="s">
+        <v>1449</v>
+      </c>
+      <c r="ADZ41" s="1">
+        <v>46302.64607638889</v>
+      </c>
+      <c r="AEB41" t="s">
+        <v>736</v>
+      </c>
+      <c r="AED41" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE41" t="s">
+        <v>1450</v>
+      </c>
+      <c r="AEF41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:812" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D42" t="s">
+        <v>592</v>
+      </c>
+      <c r="E42" t="s">
+        <v>754</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1452</v>
+      </c>
+      <c r="EN42" t="s">
+        <v>968</v>
+      </c>
+      <c r="EO42">
+        <v>1206</v>
+      </c>
+      <c r="EP42">
+        <v>1280</v>
+      </c>
+      <c r="EQ42" t="s">
+        <v>713</v>
+      </c>
+      <c r="ER42" t="s">
+        <v>1453</v>
+      </c>
+      <c r="ES42">
+        <v>1</v>
+      </c>
+      <c r="ET42">
+        <v>0</v>
+      </c>
+      <c r="EU42">
+        <v>0</v>
+      </c>
+      <c r="EV42">
+        <v>0</v>
+      </c>
+      <c r="EW42">
+        <v>1</v>
+      </c>
+      <c r="EX42">
+        <v>0</v>
+      </c>
+      <c r="EZ42" t="s">
+        <v>713</v>
+      </c>
+      <c r="FA42">
+        <v>25</v>
+      </c>
+      <c r="FB42" t="s">
+        <v>1119</v>
+      </c>
+      <c r="FC42">
+        <v>0</v>
+      </c>
+      <c r="FD42">
+        <v>1</v>
+      </c>
+      <c r="FE42">
+        <v>1</v>
+      </c>
+      <c r="FF42" t="s">
+        <v>713</v>
+      </c>
+      <c r="FG42" t="s">
+        <v>1454</v>
+      </c>
+      <c r="FH42" t="s">
+        <v>713</v>
+      </c>
+      <c r="FI42">
+        <v>0</v>
+      </c>
+      <c r="FJ42" t="s">
+        <v>844</v>
+      </c>
+      <c r="NL42">
+        <v>306</v>
+      </c>
+      <c r="NM42">
+        <v>351</v>
+      </c>
+      <c r="NO42">
+        <v>238</v>
+      </c>
+      <c r="NP42">
+        <v>248</v>
+      </c>
+      <c r="NR42">
+        <v>253</v>
+      </c>
+      <c r="NS42">
+        <v>201</v>
+      </c>
+      <c r="SC42" s="1"/>
+      <c r="TH42" t="s">
+        <v>1455</v>
+      </c>
+      <c r="ZK42" s="1"/>
+      <c r="ADN42" s="1"/>
+      <c r="ADV42" s="1"/>
+      <c r="ADX42">
+        <v>888185704</v>
+      </c>
+      <c r="ADY42" t="s">
+        <v>1456</v>
+      </c>
+      <c r="ADZ42" s="1">
+        <v>46302.655925925923</v>
+      </c>
+      <c r="AEB42" t="s">
+        <v>736</v>
+      </c>
+      <c r="AED42" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE42" t="s">
+        <v>1457</v>
+      </c>
+      <c r="AEF42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:812" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B43" t="s">
+        <v>708</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D43" t="s">
+        <v>592</v>
+      </c>
+      <c r="E43" t="s">
+        <v>754</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1452</v>
+      </c>
+      <c r="EN43" t="s">
+        <v>756</v>
+      </c>
+      <c r="FQ43">
+        <v>31</v>
+      </c>
+      <c r="FR43">
+        <v>35</v>
+      </c>
+      <c r="FS43">
+        <v>0</v>
+      </c>
+      <c r="FT43">
+        <v>0</v>
+      </c>
+      <c r="FV43">
+        <v>45</v>
+      </c>
+      <c r="FW43">
+        <v>36</v>
+      </c>
+      <c r="FX43">
+        <v>0</v>
+      </c>
+      <c r="FY43">
+        <v>0</v>
+      </c>
+      <c r="GA43">
+        <v>28</v>
+      </c>
+      <c r="GB43">
+        <v>31</v>
+      </c>
+      <c r="GC43">
+        <v>0</v>
+      </c>
+      <c r="GD43">
+        <v>0</v>
+      </c>
+      <c r="GF43">
+        <v>3</v>
+      </c>
+      <c r="GG43">
+        <v>2</v>
+      </c>
+      <c r="GH43">
+        <v>0</v>
+      </c>
+      <c r="GI43">
+        <v>0</v>
+      </c>
+      <c r="GK43">
+        <v>0</v>
+      </c>
+      <c r="GL43">
+        <v>2</v>
+      </c>
+      <c r="GM43">
+        <v>0</v>
+      </c>
+      <c r="GN43">
+        <v>0</v>
+      </c>
+      <c r="GO43" t="s">
+        <v>1459</v>
+      </c>
+      <c r="GP43">
+        <v>1</v>
+      </c>
+      <c r="GQ43">
+        <v>1</v>
+      </c>
+      <c r="GR43">
+        <v>1</v>
+      </c>
+      <c r="GS43">
+        <v>1</v>
+      </c>
+      <c r="GT43">
+        <v>1</v>
+      </c>
+      <c r="GU43">
+        <v>0</v>
+      </c>
+      <c r="GV43">
+        <v>1</v>
+      </c>
+      <c r="GW43" t="s">
+        <v>1347</v>
+      </c>
+      <c r="GX43">
+        <v>1</v>
+      </c>
+      <c r="GY43">
+        <v>0</v>
+      </c>
+      <c r="GZ43">
+        <v>1</v>
+      </c>
+      <c r="HA43">
+        <v>1</v>
+      </c>
+      <c r="HB43">
+        <v>0</v>
+      </c>
+      <c r="HD43" t="s">
+        <v>713</v>
+      </c>
+      <c r="HE43" t="s">
+        <v>1460</v>
+      </c>
+      <c r="HF43" t="s">
+        <v>734</v>
+      </c>
+      <c r="HG43" t="s">
+        <v>734</v>
+      </c>
+      <c r="HI43" t="s">
+        <v>713</v>
+      </c>
+      <c r="HJ43" t="s">
+        <v>1461</v>
+      </c>
+      <c r="HQ43" t="s">
+        <v>767</v>
+      </c>
+      <c r="HR43">
+        <v>16</v>
+      </c>
+      <c r="HS43" t="s">
+        <v>1462</v>
+      </c>
+      <c r="HU43" t="s">
+        <v>767</v>
+      </c>
+      <c r="HV43">
+        <v>22</v>
+      </c>
+      <c r="HW43" t="s">
+        <v>1463</v>
+      </c>
+      <c r="HY43" t="s">
+        <v>767</v>
+      </c>
+      <c r="HZ43">
+        <v>21</v>
+      </c>
+      <c r="IA43" t="s">
+        <v>1464</v>
+      </c>
+      <c r="IC43" t="s">
+        <v>767</v>
+      </c>
+      <c r="ID43">
+        <v>25</v>
+      </c>
+      <c r="IE43" t="s">
+        <v>1465</v>
+      </c>
+      <c r="IG43" t="s">
+        <v>767</v>
+      </c>
+      <c r="IH43">
+        <v>21</v>
+      </c>
+      <c r="II43" t="s">
+        <v>1466</v>
+      </c>
+      <c r="IS43" t="s">
+        <v>770</v>
+      </c>
+      <c r="IT43" t="s">
+        <v>881</v>
+      </c>
+      <c r="IU43" t="s">
+        <v>1467</v>
+      </c>
+      <c r="IV43" t="s">
+        <v>838</v>
+      </c>
+      <c r="IW43" t="s">
+        <v>1468</v>
+      </c>
+      <c r="IX43" t="s">
+        <v>718</v>
+      </c>
+      <c r="IZ43" t="s">
+        <v>770</v>
+      </c>
+      <c r="JA43" t="s">
+        <v>771</v>
+      </c>
+      <c r="JB43" t="s">
+        <v>1469</v>
+      </c>
+      <c r="JC43" t="s">
+        <v>838</v>
+      </c>
+      <c r="JD43" t="s">
+        <v>1470</v>
+      </c>
+      <c r="JE43" t="s">
+        <v>722</v>
+      </c>
+      <c r="JG43" t="s">
+        <v>770</v>
+      </c>
+      <c r="JH43" t="s">
+        <v>881</v>
+      </c>
+      <c r="JI43" t="s">
+        <v>1471</v>
+      </c>
+      <c r="JJ43" t="s">
+        <v>838</v>
+      </c>
+      <c r="JK43" t="s">
+        <v>1472</v>
+      </c>
+      <c r="JL43" t="s">
+        <v>722</v>
+      </c>
+      <c r="JN43" t="s">
+        <v>770</v>
+      </c>
+      <c r="JO43" t="s">
+        <v>771</v>
+      </c>
+      <c r="JP43" t="s">
+        <v>1473</v>
+      </c>
+      <c r="JQ43" t="s">
+        <v>838</v>
+      </c>
+      <c r="JR43" t="s">
+        <v>1472</v>
+      </c>
+      <c r="JS43" t="s">
+        <v>722</v>
+      </c>
+      <c r="JU43" t="s">
+        <v>839</v>
+      </c>
+      <c r="JV43" t="s">
+        <v>881</v>
+      </c>
+      <c r="JW43" t="s">
+        <v>1474</v>
+      </c>
+      <c r="JX43" t="s">
+        <v>838</v>
+      </c>
+      <c r="JY43" t="s">
+        <v>1468</v>
+      </c>
+      <c r="JZ43" t="s">
+        <v>722</v>
+      </c>
+      <c r="KB43" t="s">
+        <v>770</v>
+      </c>
+      <c r="KC43" t="s">
+        <v>771</v>
+      </c>
+      <c r="KD43" t="s">
+        <v>1475</v>
+      </c>
+      <c r="KE43" t="s">
+        <v>838</v>
+      </c>
+      <c r="KF43" t="s">
+        <v>1468</v>
+      </c>
+      <c r="KG43" t="s">
+        <v>718</v>
+      </c>
+      <c r="KH43" t="s">
+        <v>1437</v>
+      </c>
+      <c r="KI43">
+        <v>0</v>
+      </c>
+      <c r="KJ43">
+        <v>1</v>
+      </c>
+      <c r="KK43">
+        <v>1</v>
+      </c>
+      <c r="KL43">
+        <v>0</v>
+      </c>
+      <c r="KN43" t="s">
+        <v>1476</v>
+      </c>
+      <c r="KO43" t="s">
+        <v>1477</v>
+      </c>
+      <c r="KP43" t="s">
+        <v>1478</v>
+      </c>
+      <c r="KQ43" t="s">
+        <v>1479</v>
+      </c>
+      <c r="NL43">
+        <v>306</v>
+      </c>
+      <c r="NM43">
+        <v>351</v>
+      </c>
+      <c r="NO43">
+        <v>238</v>
+      </c>
+      <c r="NP43">
+        <v>248</v>
+      </c>
+      <c r="NR43">
+        <v>253</v>
+      </c>
+      <c r="NS43">
+        <v>201</v>
+      </c>
+      <c r="SC43" s="1"/>
+      <c r="TH43" t="s">
+        <v>1480</v>
+      </c>
+      <c r="ZK43" s="1"/>
+      <c r="ADN43" s="1"/>
+      <c r="ADV43" s="1"/>
+      <c r="ADX43">
+        <v>888187658</v>
+      </c>
+      <c r="ADY43" t="s">
+        <v>1481</v>
+      </c>
+      <c r="ADZ43" s="1">
+        <v>46302.657418981478</v>
+      </c>
+      <c r="AEB43" t="s">
+        <v>736</v>
+      </c>
+      <c r="AED43" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE43" t="s">
+        <v>1482</v>
+      </c>
+      <c r="AEF43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:812" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B44" t="s">
+        <v>708</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D44" t="s">
+        <v>592</v>
+      </c>
+      <c r="E44" t="s">
+        <v>754</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1483</v>
+      </c>
+      <c r="EN44" t="s">
+        <v>968</v>
+      </c>
+      <c r="EO44">
+        <v>990</v>
+      </c>
+      <c r="EP44">
+        <v>785</v>
+      </c>
+      <c r="EQ44" t="s">
+        <v>713</v>
+      </c>
+      <c r="ER44" t="s">
+        <v>1207</v>
+      </c>
+      <c r="ES44">
+        <v>0</v>
+      </c>
+      <c r="ET44">
+        <v>1</v>
+      </c>
+      <c r="EU44">
+        <v>0</v>
+      </c>
+      <c r="EV44">
+        <v>1</v>
+      </c>
+      <c r="EW44">
+        <v>0</v>
+      </c>
+      <c r="EX44">
+        <v>0</v>
+      </c>
+      <c r="EZ44" t="s">
+        <v>713</v>
+      </c>
+      <c r="FA44">
+        <v>30</v>
+      </c>
+      <c r="FB44" t="s">
+        <v>1119</v>
+      </c>
+      <c r="FC44">
+        <v>0</v>
+      </c>
+      <c r="FD44">
+        <v>1</v>
+      </c>
+      <c r="FE44">
+        <v>1</v>
+      </c>
+      <c r="FF44" t="s">
+        <v>713</v>
+      </c>
+      <c r="FG44" t="s">
+        <v>1484</v>
+      </c>
+      <c r="FH44" t="s">
+        <v>734</v>
+      </c>
+      <c r="NL44">
+        <v>315</v>
+      </c>
+      <c r="NM44">
+        <v>256</v>
+      </c>
+      <c r="NO44">
+        <v>193</v>
+      </c>
+      <c r="NP44">
+        <v>148</v>
+      </c>
+      <c r="NR44">
+        <v>87</v>
+      </c>
+      <c r="NS44">
+        <v>62</v>
+      </c>
+      <c r="SC44" s="1"/>
+      <c r="TH44" t="s">
+        <v>1485</v>
+      </c>
+      <c r="ZK44" s="1"/>
+      <c r="ADN44" s="1"/>
+      <c r="ADV44" s="1"/>
+      <c r="ADX44">
+        <v>888194246</v>
+      </c>
+      <c r="ADY44" t="s">
+        <v>1486</v>
+      </c>
+      <c r="ADZ44" s="1">
+        <v>46302.662210648137</v>
+      </c>
+      <c r="AEB44" t="s">
+        <v>736</v>
+      </c>
+      <c r="AED44" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AEE44" t="s">
+        <v>1487</v>
+      </c>
+      <c r="AEF44">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5686D5D8-9D7D-8446-B8A3-87C9D3C76E07}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC816450-3732-424E-8160-7611F27CE743}"/>
   <bookViews>
     <workbookView xWindow="3220" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="1567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="1567">
   <si>
     <t>Date</t>
   </si>
@@ -4805,7 +4805,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFF46" totalsRowShown="0">
   <autoFilter ref="A1:AFF46" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="838">
-    <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
     <tableColumn id="3" xr3:uid="{1A468597-D831-D84D-804A-CED0115BE04C}" name="Specify"/>
     <tableColumn id="4" xr3:uid="{1393CF8E-733A-E140-A757-7249B3FBBBF5}" name="District"/>
@@ -5301,7 +5301,7 @@
     <tableColumn id="494" xr3:uid="{24252B5A-931B-2E45-8B68-6BA232326CEB}" name="Main debate point or objection raised before consensus was reached by members of the community"/>
     <tableColumn id="495" xr3:uid="{68B5845F-8D3E-2443-89FD-779AA51C6980}" name="Were community media highlights or clean cooking/gender dialogue photos captured for social media PR reporting?"/>
     <tableColumn id="496" xr3:uid="{FB56AF65-E271-2A46-94BC-9071226C9CC0}" name="Provide a short description of the captured community highlight"/>
-    <tableColumn id="497" xr3:uid="{F49466C0-F719-E344-9751-6ED4A3B8F9CA}" name="Did community members mention or give feedback on the campaign radio broadcasts during the gathering?" dataDxfId="6"/>
+    <tableColumn id="497" xr3:uid="{F49466C0-F719-E344-9751-6ED4A3B8F9CA}" name="Did community members mention or give feedback on the campaign radio broadcasts during the gathering?" dataDxfId="5"/>
     <tableColumn id="498" xr3:uid="{B921394E-D83F-5A42-AB33-0A93E92D1306}" name="How many indicated they heard the radio campaign on radio"/>
     <tableColumn id="499" xr3:uid="{BAA1B846-EFE7-2B4F-A9DD-2DE58E2F1EBA}" name="Summary of community radio feedback (if any)"/>
     <tableColumn id="500" xr3:uid="{A40C09EA-5F54-1F42-B126-6540599803CE}" name="Storyteller names and age"/>
@@ -5491,7 +5491,7 @@
     <tableColumn id="684" xr3:uid="{B1F66958-3D43-B94B-9C16-74192AC24756}" name="&lt;span style=&quot;display:none&quot;&gt;row-Can they recall activities from the session&lt;/span&gt;"/>
     <tableColumn id="685" xr3:uid="{29E0C23A-62D1-074E-9672-94000C9952EF}" name="Explain your response above"/>
     <tableColumn id="686" xr3:uid="{7184D4B5-497E-8B42-BA7E-93956BB75536}" name="&lt;span style=&quot;display:none&quot;&gt;row-Explain in their own words&lt;/span&gt;"/>
-    <tableColumn id="687" xr3:uid="{A87F9C28-2C9B-7947-8188-2708D92754AA}" name="Were the foods used in the demonstration available in the local market/garden today?" dataDxfId="5"/>
+    <tableColumn id="687" xr3:uid="{A87F9C28-2C9B-7947-8188-2708D92754AA}" name="Were the foods used in the demonstration available in the local market/garden today?" dataDxfId="4"/>
     <tableColumn id="688" xr3:uid="{163F27DD-60AE-B546-BC3D-EDFB40B458B1}" name="##### Learner 257"/>
     <tableColumn id="689" xr3:uid="{01F5B0BF-E941-BA4E-B9DC-B55C53601615}" name="Did the demonstration show an alternative replacement food?"/>
     <tableColumn id="690" xr3:uid="{07527EF8-6756-3E4F-A4FB-9C7CAA3A1F1C}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Can they recall activities from the session&lt;/span&gt;"/>
@@ -5598,7 +5598,7 @@
     <tableColumn id="791" xr3:uid="{4C0A5DF5-86B2-D849-95A5-CB71300B7CB0}" name="##### Caregiver 159"/>
     <tableColumn id="792" xr3:uid="{E5325280-A774-3B4A-9ED8-84FA8A8874F1}" name="&lt;span style=&quot;display:none&quot;&gt;row-What is most difficult or gets in the way of preparing balanced meals at home?&lt;/span&gt;"/>
     <tableColumn id="793" xr3:uid="{DB727688-D385-C245-8A2D-AF7B898277DE}" name="&lt;span style=&quot;display:none&quot;&gt;row-Despite those difficulties, which action can they realistically try at home?&lt;/span&gt;"/>
-    <tableColumn id="794" xr3:uid="{250149CA-1640-2040-8485-513B1F14F7BC}" name="&lt;span style=&quot;display:none&quot;&gt;row-Column&lt;/span&gt;" dataDxfId="4"/>
+    <tableColumn id="794" xr3:uid="{250149CA-1640-2040-8485-513B1F14F7BC}" name="&lt;span style=&quot;display:none&quot;&gt;row-Column&lt;/span&gt;" dataDxfId="3"/>
     <tableColumn id="795" xr3:uid="{2D8627C1-C63D-B947-B59B-912D1C5CA4F6}" name="Male Elders Present"/>
     <tableColumn id="796" xr3:uid="{7E068712-10C1-7E45-82C2-547C0A0C71FB}" name="Female Elders Present"/>
     <tableColumn id="797" xr3:uid="{7DFD7878-2F3F-3643-A2BD-5E4E0BE589AC}" name="Young Men / Fathers"/>
@@ -5606,11 +5606,11 @@
     <tableColumn id="799" xr3:uid="{001CD147-E387-1F47-BE40-9AC957C013CD}" name="Community Agreement (Record in their exact words with NO personal names)"/>
     <tableColumn id="800" xr3:uid="{D8A7EC63-50BC-274A-86D2-668C7D822872}" name="Named community body or structure responsible for follow-up"/>
     <tableColumn id="801" xr3:uid="{0C08E4AF-A66A-0546-AA7A-E85453EA2AAA}" name="Story Collector Name &amp; Role"/>
-    <tableColumn id="802" xr3:uid="{804E32AA-4C22-9C4A-89AD-8565D5E43A3F}" name="Storyteller Category" dataDxfId="3"/>
+    <tableColumn id="802" xr3:uid="{804E32AA-4C22-9C4A-89AD-8565D5E43A3F}" name="Storyteller Category" dataDxfId="2"/>
     <tableColumn id="803" xr3:uid="{0B2A7644-1219-7F45-BD58-C140D0F9A9F1}" name="Record the storyteller's actual words and dont try to re-interprete them"/>
     <tableColumn id="804" xr3:uid="{C6C34708-06EA-6C4E-96CF-F8A94B96848E}" name="What specific nutribus event, activity, chart, or discussion caused the shift"/>
     <tableColumn id="805" xr3:uid="{38679512-AF49-9741-99A0-3E49B75219C7}" name="What was physically done differently at home, class, or community after attending nutribus activities"/>
-    <tableColumn id="806" xr3:uid="{7948810D-68E4-9042-97FB-D505C399CD49}" name="Did learners actively handle materials and practice rather than listen passively?60" dataDxfId="2"/>
+    <tableColumn id="806" xr3:uid="{7948810D-68E4-9042-97FB-D505C399CD49}" name="Did learners actively handle materials and practice rather than listen passively?60" dataDxfId="1"/>
     <tableColumn id="807" xr3:uid="{5184A4C6-CB6E-BE4F-A410-850CD982E8DA}" name="Was any learner excluded or left out during sessions?"/>
     <tableColumn id="808" xr3:uid="{8DFC507D-7250-144D-B9FC-922148269969}" name="what comments from the spectators"/>
     <tableColumn id="809" xr3:uid="{C9F63958-2150-0049-BA05-613C84E904C2}" name="Were all demonstrated foods sourced locally"/>
@@ -15893,9 +15893,6 @@
       <c r="KJ30" t="s">
         <v>716</v>
       </c>
-      <c r="KK30" t="s">
-        <v>706</v>
-      </c>
       <c r="KL30">
         <v>0</v>
       </c>
@@ -16751,9 +16748,6 @@
       <c r="KJ33" t="s">
         <v>720</v>
       </c>
-      <c r="KK33" t="s">
-        <v>706</v>
-      </c>
       <c r="KL33">
         <v>0</v>
       </c>
@@ -17606,9 +17600,6 @@
       <c r="KJ36" t="s">
         <v>720</v>
       </c>
-      <c r="KK36" t="s">
-        <v>706</v>
-      </c>
       <c r="KL36">
         <v>0</v>
       </c>
@@ -18090,9 +18081,6 @@
       <c r="KJ38" t="s">
         <v>720</v>
       </c>
-      <c r="KK38" t="s">
-        <v>706</v>
-      </c>
       <c r="KL38">
         <v>0</v>
       </c>
@@ -18457,9 +18445,6 @@
       </c>
       <c r="KJ39" t="s">
         <v>720</v>
-      </c>
-      <c r="KK39" t="s">
-        <v>706</v>
       </c>
       <c r="KL39">
         <v>0</v>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC816450-3732-424E-8160-7611F27CE743}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4432CC1A-B7A7-D441-BE78-3BA88A4F0FF0}"/>
   <bookViews>
-    <workbookView xWindow="3220" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nutribus 2.0 Activity" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="1567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="1651">
   <si>
     <t>Date</t>
   </si>
@@ -4721,6 +4721,258 @@
   </si>
   <si>
     <t>Observed community commitment to clean cooking practices:4</t>
+  </si>
+  <si>
+    <t>KARITA P/S</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>it promotes proper growth</t>
+  </si>
+  <si>
+    <t>both have equal rights to eating</t>
+  </si>
+  <si>
+    <t>it promotes equality</t>
+  </si>
+  <si>
+    <t>it promotes good relationship among chilren</t>
+  </si>
+  <si>
+    <t>it promotes good health among both gender</t>
+  </si>
+  <si>
+    <t>it reduces work load on girls</t>
+  </si>
+  <si>
+    <t>5cc16cbc-795b-4bbf-b2c4-bf9af47e3d05</t>
+  </si>
+  <si>
+    <t>vxRzebfEJt7bLTTkC3QLwK</t>
+  </si>
+  <si>
+    <t>uuid:5cc16cbc-795b-4bbf-b2c4-bf9af47e3d05</t>
+  </si>
+  <si>
+    <t>Nutri Club patron Another teacher Nutri Club member District cordinator Other</t>
+  </si>
+  <si>
+    <t>Head teacher</t>
+  </si>
+  <si>
+    <t>They were doing demonstrations of the activities taugt</t>
+  </si>
+  <si>
+    <t>Every thing was explained well</t>
+  </si>
+  <si>
+    <t>no it leaves girls behind</t>
+  </si>
+  <si>
+    <t>yes,both have rights to equal educatio</t>
+  </si>
+  <si>
+    <t>yes both have to be responsible</t>
+  </si>
+  <si>
+    <t>Equality should be for all chilren</t>
+  </si>
+  <si>
+    <t>girls should go to school to become leaders tomorow</t>
+  </si>
+  <si>
+    <t>it helps reduce heavy work from girls</t>
+  </si>
+  <si>
+    <t>all children should be given food equally</t>
+  </si>
+  <si>
+    <t>it promotes unity among children at home</t>
+  </si>
+  <si>
+    <t>both gender have right to proper food</t>
+  </si>
+  <si>
+    <t>houes chores is good to give both children since it promotes hard work</t>
+  </si>
+  <si>
+    <t>girls are encouraged when helped by boys</t>
+  </si>
+  <si>
+    <t>it promotes hardwork among chilren</t>
+  </si>
+  <si>
+    <t>learning should involve all gender</t>
+  </si>
+  <si>
+    <t>work should be shared both gender at home</t>
+  </si>
+  <si>
+    <t>goodfeeding promotes good health in chilren</t>
+  </si>
+  <si>
+    <t>education is imporatnt for both gender</t>
+  </si>
+  <si>
+    <t>both boys and girls have right to healthy food</t>
+  </si>
+  <si>
+    <t>very good mobilization and turnup for both teachers and pupils</t>
+  </si>
+  <si>
+    <t>nonenone</t>
+  </si>
+  <si>
+    <t>dd28c5a1-f5bb-4421-a9ed-52f77ad3ccf6</t>
+  </si>
+  <si>
+    <t>uuid:dd28c5a1-f5bb-4421-a9ed-52f77ad3ccf6</t>
+  </si>
+  <si>
+    <t>NARENGEPAK P/S</t>
+  </si>
+  <si>
+    <t>It's pinned on wall of the headteachers office</t>
+  </si>
+  <si>
+    <t>The school is already embracing the nutrition intervention however drought affected the gardens in the school but nevertheless they are ready to work together  throughout the campaign</t>
+  </si>
+  <si>
+    <t>d91cd1b7-d2a9-431d-aa2f-a6b6e302edcb</t>
+  </si>
+  <si>
+    <t>uuid:d91cd1b7-d2a9-431d-aa2f-a6b6e302edcb</t>
+  </si>
+  <si>
+    <t>Awas Francis</t>
+  </si>
+  <si>
+    <t>LORENGEDWAT P/S</t>
+  </si>
+  <si>
+    <t>Headteachers office front</t>
+  </si>
+  <si>
+    <t>The club has to have routine nutrition messages and education to strengthen the three pillars of the campaign.</t>
+  </si>
+  <si>
+    <t>23f99446-6ff6-4dcb-be69-2fb98edff794</t>
+  </si>
+  <si>
+    <t>uuid:23f99446-6ff6-4dcb-be69-2fb98edff794</t>
+  </si>
+  <si>
+    <t>NATIRAE P/S</t>
+  </si>
+  <si>
+    <t>Headteachers office in front</t>
+  </si>
+  <si>
+    <t>There is need for the patrons to engage now children in club activities and class sessions, materials in book form are need so that children can interact with materials at their free time</t>
+  </si>
+  <si>
+    <t>8e66f561-dee7-4548-844c-f11f0135fb3d</t>
+  </si>
+  <si>
+    <t>uuid:8e66f561-dee7-4548-844c-f11f0135fb3d</t>
+  </si>
+  <si>
+    <t>The participated in games, question and answer session</t>
+  </si>
+  <si>
+    <t>The materials used were understood especially the reading books, the nutri run posters. However, the video session was not all that accessible to all because the phone size was small to be viewed by all</t>
+  </si>
+  <si>
+    <t>It will encourage early marriages, A girl can miss some lessons in the morning, makes a girl to drop out of school, Makes the girl to overthink and gives her psychological torture, makes a girl to resort to marriage, it's unfair because it will promote gender inequality</t>
+  </si>
+  <si>
+    <t>To promote gender equality, for safety purposes, it's good to walk together</t>
+  </si>
+  <si>
+    <t>Both boys and girls have a right to work together, Because it's a collective responsibility for both girls and boys to do chores at home</t>
+  </si>
+  <si>
+    <t>To avoid my sister from being punished for late coming</t>
+  </si>
+  <si>
+    <t>Because both boys and girls have an equal right to education,  if we don't report this issue girls will end up dropping out of school silently,  it will help prevent early marriages</t>
+  </si>
+  <si>
+    <t>The porridge can be made stronger by adding lemon/tamarind, BOO, sugar</t>
+  </si>
+  <si>
+    <t>It is the bus that has brought us together in unity</t>
+  </si>
+  <si>
+    <t>Sharing work  makes it easy, stronger porridge requires sugar to make it tasty</t>
+  </si>
+  <si>
+    <t>The bus that gathered us together</t>
+  </si>
+  <si>
+    <t>We can add eggs to the porridge to make it nutritious</t>
+  </si>
+  <si>
+    <t>The bus keeps us together</t>
+  </si>
+  <si>
+    <t>To make nutritious porridge I will add cowpeas,cooking oil</t>
+  </si>
+  <si>
+    <t>The bus gathers us together in it and it binds us as a whole</t>
+  </si>
+  <si>
+    <t>I will hurry to and return back in the evening to finish the chores and to make porridge stronger I will add honey, milk and oranges</t>
+  </si>
+  <si>
+    <t>The bus is keeping us together</t>
+  </si>
+  <si>
+    <t>I will add ODI and porridge to make it stronger and If the chores are heavy I will wake up very early in morning</t>
+  </si>
+  <si>
+    <t>The bus is bringing us together</t>
+  </si>
+  <si>
+    <t>Lack of preparation confidence/skills Taste preference barriers</t>
+  </si>
+  <si>
+    <t>High expectations from the learners especially the need for t-shirts</t>
+  </si>
+  <si>
+    <t>The activation influenced the club members to commit to establishing vegetable gardens in their homes to help in nutrition and commercial purposes, it also helped learners to exercise their reading skills</t>
+  </si>
+  <si>
+    <t>Time management. So that learners are able to catch up with their lessons</t>
+  </si>
+  <si>
+    <t>We commit to allocate funds for buying seedlings for the school vegetable garden so as to improve the nutrition  levels  and boost the learners body immunities</t>
+  </si>
+  <si>
+    <t>Key to note, in the future the reading books should be left for the pupils because they expected the books to remain with them for reading practice</t>
+  </si>
+  <si>
+    <t>cb76b65c-2070-4518-905d-28ab3fa2963a</t>
+  </si>
+  <si>
+    <t>uuid:cb76b65c-2070-4518-905d-28ab3fa2963a</t>
+  </si>
+  <si>
+    <t>KATHILE P/S</t>
+  </si>
+  <si>
+    <t>On the wall of the headteachers office</t>
+  </si>
+  <si>
+    <t>The school nutrition club was inactive but it was reactivated prior to school bus activation</t>
+  </si>
+  <si>
+    <t>43765118-2ea1-4199-ab81-a69caf2af8c3</t>
+  </si>
+  <si>
+    <t>uuid:43765118-2ea1-4199-ab81-a69caf2af8c3</t>
   </si>
 </sst>
 </file>
@@ -4802,8 +5054,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFF46" totalsRowShown="0">
-  <autoFilter ref="A1:AFF46" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFF53" totalsRowShown="0">
+  <autoFilter ref="A1:AFF53" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="838">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -5935,7 +6187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFF46"/>
+  <dimension ref="A1:AFF53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -20345,6 +20597,1585 @@
         <v>45</v>
       </c>
     </row>
+    <row r="47" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B47" t="s">
+        <v>706</v>
+      </c>
+      <c r="C47" t="s">
+        <v>951</v>
+      </c>
+      <c r="D47" t="s">
+        <v>589</v>
+      </c>
+      <c r="E47" t="s">
+        <v>709</v>
+      </c>
+      <c r="N47" t="s">
+        <v>1567</v>
+      </c>
+      <c r="P47">
+        <v>3</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47" t="s">
+        <v>711</v>
+      </c>
+      <c r="S47">
+        <v>2</v>
+      </c>
+      <c r="T47">
+        <v>1</v>
+      </c>
+      <c r="U47">
+        <v>2</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47" t="s">
+        <v>711</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>1568</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>782</v>
+      </c>
+      <c r="AH47">
+        <v>1</v>
+      </c>
+      <c r="AI47">
+        <v>1</v>
+      </c>
+      <c r="AJ47">
+        <v>1</v>
+      </c>
+      <c r="AK47">
+        <v>1</v>
+      </c>
+      <c r="AL47">
+        <v>1</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>783</v>
+      </c>
+      <c r="AN47">
+        <v>1</v>
+      </c>
+      <c r="AO47">
+        <v>1</v>
+      </c>
+      <c r="AP47">
+        <v>1</v>
+      </c>
+      <c r="AQ47" t="s">
+        <v>1569</v>
+      </c>
+      <c r="AR47" t="s">
+        <v>720</v>
+      </c>
+      <c r="AT47" t="s">
+        <v>782</v>
+      </c>
+      <c r="AU47">
+        <v>1</v>
+      </c>
+      <c r="AV47">
+        <v>1</v>
+      </c>
+      <c r="AW47">
+        <v>1</v>
+      </c>
+      <c r="AX47">
+        <v>1</v>
+      </c>
+      <c r="AY47">
+        <v>1</v>
+      </c>
+      <c r="AZ47" t="s">
+        <v>783</v>
+      </c>
+      <c r="BA47">
+        <v>1</v>
+      </c>
+      <c r="BB47">
+        <v>1</v>
+      </c>
+      <c r="BC47">
+        <v>1</v>
+      </c>
+      <c r="BD47" t="s">
+        <v>1570</v>
+      </c>
+      <c r="BE47" t="s">
+        <v>720</v>
+      </c>
+      <c r="BG47" t="s">
+        <v>782</v>
+      </c>
+      <c r="BH47">
+        <v>1</v>
+      </c>
+      <c r="BI47">
+        <v>1</v>
+      </c>
+      <c r="BJ47">
+        <v>1</v>
+      </c>
+      <c r="BK47">
+        <v>1</v>
+      </c>
+      <c r="BL47">
+        <v>1</v>
+      </c>
+      <c r="BM47" t="s">
+        <v>783</v>
+      </c>
+      <c r="BN47">
+        <v>1</v>
+      </c>
+      <c r="BO47">
+        <v>1</v>
+      </c>
+      <c r="BP47">
+        <v>1</v>
+      </c>
+      <c r="BQ47" t="s">
+        <v>1571</v>
+      </c>
+      <c r="BR47" t="s">
+        <v>720</v>
+      </c>
+      <c r="BT47" t="s">
+        <v>782</v>
+      </c>
+      <c r="BU47">
+        <v>1</v>
+      </c>
+      <c r="BV47">
+        <v>1</v>
+      </c>
+      <c r="BW47">
+        <v>1</v>
+      </c>
+      <c r="BX47">
+        <v>1</v>
+      </c>
+      <c r="BY47">
+        <v>1</v>
+      </c>
+      <c r="BZ47" t="s">
+        <v>783</v>
+      </c>
+      <c r="CA47">
+        <v>1</v>
+      </c>
+      <c r="CB47">
+        <v>1</v>
+      </c>
+      <c r="CC47">
+        <v>1</v>
+      </c>
+      <c r="CD47" t="s">
+        <v>1572</v>
+      </c>
+      <c r="CE47" t="s">
+        <v>716</v>
+      </c>
+      <c r="CG47" t="s">
+        <v>782</v>
+      </c>
+      <c r="CH47">
+        <v>1</v>
+      </c>
+      <c r="CI47">
+        <v>1</v>
+      </c>
+      <c r="CJ47">
+        <v>1</v>
+      </c>
+      <c r="CK47">
+        <v>1</v>
+      </c>
+      <c r="CL47">
+        <v>1</v>
+      </c>
+      <c r="CM47" t="s">
+        <v>783</v>
+      </c>
+      <c r="CN47">
+        <v>1</v>
+      </c>
+      <c r="CO47">
+        <v>1</v>
+      </c>
+      <c r="CP47">
+        <v>1</v>
+      </c>
+      <c r="CQ47" t="s">
+        <v>1573</v>
+      </c>
+      <c r="CR47" t="s">
+        <v>720</v>
+      </c>
+      <c r="CT47" t="s">
+        <v>782</v>
+      </c>
+      <c r="CU47">
+        <v>1</v>
+      </c>
+      <c r="CV47">
+        <v>1</v>
+      </c>
+      <c r="CW47">
+        <v>1</v>
+      </c>
+      <c r="CX47">
+        <v>1</v>
+      </c>
+      <c r="CY47">
+        <v>1</v>
+      </c>
+      <c r="CZ47" t="s">
+        <v>783</v>
+      </c>
+      <c r="DA47">
+        <v>1</v>
+      </c>
+      <c r="DB47">
+        <v>1</v>
+      </c>
+      <c r="DC47">
+        <v>1</v>
+      </c>
+      <c r="DD47" t="s">
+        <v>1574</v>
+      </c>
+      <c r="DE47" t="s">
+        <v>720</v>
+      </c>
+      <c r="DF47" t="s">
+        <v>1167</v>
+      </c>
+      <c r="DG47">
+        <v>1</v>
+      </c>
+      <c r="DH47">
+        <v>1</v>
+      </c>
+      <c r="DI47">
+        <v>1</v>
+      </c>
+      <c r="DJ47">
+        <v>1</v>
+      </c>
+      <c r="DK47">
+        <v>1</v>
+      </c>
+      <c r="DL47">
+        <v>1</v>
+      </c>
+      <c r="DM47">
+        <v>1</v>
+      </c>
+      <c r="DN47">
+        <v>1</v>
+      </c>
+      <c r="DO47">
+        <v>1</v>
+      </c>
+      <c r="DP47" t="s">
+        <v>732</v>
+      </c>
+      <c r="EI47">
+        <v>2</v>
+      </c>
+      <c r="EK47">
+        <v>2</v>
+      </c>
+      <c r="EM47">
+        <v>3</v>
+      </c>
+      <c r="SC47" s="1"/>
+      <c r="UG47" t="s">
+        <v>1149</v>
+      </c>
+      <c r="ZK47" s="1"/>
+      <c r="ADN47" s="1"/>
+      <c r="ADV47" s="1"/>
+      <c r="ADZ47" s="1"/>
+      <c r="AEX47">
+        <v>888660682</v>
+      </c>
+      <c r="AEY47" t="s">
+        <v>1575</v>
+      </c>
+      <c r="AEZ47" s="1">
+        <v>46303.340243055558</v>
+      </c>
+      <c r="AFB47" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD47" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE47" t="s">
+        <v>1577</v>
+      </c>
+      <c r="AFF47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B48" t="s">
+        <v>965</v>
+      </c>
+      <c r="D48" t="s">
+        <v>589</v>
+      </c>
+      <c r="E48" t="s">
+        <v>752</v>
+      </c>
+      <c r="N48" t="s">
+        <v>1567</v>
+      </c>
+      <c r="EN48" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT48">
+        <v>254</v>
+      </c>
+      <c r="FU48">
+        <v>163</v>
+      </c>
+      <c r="FV48">
+        <v>49</v>
+      </c>
+      <c r="FW48">
+        <v>45</v>
+      </c>
+      <c r="FY48">
+        <v>125</v>
+      </c>
+      <c r="FZ48">
+        <v>143</v>
+      </c>
+      <c r="GA48">
+        <v>19</v>
+      </c>
+      <c r="GB48">
+        <v>20</v>
+      </c>
+      <c r="GD48">
+        <v>178</v>
+      </c>
+      <c r="GE48">
+        <v>160</v>
+      </c>
+      <c r="GF48">
+        <v>39</v>
+      </c>
+      <c r="GG48">
+        <v>32</v>
+      </c>
+      <c r="GI48">
+        <v>8</v>
+      </c>
+      <c r="GJ48">
+        <v>6</v>
+      </c>
+      <c r="GK48">
+        <v>0</v>
+      </c>
+      <c r="GL48">
+        <v>0</v>
+      </c>
+      <c r="GN48">
+        <v>0</v>
+      </c>
+      <c r="GO48">
+        <v>0</v>
+      </c>
+      <c r="GP48">
+        <v>0</v>
+      </c>
+      <c r="GQ48">
+        <v>0</v>
+      </c>
+      <c r="GR48" t="s">
+        <v>1103</v>
+      </c>
+      <c r="GS48">
+        <v>1</v>
+      </c>
+      <c r="GT48">
+        <v>1</v>
+      </c>
+      <c r="GU48">
+        <v>1</v>
+      </c>
+      <c r="GV48">
+        <v>1</v>
+      </c>
+      <c r="GW48">
+        <v>1</v>
+      </c>
+      <c r="GX48">
+        <v>1</v>
+      </c>
+      <c r="GY48">
+        <v>1</v>
+      </c>
+      <c r="GZ48" t="s">
+        <v>1578</v>
+      </c>
+      <c r="HA48">
+        <v>1</v>
+      </c>
+      <c r="HB48">
+        <v>1</v>
+      </c>
+      <c r="HC48">
+        <v>1</v>
+      </c>
+      <c r="HD48">
+        <v>1</v>
+      </c>
+      <c r="HE48">
+        <v>1</v>
+      </c>
+      <c r="HF48" t="s">
+        <v>1579</v>
+      </c>
+      <c r="HG48" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH48" t="s">
+        <v>1580</v>
+      </c>
+      <c r="HI48" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ48" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL48" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM48" t="s">
+        <v>1581</v>
+      </c>
+      <c r="HT48" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU48">
+        <v>53</v>
+      </c>
+      <c r="HV48" t="s">
+        <v>1582</v>
+      </c>
+      <c r="HX48" t="s">
+        <v>766</v>
+      </c>
+      <c r="HY48">
+        <v>60</v>
+      </c>
+      <c r="HZ48" t="s">
+        <v>1583</v>
+      </c>
+      <c r="IB48" t="s">
+        <v>766</v>
+      </c>
+      <c r="IC48">
+        <v>48</v>
+      </c>
+      <c r="ID48" t="s">
+        <v>1584</v>
+      </c>
+      <c r="IF48" t="s">
+        <v>766</v>
+      </c>
+      <c r="IG48">
+        <v>62</v>
+      </c>
+      <c r="IH48" t="s">
+        <v>1585</v>
+      </c>
+      <c r="IJ48" t="s">
+        <v>766</v>
+      </c>
+      <c r="IK48">
+        <v>54</v>
+      </c>
+      <c r="IL48" t="s">
+        <v>1586</v>
+      </c>
+      <c r="IV48" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW48" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX48" t="s">
+        <v>1587</v>
+      </c>
+      <c r="IY48" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ48" t="s">
+        <v>1588</v>
+      </c>
+      <c r="JA48" t="s">
+        <v>716</v>
+      </c>
+      <c r="JC48" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD48" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE48" t="s">
+        <v>1589</v>
+      </c>
+      <c r="JF48" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG48" t="s">
+        <v>1590</v>
+      </c>
+      <c r="JH48" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ48" t="s">
+        <v>835</v>
+      </c>
+      <c r="JK48" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL48" t="s">
+        <v>1591</v>
+      </c>
+      <c r="JM48" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN48" t="s">
+        <v>1592</v>
+      </c>
+      <c r="JO48" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ48" t="s">
+        <v>835</v>
+      </c>
+      <c r="JR48" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JS48" t="s">
+        <v>1593</v>
+      </c>
+      <c r="JT48" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU48" t="s">
+        <v>1594</v>
+      </c>
+      <c r="JV48" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX48" t="s">
+        <v>835</v>
+      </c>
+      <c r="JY48" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ48" t="s">
+        <v>1595</v>
+      </c>
+      <c r="KA48" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB48" t="s">
+        <v>1596</v>
+      </c>
+      <c r="KC48" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE48" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF48" t="s">
+        <v>769</v>
+      </c>
+      <c r="KG48" t="s">
+        <v>1597</v>
+      </c>
+      <c r="KH48" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI48" t="s">
+        <v>1598</v>
+      </c>
+      <c r="KJ48" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK48" t="s">
+        <v>1148</v>
+      </c>
+      <c r="KL48">
+        <v>0</v>
+      </c>
+      <c r="KM48">
+        <v>0</v>
+      </c>
+      <c r="KN48">
+        <v>1</v>
+      </c>
+      <c r="KO48">
+        <v>0</v>
+      </c>
+      <c r="KQ48" t="s">
+        <v>1149</v>
+      </c>
+      <c r="KR48" t="s">
+        <v>1599</v>
+      </c>
+      <c r="KS48" t="s">
+        <v>1600</v>
+      </c>
+      <c r="KT48" t="s">
+        <v>1149</v>
+      </c>
+      <c r="NO48">
+        <v>254</v>
+      </c>
+      <c r="NP48">
+        <v>163</v>
+      </c>
+      <c r="NR48">
+        <v>125</v>
+      </c>
+      <c r="NS48">
+        <v>146</v>
+      </c>
+      <c r="NU48">
+        <v>178</v>
+      </c>
+      <c r="NV48">
+        <v>160</v>
+      </c>
+      <c r="SC48" s="1"/>
+      <c r="UG48" t="s">
+        <v>1149</v>
+      </c>
+      <c r="ZK48" s="1"/>
+      <c r="ADN48" s="1"/>
+      <c r="ADV48" s="1"/>
+      <c r="ADZ48" s="1"/>
+      <c r="AEX48">
+        <v>888693909</v>
+      </c>
+      <c r="AEY48" t="s">
+        <v>1601</v>
+      </c>
+      <c r="AEZ48" s="1">
+        <v>46303.364583333343</v>
+      </c>
+      <c r="AFB48" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD48" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE48" t="s">
+        <v>1602</v>
+      </c>
+      <c r="AFF48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D49" t="s">
+        <v>592</v>
+      </c>
+      <c r="E49" t="s">
+        <v>752</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1603</v>
+      </c>
+      <c r="EN49" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO49">
+        <v>892</v>
+      </c>
+      <c r="EP49">
+        <v>705</v>
+      </c>
+      <c r="EQ49" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER49" t="s">
+        <v>1157</v>
+      </c>
+      <c r="ES49">
+        <v>0</v>
+      </c>
+      <c r="ET49">
+        <v>1</v>
+      </c>
+      <c r="EU49">
+        <v>0</v>
+      </c>
+      <c r="EV49">
+        <v>1</v>
+      </c>
+      <c r="EW49">
+        <v>0</v>
+      </c>
+      <c r="EX49">
+        <v>0</v>
+      </c>
+      <c r="EZ49" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA49">
+        <v>30</v>
+      </c>
+      <c r="FB49" t="s">
+        <v>1069</v>
+      </c>
+      <c r="FC49">
+        <v>0</v>
+      </c>
+      <c r="FD49">
+        <v>1</v>
+      </c>
+      <c r="FE49">
+        <v>1</v>
+      </c>
+      <c r="FF49" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG49" t="s">
+        <v>1604</v>
+      </c>
+      <c r="FH49" t="s">
+        <v>732</v>
+      </c>
+      <c r="NO49">
+        <v>560</v>
+      </c>
+      <c r="NP49">
+        <v>492</v>
+      </c>
+      <c r="NR49">
+        <v>180</v>
+      </c>
+      <c r="NS49">
+        <v>134</v>
+      </c>
+      <c r="NU49">
+        <v>81</v>
+      </c>
+      <c r="NV49">
+        <v>38</v>
+      </c>
+      <c r="SC49" s="1"/>
+      <c r="UG49" t="s">
+        <v>1605</v>
+      </c>
+      <c r="ZK49" s="1"/>
+      <c r="ADN49" s="1"/>
+      <c r="ADV49" s="1"/>
+      <c r="ADZ49" s="1"/>
+      <c r="AEX49">
+        <v>888703239</v>
+      </c>
+      <c r="AEY49" t="s">
+        <v>1606</v>
+      </c>
+      <c r="AEZ49" s="1">
+        <v>46303.371145833327</v>
+      </c>
+      <c r="AFB49" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD49" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE49" t="s">
+        <v>1607</v>
+      </c>
+      <c r="AFF49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B50" t="s">
+        <v>706</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D50" t="s">
+        <v>590</v>
+      </c>
+      <c r="E50" t="s">
+        <v>752</v>
+      </c>
+      <c r="L50" t="s">
+        <v>1609</v>
+      </c>
+      <c r="EN50" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO50">
+        <v>788</v>
+      </c>
+      <c r="EP50">
+        <v>447</v>
+      </c>
+      <c r="EQ50" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER50" t="s">
+        <v>1393</v>
+      </c>
+      <c r="ES50">
+        <v>0</v>
+      </c>
+      <c r="ET50">
+        <v>1</v>
+      </c>
+      <c r="EU50">
+        <v>0</v>
+      </c>
+      <c r="EV50">
+        <v>0</v>
+      </c>
+      <c r="EW50">
+        <v>1</v>
+      </c>
+      <c r="EX50">
+        <v>0</v>
+      </c>
+      <c r="EZ50" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA50">
+        <v>60</v>
+      </c>
+      <c r="FB50" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC50">
+        <v>1</v>
+      </c>
+      <c r="FD50">
+        <v>1</v>
+      </c>
+      <c r="FE50">
+        <v>1</v>
+      </c>
+      <c r="FF50" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG50" t="s">
+        <v>1610</v>
+      </c>
+      <c r="FH50" t="s">
+        <v>732</v>
+      </c>
+      <c r="NO50">
+        <v>589</v>
+      </c>
+      <c r="NP50">
+        <v>254</v>
+      </c>
+      <c r="NR50">
+        <v>109</v>
+      </c>
+      <c r="NS50">
+        <v>113</v>
+      </c>
+      <c r="NU50">
+        <v>90</v>
+      </c>
+      <c r="NV50">
+        <v>80</v>
+      </c>
+      <c r="SC50" s="1"/>
+      <c r="UG50" t="s">
+        <v>1611</v>
+      </c>
+      <c r="ZK50" s="1"/>
+      <c r="ADN50" s="1"/>
+      <c r="ADV50" s="1"/>
+      <c r="ADZ50" s="1"/>
+      <c r="AEX50">
+        <v>888730918</v>
+      </c>
+      <c r="AEY50" t="s">
+        <v>1612</v>
+      </c>
+      <c r="AEZ50" s="1">
+        <v>46303.39203703704</v>
+      </c>
+      <c r="AFB50" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD50" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE50" t="s">
+        <v>1613</v>
+      </c>
+      <c r="AFF50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B51" t="s">
+        <v>706</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D51" t="s">
+        <v>590</v>
+      </c>
+      <c r="E51" t="s">
+        <v>752</v>
+      </c>
+      <c r="L51" t="s">
+        <v>1614</v>
+      </c>
+      <c r="EN51" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO51">
+        <v>1156</v>
+      </c>
+      <c r="EP51">
+        <v>784</v>
+      </c>
+      <c r="EQ51" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER51" t="s">
+        <v>1393</v>
+      </c>
+      <c r="ES51">
+        <v>0</v>
+      </c>
+      <c r="ET51">
+        <v>1</v>
+      </c>
+      <c r="EU51">
+        <v>0</v>
+      </c>
+      <c r="EV51">
+        <v>0</v>
+      </c>
+      <c r="EW51">
+        <v>1</v>
+      </c>
+      <c r="EX51">
+        <v>0</v>
+      </c>
+      <c r="EZ51" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA51">
+        <v>60</v>
+      </c>
+      <c r="FB51" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC51">
+        <v>1</v>
+      </c>
+      <c r="FD51">
+        <v>1</v>
+      </c>
+      <c r="FE51">
+        <v>1</v>
+      </c>
+      <c r="FF51" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG51" t="s">
+        <v>1615</v>
+      </c>
+      <c r="FH51" t="s">
+        <v>732</v>
+      </c>
+      <c r="NO51">
+        <v>490</v>
+      </c>
+      <c r="NP51">
+        <v>355</v>
+      </c>
+      <c r="NR51">
+        <v>315</v>
+      </c>
+      <c r="NS51">
+        <v>200</v>
+      </c>
+      <c r="NU51">
+        <v>309</v>
+      </c>
+      <c r="NV51">
+        <v>180</v>
+      </c>
+      <c r="SC51" s="1"/>
+      <c r="UG51" t="s">
+        <v>1616</v>
+      </c>
+      <c r="ZK51" s="1"/>
+      <c r="ADN51" s="1"/>
+      <c r="ADV51" s="1"/>
+      <c r="ADZ51" s="1"/>
+      <c r="AEX51">
+        <v>889036553</v>
+      </c>
+      <c r="AEY51" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AEZ51" s="1">
+        <v>46303.623703703714</v>
+      </c>
+      <c r="AFB51" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD51" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE51" t="s">
+        <v>1618</v>
+      </c>
+      <c r="AFF51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D52" t="s">
+        <v>592</v>
+      </c>
+      <c r="E52" t="s">
+        <v>752</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1603</v>
+      </c>
+      <c r="EN52" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT52">
+        <v>250</v>
+      </c>
+      <c r="FU52">
+        <v>150</v>
+      </c>
+      <c r="FV52">
+        <v>0</v>
+      </c>
+      <c r="FW52">
+        <v>0</v>
+      </c>
+      <c r="FY52">
+        <v>120</v>
+      </c>
+      <c r="FZ52">
+        <v>95</v>
+      </c>
+      <c r="GA52">
+        <v>0</v>
+      </c>
+      <c r="GB52">
+        <v>0</v>
+      </c>
+      <c r="GD52">
+        <v>70</v>
+      </c>
+      <c r="GE52">
+        <v>30</v>
+      </c>
+      <c r="GF52">
+        <v>0</v>
+      </c>
+      <c r="GG52">
+        <v>0</v>
+      </c>
+      <c r="GI52">
+        <v>3</v>
+      </c>
+      <c r="GJ52">
+        <v>1</v>
+      </c>
+      <c r="GK52">
+        <v>0</v>
+      </c>
+      <c r="GL52">
+        <v>0</v>
+      </c>
+      <c r="GN52">
+        <v>0</v>
+      </c>
+      <c r="GO52">
+        <v>0</v>
+      </c>
+      <c r="GP52">
+        <v>0</v>
+      </c>
+      <c r="GQ52">
+        <v>0</v>
+      </c>
+      <c r="GR52" t="s">
+        <v>1406</v>
+      </c>
+      <c r="GS52">
+        <v>1</v>
+      </c>
+      <c r="GT52">
+        <v>1</v>
+      </c>
+      <c r="GU52">
+        <v>1</v>
+      </c>
+      <c r="GV52">
+        <v>1</v>
+      </c>
+      <c r="GW52">
+        <v>1</v>
+      </c>
+      <c r="GX52">
+        <v>0</v>
+      </c>
+      <c r="GY52">
+        <v>1</v>
+      </c>
+      <c r="GZ52" t="s">
+        <v>1323</v>
+      </c>
+      <c r="HA52">
+        <v>1</v>
+      </c>
+      <c r="HB52">
+        <v>1</v>
+      </c>
+      <c r="HC52">
+        <v>0</v>
+      </c>
+      <c r="HD52">
+        <v>1</v>
+      </c>
+      <c r="HE52">
+        <v>0</v>
+      </c>
+      <c r="HG52" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH52" t="s">
+        <v>1619</v>
+      </c>
+      <c r="HI52" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ52" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL52" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM52" t="s">
+        <v>1620</v>
+      </c>
+      <c r="HT52" t="s">
+        <v>765</v>
+      </c>
+      <c r="HU52">
+        <v>21</v>
+      </c>
+      <c r="HV52" t="s">
+        <v>1621</v>
+      </c>
+      <c r="HX52" t="s">
+        <v>765</v>
+      </c>
+      <c r="HY52">
+        <v>21</v>
+      </c>
+      <c r="HZ52" t="s">
+        <v>1622</v>
+      </c>
+      <c r="IB52" t="s">
+        <v>765</v>
+      </c>
+      <c r="IC52">
+        <v>21</v>
+      </c>
+      <c r="ID52" t="s">
+        <v>1623</v>
+      </c>
+      <c r="IF52" t="s">
+        <v>765</v>
+      </c>
+      <c r="IG52">
+        <v>18</v>
+      </c>
+      <c r="IH52" t="s">
+        <v>1624</v>
+      </c>
+      <c r="IJ52" t="s">
+        <v>765</v>
+      </c>
+      <c r="IK52">
+        <v>21</v>
+      </c>
+      <c r="IL52" t="s">
+        <v>1625</v>
+      </c>
+      <c r="IV52" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW52" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX52" t="s">
+        <v>1626</v>
+      </c>
+      <c r="IY52" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ52" t="s">
+        <v>1627</v>
+      </c>
+      <c r="JA52" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC52" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD52" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE52" t="s">
+        <v>1628</v>
+      </c>
+      <c r="JF52" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG52" t="s">
+        <v>1629</v>
+      </c>
+      <c r="JH52" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ52" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK52" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL52" t="s">
+        <v>1630</v>
+      </c>
+      <c r="JM52" t="s">
+        <v>839</v>
+      </c>
+      <c r="JN52" t="s">
+        <v>1631</v>
+      </c>
+      <c r="JO52" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ52" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR52" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS52" t="s">
+        <v>1632</v>
+      </c>
+      <c r="JT52" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU52" t="s">
+        <v>1633</v>
+      </c>
+      <c r="JV52" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX52" t="s">
+        <v>835</v>
+      </c>
+      <c r="JY52" t="s">
+        <v>879</v>
+      </c>
+      <c r="JZ52" t="s">
+        <v>1634</v>
+      </c>
+      <c r="KA52" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB52" t="s">
+        <v>1635</v>
+      </c>
+      <c r="KC52" t="s">
+        <v>720</v>
+      </c>
+      <c r="KE52" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF52" t="s">
+        <v>879</v>
+      </c>
+      <c r="KG52" t="s">
+        <v>1636</v>
+      </c>
+      <c r="KH52" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI52" t="s">
+        <v>1637</v>
+      </c>
+      <c r="KJ52" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK52" t="s">
+        <v>1638</v>
+      </c>
+      <c r="KL52">
+        <v>1</v>
+      </c>
+      <c r="KM52">
+        <v>1</v>
+      </c>
+      <c r="KN52">
+        <v>0</v>
+      </c>
+      <c r="KO52">
+        <v>0</v>
+      </c>
+      <c r="KP52" t="s">
+        <v>842</v>
+      </c>
+      <c r="KQ52" t="s">
+        <v>1639</v>
+      </c>
+      <c r="KR52" t="s">
+        <v>1640</v>
+      </c>
+      <c r="KS52" t="s">
+        <v>1641</v>
+      </c>
+      <c r="KT52" t="s">
+        <v>1642</v>
+      </c>
+      <c r="NO52">
+        <v>560</v>
+      </c>
+      <c r="NP52">
+        <v>492</v>
+      </c>
+      <c r="NR52">
+        <v>180</v>
+      </c>
+      <c r="NS52">
+        <v>134</v>
+      </c>
+      <c r="NU52">
+        <v>81</v>
+      </c>
+      <c r="NV52">
+        <v>38</v>
+      </c>
+      <c r="SC52" s="1"/>
+      <c r="UG52" t="s">
+        <v>1643</v>
+      </c>
+      <c r="ZK52" s="1"/>
+      <c r="ADN52" s="1"/>
+      <c r="ADV52" s="1"/>
+      <c r="ADZ52" s="1"/>
+      <c r="AEX52">
+        <v>889131552</v>
+      </c>
+      <c r="AEY52" t="s">
+        <v>1644</v>
+      </c>
+      <c r="AEZ52" s="1">
+        <v>46303.706770833327</v>
+      </c>
+      <c r="AFB52" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD52" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE52" t="s">
+        <v>1645</v>
+      </c>
+      <c r="AFF52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D53" t="s">
+        <v>592</v>
+      </c>
+      <c r="E53" t="s">
+        <v>752</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1646</v>
+      </c>
+      <c r="EN53" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO53">
+        <v>913</v>
+      </c>
+      <c r="EP53">
+        <v>570</v>
+      </c>
+      <c r="EQ53" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER53" t="s">
+        <v>1393</v>
+      </c>
+      <c r="ES53">
+        <v>0</v>
+      </c>
+      <c r="ET53">
+        <v>1</v>
+      </c>
+      <c r="EU53">
+        <v>0</v>
+      </c>
+      <c r="EV53">
+        <v>0</v>
+      </c>
+      <c r="EW53">
+        <v>1</v>
+      </c>
+      <c r="EX53">
+        <v>0</v>
+      </c>
+      <c r="EZ53" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA53">
+        <v>30</v>
+      </c>
+      <c r="FB53" t="s">
+        <v>1069</v>
+      </c>
+      <c r="FC53">
+        <v>0</v>
+      </c>
+      <c r="FD53">
+        <v>1</v>
+      </c>
+      <c r="FE53">
+        <v>1</v>
+      </c>
+      <c r="FF53" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG53" t="s">
+        <v>1647</v>
+      </c>
+      <c r="FH53" t="s">
+        <v>732</v>
+      </c>
+      <c r="NO53">
+        <v>251</v>
+      </c>
+      <c r="NP53">
+        <v>237</v>
+      </c>
+      <c r="NR53">
+        <v>64</v>
+      </c>
+      <c r="NS53">
+        <v>62</v>
+      </c>
+      <c r="NU53">
+        <v>67</v>
+      </c>
+      <c r="NV53">
+        <v>42</v>
+      </c>
+      <c r="SC53" s="1"/>
+      <c r="UG53" t="s">
+        <v>1648</v>
+      </c>
+      <c r="ZK53" s="1"/>
+      <c r="ADN53" s="1"/>
+      <c r="ADV53" s="1"/>
+      <c r="ADZ53" s="1"/>
+      <c r="AEX53">
+        <v>889137892</v>
+      </c>
+      <c r="AEY53" t="s">
+        <v>1649</v>
+      </c>
+      <c r="AEZ53" s="1">
+        <v>46303.713113425933</v>
+      </c>
+      <c r="AFB53" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD53" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE53" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AFF53">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4432CC1A-B7A7-D441-BE78-3BA88A4F0FF0}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F034419B-5147-C14A-99DF-283ADD9E4518}"/>
   <bookViews>
     <workbookView xWindow="3360" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="1651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="1701">
   <si>
     <t>Date</t>
   </si>
@@ -4973,6 +4973,156 @@
   </si>
   <si>
     <t>uuid:43765118-2ea1-4199-ab81-a69caf2af8c3</t>
+  </si>
+  <si>
+    <t>KALOSARICH P/S</t>
+  </si>
+  <si>
+    <t>Ajok consulate and Auma florence</t>
+  </si>
+  <si>
+    <t>Both in the classroom and outside</t>
+  </si>
+  <si>
+    <t>09:21:00.000+03:00</t>
+  </si>
+  <si>
+    <t>10:21:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing</t>
+  </si>
+  <si>
+    <t>Growing of greens,beans ,sorghum</t>
+  </si>
+  <si>
+    <t>Need for real local food stuff to be available</t>
+  </si>
+  <si>
+    <t>fef8a134-4112-41a7-9cad-d4fcd601dff2</t>
+  </si>
+  <si>
+    <t>uuid:fef8a134-4112-41a7-9cad-d4fcd601dff2</t>
+  </si>
+  <si>
+    <t>NAPUMPUM P/S</t>
+  </si>
+  <si>
+    <t>Okello haron and ayoo florence</t>
+  </si>
+  <si>
+    <t>Both inside and outside classroom</t>
+  </si>
+  <si>
+    <t>00:10:00.000+03:00</t>
+  </si>
+  <si>
+    <t>02:01:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Sorghum,beans nyebutyi</t>
+  </si>
+  <si>
+    <t>Involvement of parents</t>
+  </si>
+  <si>
+    <t>665d5e6a-69c5-452f-aa83-ce8a932bd763</t>
+  </si>
+  <si>
+    <t>uuid:665d5e6a-69c5-452f-aa83-ce8a932bd763</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Metu porridge supplementation demonstrated Structured dialogue on rebalancing chores Fair food portions for all genders Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>Nutri Club patron District cordinator Other</t>
+  </si>
+  <si>
+    <t>Deputy Headteacher</t>
+  </si>
+  <si>
+    <t>Learners actively participated in the games hands on</t>
+  </si>
+  <si>
+    <t>Because the session was engaging and interactive</t>
+  </si>
+  <si>
+    <t>It is because it will lead to early marriage, girls will end up dropping out of school, girls will end up getting pregnant at an early age</t>
+  </si>
+  <si>
+    <t>It is important so that we all make it early to class, so as to simplify work,</t>
+  </si>
+  <si>
+    <t>In order to simply work, to avoid quarrels at home, to make sure that we collect enough firewood, collecting firewood together is good because the food being cooked is for everyone</t>
+  </si>
+  <si>
+    <t>To reduce absenteeism from girls, to avoid girls from coming late to school, To improve on her performance in class, to prevent girls from being attacked by wrong doers along the way, to allow the girl to rest</t>
+  </si>
+  <si>
+    <t>To make sure that the girl gets back to school,  if I don't speak up the girl will end up getting pregnant at an early age, Because even a girl has a right to education</t>
+  </si>
+  <si>
+    <t>Both boys and girls should share household chores so that they'll be able to get to school on time</t>
+  </si>
+  <si>
+    <t>The bus brings us together and creates untiy</t>
+  </si>
+  <si>
+    <t>When gets heavy in the morning, I will first rush to school and then get back in the evening to finish the chores</t>
+  </si>
+  <si>
+    <t>The bus is important in uniting people together</t>
+  </si>
+  <si>
+    <t>I will tell people at home that, in order to make a stronger porridge, we need to use maize flour, water, sugar and milk</t>
+  </si>
+  <si>
+    <t>The bus puts us together</t>
+  </si>
+  <si>
+    <t>Workload sharing is key and paramount for a peaceful home</t>
+  </si>
+  <si>
+    <t>It is the bus that has brought us together</t>
+  </si>
+  <si>
+    <t>Sharing work simplifies it and makes us reach school early</t>
+  </si>
+  <si>
+    <t>It means that the bus brings us together</t>
+  </si>
+  <si>
+    <t>I will wake up early in the morning and finish the chores</t>
+  </si>
+  <si>
+    <t>The bus gathers us together</t>
+  </si>
+  <si>
+    <t>Lack of preparation confidence/skills Taste preference barriers Other</t>
+  </si>
+  <si>
+    <t>There is limited access to the cooking materials</t>
+  </si>
+  <si>
+    <t>The learners attendance during activation was low compared to the average weekly attendance because the activation happened in the afternoon and some of the lower primary pupils had left</t>
+  </si>
+  <si>
+    <t>The nutrition club was created successfully</t>
+  </si>
+  <si>
+    <t>Time management</t>
+  </si>
+  <si>
+    <t>We commit that we are going to support the nutribus campaign and empower our nutrition club members  to do the club activities effectively</t>
+  </si>
+  <si>
+    <t>There should always be prior mobilization of the schools and communities to ensure the targeted people participate .  This is because the teachers of kathile didn't attend orientation because the information didn't reach them on time but nonetheless they got oriented on the day of activation</t>
+  </si>
+  <si>
+    <t>e87fcc04-265d-417c-9a8e-9532a2870656</t>
+  </si>
+  <si>
+    <t>uuid:e87fcc04-265d-417c-9a8e-9532a2870656</t>
   </si>
 </sst>
 </file>
@@ -5054,8 +5204,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFF53" totalsRowShown="0">
-  <autoFilter ref="A1:AFF53" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFF56" totalsRowShown="0">
+  <autoFilter ref="A1:AFF56" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="838">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -6187,7 +6337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFF53"/>
+  <dimension ref="A1:AFF56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -22176,6 +22326,597 @@
         <v>52</v>
       </c>
     </row>
+    <row r="54" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B54" t="s">
+        <v>803</v>
+      </c>
+      <c r="D54" t="s">
+        <v>594</v>
+      </c>
+      <c r="E54" t="s">
+        <v>738</v>
+      </c>
+      <c r="I54" t="s">
+        <v>1651</v>
+      </c>
+      <c r="SC54" s="1"/>
+      <c r="SU54" t="s">
+        <v>740</v>
+      </c>
+      <c r="SV54">
+        <v>1</v>
+      </c>
+      <c r="SW54">
+        <v>0</v>
+      </c>
+      <c r="SX54" t="s">
+        <v>1652</v>
+      </c>
+      <c r="SY54">
+        <v>13</v>
+      </c>
+      <c r="SZ54">
+        <v>24</v>
+      </c>
+      <c r="TA54" t="s">
+        <v>1653</v>
+      </c>
+      <c r="TB54" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TC54" t="s">
+        <v>1654</v>
+      </c>
+      <c r="TD54" t="s">
+        <v>1655</v>
+      </c>
+      <c r="TE54">
+        <v>39</v>
+      </c>
+      <c r="TF54">
+        <v>31</v>
+      </c>
+      <c r="TG54">
+        <v>2</v>
+      </c>
+      <c r="TH54">
+        <v>4</v>
+      </c>
+      <c r="TI54" t="s">
+        <v>1656</v>
+      </c>
+      <c r="TJ54">
+        <v>0</v>
+      </c>
+      <c r="TK54">
+        <v>0</v>
+      </c>
+      <c r="TL54">
+        <v>1</v>
+      </c>
+      <c r="TM54">
+        <v>0</v>
+      </c>
+      <c r="TN54">
+        <v>0</v>
+      </c>
+      <c r="TO54" t="s">
+        <v>1657</v>
+      </c>
+      <c r="UG54" t="s">
+        <v>1658</v>
+      </c>
+      <c r="ZK54" s="1"/>
+      <c r="ADN54" s="1"/>
+      <c r="ADV54" s="1"/>
+      <c r="ADZ54" s="1"/>
+      <c r="AEX54">
+        <v>890222696</v>
+      </c>
+      <c r="AEY54" t="s">
+        <v>1659</v>
+      </c>
+      <c r="AEZ54" s="1">
+        <v>46305.225034722222</v>
+      </c>
+      <c r="AFB54" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD54" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE54" t="s">
+        <v>1660</v>
+      </c>
+      <c r="AFF54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B55" t="s">
+        <v>803</v>
+      </c>
+      <c r="D55" t="s">
+        <v>594</v>
+      </c>
+      <c r="E55" t="s">
+        <v>738</v>
+      </c>
+      <c r="I55" t="s">
+        <v>1661</v>
+      </c>
+      <c r="SC55" s="1"/>
+      <c r="SU55" t="s">
+        <v>740</v>
+      </c>
+      <c r="SV55">
+        <v>1</v>
+      </c>
+      <c r="SW55">
+        <v>0</v>
+      </c>
+      <c r="SX55" t="s">
+        <v>1662</v>
+      </c>
+      <c r="SY55">
+        <v>26</v>
+      </c>
+      <c r="SZ55">
+        <v>19</v>
+      </c>
+      <c r="TA55" t="s">
+        <v>1663</v>
+      </c>
+      <c r="TB55" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TC55" t="s">
+        <v>1664</v>
+      </c>
+      <c r="TD55" t="s">
+        <v>1665</v>
+      </c>
+      <c r="TE55">
+        <v>30</v>
+      </c>
+      <c r="TF55">
+        <v>25</v>
+      </c>
+      <c r="TG55">
+        <v>1</v>
+      </c>
+      <c r="TH55">
+        <v>1</v>
+      </c>
+      <c r="TI55" t="s">
+        <v>745</v>
+      </c>
+      <c r="TJ55">
+        <v>0</v>
+      </c>
+      <c r="TK55">
+        <v>0</v>
+      </c>
+      <c r="TL55">
+        <v>1</v>
+      </c>
+      <c r="TM55">
+        <v>1</v>
+      </c>
+      <c r="TN55">
+        <v>0</v>
+      </c>
+      <c r="TO55" t="s">
+        <v>1666</v>
+      </c>
+      <c r="UG55" t="s">
+        <v>1667</v>
+      </c>
+      <c r="ZK55" s="1"/>
+      <c r="ADN55" s="1"/>
+      <c r="ADV55" s="1"/>
+      <c r="ADZ55" s="1"/>
+      <c r="AEX55">
+        <v>890247399</v>
+      </c>
+      <c r="AEY55" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AEZ55" s="1">
+        <v>46305.244074074071</v>
+      </c>
+      <c r="AFB55" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD55" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE55" t="s">
+        <v>1669</v>
+      </c>
+      <c r="AFF55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:838" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D56" t="s">
+        <v>592</v>
+      </c>
+      <c r="E56" t="s">
+        <v>752</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1646</v>
+      </c>
+      <c r="EN56" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT56">
+        <v>50</v>
+      </c>
+      <c r="FU56">
+        <v>45</v>
+      </c>
+      <c r="FV56">
+        <v>0</v>
+      </c>
+      <c r="FW56">
+        <v>0</v>
+      </c>
+      <c r="FY56">
+        <v>60</v>
+      </c>
+      <c r="FZ56">
+        <v>55</v>
+      </c>
+      <c r="GA56">
+        <v>0</v>
+      </c>
+      <c r="GB56">
+        <v>0</v>
+      </c>
+      <c r="GD56">
+        <v>55</v>
+      </c>
+      <c r="GE56">
+        <v>39</v>
+      </c>
+      <c r="GF56">
+        <v>0</v>
+      </c>
+      <c r="GG56">
+        <v>0</v>
+      </c>
+      <c r="GI56">
+        <v>1</v>
+      </c>
+      <c r="GJ56">
+        <v>2</v>
+      </c>
+      <c r="GK56">
+        <v>0</v>
+      </c>
+      <c r="GL56">
+        <v>0</v>
+      </c>
+      <c r="GN56">
+        <v>0</v>
+      </c>
+      <c r="GO56">
+        <v>0</v>
+      </c>
+      <c r="GP56">
+        <v>0</v>
+      </c>
+      <c r="GQ56">
+        <v>0</v>
+      </c>
+      <c r="GR56" t="s">
+        <v>1670</v>
+      </c>
+      <c r="GS56">
+        <v>1</v>
+      </c>
+      <c r="GT56">
+        <v>0</v>
+      </c>
+      <c r="GU56">
+        <v>1</v>
+      </c>
+      <c r="GV56">
+        <v>1</v>
+      </c>
+      <c r="GW56">
+        <v>1</v>
+      </c>
+      <c r="GX56">
+        <v>0</v>
+      </c>
+      <c r="GY56">
+        <v>1</v>
+      </c>
+      <c r="GZ56" t="s">
+        <v>1671</v>
+      </c>
+      <c r="HA56">
+        <v>1</v>
+      </c>
+      <c r="HB56">
+        <v>0</v>
+      </c>
+      <c r="HC56">
+        <v>0</v>
+      </c>
+      <c r="HD56">
+        <v>1</v>
+      </c>
+      <c r="HE56">
+        <v>1</v>
+      </c>
+      <c r="HF56" t="s">
+        <v>1672</v>
+      </c>
+      <c r="HG56" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH56" t="s">
+        <v>1673</v>
+      </c>
+      <c r="HI56" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ56" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL56" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM56" t="s">
+        <v>1674</v>
+      </c>
+      <c r="HT56" t="s">
+        <v>765</v>
+      </c>
+      <c r="HU56">
+        <v>14</v>
+      </c>
+      <c r="HV56" t="s">
+        <v>1675</v>
+      </c>
+      <c r="HX56" t="s">
+        <v>765</v>
+      </c>
+      <c r="HY56">
+        <v>14</v>
+      </c>
+      <c r="HZ56" t="s">
+        <v>1676</v>
+      </c>
+      <c r="IB56" t="s">
+        <v>765</v>
+      </c>
+      <c r="IC56">
+        <v>14</v>
+      </c>
+      <c r="ID56" t="s">
+        <v>1677</v>
+      </c>
+      <c r="IF56" t="s">
+        <v>765</v>
+      </c>
+      <c r="IG56">
+        <v>8</v>
+      </c>
+      <c r="IH56" t="s">
+        <v>1678</v>
+      </c>
+      <c r="IJ56" t="s">
+        <v>765</v>
+      </c>
+      <c r="IK56">
+        <v>14</v>
+      </c>
+      <c r="IL56" t="s">
+        <v>1679</v>
+      </c>
+      <c r="IV56" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW56" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX56" t="s">
+        <v>1680</v>
+      </c>
+      <c r="IY56" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ56" t="s">
+        <v>1681</v>
+      </c>
+      <c r="JA56" t="s">
+        <v>716</v>
+      </c>
+      <c r="JC56" t="s">
+        <v>835</v>
+      </c>
+      <c r="JD56" t="s">
+        <v>879</v>
+      </c>
+      <c r="JE56" t="s">
+        <v>1682</v>
+      </c>
+      <c r="JF56" t="s">
+        <v>839</v>
+      </c>
+      <c r="JG56" t="s">
+        <v>1683</v>
+      </c>
+      <c r="JH56" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ56" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK56" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL56" t="s">
+        <v>1684</v>
+      </c>
+      <c r="JM56" t="s">
+        <v>839</v>
+      </c>
+      <c r="JN56" t="s">
+        <v>1685</v>
+      </c>
+      <c r="JO56" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ56" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR56" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS56" t="s">
+        <v>1686</v>
+      </c>
+      <c r="JT56" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU56" t="s">
+        <v>1687</v>
+      </c>
+      <c r="JV56" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX56" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY56" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ56" t="s">
+        <v>1688</v>
+      </c>
+      <c r="KA56" t="s">
+        <v>839</v>
+      </c>
+      <c r="KB56" t="s">
+        <v>1689</v>
+      </c>
+      <c r="KC56" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE56" t="s">
+        <v>837</v>
+      </c>
+      <c r="KF56" t="s">
+        <v>879</v>
+      </c>
+      <c r="KG56" t="s">
+        <v>1690</v>
+      </c>
+      <c r="KH56" t="s">
+        <v>839</v>
+      </c>
+      <c r="KI56" t="s">
+        <v>1691</v>
+      </c>
+      <c r="KJ56" t="s">
+        <v>720</v>
+      </c>
+      <c r="KK56" t="s">
+        <v>1692</v>
+      </c>
+      <c r="KL56">
+        <v>1</v>
+      </c>
+      <c r="KM56">
+        <v>1</v>
+      </c>
+      <c r="KN56">
+        <v>0</v>
+      </c>
+      <c r="KO56">
+        <v>1</v>
+      </c>
+      <c r="KP56" t="s">
+        <v>1693</v>
+      </c>
+      <c r="KQ56" t="s">
+        <v>1694</v>
+      </c>
+      <c r="KR56" t="s">
+        <v>1695</v>
+      </c>
+      <c r="KS56" t="s">
+        <v>1696</v>
+      </c>
+      <c r="KT56" t="s">
+        <v>1697</v>
+      </c>
+      <c r="NO56">
+        <v>251</v>
+      </c>
+      <c r="NP56">
+        <v>237</v>
+      </c>
+      <c r="NR56">
+        <v>64</v>
+      </c>
+      <c r="NS56">
+        <v>62</v>
+      </c>
+      <c r="NU56">
+        <v>67</v>
+      </c>
+      <c r="NV56">
+        <v>42</v>
+      </c>
+      <c r="SC56" s="1"/>
+      <c r="UG56" t="s">
+        <v>1698</v>
+      </c>
+      <c r="ZK56" s="1"/>
+      <c r="ADN56" s="1"/>
+      <c r="ADV56" s="1"/>
+      <c r="ADZ56" s="1"/>
+      <c r="AEX56">
+        <v>890950633</v>
+      </c>
+      <c r="AEY56" t="s">
+        <v>1699</v>
+      </c>
+      <c r="AEZ56" s="1">
+        <v>46306.242256944453</v>
+      </c>
+      <c r="AFB56" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFD56" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFE56" t="s">
+        <v>1700</v>
+      </c>
+      <c r="AFF56">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F034419B-5147-C14A-99DF-283ADD9E4518}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE9DD535-DABF-064F-9453-4D5836E63955}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2420" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nutribus 2.0 Activity" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="1701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3102" uniqueCount="1718">
   <si>
     <t>Date</t>
   </si>
@@ -5123,6 +5123,57 @@
   </si>
   <si>
     <t>uuid:e87fcc04-265d-417c-9a8e-9532a2870656</t>
+  </si>
+  <si>
+    <t>Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Limited access to the cooking materials</t>
+  </si>
+  <si>
+    <t>Monday Thursday</t>
+  </si>
+  <si>
+    <t>infront of main office and and compound</t>
+  </si>
+  <si>
+    <t>The pupil dont have dinning hall to eat hence children eat in classrooms andd under trees  at the compound wwhich iis risky with thunder</t>
+  </si>
+  <si>
+    <t>2dd6186c-a950-4126-9763-a416599a1d30</t>
+  </si>
+  <si>
+    <t>vAJE9CmMPc4o4KutAxpHv6</t>
+  </si>
+  <si>
+    <t>uuid:2dd6186c-a950-4126-9763-a416599a1d30</t>
+  </si>
+  <si>
+    <t>Activity shall be carried  out twice a week thats Mondy Thursday</t>
+  </si>
+  <si>
+    <t>Both have equal rights on eeducation</t>
+  </si>
+  <si>
+    <t>Both boys and giirls should  be given work at the same time</t>
+  </si>
+  <si>
+    <t>house chores should be  done by both men and  wometn</t>
+  </si>
+  <si>
+    <t>greens are good for our  diet at home too</t>
+  </si>
+  <si>
+    <t>its good to use energy saving cookkers beccause it saves time for classs</t>
+  </si>
+  <si>
+    <t>Its good to know of Wfp toll number so that we can call any time if we  need  their help</t>
+  </si>
+  <si>
+    <t>Climate-Smart Cooking One-Pager Manuals WFP Toll-Free Feedback Display Board</t>
+  </si>
+  <si>
+    <t>d802cd7c-ac85-48a9-a6a9-e3fe83a7d153</t>
+  </si>
+  <si>
+    <t>uuid:d802cd7c-ac85-48a9-a6a9-e3fe83a7d153</t>
   </si>
 </sst>
 </file>
@@ -5204,9 +5255,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFF56" totalsRowShown="0">
-  <autoFilter ref="A1:AFF56" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
-  <tableColumns count="838">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG58" totalsRowShown="0">
+  <autoFilter ref="A1:AFG58" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+  <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
     <tableColumn id="3" xr3:uid="{1A468597-D831-D84D-804A-CED0115BE04C}" name="Specify"/>
@@ -5508,6 +5559,7 @@
     <tableColumn id="299" xr3:uid="{128D3A95-D2A2-4142-BE28-3A4350C17525}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Taste preference barriers"/>
     <tableColumn id="300" xr3:uid="{EA034228-1858-8645-BA56-AB7DAC43B393}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Ingredients not prioritized at household level"/>
     <tableColumn id="301" xr3:uid="{78651C36-CF91-A443-BA61-7B223248FF9C}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Other"/>
+    <tableColumn id="839" xr3:uid="{A4F88C8E-2C4B-3F4C-AE45-612B8EE101E4}" name="Despite cash support or purchasing power, what is the primary reason for low uptake or lack of know-how regarding preparing WFP's Metu porridge?/Limited access to the cooking materials"/>
     <tableColumn id="302" xr3:uid="{14FBBFC7-B10D-DF43-8387-CC007AC1937C}" name="Specify12"/>
     <tableColumn id="303" xr3:uid="{90605ED0-952D-0C4D-B8B7-AD0F9E24E927}" name="Key delivery issue or barrier observed during activation"/>
     <tableColumn id="304" xr3:uid="{5EC5AE34-E0A7-1443-8361-097529342012}" name="Key success observed during activation"/>
@@ -6337,7 +6389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFF56"/>
+  <dimension ref="A1:AFG58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -6571,351 +6623,351 @@
     <col min="297" max="297" width="74" customWidth="1"/>
     <col min="298" max="299" width="85.6640625" customWidth="1"/>
     <col min="300" max="300" width="83.1640625" customWidth="1"/>
-    <col min="301" max="301" width="15.33203125" customWidth="1"/>
-    <col min="302" max="302" width="41" customWidth="1"/>
-    <col min="303" max="308" width="85.6640625" customWidth="1"/>
-    <col min="309" max="309" width="75.83203125" customWidth="1"/>
-    <col min="310" max="311" width="85.6640625" customWidth="1"/>
-    <col min="312" max="312" width="85" customWidth="1"/>
-    <col min="313" max="313" width="27.1640625" customWidth="1"/>
-    <col min="314" max="314" width="35.6640625" customWidth="1"/>
-    <col min="315" max="315" width="13.33203125" customWidth="1"/>
-    <col min="316" max="316" width="24" customWidth="1"/>
-    <col min="317" max="317" width="12.83203125" customWidth="1"/>
-    <col min="318" max="318" width="14.5" customWidth="1"/>
-    <col min="319" max="319" width="22" customWidth="1"/>
-    <col min="320" max="320" width="40.5" customWidth="1"/>
-    <col min="321" max="321" width="42.1640625" customWidth="1"/>
-    <col min="322" max="322" width="23.5" customWidth="1"/>
-    <col min="323" max="323" width="42.33203125" customWidth="1"/>
-    <col min="324" max="324" width="44" customWidth="1"/>
-    <col min="325" max="325" width="19" customWidth="1"/>
-    <col min="326" max="326" width="42.33203125" customWidth="1"/>
-    <col min="327" max="327" width="44" customWidth="1"/>
-    <col min="328" max="328" width="20.6640625" customWidth="1"/>
-    <col min="329" max="329" width="42.33203125" customWidth="1"/>
-    <col min="330" max="330" width="44" customWidth="1"/>
-    <col min="331" max="331" width="16.83203125" customWidth="1"/>
-    <col min="332" max="332" width="42.33203125" customWidth="1"/>
-    <col min="333" max="333" width="44" customWidth="1"/>
-    <col min="334" max="334" width="18.5" customWidth="1"/>
-    <col min="335" max="335" width="40.33203125" customWidth="1"/>
-    <col min="336" max="336" width="42" customWidth="1"/>
-    <col min="337" max="337" width="57.1640625" customWidth="1"/>
-    <col min="338" max="338" width="85.6640625" customWidth="1"/>
-    <col min="339" max="339" width="46.33203125" customWidth="1"/>
-    <col min="340" max="340" width="62.6640625" customWidth="1"/>
-    <col min="341" max="341" width="53.5" customWidth="1"/>
-    <col min="342" max="345" width="85.6640625" customWidth="1"/>
-    <col min="346" max="346" width="35.1640625" customWidth="1"/>
-    <col min="347" max="347" width="85" customWidth="1"/>
-    <col min="348" max="348" width="64.6640625" customWidth="1"/>
-    <col min="349" max="349" width="68.33203125" customWidth="1"/>
-    <col min="350" max="350" width="31" customWidth="1"/>
-    <col min="351" max="351" width="41.1640625" customWidth="1"/>
-    <col min="352" max="352" width="11.5" customWidth="1"/>
-    <col min="353" max="353" width="16.6640625" customWidth="1"/>
-    <col min="354" max="362" width="85.6640625" customWidth="1"/>
-    <col min="363" max="363" width="58.6640625" customWidth="1"/>
-    <col min="364" max="364" width="68.83203125" customWidth="1"/>
-    <col min="365" max="365" width="39.1640625" customWidth="1"/>
-    <col min="366" max="366" width="16.6640625" customWidth="1"/>
-    <col min="367" max="375" width="85.6640625" customWidth="1"/>
-    <col min="376" max="376" width="60.5" customWidth="1"/>
-    <col min="377" max="377" width="70.6640625" customWidth="1"/>
-    <col min="378" max="378" width="41" customWidth="1"/>
-    <col min="379" max="379" width="16.6640625" customWidth="1"/>
-    <col min="380" max="388" width="85.6640625" customWidth="1"/>
-    <col min="389" max="389" width="60.5" customWidth="1"/>
-    <col min="390" max="390" width="70.6640625" customWidth="1"/>
-    <col min="391" max="391" width="41" customWidth="1"/>
-    <col min="392" max="392" width="57.5" customWidth="1"/>
-    <col min="393" max="393" width="54" customWidth="1"/>
-    <col min="394" max="394" width="42.6640625" customWidth="1"/>
-    <col min="395" max="395" width="58.5" customWidth="1"/>
-    <col min="396" max="396" width="69" customWidth="1"/>
-    <col min="397" max="397" width="52.5" customWidth="1"/>
-    <col min="398" max="398" width="55.5" customWidth="1"/>
-    <col min="399" max="399" width="49" customWidth="1"/>
-    <col min="400" max="400" width="56.1640625" customWidth="1"/>
-    <col min="401" max="401" width="23.33203125" customWidth="1"/>
-    <col min="402" max="402" width="15.6640625" customWidth="1"/>
-    <col min="403" max="403" width="47" customWidth="1"/>
-    <col min="404" max="404" width="85.6640625" customWidth="1"/>
-    <col min="405" max="405" width="61.5" customWidth="1"/>
-    <col min="406" max="406" width="63.5" customWidth="1"/>
-    <col min="407" max="407" width="66.83203125" customWidth="1"/>
-    <col min="408" max="408" width="83.6640625" customWidth="1"/>
-    <col min="409" max="409" width="31.6640625" customWidth="1"/>
-    <col min="410" max="410" width="40.83203125" customWidth="1"/>
-    <col min="411" max="411" width="64.83203125" customWidth="1"/>
-    <col min="412" max="412" width="81.33203125" customWidth="1"/>
-    <col min="413" max="413" width="85.6640625" customWidth="1"/>
-    <col min="414" max="414" width="84.83203125" customWidth="1"/>
-    <col min="415" max="415" width="51.83203125" customWidth="1"/>
-    <col min="416" max="416" width="27.5" customWidth="1"/>
-    <col min="417" max="418" width="46.6640625" customWidth="1"/>
-    <col min="419" max="419" width="17.33203125" customWidth="1"/>
-    <col min="420" max="420" width="34.33203125" customWidth="1"/>
-    <col min="421" max="421" width="35.83203125" customWidth="1"/>
-    <col min="422" max="422" width="34.83203125" customWidth="1"/>
-    <col min="423" max="423" width="24.83203125" customWidth="1"/>
-    <col min="424" max="424" width="11" customWidth="1"/>
-    <col min="425" max="425" width="10.33203125" customWidth="1"/>
-    <col min="426" max="427" width="13.33203125" customWidth="1"/>
-    <col min="428" max="428" width="26.83203125" customWidth="1"/>
-    <col min="429" max="429" width="28.5" customWidth="1"/>
-    <col min="430" max="430" width="24.5" customWidth="1"/>
-    <col min="431" max="433" width="85.6640625" customWidth="1"/>
-    <col min="434" max="434" width="81" customWidth="1"/>
-    <col min="435" max="435" width="85.6640625" customWidth="1"/>
-    <col min="436" max="436" width="64.6640625" customWidth="1"/>
-    <col min="437" max="437" width="26.1640625" customWidth="1"/>
-    <col min="442" max="442" width="20.33203125" customWidth="1"/>
-    <col min="443" max="443" width="22" customWidth="1"/>
-    <col min="444" max="444" width="26.5" customWidth="1"/>
-    <col min="445" max="447" width="85.6640625" customWidth="1"/>
-    <col min="448" max="448" width="83" customWidth="1"/>
-    <col min="449" max="449" width="85.6640625" customWidth="1"/>
-    <col min="450" max="450" width="47.83203125" customWidth="1"/>
-    <col min="451" max="451" width="37.5" customWidth="1"/>
-    <col min="452" max="452" width="34.6640625" customWidth="1"/>
-    <col min="453" max="453" width="13.33203125" customWidth="1"/>
-    <col min="454" max="454" width="9" customWidth="1"/>
-    <col min="456" max="456" width="13.33203125" customWidth="1"/>
-    <col min="457" max="457" width="14.83203125" customWidth="1"/>
-    <col min="458" max="458" width="17.5" customWidth="1"/>
-    <col min="459" max="459" width="27.83203125" customWidth="1"/>
-    <col min="460" max="460" width="41.6640625" customWidth="1"/>
-    <col min="461" max="461" width="31.1640625" customWidth="1"/>
-    <col min="462" max="462" width="37.6640625" customWidth="1"/>
-    <col min="463" max="463" width="85.6640625" customWidth="1"/>
-    <col min="464" max="464" width="51.1640625" customWidth="1"/>
-    <col min="465" max="465" width="21.83203125" customWidth="1"/>
-    <col min="466" max="466" width="64.33203125" customWidth="1"/>
-    <col min="467" max="467" width="21.5" customWidth="1"/>
-    <col min="468" max="468" width="45.5" customWidth="1"/>
-    <col min="469" max="469" width="47.33203125" customWidth="1"/>
-    <col min="470" max="470" width="46" customWidth="1"/>
-    <col min="471" max="471" width="71.33203125" customWidth="1"/>
-    <col min="472" max="472" width="78" customWidth="1"/>
-    <col min="473" max="473" width="81.33203125" customWidth="1"/>
-    <col min="474" max="476" width="85.6640625" customWidth="1"/>
-    <col min="477" max="477" width="36.33203125" customWidth="1"/>
-    <col min="478" max="478" width="43.5" customWidth="1"/>
-    <col min="479" max="479" width="43.33203125" customWidth="1"/>
-    <col min="480" max="480" width="46.1640625" customWidth="1"/>
-    <col min="481" max="481" width="44" customWidth="1"/>
-    <col min="482" max="482" width="41.83203125" customWidth="1"/>
-    <col min="483" max="483" width="45.33203125" customWidth="1"/>
-    <col min="484" max="484" width="29.5" customWidth="1"/>
-    <col min="485" max="485" width="46.33203125" customWidth="1"/>
-    <col min="486" max="486" width="47" customWidth="1"/>
-    <col min="487" max="487" width="44.33203125" customWidth="1"/>
-    <col min="488" max="488" width="49.5" customWidth="1"/>
-    <col min="489" max="489" width="50.83203125" customWidth="1"/>
-    <col min="490" max="490" width="67.6640625" customWidth="1"/>
-    <col min="491" max="491" width="50.1640625" customWidth="1"/>
-    <col min="492" max="492" width="33.6640625" customWidth="1"/>
-    <col min="493" max="493" width="63.5" customWidth="1"/>
-    <col min="494" max="494" width="53.5" customWidth="1"/>
-    <col min="495" max="495" width="61.33203125" customWidth="1"/>
-    <col min="496" max="496" width="57.6640625" customWidth="1"/>
-    <col min="497" max="497" width="51.83203125" customWidth="1"/>
-    <col min="498" max="498" width="32.33203125" customWidth="1"/>
-    <col min="499" max="499" width="16.1640625" customWidth="1"/>
-    <col min="500" max="500" width="15.33203125" customWidth="1"/>
-    <col min="501" max="501" width="51" customWidth="1"/>
-    <col min="502" max="502" width="24.6640625" customWidth="1"/>
-    <col min="503" max="503" width="43" customWidth="1"/>
-    <col min="504" max="504" width="32.83203125" customWidth="1"/>
-    <col min="505" max="505" width="78.6640625" customWidth="1"/>
-    <col min="506" max="506" width="31.33203125" customWidth="1"/>
-    <col min="507" max="507" width="68.1640625" customWidth="1"/>
-    <col min="508" max="508" width="63.5" customWidth="1"/>
-    <col min="509" max="509" width="59" customWidth="1"/>
-    <col min="510" max="510" width="71.33203125" customWidth="1"/>
-    <col min="511" max="511" width="62.5" customWidth="1"/>
-    <col min="512" max="512" width="26.6640625" customWidth="1"/>
-    <col min="513" max="513" width="58.33203125" customWidth="1"/>
-    <col min="514" max="514" width="44.83203125" customWidth="1"/>
-    <col min="515" max="515" width="38.33203125" customWidth="1"/>
-    <col min="516" max="516" width="80.5" customWidth="1"/>
-    <col min="517" max="517" width="38" customWidth="1"/>
-    <col min="518" max="518" width="26" customWidth="1"/>
-    <col min="519" max="519" width="31.1640625" customWidth="1"/>
-    <col min="520" max="520" width="44.83203125" customWidth="1"/>
-    <col min="521" max="521" width="80.5" customWidth="1"/>
-    <col min="522" max="522" width="34.33203125" customWidth="1"/>
-    <col min="523" max="523" width="28.33203125" customWidth="1"/>
-    <col min="524" max="524" width="17.83203125" customWidth="1"/>
-    <col min="525" max="525" width="44.83203125" customWidth="1"/>
-    <col min="526" max="526" width="39" customWidth="1"/>
-    <col min="527" max="527" width="80.5" customWidth="1"/>
-    <col min="528" max="528" width="38.1640625" customWidth="1"/>
-    <col min="529" max="529" width="49.5" customWidth="1"/>
-    <col min="530" max="530" width="51" customWidth="1"/>
-    <col min="531" max="531" width="25.83203125" customWidth="1"/>
-    <col min="532" max="532" width="31.5" customWidth="1"/>
-    <col min="533" max="533" width="32.83203125" customWidth="1"/>
-    <col min="534" max="534" width="40.6640625" customWidth="1"/>
-    <col min="535" max="535" width="55.33203125" customWidth="1"/>
-    <col min="536" max="536" width="69.83203125" customWidth="1"/>
-    <col min="537" max="537" width="49.83203125" customWidth="1"/>
-    <col min="538" max="538" width="28.5" customWidth="1"/>
-    <col min="539" max="539" width="53" customWidth="1"/>
-    <col min="540" max="540" width="31.83203125" customWidth="1"/>
-    <col min="541" max="541" width="65.1640625" customWidth="1"/>
-    <col min="542" max="542" width="42.1640625" customWidth="1"/>
-    <col min="543" max="543" width="20.6640625" customWidth="1"/>
-    <col min="544" max="544" width="43.1640625" customWidth="1"/>
-    <col min="545" max="545" width="67" customWidth="1"/>
-    <col min="546" max="546" width="84.5" customWidth="1"/>
-    <col min="547" max="547" width="71" customWidth="1"/>
-    <col min="548" max="548" width="78.6640625" customWidth="1"/>
-    <col min="549" max="549" width="79.5" customWidth="1"/>
-    <col min="550" max="550" width="77.6640625" customWidth="1"/>
-    <col min="551" max="551" width="85" customWidth="1"/>
-    <col min="552" max="552" width="22.1640625" customWidth="1"/>
-    <col min="553" max="553" width="42" customWidth="1"/>
-    <col min="554" max="554" width="21.83203125" customWidth="1"/>
-    <col min="555" max="555" width="55.5" customWidth="1"/>
-    <col min="556" max="556" width="23.33203125" customWidth="1"/>
-    <col min="557" max="557" width="54.83203125" customWidth="1"/>
-    <col min="558" max="558" width="12.1640625" customWidth="1"/>
-    <col min="559" max="559" width="20.33203125" customWidth="1"/>
-    <col min="560" max="560" width="13.6640625" customWidth="1"/>
-    <col min="561" max="561" width="17.5" customWidth="1"/>
-    <col min="562" max="562" width="42.83203125" customWidth="1"/>
-    <col min="563" max="563" width="74" customWidth="1"/>
-    <col min="564" max="564" width="75.1640625" customWidth="1"/>
-    <col min="565" max="565" width="77.1640625" customWidth="1"/>
-    <col min="566" max="566" width="67.5" customWidth="1"/>
-    <col min="567" max="567" width="72" customWidth="1"/>
-    <col min="568" max="568" width="80" customWidth="1"/>
-    <col min="569" max="569" width="24.1640625" customWidth="1"/>
-    <col min="570" max="570" width="70.33203125" customWidth="1"/>
-    <col min="571" max="571" width="24.1640625" customWidth="1"/>
-    <col min="572" max="572" width="14.5" customWidth="1"/>
-    <col min="573" max="573" width="9" customWidth="1"/>
-    <col min="574" max="574" width="30.1640625" customWidth="1"/>
-    <col min="575" max="575" width="48.1640625" customWidth="1"/>
-    <col min="576" max="576" width="38.33203125" customWidth="1"/>
-    <col min="577" max="577" width="20" customWidth="1"/>
-    <col min="578" max="578" width="27" customWidth="1"/>
-    <col min="579" max="579" width="24.1640625" customWidth="1"/>
-    <col min="580" max="580" width="17.33203125" customWidth="1"/>
-    <col min="581" max="581" width="72.5" customWidth="1"/>
-    <col min="582" max="582" width="66" customWidth="1"/>
-    <col min="583" max="583" width="25.1640625" customWidth="1"/>
-    <col min="584" max="584" width="54.6640625" customWidth="1"/>
-    <col min="585" max="585" width="69.5" customWidth="1"/>
-    <col min="586" max="586" width="17.33203125" customWidth="1"/>
-    <col min="587" max="587" width="51.33203125" customWidth="1"/>
-    <col min="588" max="588" width="67.83203125" customWidth="1"/>
-    <col min="589" max="589" width="17.83203125" customWidth="1"/>
-    <col min="590" max="590" width="56.5" customWidth="1"/>
-    <col min="591" max="591" width="17.83203125" customWidth="1"/>
-    <col min="592" max="592" width="15.6640625" customWidth="1"/>
-    <col min="593" max="593" width="37" customWidth="1"/>
-    <col min="594" max="594" width="67.83203125" customWidth="1"/>
-    <col min="595" max="595" width="34.33203125" customWidth="1"/>
-    <col min="596" max="596" width="56.5" customWidth="1"/>
-    <col min="597" max="597" width="24.1640625" customWidth="1"/>
-    <col min="598" max="598" width="15.6640625" customWidth="1"/>
-    <col min="599" max="599" width="14.33203125" customWidth="1"/>
-    <col min="600" max="600" width="67.83203125" customWidth="1"/>
-    <col min="601" max="601" width="64.6640625" customWidth="1"/>
-    <col min="602" max="602" width="79.1640625" customWidth="1"/>
-    <col min="603" max="603" width="81.83203125" customWidth="1"/>
-    <col min="604" max="604" width="85.6640625" customWidth="1"/>
-    <col min="605" max="605" width="81" customWidth="1"/>
-    <col min="606" max="606" width="78.6640625" customWidth="1"/>
-    <col min="607" max="607" width="56.5" customWidth="1"/>
-    <col min="608" max="608" width="62" customWidth="1"/>
-    <col min="609" max="609" width="84.1640625" customWidth="1"/>
-    <col min="610" max="610" width="83" customWidth="1"/>
-    <col min="611" max="611" width="85.6640625" customWidth="1"/>
-    <col min="612" max="612" width="78.83203125" customWidth="1"/>
-    <col min="613" max="613" width="49.6640625" customWidth="1"/>
-    <col min="614" max="614" width="51.83203125" customWidth="1"/>
-    <col min="615" max="615" width="30.5" customWidth="1"/>
-    <col min="616" max="616" width="61.83203125" customWidth="1"/>
-    <col min="617" max="617" width="63.5" customWidth="1"/>
-    <col min="618" max="618" width="56.1640625" customWidth="1"/>
-    <col min="619" max="619" width="62.5" customWidth="1"/>
-    <col min="620" max="620" width="60.1640625" customWidth="1"/>
-    <col min="621" max="621" width="63.6640625" customWidth="1"/>
-    <col min="622" max="622" width="74" customWidth="1"/>
-    <col min="623" max="623" width="14.33203125" customWidth="1"/>
-    <col min="624" max="624" width="20" customWidth="1"/>
-    <col min="625" max="625" width="66.5" customWidth="1"/>
-    <col min="626" max="626" width="81" customWidth="1"/>
-    <col min="627" max="627" width="83.6640625" customWidth="1"/>
-    <col min="628" max="628" width="85.6640625" customWidth="1"/>
-    <col min="629" max="629" width="82.83203125" customWidth="1"/>
-    <col min="630" max="630" width="80.5" customWidth="1"/>
-    <col min="631" max="631" width="32.1640625" customWidth="1"/>
-    <col min="632" max="632" width="63.83203125" customWidth="1"/>
-    <col min="633" max="633" width="85.6640625" customWidth="1"/>
-    <col min="634" max="634" width="84.83203125" customWidth="1"/>
-    <col min="635" max="635" width="85.6640625" customWidth="1"/>
-    <col min="636" max="636" width="80.6640625" customWidth="1"/>
-    <col min="637" max="637" width="32.6640625" customWidth="1"/>
-    <col min="638" max="638" width="53.6640625" customWidth="1"/>
-    <col min="639" max="639" width="56.83203125" customWidth="1"/>
-    <col min="640" max="640" width="27.33203125" customWidth="1"/>
-    <col min="641" max="641" width="57.83203125" customWidth="1"/>
-    <col min="642" max="642" width="28.83203125" customWidth="1"/>
-    <col min="643" max="643" width="35.1640625" customWidth="1"/>
-    <col min="644" max="644" width="36.5" customWidth="1"/>
-    <col min="645" max="645" width="48.6640625" customWidth="1"/>
-    <col min="646" max="646" width="44.33203125" customWidth="1"/>
-    <col min="647" max="647" width="54" customWidth="1"/>
-    <col min="648" max="648" width="23.1640625" customWidth="1"/>
-    <col min="649" max="649" width="61.5" customWidth="1"/>
-    <col min="650" max="650" width="16" customWidth="1"/>
-    <col min="651" max="651" width="13.5" customWidth="1"/>
-    <col min="652" max="652" width="14.33203125" customWidth="1"/>
-    <col min="653" max="653" width="16" customWidth="1"/>
-    <col min="654" max="654" width="47" customWidth="1"/>
-    <col min="655" max="655" width="52" customWidth="1"/>
-    <col min="656" max="656" width="26" customWidth="1"/>
-    <col min="657" max="657" width="78" customWidth="1"/>
-    <col min="658" max="658" width="66" customWidth="1"/>
-    <col min="659" max="659" width="62.6640625" customWidth="1"/>
-    <col min="660" max="660" width="12.83203125" customWidth="1"/>
-    <col min="661" max="661" width="18.6640625" customWidth="1"/>
-    <col min="662" max="663" width="85.6640625" customWidth="1"/>
-    <col min="664" max="664" width="42.33203125" customWidth="1"/>
-    <col min="665" max="665" width="18.6640625" customWidth="1"/>
-    <col min="666" max="667" width="85.6640625" customWidth="1"/>
-    <col min="668" max="668" width="40.5" customWidth="1"/>
-    <col min="669" max="669" width="18.83203125" customWidth="1"/>
-    <col min="670" max="670" width="20.5" customWidth="1"/>
-    <col min="671" max="671" width="19.5" customWidth="1"/>
-    <col min="672" max="672" width="45.83203125" customWidth="1"/>
-    <col min="673" max="673" width="62.83203125" customWidth="1"/>
-    <col min="674" max="674" width="51.33203125" customWidth="1"/>
-    <col min="675" max="675" width="25.33203125" customWidth="1"/>
-    <col min="676" max="676" width="19" customWidth="1"/>
-    <col min="677" max="677" width="58.5" customWidth="1"/>
-    <col min="678" max="678" width="59.83203125" customWidth="1"/>
-    <col min="679" max="679" width="80.1640625" customWidth="1"/>
-    <col min="680" max="680" width="31.1640625" customWidth="1"/>
-    <col min="681" max="681" width="37.6640625" customWidth="1"/>
-    <col min="682" max="682" width="36" customWidth="1"/>
-    <col min="683" max="683" width="22.83203125" customWidth="1"/>
-    <col min="687" max="688" width="17.33203125" customWidth="1"/>
-    <col min="690" max="690" width="15" customWidth="1"/>
-    <col min="691" max="691" width="12.5" customWidth="1"/>
-    <col min="692" max="692" width="15.33203125" customWidth="1"/>
-    <col min="790" max="790" width="57" bestFit="1" customWidth="1"/>
-    <col min="794" max="794" width="40.83203125" bestFit="1" customWidth="1"/>
-    <col min="806" max="806" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="301" max="302" width="15.33203125" customWidth="1"/>
+    <col min="303" max="303" width="41" customWidth="1"/>
+    <col min="304" max="309" width="85.6640625" customWidth="1"/>
+    <col min="310" max="310" width="75.83203125" customWidth="1"/>
+    <col min="311" max="312" width="85.6640625" customWidth="1"/>
+    <col min="313" max="313" width="85" customWidth="1"/>
+    <col min="314" max="314" width="27.1640625" customWidth="1"/>
+    <col min="315" max="315" width="35.6640625" customWidth="1"/>
+    <col min="316" max="316" width="13.33203125" customWidth="1"/>
+    <col min="317" max="317" width="24" customWidth="1"/>
+    <col min="318" max="318" width="12.83203125" customWidth="1"/>
+    <col min="319" max="319" width="14.5" customWidth="1"/>
+    <col min="320" max="320" width="22" customWidth="1"/>
+    <col min="321" max="321" width="40.5" customWidth="1"/>
+    <col min="322" max="322" width="42.1640625" customWidth="1"/>
+    <col min="323" max="323" width="23.5" customWidth="1"/>
+    <col min="324" max="324" width="42.33203125" customWidth="1"/>
+    <col min="325" max="325" width="44" customWidth="1"/>
+    <col min="326" max="326" width="19" customWidth="1"/>
+    <col min="327" max="327" width="42.33203125" customWidth="1"/>
+    <col min="328" max="328" width="44" customWidth="1"/>
+    <col min="329" max="329" width="20.6640625" customWidth="1"/>
+    <col min="330" max="330" width="42.33203125" customWidth="1"/>
+    <col min="331" max="331" width="44" customWidth="1"/>
+    <col min="332" max="332" width="16.83203125" customWidth="1"/>
+    <col min="333" max="333" width="42.33203125" customWidth="1"/>
+    <col min="334" max="334" width="44" customWidth="1"/>
+    <col min="335" max="335" width="18.5" customWidth="1"/>
+    <col min="336" max="336" width="40.33203125" customWidth="1"/>
+    <col min="337" max="337" width="42" customWidth="1"/>
+    <col min="338" max="338" width="57.1640625" customWidth="1"/>
+    <col min="339" max="339" width="85.6640625" customWidth="1"/>
+    <col min="340" max="340" width="46.33203125" customWidth="1"/>
+    <col min="341" max="341" width="62.6640625" customWidth="1"/>
+    <col min="342" max="342" width="53.5" customWidth="1"/>
+    <col min="343" max="346" width="85.6640625" customWidth="1"/>
+    <col min="347" max="347" width="35.1640625" customWidth="1"/>
+    <col min="348" max="348" width="85" customWidth="1"/>
+    <col min="349" max="349" width="64.6640625" customWidth="1"/>
+    <col min="350" max="350" width="68.33203125" customWidth="1"/>
+    <col min="351" max="351" width="31" customWidth="1"/>
+    <col min="352" max="352" width="41.1640625" customWidth="1"/>
+    <col min="353" max="353" width="11.5" customWidth="1"/>
+    <col min="354" max="354" width="16.6640625" customWidth="1"/>
+    <col min="355" max="363" width="85.6640625" customWidth="1"/>
+    <col min="364" max="364" width="58.6640625" customWidth="1"/>
+    <col min="365" max="365" width="68.83203125" customWidth="1"/>
+    <col min="366" max="366" width="39.1640625" customWidth="1"/>
+    <col min="367" max="367" width="16.6640625" customWidth="1"/>
+    <col min="368" max="376" width="85.6640625" customWidth="1"/>
+    <col min="377" max="377" width="60.5" customWidth="1"/>
+    <col min="378" max="378" width="70.6640625" customWidth="1"/>
+    <col min="379" max="379" width="41" customWidth="1"/>
+    <col min="380" max="380" width="16.6640625" customWidth="1"/>
+    <col min="381" max="389" width="85.6640625" customWidth="1"/>
+    <col min="390" max="390" width="60.5" customWidth="1"/>
+    <col min="391" max="391" width="70.6640625" customWidth="1"/>
+    <col min="392" max="392" width="41" customWidth="1"/>
+    <col min="393" max="393" width="57.5" customWidth="1"/>
+    <col min="394" max="394" width="54" customWidth="1"/>
+    <col min="395" max="395" width="42.6640625" customWidth="1"/>
+    <col min="396" max="396" width="58.5" customWidth="1"/>
+    <col min="397" max="397" width="69" customWidth="1"/>
+    <col min="398" max="398" width="52.5" customWidth="1"/>
+    <col min="399" max="399" width="55.5" customWidth="1"/>
+    <col min="400" max="400" width="49" customWidth="1"/>
+    <col min="401" max="401" width="56.1640625" customWidth="1"/>
+    <col min="402" max="402" width="23.33203125" customWidth="1"/>
+    <col min="403" max="403" width="15.6640625" customWidth="1"/>
+    <col min="404" max="404" width="47" customWidth="1"/>
+    <col min="405" max="405" width="85.6640625" customWidth="1"/>
+    <col min="406" max="406" width="61.5" customWidth="1"/>
+    <col min="407" max="407" width="63.5" customWidth="1"/>
+    <col min="408" max="408" width="66.83203125" customWidth="1"/>
+    <col min="409" max="409" width="83.6640625" customWidth="1"/>
+    <col min="410" max="410" width="31.6640625" customWidth="1"/>
+    <col min="411" max="411" width="40.83203125" customWidth="1"/>
+    <col min="412" max="412" width="64.83203125" customWidth="1"/>
+    <col min="413" max="413" width="81.33203125" customWidth="1"/>
+    <col min="414" max="414" width="85.6640625" customWidth="1"/>
+    <col min="415" max="415" width="84.83203125" customWidth="1"/>
+    <col min="416" max="416" width="51.83203125" customWidth="1"/>
+    <col min="417" max="417" width="27.5" customWidth="1"/>
+    <col min="418" max="419" width="46.6640625" customWidth="1"/>
+    <col min="420" max="420" width="17.33203125" customWidth="1"/>
+    <col min="421" max="421" width="34.33203125" customWidth="1"/>
+    <col min="422" max="422" width="35.83203125" customWidth="1"/>
+    <col min="423" max="423" width="34.83203125" customWidth="1"/>
+    <col min="424" max="424" width="24.83203125" customWidth="1"/>
+    <col min="425" max="425" width="11" customWidth="1"/>
+    <col min="426" max="426" width="10.33203125" customWidth="1"/>
+    <col min="427" max="428" width="13.33203125" customWidth="1"/>
+    <col min="429" max="429" width="26.83203125" customWidth="1"/>
+    <col min="430" max="430" width="28.5" customWidth="1"/>
+    <col min="431" max="431" width="24.5" customWidth="1"/>
+    <col min="432" max="434" width="85.6640625" customWidth="1"/>
+    <col min="435" max="435" width="81" customWidth="1"/>
+    <col min="436" max="436" width="85.6640625" customWidth="1"/>
+    <col min="437" max="437" width="64.6640625" customWidth="1"/>
+    <col min="438" max="438" width="26.1640625" customWidth="1"/>
+    <col min="443" max="443" width="20.33203125" customWidth="1"/>
+    <col min="444" max="444" width="22" customWidth="1"/>
+    <col min="445" max="445" width="26.5" customWidth="1"/>
+    <col min="446" max="448" width="85.6640625" customWidth="1"/>
+    <col min="449" max="449" width="83" customWidth="1"/>
+    <col min="450" max="450" width="85.6640625" customWidth="1"/>
+    <col min="451" max="451" width="47.83203125" customWidth="1"/>
+    <col min="452" max="452" width="37.5" customWidth="1"/>
+    <col min="453" max="453" width="34.6640625" customWidth="1"/>
+    <col min="454" max="454" width="13.33203125" customWidth="1"/>
+    <col min="455" max="455" width="9" customWidth="1"/>
+    <col min="457" max="457" width="13.33203125" customWidth="1"/>
+    <col min="458" max="458" width="14.83203125" customWidth="1"/>
+    <col min="459" max="459" width="17.5" customWidth="1"/>
+    <col min="460" max="460" width="27.83203125" customWidth="1"/>
+    <col min="461" max="461" width="41.6640625" customWidth="1"/>
+    <col min="462" max="462" width="31.1640625" customWidth="1"/>
+    <col min="463" max="463" width="37.6640625" customWidth="1"/>
+    <col min="464" max="464" width="85.6640625" customWidth="1"/>
+    <col min="465" max="465" width="51.1640625" customWidth="1"/>
+    <col min="466" max="466" width="21.83203125" customWidth="1"/>
+    <col min="467" max="467" width="64.33203125" customWidth="1"/>
+    <col min="468" max="468" width="21.5" customWidth="1"/>
+    <col min="469" max="469" width="45.5" customWidth="1"/>
+    <col min="470" max="470" width="47.33203125" customWidth="1"/>
+    <col min="471" max="471" width="46" customWidth="1"/>
+    <col min="472" max="472" width="71.33203125" customWidth="1"/>
+    <col min="473" max="473" width="78" customWidth="1"/>
+    <col min="474" max="474" width="81.33203125" customWidth="1"/>
+    <col min="475" max="477" width="85.6640625" customWidth="1"/>
+    <col min="478" max="478" width="36.33203125" customWidth="1"/>
+    <col min="479" max="479" width="43.5" customWidth="1"/>
+    <col min="480" max="480" width="43.33203125" customWidth="1"/>
+    <col min="481" max="481" width="46.1640625" customWidth="1"/>
+    <col min="482" max="482" width="44" customWidth="1"/>
+    <col min="483" max="483" width="41.83203125" customWidth="1"/>
+    <col min="484" max="484" width="45.33203125" customWidth="1"/>
+    <col min="485" max="485" width="29.5" customWidth="1"/>
+    <col min="486" max="486" width="46.33203125" customWidth="1"/>
+    <col min="487" max="487" width="47" customWidth="1"/>
+    <col min="488" max="488" width="44.33203125" customWidth="1"/>
+    <col min="489" max="489" width="49.5" customWidth="1"/>
+    <col min="490" max="490" width="50.83203125" customWidth="1"/>
+    <col min="491" max="491" width="67.6640625" customWidth="1"/>
+    <col min="492" max="492" width="50.1640625" customWidth="1"/>
+    <col min="493" max="493" width="33.6640625" customWidth="1"/>
+    <col min="494" max="494" width="63.5" customWidth="1"/>
+    <col min="495" max="495" width="53.5" customWidth="1"/>
+    <col min="496" max="496" width="61.33203125" customWidth="1"/>
+    <col min="497" max="497" width="57.6640625" customWidth="1"/>
+    <col min="498" max="498" width="51.83203125" customWidth="1"/>
+    <col min="499" max="499" width="32.33203125" customWidth="1"/>
+    <col min="500" max="500" width="16.1640625" customWidth="1"/>
+    <col min="501" max="501" width="15.33203125" customWidth="1"/>
+    <col min="502" max="502" width="51" customWidth="1"/>
+    <col min="503" max="503" width="24.6640625" customWidth="1"/>
+    <col min="504" max="504" width="43" customWidth="1"/>
+    <col min="505" max="505" width="32.83203125" customWidth="1"/>
+    <col min="506" max="506" width="78.6640625" customWidth="1"/>
+    <col min="507" max="507" width="31.33203125" customWidth="1"/>
+    <col min="508" max="508" width="68.1640625" customWidth="1"/>
+    <col min="509" max="509" width="63.5" customWidth="1"/>
+    <col min="510" max="510" width="59" customWidth="1"/>
+    <col min="511" max="511" width="71.33203125" customWidth="1"/>
+    <col min="512" max="512" width="62.5" customWidth="1"/>
+    <col min="513" max="513" width="26.6640625" customWidth="1"/>
+    <col min="514" max="514" width="58.33203125" customWidth="1"/>
+    <col min="515" max="515" width="44.83203125" customWidth="1"/>
+    <col min="516" max="516" width="38.33203125" customWidth="1"/>
+    <col min="517" max="517" width="80.5" customWidth="1"/>
+    <col min="518" max="518" width="38" customWidth="1"/>
+    <col min="519" max="519" width="26" customWidth="1"/>
+    <col min="520" max="520" width="31.1640625" customWidth="1"/>
+    <col min="521" max="521" width="44.83203125" customWidth="1"/>
+    <col min="522" max="522" width="80.5" customWidth="1"/>
+    <col min="523" max="523" width="34.33203125" customWidth="1"/>
+    <col min="524" max="524" width="28.33203125" customWidth="1"/>
+    <col min="525" max="525" width="17.83203125" customWidth="1"/>
+    <col min="526" max="526" width="44.83203125" customWidth="1"/>
+    <col min="527" max="527" width="39" customWidth="1"/>
+    <col min="528" max="528" width="80.5" customWidth="1"/>
+    <col min="529" max="529" width="38.1640625" customWidth="1"/>
+    <col min="530" max="530" width="49.5" customWidth="1"/>
+    <col min="531" max="531" width="51" customWidth="1"/>
+    <col min="532" max="532" width="25.83203125" customWidth="1"/>
+    <col min="533" max="533" width="31.5" customWidth="1"/>
+    <col min="534" max="534" width="32.83203125" customWidth="1"/>
+    <col min="535" max="535" width="40.6640625" customWidth="1"/>
+    <col min="536" max="536" width="55.33203125" customWidth="1"/>
+    <col min="537" max="537" width="69.83203125" customWidth="1"/>
+    <col min="538" max="538" width="49.83203125" customWidth="1"/>
+    <col min="539" max="539" width="28.5" customWidth="1"/>
+    <col min="540" max="540" width="53" customWidth="1"/>
+    <col min="541" max="541" width="31.83203125" customWidth="1"/>
+    <col min="542" max="542" width="65.1640625" customWidth="1"/>
+    <col min="543" max="543" width="42.1640625" customWidth="1"/>
+    <col min="544" max="544" width="20.6640625" customWidth="1"/>
+    <col min="545" max="545" width="43.1640625" customWidth="1"/>
+    <col min="546" max="546" width="67" customWidth="1"/>
+    <col min="547" max="547" width="84.5" customWidth="1"/>
+    <col min="548" max="548" width="71" customWidth="1"/>
+    <col min="549" max="549" width="78.6640625" customWidth="1"/>
+    <col min="550" max="550" width="79.5" customWidth="1"/>
+    <col min="551" max="551" width="77.6640625" customWidth="1"/>
+    <col min="552" max="552" width="85" customWidth="1"/>
+    <col min="553" max="553" width="22.1640625" customWidth="1"/>
+    <col min="554" max="554" width="42" customWidth="1"/>
+    <col min="555" max="555" width="21.83203125" customWidth="1"/>
+    <col min="556" max="556" width="55.5" customWidth="1"/>
+    <col min="557" max="557" width="23.33203125" customWidth="1"/>
+    <col min="558" max="558" width="54.83203125" customWidth="1"/>
+    <col min="559" max="559" width="12.1640625" customWidth="1"/>
+    <col min="560" max="560" width="20.33203125" customWidth="1"/>
+    <col min="561" max="561" width="13.6640625" customWidth="1"/>
+    <col min="562" max="562" width="17.5" customWidth="1"/>
+    <col min="563" max="563" width="42.83203125" customWidth="1"/>
+    <col min="564" max="564" width="74" customWidth="1"/>
+    <col min="565" max="565" width="75.1640625" customWidth="1"/>
+    <col min="566" max="566" width="77.1640625" customWidth="1"/>
+    <col min="567" max="567" width="67.5" customWidth="1"/>
+    <col min="568" max="568" width="72" customWidth="1"/>
+    <col min="569" max="569" width="80" customWidth="1"/>
+    <col min="570" max="570" width="24.1640625" customWidth="1"/>
+    <col min="571" max="571" width="70.33203125" customWidth="1"/>
+    <col min="572" max="572" width="24.1640625" customWidth="1"/>
+    <col min="573" max="573" width="14.5" customWidth="1"/>
+    <col min="574" max="574" width="9" customWidth="1"/>
+    <col min="575" max="575" width="30.1640625" customWidth="1"/>
+    <col min="576" max="576" width="48.1640625" customWidth="1"/>
+    <col min="577" max="577" width="38.33203125" customWidth="1"/>
+    <col min="578" max="578" width="20" customWidth="1"/>
+    <col min="579" max="579" width="27" customWidth="1"/>
+    <col min="580" max="580" width="24.1640625" customWidth="1"/>
+    <col min="581" max="581" width="17.33203125" customWidth="1"/>
+    <col min="582" max="582" width="72.5" customWidth="1"/>
+    <col min="583" max="583" width="66" customWidth="1"/>
+    <col min="584" max="584" width="25.1640625" customWidth="1"/>
+    <col min="585" max="585" width="54.6640625" customWidth="1"/>
+    <col min="586" max="586" width="69.5" customWidth="1"/>
+    <col min="587" max="587" width="17.33203125" customWidth="1"/>
+    <col min="588" max="588" width="51.33203125" customWidth="1"/>
+    <col min="589" max="589" width="67.83203125" customWidth="1"/>
+    <col min="590" max="590" width="17.83203125" customWidth="1"/>
+    <col min="591" max="591" width="56.5" customWidth="1"/>
+    <col min="592" max="592" width="17.83203125" customWidth="1"/>
+    <col min="593" max="593" width="15.6640625" customWidth="1"/>
+    <col min="594" max="594" width="37" customWidth="1"/>
+    <col min="595" max="595" width="67.83203125" customWidth="1"/>
+    <col min="596" max="596" width="34.33203125" customWidth="1"/>
+    <col min="597" max="597" width="56.5" customWidth="1"/>
+    <col min="598" max="598" width="24.1640625" customWidth="1"/>
+    <col min="599" max="599" width="15.6640625" customWidth="1"/>
+    <col min="600" max="600" width="14.33203125" customWidth="1"/>
+    <col min="601" max="601" width="67.83203125" customWidth="1"/>
+    <col min="602" max="602" width="64.6640625" customWidth="1"/>
+    <col min="603" max="603" width="79.1640625" customWidth="1"/>
+    <col min="604" max="604" width="81.83203125" customWidth="1"/>
+    <col min="605" max="605" width="85.6640625" customWidth="1"/>
+    <col min="606" max="606" width="81" customWidth="1"/>
+    <col min="607" max="607" width="78.6640625" customWidth="1"/>
+    <col min="608" max="608" width="56.5" customWidth="1"/>
+    <col min="609" max="609" width="62" customWidth="1"/>
+    <col min="610" max="610" width="84.1640625" customWidth="1"/>
+    <col min="611" max="611" width="83" customWidth="1"/>
+    <col min="612" max="612" width="85.6640625" customWidth="1"/>
+    <col min="613" max="613" width="78.83203125" customWidth="1"/>
+    <col min="614" max="614" width="49.6640625" customWidth="1"/>
+    <col min="615" max="615" width="51.83203125" customWidth="1"/>
+    <col min="616" max="616" width="30.5" customWidth="1"/>
+    <col min="617" max="617" width="61.83203125" customWidth="1"/>
+    <col min="618" max="618" width="63.5" customWidth="1"/>
+    <col min="619" max="619" width="56.1640625" customWidth="1"/>
+    <col min="620" max="620" width="62.5" customWidth="1"/>
+    <col min="621" max="621" width="60.1640625" customWidth="1"/>
+    <col min="622" max="622" width="63.6640625" customWidth="1"/>
+    <col min="623" max="623" width="74" customWidth="1"/>
+    <col min="624" max="624" width="14.33203125" customWidth="1"/>
+    <col min="625" max="625" width="20" customWidth="1"/>
+    <col min="626" max="626" width="66.5" customWidth="1"/>
+    <col min="627" max="627" width="81" customWidth="1"/>
+    <col min="628" max="628" width="83.6640625" customWidth="1"/>
+    <col min="629" max="629" width="85.6640625" customWidth="1"/>
+    <col min="630" max="630" width="82.83203125" customWidth="1"/>
+    <col min="631" max="631" width="80.5" customWidth="1"/>
+    <col min="632" max="632" width="32.1640625" customWidth="1"/>
+    <col min="633" max="633" width="63.83203125" customWidth="1"/>
+    <col min="634" max="634" width="85.6640625" customWidth="1"/>
+    <col min="635" max="635" width="84.83203125" customWidth="1"/>
+    <col min="636" max="636" width="85.6640625" customWidth="1"/>
+    <col min="637" max="637" width="80.6640625" customWidth="1"/>
+    <col min="638" max="638" width="32.6640625" customWidth="1"/>
+    <col min="639" max="639" width="53.6640625" customWidth="1"/>
+    <col min="640" max="640" width="56.83203125" customWidth="1"/>
+    <col min="641" max="641" width="27.33203125" customWidth="1"/>
+    <col min="642" max="642" width="57.83203125" customWidth="1"/>
+    <col min="643" max="643" width="28.83203125" customWidth="1"/>
+    <col min="644" max="644" width="35.1640625" customWidth="1"/>
+    <col min="645" max="645" width="36.5" customWidth="1"/>
+    <col min="646" max="646" width="48.6640625" customWidth="1"/>
+    <col min="647" max="647" width="44.33203125" customWidth="1"/>
+    <col min="648" max="648" width="54" customWidth="1"/>
+    <col min="649" max="649" width="23.1640625" customWidth="1"/>
+    <col min="650" max="650" width="61.5" customWidth="1"/>
+    <col min="651" max="651" width="16" customWidth="1"/>
+    <col min="652" max="652" width="13.5" customWidth="1"/>
+    <col min="653" max="653" width="14.33203125" customWidth="1"/>
+    <col min="654" max="654" width="16" customWidth="1"/>
+    <col min="655" max="655" width="47" customWidth="1"/>
+    <col min="656" max="656" width="52" customWidth="1"/>
+    <col min="657" max="657" width="26" customWidth="1"/>
+    <col min="658" max="658" width="78" customWidth="1"/>
+    <col min="659" max="659" width="66" customWidth="1"/>
+    <col min="660" max="660" width="62.6640625" customWidth="1"/>
+    <col min="661" max="661" width="12.83203125" customWidth="1"/>
+    <col min="662" max="662" width="18.6640625" customWidth="1"/>
+    <col min="663" max="664" width="85.6640625" customWidth="1"/>
+    <col min="665" max="665" width="42.33203125" customWidth="1"/>
+    <col min="666" max="666" width="18.6640625" customWidth="1"/>
+    <col min="667" max="668" width="85.6640625" customWidth="1"/>
+    <col min="669" max="669" width="40.5" customWidth="1"/>
+    <col min="670" max="670" width="18.83203125" customWidth="1"/>
+    <col min="671" max="671" width="20.5" customWidth="1"/>
+    <col min="672" max="672" width="19.5" customWidth="1"/>
+    <col min="673" max="673" width="45.83203125" customWidth="1"/>
+    <col min="674" max="674" width="62.83203125" customWidth="1"/>
+    <col min="675" max="675" width="51.33203125" customWidth="1"/>
+    <col min="676" max="676" width="25.33203125" customWidth="1"/>
+    <col min="677" max="677" width="19" customWidth="1"/>
+    <col min="678" max="678" width="58.5" customWidth="1"/>
+    <col min="679" max="679" width="59.83203125" customWidth="1"/>
+    <col min="680" max="680" width="80.1640625" customWidth="1"/>
+    <col min="681" max="681" width="31.1640625" customWidth="1"/>
+    <col min="682" max="682" width="37.6640625" customWidth="1"/>
+    <col min="683" max="683" width="36" customWidth="1"/>
+    <col min="684" max="684" width="22.83203125" customWidth="1"/>
+    <col min="688" max="689" width="17.33203125" customWidth="1"/>
+    <col min="691" max="691" width="15" customWidth="1"/>
+    <col min="692" max="692" width="12.5" customWidth="1"/>
+    <col min="693" max="693" width="15.33203125" customWidth="1"/>
+    <col min="791" max="791" width="57" bestFit="1" customWidth="1"/>
+    <col min="795" max="795" width="40.83203125" bestFit="1" customWidth="1"/>
+    <col min="807" max="807" width="17.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7820,1618 +7872,1621 @@
         <v>645</v>
       </c>
       <c r="KP1" t="s">
+        <v>1701</v>
+      </c>
+      <c r="KQ1" t="s">
         <v>973</v>
       </c>
-      <c r="KQ1" t="s">
+      <c r="KR1" t="s">
         <v>212</v>
       </c>
-      <c r="KR1" t="s">
+      <c r="KS1" t="s">
         <v>213</v>
       </c>
-      <c r="KS1" t="s">
+      <c r="KT1" t="s">
         <v>942</v>
       </c>
-      <c r="KT1" t="s">
+      <c r="KU1" t="s">
         <v>215</v>
       </c>
-      <c r="KU1" t="s">
+      <c r="KV1" t="s">
         <v>216</v>
       </c>
-      <c r="KV1" t="s">
+      <c r="KW1" t="s">
         <v>217</v>
       </c>
-      <c r="KW1" t="s">
+      <c r="KX1" t="s">
         <v>218</v>
       </c>
-      <c r="KX1" t="s">
+      <c r="KY1" t="s">
         <v>219</v>
       </c>
-      <c r="KY1" t="s">
+      <c r="KZ1" t="s">
         <v>992</v>
       </c>
-      <c r="KZ1" t="s">
+      <c r="LA1" t="s">
         <v>220</v>
       </c>
-      <c r="LA1" t="s">
+      <c r="LB1" t="s">
         <v>1518</v>
       </c>
-      <c r="LB1" t="s">
+      <c r="LC1" t="s">
         <v>221</v>
       </c>
-      <c r="LC1" t="s">
+      <c r="LD1" t="s">
         <v>222</v>
       </c>
-      <c r="LD1" t="s">
+      <c r="LE1" t="s">
         <v>223</v>
       </c>
-      <c r="LE1" t="s">
+      <c r="LF1" t="s">
         <v>224</v>
       </c>
-      <c r="LF1" t="s">
+      <c r="LG1" t="s">
         <v>225</v>
       </c>
-      <c r="LG1" t="s">
+      <c r="LH1" t="s">
         <v>646</v>
       </c>
-      <c r="LH1" t="s">
+      <c r="LI1" t="s">
         <v>647</v>
       </c>
-      <c r="LI1" t="s">
+      <c r="LJ1" t="s">
         <v>648</v>
       </c>
-      <c r="LJ1" t="s">
+      <c r="LK1" t="s">
         <v>1075</v>
       </c>
-      <c r="LK1" t="s">
+      <c r="LL1" t="s">
         <v>1076</v>
       </c>
-      <c r="LL1" t="s">
+      <c r="LM1" t="s">
         <v>226</v>
       </c>
-      <c r="LM1" t="s">
+      <c r="LN1" t="s">
         <v>1519</v>
       </c>
-      <c r="LN1" t="s">
+      <c r="LO1" t="s">
         <v>227</v>
       </c>
-      <c r="LO1" t="s">
+      <c r="LP1" t="s">
         <v>228</v>
       </c>
-      <c r="LP1" t="s">
+      <c r="LQ1" t="s">
         <v>229</v>
       </c>
-      <c r="LQ1" t="s">
+      <c r="LR1" t="s">
         <v>230</v>
       </c>
-      <c r="LR1" t="s">
+      <c r="LS1" t="s">
         <v>231</v>
       </c>
-      <c r="LS1" t="s">
+      <c r="LT1" t="s">
         <v>1520</v>
       </c>
-      <c r="LT1" t="s">
+      <c r="LU1" t="s">
         <v>1521</v>
       </c>
-      <c r="LU1" t="s">
+      <c r="LV1" t="s">
         <v>233</v>
       </c>
-      <c r="LV1" t="s">
+      <c r="LW1" t="s">
         <v>234</v>
       </c>
-      <c r="LW1" t="s">
+      <c r="LX1" t="s">
         <v>235</v>
       </c>
-      <c r="LX1" t="s">
+      <c r="LY1" t="s">
         <v>236</v>
       </c>
-      <c r="LY1" t="s">
+      <c r="LZ1" t="s">
         <v>237</v>
       </c>
-      <c r="LZ1" t="s">
+      <c r="MA1" t="s">
         <v>238</v>
       </c>
-      <c r="MA1" t="s">
+      <c r="MB1" t="s">
         <v>1522</v>
       </c>
-      <c r="MB1" t="s">
+      <c r="MC1" t="s">
         <v>239</v>
       </c>
-      <c r="MC1" t="s">
+      <c r="MD1" t="s">
         <v>240</v>
       </c>
-      <c r="MD1" t="s">
+      <c r="ME1" t="s">
         <v>241</v>
       </c>
-      <c r="ME1" t="s">
+      <c r="MF1" t="s">
         <v>242</v>
       </c>
-      <c r="MF1" t="s">
+      <c r="MG1" t="s">
         <v>243</v>
       </c>
-      <c r="MG1" t="s">
+      <c r="MH1" t="s">
         <v>244</v>
       </c>
-      <c r="MH1" t="s">
+      <c r="MI1" t="s">
         <v>1523</v>
       </c>
-      <c r="MI1" t="s">
+      <c r="MJ1" t="s">
         <v>245</v>
       </c>
-      <c r="MJ1" t="s">
+      <c r="MK1" t="s">
         <v>246</v>
       </c>
-      <c r="MK1" t="s">
+      <c r="ML1" t="s">
         <v>247</v>
       </c>
-      <c r="ML1" t="s">
+      <c r="MM1" t="s">
         <v>248</v>
       </c>
-      <c r="MM1" t="s">
+      <c r="MN1" t="s">
         <v>249</v>
       </c>
-      <c r="MN1" t="s">
+      <c r="MO1" t="s">
         <v>649</v>
       </c>
-      <c r="MO1" t="s">
+      <c r="MP1" t="s">
         <v>1524</v>
       </c>
-      <c r="MP1" t="s">
+      <c r="MQ1" t="s">
         <v>650</v>
       </c>
-      <c r="MQ1" t="s">
+      <c r="MR1" t="s">
         <v>651</v>
       </c>
-      <c r="MR1" t="s">
+      <c r="MS1" t="s">
         <v>652</v>
       </c>
-      <c r="MS1" t="s">
+      <c r="MT1" t="s">
         <v>653</v>
       </c>
-      <c r="MT1" t="s">
+      <c r="MU1" t="s">
         <v>654</v>
       </c>
-      <c r="MU1" t="s">
+      <c r="MV1" t="s">
         <v>655</v>
       </c>
-      <c r="MV1" t="s">
+      <c r="MW1" t="s">
         <v>1525</v>
       </c>
-      <c r="MW1" t="s">
+      <c r="MX1" t="s">
         <v>250</v>
       </c>
-      <c r="MX1" t="s">
+      <c r="MY1" t="s">
         <v>251</v>
       </c>
-      <c r="MY1" t="s">
+      <c r="MZ1" t="s">
         <v>252</v>
       </c>
-      <c r="MZ1" t="s">
+      <c r="NA1" t="s">
         <v>253</v>
       </c>
-      <c r="NA1" t="s">
+      <c r="NB1" t="s">
         <v>254</v>
       </c>
-      <c r="NB1" t="s">
+      <c r="NC1" t="s">
         <v>255</v>
       </c>
-      <c r="NC1" t="s">
+      <c r="ND1" t="s">
         <v>1526</v>
       </c>
-      <c r="ND1" t="s">
+      <c r="NE1" t="s">
         <v>256</v>
       </c>
-      <c r="NE1" t="s">
+      <c r="NF1" t="s">
         <v>257</v>
       </c>
-      <c r="NF1" t="s">
+      <c r="NG1" t="s">
         <v>258</v>
       </c>
-      <c r="NG1" t="s">
+      <c r="NH1" t="s">
         <v>259</v>
       </c>
-      <c r="NH1" t="s">
+      <c r="NI1" t="s">
         <v>260</v>
       </c>
-      <c r="NI1" t="s">
+      <c r="NJ1" t="s">
         <v>656</v>
       </c>
-      <c r="NJ1" t="s">
+      <c r="NK1" t="s">
         <v>657</v>
       </c>
-      <c r="NK1" t="s">
+      <c r="NL1" t="s">
         <v>658</v>
       </c>
-      <c r="NL1" t="s">
+      <c r="NM1" t="s">
         <v>659</v>
       </c>
-      <c r="NM1" t="s">
+      <c r="NN1" t="s">
         <v>660</v>
       </c>
-      <c r="NN1" t="s">
+      <c r="NO1" t="s">
         <v>943</v>
       </c>
-      <c r="NO1" t="s">
+      <c r="NP1" t="s">
         <v>661</v>
       </c>
-      <c r="NP1" t="s">
+      <c r="NQ1" t="s">
         <v>662</v>
       </c>
-      <c r="NQ1" t="s">
+      <c r="NR1" t="s">
         <v>944</v>
       </c>
-      <c r="NR1" t="s">
+      <c r="NS1" t="s">
         <v>666</v>
       </c>
-      <c r="NS1" t="s">
+      <c r="NT1" t="s">
         <v>667</v>
       </c>
-      <c r="NT1" t="s">
+      <c r="NU1" t="s">
         <v>945</v>
       </c>
-      <c r="NU1" t="s">
+      <c r="NV1" t="s">
         <v>671</v>
       </c>
-      <c r="NV1" t="s">
+      <c r="NW1" t="s">
         <v>672</v>
       </c>
-      <c r="NW1" t="s">
+      <c r="NX1" t="s">
         <v>261</v>
       </c>
-      <c r="NX1" t="s">
+      <c r="NY1" t="s">
         <v>676</v>
       </c>
-      <c r="NY1" t="s">
+      <c r="NZ1" t="s">
         <v>262</v>
       </c>
-      <c r="NZ1" t="s">
+      <c r="OA1" t="s">
         <v>677</v>
       </c>
-      <c r="OA1" t="s">
+      <c r="OB1" t="s">
         <v>678</v>
       </c>
-      <c r="OB1" t="s">
+      <c r="OC1" t="s">
         <v>679</v>
       </c>
-      <c r="OC1" t="s">
+      <c r="OD1" t="s">
         <v>680</v>
       </c>
-      <c r="OD1" t="s">
+      <c r="OE1" t="s">
         <v>681</v>
       </c>
-      <c r="OE1" t="s">
+      <c r="OF1" t="s">
         <v>946</v>
       </c>
-      <c r="OF1" t="s">
+      <c r="OG1" t="s">
         <v>947</v>
       </c>
-      <c r="OG1" t="s">
+      <c r="OH1" t="s">
         <v>993</v>
       </c>
-      <c r="OH1" t="s">
+      <c r="OI1" t="s">
         <v>682</v>
       </c>
-      <c r="OI1" t="s">
+      <c r="OJ1" t="s">
         <v>683</v>
       </c>
-      <c r="OJ1" t="s">
+      <c r="OK1" t="s">
         <v>684</v>
       </c>
-      <c r="OK1" t="s">
+      <c r="OL1" t="s">
         <v>685</v>
       </c>
-      <c r="OL1" t="s">
+      <c r="OM1" t="s">
         <v>686</v>
       </c>
-      <c r="OM1" t="s">
+      <c r="ON1" t="s">
         <v>1527</v>
       </c>
-      <c r="ON1" t="s">
+      <c r="OO1" t="s">
         <v>263</v>
       </c>
-      <c r="OO1" t="s">
+      <c r="OP1" t="s">
         <v>1528</v>
       </c>
-      <c r="OP1" t="s">
+      <c r="OQ1" t="s">
         <v>1529</v>
       </c>
-      <c r="OQ1" t="s">
+      <c r="OR1" t="s">
         <v>264</v>
       </c>
-      <c r="OR1" t="s">
+      <c r="OS1" t="s">
         <v>1530</v>
       </c>
-      <c r="OS1" t="s">
+      <c r="OT1" t="s">
         <v>1531</v>
       </c>
-      <c r="OT1" t="s">
+      <c r="OU1" t="s">
         <v>265</v>
       </c>
-      <c r="OU1" t="s">
+      <c r="OV1" t="s">
         <v>1532</v>
       </c>
-      <c r="OV1" t="s">
+      <c r="OW1" t="s">
         <v>1533</v>
       </c>
-      <c r="OW1" t="s">
+      <c r="OX1" t="s">
         <v>266</v>
       </c>
-      <c r="OX1" t="s">
+      <c r="OY1" t="s">
         <v>1534</v>
       </c>
-      <c r="OY1" t="s">
+      <c r="OZ1" t="s">
         <v>1535</v>
       </c>
-      <c r="OZ1" t="s">
+      <c r="PA1" t="s">
         <v>267</v>
       </c>
-      <c r="PA1" t="s">
+      <c r="PB1" t="s">
         <v>1536</v>
       </c>
-      <c r="PB1" t="s">
+      <c r="PC1" t="s">
         <v>1537</v>
       </c>
-      <c r="PC1" t="s">
+      <c r="PD1" t="s">
         <v>268</v>
       </c>
-      <c r="PD1" t="s">
+      <c r="PE1" t="s">
         <v>1538</v>
       </c>
-      <c r="PE1" t="s">
+      <c r="PF1" t="s">
         <v>1539</v>
       </c>
-      <c r="PF1" t="s">
+      <c r="PG1" t="s">
         <v>269</v>
       </c>
-      <c r="PG1" t="s">
+      <c r="PH1" t="s">
         <v>270</v>
       </c>
-      <c r="PH1" t="s">
+      <c r="PI1" t="s">
         <v>271</v>
       </c>
-      <c r="PI1" t="s">
+      <c r="PJ1" t="s">
         <v>272</v>
       </c>
-      <c r="PJ1" t="s">
+      <c r="PK1" t="s">
         <v>994</v>
       </c>
-      <c r="PK1" t="s">
+      <c r="PL1" t="s">
         <v>273</v>
       </c>
-      <c r="PL1" t="s">
+      <c r="PM1" t="s">
         <v>274</v>
       </c>
-      <c r="PM1" t="s">
+      <c r="PN1" t="s">
         <v>687</v>
       </c>
-      <c r="PN1" t="s">
+      <c r="PO1" t="s">
         <v>688</v>
       </c>
-      <c r="PO1" t="s">
+      <c r="PP1" t="s">
         <v>1540</v>
       </c>
-      <c r="PP1" t="s">
+      <c r="PQ1" t="s">
         <v>275</v>
       </c>
-      <c r="PQ1" t="s">
+      <c r="PR1" t="s">
         <v>1437</v>
       </c>
-      <c r="PR1" t="s">
+      <c r="PS1" t="s">
         <v>1438</v>
       </c>
-      <c r="PS1" t="s">
+      <c r="PT1" t="s">
         <v>1439</v>
       </c>
-      <c r="PT1" t="s">
+      <c r="PU1" t="s">
         <v>1440</v>
       </c>
-      <c r="PU1" t="s">
+      <c r="PV1" t="s">
         <v>1541</v>
       </c>
-      <c r="PV1" t="s">
+      <c r="PW1" t="s">
         <v>276</v>
       </c>
-      <c r="PW1" t="s">
+      <c r="PX1" t="s">
         <v>277</v>
       </c>
-      <c r="PX1" t="s">
+      <c r="PY1" t="s">
         <v>278</v>
       </c>
-      <c r="PY1" t="s">
+      <c r="PZ1" t="s">
         <v>279</v>
       </c>
-      <c r="PZ1" t="s">
+      <c r="QA1" t="s">
         <v>280</v>
       </c>
-      <c r="QA1" t="s">
+      <c r="QB1" t="s">
         <v>281</v>
       </c>
-      <c r="QB1" t="s">
+      <c r="QC1" t="s">
         <v>282</v>
       </c>
-      <c r="QC1" t="s">
+      <c r="QD1" t="s">
         <v>283</v>
       </c>
-      <c r="QD1" t="s">
+      <c r="QE1" t="s">
         <v>284</v>
       </c>
-      <c r="QE1" t="s">
+      <c r="QF1" t="s">
         <v>285</v>
       </c>
-      <c r="QF1" t="s">
+      <c r="QG1" t="s">
         <v>286</v>
       </c>
-      <c r="QG1" t="s">
+      <c r="QH1" t="s">
         <v>1542</v>
       </c>
-      <c r="QH1" t="s">
+      <c r="QI1" t="s">
         <v>287</v>
       </c>
-      <c r="QI1" t="s">
+      <c r="QJ1" t="s">
         <v>288</v>
       </c>
-      <c r="QJ1" t="s">
+      <c r="QK1" t="s">
         <v>289</v>
       </c>
-      <c r="QK1" t="s">
+      <c r="QL1" t="s">
         <v>290</v>
       </c>
-      <c r="QL1" t="s">
+      <c r="QM1" t="s">
         <v>291</v>
       </c>
-      <c r="QM1" t="s">
+      <c r="QN1" t="s">
         <v>1543</v>
       </c>
-      <c r="QN1" t="s">
+      <c r="QO1" t="s">
         <v>292</v>
       </c>
-      <c r="QO1" t="s">
+      <c r="QP1" t="s">
         <v>293</v>
       </c>
-      <c r="QP1" t="s">
+      <c r="QQ1" t="s">
         <v>294</v>
       </c>
-      <c r="QQ1" t="s">
+      <c r="QR1" t="s">
         <v>295</v>
       </c>
-      <c r="QR1" t="s">
+      <c r="QS1" t="s">
         <v>296</v>
       </c>
-      <c r="QS1" t="s">
+      <c r="QT1" t="s">
         <v>1544</v>
       </c>
-      <c r="QT1" t="s">
+      <c r="QU1" t="s">
         <v>297</v>
       </c>
-      <c r="QU1" t="s">
+      <c r="QV1" t="s">
         <v>298</v>
       </c>
-      <c r="QV1" t="s">
+      <c r="QW1" t="s">
         <v>299</v>
       </c>
-      <c r="QW1" t="s">
+      <c r="QX1" t="s">
         <v>300</v>
       </c>
-      <c r="QX1" t="s">
+      <c r="QY1" t="s">
         <v>301</v>
       </c>
-      <c r="QY1" t="s">
+      <c r="QZ1" t="s">
         <v>1545</v>
       </c>
-      <c r="QZ1" t="s">
+      <c r="RA1" t="s">
         <v>302</v>
       </c>
-      <c r="RA1" t="s">
+      <c r="RB1" t="s">
         <v>1441</v>
       </c>
-      <c r="RB1" t="s">
+      <c r="RC1" t="s">
         <v>1442</v>
       </c>
-      <c r="RC1" t="s">
+      <c r="RD1" t="s">
         <v>1443</v>
       </c>
-      <c r="RD1" t="s">
+      <c r="RE1" t="s">
         <v>1444</v>
       </c>
-      <c r="RE1" t="s">
+      <c r="RF1" t="s">
         <v>1445</v>
       </c>
-      <c r="RF1" t="s">
+      <c r="RG1" t="s">
         <v>1446</v>
       </c>
-      <c r="RG1" t="s">
+      <c r="RH1" t="s">
         <v>1447</v>
       </c>
-      <c r="RH1" t="s">
+      <c r="RI1" t="s">
         <v>1546</v>
       </c>
-      <c r="RI1" t="s">
+      <c r="RJ1" t="s">
         <v>1448</v>
       </c>
-      <c r="RJ1" t="s">
+      <c r="RK1" t="s">
         <v>1449</v>
       </c>
-      <c r="RK1" t="s">
+      <c r="RL1" t="s">
         <v>1450</v>
       </c>
-      <c r="RL1" t="s">
+      <c r="RM1" t="s">
         <v>1451</v>
       </c>
-      <c r="RM1" t="s">
+      <c r="RN1" t="s">
         <v>1547</v>
       </c>
-      <c r="RN1" t="s">
+      <c r="RO1" t="s">
         <v>303</v>
       </c>
-      <c r="RO1" t="s">
+      <c r="RP1" t="s">
         <v>304</v>
       </c>
-      <c r="RP1" t="s">
+      <c r="RQ1" t="s">
         <v>305</v>
       </c>
-      <c r="RQ1" t="s">
+      <c r="RR1" t="s">
         <v>306</v>
       </c>
-      <c r="RR1" t="s">
+      <c r="RS1" t="s">
         <v>1452</v>
       </c>
-      <c r="RS1" t="s">
+      <c r="RT1" t="s">
         <v>1453</v>
       </c>
-      <c r="RT1" t="s">
+      <c r="RU1" t="s">
         <v>1454</v>
       </c>
-      <c r="RU1" t="s">
+      <c r="RV1" t="s">
         <v>1455</v>
       </c>
-      <c r="RV1" t="s">
+      <c r="RW1" t="s">
         <v>1456</v>
       </c>
-      <c r="RW1" t="s">
+      <c r="RX1" t="s">
         <v>1548</v>
       </c>
-      <c r="RX1" t="s">
+      <c r="RY1" t="s">
         <v>308</v>
       </c>
-      <c r="RY1" t="s">
+      <c r="RZ1" t="s">
         <v>948</v>
       </c>
-      <c r="RZ1" t="s">
+      <c r="SA1" t="s">
         <v>949</v>
       </c>
-      <c r="SA1" t="s">
+      <c r="SB1" t="s">
         <v>689</v>
       </c>
-      <c r="SB1" t="s">
+      <c r="SC1" t="s">
         <v>690</v>
       </c>
-      <c r="SC1" t="s">
+      <c r="SD1" t="s">
         <v>691</v>
       </c>
-      <c r="SD1" t="s">
+      <c r="SE1" t="s">
         <v>1077</v>
       </c>
-      <c r="SE1" t="s">
+      <c r="SF1" t="s">
         <v>692</v>
       </c>
-      <c r="SF1" t="s">
+      <c r="SG1" t="s">
         <v>311</v>
       </c>
-      <c r="SG1" t="s">
+      <c r="SH1" t="s">
         <v>312</v>
       </c>
-      <c r="SH1" t="s">
+      <c r="SI1" t="s">
         <v>313</v>
       </c>
-      <c r="SI1" t="s">
+      <c r="SJ1" t="s">
         <v>314</v>
       </c>
-      <c r="SJ1" t="s">
+      <c r="SK1" t="s">
         <v>315</v>
       </c>
-      <c r="SK1" t="s">
+      <c r="SL1" t="s">
         <v>1549</v>
       </c>
-      <c r="SL1" t="s">
+      <c r="SM1" t="s">
         <v>316</v>
       </c>
-      <c r="SM1" t="s">
+      <c r="SN1" t="s">
         <v>317</v>
       </c>
-      <c r="SN1" t="s">
+      <c r="SO1" t="s">
         <v>318</v>
       </c>
-      <c r="SO1" t="s">
+      <c r="SP1" t="s">
         <v>319</v>
       </c>
-      <c r="SP1" t="s">
+      <c r="SQ1" t="s">
         <v>320</v>
       </c>
-      <c r="SQ1" t="s">
+      <c r="SR1" t="s">
         <v>321</v>
       </c>
-      <c r="SR1" t="s">
+      <c r="SS1" t="s">
         <v>322</v>
       </c>
-      <c r="SS1" t="s">
+      <c r="ST1" t="s">
         <v>323</v>
       </c>
-      <c r="ST1" t="s">
+      <c r="SU1" t="s">
         <v>324</v>
       </c>
-      <c r="SU1" t="s">
+      <c r="SV1" t="s">
         <v>325</v>
       </c>
-      <c r="SV1" t="s">
+      <c r="SW1" t="s">
         <v>326</v>
       </c>
-      <c r="SW1" t="s">
+      <c r="SX1" t="s">
         <v>327</v>
       </c>
-      <c r="SX1" t="s">
+      <c r="SY1" t="s">
         <v>328</v>
       </c>
-      <c r="SY1" t="s">
+      <c r="SZ1" t="s">
         <v>329</v>
       </c>
-      <c r="SZ1" t="s">
+      <c r="TA1" t="s">
         <v>330</v>
       </c>
-      <c r="TA1" t="s">
+      <c r="TB1" t="s">
         <v>331</v>
       </c>
-      <c r="TB1" t="s">
+      <c r="TC1" t="s">
         <v>332</v>
       </c>
-      <c r="TC1" t="s">
+      <c r="TD1" t="s">
         <v>333</v>
       </c>
-      <c r="TD1" t="s">
+      <c r="TE1" t="s">
         <v>334</v>
       </c>
-      <c r="TE1" t="s">
+      <c r="TF1" t="s">
         <v>335</v>
       </c>
-      <c r="TF1" t="s">
+      <c r="TG1" t="s">
         <v>336</v>
       </c>
-      <c r="TG1" t="s">
+      <c r="TH1" t="s">
         <v>337</v>
       </c>
-      <c r="TH1" t="s">
+      <c r="TI1" t="s">
         <v>338</v>
       </c>
-      <c r="TI1" t="s">
+      <c r="TJ1" t="s">
         <v>339</v>
       </c>
-      <c r="TJ1" t="s">
+      <c r="TK1" t="s">
         <v>340</v>
       </c>
-      <c r="TK1" t="s">
+      <c r="TL1" t="s">
         <v>341</v>
       </c>
-      <c r="TL1" t="s">
+      <c r="TM1" t="s">
         <v>342</v>
       </c>
-      <c r="TM1" t="s">
+      <c r="TN1" t="s">
         <v>343</v>
       </c>
-      <c r="TN1" t="s">
+      <c r="TO1" t="s">
         <v>344</v>
       </c>
-      <c r="TO1" t="s">
+      <c r="TP1" t="s">
         <v>345</v>
       </c>
-      <c r="TP1" t="s">
+      <c r="TQ1" t="s">
         <v>346</v>
       </c>
-      <c r="TQ1" t="s">
+      <c r="TR1" t="s">
         <v>347</v>
       </c>
-      <c r="TR1" t="s">
+      <c r="TS1" t="s">
         <v>348</v>
       </c>
-      <c r="TS1" t="s">
+      <c r="TT1" t="s">
         <v>349</v>
       </c>
-      <c r="TT1" t="s">
+      <c r="TU1" t="s">
         <v>350</v>
       </c>
-      <c r="TU1" t="s">
+      <c r="TV1" t="s">
         <v>351</v>
       </c>
-      <c r="TV1" t="s">
+      <c r="TW1" t="s">
         <v>352</v>
       </c>
-      <c r="TW1" t="s">
+      <c r="TX1" t="s">
         <v>1550</v>
       </c>
-      <c r="TX1" t="s">
+      <c r="TY1" t="s">
         <v>1551</v>
       </c>
-      <c r="TY1" t="s">
+      <c r="TZ1" t="s">
         <v>1552</v>
       </c>
-      <c r="TZ1" t="s">
+      <c r="UA1" t="s">
         <v>1553</v>
       </c>
-      <c r="UA1" t="s">
+      <c r="UB1" t="s">
         <v>1554</v>
       </c>
-      <c r="UB1" t="s">
+      <c r="UC1" t="s">
         <v>1555</v>
       </c>
-      <c r="UC1" t="s">
+      <c r="UD1" t="s">
         <v>353</v>
       </c>
-      <c r="UD1" t="s">
+      <c r="UE1" t="s">
         <v>354</v>
       </c>
-      <c r="UE1" t="s">
+      <c r="UF1" t="s">
         <v>355</v>
       </c>
-      <c r="UF1" t="s">
+      <c r="UG1" t="s">
         <v>356</v>
       </c>
-      <c r="UG1" t="s">
+      <c r="UH1" t="s">
         <v>705</v>
       </c>
-      <c r="UH1" t="s">
+      <c r="UI1" t="s">
         <v>1556</v>
       </c>
-      <c r="UI1" t="s">
+      <c r="UJ1" t="s">
         <v>1557</v>
       </c>
-      <c r="UJ1" t="s">
+      <c r="UK1" t="s">
         <v>4</v>
       </c>
-      <c r="UK1" t="s">
+      <c r="UL1" t="s">
         <v>357</v>
       </c>
-      <c r="UL1" t="s">
+      <c r="UM1" t="s">
         <v>358</v>
       </c>
-      <c r="UM1" t="s">
+      <c r="UN1" t="s">
         <v>359</v>
       </c>
-      <c r="UN1" t="s">
+      <c r="UO1" t="s">
         <v>360</v>
       </c>
-      <c r="UO1" t="s">
+      <c r="UP1" t="s">
         <v>361</v>
       </c>
-      <c r="UP1" t="s">
+      <c r="UQ1" t="s">
         <v>362</v>
       </c>
-      <c r="UQ1" t="s">
+      <c r="UR1" t="s">
         <v>363</v>
       </c>
-      <c r="UR1" t="s">
+      <c r="US1" t="s">
         <v>364</v>
       </c>
-      <c r="US1" t="s">
+      <c r="UT1" t="s">
         <v>365</v>
       </c>
-      <c r="UT1" t="s">
+      <c r="UU1" t="s">
         <v>366</v>
       </c>
-      <c r="UU1" t="s">
+      <c r="UV1" t="s">
         <v>367</v>
       </c>
-      <c r="UV1" t="s">
+      <c r="UW1" t="s">
         <v>368</v>
       </c>
-      <c r="UW1" t="s">
+      <c r="UX1" t="s">
         <v>369</v>
       </c>
-      <c r="UX1" t="s">
+      <c r="UY1" t="s">
         <v>370</v>
       </c>
-      <c r="UY1" t="s">
+      <c r="UZ1" t="s">
         <v>371</v>
       </c>
-      <c r="UZ1" t="s">
+      <c r="VA1" t="s">
         <v>372</v>
       </c>
-      <c r="VA1" t="s">
+      <c r="VB1" t="s">
         <v>373</v>
       </c>
-      <c r="VB1" t="s">
+      <c r="VC1" t="s">
         <v>374</v>
       </c>
-      <c r="VC1" t="s">
+      <c r="VD1" t="s">
         <v>375</v>
       </c>
-      <c r="VD1" t="s">
+      <c r="VE1" t="s">
         <v>376</v>
       </c>
-      <c r="VE1" t="s">
+      <c r="VF1" t="s">
         <v>377</v>
       </c>
-      <c r="VF1" t="s">
+      <c r="VG1" t="s">
         <v>378</v>
       </c>
-      <c r="VG1" t="s">
+      <c r="VH1" t="s">
         <v>379</v>
       </c>
-      <c r="VH1" t="s">
+      <c r="VI1" t="s">
         <v>380</v>
       </c>
-      <c r="VI1" t="s">
+      <c r="VJ1" t="s">
         <v>381</v>
       </c>
-      <c r="VJ1" t="s">
+      <c r="VK1" t="s">
         <v>382</v>
       </c>
-      <c r="VK1" t="s">
+      <c r="VL1" t="s">
         <v>383</v>
       </c>
-      <c r="VL1" t="s">
+      <c r="VM1" t="s">
         <v>384</v>
       </c>
-      <c r="VM1" t="s">
+      <c r="VN1" t="s">
         <v>385</v>
       </c>
-      <c r="VN1" t="s">
+      <c r="VO1" t="s">
         <v>386</v>
       </c>
-      <c r="VO1" t="s">
+      <c r="VP1" t="s">
         <v>387</v>
       </c>
-      <c r="VP1" t="s">
+      <c r="VQ1" t="s">
         <v>388</v>
       </c>
-      <c r="VQ1" t="s">
+      <c r="VR1" t="s">
         <v>389</v>
       </c>
-      <c r="VR1" t="s">
+      <c r="VS1" t="s">
         <v>390</v>
       </c>
-      <c r="VS1" t="s">
+      <c r="VT1" t="s">
         <v>391</v>
       </c>
-      <c r="VT1" t="s">
+      <c r="VU1" t="s">
         <v>392</v>
       </c>
-      <c r="VU1" t="s">
+      <c r="VV1" t="s">
         <v>393</v>
       </c>
-      <c r="VV1" t="s">
+      <c r="VW1" t="s">
         <v>394</v>
       </c>
-      <c r="VW1" t="s">
+      <c r="VX1" t="s">
         <v>17</v>
       </c>
-      <c r="VX1" t="s">
+      <c r="VY1" t="s">
         <v>395</v>
       </c>
-      <c r="VY1" t="s">
+      <c r="VZ1" t="s">
         <v>396</v>
       </c>
-      <c r="VZ1" t="s">
+      <c r="WA1" t="s">
         <v>397</v>
       </c>
-      <c r="WA1" t="s">
+      <c r="WB1" t="s">
         <v>398</v>
       </c>
-      <c r="WB1" t="s">
+      <c r="WC1" t="s">
         <v>399</v>
       </c>
-      <c r="WC1" t="s">
+      <c r="WD1" t="s">
         <v>400</v>
       </c>
-      <c r="WD1" t="s">
+      <c r="WE1" t="s">
         <v>401</v>
       </c>
-      <c r="WE1" t="s">
+      <c r="WF1" t="s">
         <v>402</v>
       </c>
-      <c r="WF1" t="s">
+      <c r="WG1" t="s">
         <v>403</v>
       </c>
-      <c r="WG1" t="s">
+      <c r="WH1" t="s">
         <v>404</v>
       </c>
-      <c r="WH1" t="s">
+      <c r="WI1" t="s">
         <v>405</v>
       </c>
-      <c r="WI1" t="s">
+      <c r="WJ1" t="s">
         <v>406</v>
       </c>
-      <c r="WJ1" t="s">
+      <c r="WK1" t="s">
         <v>407</v>
       </c>
-      <c r="WK1" t="s">
+      <c r="WL1" t="s">
         <v>408</v>
       </c>
-      <c r="WL1" t="s">
+      <c r="WM1" t="s">
         <v>409</v>
       </c>
-      <c r="WM1" t="s">
+      <c r="WN1" t="s">
         <v>410</v>
       </c>
-      <c r="WN1" t="s">
+      <c r="WO1" t="s">
         <v>411</v>
       </c>
-      <c r="WO1" t="s">
+      <c r="WP1" t="s">
         <v>412</v>
       </c>
-      <c r="WP1" t="s">
+      <c r="WQ1" t="s">
         <v>413</v>
       </c>
-      <c r="WQ1" t="s">
+      <c r="WR1" t="s">
         <v>414</v>
       </c>
-      <c r="WR1" t="s">
+      <c r="WS1" t="s">
         <v>415</v>
       </c>
-      <c r="WS1" t="s">
+      <c r="WT1" t="s">
         <v>416</v>
       </c>
-      <c r="WT1" t="s">
+      <c r="WU1" t="s">
         <v>417</v>
       </c>
-      <c r="WU1" t="s">
+      <c r="WV1" t="s">
         <v>418</v>
       </c>
-      <c r="WV1" t="s">
+      <c r="WW1" t="s">
         <v>419</v>
       </c>
-      <c r="WW1" t="s">
+      <c r="WX1" t="s">
         <v>420</v>
       </c>
-      <c r="WX1" t="s">
+      <c r="WY1" t="s">
         <v>421</v>
       </c>
-      <c r="WY1" t="s">
+      <c r="WZ1" t="s">
         <v>422</v>
       </c>
-      <c r="WZ1" t="s">
+      <c r="XA1" t="s">
         <v>423</v>
       </c>
-      <c r="XA1" t="s">
+      <c r="XB1" t="s">
         <v>424</v>
       </c>
-      <c r="XB1" t="s">
+      <c r="XC1" t="s">
         <v>425</v>
       </c>
-      <c r="XC1" t="s">
+      <c r="XD1" t="s">
         <v>426</v>
       </c>
-      <c r="XD1" t="s">
+      <c r="XE1" t="s">
         <v>427</v>
       </c>
-      <c r="XE1" t="s">
+      <c r="XF1" t="s">
         <v>428</v>
       </c>
-      <c r="XF1" t="s">
+      <c r="XG1" t="s">
         <v>429</v>
       </c>
-      <c r="XG1" t="s">
+      <c r="XH1" t="s">
         <v>430</v>
       </c>
-      <c r="XH1" t="s">
+      <c r="XI1" t="s">
         <v>431</v>
       </c>
-      <c r="XI1" t="s">
+      <c r="XJ1" t="s">
         <v>432</v>
       </c>
-      <c r="XJ1" t="s">
+      <c r="XK1" t="s">
         <v>433</v>
       </c>
-      <c r="XK1" t="s">
+      <c r="XL1" t="s">
         <v>434</v>
       </c>
-      <c r="XL1" t="s">
+      <c r="XM1" t="s">
         <v>435</v>
       </c>
-      <c r="XM1" t="s">
+      <c r="XN1" t="s">
         <v>436</v>
       </c>
-      <c r="XN1" t="s">
+      <c r="XO1" t="s">
         <v>437</v>
       </c>
-      <c r="XO1" t="s">
+      <c r="XP1" t="s">
         <v>438</v>
       </c>
-      <c r="XP1" t="s">
+      <c r="XQ1" t="s">
         <v>439</v>
       </c>
-      <c r="XQ1" t="s">
+      <c r="XR1" t="s">
         <v>440</v>
       </c>
-      <c r="XR1" t="s">
+      <c r="XS1" t="s">
         <v>441</v>
       </c>
-      <c r="XS1" t="s">
+      <c r="XT1" t="s">
         <v>442</v>
       </c>
-      <c r="XT1" t="s">
+      <c r="XU1" t="s">
         <v>443</v>
       </c>
-      <c r="XU1" t="s">
+      <c r="XV1" t="s">
         <v>444</v>
       </c>
-      <c r="XV1" t="s">
+      <c r="XW1" t="s">
         <v>445</v>
       </c>
-      <c r="XW1" t="s">
+      <c r="XX1" t="s">
         <v>446</v>
       </c>
-      <c r="XX1" t="s">
+      <c r="XY1" t="s">
         <v>447</v>
       </c>
-      <c r="XY1" t="s">
+      <c r="XZ1" t="s">
         <v>448</v>
       </c>
-      <c r="XZ1" t="s">
+      <c r="YA1" t="s">
         <v>449</v>
       </c>
-      <c r="YA1" t="s">
+      <c r="YB1" t="s">
         <v>450</v>
       </c>
-      <c r="YB1" t="s">
+      <c r="YC1" t="s">
         <v>451</v>
       </c>
-      <c r="YC1" t="s">
+      <c r="YD1" t="s">
         <v>452</v>
       </c>
-      <c r="YD1" t="s">
+      <c r="YE1" t="s">
         <v>453</v>
       </c>
-      <c r="YE1" t="s">
+      <c r="YF1" t="s">
         <v>454</v>
       </c>
-      <c r="YF1" t="s">
+      <c r="YG1" t="s">
         <v>455</v>
       </c>
-      <c r="YG1" t="s">
+      <c r="YH1" t="s">
         <v>456</v>
       </c>
-      <c r="YH1" t="s">
+      <c r="YI1" t="s">
         <v>457</v>
       </c>
-      <c r="YI1" t="s">
+      <c r="YJ1" t="s">
         <v>458</v>
       </c>
-      <c r="YJ1" t="s">
+      <c r="YK1" t="s">
         <v>459</v>
       </c>
-      <c r="YK1" t="s">
+      <c r="YL1" t="s">
         <v>460</v>
       </c>
-      <c r="YL1" t="s">
+      <c r="YM1" t="s">
         <v>461</v>
       </c>
-      <c r="YM1" t="s">
+      <c r="YN1" t="s">
         <v>462</v>
       </c>
-      <c r="YN1" t="s">
+      <c r="YO1" t="s">
         <v>463</v>
       </c>
-      <c r="YO1" t="s">
+      <c r="YP1" t="s">
         <v>464</v>
       </c>
-      <c r="YP1" t="s">
+      <c r="YQ1" t="s">
         <v>465</v>
       </c>
-      <c r="YQ1" t="s">
+      <c r="YR1" t="s">
         <v>466</v>
       </c>
-      <c r="YR1" t="s">
+      <c r="YS1" t="s">
         <v>467</v>
       </c>
-      <c r="YS1" t="s">
+      <c r="YT1" t="s">
         <v>468</v>
       </c>
-      <c r="YT1" t="s">
+      <c r="YU1" t="s">
         <v>469</v>
       </c>
-      <c r="YU1" t="s">
+      <c r="YV1" t="s">
         <v>470</v>
       </c>
-      <c r="YV1" t="s">
+      <c r="YW1" t="s">
         <v>471</v>
       </c>
-      <c r="YW1" t="s">
+      <c r="YX1" t="s">
         <v>472</v>
       </c>
-      <c r="YX1" t="s">
+      <c r="YY1" t="s">
         <v>473</v>
       </c>
-      <c r="YY1" t="s">
+      <c r="YZ1" t="s">
         <v>474</v>
       </c>
-      <c r="YZ1" t="s">
+      <c r="ZA1" t="s">
         <v>475</v>
       </c>
-      <c r="ZA1" t="s">
+      <c r="ZB1" t="s">
         <v>476</v>
       </c>
-      <c r="ZB1" t="s">
+      <c r="ZC1" t="s">
         <v>477</v>
       </c>
-      <c r="ZC1" t="s">
+      <c r="ZD1" t="s">
         <v>478</v>
       </c>
-      <c r="ZD1" t="s">
+      <c r="ZE1" t="s">
         <v>479</v>
       </c>
-      <c r="ZE1" t="s">
+      <c r="ZF1" t="s">
         <v>480</v>
       </c>
-      <c r="ZF1" t="s">
+      <c r="ZG1" t="s">
         <v>1558</v>
       </c>
-      <c r="ZG1" t="s">
+      <c r="ZH1" t="s">
         <v>481</v>
       </c>
-      <c r="ZH1" t="s">
+      <c r="ZI1" t="s">
         <v>482</v>
       </c>
-      <c r="ZI1" t="s">
+      <c r="ZJ1" t="s">
         <v>483</v>
       </c>
-      <c r="ZJ1" t="s">
+      <c r="ZK1" t="s">
         <v>484</v>
       </c>
-      <c r="ZK1" t="s">
+      <c r="ZL1" t="s">
         <v>485</v>
       </c>
-      <c r="ZL1" t="s">
+      <c r="ZM1" t="s">
         <v>1559</v>
       </c>
-      <c r="ZM1" t="s">
+      <c r="ZN1" t="s">
         <v>486</v>
       </c>
-      <c r="ZN1" t="s">
+      <c r="ZO1" t="s">
         <v>487</v>
       </c>
-      <c r="ZO1" t="s">
+      <c r="ZP1" t="s">
         <v>488</v>
       </c>
-      <c r="ZP1" t="s">
+      <c r="ZQ1" t="s">
         <v>489</v>
       </c>
-      <c r="ZQ1" t="s">
+      <c r="ZR1" t="s">
         <v>490</v>
       </c>
-      <c r="ZR1" t="s">
+      <c r="ZS1" t="s">
         <v>88</v>
       </c>
-      <c r="ZS1" t="s">
+      <c r="ZT1" t="s">
         <v>89</v>
       </c>
-      <c r="ZT1" t="s">
+      <c r="ZU1" t="s">
         <v>90</v>
       </c>
-      <c r="ZU1" t="s">
+      <c r="ZV1" t="s">
         <v>91</v>
       </c>
-      <c r="ZV1" t="s">
+      <c r="ZW1" t="s">
         <v>693</v>
       </c>
-      <c r="ZW1" t="s">
+      <c r="ZX1" t="s">
         <v>92</v>
       </c>
-      <c r="ZX1" t="s">
+      <c r="ZY1" t="s">
         <v>694</v>
       </c>
-      <c r="ZY1" t="s">
+      <c r="ZZ1" t="s">
         <v>695</v>
       </c>
-      <c r="ZZ1" t="s">
+      <c r="AAA1" t="s">
         <v>696</v>
       </c>
-      <c r="AAA1" t="s">
+      <c r="AAB1" t="s">
         <v>697</v>
       </c>
-      <c r="AAB1" t="s">
+      <c r="AAC1" t="s">
         <v>111</v>
       </c>
-      <c r="AAC1" t="s">
+      <c r="AAD1" t="s">
         <v>194</v>
       </c>
-      <c r="AAD1" t="s">
+      <c r="AAE1" t="s">
         <v>491</v>
       </c>
-      <c r="AAE1" t="s">
+      <c r="AAF1" t="s">
         <v>112</v>
       </c>
-      <c r="AAF1" t="s">
+      <c r="AAG1" t="s">
         <v>492</v>
       </c>
-      <c r="AAG1" t="s">
+      <c r="AAH1" t="s">
         <v>493</v>
       </c>
-      <c r="AAH1" t="s">
+      <c r="AAI1" t="s">
         <v>113</v>
       </c>
-      <c r="AAI1" t="s">
+      <c r="AAJ1" t="s">
         <v>494</v>
       </c>
-      <c r="AAJ1" t="s">
+      <c r="AAK1" t="s">
         <v>495</v>
       </c>
-      <c r="AAK1" t="s">
+      <c r="AAL1" t="s">
         <v>114</v>
       </c>
-      <c r="AAL1" t="s">
+      <c r="AAM1" t="s">
         <v>200</v>
       </c>
-      <c r="AAM1" t="s">
+      <c r="AAN1" t="s">
         <v>496</v>
       </c>
-      <c r="AAN1" t="s">
+      <c r="AAO1" t="s">
         <v>115</v>
       </c>
-      <c r="AAO1" t="s">
+      <c r="AAP1" t="s">
         <v>497</v>
       </c>
-      <c r="AAP1" t="s">
+      <c r="AAQ1" t="s">
         <v>498</v>
       </c>
-      <c r="AAQ1" t="s">
+      <c r="AAR1" t="s">
         <v>499</v>
       </c>
-      <c r="AAR1" t="s">
+      <c r="AAS1" t="s">
         <v>500</v>
       </c>
-      <c r="AAS1" t="s">
+      <c r="AAT1" t="s">
         <v>501</v>
       </c>
-      <c r="AAT1" t="s">
+      <c r="AAU1" t="s">
         <v>502</v>
       </c>
-      <c r="AAU1" t="s">
+      <c r="AAV1" t="s">
         <v>503</v>
       </c>
-      <c r="AAV1" t="s">
+      <c r="AAW1" t="s">
         <v>116</v>
       </c>
-      <c r="AAW1" t="s">
+      <c r="AAX1" t="s">
         <v>504</v>
       </c>
-      <c r="AAX1" t="s">
+      <c r="AAY1" t="s">
         <v>505</v>
       </c>
-      <c r="AAY1" t="s">
+      <c r="AAZ1" t="s">
         <v>506</v>
       </c>
-      <c r="AAZ1" t="s">
+      <c r="ABA1" t="s">
         <v>507</v>
       </c>
-      <c r="ABA1" t="s">
+      <c r="ABB1" t="s">
         <v>508</v>
       </c>
-      <c r="ABB1" t="s">
+      <c r="ABC1" t="s">
         <v>509</v>
       </c>
-      <c r="ABC1" t="s">
+      <c r="ABD1" t="s">
         <v>510</v>
       </c>
-      <c r="ABD1" t="s">
+      <c r="ABE1" t="s">
         <v>511</v>
       </c>
-      <c r="ABE1" t="s">
+      <c r="ABF1" t="s">
         <v>512</v>
       </c>
-      <c r="ABF1" t="s">
+      <c r="ABG1" t="s">
         <v>513</v>
       </c>
-      <c r="ABG1" t="s">
+      <c r="ABH1" t="s">
         <v>514</v>
       </c>
-      <c r="ABH1" t="s">
+      <c r="ABI1" t="s">
         <v>515</v>
       </c>
-      <c r="ABI1" t="s">
+      <c r="ABJ1" t="s">
         <v>516</v>
       </c>
-      <c r="ABJ1" t="s">
+      <c r="ABK1" t="s">
         <v>517</v>
       </c>
-      <c r="ABK1" t="s">
+      <c r="ABL1" t="s">
         <v>518</v>
       </c>
-      <c r="ABL1" t="s">
+      <c r="ABM1" t="s">
         <v>519</v>
       </c>
-      <c r="ABM1" t="s">
+      <c r="ABN1" t="s">
         <v>520</v>
       </c>
-      <c r="ABN1" t="s">
+      <c r="ABO1" t="s">
         <v>521</v>
       </c>
-      <c r="ABO1" t="s">
+      <c r="ABP1" t="s">
         <v>522</v>
       </c>
-      <c r="ABP1" t="s">
+      <c r="ABQ1" t="s">
         <v>523</v>
       </c>
-      <c r="ABQ1" t="s">
+      <c r="ABR1" t="s">
         <v>524</v>
       </c>
-      <c r="ABR1" t="s">
+      <c r="ABS1" t="s">
         <v>525</v>
       </c>
-      <c r="ABS1" t="s">
+      <c r="ABT1" t="s">
         <v>526</v>
       </c>
-      <c r="ABT1" t="s">
+      <c r="ABU1" t="s">
         <v>527</v>
       </c>
-      <c r="ABU1" t="s">
+      <c r="ABV1" t="s">
         <v>528</v>
       </c>
-      <c r="ABV1" t="s">
+      <c r="ABW1" t="s">
         <v>529</v>
       </c>
-      <c r="ABW1" t="s">
+      <c r="ABX1" t="s">
         <v>530</v>
       </c>
-      <c r="ABX1" t="s">
+      <c r="ABY1" t="s">
         <v>531</v>
       </c>
-      <c r="ABY1" t="s">
+      <c r="ABZ1" t="s">
         <v>532</v>
       </c>
-      <c r="ABZ1" t="s">
+      <c r="ACA1" t="s">
         <v>533</v>
       </c>
-      <c r="ACA1" t="s">
+      <c r="ACB1" t="s">
         <v>534</v>
       </c>
-      <c r="ACB1" t="s">
+      <c r="ACC1" t="s">
         <v>535</v>
       </c>
-      <c r="ACC1" t="s">
+      <c r="ACD1" t="s">
         <v>536</v>
       </c>
-      <c r="ACD1" t="s">
+      <c r="ACE1" t="s">
         <v>537</v>
       </c>
-      <c r="ACE1" t="s">
+      <c r="ACF1" t="s">
         <v>538</v>
       </c>
-      <c r="ACF1" t="s">
+      <c r="ACG1" t="s">
         <v>539</v>
       </c>
-      <c r="ACG1" t="s">
+      <c r="ACH1" t="s">
         <v>540</v>
       </c>
-      <c r="ACH1" t="s">
+      <c r="ACI1" t="s">
         <v>541</v>
       </c>
-      <c r="ACI1" t="s">
+      <c r="ACJ1" t="s">
         <v>542</v>
       </c>
-      <c r="ACJ1" t="s">
+      <c r="ACK1" t="s">
         <v>543</v>
       </c>
-      <c r="ACK1" t="s">
+      <c r="ACL1" t="s">
         <v>544</v>
       </c>
-      <c r="ACL1" t="s">
+      <c r="ACM1" t="s">
         <v>545</v>
       </c>
-      <c r="ACM1" t="s">
+      <c r="ACN1" t="s">
         <v>95</v>
       </c>
-      <c r="ACN1" t="s">
+      <c r="ACO1" t="s">
         <v>96</v>
       </c>
-      <c r="ACO1" t="s">
+      <c r="ACP1" t="s">
         <v>97</v>
       </c>
-      <c r="ACP1" t="s">
+      <c r="ACQ1" t="s">
         <v>98</v>
       </c>
-      <c r="ACQ1" t="s">
+      <c r="ACR1" t="s">
         <v>99</v>
       </c>
-      <c r="ACR1" t="s">
+      <c r="ACS1" t="s">
         <v>100</v>
       </c>
-      <c r="ACS1" t="s">
+      <c r="ACT1" t="s">
         <v>101</v>
       </c>
-      <c r="ACT1" t="s">
+      <c r="ACU1" t="s">
         <v>546</v>
       </c>
-      <c r="ACU1" t="s">
+      <c r="ACV1" t="s">
         <v>547</v>
       </c>
-      <c r="ACV1" t="s">
+      <c r="ACW1" t="s">
         <v>103</v>
       </c>
-      <c r="ACW1" t="s">
+      <c r="ACX1" t="s">
         <v>548</v>
       </c>
-      <c r="ACX1" t="s">
+      <c r="ACY1" t="s">
         <v>549</v>
       </c>
-      <c r="ACY1" t="s">
+      <c r="ACZ1" t="s">
         <v>550</v>
       </c>
-      <c r="ACZ1" t="s">
+      <c r="ADA1" t="s">
         <v>551</v>
       </c>
-      <c r="ADA1" t="s">
+      <c r="ADB1" t="s">
         <v>552</v>
       </c>
-      <c r="ADB1" t="s">
+      <c r="ADC1" t="s">
         <v>553</v>
       </c>
-      <c r="ADC1" t="s">
+      <c r="ADD1" t="s">
         <v>554</v>
       </c>
-      <c r="ADD1" t="s">
+      <c r="ADE1" t="s">
         <v>555</v>
       </c>
-      <c r="ADE1" t="s">
+      <c r="ADF1" t="s">
         <v>556</v>
       </c>
-      <c r="ADF1" t="s">
+      <c r="ADG1" t="s">
         <v>557</v>
       </c>
-      <c r="ADG1" t="s">
+      <c r="ADH1" t="s">
         <v>1560</v>
       </c>
-      <c r="ADH1" t="s">
+      <c r="ADI1" t="s">
         <v>558</v>
       </c>
-      <c r="ADI1" t="s">
+      <c r="ADJ1" t="s">
         <v>559</v>
       </c>
-      <c r="ADJ1" t="s">
+      <c r="ADK1" t="s">
         <v>560</v>
       </c>
-      <c r="ADK1" t="s">
+      <c r="ADL1" t="s">
         <v>1561</v>
       </c>
-      <c r="ADL1" t="s">
+      <c r="ADM1" t="s">
         <v>561</v>
       </c>
-      <c r="ADM1" t="s">
+      <c r="ADN1" t="s">
         <v>562</v>
       </c>
-      <c r="ADN1" t="s">
+      <c r="ADO1" t="s">
         <v>563</v>
       </c>
-      <c r="ADO1" t="s">
+      <c r="ADP1" t="s">
         <v>564</v>
       </c>
-      <c r="ADP1" t="s">
+      <c r="ADQ1" t="s">
         <v>565</v>
       </c>
-      <c r="ADQ1" t="s">
+      <c r="ADR1" t="s">
         <v>566</v>
       </c>
-      <c r="ADR1" t="s">
+      <c r="ADS1" t="s">
         <v>567</v>
       </c>
-      <c r="ADS1" t="s">
+      <c r="ADT1" t="s">
         <v>568</v>
       </c>
-      <c r="ADT1" t="s">
+      <c r="ADU1" t="s">
         <v>569</v>
       </c>
-      <c r="ADU1" t="s">
+      <c r="ADV1" t="s">
         <v>570</v>
       </c>
-      <c r="ADV1" t="s">
+      <c r="ADW1" t="s">
         <v>571</v>
       </c>
-      <c r="ADW1" t="s">
+      <c r="ADX1" t="s">
         <v>572</v>
       </c>
-      <c r="ADX1" t="s">
+      <c r="ADY1" t="s">
         <v>573</v>
       </c>
-      <c r="ADY1" t="s">
+      <c r="ADZ1" t="s">
         <v>574</v>
       </c>
-      <c r="ADZ1" t="s">
+      <c r="AEA1" t="s">
         <v>1562</v>
       </c>
-      <c r="AEA1" t="s">
+      <c r="AEB1" t="s">
         <v>157</v>
       </c>
-      <c r="AEB1" t="s">
+      <c r="AEC1" t="s">
         <v>575</v>
       </c>
-      <c r="AEC1" t="s">
+      <c r="AED1" t="s">
         <v>576</v>
       </c>
-      <c r="AED1" t="s">
+      <c r="AEE1" t="s">
         <v>1563</v>
       </c>
-      <c r="AEE1" t="s">
+      <c r="AEF1" t="s">
         <v>577</v>
       </c>
-      <c r="AEF1" t="s">
+      <c r="AEG1" t="s">
         <v>214</v>
       </c>
-      <c r="AEG1" t="s">
+      <c r="AEH1" t="s">
         <v>578</v>
       </c>
-      <c r="AEH1" t="s">
+      <c r="AEI1" t="s">
         <v>579</v>
       </c>
-      <c r="AEI1" t="s">
+      <c r="AEJ1" t="s">
         <v>1564</v>
       </c>
-      <c r="AEJ1" t="s">
+      <c r="AEK1" t="s">
         <v>663</v>
       </c>
-      <c r="AEK1" t="s">
+      <c r="AEL1" t="s">
         <v>664</v>
       </c>
-      <c r="AEL1" t="s">
+      <c r="AEM1" t="s">
         <v>665</v>
       </c>
-      <c r="AEM1" t="s">
+      <c r="AEN1" t="s">
         <v>668</v>
       </c>
-      <c r="AEN1" t="s">
+      <c r="AEO1" t="s">
         <v>669</v>
       </c>
-      <c r="AEO1" t="s">
+      <c r="AEP1" t="s">
         <v>670</v>
       </c>
-      <c r="AEP1" t="s">
+      <c r="AEQ1" t="s">
         <v>673</v>
       </c>
-      <c r="AEQ1" t="s">
+      <c r="AER1" t="s">
         <v>674</v>
       </c>
-      <c r="AER1" t="s">
+      <c r="AES1" t="s">
         <v>675</v>
       </c>
-      <c r="AES1" t="s">
+      <c r="AET1" t="s">
         <v>1565</v>
       </c>
-      <c r="AET1" t="s">
+      <c r="AEU1" t="s">
         <v>1566</v>
       </c>
-      <c r="AEU1" t="s">
+      <c r="AEV1" t="s">
         <v>307</v>
       </c>
-      <c r="AEV1" t="s">
+      <c r="AEW1" t="s">
         <v>309</v>
       </c>
-      <c r="AEW1" t="s">
+      <c r="AEX1" t="s">
         <v>310</v>
       </c>
-      <c r="AEX1" t="s">
+      <c r="AEY1" t="s">
         <v>580</v>
       </c>
-      <c r="AEY1" t="s">
+      <c r="AEZ1" t="s">
         <v>581</v>
       </c>
-      <c r="AEZ1" t="s">
+      <c r="AFA1" t="s">
         <v>582</v>
       </c>
-      <c r="AFA1" t="s">
+      <c r="AFB1" t="s">
         <v>583</v>
       </c>
-      <c r="AFB1" t="s">
+      <c r="AFC1" t="s">
         <v>584</v>
       </c>
-      <c r="AFC1" t="s">
+      <c r="AFD1" t="s">
         <v>585</v>
       </c>
-      <c r="AFD1" t="s">
+      <c r="AFE1" t="s">
         <v>586</v>
       </c>
-      <c r="AFE1" t="s">
+      <c r="AFF1" t="s">
         <v>587</v>
       </c>
-      <c r="AFF1" t="s">
+      <c r="AFG1" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="2" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>46297</v>
       </c>
@@ -9738,32 +9793,32 @@
       <c r="EM2">
         <v>1</v>
       </c>
-      <c r="UJ2" t="s">
+      <c r="UK2" t="s">
         <v>708</v>
       </c>
-      <c r="AEX2">
+      <c r="AEY2">
         <v>884394036</v>
       </c>
-      <c r="AEY2" t="s">
+      <c r="AEZ2" t="s">
         <v>733</v>
       </c>
-      <c r="AEZ2" s="1">
+      <c r="AFA2" s="1">
         <v>46297.550879629627</v>
       </c>
-      <c r="AFB2" t="s">
+      <c r="AFC2" t="s">
         <v>734</v>
       </c>
-      <c r="AFD2" t="s">
+      <c r="AFE2" t="s">
         <v>735</v>
       </c>
-      <c r="AFE2" t="s">
+      <c r="AFF2" t="s">
         <v>736</v>
       </c>
-      <c r="AFF2">
+      <c r="AFG2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>46297</v>
       </c>
@@ -9782,98 +9837,98 @@
       <c r="G3" t="s">
         <v>739</v>
       </c>
-      <c r="SU3" t="s">
+      <c r="SV3" t="s">
         <v>740</v>
       </c>
-      <c r="SV3">
-        <v>1</v>
-      </c>
       <c r="SW3">
-        <v>0</v>
-      </c>
-      <c r="SX3" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX3">
+        <v>0</v>
+      </c>
+      <c r="SY3" t="s">
         <v>741</v>
       </c>
-      <c r="SY3">
+      <c r="SZ3">
         <v>16</v>
       </c>
-      <c r="SZ3">
+      <c r="TA3">
         <v>25</v>
       </c>
-      <c r="TA3" t="s">
+      <c r="TB3" t="s">
         <v>742</v>
       </c>
-      <c r="TB3" s="1">
+      <c r="TC3" s="1">
         <v>46297</v>
       </c>
-      <c r="TC3" t="s">
+      <c r="TD3" t="s">
         <v>743</v>
       </c>
-      <c r="TD3" t="s">
+      <c r="TE3" t="s">
         <v>744</v>
       </c>
-      <c r="TE3">
+      <c r="TF3">
         <v>12</v>
       </c>
-      <c r="TF3">
+      <c r="TG3">
         <v>24</v>
       </c>
-      <c r="TG3">
-        <v>0</v>
-      </c>
       <c r="TH3">
         <v>0</v>
       </c>
-      <c r="TI3" t="s">
+      <c r="TI3">
+        <v>0</v>
+      </c>
+      <c r="TJ3" t="s">
         <v>745</v>
       </c>
-      <c r="TJ3">
-        <v>0</v>
-      </c>
       <c r="TK3">
         <v>0</v>
       </c>
       <c r="TL3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TM3">
         <v>1</v>
       </c>
       <c r="TN3">
-        <v>0</v>
-      </c>
-      <c r="TO3" t="s">
+        <v>1</v>
+      </c>
+      <c r="TO3">
+        <v>0</v>
+      </c>
+      <c r="TP3" t="s">
         <v>746</v>
       </c>
-      <c r="UG3" t="s">
+      <c r="UH3" t="s">
         <v>747</v>
       </c>
-      <c r="UJ3" t="s">
+      <c r="UK3" t="s">
         <v>708</v>
       </c>
-      <c r="AEX3">
+      <c r="AEY3">
         <v>884613428</v>
       </c>
-      <c r="AEY3" t="s">
+      <c r="AEZ3" t="s">
         <v>748</v>
       </c>
-      <c r="AEZ3" s="1">
+      <c r="AFA3" s="1">
         <v>46297.744189814817</v>
       </c>
-      <c r="AFB3" t="s">
+      <c r="AFC3" t="s">
         <v>734</v>
       </c>
-      <c r="AFD3" t="s">
+      <c r="AFE3" t="s">
         <v>749</v>
       </c>
-      <c r="AFE3" t="s">
+      <c r="AFF3" t="s">
         <v>750</v>
       </c>
-      <c r="AFF3">
+      <c r="AFG3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>46297</v>
       </c>
@@ -10039,32 +10094,32 @@
       <c r="KF4" t="s">
         <v>769</v>
       </c>
-      <c r="UJ4" t="s">
+      <c r="UK4" t="s">
         <v>708</v>
       </c>
-      <c r="AEX4">
+      <c r="AEY4">
         <v>884667912</v>
       </c>
-      <c r="AEY4" t="s">
+      <c r="AEZ4" t="s">
         <v>770</v>
       </c>
-      <c r="AEZ4" s="1">
+      <c r="AFA4" s="1">
         <v>46297.806550925918</v>
       </c>
-      <c r="AFB4" t="s">
+      <c r="AFC4" t="s">
         <v>734</v>
       </c>
-      <c r="AFD4" t="s">
+      <c r="AFE4" t="s">
         <v>771</v>
       </c>
-      <c r="AFE4" t="s">
+      <c r="AFF4" t="s">
         <v>772</v>
       </c>
-      <c r="AFF4">
+      <c r="AFG4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>46298</v>
       </c>
@@ -10371,35 +10426,35 @@
       <c r="EM5">
         <v>0</v>
       </c>
-      <c r="UG5" t="s">
+      <c r="UH5" t="s">
         <v>787</v>
       </c>
-      <c r="UJ5" t="s">
+      <c r="UK5" t="s">
         <v>708</v>
       </c>
-      <c r="AEX5">
+      <c r="AEY5">
         <v>885064065</v>
       </c>
-      <c r="AEY5" t="s">
+      <c r="AEZ5" t="s">
         <v>788</v>
       </c>
-      <c r="AEZ5" s="1">
+      <c r="AFA5" s="1">
         <v>46298.597939814812</v>
       </c>
-      <c r="AFB5" t="s">
+      <c r="AFC5" t="s">
         <v>734</v>
       </c>
-      <c r="AFD5" t="s">
+      <c r="AFE5" t="s">
         <v>749</v>
       </c>
-      <c r="AFE5" t="s">
+      <c r="AFF5" t="s">
         <v>789</v>
       </c>
-      <c r="AFF5">
+      <c r="AFG5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>46298</v>
       </c>
@@ -10706,35 +10761,35 @@
       <c r="EM6">
         <v>5</v>
       </c>
-      <c r="UG6" t="s">
+      <c r="UH6" t="s">
         <v>800</v>
       </c>
-      <c r="UJ6" t="s">
+      <c r="UK6" t="s">
         <v>708</v>
       </c>
-      <c r="AEX6">
+      <c r="AEY6">
         <v>885072414</v>
       </c>
-      <c r="AEY6" t="s">
+      <c r="AEZ6" t="s">
         <v>801</v>
       </c>
-      <c r="AEZ6" s="1">
+      <c r="AFA6" s="1">
         <v>46298.609120370369</v>
       </c>
-      <c r="AFB6" t="s">
+      <c r="AFC6" t="s">
         <v>734</v>
       </c>
-      <c r="AFD6" t="s">
+      <c r="AFE6" t="s">
         <v>749</v>
       </c>
-      <c r="AFE6" t="s">
+      <c r="AFF6" t="s">
         <v>802</v>
       </c>
-      <c r="AFF6">
+      <c r="AFG6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>46297</v>
       </c>
@@ -11074,35 +11129,35 @@
       <c r="EM7">
         <v>1</v>
       </c>
-      <c r="UG7" t="s">
+      <c r="UH7" t="s">
         <v>1007</v>
       </c>
-      <c r="UJ7" t="s">
+      <c r="UK7" t="s">
         <v>708</v>
       </c>
-      <c r="AEX7">
+      <c r="AEY7">
         <v>885187630</v>
       </c>
-      <c r="AEY7" t="s">
+      <c r="AEZ7" t="s">
         <v>1008</v>
       </c>
-      <c r="AEZ7" s="1">
+      <c r="AFA7" s="1">
         <v>46298.763460648152</v>
       </c>
-      <c r="AFB7" t="s">
+      <c r="AFC7" t="s">
         <v>734</v>
       </c>
-      <c r="AFD7" t="s">
+      <c r="AFE7" t="s">
         <v>749</v>
       </c>
-      <c r="AFE7" t="s">
+      <c r="AFF7" t="s">
         <v>816</v>
       </c>
-      <c r="AFF7">
+      <c r="AFG7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>46295</v>
       </c>
@@ -11388,89 +11443,89 @@
       <c r="KO8">
         <v>1</v>
       </c>
-      <c r="KQ8" t="s">
+      <c r="KR8" t="s">
         <v>842</v>
       </c>
-      <c r="KR8" t="s">
+      <c r="KS8" t="s">
         <v>843</v>
       </c>
-      <c r="KT8" t="s">
+      <c r="KU8" t="s">
         <v>845</v>
       </c>
-      <c r="NO8">
-        <v>0</v>
-      </c>
       <c r="NP8">
         <v>0</v>
       </c>
-      <c r="NR8">
+      <c r="NQ8">
+        <v>0</v>
+      </c>
+      <c r="NS8">
         <v>650</v>
       </c>
-      <c r="NS8">
+      <c r="NT8">
         <v>375</v>
       </c>
-      <c r="NU8">
+      <c r="NV8">
         <v>86</v>
       </c>
-      <c r="NV8">
+      <c r="NW8">
         <v>91</v>
       </c>
-      <c r="UG8" t="s">
+      <c r="UH8" t="s">
         <v>846</v>
       </c>
-      <c r="UJ8" t="s">
+      <c r="UK8" t="s">
         <v>708</v>
-      </c>
-      <c r="ADZ8" t="s">
-        <v>711</v>
       </c>
       <c r="AEA8" t="s">
         <v>711</v>
       </c>
-      <c r="AEF8" t="s">
+      <c r="AEB8" t="s">
+        <v>711</v>
+      </c>
+      <c r="AEG8" t="s">
         <v>844</v>
       </c>
-      <c r="AEK8">
-        <v>0</v>
-      </c>
       <c r="AEL8">
         <v>0</v>
       </c>
-      <c r="AEN8">
+      <c r="AEM8">
+        <v>0</v>
+      </c>
+      <c r="AEO8">
         <v>254</v>
       </c>
-      <c r="AEO8">
+      <c r="AEP8">
         <v>125</v>
       </c>
-      <c r="AEQ8">
+      <c r="AER8">
         <v>44</v>
       </c>
-      <c r="AER8">
+      <c r="AES8">
         <v>67</v>
       </c>
-      <c r="AEX8">
+      <c r="AEY8">
         <v>885200260</v>
       </c>
-      <c r="AEY8" t="s">
+      <c r="AEZ8" t="s">
         <v>847</v>
       </c>
-      <c r="AEZ8" s="1">
+      <c r="AFA8" s="1">
         <v>46298.788032407407</v>
       </c>
-      <c r="AFB8" t="s">
+      <c r="AFC8" t="s">
         <v>734</v>
       </c>
-      <c r="AFD8" t="s">
+      <c r="AFE8" t="s">
         <v>749</v>
       </c>
-      <c r="AFE8" t="s">
+      <c r="AFF8" t="s">
         <v>848</v>
       </c>
-      <c r="AFF8">
+      <c r="AFG8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>46298</v>
       </c>
@@ -11774,35 +11829,35 @@
       <c r="EM9">
         <v>0</v>
       </c>
-      <c r="UG9" t="s">
+      <c r="UH9" t="s">
         <v>856</v>
       </c>
-      <c r="UJ9" t="s">
+      <c r="UK9" t="s">
         <v>708</v>
       </c>
-      <c r="AEX9">
+      <c r="AEY9">
         <v>885201939</v>
       </c>
-      <c r="AEY9" t="s">
+      <c r="AEZ9" t="s">
         <v>1015</v>
       </c>
-      <c r="AEZ9" s="1">
+      <c r="AFA9" s="1">
         <v>46298.791562500002</v>
       </c>
-      <c r="AFB9" t="s">
+      <c r="AFC9" t="s">
         <v>734</v>
       </c>
-      <c r="AFD9" t="s">
+      <c r="AFE9" t="s">
         <v>749</v>
       </c>
-      <c r="AFE9" t="s">
+      <c r="AFF9" t="s">
         <v>857</v>
       </c>
-      <c r="AFF9">
+      <c r="AFG9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46296</v>
       </c>
@@ -12070,89 +12125,89 @@
       <c r="KO10">
         <v>0</v>
       </c>
-      <c r="KQ10" t="s">
+      <c r="KR10" t="s">
         <v>891</v>
       </c>
-      <c r="KR10" t="s">
+      <c r="KS10" t="s">
         <v>892</v>
       </c>
-      <c r="KT10" t="s">
+      <c r="KU10" t="s">
         <v>894</v>
       </c>
-      <c r="NO10">
+      <c r="NP10">
         <v>90</v>
       </c>
-      <c r="NP10">
+      <c r="NQ10">
         <v>105</v>
       </c>
-      <c r="NR10">
+      <c r="NS10">
         <v>150</v>
       </c>
-      <c r="NS10">
+      <c r="NT10">
         <v>180</v>
       </c>
-      <c r="NU10">
+      <c r="NV10">
         <v>118</v>
       </c>
-      <c r="NV10">
+      <c r="NW10">
         <v>105</v>
       </c>
-      <c r="UG10" t="s">
+      <c r="UH10" t="s">
         <v>895</v>
       </c>
-      <c r="UJ10" t="s">
+      <c r="UK10" t="s">
         <v>708</v>
       </c>
-      <c r="ADZ10" t="s">
+      <c r="AEA10" t="s">
         <v>711</v>
       </c>
-      <c r="AEA10" t="s">
+      <c r="AEB10" t="s">
         <v>732</v>
       </c>
-      <c r="AEF10" t="s">
+      <c r="AEG10" t="s">
         <v>893</v>
       </c>
-      <c r="AEK10">
+      <c r="AEL10">
         <v>90</v>
       </c>
-      <c r="AEL10">
+      <c r="AEM10">
         <v>140</v>
       </c>
-      <c r="AEN10">
+      <c r="AEO10">
         <v>150</v>
       </c>
-      <c r="AEO10">
+      <c r="AEP10">
         <v>200</v>
       </c>
-      <c r="AEQ10">
+      <c r="AER10">
         <v>100</v>
       </c>
-      <c r="AER10">
+      <c r="AES10">
         <v>90</v>
       </c>
-      <c r="AEX10">
+      <c r="AEY10">
         <v>885374147</v>
       </c>
-      <c r="AEY10" t="s">
+      <c r="AEZ10" t="s">
         <v>896</v>
       </c>
-      <c r="AEZ10" s="1">
+      <c r="AFA10" s="1">
         <v>46299.338842592602</v>
       </c>
-      <c r="AFB10" t="s">
+      <c r="AFC10" t="s">
         <v>734</v>
       </c>
-      <c r="AFD10" t="s">
+      <c r="AFE10" t="s">
         <v>749</v>
       </c>
-      <c r="AFE10" t="s">
+      <c r="AFF10" t="s">
         <v>897</v>
       </c>
-      <c r="AFF10">
+      <c r="AFG10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46298</v>
       </c>
@@ -12459,35 +12514,35 @@
       <c r="EM11">
         <v>1</v>
       </c>
-      <c r="UG11" t="s">
+      <c r="UH11" t="s">
         <v>909</v>
       </c>
-      <c r="UJ11" t="s">
+      <c r="UK11" t="s">
         <v>898</v>
       </c>
-      <c r="AEX11">
+      <c r="AEY11">
         <v>885381637</v>
       </c>
-      <c r="AEY11" t="s">
+      <c r="AEZ11" t="s">
         <v>910</v>
       </c>
-      <c r="AEZ11" s="1">
+      <c r="AFA11" s="1">
         <v>46299.352372685193</v>
       </c>
-      <c r="AFB11" t="s">
+      <c r="AFC11" t="s">
         <v>734</v>
       </c>
-      <c r="AFD11" t="s">
+      <c r="AFE11" t="s">
         <v>749</v>
       </c>
-      <c r="AFE11" t="s">
+      <c r="AFF11" t="s">
         <v>911</v>
       </c>
-      <c r="AFF11">
+      <c r="AFG11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46298</v>
       </c>
@@ -12794,35 +12849,35 @@
       <c r="EM12">
         <v>40</v>
       </c>
-      <c r="UG12" t="s">
+      <c r="UH12" t="s">
         <v>962</v>
       </c>
-      <c r="UJ12" t="s">
+      <c r="UK12" t="s">
         <v>708</v>
       </c>
-      <c r="AEX12">
+      <c r="AEY12">
         <v>886644705</v>
       </c>
-      <c r="AEY12" t="s">
+      <c r="AEZ12" t="s">
         <v>1017</v>
       </c>
-      <c r="AEZ12" s="1">
+      <c r="AFA12" s="1">
         <v>46301.235891203702</v>
       </c>
-      <c r="AFB12" t="s">
+      <c r="AFC12" t="s">
         <v>734</v>
       </c>
-      <c r="AFD12" t="s">
+      <c r="AFE12" t="s">
         <v>963</v>
       </c>
-      <c r="AFE12" t="s">
+      <c r="AFF12" t="s">
         <v>964</v>
       </c>
-      <c r="AFF12">
+      <c r="AFG12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46298</v>
       </c>
@@ -12883,95 +12938,95 @@
       <c r="FI13">
         <v>11</v>
       </c>
-      <c r="NO13">
+      <c r="NP13">
         <v>66</v>
       </c>
-      <c r="NP13">
+      <c r="NQ13">
         <v>54</v>
       </c>
-      <c r="NR13">
+      <c r="NS13">
         <v>41</v>
       </c>
-      <c r="NS13">
+      <c r="NT13">
         <v>74</v>
       </c>
-      <c r="NU13">
+      <c r="NV13">
         <v>71</v>
       </c>
-      <c r="NV13">
+      <c r="NW13">
         <v>33</v>
       </c>
-      <c r="UG13" t="s">
+      <c r="UH13" t="s">
         <v>969</v>
       </c>
-      <c r="UJ13" t="s">
+      <c r="UK13" t="s">
         <v>708</v>
       </c>
-      <c r="ACM13" t="s">
+      <c r="ACN13" t="s">
         <v>970</v>
       </c>
-      <c r="ACN13">
-        <v>0</v>
-      </c>
       <c r="ACO13">
         <v>0</v>
       </c>
       <c r="ACP13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ACQ13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ACR13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ACS13">
-        <v>0</v>
-      </c>
-      <c r="ACV13" t="s">
+        <v>1</v>
+      </c>
+      <c r="ACT13">
+        <v>0</v>
+      </c>
+      <c r="ACW13" t="s">
         <v>711</v>
       </c>
-      <c r="AEK13">
+      <c r="AEL13">
         <v>34</v>
       </c>
-      <c r="AEL13">
+      <c r="AEM13">
         <v>51</v>
       </c>
-      <c r="AEN13">
+      <c r="AEO13">
         <v>55</v>
       </c>
-      <c r="AEO13">
+      <c r="AEP13">
         <v>67</v>
       </c>
-      <c r="AEQ13">
+      <c r="AER13">
         <v>22</v>
       </c>
-      <c r="AER13">
+      <c r="AES13">
         <v>78</v>
       </c>
-      <c r="AEX13">
+      <c r="AEY13">
         <v>886659275</v>
       </c>
-      <c r="AEY13" t="s">
+      <c r="AEZ13" t="s">
         <v>971</v>
       </c>
-      <c r="AEZ13" s="1">
+      <c r="AFA13" s="1">
         <v>46301.252986111111</v>
       </c>
-      <c r="AFB13" t="s">
+      <c r="AFC13" t="s">
         <v>734</v>
       </c>
-      <c r="AFD13" t="s">
+      <c r="AFE13" t="s">
         <v>963</v>
       </c>
-      <c r="AFE13" t="s">
+      <c r="AFF13" t="s">
         <v>972</v>
       </c>
-      <c r="AFF13">
+      <c r="AFG13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>46301</v>
       </c>
@@ -12990,56 +13045,53 @@
       <c r="H14" t="s">
         <v>981</v>
       </c>
-      <c r="SU14" t="s">
+      <c r="SV14" t="s">
         <v>740</v>
       </c>
-      <c r="SV14">
-        <v>1</v>
-      </c>
       <c r="SW14">
-        <v>0</v>
-      </c>
-      <c r="SX14" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX14">
+        <v>0</v>
+      </c>
+      <c r="SY14" t="s">
         <v>982</v>
       </c>
-      <c r="SY14">
+      <c r="SZ14">
         <v>26</v>
       </c>
-      <c r="SZ14">
+      <c r="TA14">
         <v>34</v>
       </c>
-      <c r="TA14" t="s">
+      <c r="TB14" t="s">
         <v>983</v>
       </c>
-      <c r="TB14" s="1">
+      <c r="TC14" s="1">
         <v>46301</v>
       </c>
-      <c r="TC14" t="s">
+      <c r="TD14" t="s">
         <v>984</v>
       </c>
-      <c r="TD14" t="s">
+      <c r="TE14" t="s">
         <v>985</v>
       </c>
-      <c r="TE14">
+      <c r="TF14">
         <v>51</v>
       </c>
-      <c r="TF14">
+      <c r="TG14">
         <v>63</v>
       </c>
-      <c r="TG14">
-        <v>1</v>
-      </c>
       <c r="TH14">
-        <v>0</v>
-      </c>
-      <c r="TI14" t="s">
+        <v>1</v>
+      </c>
+      <c r="TI14">
+        <v>0</v>
+      </c>
+      <c r="TJ14" t="s">
         <v>986</v>
       </c>
-      <c r="TJ14">
-        <v>0</v>
-      </c>
       <c r="TK14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TL14">
         <v>1</v>
@@ -13050,38 +13102,41 @@
       <c r="TN14">
         <v>1</v>
       </c>
-      <c r="TO14" t="s">
+      <c r="TO14">
+        <v>1</v>
+      </c>
+      <c r="TP14" t="s">
         <v>987</v>
       </c>
-      <c r="UG14" t="s">
+      <c r="UH14" t="s">
         <v>988</v>
       </c>
-      <c r="UJ14" t="s">
+      <c r="UK14" t="s">
         <v>708</v>
       </c>
-      <c r="AEX14">
+      <c r="AEY14">
         <v>886820155</v>
       </c>
-      <c r="AEY14" t="s">
+      <c r="AEZ14" t="s">
         <v>989</v>
       </c>
-      <c r="AEZ14" s="1">
+      <c r="AFA14" s="1">
         <v>46301.379594907397</v>
       </c>
-      <c r="AFB14" t="s">
+      <c r="AFC14" t="s">
         <v>734</v>
       </c>
-      <c r="AFD14" t="s">
+      <c r="AFE14" t="s">
         <v>749</v>
       </c>
-      <c r="AFE14" t="s">
+      <c r="AFF14" t="s">
         <v>990</v>
       </c>
-      <c r="AFF14">
+      <c r="AFG14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>46301</v>
       </c>
@@ -13100,56 +13155,53 @@
       <c r="H15" t="s">
         <v>774</v>
       </c>
-      <c r="SU15" t="s">
+      <c r="SV15" t="s">
         <v>740</v>
       </c>
-      <c r="SV15">
-        <v>1</v>
-      </c>
       <c r="SW15">
-        <v>0</v>
-      </c>
-      <c r="SX15" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX15">
+        <v>0</v>
+      </c>
+      <c r="SY15" t="s">
         <v>995</v>
-      </c>
-      <c r="SY15">
-        <v>30</v>
       </c>
       <c r="SZ15">
         <v>30</v>
       </c>
-      <c r="TA15" t="s">
+      <c r="TA15">
+        <v>30</v>
+      </c>
+      <c r="TB15" t="s">
         <v>996</v>
       </c>
-      <c r="TB15" s="1">
+      <c r="TC15" s="1">
         <v>46301</v>
       </c>
-      <c r="TC15" t="s">
+      <c r="TD15" t="s">
         <v>997</v>
       </c>
-      <c r="TD15" t="s">
+      <c r="TE15" t="s">
         <v>998</v>
       </c>
-      <c r="TE15">
+      <c r="TF15">
         <v>112</v>
       </c>
-      <c r="TF15">
+      <c r="TG15">
         <v>104</v>
       </c>
-      <c r="TG15">
-        <v>0</v>
-      </c>
       <c r="TH15">
         <v>0</v>
       </c>
-      <c r="TI15" t="s">
+      <c r="TI15">
+        <v>0</v>
+      </c>
+      <c r="TJ15" t="s">
         <v>986</v>
       </c>
-      <c r="TJ15">
-        <v>0</v>
-      </c>
       <c r="TK15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TL15">
         <v>1</v>
@@ -13160,35 +13212,38 @@
       <c r="TN15">
         <v>1</v>
       </c>
-      <c r="TO15" t="s">
+      <c r="TO15">
+        <v>1</v>
+      </c>
+      <c r="TP15" t="s">
         <v>999</v>
       </c>
-      <c r="UG15" t="s">
+      <c r="UH15" t="s">
         <v>1000</v>
       </c>
-      <c r="AEX15">
+      <c r="AEY15">
         <v>886940645</v>
       </c>
-      <c r="AEY15" t="s">
+      <c r="AEZ15" t="s">
         <v>1001</v>
       </c>
-      <c r="AEZ15" s="1">
+      <c r="AFA15" s="1">
         <v>46301.473958333343</v>
       </c>
-      <c r="AFB15" t="s">
+      <c r="AFC15" t="s">
         <v>734</v>
       </c>
-      <c r="AFD15" t="s">
+      <c r="AFE15" t="s">
         <v>1002</v>
       </c>
-      <c r="AFE15" t="s">
+      <c r="AFF15" t="s">
         <v>1003</v>
       </c>
-      <c r="AFF15">
+      <c r="AFG15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>46183</v>
       </c>
@@ -13495,32 +13550,32 @@
       <c r="EM16">
         <v>0</v>
       </c>
-      <c r="UG16" t="s">
+      <c r="UH16" t="s">
         <v>1028</v>
       </c>
-      <c r="AEX16">
+      <c r="AEY16">
         <v>887139498</v>
       </c>
-      <c r="AEY16" t="s">
+      <c r="AEZ16" t="s">
         <v>1029</v>
       </c>
-      <c r="AEZ16" s="1">
+      <c r="AFA16" s="1">
         <v>46301.599861111114</v>
       </c>
-      <c r="AFB16" t="s">
+      <c r="AFC16" t="s">
         <v>734</v>
       </c>
-      <c r="AFD16" t="s">
+      <c r="AFE16" t="s">
         <v>1030</v>
       </c>
-      <c r="AFE16" t="s">
+      <c r="AFF16" t="s">
         <v>1031</v>
       </c>
-      <c r="AFF16">
+      <c r="AFG16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>46301</v>
       </c>
@@ -13539,54 +13594,51 @@
       <c r="H17" t="s">
         <v>1032</v>
       </c>
-      <c r="SU17" t="s">
+      <c r="SV17" t="s">
         <v>740</v>
       </c>
-      <c r="SV17">
-        <v>1</v>
-      </c>
       <c r="SW17">
-        <v>0</v>
-      </c>
-      <c r="SX17" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX17">
+        <v>0</v>
+      </c>
+      <c r="SY17" t="s">
         <v>1033</v>
       </c>
-      <c r="SY17">
+      <c r="SZ17">
         <v>24</v>
       </c>
-      <c r="SZ17">
+      <c r="TA17">
         <v>36</v>
       </c>
-      <c r="TA17" t="s">
+      <c r="TB17" t="s">
         <v>1034</v>
       </c>
-      <c r="TB17" s="1">
+      <c r="TC17" s="1">
         <v>46301</v>
       </c>
-      <c r="TC17" t="s">
+      <c r="TD17" t="s">
         <v>1035</v>
       </c>
-      <c r="TD17" t="s">
+      <c r="TE17" t="s">
         <v>1036</v>
       </c>
-      <c r="TE17">
+      <c r="TF17">
         <v>63</v>
       </c>
-      <c r="TF17">
+      <c r="TG17">
         <v>54</v>
       </c>
-      <c r="TG17">
-        <v>0</v>
-      </c>
       <c r="TH17">
         <v>0</v>
       </c>
-      <c r="TI17" t="s">
+      <c r="TI17">
+        <v>0</v>
+      </c>
+      <c r="TJ17" t="s">
         <v>1037</v>
       </c>
-      <c r="TJ17">
-        <v>1</v>
-      </c>
       <c r="TK17">
         <v>1</v>
       </c>
@@ -13599,35 +13651,38 @@
       <c r="TN17">
         <v>1</v>
       </c>
-      <c r="TO17" t="s">
+      <c r="TO17">
+        <v>1</v>
+      </c>
+      <c r="TP17" t="s">
         <v>1038</v>
       </c>
-      <c r="UG17" t="s">
+      <c r="UH17" t="s">
         <v>1039</v>
       </c>
-      <c r="AEX17">
+      <c r="AEY17">
         <v>887285852</v>
       </c>
-      <c r="AEY17" t="s">
+      <c r="AEZ17" t="s">
         <v>1040</v>
       </c>
-      <c r="AEZ17" s="1">
+      <c r="AFA17" s="1">
         <v>46301.698564814818</v>
       </c>
-      <c r="AFB17" t="s">
+      <c r="AFC17" t="s">
         <v>734</v>
       </c>
-      <c r="AFD17" t="s">
+      <c r="AFE17" t="s">
         <v>1030</v>
       </c>
-      <c r="AFE17" t="s">
+      <c r="AFF17" t="s">
         <v>1041</v>
       </c>
-      <c r="AFF17">
+      <c r="AFG17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>46301</v>
       </c>
@@ -13646,98 +13701,98 @@
       <c r="I18" t="s">
         <v>1042</v>
       </c>
-      <c r="SU18" t="s">
+      <c r="SV18" t="s">
         <v>740</v>
       </c>
-      <c r="SV18">
-        <v>1</v>
-      </c>
       <c r="SW18">
-        <v>0</v>
-      </c>
-      <c r="SX18" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX18">
+        <v>0</v>
+      </c>
+      <c r="SY18" t="s">
         <v>1043</v>
       </c>
-      <c r="SY18">
+      <c r="SZ18">
         <v>2</v>
       </c>
-      <c r="SZ18">
-        <v>1</v>
-      </c>
-      <c r="TA18" t="s">
+      <c r="TA18">
+        <v>1</v>
+      </c>
+      <c r="TB18" t="s">
         <v>1044</v>
       </c>
-      <c r="TB18" s="1">
+      <c r="TC18" s="1">
         <v>46301</v>
       </c>
-      <c r="TC18" t="s">
+      <c r="TD18" t="s">
         <v>1045</v>
       </c>
-      <c r="TD18" t="s">
+      <c r="TE18" t="s">
         <v>1046</v>
       </c>
-      <c r="TE18">
+      <c r="TF18">
         <v>31</v>
       </c>
-      <c r="TF18">
+      <c r="TG18">
         <v>26</v>
       </c>
-      <c r="TG18">
+      <c r="TH18">
         <v>2</v>
       </c>
-      <c r="TH18">
-        <v>1</v>
-      </c>
-      <c r="TI18" t="s">
+      <c r="TI18">
+        <v>1</v>
+      </c>
+      <c r="TJ18" t="s">
         <v>745</v>
       </c>
-      <c r="TJ18">
-        <v>0</v>
-      </c>
       <c r="TK18">
         <v>0</v>
       </c>
       <c r="TL18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TM18">
         <v>1</v>
       </c>
       <c r="TN18">
-        <v>0</v>
-      </c>
-      <c r="TO18" t="s">
+        <v>1</v>
+      </c>
+      <c r="TO18">
+        <v>0</v>
+      </c>
+      <c r="TP18" t="s">
         <v>1047</v>
       </c>
-      <c r="UG18" t="s">
+      <c r="UH18" t="s">
         <v>1048</v>
       </c>
-      <c r="UJ18" t="s">
+      <c r="UK18" t="s">
         <v>708</v>
       </c>
-      <c r="AEX18">
+      <c r="AEY18">
         <v>887314303</v>
       </c>
-      <c r="AEY18" t="s">
+      <c r="AEZ18" t="s">
         <v>1049</v>
       </c>
-      <c r="AEZ18" s="1">
+      <c r="AFA18" s="1">
         <v>46301.718159722222</v>
       </c>
-      <c r="AFB18" t="s">
+      <c r="AFC18" t="s">
         <v>734</v>
       </c>
-      <c r="AFD18" t="s">
+      <c r="AFE18" t="s">
         <v>963</v>
       </c>
-      <c r="AFE18" t="s">
+      <c r="AFF18" t="s">
         <v>1050</v>
       </c>
-      <c r="AFF18">
+      <c r="AFG18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>46301</v>
       </c>
@@ -13756,95 +13811,95 @@
       <c r="I19" t="s">
         <v>1051</v>
       </c>
-      <c r="SU19" t="s">
+      <c r="SV19" t="s">
         <v>740</v>
       </c>
-      <c r="SV19">
-        <v>1</v>
-      </c>
       <c r="SW19">
-        <v>0</v>
-      </c>
-      <c r="SX19" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX19">
+        <v>0</v>
+      </c>
+      <c r="SY19" t="s">
         <v>1052</v>
-      </c>
-      <c r="SY19">
-        <v>2</v>
       </c>
       <c r="SZ19">
         <v>2</v>
       </c>
-      <c r="TA19" t="s">
+      <c r="TA19">
+        <v>2</v>
+      </c>
+      <c r="TB19" t="s">
         <v>1053</v>
       </c>
-      <c r="TB19" s="1">
+      <c r="TC19" s="1">
         <v>46301</v>
       </c>
-      <c r="TC19" t="s">
+      <c r="TD19" t="s">
         <v>1054</v>
       </c>
-      <c r="TD19" t="s">
+      <c r="TE19" t="s">
         <v>1055</v>
       </c>
-      <c r="TE19">
+      <c r="TF19">
         <v>39</v>
       </c>
-      <c r="TF19">
+      <c r="TG19">
         <v>23</v>
       </c>
-      <c r="TG19">
-        <v>0</v>
-      </c>
       <c r="TH19">
-        <v>1</v>
-      </c>
-      <c r="TI19" t="s">
+        <v>0</v>
+      </c>
+      <c r="TI19">
+        <v>1</v>
+      </c>
+      <c r="TJ19" t="s">
         <v>745</v>
       </c>
-      <c r="TJ19">
-        <v>0</v>
-      </c>
       <c r="TK19">
         <v>0</v>
       </c>
       <c r="TL19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TM19">
         <v>1</v>
       </c>
       <c r="TN19">
-        <v>0</v>
-      </c>
-      <c r="TO19" t="s">
+        <v>1</v>
+      </c>
+      <c r="TO19">
+        <v>0</v>
+      </c>
+      <c r="TP19" t="s">
         <v>1056</v>
       </c>
-      <c r="UG19" t="s">
+      <c r="UH19" t="s">
         <v>1057</v>
       </c>
-      <c r="AEX19">
+      <c r="AEY19">
         <v>887319690</v>
       </c>
-      <c r="AEY19" t="s">
+      <c r="AEZ19" t="s">
         <v>1058</v>
       </c>
-      <c r="AEZ19" s="1">
+      <c r="AFA19" s="1">
         <v>46301.722268518519</v>
       </c>
-      <c r="AFB19" t="s">
+      <c r="AFC19" t="s">
         <v>734</v>
       </c>
-      <c r="AFD19" t="s">
+      <c r="AFE19" t="s">
         <v>1030</v>
       </c>
-      <c r="AFE19" t="s">
+      <c r="AFF19" t="s">
         <v>1059</v>
       </c>
-      <c r="AFF19">
+      <c r="AFG19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>46302</v>
       </c>
@@ -13863,56 +13918,53 @@
       <c r="H20" t="s">
         <v>1060</v>
       </c>
-      <c r="SU20" t="s">
+      <c r="SV20" t="s">
         <v>740</v>
       </c>
-      <c r="SV20">
-        <v>1</v>
-      </c>
       <c r="SW20">
-        <v>0</v>
-      </c>
-      <c r="SX20" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX20">
+        <v>0</v>
+      </c>
+      <c r="SY20" t="s">
         <v>1061</v>
-      </c>
-      <c r="SY20">
-        <v>30</v>
       </c>
       <c r="SZ20">
         <v>30</v>
       </c>
-      <c r="TA20" t="s">
+      <c r="TA20">
+        <v>30</v>
+      </c>
+      <c r="TB20" t="s">
         <v>996</v>
       </c>
-      <c r="TB20" s="1">
+      <c r="TC20" s="1">
         <v>46302</v>
       </c>
-      <c r="TC20" t="s">
+      <c r="TD20" t="s">
         <v>1062</v>
       </c>
-      <c r="TD20" t="s">
+      <c r="TE20" t="s">
         <v>1063</v>
       </c>
-      <c r="TE20">
+      <c r="TF20">
         <v>81</v>
       </c>
-      <c r="TF20">
+      <c r="TG20">
         <v>104</v>
       </c>
-      <c r="TG20">
-        <v>1</v>
-      </c>
       <c r="TH20">
-        <v>0</v>
-      </c>
-      <c r="TI20" t="s">
+        <v>1</v>
+      </c>
+      <c r="TI20">
+        <v>0</v>
+      </c>
+      <c r="TJ20" t="s">
         <v>986</v>
       </c>
-      <c r="TJ20">
-        <v>0</v>
-      </c>
       <c r="TK20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TL20">
         <v>1</v>
@@ -13923,35 +13975,38 @@
       <c r="TN20">
         <v>1</v>
       </c>
-      <c r="TO20" t="s">
+      <c r="TO20">
+        <v>1</v>
+      </c>
+      <c r="TP20" t="s">
         <v>1064</v>
       </c>
-      <c r="UG20" t="s">
+      <c r="UH20" t="s">
         <v>1065</v>
       </c>
-      <c r="AEX20">
+      <c r="AEY20">
         <v>887710163</v>
       </c>
-      <c r="AEY20" t="s">
+      <c r="AEZ20" t="s">
         <v>1066</v>
       </c>
-      <c r="AEZ20" s="1">
+      <c r="AFA20" s="1">
         <v>46302.307881944442</v>
       </c>
-      <c r="AFB20" t="s">
+      <c r="AFC20" t="s">
         <v>734</v>
       </c>
-      <c r="AFD20" t="s">
+      <c r="AFE20" t="s">
         <v>1030</v>
       </c>
-      <c r="AFE20" t="s">
+      <c r="AFF20" t="s">
         <v>1067</v>
       </c>
-      <c r="AFF20">
+      <c r="AFG20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>46302</v>
       </c>
@@ -14009,38 +14064,35 @@
       <c r="FH21" t="s">
         <v>732</v>
       </c>
-      <c r="NO21">
-        <v>276</v>
-      </c>
       <c r="NP21">
         <v>276</v>
       </c>
-      <c r="NR21">
-        <v>201</v>
+      <c r="NQ21">
+        <v>276</v>
       </c>
       <c r="NS21">
         <v>201</v>
       </c>
-      <c r="NU21">
-        <v>85</v>
+      <c r="NT21">
+        <v>201</v>
       </c>
       <c r="NV21">
         <v>85</v>
       </c>
-      <c r="UG21" t="s">
+      <c r="NW21">
+        <v>85</v>
+      </c>
+      <c r="UH21" t="s">
         <v>1071</v>
       </c>
-      <c r="UJ21" t="s">
+      <c r="UK21" t="s">
         <v>708</v>
       </c>
-      <c r="ACM21" t="s">
+      <c r="ACN21" t="s">
         <v>1072</v>
       </c>
-      <c r="ACN21">
-        <v>1</v>
-      </c>
       <c r="ACO21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ACP21">
         <v>0</v>
@@ -14049,55 +14101,58 @@
         <v>0</v>
       </c>
       <c r="ACR21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ACS21">
         <v>1</v>
       </c>
-      <c r="ACV21" t="s">
+      <c r="ACT21">
+        <v>1</v>
+      </c>
+      <c r="ACW21" t="s">
         <v>732</v>
-      </c>
-      <c r="AEK21">
-        <v>304</v>
       </c>
       <c r="AEL21">
         <v>304</v>
       </c>
-      <c r="AEN21">
-        <v>269</v>
+      <c r="AEM21">
+        <v>304</v>
       </c>
       <c r="AEO21">
         <v>269</v>
       </c>
-      <c r="AEQ21">
-        <v>67</v>
+      <c r="AEP21">
+        <v>269</v>
       </c>
       <c r="AER21">
         <v>67</v>
       </c>
-      <c r="AEX21">
+      <c r="AES21">
+        <v>67</v>
+      </c>
+      <c r="AEY21">
         <v>887751145</v>
       </c>
-      <c r="AEY21" t="s">
+      <c r="AEZ21" t="s">
         <v>1073</v>
       </c>
-      <c r="AEZ21" s="1">
+      <c r="AFA21" s="1">
         <v>46302.341898148137</v>
       </c>
-      <c r="AFB21" t="s">
+      <c r="AFC21" t="s">
         <v>734</v>
       </c>
-      <c r="AFD21" t="s">
+      <c r="AFE21" t="s">
         <v>963</v>
       </c>
-      <c r="AFE21" t="s">
+      <c r="AFF21" t="s">
         <v>1074</v>
       </c>
-      <c r="AFF21">
+      <c r="AFG21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>46302</v>
       </c>
@@ -14116,56 +14171,53 @@
       <c r="H22" t="s">
         <v>1078</v>
       </c>
-      <c r="SU22" t="s">
+      <c r="SV22" t="s">
         <v>740</v>
       </c>
-      <c r="SV22">
-        <v>1</v>
-      </c>
       <c r="SW22">
-        <v>0</v>
-      </c>
-      <c r="SX22" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX22">
+        <v>0</v>
+      </c>
+      <c r="SY22" t="s">
         <v>1079</v>
       </c>
-      <c r="SY22">
+      <c r="SZ22">
         <v>25</v>
       </c>
-      <c r="SZ22">
+      <c r="TA22">
         <v>30</v>
       </c>
-      <c r="TA22" t="s">
+      <c r="TB22" t="s">
         <v>996</v>
       </c>
-      <c r="TB22" s="1">
+      <c r="TC22" s="1">
         <v>46302</v>
       </c>
-      <c r="TC22" t="s">
+      <c r="TD22" t="s">
         <v>1080</v>
       </c>
-      <c r="TD22" t="s">
+      <c r="TE22" t="s">
         <v>1081</v>
       </c>
-      <c r="TE22">
+      <c r="TF22">
         <v>71</v>
       </c>
-      <c r="TF22">
+      <c r="TG22">
         <v>74</v>
       </c>
-      <c r="TG22">
-        <v>1</v>
-      </c>
       <c r="TH22">
-        <v>0</v>
-      </c>
-      <c r="TI22" t="s">
+        <v>1</v>
+      </c>
+      <c r="TI22">
+        <v>0</v>
+      </c>
+      <c r="TJ22" t="s">
         <v>986</v>
       </c>
-      <c r="TJ22">
-        <v>0</v>
-      </c>
       <c r="TK22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TL22">
         <v>1</v>
@@ -14176,35 +14228,38 @@
       <c r="TN22">
         <v>1</v>
       </c>
-      <c r="TO22" t="s">
+      <c r="TO22">
+        <v>1</v>
+      </c>
+      <c r="TP22" t="s">
         <v>1082</v>
       </c>
-      <c r="UG22" t="s">
+      <c r="UH22" t="s">
         <v>1083</v>
       </c>
-      <c r="AEX22">
+      <c r="AEY22">
         <v>887875691</v>
       </c>
-      <c r="AEY22" t="s">
+      <c r="AEZ22" t="s">
         <v>1084</v>
       </c>
-      <c r="AEZ22" s="1">
+      <c r="AFA22" s="1">
         <v>46302.434293981481</v>
       </c>
-      <c r="AFB22" t="s">
+      <c r="AFC22" t="s">
         <v>734</v>
       </c>
-      <c r="AFD22" t="s">
+      <c r="AFE22" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE22" t="s">
+      <c r="AFF22" t="s">
         <v>1086</v>
       </c>
-      <c r="AFF22">
+      <c r="AFG22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>46302</v>
       </c>
@@ -14223,95 +14278,95 @@
       <c r="I23" t="s">
         <v>1088</v>
       </c>
-      <c r="SU23" t="s">
+      <c r="SV23" t="s">
         <v>740</v>
       </c>
-      <c r="SV23">
-        <v>1</v>
-      </c>
       <c r="SW23">
-        <v>0</v>
-      </c>
-      <c r="SX23" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX23">
+        <v>0</v>
+      </c>
+      <c r="SY23" t="s">
         <v>1089</v>
       </c>
-      <c r="SY23">
+      <c r="SZ23">
         <v>5</v>
       </c>
-      <c r="SZ23">
+      <c r="TA23">
         <v>23</v>
       </c>
-      <c r="TA23" t="s">
+      <c r="TB23" t="s">
         <v>1090</v>
       </c>
-      <c r="TB23" s="1">
+      <c r="TC23" s="1">
         <v>46301</v>
       </c>
-      <c r="TC23" t="s">
+      <c r="TD23" t="s">
         <v>1091</v>
       </c>
-      <c r="TD23" t="s">
+      <c r="TE23" t="s">
         <v>1092</v>
       </c>
-      <c r="TE23">
+      <c r="TF23">
         <v>5</v>
       </c>
-      <c r="TF23">
+      <c r="TG23">
         <v>23</v>
       </c>
-      <c r="TG23">
-        <v>0</v>
-      </c>
       <c r="TH23">
         <v>0</v>
       </c>
-      <c r="TI23" t="s">
+      <c r="TI23">
+        <v>0</v>
+      </c>
+      <c r="TJ23" t="s">
         <v>745</v>
       </c>
-      <c r="TJ23">
-        <v>0</v>
-      </c>
       <c r="TK23">
         <v>0</v>
       </c>
       <c r="TL23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TM23">
         <v>1</v>
       </c>
       <c r="TN23">
-        <v>0</v>
-      </c>
-      <c r="TO23" t="s">
+        <v>1</v>
+      </c>
+      <c r="TO23">
+        <v>0</v>
+      </c>
+      <c r="TP23" t="s">
         <v>1093</v>
       </c>
-      <c r="UG23" t="s">
+      <c r="UH23" t="s">
         <v>1094</v>
       </c>
-      <c r="AEX23">
+      <c r="AEY23">
         <v>887914294</v>
       </c>
-      <c r="AEY23" t="s">
+      <c r="AEZ23" t="s">
         <v>1095</v>
       </c>
-      <c r="AEZ23" s="1">
+      <c r="AFA23" s="1">
         <v>46302.464733796303</v>
       </c>
-      <c r="AFB23" t="s">
+      <c r="AFC23" t="s">
         <v>734</v>
       </c>
-      <c r="AFD23" t="s">
+      <c r="AFE23" t="s">
         <v>1030</v>
       </c>
-      <c r="AFE23" t="s">
+      <c r="AFF23" t="s">
         <v>1096</v>
       </c>
-      <c r="AFF23">
+      <c r="AFG23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>46296</v>
       </c>
@@ -14387,50 +14442,50 @@
       <c r="FH24" t="s">
         <v>732</v>
       </c>
-      <c r="NO24">
+      <c r="NP24">
         <v>193</v>
       </c>
-      <c r="NP24">
+      <c r="NQ24">
         <v>190</v>
       </c>
-      <c r="NR24">
+      <c r="NS24">
         <v>51</v>
       </c>
-      <c r="NS24">
+      <c r="NT24">
         <v>36</v>
       </c>
-      <c r="NU24">
+      <c r="NV24">
         <v>24</v>
       </c>
-      <c r="NV24">
+      <c r="NW24">
         <v>27</v>
       </c>
-      <c r="UG24" t="s">
+      <c r="UH24" t="s">
         <v>1100</v>
       </c>
-      <c r="AEX24">
+      <c r="AEY24">
         <v>887959840</v>
       </c>
-      <c r="AEY24" t="s">
+      <c r="AEZ24" t="s">
         <v>1101</v>
       </c>
-      <c r="AEZ24" s="1">
+      <c r="AFA24" s="1">
         <v>46302.49622685185</v>
       </c>
-      <c r="AFB24" t="s">
+      <c r="AFC24" t="s">
         <v>734</v>
       </c>
-      <c r="AFD24" t="s">
+      <c r="AFE24" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE24" t="s">
+      <c r="AFF24" t="s">
         <v>1102</v>
       </c>
-      <c r="AFF24">
+      <c r="AFG24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>46303</v>
       </c>
@@ -14713,89 +14768,89 @@
       <c r="KO25">
         <v>1</v>
       </c>
-      <c r="KQ25" t="s">
-        <v>1123</v>
-      </c>
       <c r="KR25" t="s">
         <v>1123</v>
       </c>
-      <c r="KT25" t="s">
+      <c r="KS25" t="s">
+        <v>1123</v>
+      </c>
+      <c r="KU25" t="s">
         <v>1124</v>
       </c>
-      <c r="NO25">
+      <c r="NP25">
         <v>62</v>
       </c>
-      <c r="NP25">
+      <c r="NQ25">
         <v>53</v>
       </c>
-      <c r="NR25">
+      <c r="NS25">
         <v>63</v>
       </c>
-      <c r="NS25">
+      <c r="NT25">
         <v>53</v>
       </c>
-      <c r="NU25">
+      <c r="NV25">
         <v>53</v>
       </c>
-      <c r="NV25">
+      <c r="NW25">
         <v>50</v>
       </c>
-      <c r="UG25" t="s">
+      <c r="UH25" t="s">
         <v>1125</v>
       </c>
-      <c r="UJ25" t="s">
+      <c r="UK25" t="s">
         <v>708</v>
       </c>
-      <c r="ADZ25" t="s">
+      <c r="AEA25" t="s">
         <v>711</v>
       </c>
-      <c r="AEA25" t="s">
+      <c r="AEB25" t="s">
         <v>732</v>
       </c>
-      <c r="AEF25" t="s">
+      <c r="AEG25" t="s">
         <v>1123</v>
       </c>
-      <c r="AEK25">
+      <c r="AEL25">
         <v>65</v>
       </c>
-      <c r="AEL25">
+      <c r="AEM25">
         <v>52</v>
       </c>
-      <c r="AEN25">
+      <c r="AEO25">
         <v>62</v>
       </c>
-      <c r="AEO25">
+      <c r="AEP25">
         <v>74</v>
       </c>
-      <c r="AEQ25">
+      <c r="AER25">
         <v>60</v>
       </c>
-      <c r="AER25">
+      <c r="AES25">
         <v>68</v>
       </c>
-      <c r="AEX25">
+      <c r="AEY25">
         <v>887974567</v>
       </c>
-      <c r="AEY25" t="s">
+      <c r="AEZ25" t="s">
         <v>1126</v>
       </c>
-      <c r="AEZ25" s="1">
+      <c r="AFA25" s="1">
         <v>46302.506296296298</v>
       </c>
-      <c r="AFB25" t="s">
+      <c r="AFC25" t="s">
         <v>734</v>
       </c>
-      <c r="AFD25" t="s">
+      <c r="AFE25" t="s">
         <v>963</v>
       </c>
-      <c r="AFE25" t="s">
+      <c r="AFF25" t="s">
         <v>1127</v>
       </c>
-      <c r="AFF25">
+      <c r="AFG25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>46299</v>
       </c>
@@ -15078,89 +15133,89 @@
       <c r="KO26">
         <v>0</v>
       </c>
-      <c r="KQ26" t="s">
+      <c r="KR26" t="s">
         <v>1149</v>
       </c>
-      <c r="KR26" t="s">
+      <c r="KS26" t="s">
         <v>1150</v>
       </c>
-      <c r="KT26" t="s">
+      <c r="KU26" t="s">
         <v>1151</v>
       </c>
-      <c r="NO26">
+      <c r="NP26">
         <v>319</v>
       </c>
-      <c r="NP26">
+      <c r="NQ26">
         <v>338</v>
       </c>
-      <c r="NR26">
+      <c r="NS26">
         <v>98</v>
       </c>
-      <c r="NS26">
+      <c r="NT26">
         <v>92</v>
       </c>
-      <c r="NU26">
+      <c r="NV26">
         <v>86</v>
       </c>
-      <c r="NV26">
+      <c r="NW26">
         <v>67</v>
       </c>
-      <c r="UG26" t="s">
+      <c r="UH26" t="s">
         <v>1152</v>
       </c>
-      <c r="UJ26" t="s">
+      <c r="UK26" t="s">
         <v>708</v>
       </c>
-      <c r="ADZ26" t="s">
+      <c r="AEA26" t="s">
         <v>711</v>
       </c>
-      <c r="AEA26" t="s">
+      <c r="AEB26" t="s">
         <v>732</v>
       </c>
-      <c r="AEF26" t="s">
+      <c r="AEG26" t="s">
         <v>1153</v>
       </c>
-      <c r="AEK26">
+      <c r="AEL26">
         <v>319</v>
       </c>
-      <c r="AEL26">
+      <c r="AEM26">
         <v>338</v>
       </c>
-      <c r="AEN26">
+      <c r="AEO26">
         <v>98</v>
       </c>
-      <c r="AEO26">
+      <c r="AEP26">
         <v>92</v>
       </c>
-      <c r="AEQ26">
+      <c r="AER26">
         <v>86</v>
       </c>
-      <c r="AER26">
+      <c r="AES26">
         <v>67</v>
       </c>
-      <c r="AEX26">
+      <c r="AEY26">
         <v>887974580</v>
       </c>
-      <c r="AEY26" t="s">
+      <c r="AEZ26" t="s">
         <v>1154</v>
       </c>
-      <c r="AEZ26" s="1">
+      <c r="AFA26" s="1">
         <v>46302.506296296298</v>
       </c>
-      <c r="AFB26" t="s">
+      <c r="AFC26" t="s">
         <v>734</v>
       </c>
-      <c r="AFD26" t="s">
+      <c r="AFE26" t="s">
         <v>963</v>
       </c>
-      <c r="AFE26" t="s">
+      <c r="AFF26" t="s">
         <v>1155</v>
       </c>
-      <c r="AFF26">
+      <c r="AFG26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>46305</v>
       </c>
@@ -15218,95 +15273,95 @@
       <c r="FI27">
         <v>333</v>
       </c>
-      <c r="NO27">
+      <c r="NP27">
         <v>319</v>
       </c>
-      <c r="NP27">
+      <c r="NQ27">
         <v>338</v>
       </c>
-      <c r="NR27">
+      <c r="NS27">
         <v>105</v>
       </c>
-      <c r="NS27">
+      <c r="NT27">
         <v>100</v>
       </c>
-      <c r="NU27">
+      <c r="NV27">
         <v>93</v>
       </c>
-      <c r="NV27">
+      <c r="NW27">
         <v>84</v>
       </c>
-      <c r="UG27" t="s">
+      <c r="UH27" t="s">
         <v>1156</v>
       </c>
-      <c r="UJ27" t="s">
+      <c r="UK27" t="s">
         <v>708</v>
       </c>
-      <c r="ACM27" t="s">
+      <c r="ACN27" t="s">
         <v>1157</v>
       </c>
-      <c r="ACN27">
-        <v>0</v>
-      </c>
       <c r="ACO27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ACP27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ACQ27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ACR27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ACS27">
         <v>0</v>
       </c>
-      <c r="ACV27" t="s">
+      <c r="ACT27">
+        <v>0</v>
+      </c>
+      <c r="ACW27" t="s">
         <v>711</v>
       </c>
-      <c r="AEK27">
+      <c r="AEL27">
         <v>319</v>
       </c>
-      <c r="AEL27">
+      <c r="AEM27">
         <v>338</v>
       </c>
-      <c r="AEN27">
+      <c r="AEO27">
         <v>105</v>
       </c>
-      <c r="AEO27">
+      <c r="AEP27">
         <v>100</v>
       </c>
-      <c r="AEQ27">
+      <c r="AER27">
         <v>93</v>
       </c>
-      <c r="AER27">
+      <c r="AES27">
         <v>84</v>
       </c>
-      <c r="AEX27">
+      <c r="AEY27">
         <v>887974595</v>
       </c>
-      <c r="AEY27" t="s">
+      <c r="AEZ27" t="s">
         <v>1158</v>
       </c>
-      <c r="AEZ27" s="1">
+      <c r="AFA27" s="1">
         <v>46302.506307870368</v>
       </c>
-      <c r="AFB27" t="s">
+      <c r="AFC27" t="s">
         <v>734</v>
       </c>
-      <c r="AFD27" t="s">
+      <c r="AFE27" t="s">
         <v>963</v>
       </c>
-      <c r="AFE27" t="s">
+      <c r="AFF27" t="s">
         <v>1159</v>
       </c>
-      <c r="AFF27">
+      <c r="AFG27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>46297</v>
       </c>
@@ -15610,35 +15665,35 @@
       <c r="EM28">
         <v>3</v>
       </c>
-      <c r="UG28" t="s">
+      <c r="UH28" t="s">
         <v>1168</v>
       </c>
-      <c r="UJ28" t="s">
+      <c r="UK28" t="s">
         <v>708</v>
       </c>
-      <c r="AEX28">
+      <c r="AEY28">
         <v>887974610</v>
       </c>
-      <c r="AEY28" t="s">
+      <c r="AEZ28" t="s">
         <v>1169</v>
       </c>
-      <c r="AEZ28" s="1">
+      <c r="AFA28" s="1">
         <v>46302.506307870368</v>
       </c>
-      <c r="AFB28" t="s">
+      <c r="AFC28" t="s">
         <v>734</v>
       </c>
-      <c r="AFD28" t="s">
+      <c r="AFE28" t="s">
         <v>963</v>
       </c>
-      <c r="AFE28" t="s">
+      <c r="AFF28" t="s">
         <v>1170</v>
       </c>
-      <c r="AFF28">
+      <c r="AFG28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>46326</v>
       </c>
@@ -15921,89 +15976,89 @@
       <c r="KO29">
         <v>0</v>
       </c>
-      <c r="KQ29" t="s">
+      <c r="KR29" t="s">
         <v>1189</v>
       </c>
-      <c r="KR29" t="s">
+      <c r="KS29" t="s">
         <v>1190</v>
       </c>
-      <c r="KT29" t="s">
+      <c r="KU29" t="s">
         <v>1191</v>
       </c>
-      <c r="NO29">
+      <c r="NP29">
         <v>253</v>
       </c>
-      <c r="NP29">
+      <c r="NQ29">
         <v>144</v>
       </c>
-      <c r="NR29">
+      <c r="NS29">
         <v>102</v>
       </c>
-      <c r="NS29">
+      <c r="NT29">
         <v>107</v>
       </c>
-      <c r="NU29">
+      <c r="NV29">
         <v>112</v>
       </c>
-      <c r="NV29">
+      <c r="NW29">
         <v>133</v>
       </c>
-      <c r="UG29" t="s">
+      <c r="UH29" t="s">
         <v>1192</v>
       </c>
-      <c r="UJ29" t="s">
+      <c r="UK29" t="s">
         <v>708</v>
-      </c>
-      <c r="ADZ29" t="s">
-        <v>711</v>
       </c>
       <c r="AEA29" t="s">
         <v>711</v>
       </c>
-      <c r="AEF29" t="s">
+      <c r="AEB29" t="s">
+        <v>711</v>
+      </c>
+      <c r="AEG29" t="s">
         <v>1193</v>
       </c>
-      <c r="AEK29">
+      <c r="AEL29">
         <v>253</v>
       </c>
-      <c r="AEL29">
+      <c r="AEM29">
         <v>144</v>
       </c>
-      <c r="AEN29">
+      <c r="AEO29">
         <v>102</v>
       </c>
-      <c r="AEO29">
+      <c r="AEP29">
         <v>107</v>
       </c>
-      <c r="AEQ29">
+      <c r="AER29">
         <v>112</v>
       </c>
-      <c r="AER29">
+      <c r="AES29">
         <v>133</v>
       </c>
-      <c r="AEX29">
+      <c r="AEY29">
         <v>887974623</v>
       </c>
-      <c r="AEY29" t="s">
+      <c r="AEZ29" t="s">
         <v>1194</v>
       </c>
-      <c r="AEZ29" s="1">
+      <c r="AFA29" s="1">
         <v>46302.506319444437</v>
       </c>
-      <c r="AFB29" t="s">
+      <c r="AFC29" t="s">
         <v>734</v>
       </c>
-      <c r="AFD29" t="s">
+      <c r="AFE29" t="s">
         <v>963</v>
       </c>
-      <c r="AFE29" t="s">
+      <c r="AFF29" t="s">
         <v>1195</v>
       </c>
-      <c r="AFF29">
+      <c r="AFG29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>46297</v>
       </c>
@@ -16307,62 +16362,62 @@
       <c r="KO30">
         <v>1</v>
       </c>
-      <c r="KQ30" t="s">
+      <c r="KR30" t="s">
         <v>1214</v>
       </c>
-      <c r="KR30" t="s">
+      <c r="KS30" t="s">
         <v>1215</v>
       </c>
-      <c r="KS30" t="s">
+      <c r="KT30" t="s">
         <v>1216</v>
       </c>
-      <c r="KT30" t="s">
+      <c r="KU30" t="s">
         <v>1217</v>
       </c>
-      <c r="NO30">
+      <c r="NP30">
         <v>194</v>
       </c>
-      <c r="NP30">
+      <c r="NQ30">
         <v>191</v>
       </c>
-      <c r="NR30">
+      <c r="NS30">
         <v>53</v>
       </c>
-      <c r="NS30">
+      <c r="NT30">
         <v>37</v>
       </c>
-      <c r="NU30">
+      <c r="NV30">
         <v>24</v>
       </c>
-      <c r="NV30">
+      <c r="NW30">
         <v>27</v>
       </c>
-      <c r="UG30" t="s">
+      <c r="UH30" t="s">
         <v>1218</v>
       </c>
-      <c r="AEX30">
+      <c r="AEY30">
         <v>887985732</v>
       </c>
-      <c r="AEY30" t="s">
+      <c r="AEZ30" t="s">
         <v>1219</v>
       </c>
-      <c r="AEZ30" s="1">
+      <c r="AFA30" s="1">
         <v>46302.513831018521</v>
       </c>
-      <c r="AFB30" t="s">
+      <c r="AFC30" t="s">
         <v>734</v>
       </c>
-      <c r="AFD30" t="s">
+      <c r="AFE30" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE30" t="s">
+      <c r="AFF30" t="s">
         <v>1220</v>
       </c>
-      <c r="AFF30">
+      <c r="AFG30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>46302</v>
       </c>
@@ -16711,35 +16766,35 @@
       <c r="EM31">
         <v>8</v>
       </c>
-      <c r="UG31" t="s">
+      <c r="UH31" t="s">
         <v>1233</v>
       </c>
-      <c r="UJ31" t="s">
+      <c r="UK31" t="s">
         <v>708</v>
       </c>
-      <c r="AEX31">
+      <c r="AEY31">
         <v>887990407</v>
       </c>
-      <c r="AEY31" t="s">
+      <c r="AEZ31" t="s">
         <v>1234</v>
       </c>
-      <c r="AEZ31" s="1">
+      <c r="AFA31" s="1">
         <v>46302.516724537039</v>
       </c>
-      <c r="AFB31" t="s">
+      <c r="AFC31" t="s">
         <v>734</v>
       </c>
-      <c r="AFD31" t="s">
+      <c r="AFE31" t="s">
         <v>963</v>
       </c>
-      <c r="AFE31" t="s">
+      <c r="AFF31" t="s">
         <v>1235</v>
       </c>
-      <c r="AFF31">
+      <c r="AFG31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>46296</v>
       </c>
@@ -16815,50 +16870,50 @@
       <c r="FH32" t="s">
         <v>732</v>
       </c>
-      <c r="NO32">
+      <c r="NP32">
         <v>124</v>
       </c>
-      <c r="NP32">
+      <c r="NQ32">
         <v>115</v>
       </c>
-      <c r="NR32">
+      <c r="NS32">
         <v>171</v>
       </c>
-      <c r="NS32">
+      <c r="NT32">
         <v>150</v>
       </c>
-      <c r="NU32">
+      <c r="NV32">
         <v>184</v>
       </c>
-      <c r="NV32">
+      <c r="NW32">
         <v>189</v>
       </c>
-      <c r="UG32" t="s">
+      <c r="UH32" t="s">
         <v>1123</v>
       </c>
-      <c r="AEX32">
+      <c r="AEY32">
         <v>887992049</v>
       </c>
-      <c r="AEY32" t="s">
+      <c r="AEZ32" t="s">
         <v>1238</v>
       </c>
-      <c r="AEZ32" s="1">
+      <c r="AFA32" s="1">
         <v>46302.517812500002</v>
       </c>
-      <c r="AFB32" t="s">
+      <c r="AFC32" t="s">
         <v>734</v>
       </c>
-      <c r="AFD32" t="s">
+      <c r="AFE32" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE32" t="s">
+      <c r="AFF32" t="s">
         <v>1239</v>
       </c>
-      <c r="AFF32">
+      <c r="AFG32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>46297</v>
       </c>
@@ -17162,62 +17217,62 @@
       <c r="KO33">
         <v>1</v>
       </c>
-      <c r="KQ33" t="s">
+      <c r="KR33" t="s">
         <v>1259</v>
       </c>
-      <c r="KR33" t="s">
+      <c r="KS33" t="s">
         <v>1260</v>
       </c>
-      <c r="KS33" t="s">
+      <c r="KT33" t="s">
         <v>1261</v>
       </c>
-      <c r="KT33" t="s">
+      <c r="KU33" t="s">
         <v>1262</v>
       </c>
-      <c r="NO33">
+      <c r="NP33">
         <v>124</v>
       </c>
-      <c r="NP33">
+      <c r="NQ33">
         <v>115</v>
       </c>
-      <c r="NR33">
+      <c r="NS33">
         <v>171</v>
       </c>
-      <c r="NS33">
+      <c r="NT33">
         <v>194</v>
       </c>
-      <c r="NU33">
+      <c r="NV33">
         <v>185</v>
       </c>
-      <c r="NV33">
+      <c r="NW33">
         <v>186</v>
       </c>
-      <c r="UG33" t="s">
+      <c r="UH33" t="s">
         <v>1263</v>
       </c>
-      <c r="AEX33">
+      <c r="AEY33">
         <v>888012107</v>
       </c>
-      <c r="AEY33" t="s">
+      <c r="AEZ33" t="s">
         <v>1264</v>
       </c>
-      <c r="AEZ33" s="1">
+      <c r="AFA33" s="1">
         <v>46302.531006944453</v>
       </c>
-      <c r="AFB33" t="s">
+      <c r="AFC33" t="s">
         <v>734</v>
       </c>
-      <c r="AFD33" t="s">
+      <c r="AFE33" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE33" t="s">
+      <c r="AFF33" t="s">
         <v>1265</v>
       </c>
-      <c r="AFF33">
+      <c r="AFG33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>46302</v>
       </c>
@@ -17503,89 +17558,89 @@
       <c r="KO34">
         <v>1</v>
       </c>
-      <c r="KQ34" t="s">
+      <c r="KR34" t="s">
         <v>1285</v>
       </c>
-      <c r="KR34" t="s">
+      <c r="KS34" t="s">
         <v>1286</v>
       </c>
-      <c r="KT34" t="s">
+      <c r="KU34" t="s">
         <v>1149</v>
       </c>
-      <c r="NO34">
+      <c r="NP34">
         <v>209</v>
       </c>
-      <c r="NP34">
+      <c r="NQ34">
         <v>212</v>
       </c>
-      <c r="NR34">
+      <c r="NS34">
         <v>140</v>
       </c>
-      <c r="NS34">
+      <c r="NT34">
         <v>147</v>
       </c>
-      <c r="NU34">
+      <c r="NV34">
         <v>118</v>
       </c>
-      <c r="NV34">
+      <c r="NW34">
         <v>1226</v>
       </c>
-      <c r="UG34" t="s">
+      <c r="UH34" t="s">
         <v>1149</v>
       </c>
-      <c r="UJ34" t="s">
+      <c r="UK34" t="s">
         <v>708</v>
       </c>
-      <c r="ADZ34" t="s">
+      <c r="AEA34" t="s">
         <v>711</v>
       </c>
-      <c r="AEA34" t="s">
+      <c r="AEB34" t="s">
         <v>732</v>
       </c>
-      <c r="AEF34" t="s">
+      <c r="AEG34" t="s">
         <v>1149</v>
       </c>
-      <c r="AEK34">
+      <c r="AEL34">
         <v>209</v>
       </c>
-      <c r="AEL34">
+      <c r="AEM34">
         <v>212</v>
       </c>
-      <c r="AEN34">
+      <c r="AEO34">
         <v>140</v>
       </c>
-      <c r="AEO34">
+      <c r="AEP34">
         <v>147</v>
       </c>
-      <c r="AEQ34">
+      <c r="AER34">
         <v>118</v>
       </c>
-      <c r="AER34">
+      <c r="AES34">
         <v>126</v>
       </c>
-      <c r="AEX34">
+      <c r="AEY34">
         <v>888016271</v>
       </c>
-      <c r="AEY34" t="s">
+      <c r="AEZ34" t="s">
         <v>1287</v>
       </c>
-      <c r="AEZ34" s="1">
+      <c r="AFA34" s="1">
         <v>46302.533784722233</v>
       </c>
-      <c r="AFB34" t="s">
+      <c r="AFC34" t="s">
         <v>734</v>
       </c>
-      <c r="AFD34" t="s">
+      <c r="AFE34" t="s">
         <v>963</v>
       </c>
-      <c r="AFE34" t="s">
+      <c r="AFF34" t="s">
         <v>1288</v>
       </c>
-      <c r="AFF34">
+      <c r="AFG34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>46297</v>
       </c>
@@ -17661,50 +17716,50 @@
       <c r="FH35" t="s">
         <v>732</v>
       </c>
-      <c r="NO35">
+      <c r="NP35">
         <v>253</v>
       </c>
-      <c r="NP35">
+      <c r="NQ35">
         <v>230</v>
       </c>
-      <c r="NR35">
+      <c r="NS35">
         <v>201</v>
       </c>
-      <c r="NS35">
+      <c r="NT35">
         <v>180</v>
       </c>
-      <c r="NU35">
+      <c r="NV35">
         <v>237</v>
       </c>
-      <c r="NV35">
+      <c r="NW35">
         <v>243</v>
       </c>
-      <c r="UG35" t="s">
+      <c r="UH35" t="s">
         <v>1291</v>
       </c>
-      <c r="AEX35">
+      <c r="AEY35">
         <v>888043285</v>
       </c>
-      <c r="AEY35" t="s">
+      <c r="AEZ35" t="s">
         <v>1292</v>
       </c>
-      <c r="AEZ35" s="1">
+      <c r="AFA35" s="1">
         <v>46302.553067129629</v>
       </c>
-      <c r="AFB35" t="s">
+      <c r="AFC35" t="s">
         <v>734</v>
       </c>
-      <c r="AFD35" t="s">
+      <c r="AFE35" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE35" t="s">
+      <c r="AFF35" t="s">
         <v>1293</v>
       </c>
-      <c r="AFF35">
+      <c r="AFG35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>46301</v>
       </c>
@@ -18014,62 +18069,62 @@
       <c r="KO36">
         <v>1</v>
       </c>
-      <c r="KQ36" t="s">
+      <c r="KR36" t="s">
         <v>1312</v>
       </c>
-      <c r="KR36" t="s">
+      <c r="KS36" t="s">
         <v>1313</v>
       </c>
-      <c r="KS36" t="s">
+      <c r="KT36" t="s">
         <v>1314</v>
       </c>
-      <c r="KT36" t="s">
+      <c r="KU36" t="s">
         <v>1315</v>
       </c>
-      <c r="NO36">
+      <c r="NP36">
         <v>254</v>
       </c>
-      <c r="NP36">
+      <c r="NQ36">
         <v>231</v>
       </c>
-      <c r="NR36">
+      <c r="NS36">
         <v>205</v>
       </c>
-      <c r="NS36">
+      <c r="NT36">
         <v>187</v>
       </c>
-      <c r="NU36">
+      <c r="NV36">
         <v>237</v>
       </c>
-      <c r="NV36">
+      <c r="NW36">
         <v>482</v>
       </c>
-      <c r="UG36" t="s">
+      <c r="UH36" t="s">
         <v>1316</v>
       </c>
-      <c r="AEX36">
+      <c r="AEY36">
         <v>888059430</v>
       </c>
-      <c r="AEY36" t="s">
+      <c r="AEZ36" t="s">
         <v>1317</v>
       </c>
-      <c r="AEZ36" s="1">
+      <c r="AFA36" s="1">
         <v>46302.564606481479</v>
       </c>
-      <c r="AFB36" t="s">
+      <c r="AFC36" t="s">
         <v>734</v>
       </c>
-      <c r="AFD36" t="s">
+      <c r="AFE36" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE36" t="s">
+      <c r="AFF36" t="s">
         <v>1318</v>
       </c>
-      <c r="AFF36">
+      <c r="AFG36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>46301</v>
       </c>
@@ -18145,50 +18200,50 @@
       <c r="FH37" t="s">
         <v>732</v>
       </c>
-      <c r="NO37">
+      <c r="NP37">
         <v>170</v>
       </c>
-      <c r="NP37">
+      <c r="NQ37">
         <v>102</v>
       </c>
-      <c r="NR37">
+      <c r="NS37">
         <v>203</v>
       </c>
-      <c r="NS37">
+      <c r="NT37">
         <v>161</v>
       </c>
-      <c r="NU37">
+      <c r="NV37">
         <v>645</v>
       </c>
-      <c r="NV37">
+      <c r="NW37">
         <v>275</v>
       </c>
-      <c r="UG37" t="s">
+      <c r="UH37" t="s">
         <v>1320</v>
       </c>
-      <c r="AEX37">
+      <c r="AEY37">
         <v>888068959</v>
       </c>
-      <c r="AEY37" t="s">
+      <c r="AEZ37" t="s">
         <v>1321</v>
       </c>
-      <c r="AEZ37" s="1">
+      <c r="AFA37" s="1">
         <v>46302.571493055562</v>
       </c>
-      <c r="AFB37" t="s">
+      <c r="AFC37" t="s">
         <v>734</v>
       </c>
-      <c r="AFD37" t="s">
+      <c r="AFE37" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE37" t="s">
+      <c r="AFF37" t="s">
         <v>1322</v>
       </c>
-      <c r="AFF37">
+      <c r="AFG37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>46301</v>
       </c>
@@ -18495,62 +18550,62 @@
       <c r="KO38">
         <v>1</v>
       </c>
-      <c r="KQ38" t="s">
+      <c r="KR38" t="s">
         <v>1342</v>
       </c>
-      <c r="KR38" t="s">
+      <c r="KS38" t="s">
         <v>1343</v>
       </c>
-      <c r="KS38" t="s">
+      <c r="KT38" t="s">
         <v>1344</v>
       </c>
-      <c r="KT38" t="s">
+      <c r="KU38" t="s">
         <v>1345</v>
       </c>
-      <c r="NO38">
+      <c r="NP38">
         <v>170</v>
       </c>
-      <c r="NP38">
+      <c r="NQ38">
         <v>106</v>
       </c>
-      <c r="NR38">
+      <c r="NS38">
         <v>207</v>
       </c>
-      <c r="NS38">
+      <c r="NT38">
         <v>167</v>
       </c>
-      <c r="NU38">
+      <c r="NV38">
         <v>270</v>
       </c>
-      <c r="NV38">
+      <c r="NW38">
         <v>276</v>
       </c>
-      <c r="UG38" t="s">
+      <c r="UH38" t="s">
         <v>1149</v>
       </c>
-      <c r="AEX38">
+      <c r="AEY38">
         <v>888115900</v>
       </c>
-      <c r="AEY38" t="s">
+      <c r="AEZ38" t="s">
         <v>1346</v>
       </c>
-      <c r="AEZ38" s="1">
+      <c r="AFA38" s="1">
         <v>46302.604409722233</v>
       </c>
-      <c r="AFB38" t="s">
+      <c r="AFC38" t="s">
         <v>734</v>
       </c>
-      <c r="AFD38" t="s">
+      <c r="AFE38" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE38" t="s">
+      <c r="AFF38" t="s">
         <v>1347</v>
       </c>
-      <c r="AFF38">
+      <c r="AFG38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>46295</v>
       </c>
@@ -18860,62 +18915,62 @@
       <c r="KO39">
         <v>1</v>
       </c>
-      <c r="KQ39" t="s">
+      <c r="KR39" t="s">
         <v>1367</v>
       </c>
-      <c r="KR39" t="s">
+      <c r="KS39" t="s">
         <v>1368</v>
       </c>
-      <c r="KS39" t="s">
+      <c r="KT39" t="s">
         <v>1369</v>
       </c>
-      <c r="KT39" t="s">
+      <c r="KU39" t="s">
         <v>1370</v>
       </c>
-      <c r="NO39">
+      <c r="NP39">
         <v>67</v>
       </c>
-      <c r="NP39">
+      <c r="NQ39">
         <v>128</v>
       </c>
-      <c r="NR39">
+      <c r="NS39">
         <v>159</v>
       </c>
-      <c r="NS39">
+      <c r="NT39">
         <v>295</v>
       </c>
-      <c r="NU39">
+      <c r="NV39">
         <v>323</v>
       </c>
-      <c r="NV39">
+      <c r="NW39">
         <v>591</v>
       </c>
-      <c r="UG39" t="s">
+      <c r="UH39" t="s">
         <v>1149</v>
       </c>
-      <c r="AEX39">
+      <c r="AEY39">
         <v>888139197</v>
       </c>
-      <c r="AEY39" t="s">
+      <c r="AEZ39" t="s">
         <v>1371</v>
       </c>
-      <c r="AEZ39" s="1">
+      <c r="AFA39" s="1">
         <v>46302.620891203696</v>
       </c>
-      <c r="AFB39" t="s">
+      <c r="AFC39" t="s">
         <v>734</v>
       </c>
-      <c r="AFD39" t="s">
+      <c r="AFE39" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE39" t="s">
+      <c r="AFF39" t="s">
         <v>1372</v>
       </c>
-      <c r="AFF39">
+      <c r="AFG39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>46302</v>
       </c>
@@ -19222,62 +19277,62 @@
       <c r="KO40">
         <v>0</v>
       </c>
-      <c r="KQ40" t="s">
+      <c r="KR40" t="s">
         <v>1385</v>
       </c>
-      <c r="KR40" t="s">
+      <c r="KS40" t="s">
         <v>1386</v>
       </c>
-      <c r="KS40" t="s">
+      <c r="KT40" t="s">
         <v>1387</v>
       </c>
-      <c r="KT40" t="s">
+      <c r="KU40" t="s">
         <v>1388</v>
       </c>
-      <c r="NO40">
+      <c r="NP40">
         <v>276</v>
       </c>
-      <c r="NP40">
+      <c r="NQ40">
         <v>304</v>
       </c>
-      <c r="NR40">
+      <c r="NS40">
         <v>201</v>
       </c>
-      <c r="NS40">
+      <c r="NT40">
         <v>269</v>
       </c>
-      <c r="NU40">
+      <c r="NV40">
         <v>85</v>
       </c>
-      <c r="NV40">
+      <c r="NW40">
         <v>67</v>
       </c>
-      <c r="UG40" t="s">
+      <c r="UH40" t="s">
         <v>1389</v>
       </c>
-      <c r="AEX40">
+      <c r="AEY40">
         <v>888162934</v>
       </c>
-      <c r="AEY40" t="s">
+      <c r="AEZ40" t="s">
         <v>1390</v>
       </c>
-      <c r="AEZ40" s="1">
+      <c r="AFA40" s="1">
         <v>46302.638159722221</v>
       </c>
-      <c r="AFB40" t="s">
+      <c r="AFC40" t="s">
         <v>734</v>
       </c>
-      <c r="AFD40" t="s">
+      <c r="AFE40" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE40" t="s">
+      <c r="AFF40" t="s">
         <v>1391</v>
       </c>
-      <c r="AFF40">
+      <c r="AFG40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>46302</v>
       </c>
@@ -19362,50 +19417,50 @@
       <c r="FJ41" t="s">
         <v>842</v>
       </c>
-      <c r="NO41">
+      <c r="NP41">
         <v>492</v>
       </c>
-      <c r="NP41">
+      <c r="NQ41">
         <v>465</v>
       </c>
-      <c r="NR41">
+      <c r="NS41">
         <v>233</v>
       </c>
-      <c r="NS41">
+      <c r="NT41">
         <v>173</v>
       </c>
-      <c r="NU41">
+      <c r="NV41">
         <v>113</v>
       </c>
-      <c r="NV41">
+      <c r="NW41">
         <v>80</v>
       </c>
-      <c r="UG41" t="s">
+      <c r="UH41" t="s">
         <v>1395</v>
       </c>
-      <c r="AEX41">
+      <c r="AEY41">
         <v>888172725</v>
       </c>
-      <c r="AEY41" t="s">
+      <c r="AEZ41" t="s">
         <v>1396</v>
       </c>
-      <c r="AEZ41" s="1">
+      <c r="AFA41" s="1">
         <v>46302.64607638889</v>
       </c>
-      <c r="AFB41" t="s">
+      <c r="AFC41" t="s">
         <v>734</v>
       </c>
-      <c r="AFD41" t="s">
+      <c r="AFE41" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE41" t="s">
+      <c r="AFF41" t="s">
         <v>1397</v>
       </c>
-      <c r="AFF41">
+      <c r="AFG41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>46301</v>
       </c>
@@ -19487,50 +19542,50 @@
       <c r="FJ42" t="s">
         <v>842</v>
       </c>
-      <c r="NO42">
+      <c r="NP42">
         <v>306</v>
       </c>
-      <c r="NP42">
+      <c r="NQ42">
         <v>351</v>
       </c>
-      <c r="NR42">
+      <c r="NS42">
         <v>238</v>
       </c>
-      <c r="NS42">
+      <c r="NT42">
         <v>248</v>
       </c>
-      <c r="NU42">
+      <c r="NV42">
         <v>253</v>
       </c>
-      <c r="NV42">
+      <c r="NW42">
         <v>201</v>
       </c>
-      <c r="UG42" t="s">
+      <c r="UH42" t="s">
         <v>1402</v>
       </c>
-      <c r="AEX42">
+      <c r="AEY42">
         <v>888185704</v>
       </c>
-      <c r="AEY42" t="s">
+      <c r="AEZ42" t="s">
         <v>1403</v>
       </c>
-      <c r="AEZ42" s="1">
+      <c r="AFA42" s="1">
         <v>46302.655925925923</v>
       </c>
-      <c r="AFB42" t="s">
+      <c r="AFC42" t="s">
         <v>734</v>
       </c>
-      <c r="AFD42" t="s">
+      <c r="AFE42" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE42" t="s">
+      <c r="AFF42" t="s">
         <v>1404</v>
       </c>
-      <c r="AFF42">
+      <c r="AFG42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>46301</v>
       </c>
@@ -19840,62 +19895,62 @@
       <c r="KO43">
         <v>0</v>
       </c>
-      <c r="KQ43" t="s">
+      <c r="KR43" t="s">
         <v>1423</v>
       </c>
-      <c r="KR43" t="s">
+      <c r="KS43" t="s">
         <v>1424</v>
       </c>
-      <c r="KS43" t="s">
+      <c r="KT43" t="s">
         <v>1425</v>
       </c>
-      <c r="KT43" t="s">
+      <c r="KU43" t="s">
         <v>1426</v>
       </c>
-      <c r="NO43">
+      <c r="NP43">
         <v>306</v>
       </c>
-      <c r="NP43">
+      <c r="NQ43">
         <v>351</v>
       </c>
-      <c r="NR43">
+      <c r="NS43">
         <v>238</v>
       </c>
-      <c r="NS43">
+      <c r="NT43">
         <v>248</v>
       </c>
-      <c r="NU43">
+      <c r="NV43">
         <v>253</v>
       </c>
-      <c r="NV43">
+      <c r="NW43">
         <v>201</v>
       </c>
-      <c r="UG43" t="s">
+      <c r="UH43" t="s">
         <v>1427</v>
       </c>
-      <c r="AEX43">
+      <c r="AEY43">
         <v>888187658</v>
       </c>
-      <c r="AEY43" t="s">
+      <c r="AEZ43" t="s">
         <v>1428</v>
       </c>
-      <c r="AEZ43" s="1">
+      <c r="AFA43" s="1">
         <v>46302.657418981478</v>
       </c>
-      <c r="AFB43" t="s">
+      <c r="AFC43" t="s">
         <v>734</v>
       </c>
-      <c r="AFD43" t="s">
+      <c r="AFE43" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE43" t="s">
+      <c r="AFF43" t="s">
         <v>1429</v>
       </c>
-      <c r="AFF43">
+      <c r="AFG43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>46301</v>
       </c>
@@ -19974,50 +20029,50 @@
       <c r="FH44" t="s">
         <v>732</v>
       </c>
-      <c r="NO44">
+      <c r="NP44">
         <v>315</v>
       </c>
-      <c r="NP44">
+      <c r="NQ44">
         <v>256</v>
       </c>
-      <c r="NR44">
+      <c r="NS44">
         <v>193</v>
       </c>
-      <c r="NS44">
+      <c r="NT44">
         <v>148</v>
       </c>
-      <c r="NU44">
+      <c r="NV44">
         <v>87</v>
       </c>
-      <c r="NV44">
+      <c r="NW44">
         <v>62</v>
       </c>
-      <c r="UG44" t="s">
+      <c r="UH44" t="s">
         <v>1432</v>
       </c>
-      <c r="AEX44">
+      <c r="AEY44">
         <v>888194246</v>
       </c>
-      <c r="AEY44" t="s">
+      <c r="AEZ44" t="s">
         <v>1433</v>
       </c>
-      <c r="AEZ44" s="1">
+      <c r="AFA44" s="1">
         <v>46302.662210648137</v>
       </c>
-      <c r="AFB44" t="s">
+      <c r="AFC44" t="s">
         <v>734</v>
       </c>
-      <c r="AFD44" t="s">
+      <c r="AFE44" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE44" t="s">
+      <c r="AFF44" t="s">
         <v>1434</v>
       </c>
-      <c r="AFF44">
+      <c r="AFG44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>46301</v>
       </c>
@@ -20327,62 +20382,62 @@
       <c r="KO45">
         <v>0</v>
       </c>
-      <c r="KQ45" t="s">
+      <c r="KR45" t="s">
         <v>1477</v>
       </c>
-      <c r="KR45" t="s">
+      <c r="KS45" t="s">
         <v>1478</v>
       </c>
-      <c r="KS45" t="s">
+      <c r="KT45" t="s">
         <v>1479</v>
       </c>
-      <c r="KT45" t="s">
+      <c r="KU45" t="s">
         <v>1480</v>
       </c>
-      <c r="NO45">
+      <c r="NP45">
         <v>315</v>
       </c>
-      <c r="NP45">
+      <c r="NQ45">
         <v>256</v>
       </c>
-      <c r="NR45">
+      <c r="NS45">
         <v>193</v>
       </c>
-      <c r="NS45">
+      <c r="NT45">
         <v>148</v>
       </c>
-      <c r="NU45">
+      <c r="NV45">
         <v>87</v>
       </c>
-      <c r="NV45">
+      <c r="NW45">
         <v>62</v>
       </c>
-      <c r="UG45" t="s">
+      <c r="UH45" t="s">
         <v>1481</v>
       </c>
-      <c r="AEX45">
+      <c r="AEY45">
         <v>888279907</v>
       </c>
-      <c r="AEY45" t="s">
+      <c r="AEZ45" t="s">
         <v>1482</v>
       </c>
-      <c r="AEZ45" s="1">
+      <c r="AFA45" s="1">
         <v>46302.729814814818</v>
       </c>
-      <c r="AFB45" t="s">
+      <c r="AFC45" t="s">
         <v>734</v>
       </c>
-      <c r="AFD45" t="s">
+      <c r="AFE45" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE45" t="s">
+      <c r="AFF45" t="s">
         <v>1483</v>
       </c>
-      <c r="AFF45">
+      <c r="AFG45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>46302</v>
       </c>
@@ -20692,62 +20747,62 @@
       <c r="KO46">
         <v>0</v>
       </c>
-      <c r="KQ46" t="s">
+      <c r="KR46" t="s">
         <v>1503</v>
       </c>
-      <c r="KR46" t="s">
+      <c r="KS46" t="s">
         <v>1504</v>
       </c>
-      <c r="KS46" t="s">
+      <c r="KT46" t="s">
         <v>1505</v>
       </c>
-      <c r="KT46" t="s">
+      <c r="KU46" t="s">
         <v>1506</v>
       </c>
-      <c r="NO46">
+      <c r="NP46">
         <v>280</v>
       </c>
-      <c r="NP46">
+      <c r="NQ46">
         <v>165</v>
       </c>
-      <c r="NR46">
+      <c r="NS46">
         <v>215</v>
       </c>
-      <c r="NS46">
+      <c r="NT46">
         <v>205</v>
       </c>
-      <c r="NU46">
+      <c r="NV46">
         <v>263</v>
       </c>
-      <c r="NV46">
+      <c r="NW46">
         <v>115</v>
       </c>
-      <c r="UG46" t="s">
+      <c r="UH46" t="s">
         <v>1507</v>
       </c>
-      <c r="AEX46">
+      <c r="AEY46">
         <v>888285118</v>
       </c>
-      <c r="AEY46" t="s">
+      <c r="AEZ46" t="s">
         <v>1508</v>
       </c>
-      <c r="AEZ46" s="1">
+      <c r="AFA46" s="1">
         <v>46302.734884259262</v>
       </c>
-      <c r="AFB46" t="s">
+      <c r="AFC46" t="s">
         <v>734</v>
       </c>
-      <c r="AFD46" t="s">
+      <c r="AFE46" t="s">
         <v>1085</v>
       </c>
-      <c r="AFE46" t="s">
+      <c r="AFF46" t="s">
         <v>1509</v>
       </c>
-      <c r="AFF46">
+      <c r="AFG46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46302</v>
       </c>
@@ -21054,37 +21109,37 @@
       <c r="EM47">
         <v>3</v>
       </c>
-      <c r="SC47" s="1"/>
-      <c r="UG47" t="s">
+      <c r="SD47" s="1"/>
+      <c r="UH47" t="s">
         <v>1149</v>
       </c>
-      <c r="ZK47" s="1"/>
-      <c r="ADN47" s="1"/>
-      <c r="ADV47" s="1"/>
-      <c r="ADZ47" s="1"/>
-      <c r="AEX47">
+      <c r="ZL47" s="1"/>
+      <c r="ADO47" s="1"/>
+      <c r="ADW47" s="1"/>
+      <c r="AEA47" s="1"/>
+      <c r="AEY47">
         <v>888660682</v>
       </c>
-      <c r="AEY47" t="s">
+      <c r="AEZ47" t="s">
         <v>1575</v>
       </c>
-      <c r="AEZ47" s="1">
+      <c r="AFA47" s="1">
         <v>46303.340243055558</v>
       </c>
-      <c r="AFB47" t="s">
+      <c r="AFC47" t="s">
         <v>734</v>
       </c>
-      <c r="AFD47" t="s">
+      <c r="AFE47" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE47" t="s">
+      <c r="AFF47" t="s">
         <v>1577</v>
       </c>
-      <c r="AFF47">
+      <c r="AFG47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46303</v>
       </c>
@@ -21394,67 +21449,67 @@
       <c r="KO48">
         <v>0</v>
       </c>
-      <c r="KQ48" t="s">
+      <c r="KR48" t="s">
         <v>1149</v>
       </c>
-      <c r="KR48" t="s">
+      <c r="KS48" t="s">
         <v>1599</v>
       </c>
-      <c r="KS48" t="s">
+      <c r="KT48" t="s">
         <v>1600</v>
       </c>
-      <c r="KT48" t="s">
+      <c r="KU48" t="s">
         <v>1149</v>
       </c>
-      <c r="NO48">
+      <c r="NP48">
         <v>254</v>
       </c>
-      <c r="NP48">
+      <c r="NQ48">
         <v>163</v>
       </c>
-      <c r="NR48">
+      <c r="NS48">
         <v>125</v>
       </c>
-      <c r="NS48">
+      <c r="NT48">
         <v>146</v>
       </c>
-      <c r="NU48">
+      <c r="NV48">
         <v>178</v>
       </c>
-      <c r="NV48">
+      <c r="NW48">
         <v>160</v>
       </c>
-      <c r="SC48" s="1"/>
-      <c r="UG48" t="s">
+      <c r="SD48" s="1"/>
+      <c r="UH48" t="s">
         <v>1149</v>
       </c>
-      <c r="ZK48" s="1"/>
-      <c r="ADN48" s="1"/>
-      <c r="ADV48" s="1"/>
-      <c r="ADZ48" s="1"/>
-      <c r="AEX48">
+      <c r="ZL48" s="1"/>
+      <c r="ADO48" s="1"/>
+      <c r="ADW48" s="1"/>
+      <c r="AEA48" s="1"/>
+      <c r="AEY48">
         <v>888693909</v>
       </c>
-      <c r="AEY48" t="s">
+      <c r="AEZ48" t="s">
         <v>1601</v>
       </c>
-      <c r="AEZ48" s="1">
+      <c r="AFA48" s="1">
         <v>46303.364583333343</v>
       </c>
-      <c r="AFB48" t="s">
+      <c r="AFC48" t="s">
         <v>734</v>
       </c>
-      <c r="AFD48" t="s">
+      <c r="AFE48" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE48" t="s">
+      <c r="AFF48" t="s">
         <v>1602</v>
       </c>
-      <c r="AFF48">
+      <c r="AFG48">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>46303</v>
       </c>
@@ -21530,55 +21585,55 @@
       <c r="FH49" t="s">
         <v>732</v>
       </c>
-      <c r="NO49">
+      <c r="NP49">
         <v>560</v>
       </c>
-      <c r="NP49">
+      <c r="NQ49">
         <v>492</v>
       </c>
-      <c r="NR49">
+      <c r="NS49">
         <v>180</v>
       </c>
-      <c r="NS49">
+      <c r="NT49">
         <v>134</v>
       </c>
-      <c r="NU49">
+      <c r="NV49">
         <v>81</v>
       </c>
-      <c r="NV49">
+      <c r="NW49">
         <v>38</v>
       </c>
-      <c r="SC49" s="1"/>
-      <c r="UG49" t="s">
+      <c r="SD49" s="1"/>
+      <c r="UH49" t="s">
         <v>1605</v>
       </c>
-      <c r="ZK49" s="1"/>
-      <c r="ADN49" s="1"/>
-      <c r="ADV49" s="1"/>
-      <c r="ADZ49" s="1"/>
-      <c r="AEX49">
+      <c r="ZL49" s="1"/>
+      <c r="ADO49" s="1"/>
+      <c r="ADW49" s="1"/>
+      <c r="AEA49" s="1"/>
+      <c r="AEY49">
         <v>888703239</v>
       </c>
-      <c r="AEY49" t="s">
+      <c r="AEZ49" t="s">
         <v>1606</v>
       </c>
-      <c r="AEZ49" s="1">
+      <c r="AFA49" s="1">
         <v>46303.371145833327</v>
       </c>
-      <c r="AFB49" t="s">
+      <c r="AFC49" t="s">
         <v>734</v>
       </c>
-      <c r="AFD49" t="s">
+      <c r="AFE49" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE49" t="s">
+      <c r="AFF49" t="s">
         <v>1607</v>
       </c>
-      <c r="AFF49">
+      <c r="AFG49">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46301</v>
       </c>
@@ -21657,55 +21712,55 @@
       <c r="FH50" t="s">
         <v>732</v>
       </c>
-      <c r="NO50">
+      <c r="NP50">
         <v>589</v>
       </c>
-      <c r="NP50">
+      <c r="NQ50">
         <v>254</v>
       </c>
-      <c r="NR50">
+      <c r="NS50">
         <v>109</v>
       </c>
-      <c r="NS50">
+      <c r="NT50">
         <v>113</v>
       </c>
-      <c r="NU50">
+      <c r="NV50">
         <v>90</v>
       </c>
-      <c r="NV50">
+      <c r="NW50">
         <v>80</v>
       </c>
-      <c r="SC50" s="1"/>
-      <c r="UG50" t="s">
+      <c r="SD50" s="1"/>
+      <c r="UH50" t="s">
         <v>1611</v>
       </c>
-      <c r="ZK50" s="1"/>
-      <c r="ADN50" s="1"/>
-      <c r="ADV50" s="1"/>
-      <c r="ADZ50" s="1"/>
-      <c r="AEX50">
+      <c r="ZL50" s="1"/>
+      <c r="ADO50" s="1"/>
+      <c r="ADW50" s="1"/>
+      <c r="AEA50" s="1"/>
+      <c r="AEY50">
         <v>888730918</v>
       </c>
-      <c r="AEY50" t="s">
+      <c r="AEZ50" t="s">
         <v>1612</v>
       </c>
-      <c r="AEZ50" s="1">
+      <c r="AFA50" s="1">
         <v>46303.39203703704</v>
       </c>
-      <c r="AFB50" t="s">
+      <c r="AFC50" t="s">
         <v>734</v>
       </c>
-      <c r="AFD50" t="s">
+      <c r="AFE50" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE50" t="s">
+      <c r="AFF50" t="s">
         <v>1613</v>
       </c>
-      <c r="AFF50">
+      <c r="AFG50">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>46301</v>
       </c>
@@ -21784,55 +21839,55 @@
       <c r="FH51" t="s">
         <v>732</v>
       </c>
-      <c r="NO51">
+      <c r="NP51">
         <v>490</v>
       </c>
-      <c r="NP51">
+      <c r="NQ51">
         <v>355</v>
       </c>
-      <c r="NR51">
+      <c r="NS51">
         <v>315</v>
       </c>
-      <c r="NS51">
+      <c r="NT51">
         <v>200</v>
       </c>
-      <c r="NU51">
+      <c r="NV51">
         <v>309</v>
       </c>
-      <c r="NV51">
+      <c r="NW51">
         <v>180</v>
       </c>
-      <c r="SC51" s="1"/>
-      <c r="UG51" t="s">
+      <c r="SD51" s="1"/>
+      <c r="UH51" t="s">
         <v>1616</v>
       </c>
-      <c r="ZK51" s="1"/>
-      <c r="ADN51" s="1"/>
-      <c r="ADV51" s="1"/>
-      <c r="ADZ51" s="1"/>
-      <c r="AEX51">
+      <c r="ZL51" s="1"/>
+      <c r="ADO51" s="1"/>
+      <c r="ADW51" s="1"/>
+      <c r="AEA51" s="1"/>
+      <c r="AEY51">
         <v>889036553</v>
       </c>
-      <c r="AEY51" t="s">
+      <c r="AEZ51" t="s">
         <v>1617</v>
       </c>
-      <c r="AEZ51" s="1">
+      <c r="AFA51" s="1">
         <v>46303.623703703714</v>
       </c>
-      <c r="AFB51" t="s">
+      <c r="AFC51" t="s">
         <v>734</v>
       </c>
-      <c r="AFD51" t="s">
+      <c r="AFE51" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE51" t="s">
+      <c r="AFF51" t="s">
         <v>1618</v>
       </c>
-      <c r="AFF51">
+      <c r="AFG51">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>46303</v>
       </c>
@@ -22139,70 +22194,70 @@
       <c r="KO52">
         <v>0</v>
       </c>
-      <c r="KP52" t="s">
+      <c r="KQ52" t="s">
         <v>842</v>
       </c>
-      <c r="KQ52" t="s">
+      <c r="KR52" t="s">
         <v>1639</v>
       </c>
-      <c r="KR52" t="s">
+      <c r="KS52" t="s">
         <v>1640</v>
       </c>
-      <c r="KS52" t="s">
+      <c r="KT52" t="s">
         <v>1641</v>
       </c>
-      <c r="KT52" t="s">
+      <c r="KU52" t="s">
         <v>1642</v>
       </c>
-      <c r="NO52">
+      <c r="NP52">
         <v>560</v>
       </c>
-      <c r="NP52">
+      <c r="NQ52">
         <v>492</v>
       </c>
-      <c r="NR52">
+      <c r="NS52">
         <v>180</v>
       </c>
-      <c r="NS52">
+      <c r="NT52">
         <v>134</v>
       </c>
-      <c r="NU52">
+      <c r="NV52">
         <v>81</v>
       </c>
-      <c r="NV52">
+      <c r="NW52">
         <v>38</v>
       </c>
-      <c r="SC52" s="1"/>
-      <c r="UG52" t="s">
+      <c r="SD52" s="1"/>
+      <c r="UH52" t="s">
         <v>1643</v>
       </c>
-      <c r="ZK52" s="1"/>
-      <c r="ADN52" s="1"/>
-      <c r="ADV52" s="1"/>
-      <c r="ADZ52" s="1"/>
-      <c r="AEX52">
+      <c r="ZL52" s="1"/>
+      <c r="ADO52" s="1"/>
+      <c r="ADW52" s="1"/>
+      <c r="AEA52" s="1"/>
+      <c r="AEY52">
         <v>889131552</v>
       </c>
-      <c r="AEY52" t="s">
+      <c r="AEZ52" t="s">
         <v>1644</v>
       </c>
-      <c r="AEZ52" s="1">
+      <c r="AFA52" s="1">
         <v>46303.706770833327</v>
       </c>
-      <c r="AFB52" t="s">
+      <c r="AFC52" t="s">
         <v>734</v>
       </c>
-      <c r="AFD52" t="s">
+      <c r="AFE52" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE52" t="s">
+      <c r="AFF52" t="s">
         <v>1645</v>
       </c>
-      <c r="AFF52">
+      <c r="AFG52">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>46303</v>
       </c>
@@ -22278,55 +22333,55 @@
       <c r="FH53" t="s">
         <v>732</v>
       </c>
-      <c r="NO53">
+      <c r="NP53">
         <v>251</v>
       </c>
-      <c r="NP53">
+      <c r="NQ53">
         <v>237</v>
       </c>
-      <c r="NR53">
+      <c r="NS53">
         <v>64</v>
       </c>
-      <c r="NS53">
+      <c r="NT53">
         <v>62</v>
       </c>
-      <c r="NU53">
+      <c r="NV53">
         <v>67</v>
       </c>
-      <c r="NV53">
+      <c r="NW53">
         <v>42</v>
       </c>
-      <c r="SC53" s="1"/>
-      <c r="UG53" t="s">
+      <c r="SD53" s="1"/>
+      <c r="UH53" t="s">
         <v>1648</v>
       </c>
-      <c r="ZK53" s="1"/>
-      <c r="ADN53" s="1"/>
-      <c r="ADV53" s="1"/>
-      <c r="ADZ53" s="1"/>
-      <c r="AEX53">
+      <c r="ZL53" s="1"/>
+      <c r="ADO53" s="1"/>
+      <c r="ADW53" s="1"/>
+      <c r="AEA53" s="1"/>
+      <c r="AEY53">
         <v>889137892</v>
       </c>
-      <c r="AEY53" t="s">
+      <c r="AEZ53" t="s">
         <v>1649</v>
       </c>
-      <c r="AEZ53" s="1">
+      <c r="AFA53" s="1">
         <v>46303.713113425933</v>
       </c>
-      <c r="AFB53" t="s">
+      <c r="AFC53" t="s">
         <v>734</v>
       </c>
-      <c r="AFD53" t="s">
+      <c r="AFE53" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE53" t="s">
+      <c r="AFF53" t="s">
         <v>1650</v>
       </c>
-      <c r="AFF53">
+      <c r="AFG53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>46303</v>
       </c>
@@ -22342,100 +22397,100 @@
       <c r="I54" t="s">
         <v>1651</v>
       </c>
-      <c r="SC54" s="1"/>
-      <c r="SU54" t="s">
+      <c r="SD54" s="1"/>
+      <c r="SV54" t="s">
         <v>740</v>
       </c>
-      <c r="SV54">
-        <v>1</v>
-      </c>
       <c r="SW54">
-        <v>0</v>
-      </c>
-      <c r="SX54" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX54">
+        <v>0</v>
+      </c>
+      <c r="SY54" t="s">
         <v>1652</v>
       </c>
-      <c r="SY54">
+      <c r="SZ54">
         <v>13</v>
       </c>
-      <c r="SZ54">
+      <c r="TA54">
         <v>24</v>
       </c>
-      <c r="TA54" t="s">
+      <c r="TB54" t="s">
         <v>1653</v>
       </c>
-      <c r="TB54" s="1">
+      <c r="TC54" s="1">
         <v>46303</v>
       </c>
-      <c r="TC54" t="s">
+      <c r="TD54" t="s">
         <v>1654</v>
       </c>
-      <c r="TD54" t="s">
+      <c r="TE54" t="s">
         <v>1655</v>
       </c>
-      <c r="TE54">
+      <c r="TF54">
         <v>39</v>
       </c>
-      <c r="TF54">
+      <c r="TG54">
         <v>31</v>
       </c>
-      <c r="TG54">
+      <c r="TH54">
         <v>2</v>
       </c>
-      <c r="TH54">
+      <c r="TI54">
         <v>4</v>
       </c>
-      <c r="TI54" t="s">
+      <c r="TJ54" t="s">
         <v>1656</v>
       </c>
-      <c r="TJ54">
-        <v>0</v>
-      </c>
       <c r="TK54">
         <v>0</v>
       </c>
       <c r="TL54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TM54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="TN54">
         <v>0</v>
       </c>
-      <c r="TO54" t="s">
+      <c r="TO54">
+        <v>0</v>
+      </c>
+      <c r="TP54" t="s">
         <v>1657</v>
       </c>
-      <c r="UG54" t="s">
+      <c r="UH54" t="s">
         <v>1658</v>
       </c>
-      <c r="ZK54" s="1"/>
-      <c r="ADN54" s="1"/>
-      <c r="ADV54" s="1"/>
-      <c r="ADZ54" s="1"/>
-      <c r="AEX54">
+      <c r="ZL54" s="1"/>
+      <c r="ADO54" s="1"/>
+      <c r="ADW54" s="1"/>
+      <c r="AEA54" s="1"/>
+      <c r="AEY54">
         <v>890222696</v>
       </c>
-      <c r="AEY54" t="s">
+      <c r="AEZ54" t="s">
         <v>1659</v>
       </c>
-      <c r="AEZ54" s="1">
+      <c r="AFA54" s="1">
         <v>46305.225034722222</v>
       </c>
-      <c r="AFB54" t="s">
+      <c r="AFC54" t="s">
         <v>734</v>
       </c>
-      <c r="AFD54" t="s">
+      <c r="AFE54" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE54" t="s">
+      <c r="AFF54" t="s">
         <v>1660</v>
       </c>
-      <c r="AFF54">
+      <c r="AFG54">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>46303</v>
       </c>
@@ -22451,100 +22506,100 @@
       <c r="I55" t="s">
         <v>1661</v>
       </c>
-      <c r="SC55" s="1"/>
-      <c r="SU55" t="s">
+      <c r="SD55" s="1"/>
+      <c r="SV55" t="s">
         <v>740</v>
       </c>
-      <c r="SV55">
-        <v>1</v>
-      </c>
       <c r="SW55">
-        <v>0</v>
-      </c>
-      <c r="SX55" t="s">
+        <v>1</v>
+      </c>
+      <c r="SX55">
+        <v>0</v>
+      </c>
+      <c r="SY55" t="s">
         <v>1662</v>
       </c>
-      <c r="SY55">
+      <c r="SZ55">
         <v>26</v>
       </c>
-      <c r="SZ55">
+      <c r="TA55">
         <v>19</v>
       </c>
-      <c r="TA55" t="s">
+      <c r="TB55" t="s">
         <v>1663</v>
       </c>
-      <c r="TB55" s="1">
+      <c r="TC55" s="1">
         <v>46303</v>
       </c>
-      <c r="TC55" t="s">
+      <c r="TD55" t="s">
         <v>1664</v>
       </c>
-      <c r="TD55" t="s">
+      <c r="TE55" t="s">
         <v>1665</v>
       </c>
-      <c r="TE55">
+      <c r="TF55">
         <v>30</v>
       </c>
-      <c r="TF55">
+      <c r="TG55">
         <v>25</v>
       </c>
-      <c r="TG55">
-        <v>1</v>
-      </c>
       <c r="TH55">
         <v>1</v>
       </c>
-      <c r="TI55" t="s">
+      <c r="TI55">
+        <v>1</v>
+      </c>
+      <c r="TJ55" t="s">
         <v>745</v>
       </c>
-      <c r="TJ55">
-        <v>0</v>
-      </c>
       <c r="TK55">
         <v>0</v>
       </c>
       <c r="TL55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="TM55">
         <v>1</v>
       </c>
       <c r="TN55">
-        <v>0</v>
-      </c>
-      <c r="TO55" t="s">
+        <v>1</v>
+      </c>
+      <c r="TO55">
+        <v>0</v>
+      </c>
+      <c r="TP55" t="s">
         <v>1666</v>
       </c>
-      <c r="UG55" t="s">
+      <c r="UH55" t="s">
         <v>1667</v>
       </c>
-      <c r="ZK55" s="1"/>
-      <c r="ADN55" s="1"/>
-      <c r="ADV55" s="1"/>
-      <c r="ADZ55" s="1"/>
-      <c r="AEX55">
+      <c r="ZL55" s="1"/>
+      <c r="ADO55" s="1"/>
+      <c r="ADW55" s="1"/>
+      <c r="AEA55" s="1"/>
+      <c r="AEY55">
         <v>890247399</v>
       </c>
-      <c r="AEY55" t="s">
+      <c r="AEZ55" t="s">
         <v>1668</v>
       </c>
-      <c r="AEZ55" s="1">
+      <c r="AFA55" s="1">
         <v>46305.244074074071</v>
       </c>
-      <c r="AFB55" t="s">
+      <c r="AFC55" t="s">
         <v>734</v>
       </c>
-      <c r="AFD55" t="s">
+      <c r="AFE55" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE55" t="s">
+      <c r="AFF55" t="s">
         <v>1669</v>
       </c>
-      <c r="AFF55">
+      <c r="AFG55">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:838" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:839" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>46303</v>
       </c>
@@ -22854,67 +22909,540 @@
       <c r="KO56">
         <v>1</v>
       </c>
-      <c r="KP56" t="s">
+      <c r="KP56">
+        <v>1</v>
+      </c>
+      <c r="KQ56" t="s">
         <v>1693</v>
       </c>
-      <c r="KQ56" t="s">
+      <c r="KR56" t="s">
         <v>1694</v>
       </c>
-      <c r="KR56" t="s">
+      <c r="KS56" t="s">
         <v>1695</v>
       </c>
-      <c r="KS56" t="s">
+      <c r="KT56" t="s">
         <v>1696</v>
       </c>
-      <c r="KT56" t="s">
+      <c r="KU56" t="s">
         <v>1697</v>
       </c>
-      <c r="NO56">
+      <c r="NP56">
         <v>251</v>
       </c>
-      <c r="NP56">
+      <c r="NQ56">
         <v>237</v>
       </c>
-      <c r="NR56">
+      <c r="NS56">
         <v>64</v>
       </c>
-      <c r="NS56">
+      <c r="NT56">
         <v>62</v>
       </c>
-      <c r="NU56">
+      <c r="NV56">
         <v>67</v>
       </c>
-      <c r="NV56">
+      <c r="NW56">
         <v>42</v>
       </c>
-      <c r="SC56" s="1"/>
-      <c r="UG56" t="s">
+      <c r="SD56" s="1"/>
+      <c r="UH56" t="s">
         <v>1698</v>
       </c>
-      <c r="ZK56" s="1"/>
-      <c r="ADN56" s="1"/>
-      <c r="ADV56" s="1"/>
-      <c r="ADZ56" s="1"/>
-      <c r="AEX56">
+      <c r="ZL56" s="1"/>
+      <c r="ADO56" s="1"/>
+      <c r="ADW56" s="1"/>
+      <c r="AEA56" s="1"/>
+      <c r="AEY56">
         <v>890950633</v>
       </c>
-      <c r="AEY56" t="s">
+      <c r="AEZ56" t="s">
         <v>1699</v>
       </c>
-      <c r="AEZ56" s="1">
+      <c r="AFA56" s="1">
         <v>46306.242256944453</v>
       </c>
-      <c r="AFB56" t="s">
+      <c r="AFC56" t="s">
         <v>734</v>
       </c>
-      <c r="AFD56" t="s">
+      <c r="AFE56" t="s">
         <v>1576</v>
       </c>
-      <c r="AFE56" t="s">
+      <c r="AFF56" t="s">
         <v>1700</v>
       </c>
-      <c r="AFF56">
+      <c r="AFG56">
         <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B57" t="s">
+        <v>951</v>
+      </c>
+      <c r="D57" t="s">
+        <v>589</v>
+      </c>
+      <c r="E57" t="s">
+        <v>752</v>
+      </c>
+      <c r="N57" t="s">
+        <v>1128</v>
+      </c>
+      <c r="EN57" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO57">
+        <v>380</v>
+      </c>
+      <c r="EP57">
+        <v>398</v>
+      </c>
+      <c r="EQ57" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER57" t="s">
+        <v>1702</v>
+      </c>
+      <c r="ES57">
+        <v>1</v>
+      </c>
+      <c r="ET57">
+        <v>0</v>
+      </c>
+      <c r="EU57">
+        <v>0</v>
+      </c>
+      <c r="EV57">
+        <v>1</v>
+      </c>
+      <c r="EW57">
+        <v>0</v>
+      </c>
+      <c r="EX57">
+        <v>0</v>
+      </c>
+      <c r="EZ57" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA57">
+        <v>30</v>
+      </c>
+      <c r="FB57" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC57">
+        <v>1</v>
+      </c>
+      <c r="FD57">
+        <v>1</v>
+      </c>
+      <c r="FE57">
+        <v>1</v>
+      </c>
+      <c r="FF57" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG57" t="s">
+        <v>1703</v>
+      </c>
+      <c r="FH57" t="s">
+        <v>711</v>
+      </c>
+      <c r="FI57">
+        <v>3</v>
+      </c>
+      <c r="FJ57" t="s">
+        <v>706</v>
+      </c>
+      <c r="FK57">
+        <v>0</v>
+      </c>
+      <c r="FL57">
+        <v>1</v>
+      </c>
+      <c r="NP57">
+        <v>254</v>
+      </c>
+      <c r="NQ57">
+        <v>163</v>
+      </c>
+      <c r="NS57">
+        <v>125</v>
+      </c>
+      <c r="NT57">
+        <v>143</v>
+      </c>
+      <c r="NV57">
+        <v>178</v>
+      </c>
+      <c r="NW57">
+        <v>160</v>
+      </c>
+      <c r="SD57" s="1"/>
+      <c r="UH57" t="s">
+        <v>1704</v>
+      </c>
+      <c r="ZL57" s="1"/>
+      <c r="ADO57" s="1"/>
+      <c r="ADW57" s="1"/>
+      <c r="AEA57" s="1"/>
+      <c r="AEY57">
+        <v>891698223</v>
+      </c>
+      <c r="AEZ57" t="s">
+        <v>1705</v>
+      </c>
+      <c r="AFA57" s="1">
+        <v>46307.476585648154</v>
+      </c>
+      <c r="AFC57" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE57" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF57" t="s">
+        <v>1707</v>
+      </c>
+      <c r="AFG57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B58" t="s">
+        <v>951</v>
+      </c>
+      <c r="D58" t="s">
+        <v>589</v>
+      </c>
+      <c r="E58" t="s">
+        <v>709</v>
+      </c>
+      <c r="N58" t="s">
+        <v>1128</v>
+      </c>
+      <c r="P58">
+        <v>8</v>
+      </c>
+      <c r="Q58">
+        <v>6</v>
+      </c>
+      <c r="R58" t="s">
+        <v>732</v>
+      </c>
+      <c r="S58">
+        <v>2</v>
+      </c>
+      <c r="T58">
+        <v>1</v>
+      </c>
+      <c r="U58">
+        <v>2</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58" t="s">
+        <v>711</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AG58" t="s">
+        <v>955</v>
+      </c>
+      <c r="AH58">
+        <v>0</v>
+      </c>
+      <c r="AI58">
+        <v>0</v>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>1</v>
+      </c>
+      <c r="AM58" t="s">
+        <v>722</v>
+      </c>
+      <c r="AN58">
+        <v>0</v>
+      </c>
+      <c r="AO58">
+        <v>1</v>
+      </c>
+      <c r="AP58">
+        <v>0</v>
+      </c>
+      <c r="AQ58" t="s">
+        <v>1709</v>
+      </c>
+      <c r="AR58" t="s">
+        <v>716</v>
+      </c>
+      <c r="AT58" t="s">
+        <v>955</v>
+      </c>
+      <c r="AU58">
+        <v>0</v>
+      </c>
+      <c r="AV58">
+        <v>0</v>
+      </c>
+      <c r="AW58">
+        <v>0</v>
+      </c>
+      <c r="AX58">
+        <v>0</v>
+      </c>
+      <c r="AY58">
+        <v>1</v>
+      </c>
+      <c r="AZ58" t="s">
+        <v>722</v>
+      </c>
+      <c r="BA58">
+        <v>0</v>
+      </c>
+      <c r="BB58">
+        <v>1</v>
+      </c>
+      <c r="BC58">
+        <v>0</v>
+      </c>
+      <c r="BD58" t="s">
+        <v>1710</v>
+      </c>
+      <c r="BE58" t="s">
+        <v>720</v>
+      </c>
+      <c r="BG58" t="s">
+        <v>808</v>
+      </c>
+      <c r="BH58">
+        <v>0</v>
+      </c>
+      <c r="BI58">
+        <v>1</v>
+      </c>
+      <c r="BJ58">
+        <v>0</v>
+      </c>
+      <c r="BK58">
+        <v>0</v>
+      </c>
+      <c r="BL58">
+        <v>0</v>
+      </c>
+      <c r="BM58" t="s">
+        <v>722</v>
+      </c>
+      <c r="BN58">
+        <v>0</v>
+      </c>
+      <c r="BO58">
+        <v>1</v>
+      </c>
+      <c r="BP58">
+        <v>0</v>
+      </c>
+      <c r="BQ58" t="s">
+        <v>1711</v>
+      </c>
+      <c r="BR58" t="s">
+        <v>716</v>
+      </c>
+      <c r="BT58" t="s">
+        <v>806</v>
+      </c>
+      <c r="BU58">
+        <v>0</v>
+      </c>
+      <c r="BV58">
+        <v>0</v>
+      </c>
+      <c r="BW58">
+        <v>0</v>
+      </c>
+      <c r="BX58">
+        <v>1</v>
+      </c>
+      <c r="BY58">
+        <v>0</v>
+      </c>
+      <c r="BZ58" t="s">
+        <v>714</v>
+      </c>
+      <c r="CA58">
+        <v>1</v>
+      </c>
+      <c r="CB58">
+        <v>0</v>
+      </c>
+      <c r="CC58">
+        <v>0</v>
+      </c>
+      <c r="CD58" t="s">
+        <v>1712</v>
+      </c>
+      <c r="CE58" t="s">
+        <v>720</v>
+      </c>
+      <c r="CG58" t="s">
+        <v>713</v>
+      </c>
+      <c r="CH58">
+        <v>0</v>
+      </c>
+      <c r="CI58">
+        <v>0</v>
+      </c>
+      <c r="CJ58">
+        <v>1</v>
+      </c>
+      <c r="CK58">
+        <v>0</v>
+      </c>
+      <c r="CL58">
+        <v>0</v>
+      </c>
+      <c r="CM58" t="s">
+        <v>718</v>
+      </c>
+      <c r="CN58">
+        <v>0</v>
+      </c>
+      <c r="CO58">
+        <v>1</v>
+      </c>
+      <c r="CP58">
+        <v>1</v>
+      </c>
+      <c r="CQ58" t="s">
+        <v>1713</v>
+      </c>
+      <c r="CR58" t="s">
+        <v>716</v>
+      </c>
+      <c r="CT58" t="s">
+        <v>713</v>
+      </c>
+      <c r="CU58">
+        <v>0</v>
+      </c>
+      <c r="CV58">
+        <v>0</v>
+      </c>
+      <c r="CW58">
+        <v>1</v>
+      </c>
+      <c r="CX58">
+        <v>0</v>
+      </c>
+      <c r="CY58">
+        <v>0</v>
+      </c>
+      <c r="CZ58" t="s">
+        <v>852</v>
+      </c>
+      <c r="DA58">
+        <v>0</v>
+      </c>
+      <c r="DB58">
+        <v>0</v>
+      </c>
+      <c r="DC58">
+        <v>1</v>
+      </c>
+      <c r="DD58" t="s">
+        <v>1714</v>
+      </c>
+      <c r="DE58" t="s">
+        <v>720</v>
+      </c>
+      <c r="DF58" t="s">
+        <v>1715</v>
+      </c>
+      <c r="DG58">
+        <v>0</v>
+      </c>
+      <c r="DH58">
+        <v>0</v>
+      </c>
+      <c r="DI58">
+        <v>1</v>
+      </c>
+      <c r="DJ58">
+        <v>0</v>
+      </c>
+      <c r="DK58">
+        <v>1</v>
+      </c>
+      <c r="DL58">
+        <v>0</v>
+      </c>
+      <c r="DM58">
+        <v>0</v>
+      </c>
+      <c r="DN58">
+        <v>0</v>
+      </c>
+      <c r="DO58">
+        <v>0</v>
+      </c>
+      <c r="DP58" t="s">
+        <v>732</v>
+      </c>
+      <c r="EI58">
+        <v>2</v>
+      </c>
+      <c r="EK58">
+        <v>5</v>
+      </c>
+      <c r="EM58">
+        <v>5</v>
+      </c>
+      <c r="SD58" s="1"/>
+      <c r="UH58" t="s">
+        <v>842</v>
+      </c>
+      <c r="ZL58" s="1"/>
+      <c r="ADO58" s="1"/>
+      <c r="ADW58" s="1"/>
+      <c r="AEA58" s="1"/>
+      <c r="AEY58">
+        <v>891714756</v>
+      </c>
+      <c r="AEZ58" t="s">
+        <v>1716</v>
+      </c>
+      <c r="AFA58" s="1">
+        <v>46307.488958333342</v>
+      </c>
+      <c r="AFC58" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE58" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF58" t="s">
+        <v>1717</v>
+      </c>
+      <c r="AFG58">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE9DD535-DABF-064F-9453-4D5836E63955}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1308D65-37B7-A146-A8F6-8F24F68B3497}"/>
   <bookViews>
     <workbookView xWindow="2420" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1308D65-37B7-A146-A8F6-8F24F68B3497}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBDC11F0-182E-B946-BEF9-F35D74F0E5B8}"/>
   <bookViews>
     <workbookView xWindow="2420" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3102" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4384" uniqueCount="2152">
   <si>
     <t>Date</t>
   </si>
@@ -5174,6 +5174,1308 @@
   </si>
   <si>
     <t>uuid:d802cd7c-ac85-48a9-a6a9-e3fe83a7d153</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Metu porridge supplementation demonstrated Fair food portions for all genders Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>Reading of story books, round game play,classroom session,dancing challenge</t>
+  </si>
+  <si>
+    <t>The materials were easy to beunderstood because sometimes the words they understand were translated to ngakarimojong</t>
+  </si>
+  <si>
+    <t>It makes them miss school or classes, it exposes them to early marriage,</t>
+  </si>
+  <si>
+    <t>They all report to school early to attend to classes, they finish work together.</t>
+  </si>
+  <si>
+    <t>That is the work for girls, we cook because some of them don't have girls at home</t>
+  </si>
+  <si>
+    <t>Help their sisters makes them feel loved at home and also they are able to report school early, they have the morale to do work</t>
+  </si>
+  <si>
+    <t>Because they will rape in the bush, she will miss school,</t>
+  </si>
+  <si>
+    <t>The children should get up early so that they do house chores together and finish early inorder to report to school .</t>
+  </si>
+  <si>
+    <t>The bus brings together with excitement</t>
+  </si>
+  <si>
+    <t>Sweep, fetch water, cook tea very early with our siblings</t>
+  </si>
+  <si>
+    <t>Together the bus brings us</t>
+  </si>
+  <si>
+    <t>Wake up early and do homework</t>
+  </si>
+  <si>
+    <t>The bus brings us together.</t>
+  </si>
+  <si>
+    <t>Children to Share work together at home with brothers and sisters</t>
+  </si>
+  <si>
+    <t>Finish work in the evening so that little can be done in the morning</t>
+  </si>
+  <si>
+    <t>Our parents should help us do part of the house chores.</t>
+  </si>
+  <si>
+    <t>The bus brings together and brings good colours</t>
+  </si>
+  <si>
+    <t>Some of the items are not available, lack of money to buy some of the items</t>
+  </si>
+  <si>
+    <t>The willingness to try the preparation of METU porridge and taking part</t>
+  </si>
+  <si>
+    <t>Practical METU preparation inorder knowledge  is well instilled in the participants</t>
+  </si>
+  <si>
+    <t>The school has committed themselves to establish a school immediately the rains start and protect children from community bad influence like early marriage</t>
+  </si>
+  <si>
+    <t>The teachers should now start school sessions and establish school gardens while teaching children nutrition messages so that children can be able to food values they can get when they certain food values, conduct practical/class sessions of how to prepare Nutritious meals</t>
+  </si>
+  <si>
+    <t>a33ac0b3-b004-47fa-8ab6-12bff4e8304b</t>
+  </si>
+  <si>
+    <t>uuid:a33ac0b3-b004-47fa-8ab6-12bff4e8304b</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Metu porridge supplementation demonstrated Structured dialogue on rebalancing chores Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>Through questions and answers, through the outdoor nutri games</t>
+  </si>
+  <si>
+    <t>Girls and boys should share home chores together</t>
+  </si>
+  <si>
+    <t>So that they can concentrate in class</t>
+  </si>
+  <si>
+    <t>It's creates unity among family members</t>
+  </si>
+  <si>
+    <t>So she could work hard in class</t>
+  </si>
+  <si>
+    <t>Girls should be treated with respect because they are the mothers of the nation</t>
+  </si>
+  <si>
+    <t>Sugar, tamarin</t>
+  </si>
+  <si>
+    <t>It is the bus that gathers people together</t>
+  </si>
+  <si>
+    <t>Milk, pounded boo, eggs</t>
+  </si>
+  <si>
+    <t>The bus keeps children in school together</t>
+  </si>
+  <si>
+    <t>Sour milk, lemon</t>
+  </si>
+  <si>
+    <t>The bus is emonument that brings people together</t>
+  </si>
+  <si>
+    <t>The bus keeps children together</t>
+  </si>
+  <si>
+    <t>We share chores so that to help girls go to school early</t>
+  </si>
+  <si>
+    <t>Most pupils needed practical lessons</t>
+  </si>
+  <si>
+    <t>Active participation from all the members, they were all committed to practicing it at home and school as well</t>
+  </si>
+  <si>
+    <t>Early mobilisations</t>
+  </si>
+  <si>
+    <t>The pupils committed to greatly doing and practicing work</t>
+  </si>
+  <si>
+    <t>The school needs to be informed one week earlier to enable future activities run smoothly</t>
+  </si>
+  <si>
+    <t>b9bf656b-a57f-4e16-95ec-4cf49fd926d6</t>
+  </si>
+  <si>
+    <t>uuid:b9bf656b-a57f-4e16-95ec-4cf49fd926d6</t>
+  </si>
+  <si>
+    <t>KOPOTH P/S</t>
+  </si>
+  <si>
+    <t>In front of the administration classes</t>
+  </si>
+  <si>
+    <t>No observation but the school was ready for the nurtri school bus campaign</t>
+  </si>
+  <si>
+    <t>8a988423-0cb3-4ff2-8f8e-69e808fc213d</t>
+  </si>
+  <si>
+    <t>vL8o9LXe3n2B9wux9mf2QY</t>
+  </si>
+  <si>
+    <t>uuid:8a988423-0cb3-4ff2-8f8e-69e808fc213d</t>
+  </si>
+  <si>
+    <t>Reading games, nutrition games</t>
+  </si>
+  <si>
+    <t>To avoid Early marriage among girls, to avoid dirtyness</t>
+  </si>
+  <si>
+    <t>So as to avoid kidnap, working hard</t>
+  </si>
+  <si>
+    <t>Avoid work load, making work easy</t>
+  </si>
+  <si>
+    <t>To avoid child abuse, to avoid rape on the way</t>
+  </si>
+  <si>
+    <t>Promotes girl education, avoid forced marriage</t>
+  </si>
+  <si>
+    <t>Sugar, tamarind</t>
+  </si>
+  <si>
+    <t>Meaning the bus makes us do work together</t>
+  </si>
+  <si>
+    <t>Must coperat together, divide chores within ourselves</t>
+  </si>
+  <si>
+    <t>Being together, sharing ideas</t>
+  </si>
+  <si>
+    <t>Odii, honey, salt</t>
+  </si>
+  <si>
+    <t>Bus is carrying us to our destination</t>
+  </si>
+  <si>
+    <t>Doing some other work in the evening to avoid work load in the morning</t>
+  </si>
+  <si>
+    <t>It means a group of people moving together or learning together</t>
+  </si>
+  <si>
+    <t>House chore sharing</t>
+  </si>
+  <si>
+    <t>Being cooperative In what ever we do</t>
+  </si>
+  <si>
+    <t>One of the barriers was heavy rain which could not allow the children to participate well in the nutrigame</t>
+  </si>
+  <si>
+    <t>Active participation by both learners and teachers</t>
+  </si>
+  <si>
+    <t>Early and timely preparation</t>
+  </si>
+  <si>
+    <t>We the teachers and pupils of kopoth primary school do commit to promote gender equality among our school and community and also learn how to grow nutritious food locally available at home</t>
+  </si>
+  <si>
+    <t>Timely engagement with the pupils to avoid the unavoidable natural accurances like rain</t>
+  </si>
+  <si>
+    <t>1432f560-9c26-4478-85d3-70ca2ff9e027</t>
+  </si>
+  <si>
+    <t>uuid:1432f560-9c26-4478-85d3-70ca2ff9e027</t>
+  </si>
+  <si>
+    <t>LOCHOM P/S</t>
+  </si>
+  <si>
+    <t>In front of the head teacher's office</t>
+  </si>
+  <si>
+    <t>Timely communication</t>
+  </si>
+  <si>
+    <t>a380c6a0-79cd-4d16-8f3d-c17144551393</t>
+  </si>
+  <si>
+    <t>uuid:a380c6a0-79cd-4d16-8f3d-c17144551393</t>
+  </si>
+  <si>
+    <t>The activity should be carried twice a week</t>
+  </si>
+  <si>
+    <t>a good balanced diet is proper for both boys and girls at home and at school</t>
+  </si>
+  <si>
+    <t>its for all children to be treated equally</t>
+  </si>
+  <si>
+    <t>both boys and girls should be given house chores samely</t>
+  </si>
+  <si>
+    <t>using improved cooking stove safes time and firewood since little firewood is used to cook much food</t>
+  </si>
+  <si>
+    <t>Both boys and girls should collect firewood since this promotes goodfriendship at home</t>
+  </si>
+  <si>
+    <t>Its good to involve both men and women food preparation and food planning</t>
+  </si>
+  <si>
+    <t>Cooking manual</t>
+  </si>
+  <si>
+    <t>e8f2d6e1-df3e-48c2-90d9-926d9054d983</t>
+  </si>
+  <si>
+    <t>uuid:e8f2d6e1-df3e-48c2-90d9-926d9054d983</t>
+  </si>
+  <si>
+    <t>They were able to explain how rebalancing house chores is good, they participated in the outdoor nutrigame</t>
+  </si>
+  <si>
+    <t>Promotes equal treatment for both boys and girls</t>
+  </si>
+  <si>
+    <t>To prevent girls from going different directions instead of going to school</t>
+  </si>
+  <si>
+    <t>Promotes cooperation, saves time for other work, promotes equality</t>
+  </si>
+  <si>
+    <t>Avoid child labor, avoids girl child mistreatment, makes work easy</t>
+  </si>
+  <si>
+    <t>Promotes equal education, promotes friendship and togetherness,prevents illiteracy among girls</t>
+  </si>
+  <si>
+    <t>Blue band, soya</t>
+  </si>
+  <si>
+    <t>Agroup of people moving together or learning together</t>
+  </si>
+  <si>
+    <t>Waking up very early to do work</t>
+  </si>
+  <si>
+    <t>Bus means nutritious food for people</t>
+  </si>
+  <si>
+    <t>Dividing work within boys and girls to make the morning easy and ready for work</t>
+  </si>
+  <si>
+    <t>Milk, honey, sugar</t>
+  </si>
+  <si>
+    <t>Bus means equal education</t>
+  </si>
+  <si>
+    <t>Must cooperate together, waking up early in the morning.</t>
+  </si>
+  <si>
+    <t>Doing work together for a common goal,</t>
+  </si>
+  <si>
+    <t>Rain destructed some of the activities</t>
+  </si>
+  <si>
+    <t>Pupils learnt alot about nutrition and it's importance, they also learnt more on gender compared to the perception in the community</t>
+  </si>
+  <si>
+    <t>Calling the school early so that they can prepare</t>
+  </si>
+  <si>
+    <t>Lochom primary school commits to embrace nutrition and gender equality</t>
+  </si>
+  <si>
+    <t>0ce6aaba-9a20-412a-9c7e-f6b4e0a0aa12</t>
+  </si>
+  <si>
+    <t>uuid:0ce6aaba-9a20-412a-9c7e-f6b4e0a0aa12</t>
+  </si>
+  <si>
+    <t>its very important to include both gender in cooking and food planing</t>
+  </si>
+  <si>
+    <t>This promotes children to be hardworking and always commited in tasks given</t>
+  </si>
+  <si>
+    <t>Balanced diet is good for all people at home</t>
+  </si>
+  <si>
+    <t>By making both gender colecting firewood,both gender are involved in an activity equally</t>
+  </si>
+  <si>
+    <t>its very important that all pupils do work together as it promotes good relationship and sharing</t>
+  </si>
+  <si>
+    <t>Elders should not be left in any activity like open cooking demo in the community</t>
+  </si>
+  <si>
+    <t>3d8dc0f4-c078-4344-8a81-1cdd2a7b98c9</t>
+  </si>
+  <si>
+    <t>uuid:3d8dc0f4-c078-4344-8a81-1cdd2a7b98c9</t>
+  </si>
+  <si>
+    <t>LOMUKURA P/S</t>
+  </si>
+  <si>
+    <t>Elobu Francis  and lopwapon emmanuel</t>
+  </si>
+  <si>
+    <t>Both in classroom and outside</t>
+  </si>
+  <si>
+    <t>23:39:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Greens ,peas and beans</t>
+  </si>
+  <si>
+    <t>Need of  real local crops to be used</t>
+  </si>
+  <si>
+    <t>1ba57179-03e3-4570-a0c7-ed406fee29fa</t>
+  </si>
+  <si>
+    <t>uuid:1ba57179-03e3-4570-a0c7-ed406fee29fa</t>
+  </si>
+  <si>
+    <t>KANAIR P/S</t>
+  </si>
+  <si>
+    <t>Obong lawerence and Akello korina okot</t>
+  </si>
+  <si>
+    <t>12:20:00.000+03:00</t>
+  </si>
+  <si>
+    <t>14:33:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Need your use real produces from the local community</t>
+  </si>
+  <si>
+    <t>Involving headteachers in the orientation</t>
+  </si>
+  <si>
+    <t>747c1913-8119-4dd2-9a5c-1226cf980f3a</t>
+  </si>
+  <si>
+    <t>uuid:747c1913-8119-4dd2-9a5c-1226cf980f3a</t>
+  </si>
+  <si>
+    <t>Monday Wednesday</t>
+  </si>
+  <si>
+    <t>near the headteachers office</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>0a279240-b825-4696-9920-dbd3f1f074dd</t>
+  </si>
+  <si>
+    <t>uuid:0a279240-b825-4696-9920-dbd3f1f074dd</t>
+  </si>
+  <si>
+    <t>no knowledge</t>
+  </si>
+  <si>
+    <t>Reading and drama games</t>
+  </si>
+  <si>
+    <t>easy to understand</t>
+  </si>
+  <si>
+    <t>good to support each other</t>
+  </si>
+  <si>
+    <t>boys play football.</t>
+  </si>
+  <si>
+    <t>one boy agreed to share.</t>
+  </si>
+  <si>
+    <t>they ageed they need help the girls .</t>
+  </si>
+  <si>
+    <t>grassing cows is not for girls.</t>
+  </si>
+  <si>
+    <t>they said,they need to wake up early.</t>
+  </si>
+  <si>
+    <t>;school nutrition bus</t>
+  </si>
+  <si>
+    <t>every one is suposed to work</t>
+  </si>
+  <si>
+    <t>every child must go to school early</t>
+  </si>
+  <si>
+    <t>good for all children</t>
+  </si>
+  <si>
+    <t>Dont know which work</t>
+  </si>
+  <si>
+    <t>the school bus</t>
+  </si>
+  <si>
+    <t>not all work is good for children</t>
+  </si>
+  <si>
+    <t>children were happy to learn</t>
+  </si>
+  <si>
+    <t>follow</t>
+  </si>
+  <si>
+    <t>thank you to WFP for supporting our school</t>
+  </si>
+  <si>
+    <t>non</t>
+  </si>
+  <si>
+    <t>b71baa89-0617-496a-873f-e56f0f5916d9</t>
+  </si>
+  <si>
+    <t>uuid:b71baa89-0617-496a-873f-e56f0f5916d9</t>
+  </si>
+  <si>
+    <t>LOPEEI P/S</t>
+  </si>
+  <si>
+    <t>infront of office</t>
+  </si>
+  <si>
+    <t>3797cb6a-acaf-48f4-a5d3-7c50d8b2cbda</t>
+  </si>
+  <si>
+    <t>uuid:3797cb6a-acaf-48f4-a5d3-7c50d8b2cbda</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Metu porridge supplementation demonstrated Structured dialogue on rebalancing chores Fair food portions for all genders Climate-smart cooking methods explained Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>climate smart cooking methods</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>i agree to support other sisters and brothers</t>
+  </si>
+  <si>
+    <t>good to eat equal meal</t>
+  </si>
+  <si>
+    <t>boys drop graze animals</t>
+  </si>
+  <si>
+    <t>good for boys to help to fethc wateer to make work easy</t>
+  </si>
+  <si>
+    <t>not good work for girls</t>
+  </si>
+  <si>
+    <t>hurry to keep time</t>
+  </si>
+  <si>
+    <t>all boys and girls work</t>
+  </si>
+  <si>
+    <t>nutri school</t>
+  </si>
+  <si>
+    <t>good to support children to go to school</t>
+  </si>
+  <si>
+    <t>one person helps at home</t>
+  </si>
+  <si>
+    <t>i help at home to make work easy</t>
+  </si>
+  <si>
+    <t>Nutri school</t>
+  </si>
+  <si>
+    <t>girls and boys are equal</t>
+  </si>
+  <si>
+    <t>Taste preference barriers</t>
+  </si>
+  <si>
+    <t>ingridients may not be available</t>
+  </si>
+  <si>
+    <t>learners enjoyed the quiz and answer sessions, used  poems</t>
+  </si>
+  <si>
+    <t>we should engage learners of different classes per session.</t>
+  </si>
+  <si>
+    <t>I encourage children to practice what they learn during the nutrition club session even at home</t>
+  </si>
+  <si>
+    <t>food demos should also be done in schools with the teachers and support staff</t>
+  </si>
+  <si>
+    <t>e80927c7-40d2-41f3-b5d6-597344253ac0</t>
+  </si>
+  <si>
+    <t>uuid:e80927c7-40d2-41f3-b5d6-597344253ac0</t>
+  </si>
+  <si>
+    <t>priscilla</t>
+  </si>
+  <si>
+    <t>Community demonstration</t>
+  </si>
+  <si>
+    <t>Lotede village</t>
+  </si>
+  <si>
+    <t>VHT</t>
+  </si>
+  <si>
+    <t>Kokoi Catherine and Lodungokori John Bosco</t>
+  </si>
+  <si>
+    <t>UNAC AFI</t>
+  </si>
+  <si>
+    <t>Co-facilitating clean cooking/gender dialogue Mentoring local VHTs/Elders</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Practiced and cooked hands-on</t>
+  </si>
+  <si>
+    <t>how many tine can a person eat metu porriage in aday, How is the porriage mixed</t>
+  </si>
+  <si>
+    <t>Adopted fuel-saving stoves/pots</t>
+  </si>
+  <si>
+    <t>Yes, strictly compliant with obtainable seasonal foods</t>
+  </si>
+  <si>
+    <t>Improved cookstove consuming less firewood</t>
+  </si>
+  <si>
+    <t>Food items missing in the local garden or market</t>
+  </si>
+  <si>
+    <t>Serve fair and equal food portions to boys and girls</t>
+  </si>
+  <si>
+    <t>Will try it</t>
+  </si>
+  <si>
+    <t>I will try to get porriage ingridients</t>
+  </si>
+  <si>
+    <t>lack of money</t>
+  </si>
+  <si>
+    <t>Supplement Metu porridge with local wild greens</t>
+  </si>
+  <si>
+    <t>Needs VHT guidance</t>
+  </si>
+  <si>
+    <t>no money to buy</t>
+  </si>
+  <si>
+    <t>i will try to make</t>
+  </si>
+  <si>
+    <t>Sat passively and observed without speaking</t>
+  </si>
+  <si>
+    <t>a man</t>
+  </si>
+  <si>
+    <t>if food is enough</t>
+  </si>
+  <si>
+    <t>we shall try to cook metu porriage in our homes</t>
+  </si>
+  <si>
+    <t>how to get the</t>
+  </si>
+  <si>
+    <t>Need more men to participate in demonstration</t>
+  </si>
+  <si>
+    <t>72d1add6-c3e5-434c-be4e-662b0b3219f2</t>
+  </si>
+  <si>
+    <t>uuid:72d1add6-c3e5-434c-be4e-662b0b3219f2</t>
+  </si>
+  <si>
+    <t>Lepeei</t>
+  </si>
+  <si>
+    <t>Longok Jacinta and lobere william</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>difficulty to get gas cylinder in the villages</t>
+  </si>
+  <si>
+    <t>the local food can be found to make porriage</t>
+  </si>
+  <si>
+    <t>Proper fuelwood pre-drying &amp; flame/airflow management</t>
+  </si>
+  <si>
+    <t>Nothing is difficult</t>
+  </si>
+  <si>
+    <t>Practice fuel-saving cooking methods</t>
+  </si>
+  <si>
+    <t>If i can afford</t>
+  </si>
+  <si>
+    <t>get local ingridints for porriage</t>
+  </si>
+  <si>
+    <t>Scarcity of cooking water</t>
+  </si>
+  <si>
+    <t>Rebalance morning chores</t>
+  </si>
+  <si>
+    <t>i will share roles at home</t>
+  </si>
+  <si>
+    <t>Debated fair food portions</t>
+  </si>
+  <si>
+    <t>children first</t>
+  </si>
+  <si>
+    <t>increase more food portions</t>
+  </si>
+  <si>
+    <t>to try out metu porriage</t>
+  </si>
+  <si>
+    <t>VHTs</t>
+  </si>
+  <si>
+    <t>how to get clean energy for cooking yet they are expensive</t>
+  </si>
+  <si>
+    <t>b4cf4fe8-1c9d-471e-af98-954475963cc6</t>
+  </si>
+  <si>
+    <t>uuid:b4cf4fe8-1c9d-471e-af98-954475963cc6</t>
+  </si>
+  <si>
+    <t>LORENGECHORA P/S</t>
+  </si>
+  <si>
+    <t>Lolet village</t>
+  </si>
+  <si>
+    <t>Vicky Iriama</t>
+  </si>
+  <si>
+    <t>Local Council</t>
+  </si>
+  <si>
+    <t>Nutrition and how to promote school feeding support from WFP and gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other </t>
+  </si>
+  <si>
+    <t>Used group discussion on available food to support feeding of children</t>
+  </si>
+  <si>
+    <t>Needs further VHT guidance</t>
+  </si>
+  <si>
+    <t>practice what they have lerant</t>
+  </si>
+  <si>
+    <t>demonstartion</t>
+  </si>
+  <si>
+    <t>share food equally among the children</t>
+  </si>
+  <si>
+    <t>children</t>
+  </si>
+  <si>
+    <t>we commit to feed children equally</t>
+  </si>
+  <si>
+    <t>household chores</t>
+  </si>
+  <si>
+    <t>1f422127-e919-4cc0-b9e8-171bd926e084</t>
+  </si>
+  <si>
+    <t>uuid:1f422127-e919-4cc0-b9e8-171bd926e084</t>
+  </si>
+  <si>
+    <t>Infront of the administration block, and classes which are at the center of the school</t>
+  </si>
+  <si>
+    <t>The largest population of learners are from ECD-P5. This lower and middle primary was signified by many leaners unlike upper primary. The class is active and all the tollfree and other materials were displayed at the right place</t>
+  </si>
+  <si>
+    <t>a7c9db24-8e20-425e-8c79-84bcfce64dfb</t>
+  </si>
+  <si>
+    <t>uuid:a7c9db24-8e20-425e-8c79-84bcfce64dfb</t>
+  </si>
+  <si>
+    <t>AFI coordinator</t>
+  </si>
+  <si>
+    <t>Handled story books to read willingly, played round game with great excitment</t>
+  </si>
+  <si>
+    <t>Most of the materials were locally available and they were attentive listening</t>
+  </si>
+  <si>
+    <t>Its not showing love to our sister, she will delay to go to school, she will be tired and can not concentrate in class</t>
+  </si>
+  <si>
+    <t>Walk together to school, attend lessons together, promotes love in the family</t>
+  </si>
+  <si>
+    <t>Simplify work, respect for one another, to give company to the other to avoid girls from being harrased by strangers</t>
+  </si>
+  <si>
+    <t>To show love to sister, promote unity at home, simplifies work</t>
+  </si>
+  <si>
+    <t>Its not for girls to graze animals, it is not good, kills the dreams of the girl</t>
+  </si>
+  <si>
+    <t>Both boys and girls should be treated equally</t>
+  </si>
+  <si>
+    <t>Bus unites as all</t>
+  </si>
+  <si>
+    <t>The bus that brings as together</t>
+  </si>
+  <si>
+    <t>Unity must be promoted among girls at home</t>
+  </si>
+  <si>
+    <t>The bus that unites poeple together</t>
+  </si>
+  <si>
+    <t>To avoid laziness and to speed the work give at home</t>
+  </si>
+  <si>
+    <t>The bus that joints us together</t>
+  </si>
+  <si>
+    <t>Both gilrs and boys must be at school equally at the same time</t>
+  </si>
+  <si>
+    <t>The bus thatconnects as together</t>
+  </si>
+  <si>
+    <t>Both girls and boys have same rights like education</t>
+  </si>
+  <si>
+    <t>Taste preference barriers Limited access to the cooking materials</t>
+  </si>
+  <si>
+    <t>The too much rain that rained and delayed activities</t>
+  </si>
+  <si>
+    <t>Large number of leaners, teacher attendence and coorparation</t>
+  </si>
+  <si>
+    <t>Enough time for all activities</t>
+  </si>
+  <si>
+    <t>I the deputy headteacher Napiananya orimary school pledge to support Nutrition club in the school and continue monitaring their activities</t>
+  </si>
+  <si>
+    <t>The rain delayed the activities, if it could be planned during adry season.</t>
+  </si>
+  <si>
+    <t>5bde1d54-8ba9-4337-8299-2547d607dde9</t>
+  </si>
+  <si>
+    <t>uuid:5bde1d54-8ba9-4337-8299-2547d607dde9</t>
+  </si>
+  <si>
+    <t>Session two of the week</t>
+  </si>
+  <si>
+    <t>23:00:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing Gender Chore Rebalancing: Boys sharing morning water/firewood chores Peer Attendance Tracing: Checking and following up chronically absent classmates</t>
+  </si>
+  <si>
+    <t>Struggled with barriers</t>
+  </si>
+  <si>
+    <t>Eating balanced is healthy for our bodies for proper learning at school, sharing work at homes saves time and makes us report to school early</t>
+  </si>
+  <si>
+    <t>Club Pupil Leader</t>
+  </si>
+  <si>
+    <t>Advised the school patron to continue engaging children in this activity and give them meal calenders on Time</t>
+  </si>
+  <si>
+    <t>fadb3cda-433a-4408-a084-9f961072144d</t>
+  </si>
+  <si>
+    <t>uuid:fadb3cda-433a-4408-a084-9f961072144d</t>
+  </si>
+  <si>
+    <t>16:30:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Children were given meal calenders to go and mark during the independence day holiday to gather data of balanced diet at home ,they were also advised to tell there fellow siblings who are at home to report to school on Monday,they were also advised to go and share domestic work at home because there is no specific work for any gender</t>
+  </si>
+  <si>
+    <t>Teacher Patron</t>
+  </si>
+  <si>
+    <t>Advised the teachers that they should give even reading books for children to learn from those stories</t>
+  </si>
+  <si>
+    <t>cb9c6c05-bf87-438e-a5af-98da346f56f8</t>
+  </si>
+  <si>
+    <t>uuid:cb9c6c05-bf87-438e-a5af-98da346f56f8</t>
+  </si>
+  <si>
+    <t>16:00:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Watering kitchen gardens to enrich balanced diet, work sharing at both school and home ,no early marriage by young girls, girls report to school despite of any barriers</t>
+  </si>
+  <si>
+    <t>Kitchen gardens or demonstration gardens be opened in most schools since most have water for watering</t>
+  </si>
+  <si>
+    <t>6009c291-98d2-43eb-b322-8f4980727208</t>
+  </si>
+  <si>
+    <t>uuid:6009c291-98d2-43eb-b322-8f4980727208</t>
+  </si>
+  <si>
+    <t>13:00:00.000+03:00</t>
+  </si>
+  <si>
+    <t>During school meals on the day to go for independence day holiday, children were advised to eat balanced diet at home during the holiday and go and mark the meal calenders and return to the teachers,they were also advised to respect there parents,share work at home and also advise the ones who have not reported to school to come on Monday because WFP has enough food to feed them at school,they were also told to call toll free for any emergency and lastly they were told to water kitchen gardens at school before going home and of wish they did in the evening</t>
+  </si>
+  <si>
+    <t>Children who sleep at school mostly help to water kitchen gardens at school since home coming learners leave school at 5 pm</t>
+  </si>
+  <si>
+    <t>9a452121-ff7f-4ee1-89ab-25e93aab6529</t>
+  </si>
+  <si>
+    <t>uuid:9a452121-ff7f-4ee1-89ab-25e93aab6529</t>
+  </si>
+  <si>
+    <t>08:00:00.000+03:00</t>
+  </si>
+  <si>
+    <t>08:15:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat) Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing Gender Chore Rebalancing: Boys sharing morning water/firewood chores</t>
+  </si>
+  <si>
+    <t>Club members were talking on different food values and there importance during morning assembly,they also had a speech on gender and how best we can achieve the goals in life</t>
+  </si>
+  <si>
+    <t>More talking compound post need to be put up</t>
+  </si>
+  <si>
+    <t>3bacfc22-7b9c-4bc9-9dee-7df49e02ffe4</t>
+  </si>
+  <si>
+    <t>uuid:3bacfc22-7b9c-4bc9-9dee-7df49e02ffe4</t>
+  </si>
+  <si>
+    <t>Kangole North cell karenga town council</t>
+  </si>
+  <si>
+    <t>Cordinator</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>They said that most of them know this because they were taught during eyok kiyan program and AFI as well</t>
+  </si>
+  <si>
+    <t>Continued traditional 3-stone fire</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Sorghum posho</t>
+  </si>
+  <si>
+    <t>Traditional 3-stone fire used (Non-compliant)</t>
+  </si>
+  <si>
+    <t>She said the season did not favor the harvest this year so needs support from WFP</t>
+  </si>
+  <si>
+    <t>He is seeking support from WFP during this hardship of too much sunshine but thanks for the take home ratio which was given</t>
+  </si>
+  <si>
+    <t>He says most of them believe some works are for women alone</t>
+  </si>
+  <si>
+    <t>Senior women</t>
+  </si>
+  <si>
+    <t>Cost  of scholastic materials</t>
+  </si>
+  <si>
+    <t>Actively debated chore burdens</t>
+  </si>
+  <si>
+    <t>Children</t>
+  </si>
+  <si>
+    <t>Because they need more attention than us mature people because we understand</t>
+  </si>
+  <si>
+    <t>They said the tool free is only for children at school so they didn't know it's only met for them</t>
+  </si>
+  <si>
+    <t>One community member said it's way we have lived that has demonstrated this chores sharing at home</t>
+  </si>
+  <si>
+    <t>Care givers watching hands and utensils before starting to cook</t>
+  </si>
+  <si>
+    <t>The community was excited because of the discussion because it became like debate between women and men more on gender issues</t>
+  </si>
+  <si>
+    <t>adb3af8a-1a8b-4feb-bd49-7b104f00c5c8</t>
+  </si>
+  <si>
+    <t>uuid:adb3af8a-1a8b-4feb-bd49-7b104f00c5c8</t>
+  </si>
+  <si>
+    <t>Church of uganda cell</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>They said they have most of this materials of porridge at home</t>
+  </si>
+  <si>
+    <t>Orange-fleshed sweet potato (OFSP) Iron-rich beans</t>
+  </si>
+  <si>
+    <t>Improved cookstove consuming less firewood Proper fuelwood pre-drying &amp; flame/airflow management Traditional 3-stone fire used (Non-compliant)</t>
+  </si>
+  <si>
+    <t>Complaining of the sunshine which destroyed crops this year</t>
+  </si>
+  <si>
+    <t>Needs support by VHT on how to make energy saving stoves</t>
+  </si>
+  <si>
+    <t>Says sharing work at home brings love</t>
+  </si>
+  <si>
+    <t>Senior women VHTs Lead Mothers present</t>
+  </si>
+  <si>
+    <t>Cost  of scholastic materials Menstrual hygiene management</t>
+  </si>
+  <si>
+    <t>One man said in case he is in rash to look for more food for the family he has to be served first</t>
+  </si>
+  <si>
+    <t>They said they only hear it on radio</t>
+  </si>
+  <si>
+    <t>Men said women assume that men can't eat in the morning they only to drink local kwete</t>
+  </si>
+  <si>
+    <t>Women serving porridge cooked to the community</t>
+  </si>
+  <si>
+    <t>They request demonstration of other foods not only METU 1</t>
+  </si>
+  <si>
+    <t>6c29829f-0ca1-478c-95f0-47b828cc51c8</t>
+  </si>
+  <si>
+    <t>uuid:6c29829f-0ca1-478c-95f0-47b828cc51c8</t>
+  </si>
+  <si>
+    <t>Kumukoi  central cell</t>
+  </si>
+  <si>
+    <t>Akut Josephine</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>The community asked why should we not also demonstrate other foods apart from METU 1 porridge alone</t>
+  </si>
+  <si>
+    <t>Sorghum four,ground nut pasta,suger, cooking oil,</t>
+  </si>
+  <si>
+    <t>Proper fuelwood pre-drying &amp; flame/airflow management Retained heat cooking and pot covering to conserve fuel Traditional 3-stone fire used (Non-compliant)</t>
+  </si>
+  <si>
+    <t>He said the standard of living is becoming to costly now days</t>
+  </si>
+  <si>
+    <t>Sharing work saves time for other things</t>
+  </si>
+  <si>
+    <t>Family or elder disagreement</t>
+  </si>
+  <si>
+    <t>She over drinking alcohol cause</t>
+  </si>
+  <si>
+    <t>Cost  of scholastic materials Menstrual hygiene management Other</t>
+  </si>
+  <si>
+    <t>Gender equality</t>
+  </si>
+  <si>
+    <t>One man said at least someone who is looking for food to eat first because without him the younger ones will not it</t>
+  </si>
+  <si>
+    <t>Most have not been knowing the importance of it</t>
+  </si>
+  <si>
+    <t>VHT and LC 1</t>
+  </si>
+  <si>
+    <t>Promoting gender and clean hand washing practices</t>
+  </si>
+  <si>
+    <t>Continues community dialogues needed for the community for more knowledge</t>
+  </si>
+  <si>
+    <t>93431393-6454-4639-b014-174ffc8d3e27</t>
+  </si>
+  <si>
+    <t>uuid:93431393-6454-4639-b014-174ffc8d3e27</t>
+  </si>
+  <si>
+    <t>Kamukoi North</t>
+  </si>
+  <si>
+    <t>Nayang Agnes logwee</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>When they are the porridge the appreciated that it was too nice and opted to go and try</t>
+  </si>
+  <si>
+    <t>Sorghum, ground nuts etc</t>
+  </si>
+  <si>
+    <t>Improved cookstove consuming less firewood Proper fuelwood pre-drying &amp; flame/airflow management</t>
+  </si>
+  <si>
+    <t>She says the season did not favor this year since they depend on farming</t>
+  </si>
+  <si>
+    <t>Maybe WFP should continue giving take home ratio for children</t>
+  </si>
+  <si>
+    <t>VHT help in making energy saving stoves</t>
+  </si>
+  <si>
+    <t>Senior women VHTs</t>
+  </si>
+  <si>
+    <t>Cost  of scholastic materials Other</t>
+  </si>
+  <si>
+    <t>Gender and good feeding practices</t>
+  </si>
+  <si>
+    <t>Parents rashing under emergency</t>
+  </si>
+  <si>
+    <t>They will call toll free in case of anything since they have learnt it</t>
+  </si>
+  <si>
+    <t>VHTs and LC 1</t>
+  </si>
+  <si>
+    <t>Proper mobilization of children to school more so girls</t>
+  </si>
+  <si>
+    <t>Continues community dialogues needed</t>
+  </si>
+  <si>
+    <t>af2de443-89d7-4fdb-b450-b392ba3dfe17</t>
+  </si>
+  <si>
+    <t>uuid:af2de443-89d7-4fdb-b450-b392ba3dfe17</t>
+  </si>
+  <si>
+    <t>New karenga cell</t>
+  </si>
+  <si>
+    <t>Nagwee lilly</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Most of them promised to prepare it at home since they have local materials for making</t>
+  </si>
+  <si>
+    <t>Maize flour, sorghum flour</t>
+  </si>
+  <si>
+    <t>Improved cookstove consuming less firewood Proper fuelwood pre-drying &amp; flame/airflow management Retained heat cooking and pot covering to conserve fuel Traditional 3-stone fire used (Non-compliant)</t>
+  </si>
+  <si>
+    <t>The season did not work out well this year</t>
+  </si>
+  <si>
+    <t>Water source far only deepen on public pipe taps whose water is not constant</t>
+  </si>
+  <si>
+    <t>Now since the there was no harvest proper usage of food is needed</t>
+  </si>
+  <si>
+    <t>Senior men Senior women VHTs Lead Mothers present</t>
+  </si>
+  <si>
+    <t>Gender equality and good feeding practices</t>
+  </si>
+  <si>
+    <t>If most of them are grown up</t>
+  </si>
+  <si>
+    <t>They did not know about it so now they know they will call in case of any problems</t>
+  </si>
+  <si>
+    <t>One man raised the hand said stop over drinking alcohol</t>
+  </si>
+  <si>
+    <t>The community appreciates this contractive discussion</t>
+  </si>
+  <si>
+    <t>1fc62f05-c046-4faf-8749-2fab1f0eeed3</t>
+  </si>
+  <si>
+    <t>uuid:1fc62f05-c046-4faf-8749-2fab1f0eeed3</t>
+  </si>
+  <si>
+    <t>Loyoro South</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>The community members promised to continue doing it</t>
+  </si>
+  <si>
+    <t>Sorghum flour, ground nut paste , cooking oil, sugar</t>
+  </si>
+  <si>
+    <t>Improved cookstove consuming less firewood Retained heat cooking and pot covering to conserve fuel</t>
+  </si>
+  <si>
+    <t>VHT trained how best to use energy saving stoves</t>
+  </si>
+  <si>
+    <t>Scarcity of firewood</t>
+  </si>
+  <si>
+    <t>She says she will make energy saving stoves</t>
+  </si>
+  <si>
+    <t>Heavy morning chores</t>
+  </si>
+  <si>
+    <t>She will advise her husband to share work at home with her</t>
+  </si>
+  <si>
+    <t>Senior men Senior women</t>
+  </si>
+  <si>
+    <t>Gender equality and good feeding practices at home</t>
+  </si>
+  <si>
+    <t>When someone is sick</t>
+  </si>
+  <si>
+    <t>Now they know it so they shall call</t>
+  </si>
+  <si>
+    <t>One man said why is it that women are favored in all activities</t>
+  </si>
+  <si>
+    <t>1a772879-5100-4112-8ec5-9605c7ae3ce0</t>
+  </si>
+  <si>
+    <t>uuid:1a772879-5100-4112-8ec5-9605c7ae3ce0</t>
   </si>
 </sst>
 </file>
@@ -5255,8 +6557,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG58" totalsRowShown="0">
-  <autoFilter ref="A1:AFG58" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG88" totalsRowShown="0">
+  <autoFilter ref="A1:AFG88" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -6389,14 +7691,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFG58"/>
+  <dimension ref="A1:AFG88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="5" max="5" width="27.5" customWidth="1"/>
     <col min="6" max="6" width="43" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
     <col min="8" max="8" width="85.6640625" customWidth="1"/>
@@ -23445,6 +24747,6915 @@
         <v>57</v>
       </c>
     </row>
+    <row r="59" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B59" t="s">
+        <v>706</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D59" t="s">
+        <v>590</v>
+      </c>
+      <c r="E59" t="s">
+        <v>752</v>
+      </c>
+      <c r="L59" t="s">
+        <v>1614</v>
+      </c>
+      <c r="EN59" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT59">
+        <v>490</v>
+      </c>
+      <c r="FU59">
+        <v>355</v>
+      </c>
+      <c r="FV59">
+        <v>1</v>
+      </c>
+      <c r="FW59">
+        <v>0</v>
+      </c>
+      <c r="FY59">
+        <v>315</v>
+      </c>
+      <c r="FZ59">
+        <v>200</v>
+      </c>
+      <c r="GA59">
+        <v>0</v>
+      </c>
+      <c r="GB59">
+        <v>0</v>
+      </c>
+      <c r="GD59">
+        <v>309</v>
+      </c>
+      <c r="GE59">
+        <v>180</v>
+      </c>
+      <c r="GF59">
+        <v>0</v>
+      </c>
+      <c r="GG59">
+        <v>0</v>
+      </c>
+      <c r="GI59">
+        <v>6</v>
+      </c>
+      <c r="GJ59">
+        <v>0</v>
+      </c>
+      <c r="GK59">
+        <v>0</v>
+      </c>
+      <c r="GL59">
+        <v>0</v>
+      </c>
+      <c r="GN59">
+        <v>5</v>
+      </c>
+      <c r="GO59">
+        <v>15</v>
+      </c>
+      <c r="GP59">
+        <v>0</v>
+      </c>
+      <c r="GQ59">
+        <v>0</v>
+      </c>
+      <c r="GR59" t="s">
+        <v>1718</v>
+      </c>
+      <c r="GS59">
+        <v>1</v>
+      </c>
+      <c r="GT59">
+        <v>0</v>
+      </c>
+      <c r="GU59">
+        <v>1</v>
+      </c>
+      <c r="GV59">
+        <v>0</v>
+      </c>
+      <c r="GW59">
+        <v>1</v>
+      </c>
+      <c r="GX59">
+        <v>0</v>
+      </c>
+      <c r="GY59">
+        <v>1</v>
+      </c>
+      <c r="GZ59" t="s">
+        <v>1349</v>
+      </c>
+      <c r="HA59">
+        <v>1</v>
+      </c>
+      <c r="HB59">
+        <v>1</v>
+      </c>
+      <c r="HC59">
+        <v>1</v>
+      </c>
+      <c r="HD59">
+        <v>1</v>
+      </c>
+      <c r="HE59">
+        <v>0</v>
+      </c>
+      <c r="HG59" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH59" t="s">
+        <v>1719</v>
+      </c>
+      <c r="HI59" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ59" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL59" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM59" t="s">
+        <v>1720</v>
+      </c>
+      <c r="HT59" t="s">
+        <v>765</v>
+      </c>
+      <c r="HU59">
+        <v>25</v>
+      </c>
+      <c r="HV59" t="s">
+        <v>1721</v>
+      </c>
+      <c r="HX59" t="s">
+        <v>765</v>
+      </c>
+      <c r="HY59">
+        <v>35</v>
+      </c>
+      <c r="HZ59" t="s">
+        <v>1722</v>
+      </c>
+      <c r="IB59" t="s">
+        <v>833</v>
+      </c>
+      <c r="IC59">
+        <v>15</v>
+      </c>
+      <c r="ID59" t="s">
+        <v>1723</v>
+      </c>
+      <c r="IF59" t="s">
+        <v>766</v>
+      </c>
+      <c r="IG59">
+        <v>25</v>
+      </c>
+      <c r="IH59" t="s">
+        <v>1724</v>
+      </c>
+      <c r="IJ59" t="s">
+        <v>765</v>
+      </c>
+      <c r="IK59">
+        <v>45</v>
+      </c>
+      <c r="IL59" t="s">
+        <v>1725</v>
+      </c>
+      <c r="IV59" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW59" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX59" t="s">
+        <v>1726</v>
+      </c>
+      <c r="IY59" t="s">
+        <v>839</v>
+      </c>
+      <c r="IZ59" t="s">
+        <v>1727</v>
+      </c>
+      <c r="JA59" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC59" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD59" t="s">
+        <v>879</v>
+      </c>
+      <c r="JE59" t="s">
+        <v>1728</v>
+      </c>
+      <c r="JF59" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG59" t="s">
+        <v>1729</v>
+      </c>
+      <c r="JH59" t="s">
+        <v>716</v>
+      </c>
+      <c r="JJ59" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK59" t="s">
+        <v>879</v>
+      </c>
+      <c r="JL59" t="s">
+        <v>1730</v>
+      </c>
+      <c r="JM59" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN59" t="s">
+        <v>1731</v>
+      </c>
+      <c r="JO59" t="s">
+        <v>720</v>
+      </c>
+      <c r="JQ59" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR59" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS59" t="s">
+        <v>1732</v>
+      </c>
+      <c r="JT59" t="s">
+        <v>839</v>
+      </c>
+      <c r="JU59" t="s">
+        <v>1729</v>
+      </c>
+      <c r="JV59" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX59" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY59" t="s">
+        <v>879</v>
+      </c>
+      <c r="JZ59" t="s">
+        <v>1733</v>
+      </c>
+      <c r="KA59" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB59" t="s">
+        <v>1731</v>
+      </c>
+      <c r="KC59" t="s">
+        <v>720</v>
+      </c>
+      <c r="KE59" t="s">
+        <v>835</v>
+      </c>
+      <c r="KF59" t="s">
+        <v>769</v>
+      </c>
+      <c r="KG59" t="s">
+        <v>1734</v>
+      </c>
+      <c r="KH59" t="s">
+        <v>839</v>
+      </c>
+      <c r="KI59" t="s">
+        <v>1735</v>
+      </c>
+      <c r="KJ59" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK59" t="s">
+        <v>706</v>
+      </c>
+      <c r="KL59">
+        <v>0</v>
+      </c>
+      <c r="KM59">
+        <v>0</v>
+      </c>
+      <c r="KN59">
+        <v>0</v>
+      </c>
+      <c r="KO59">
+        <v>1</v>
+      </c>
+      <c r="KR59" t="s">
+        <v>1736</v>
+      </c>
+      <c r="KS59" t="s">
+        <v>1737</v>
+      </c>
+      <c r="KT59" t="s">
+        <v>1738</v>
+      </c>
+      <c r="KU59" t="s">
+        <v>1739</v>
+      </c>
+      <c r="NP59">
+        <v>490</v>
+      </c>
+      <c r="NQ59">
+        <v>355</v>
+      </c>
+      <c r="NS59">
+        <v>315</v>
+      </c>
+      <c r="NT59">
+        <v>200</v>
+      </c>
+      <c r="NV59">
+        <v>309</v>
+      </c>
+      <c r="NW59">
+        <v>180</v>
+      </c>
+      <c r="SD59" s="1"/>
+      <c r="UH59" t="s">
+        <v>1740</v>
+      </c>
+      <c r="ZL59" s="1"/>
+      <c r="ADO59" s="1"/>
+      <c r="ADW59" s="1"/>
+      <c r="AEA59" s="1"/>
+      <c r="AEY59">
+        <v>891766552</v>
+      </c>
+      <c r="AEZ59" t="s">
+        <v>1741</v>
+      </c>
+      <c r="AFA59" s="1">
+        <v>46307.531319444453</v>
+      </c>
+      <c r="AFC59" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE59" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFF59" t="s">
+        <v>1742</v>
+      </c>
+      <c r="AFG59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B60" t="s">
+        <v>737</v>
+      </c>
+      <c r="D60" t="s">
+        <v>592</v>
+      </c>
+      <c r="E60" t="s">
+        <v>752</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1392</v>
+      </c>
+      <c r="EN60" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT60">
+        <v>100</v>
+      </c>
+      <c r="FU60">
+        <v>40</v>
+      </c>
+      <c r="FV60">
+        <v>0</v>
+      </c>
+      <c r="FW60">
+        <v>0</v>
+      </c>
+      <c r="FY60">
+        <v>156</v>
+      </c>
+      <c r="FZ60">
+        <v>85</v>
+      </c>
+      <c r="GA60">
+        <v>0</v>
+      </c>
+      <c r="GB60">
+        <v>0</v>
+      </c>
+      <c r="GD60">
+        <v>89</v>
+      </c>
+      <c r="GE60">
+        <v>35</v>
+      </c>
+      <c r="GF60">
+        <v>0</v>
+      </c>
+      <c r="GG60">
+        <v>0</v>
+      </c>
+      <c r="GI60">
+        <v>4</v>
+      </c>
+      <c r="GJ60">
+        <v>0</v>
+      </c>
+      <c r="GK60">
+        <v>0</v>
+      </c>
+      <c r="GL60">
+        <v>0</v>
+      </c>
+      <c r="GN60">
+        <v>0</v>
+      </c>
+      <c r="GO60">
+        <v>0</v>
+      </c>
+      <c r="GP60">
+        <v>0</v>
+      </c>
+      <c r="GQ60">
+        <v>0</v>
+      </c>
+      <c r="GR60" t="s">
+        <v>1743</v>
+      </c>
+      <c r="GS60">
+        <v>1</v>
+      </c>
+      <c r="GT60">
+        <v>0</v>
+      </c>
+      <c r="GU60">
+        <v>1</v>
+      </c>
+      <c r="GV60">
+        <v>1</v>
+      </c>
+      <c r="GW60">
+        <v>0</v>
+      </c>
+      <c r="GX60">
+        <v>0</v>
+      </c>
+      <c r="GY60">
+        <v>1</v>
+      </c>
+      <c r="GZ60" t="s">
+        <v>1294</v>
+      </c>
+      <c r="HA60">
+        <v>1</v>
+      </c>
+      <c r="HB60">
+        <v>0</v>
+      </c>
+      <c r="HC60">
+        <v>1</v>
+      </c>
+      <c r="HD60">
+        <v>1</v>
+      </c>
+      <c r="HE60">
+        <v>0</v>
+      </c>
+      <c r="HG60" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH60" t="s">
+        <v>1744</v>
+      </c>
+      <c r="HI60" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ60" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL60" t="s">
+        <v>732</v>
+      </c>
+      <c r="HT60" t="s">
+        <v>765</v>
+      </c>
+      <c r="HU60">
+        <v>15</v>
+      </c>
+      <c r="HV60" t="s">
+        <v>1745</v>
+      </c>
+      <c r="HX60" t="s">
+        <v>765</v>
+      </c>
+      <c r="HY60">
+        <v>15</v>
+      </c>
+      <c r="HZ60" t="s">
+        <v>1746</v>
+      </c>
+      <c r="IB60" t="s">
+        <v>765</v>
+      </c>
+      <c r="IC60">
+        <v>15</v>
+      </c>
+      <c r="ID60" t="s">
+        <v>1747</v>
+      </c>
+      <c r="IF60" t="s">
+        <v>766</v>
+      </c>
+      <c r="IG60">
+        <v>15</v>
+      </c>
+      <c r="IH60" t="s">
+        <v>1748</v>
+      </c>
+      <c r="IJ60" t="s">
+        <v>765</v>
+      </c>
+      <c r="IK60">
+        <v>15</v>
+      </c>
+      <c r="IL60" t="s">
+        <v>1749</v>
+      </c>
+      <c r="IV60" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW60" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX60" t="s">
+        <v>1750</v>
+      </c>
+      <c r="IY60" t="s">
+        <v>1209</v>
+      </c>
+      <c r="IZ60" t="s">
+        <v>1751</v>
+      </c>
+      <c r="JA60" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC60" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD60" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JE60" t="s">
+        <v>1752</v>
+      </c>
+      <c r="JF60" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG60" t="s">
+        <v>1753</v>
+      </c>
+      <c r="JH60" t="s">
+        <v>716</v>
+      </c>
+      <c r="JJ60" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK60" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JL60" t="s">
+        <v>1754</v>
+      </c>
+      <c r="JM60" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JN60" t="s">
+        <v>1755</v>
+      </c>
+      <c r="JO60" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ60" t="s">
+        <v>835</v>
+      </c>
+      <c r="JR60" t="s">
+        <v>879</v>
+      </c>
+      <c r="JS60" t="s">
+        <v>842</v>
+      </c>
+      <c r="JT60" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JU60" t="s">
+        <v>842</v>
+      </c>
+      <c r="JV60" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX60" t="s">
+        <v>835</v>
+      </c>
+      <c r="JY60" t="s">
+        <v>879</v>
+      </c>
+      <c r="JZ60" t="s">
+        <v>842</v>
+      </c>
+      <c r="KA60" t="s">
+        <v>1209</v>
+      </c>
+      <c r="KB60" t="s">
+        <v>1756</v>
+      </c>
+      <c r="KC60" t="s">
+        <v>720</v>
+      </c>
+      <c r="KE60" t="s">
+        <v>835</v>
+      </c>
+      <c r="KF60" t="s">
+        <v>879</v>
+      </c>
+      <c r="KG60" t="s">
+        <v>1757</v>
+      </c>
+      <c r="KH60" t="s">
+        <v>1209</v>
+      </c>
+      <c r="KI60" t="s">
+        <v>842</v>
+      </c>
+      <c r="KJ60" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK60" t="s">
+        <v>1384</v>
+      </c>
+      <c r="KL60">
+        <v>0</v>
+      </c>
+      <c r="KM60">
+        <v>1</v>
+      </c>
+      <c r="KN60">
+        <v>1</v>
+      </c>
+      <c r="KO60">
+        <v>0</v>
+      </c>
+      <c r="KR60" t="s">
+        <v>1758</v>
+      </c>
+      <c r="KS60" t="s">
+        <v>1759</v>
+      </c>
+      <c r="KT60" t="s">
+        <v>1760</v>
+      </c>
+      <c r="KU60" t="s">
+        <v>1761</v>
+      </c>
+      <c r="NP60">
+        <v>492</v>
+      </c>
+      <c r="NQ60">
+        <v>465</v>
+      </c>
+      <c r="NS60">
+        <v>233</v>
+      </c>
+      <c r="NT60">
+        <v>173</v>
+      </c>
+      <c r="NV60">
+        <v>113</v>
+      </c>
+      <c r="NW60">
+        <v>80</v>
+      </c>
+      <c r="SD60" s="1"/>
+      <c r="UH60" t="s">
+        <v>1762</v>
+      </c>
+      <c r="ZL60" s="1"/>
+      <c r="ADO60" s="1"/>
+      <c r="ADW60" s="1"/>
+      <c r="AEA60" s="1"/>
+      <c r="AEY60">
+        <v>891812930</v>
+      </c>
+      <c r="AEZ60" t="s">
+        <v>1763</v>
+      </c>
+      <c r="AFA60" s="1">
+        <v>46307.569872685177</v>
+      </c>
+      <c r="AFC60" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE60" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFF60" t="s">
+        <v>1764</v>
+      </c>
+      <c r="AFG60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B61" t="s">
+        <v>737</v>
+      </c>
+      <c r="D61" t="s">
+        <v>592</v>
+      </c>
+      <c r="E61" t="s">
+        <v>752</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1765</v>
+      </c>
+      <c r="EN61" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO61">
+        <v>544</v>
+      </c>
+      <c r="EP61">
+        <v>515</v>
+      </c>
+      <c r="EQ61" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER61" t="s">
+        <v>1400</v>
+      </c>
+      <c r="ES61">
+        <v>1</v>
+      </c>
+      <c r="ET61">
+        <v>0</v>
+      </c>
+      <c r="EU61">
+        <v>0</v>
+      </c>
+      <c r="EV61">
+        <v>0</v>
+      </c>
+      <c r="EW61">
+        <v>1</v>
+      </c>
+      <c r="EX61">
+        <v>0</v>
+      </c>
+      <c r="EZ61" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA61">
+        <v>32</v>
+      </c>
+      <c r="FB61" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC61">
+        <v>1</v>
+      </c>
+      <c r="FD61">
+        <v>1</v>
+      </c>
+      <c r="FE61">
+        <v>1</v>
+      </c>
+      <c r="FF61" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG61" t="s">
+        <v>1766</v>
+      </c>
+      <c r="FH61" t="s">
+        <v>711</v>
+      </c>
+      <c r="FI61">
+        <v>0</v>
+      </c>
+      <c r="FJ61" t="s">
+        <v>706</v>
+      </c>
+      <c r="FK61">
+        <v>0</v>
+      </c>
+      <c r="FL61">
+        <v>1</v>
+      </c>
+      <c r="NP61">
+        <v>329</v>
+      </c>
+      <c r="NQ61">
+        <v>248</v>
+      </c>
+      <c r="NS61">
+        <v>132</v>
+      </c>
+      <c r="NT61">
+        <v>102</v>
+      </c>
+      <c r="NV61">
+        <v>111</v>
+      </c>
+      <c r="NW61">
+        <v>96</v>
+      </c>
+      <c r="SD61" s="1"/>
+      <c r="UH61" t="s">
+        <v>1767</v>
+      </c>
+      <c r="ZL61" s="1"/>
+      <c r="ADO61" s="1"/>
+      <c r="ADW61" s="1"/>
+      <c r="AEA61" s="1"/>
+      <c r="AEY61">
+        <v>891812940</v>
+      </c>
+      <c r="AEZ61" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AFA61" s="1">
+        <v>46307.569884259261</v>
+      </c>
+      <c r="AFC61" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE61" t="s">
+        <v>1769</v>
+      </c>
+      <c r="AFF61" t="s">
+        <v>1770</v>
+      </c>
+      <c r="AFG61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B62" t="s">
+        <v>737</v>
+      </c>
+      <c r="D62" t="s">
+        <v>592</v>
+      </c>
+      <c r="E62" t="s">
+        <v>752</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1765</v>
+      </c>
+      <c r="EN62" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT62">
+        <v>204</v>
+      </c>
+      <c r="FU62">
+        <v>195</v>
+      </c>
+      <c r="FV62">
+        <v>0</v>
+      </c>
+      <c r="FW62">
+        <v>0</v>
+      </c>
+      <c r="FY62">
+        <v>96</v>
+      </c>
+      <c r="FZ62">
+        <v>94</v>
+      </c>
+      <c r="GA62">
+        <v>0</v>
+      </c>
+      <c r="GB62">
+        <v>0</v>
+      </c>
+      <c r="GD62">
+        <v>89</v>
+      </c>
+      <c r="GE62">
+        <v>76</v>
+      </c>
+      <c r="GF62">
+        <v>0</v>
+      </c>
+      <c r="GG62">
+        <v>0</v>
+      </c>
+      <c r="GI62">
+        <v>3</v>
+      </c>
+      <c r="GJ62">
+        <v>2</v>
+      </c>
+      <c r="GK62">
+        <v>0</v>
+      </c>
+      <c r="GL62">
+        <v>0</v>
+      </c>
+      <c r="GN62">
+        <v>1</v>
+      </c>
+      <c r="GO62">
+        <v>0</v>
+      </c>
+      <c r="GP62">
+        <v>0</v>
+      </c>
+      <c r="GQ62">
+        <v>0</v>
+      </c>
+      <c r="GR62" t="s">
+        <v>1743</v>
+      </c>
+      <c r="GS62">
+        <v>1</v>
+      </c>
+      <c r="GT62">
+        <v>0</v>
+      </c>
+      <c r="GU62">
+        <v>1</v>
+      </c>
+      <c r="GV62">
+        <v>1</v>
+      </c>
+      <c r="GW62">
+        <v>0</v>
+      </c>
+      <c r="GX62">
+        <v>0</v>
+      </c>
+      <c r="GY62">
+        <v>1</v>
+      </c>
+      <c r="GZ62" t="s">
+        <v>1294</v>
+      </c>
+      <c r="HA62">
+        <v>1</v>
+      </c>
+      <c r="HB62">
+        <v>0</v>
+      </c>
+      <c r="HC62">
+        <v>1</v>
+      </c>
+      <c r="HD62">
+        <v>1</v>
+      </c>
+      <c r="HE62">
+        <v>0</v>
+      </c>
+      <c r="HG62" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH62" t="s">
+        <v>1771</v>
+      </c>
+      <c r="HI62" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ62" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL62" t="s">
+        <v>732</v>
+      </c>
+      <c r="HT62" t="s">
+        <v>1375</v>
+      </c>
+      <c r="HU62">
+        <v>35</v>
+      </c>
+      <c r="HV62" t="s">
+        <v>1772</v>
+      </c>
+      <c r="HX62" t="s">
+        <v>1375</v>
+      </c>
+      <c r="HY62">
+        <v>49</v>
+      </c>
+      <c r="HZ62" t="s">
+        <v>1773</v>
+      </c>
+      <c r="IB62" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IC62">
+        <v>49</v>
+      </c>
+      <c r="ID62" t="s">
+        <v>1774</v>
+      </c>
+      <c r="IF62" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IG62">
+        <v>49</v>
+      </c>
+      <c r="IH62" t="s">
+        <v>1775</v>
+      </c>
+      <c r="IJ62" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IK62">
+        <v>49</v>
+      </c>
+      <c r="IL62" t="s">
+        <v>1776</v>
+      </c>
+      <c r="IV62" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW62" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX62" t="s">
+        <v>1777</v>
+      </c>
+      <c r="IY62" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ62" t="s">
+        <v>1778</v>
+      </c>
+      <c r="JA62" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC62" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD62" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE62" t="s">
+        <v>1779</v>
+      </c>
+      <c r="JF62" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG62" t="s">
+        <v>1780</v>
+      </c>
+      <c r="JH62" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ62" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK62" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL62" t="s">
+        <v>1781</v>
+      </c>
+      <c r="JM62" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN62" t="s">
+        <v>1782</v>
+      </c>
+      <c r="JO62" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ62" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR62" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS62" t="s">
+        <v>1783</v>
+      </c>
+      <c r="JT62" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU62" t="s">
+        <v>1784</v>
+      </c>
+      <c r="JV62" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX62" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY62" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ62" t="s">
+        <v>1785</v>
+      </c>
+      <c r="KA62" t="s">
+        <v>839</v>
+      </c>
+      <c r="KB62" t="s">
+        <v>1786</v>
+      </c>
+      <c r="KC62" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE62" t="s">
+        <v>835</v>
+      </c>
+      <c r="KF62" t="s">
+        <v>1143</v>
+      </c>
+      <c r="KG62" t="s">
+        <v>842</v>
+      </c>
+      <c r="KH62" t="s">
+        <v>1209</v>
+      </c>
+      <c r="KI62" t="s">
+        <v>842</v>
+      </c>
+      <c r="KJ62" t="s">
+        <v>720</v>
+      </c>
+      <c r="KK62" t="s">
+        <v>1384</v>
+      </c>
+      <c r="KL62">
+        <v>0</v>
+      </c>
+      <c r="KM62">
+        <v>1</v>
+      </c>
+      <c r="KN62">
+        <v>1</v>
+      </c>
+      <c r="KO62">
+        <v>0</v>
+      </c>
+      <c r="KR62" t="s">
+        <v>1787</v>
+      </c>
+      <c r="KS62" t="s">
+        <v>1788</v>
+      </c>
+      <c r="KT62" t="s">
+        <v>1789</v>
+      </c>
+      <c r="KU62" t="s">
+        <v>1790</v>
+      </c>
+      <c r="NP62">
+        <v>300</v>
+      </c>
+      <c r="NQ62">
+        <v>195</v>
+      </c>
+      <c r="NS62">
+        <v>108</v>
+      </c>
+      <c r="NT62">
+        <v>102</v>
+      </c>
+      <c r="NV62">
+        <v>111</v>
+      </c>
+      <c r="NW62">
+        <v>96</v>
+      </c>
+      <c r="SD62" s="1"/>
+      <c r="UH62" t="s">
+        <v>1791</v>
+      </c>
+      <c r="ZL62" s="1"/>
+      <c r="ADO62" s="1"/>
+      <c r="ADW62" s="1"/>
+      <c r="AEA62" s="1"/>
+      <c r="AEY62">
+        <v>891812943</v>
+      </c>
+      <c r="AEZ62" t="s">
+        <v>1792</v>
+      </c>
+      <c r="AFA62" s="1">
+        <v>46307.569895833331</v>
+      </c>
+      <c r="AFC62" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE62" t="s">
+        <v>1769</v>
+      </c>
+      <c r="AFF62" t="s">
+        <v>1793</v>
+      </c>
+      <c r="AFG62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B63" t="s">
+        <v>737</v>
+      </c>
+      <c r="D63" t="s">
+        <v>592</v>
+      </c>
+      <c r="E63" t="s">
+        <v>752</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1794</v>
+      </c>
+      <c r="EN63" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO63">
+        <v>713</v>
+      </c>
+      <c r="EP63">
+        <v>597</v>
+      </c>
+      <c r="EQ63" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER63" t="s">
+        <v>1400</v>
+      </c>
+      <c r="ES63">
+        <v>1</v>
+      </c>
+      <c r="ET63">
+        <v>0</v>
+      </c>
+      <c r="EU63">
+        <v>0</v>
+      </c>
+      <c r="EV63">
+        <v>0</v>
+      </c>
+      <c r="EW63">
+        <v>1</v>
+      </c>
+      <c r="EX63">
+        <v>0</v>
+      </c>
+      <c r="EZ63" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA63">
+        <v>30</v>
+      </c>
+      <c r="FB63" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC63">
+        <v>1</v>
+      </c>
+      <c r="FD63">
+        <v>1</v>
+      </c>
+      <c r="FE63">
+        <v>1</v>
+      </c>
+      <c r="FF63" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG63" t="s">
+        <v>1795</v>
+      </c>
+      <c r="FH63" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP63">
+        <v>418</v>
+      </c>
+      <c r="NQ63">
+        <v>379</v>
+      </c>
+      <c r="NS63">
+        <v>173</v>
+      </c>
+      <c r="NT63">
+        <v>140</v>
+      </c>
+      <c r="NV63">
+        <v>122</v>
+      </c>
+      <c r="NW63">
+        <v>78</v>
+      </c>
+      <c r="SD63" s="1"/>
+      <c r="UH63" t="s">
+        <v>1796</v>
+      </c>
+      <c r="ZL63" s="1"/>
+      <c r="ADO63" s="1"/>
+      <c r="ADW63" s="1"/>
+      <c r="AEA63" s="1"/>
+      <c r="AEY63">
+        <v>891816849</v>
+      </c>
+      <c r="AEZ63" t="s">
+        <v>1797</v>
+      </c>
+      <c r="AFA63" s="1">
+        <v>46307.573634259257</v>
+      </c>
+      <c r="AFC63" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE63" t="s">
+        <v>1769</v>
+      </c>
+      <c r="AFF63" t="s">
+        <v>1798</v>
+      </c>
+      <c r="AFG63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B64" t="s">
+        <v>951</v>
+      </c>
+      <c r="D64" t="s">
+        <v>589</v>
+      </c>
+      <c r="E64" t="s">
+        <v>709</v>
+      </c>
+      <c r="N64" t="s">
+        <v>952</v>
+      </c>
+      <c r="P64">
+        <v>7</v>
+      </c>
+      <c r="Q64">
+        <v>4</v>
+      </c>
+      <c r="R64" t="s">
+        <v>711</v>
+      </c>
+      <c r="S64">
+        <v>2</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>3</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64" t="s">
+        <v>711</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>1799</v>
+      </c>
+      <c r="AG64" t="s">
+        <v>782</v>
+      </c>
+      <c r="AH64">
+        <v>1</v>
+      </c>
+      <c r="AI64">
+        <v>1</v>
+      </c>
+      <c r="AJ64">
+        <v>1</v>
+      </c>
+      <c r="AK64">
+        <v>1</v>
+      </c>
+      <c r="AL64">
+        <v>1</v>
+      </c>
+      <c r="AM64" t="s">
+        <v>783</v>
+      </c>
+      <c r="AN64">
+        <v>1</v>
+      </c>
+      <c r="AO64">
+        <v>1</v>
+      </c>
+      <c r="AP64">
+        <v>1</v>
+      </c>
+      <c r="AQ64" t="s">
+        <v>1800</v>
+      </c>
+      <c r="AR64" t="s">
+        <v>720</v>
+      </c>
+      <c r="AT64" t="s">
+        <v>1223</v>
+      </c>
+      <c r="AU64">
+        <v>1</v>
+      </c>
+      <c r="AV64">
+        <v>1</v>
+      </c>
+      <c r="AW64">
+        <v>0</v>
+      </c>
+      <c r="AX64">
+        <v>1</v>
+      </c>
+      <c r="AY64">
+        <v>1</v>
+      </c>
+      <c r="AZ64" t="s">
+        <v>727</v>
+      </c>
+      <c r="BA64">
+        <v>1</v>
+      </c>
+      <c r="BB64">
+        <v>0</v>
+      </c>
+      <c r="BC64">
+        <v>1</v>
+      </c>
+      <c r="BD64" t="s">
+        <v>1801</v>
+      </c>
+      <c r="BE64" t="s">
+        <v>716</v>
+      </c>
+      <c r="BG64" t="s">
+        <v>854</v>
+      </c>
+      <c r="BH64">
+        <v>1</v>
+      </c>
+      <c r="BI64">
+        <v>0</v>
+      </c>
+      <c r="BJ64">
+        <v>0</v>
+      </c>
+      <c r="BK64">
+        <v>1</v>
+      </c>
+      <c r="BL64">
+        <v>1</v>
+      </c>
+      <c r="BM64" t="s">
+        <v>783</v>
+      </c>
+      <c r="BN64">
+        <v>1</v>
+      </c>
+      <c r="BO64">
+        <v>1</v>
+      </c>
+      <c r="BP64">
+        <v>1</v>
+      </c>
+      <c r="BQ64" t="s">
+        <v>1802</v>
+      </c>
+      <c r="BR64" t="s">
+        <v>716</v>
+      </c>
+      <c r="BT64" t="s">
+        <v>782</v>
+      </c>
+      <c r="BU64">
+        <v>1</v>
+      </c>
+      <c r="BV64">
+        <v>1</v>
+      </c>
+      <c r="BW64">
+        <v>1</v>
+      </c>
+      <c r="BX64">
+        <v>1</v>
+      </c>
+      <c r="BY64">
+        <v>1</v>
+      </c>
+      <c r="BZ64" t="s">
+        <v>783</v>
+      </c>
+      <c r="CA64">
+        <v>1</v>
+      </c>
+      <c r="CB64">
+        <v>1</v>
+      </c>
+      <c r="CC64">
+        <v>1</v>
+      </c>
+      <c r="CD64" t="s">
+        <v>1803</v>
+      </c>
+      <c r="CE64" t="s">
+        <v>720</v>
+      </c>
+      <c r="CG64" t="s">
+        <v>854</v>
+      </c>
+      <c r="CH64">
+        <v>1</v>
+      </c>
+      <c r="CI64">
+        <v>0</v>
+      </c>
+      <c r="CJ64">
+        <v>0</v>
+      </c>
+      <c r="CK64">
+        <v>1</v>
+      </c>
+      <c r="CL64">
+        <v>1</v>
+      </c>
+      <c r="CM64" t="s">
+        <v>783</v>
+      </c>
+      <c r="CN64">
+        <v>1</v>
+      </c>
+      <c r="CO64">
+        <v>1</v>
+      </c>
+      <c r="CP64">
+        <v>1</v>
+      </c>
+      <c r="CQ64" t="s">
+        <v>1804</v>
+      </c>
+      <c r="CR64" t="s">
+        <v>716</v>
+      </c>
+      <c r="CT64" t="s">
+        <v>854</v>
+      </c>
+      <c r="CU64">
+        <v>1</v>
+      </c>
+      <c r="CV64">
+        <v>0</v>
+      </c>
+      <c r="CW64">
+        <v>0</v>
+      </c>
+      <c r="CX64">
+        <v>1</v>
+      </c>
+      <c r="CY64">
+        <v>1</v>
+      </c>
+      <c r="CZ64" t="s">
+        <v>783</v>
+      </c>
+      <c r="DA64">
+        <v>1</v>
+      </c>
+      <c r="DB64">
+        <v>1</v>
+      </c>
+      <c r="DC64">
+        <v>1</v>
+      </c>
+      <c r="DD64" t="s">
+        <v>1805</v>
+      </c>
+      <c r="DE64" t="s">
+        <v>716</v>
+      </c>
+      <c r="DF64" t="s">
+        <v>1806</v>
+      </c>
+      <c r="DG64">
+        <v>0</v>
+      </c>
+      <c r="DH64">
+        <v>0</v>
+      </c>
+      <c r="DI64">
+        <v>0</v>
+      </c>
+      <c r="DJ64">
+        <v>0</v>
+      </c>
+      <c r="DK64">
+        <v>0</v>
+      </c>
+      <c r="DL64">
+        <v>0</v>
+      </c>
+      <c r="DM64">
+        <v>0</v>
+      </c>
+      <c r="DN64">
+        <v>1</v>
+      </c>
+      <c r="DO64">
+        <v>0</v>
+      </c>
+      <c r="DP64" t="s">
+        <v>732</v>
+      </c>
+      <c r="EI64">
+        <v>2</v>
+      </c>
+      <c r="EK64">
+        <v>1</v>
+      </c>
+      <c r="EM64">
+        <v>4</v>
+      </c>
+      <c r="SD64" s="1"/>
+      <c r="UH64" t="s">
+        <v>732</v>
+      </c>
+      <c r="ZL64" s="1"/>
+      <c r="ADO64" s="1"/>
+      <c r="ADW64" s="1"/>
+      <c r="AEA64" s="1"/>
+      <c r="AEY64">
+        <v>891830446</v>
+      </c>
+      <c r="AEZ64" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AFA64" s="1">
+        <v>46307.585266203707</v>
+      </c>
+      <c r="AFC64" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE64" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF64" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AFG64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B65" t="s">
+        <v>737</v>
+      </c>
+      <c r="D65" t="s">
+        <v>592</v>
+      </c>
+      <c r="E65" t="s">
+        <v>752</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1794</v>
+      </c>
+      <c r="EN65" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT65">
+        <v>200</v>
+      </c>
+      <c r="FU65">
+        <v>180</v>
+      </c>
+      <c r="FV65">
+        <v>0</v>
+      </c>
+      <c r="FW65">
+        <v>2</v>
+      </c>
+      <c r="FY65">
+        <v>98</v>
+      </c>
+      <c r="FZ65">
+        <v>56</v>
+      </c>
+      <c r="GA65">
+        <v>0</v>
+      </c>
+      <c r="GB65">
+        <v>0</v>
+      </c>
+      <c r="GD65">
+        <v>86</v>
+      </c>
+      <c r="GE65">
+        <v>46</v>
+      </c>
+      <c r="GF65">
+        <v>0</v>
+      </c>
+      <c r="GG65">
+        <v>3</v>
+      </c>
+      <c r="GI65">
+        <v>2</v>
+      </c>
+      <c r="GJ65">
+        <v>0</v>
+      </c>
+      <c r="GK65">
+        <v>0</v>
+      </c>
+      <c r="GL65">
+        <v>0</v>
+      </c>
+      <c r="GN65">
+        <v>2</v>
+      </c>
+      <c r="GO65">
+        <v>2</v>
+      </c>
+      <c r="GP65">
+        <v>0</v>
+      </c>
+      <c r="GQ65">
+        <v>0</v>
+      </c>
+      <c r="GR65" t="s">
+        <v>1743</v>
+      </c>
+      <c r="GS65">
+        <v>1</v>
+      </c>
+      <c r="GT65">
+        <v>0</v>
+      </c>
+      <c r="GU65">
+        <v>1</v>
+      </c>
+      <c r="GV65">
+        <v>1</v>
+      </c>
+      <c r="GW65">
+        <v>0</v>
+      </c>
+      <c r="GX65">
+        <v>0</v>
+      </c>
+      <c r="GY65">
+        <v>1</v>
+      </c>
+      <c r="GZ65" t="s">
+        <v>1294</v>
+      </c>
+      <c r="HA65">
+        <v>1</v>
+      </c>
+      <c r="HB65">
+        <v>0</v>
+      </c>
+      <c r="HC65">
+        <v>1</v>
+      </c>
+      <c r="HD65">
+        <v>1</v>
+      </c>
+      <c r="HE65">
+        <v>0</v>
+      </c>
+      <c r="HG65" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH65" t="s">
+        <v>1809</v>
+      </c>
+      <c r="HI65" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ65" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL65" t="s">
+        <v>732</v>
+      </c>
+      <c r="HT65" t="s">
+        <v>1375</v>
+      </c>
+      <c r="HU65">
+        <v>15</v>
+      </c>
+      <c r="HV65" t="s">
+        <v>1810</v>
+      </c>
+      <c r="HX65" t="s">
+        <v>1375</v>
+      </c>
+      <c r="HY65">
+        <v>15</v>
+      </c>
+      <c r="HZ65" t="s">
+        <v>1811</v>
+      </c>
+      <c r="IB65" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IC65">
+        <v>15</v>
+      </c>
+      <c r="ID65" t="s">
+        <v>1812</v>
+      </c>
+      <c r="IF65" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IG65">
+        <v>15</v>
+      </c>
+      <c r="IH65" t="s">
+        <v>1813</v>
+      </c>
+      <c r="IJ65" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IK65">
+        <v>15</v>
+      </c>
+      <c r="IL65" t="s">
+        <v>1814</v>
+      </c>
+      <c r="IV65" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW65" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX65" t="s">
+        <v>1815</v>
+      </c>
+      <c r="IY65" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ65" t="s">
+        <v>1816</v>
+      </c>
+      <c r="JA65" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC65" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD65" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE65" t="s">
+        <v>1817</v>
+      </c>
+      <c r="JF65" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG65" t="s">
+        <v>1818</v>
+      </c>
+      <c r="JH65" t="s">
+        <v>716</v>
+      </c>
+      <c r="JJ65" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK65" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL65" t="s">
+        <v>1819</v>
+      </c>
+      <c r="JM65" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN65" t="s">
+        <v>1820</v>
+      </c>
+      <c r="JO65" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ65" t="s">
+        <v>835</v>
+      </c>
+      <c r="JR65" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JS65" t="s">
+        <v>842</v>
+      </c>
+      <c r="JT65" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JU65" t="s">
+        <v>842</v>
+      </c>
+      <c r="JV65" t="s">
+        <v>716</v>
+      </c>
+      <c r="JX65" t="s">
+        <v>837</v>
+      </c>
+      <c r="JY65" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JZ65" t="s">
+        <v>842</v>
+      </c>
+      <c r="KA65" t="s">
+        <v>839</v>
+      </c>
+      <c r="KB65" t="s">
+        <v>1821</v>
+      </c>
+      <c r="KC65" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE65" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF65" t="s">
+        <v>769</v>
+      </c>
+      <c r="KG65" t="s">
+        <v>1822</v>
+      </c>
+      <c r="KH65" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI65" t="s">
+        <v>1823</v>
+      </c>
+      <c r="KJ65" t="s">
+        <v>720</v>
+      </c>
+      <c r="KK65" t="s">
+        <v>1384</v>
+      </c>
+      <c r="KL65">
+        <v>0</v>
+      </c>
+      <c r="KM65">
+        <v>1</v>
+      </c>
+      <c r="KN65">
+        <v>1</v>
+      </c>
+      <c r="KO65">
+        <v>0</v>
+      </c>
+      <c r="KP65">
+        <v>0</v>
+      </c>
+      <c r="KR65" t="s">
+        <v>1824</v>
+      </c>
+      <c r="KS65" t="s">
+        <v>1825</v>
+      </c>
+      <c r="KT65" t="s">
+        <v>1826</v>
+      </c>
+      <c r="KU65" t="s">
+        <v>1827</v>
+      </c>
+      <c r="NP65">
+        <v>418</v>
+      </c>
+      <c r="NQ65">
+        <v>379</v>
+      </c>
+      <c r="NS65">
+        <v>173</v>
+      </c>
+      <c r="NT65">
+        <v>140</v>
+      </c>
+      <c r="NV65">
+        <v>122</v>
+      </c>
+      <c r="NW65">
+        <v>78</v>
+      </c>
+      <c r="SD65" s="1"/>
+      <c r="UH65" t="s">
+        <v>842</v>
+      </c>
+      <c r="ZL65" s="1"/>
+      <c r="ADO65" s="1"/>
+      <c r="ADW65" s="1"/>
+      <c r="AEA65" s="1"/>
+      <c r="AEY65">
+        <v>891841605</v>
+      </c>
+      <c r="AEZ65" t="s">
+        <v>1828</v>
+      </c>
+      <c r="AFA65" s="1">
+        <v>46307.593634259261</v>
+      </c>
+      <c r="AFC65" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE65" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF65" t="s">
+        <v>1829</v>
+      </c>
+      <c r="AFG65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B66" t="s">
+        <v>951</v>
+      </c>
+      <c r="D66" t="s">
+        <v>589</v>
+      </c>
+      <c r="E66" t="s">
+        <v>709</v>
+      </c>
+      <c r="N66" t="s">
+        <v>952</v>
+      </c>
+      <c r="P66">
+        <v>7</v>
+      </c>
+      <c r="Q66">
+        <v>4</v>
+      </c>
+      <c r="R66" t="s">
+        <v>711</v>
+      </c>
+      <c r="S66">
+        <v>2</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>3</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66" t="s">
+        <v>732</v>
+      </c>
+      <c r="AG66" t="s">
+        <v>782</v>
+      </c>
+      <c r="AH66">
+        <v>1</v>
+      </c>
+      <c r="AI66">
+        <v>1</v>
+      </c>
+      <c r="AJ66">
+        <v>1</v>
+      </c>
+      <c r="AK66">
+        <v>1</v>
+      </c>
+      <c r="AL66">
+        <v>1</v>
+      </c>
+      <c r="AM66" t="s">
+        <v>783</v>
+      </c>
+      <c r="AN66">
+        <v>1</v>
+      </c>
+      <c r="AO66">
+        <v>1</v>
+      </c>
+      <c r="AP66">
+        <v>1</v>
+      </c>
+      <c r="AQ66" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AR66" t="s">
+        <v>720</v>
+      </c>
+      <c r="AT66" t="s">
+        <v>717</v>
+      </c>
+      <c r="AU66">
+        <v>1</v>
+      </c>
+      <c r="AV66">
+        <v>0</v>
+      </c>
+      <c r="AW66">
+        <v>0</v>
+      </c>
+      <c r="AX66">
+        <v>1</v>
+      </c>
+      <c r="AY66">
+        <v>0</v>
+      </c>
+      <c r="AZ66" t="s">
+        <v>722</v>
+      </c>
+      <c r="BA66">
+        <v>0</v>
+      </c>
+      <c r="BB66">
+        <v>1</v>
+      </c>
+      <c r="BC66">
+        <v>0</v>
+      </c>
+      <c r="BD66" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BE66" t="s">
+        <v>716</v>
+      </c>
+      <c r="BG66" t="s">
+        <v>811</v>
+      </c>
+      <c r="BH66">
+        <v>0</v>
+      </c>
+      <c r="BI66">
+        <v>1</v>
+      </c>
+      <c r="BJ66">
+        <v>1</v>
+      </c>
+      <c r="BK66">
+        <v>1</v>
+      </c>
+      <c r="BL66">
+        <v>1</v>
+      </c>
+      <c r="BM66" t="s">
+        <v>783</v>
+      </c>
+      <c r="BN66">
+        <v>1</v>
+      </c>
+      <c r="BO66">
+        <v>1</v>
+      </c>
+      <c r="BP66">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="s">
+        <v>1832</v>
+      </c>
+      <c r="BR66" t="s">
+        <v>716</v>
+      </c>
+      <c r="BT66" t="s">
+        <v>782</v>
+      </c>
+      <c r="BU66">
+        <v>1</v>
+      </c>
+      <c r="BV66">
+        <v>1</v>
+      </c>
+      <c r="BW66">
+        <v>1</v>
+      </c>
+      <c r="BX66">
+        <v>1</v>
+      </c>
+      <c r="BY66">
+        <v>1</v>
+      </c>
+      <c r="BZ66" t="s">
+        <v>783</v>
+      </c>
+      <c r="CA66">
+        <v>1</v>
+      </c>
+      <c r="CB66">
+        <v>1</v>
+      </c>
+      <c r="CC66">
+        <v>1</v>
+      </c>
+      <c r="CD66" t="s">
+        <v>1833</v>
+      </c>
+      <c r="CE66" t="s">
+        <v>720</v>
+      </c>
+      <c r="CG66" t="s">
+        <v>1223</v>
+      </c>
+      <c r="CH66">
+        <v>1</v>
+      </c>
+      <c r="CI66">
+        <v>1</v>
+      </c>
+      <c r="CJ66">
+        <v>0</v>
+      </c>
+      <c r="CK66">
+        <v>1</v>
+      </c>
+      <c r="CL66">
+        <v>1</v>
+      </c>
+      <c r="CM66" t="s">
+        <v>783</v>
+      </c>
+      <c r="CN66">
+        <v>1</v>
+      </c>
+      <c r="CO66">
+        <v>1</v>
+      </c>
+      <c r="CP66">
+        <v>1</v>
+      </c>
+      <c r="CQ66" t="s">
+        <v>1834</v>
+      </c>
+      <c r="CR66" t="s">
+        <v>720</v>
+      </c>
+      <c r="CT66" t="s">
+        <v>854</v>
+      </c>
+      <c r="CU66">
+        <v>1</v>
+      </c>
+      <c r="CV66">
+        <v>0</v>
+      </c>
+      <c r="CW66">
+        <v>0</v>
+      </c>
+      <c r="CX66">
+        <v>1</v>
+      </c>
+      <c r="CY66">
+        <v>1</v>
+      </c>
+      <c r="CZ66" t="s">
+        <v>714</v>
+      </c>
+      <c r="DA66">
+        <v>1</v>
+      </c>
+      <c r="DB66">
+        <v>0</v>
+      </c>
+      <c r="DC66">
+        <v>0</v>
+      </c>
+      <c r="DD66" t="s">
+        <v>1835</v>
+      </c>
+      <c r="DE66" t="s">
+        <v>716</v>
+      </c>
+      <c r="DF66" t="s">
+        <v>1167</v>
+      </c>
+      <c r="DG66">
+        <v>1</v>
+      </c>
+      <c r="DH66">
+        <v>1</v>
+      </c>
+      <c r="DI66">
+        <v>1</v>
+      </c>
+      <c r="DJ66">
+        <v>1</v>
+      </c>
+      <c r="DK66">
+        <v>1</v>
+      </c>
+      <c r="DL66">
+        <v>1</v>
+      </c>
+      <c r="DM66">
+        <v>1</v>
+      </c>
+      <c r="DN66">
+        <v>1</v>
+      </c>
+      <c r="DO66">
+        <v>1</v>
+      </c>
+      <c r="DP66" t="s">
+        <v>732</v>
+      </c>
+      <c r="EI66">
+        <v>2</v>
+      </c>
+      <c r="EK66">
+        <v>1</v>
+      </c>
+      <c r="EM66">
+        <v>3</v>
+      </c>
+      <c r="SD66" s="1"/>
+      <c r="UH66" t="s">
+        <v>1149</v>
+      </c>
+      <c r="ZL66" s="1"/>
+      <c r="ADO66" s="1"/>
+      <c r="ADW66" s="1"/>
+      <c r="AEA66" s="1"/>
+      <c r="AEY66">
+        <v>891842296</v>
+      </c>
+      <c r="AEZ66" t="s">
+        <v>1836</v>
+      </c>
+      <c r="AFA66" s="1">
+        <v>46307.594108796293</v>
+      </c>
+      <c r="AFC66" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE66" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF66" t="s">
+        <v>1837</v>
+      </c>
+      <c r="AFG66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B67" t="s">
+        <v>803</v>
+      </c>
+      <c r="D67" t="s">
+        <v>594</v>
+      </c>
+      <c r="E67" t="s">
+        <v>738</v>
+      </c>
+      <c r="I67" t="s">
+        <v>1838</v>
+      </c>
+      <c r="SD67" s="1"/>
+      <c r="SV67" t="s">
+        <v>740</v>
+      </c>
+      <c r="SW67">
+        <v>1</v>
+      </c>
+      <c r="SX67">
+        <v>0</v>
+      </c>
+      <c r="SY67" t="s">
+        <v>1839</v>
+      </c>
+      <c r="SZ67">
+        <v>9</v>
+      </c>
+      <c r="TA67">
+        <v>5</v>
+      </c>
+      <c r="TB67" t="s">
+        <v>1840</v>
+      </c>
+      <c r="TC67" s="1">
+        <v>46307</v>
+      </c>
+      <c r="TD67" t="s">
+        <v>1045</v>
+      </c>
+      <c r="TE67" t="s">
+        <v>1841</v>
+      </c>
+      <c r="TF67">
+        <v>37</v>
+      </c>
+      <c r="TG67">
+        <v>29</v>
+      </c>
+      <c r="TH67">
+        <v>2</v>
+      </c>
+      <c r="TI67">
+        <v>1</v>
+      </c>
+      <c r="TJ67" t="s">
+        <v>745</v>
+      </c>
+      <c r="TK67">
+        <v>0</v>
+      </c>
+      <c r="TL67">
+        <v>0</v>
+      </c>
+      <c r="TM67">
+        <v>1</v>
+      </c>
+      <c r="TN67">
+        <v>1</v>
+      </c>
+      <c r="TO67">
+        <v>0</v>
+      </c>
+      <c r="TP67" t="s">
+        <v>1842</v>
+      </c>
+      <c r="UH67" t="s">
+        <v>1843</v>
+      </c>
+      <c r="ZL67" s="1"/>
+      <c r="ADO67" s="1"/>
+      <c r="ADW67" s="1"/>
+      <c r="AEA67" s="1"/>
+      <c r="AEY67">
+        <v>891909080</v>
+      </c>
+      <c r="AEZ67" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AFA67" s="1">
+        <v>46307.6481712963</v>
+      </c>
+      <c r="AFC67" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE67" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFF67" t="s">
+        <v>1845</v>
+      </c>
+      <c r="AFG67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B68" t="s">
+        <v>803</v>
+      </c>
+      <c r="D68" t="s">
+        <v>594</v>
+      </c>
+      <c r="E68" t="s">
+        <v>738</v>
+      </c>
+      <c r="I68" t="s">
+        <v>1846</v>
+      </c>
+      <c r="SD68" s="1"/>
+      <c r="SV68" t="s">
+        <v>740</v>
+      </c>
+      <c r="SW68">
+        <v>1</v>
+      </c>
+      <c r="SX68">
+        <v>0</v>
+      </c>
+      <c r="SY68" t="s">
+        <v>1847</v>
+      </c>
+      <c r="SZ68">
+        <v>11</v>
+      </c>
+      <c r="TA68">
+        <v>6</v>
+      </c>
+      <c r="TB68" t="s">
+        <v>1840</v>
+      </c>
+      <c r="TC68" s="1">
+        <v>46307</v>
+      </c>
+      <c r="TD68" t="s">
+        <v>1848</v>
+      </c>
+      <c r="TE68" t="s">
+        <v>1849</v>
+      </c>
+      <c r="TF68">
+        <v>41</v>
+      </c>
+      <c r="TG68">
+        <v>37</v>
+      </c>
+      <c r="TH68">
+        <v>1</v>
+      </c>
+      <c r="TI68">
+        <v>1</v>
+      </c>
+      <c r="TJ68" t="s">
+        <v>1656</v>
+      </c>
+      <c r="TK68">
+        <v>0</v>
+      </c>
+      <c r="TL68">
+        <v>0</v>
+      </c>
+      <c r="TM68">
+        <v>1</v>
+      </c>
+      <c r="TN68">
+        <v>0</v>
+      </c>
+      <c r="TO68">
+        <v>0</v>
+      </c>
+      <c r="TP68" t="s">
+        <v>1850</v>
+      </c>
+      <c r="UH68" t="s">
+        <v>1851</v>
+      </c>
+      <c r="ZL68" s="1"/>
+      <c r="ADO68" s="1"/>
+      <c r="ADW68" s="1"/>
+      <c r="AEA68" s="1"/>
+      <c r="AEY68">
+        <v>891910227</v>
+      </c>
+      <c r="AEZ68" t="s">
+        <v>1852</v>
+      </c>
+      <c r="AFA68" s="1">
+        <v>46307.649351851847</v>
+      </c>
+      <c r="AFC68" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE68" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFF68" t="s">
+        <v>1853</v>
+      </c>
+      <c r="AFG68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B69" t="s">
+        <v>706</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D69" t="s">
+        <v>596</v>
+      </c>
+      <c r="E69" t="s">
+        <v>752</v>
+      </c>
+      <c r="K69" t="s">
+        <v>1019</v>
+      </c>
+      <c r="EN69" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO69">
+        <v>609</v>
+      </c>
+      <c r="EP69">
+        <v>666</v>
+      </c>
+      <c r="EQ69" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER69" t="s">
+        <v>1854</v>
+      </c>
+      <c r="ES69">
+        <v>1</v>
+      </c>
+      <c r="ET69">
+        <v>0</v>
+      </c>
+      <c r="EU69">
+        <v>1</v>
+      </c>
+      <c r="EV69">
+        <v>0</v>
+      </c>
+      <c r="EW69">
+        <v>0</v>
+      </c>
+      <c r="EX69">
+        <v>0</v>
+      </c>
+      <c r="EZ69" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA69">
+        <v>30</v>
+      </c>
+      <c r="FB69" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC69">
+        <v>1</v>
+      </c>
+      <c r="FD69">
+        <v>1</v>
+      </c>
+      <c r="FE69">
+        <v>1</v>
+      </c>
+      <c r="FF69" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG69" t="s">
+        <v>1855</v>
+      </c>
+      <c r="FH69" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP69">
+        <v>311</v>
+      </c>
+      <c r="NQ69">
+        <v>338</v>
+      </c>
+      <c r="NS69">
+        <v>151</v>
+      </c>
+      <c r="NT69">
+        <v>181</v>
+      </c>
+      <c r="NV69">
+        <v>147</v>
+      </c>
+      <c r="NW69">
+        <v>147</v>
+      </c>
+      <c r="SD69" s="1"/>
+      <c r="UH69" t="s">
+        <v>1856</v>
+      </c>
+      <c r="ZL69" s="1"/>
+      <c r="ADO69" s="1"/>
+      <c r="ADW69" s="1"/>
+      <c r="AEA69" s="1"/>
+      <c r="AEY69">
+        <v>891922762</v>
+      </c>
+      <c r="AEZ69" t="s">
+        <v>1857</v>
+      </c>
+      <c r="AFA69" s="1">
+        <v>46307.660925925928</v>
+      </c>
+      <c r="AFC69" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE69" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AFF69" t="s">
+        <v>1858</v>
+      </c>
+      <c r="AFG69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B70" t="s">
+        <v>706</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D70" t="s">
+        <v>596</v>
+      </c>
+      <c r="E70" t="s">
+        <v>752</v>
+      </c>
+      <c r="K70" t="s">
+        <v>1019</v>
+      </c>
+      <c r="EN70" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT70">
+        <v>311</v>
+      </c>
+      <c r="FU70">
+        <v>338</v>
+      </c>
+      <c r="FV70">
+        <v>4</v>
+      </c>
+      <c r="FW70">
+        <v>2</v>
+      </c>
+      <c r="FY70">
+        <v>151</v>
+      </c>
+      <c r="FZ70">
+        <v>181</v>
+      </c>
+      <c r="GA70">
+        <v>0</v>
+      </c>
+      <c r="GB70">
+        <v>2</v>
+      </c>
+      <c r="GD70">
+        <v>145</v>
+      </c>
+      <c r="GE70">
+        <v>147</v>
+      </c>
+      <c r="GF70">
+        <v>1</v>
+      </c>
+      <c r="GG70">
+        <v>0</v>
+      </c>
+      <c r="GI70">
+        <v>1</v>
+      </c>
+      <c r="GJ70">
+        <v>2</v>
+      </c>
+      <c r="GK70">
+        <v>0</v>
+      </c>
+      <c r="GL70">
+        <v>0</v>
+      </c>
+      <c r="GN70">
+        <v>0</v>
+      </c>
+      <c r="GO70">
+        <v>2</v>
+      </c>
+      <c r="GP70">
+        <v>0</v>
+      </c>
+      <c r="GQ70">
+        <v>0</v>
+      </c>
+      <c r="GR70" t="s">
+        <v>1196</v>
+      </c>
+      <c r="GS70">
+        <v>1</v>
+      </c>
+      <c r="GT70">
+        <v>0</v>
+      </c>
+      <c r="GU70">
+        <v>0</v>
+      </c>
+      <c r="GV70">
+        <v>1</v>
+      </c>
+      <c r="GW70">
+        <v>1</v>
+      </c>
+      <c r="GX70">
+        <v>0</v>
+      </c>
+      <c r="GY70">
+        <v>1</v>
+      </c>
+      <c r="GZ70" t="s">
+        <v>1294</v>
+      </c>
+      <c r="HA70">
+        <v>1</v>
+      </c>
+      <c r="HB70">
+        <v>0</v>
+      </c>
+      <c r="HC70">
+        <v>1</v>
+      </c>
+      <c r="HD70">
+        <v>1</v>
+      </c>
+      <c r="HE70">
+        <v>0</v>
+      </c>
+      <c r="HF70" t="s">
+        <v>1859</v>
+      </c>
+      <c r="HG70" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH70" t="s">
+        <v>1860</v>
+      </c>
+      <c r="HI70" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ70" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL70" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM70" t="s">
+        <v>1861</v>
+      </c>
+      <c r="HT70" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU70">
+        <v>1</v>
+      </c>
+      <c r="HV70" t="s">
+        <v>1862</v>
+      </c>
+      <c r="HX70" t="s">
+        <v>830</v>
+      </c>
+      <c r="HY70">
+        <v>1</v>
+      </c>
+      <c r="HZ70" t="s">
+        <v>1863</v>
+      </c>
+      <c r="IB70" t="s">
+        <v>766</v>
+      </c>
+      <c r="IC70">
+        <v>1</v>
+      </c>
+      <c r="ID70" t="s">
+        <v>1864</v>
+      </c>
+      <c r="IF70" t="s">
+        <v>766</v>
+      </c>
+      <c r="IG70">
+        <v>2</v>
+      </c>
+      <c r="IH70" t="s">
+        <v>1865</v>
+      </c>
+      <c r="IJ70" t="s">
+        <v>765</v>
+      </c>
+      <c r="IK70">
+        <v>2</v>
+      </c>
+      <c r="IL70" t="s">
+        <v>1866</v>
+      </c>
+      <c r="IV70" t="s">
+        <v>835</v>
+      </c>
+      <c r="IW70" t="s">
+        <v>879</v>
+      </c>
+      <c r="IX70" t="s">
+        <v>1867</v>
+      </c>
+      <c r="IY70" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ70" t="s">
+        <v>1868</v>
+      </c>
+      <c r="JA70" t="s">
+        <v>716</v>
+      </c>
+      <c r="JC70" t="s">
+        <v>835</v>
+      </c>
+      <c r="JD70" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JE70" t="s">
+        <v>1869</v>
+      </c>
+      <c r="JF70" t="s">
+        <v>839</v>
+      </c>
+      <c r="JG70" t="s">
+        <v>1250</v>
+      </c>
+      <c r="JH70" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ70" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK70" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL70" t="s">
+        <v>1870</v>
+      </c>
+      <c r="JM70" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN70" t="s">
+        <v>1252</v>
+      </c>
+      <c r="JO70" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ70" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR70" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JS70" t="s">
+        <v>1871</v>
+      </c>
+      <c r="JT70" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU70" t="s">
+        <v>1252</v>
+      </c>
+      <c r="JV70" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX70" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY70" t="s">
+        <v>879</v>
+      </c>
+      <c r="JZ70" t="s">
+        <v>1872</v>
+      </c>
+      <c r="KA70" t="s">
+        <v>1209</v>
+      </c>
+      <c r="KB70" t="s">
+        <v>1873</v>
+      </c>
+      <c r="KC70" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE70" t="s">
+        <v>837</v>
+      </c>
+      <c r="KF70" t="s">
+        <v>879</v>
+      </c>
+      <c r="KG70" t="s">
+        <v>1874</v>
+      </c>
+      <c r="KH70" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI70" t="s">
+        <v>1252</v>
+      </c>
+      <c r="KJ70" t="s">
+        <v>720</v>
+      </c>
+      <c r="KK70" t="s">
+        <v>890</v>
+      </c>
+      <c r="KL70">
+        <v>1</v>
+      </c>
+      <c r="KM70">
+        <v>0</v>
+      </c>
+      <c r="KN70">
+        <v>0</v>
+      </c>
+      <c r="KO70">
+        <v>0</v>
+      </c>
+      <c r="KR70" t="s">
+        <v>1149</v>
+      </c>
+      <c r="KS70" t="s">
+        <v>1875</v>
+      </c>
+      <c r="KT70" t="s">
+        <v>1876</v>
+      </c>
+      <c r="KU70" t="s">
+        <v>1877</v>
+      </c>
+      <c r="NP70">
+        <v>311</v>
+      </c>
+      <c r="NQ70">
+        <v>338</v>
+      </c>
+      <c r="NS70">
+        <v>151</v>
+      </c>
+      <c r="NT70">
+        <v>181</v>
+      </c>
+      <c r="NV70">
+        <v>147</v>
+      </c>
+      <c r="NW70">
+        <v>147</v>
+      </c>
+      <c r="SD70" s="1"/>
+      <c r="UH70" t="s">
+        <v>1878</v>
+      </c>
+      <c r="ZL70" s="1"/>
+      <c r="ADO70" s="1"/>
+      <c r="ADW70" s="1"/>
+      <c r="AEA70" s="1"/>
+      <c r="AEY70">
+        <v>891941055</v>
+      </c>
+      <c r="AEZ70" t="s">
+        <v>1879</v>
+      </c>
+      <c r="AFA70" s="1">
+        <v>46307.677719907413</v>
+      </c>
+      <c r="AFC70" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE70" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AFF70" t="s">
+        <v>1880</v>
+      </c>
+      <c r="AFG70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B71" t="s">
+        <v>706</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D71" t="s">
+        <v>596</v>
+      </c>
+      <c r="E71" t="s">
+        <v>752</v>
+      </c>
+      <c r="K71" t="s">
+        <v>1881</v>
+      </c>
+      <c r="EN71" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO71">
+        <v>515</v>
+      </c>
+      <c r="EP71">
+        <v>566</v>
+      </c>
+      <c r="EQ71" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER71" t="s">
+        <v>1157</v>
+      </c>
+      <c r="ES71">
+        <v>0</v>
+      </c>
+      <c r="ET71">
+        <v>1</v>
+      </c>
+      <c r="EU71">
+        <v>0</v>
+      </c>
+      <c r="EV71">
+        <v>1</v>
+      </c>
+      <c r="EW71">
+        <v>0</v>
+      </c>
+      <c r="EX71">
+        <v>0</v>
+      </c>
+      <c r="EZ71" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA71">
+        <v>30</v>
+      </c>
+      <c r="FB71" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC71">
+        <v>1</v>
+      </c>
+      <c r="FD71">
+        <v>1</v>
+      </c>
+      <c r="FE71">
+        <v>1</v>
+      </c>
+      <c r="FF71" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG71" t="s">
+        <v>1882</v>
+      </c>
+      <c r="FH71" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP71">
+        <v>279</v>
+      </c>
+      <c r="NQ71">
+        <v>291</v>
+      </c>
+      <c r="NS71">
+        <v>116</v>
+      </c>
+      <c r="NT71">
+        <v>163</v>
+      </c>
+      <c r="NV71">
+        <v>120</v>
+      </c>
+      <c r="NW71">
+        <v>112</v>
+      </c>
+      <c r="SD71" s="1"/>
+      <c r="UH71" t="s">
+        <v>1123</v>
+      </c>
+      <c r="ZL71" s="1"/>
+      <c r="ADO71" s="1"/>
+      <c r="ADW71" s="1"/>
+      <c r="AEA71" s="1"/>
+      <c r="AEY71">
+        <v>891945260</v>
+      </c>
+      <c r="AEZ71" t="s">
+        <v>1883</v>
+      </c>
+      <c r="AFA71" s="1">
+        <v>46307.681597222218</v>
+      </c>
+      <c r="AFC71" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE71" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AFF71" t="s">
+        <v>1884</v>
+      </c>
+      <c r="AFG71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B72" t="s">
+        <v>706</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D72" t="s">
+        <v>596</v>
+      </c>
+      <c r="E72" t="s">
+        <v>752</v>
+      </c>
+      <c r="K72" t="s">
+        <v>1881</v>
+      </c>
+      <c r="EN72" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT72">
+        <v>102</v>
+      </c>
+      <c r="FU72">
+        <v>89</v>
+      </c>
+      <c r="FV72">
+        <v>2</v>
+      </c>
+      <c r="FW72">
+        <v>1</v>
+      </c>
+      <c r="FY72">
+        <v>110</v>
+      </c>
+      <c r="FZ72">
+        <v>103</v>
+      </c>
+      <c r="GA72">
+        <v>0</v>
+      </c>
+      <c r="GB72">
+        <v>0</v>
+      </c>
+      <c r="GD72">
+        <v>79</v>
+      </c>
+      <c r="GE72">
+        <v>68</v>
+      </c>
+      <c r="GF72">
+        <v>0</v>
+      </c>
+      <c r="GG72">
+        <v>0</v>
+      </c>
+      <c r="GI72">
+        <v>5</v>
+      </c>
+      <c r="GJ72">
+        <v>3</v>
+      </c>
+      <c r="GK72">
+        <v>0</v>
+      </c>
+      <c r="GL72">
+        <v>0</v>
+      </c>
+      <c r="GN72">
+        <v>3</v>
+      </c>
+      <c r="GO72">
+        <v>8</v>
+      </c>
+      <c r="GP72">
+        <v>0</v>
+      </c>
+      <c r="GQ72">
+        <v>0</v>
+      </c>
+      <c r="GR72" t="s">
+        <v>1885</v>
+      </c>
+      <c r="GS72">
+        <v>1</v>
+      </c>
+      <c r="GT72">
+        <v>0</v>
+      </c>
+      <c r="GU72">
+        <v>1</v>
+      </c>
+      <c r="GV72">
+        <v>1</v>
+      </c>
+      <c r="GW72">
+        <v>1</v>
+      </c>
+      <c r="GX72">
+        <v>1</v>
+      </c>
+      <c r="GY72">
+        <v>1</v>
+      </c>
+      <c r="GZ72" t="s">
+        <v>1294</v>
+      </c>
+      <c r="HA72">
+        <v>1</v>
+      </c>
+      <c r="HB72">
+        <v>0</v>
+      </c>
+      <c r="HC72">
+        <v>1</v>
+      </c>
+      <c r="HD72">
+        <v>1</v>
+      </c>
+      <c r="HE72">
+        <v>0</v>
+      </c>
+      <c r="HG72" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH72" t="s">
+        <v>1886</v>
+      </c>
+      <c r="HI72" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ72" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL72" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM72" t="s">
+        <v>1887</v>
+      </c>
+      <c r="HT72" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU72">
+        <v>1</v>
+      </c>
+      <c r="HV72" t="s">
+        <v>1888</v>
+      </c>
+      <c r="HX72" t="s">
+        <v>833</v>
+      </c>
+      <c r="HY72">
+        <v>1</v>
+      </c>
+      <c r="HZ72" t="s">
+        <v>1889</v>
+      </c>
+      <c r="IB72" t="s">
+        <v>830</v>
+      </c>
+      <c r="IC72">
+        <v>1</v>
+      </c>
+      <c r="ID72" t="s">
+        <v>1890</v>
+      </c>
+      <c r="IF72" t="s">
+        <v>830</v>
+      </c>
+      <c r="IG72">
+        <v>1</v>
+      </c>
+      <c r="IH72" t="s">
+        <v>1891</v>
+      </c>
+      <c r="IJ72" t="s">
+        <v>830</v>
+      </c>
+      <c r="IK72">
+        <v>1</v>
+      </c>
+      <c r="IL72" t="s">
+        <v>1892</v>
+      </c>
+      <c r="IV72" t="s">
+        <v>835</v>
+      </c>
+      <c r="IW72" t="s">
+        <v>879</v>
+      </c>
+      <c r="IX72" t="s">
+        <v>1893</v>
+      </c>
+      <c r="IY72" t="s">
+        <v>839</v>
+      </c>
+      <c r="IZ72" t="s">
+        <v>1363</v>
+      </c>
+      <c r="JA72" t="s">
+        <v>716</v>
+      </c>
+      <c r="JC72" t="s">
+        <v>835</v>
+      </c>
+      <c r="JD72" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE72" t="s">
+        <v>1894</v>
+      </c>
+      <c r="JF72" t="s">
+        <v>839</v>
+      </c>
+      <c r="JG72" t="s">
+        <v>1895</v>
+      </c>
+      <c r="JH72" t="s">
+        <v>716</v>
+      </c>
+      <c r="JJ72" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK72" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JL72" t="s">
+        <v>1896</v>
+      </c>
+      <c r="JM72" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN72" t="s">
+        <v>1256</v>
+      </c>
+      <c r="JO72" t="s">
+        <v>720</v>
+      </c>
+      <c r="JQ72" t="s">
+        <v>837</v>
+      </c>
+      <c r="JR72" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS72" t="s">
+        <v>1897</v>
+      </c>
+      <c r="JT72" t="s">
+        <v>839</v>
+      </c>
+      <c r="JU72" t="s">
+        <v>1337</v>
+      </c>
+      <c r="JV72" t="s">
+        <v>716</v>
+      </c>
+      <c r="JX72" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY72" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ72" t="s">
+        <v>1898</v>
+      </c>
+      <c r="KA72" t="s">
+        <v>839</v>
+      </c>
+      <c r="KB72" t="s">
+        <v>1899</v>
+      </c>
+      <c r="KC72" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE72" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF72" t="s">
+        <v>769</v>
+      </c>
+      <c r="KG72" t="s">
+        <v>1900</v>
+      </c>
+      <c r="KH72" t="s">
+        <v>839</v>
+      </c>
+      <c r="KI72" t="s">
+        <v>1211</v>
+      </c>
+      <c r="KJ72" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK72" t="s">
+        <v>1901</v>
+      </c>
+      <c r="KL72">
+        <v>0</v>
+      </c>
+      <c r="KM72">
+        <v>1</v>
+      </c>
+      <c r="KN72">
+        <v>0</v>
+      </c>
+      <c r="KO72">
+        <v>0</v>
+      </c>
+      <c r="KR72" t="s">
+        <v>1902</v>
+      </c>
+      <c r="KS72" t="s">
+        <v>1903</v>
+      </c>
+      <c r="KT72" t="s">
+        <v>1904</v>
+      </c>
+      <c r="KU72" t="s">
+        <v>1905</v>
+      </c>
+      <c r="NP72">
+        <v>279</v>
+      </c>
+      <c r="NQ72">
+        <v>292</v>
+      </c>
+      <c r="NS72">
+        <v>116</v>
+      </c>
+      <c r="NT72">
+        <v>167</v>
+      </c>
+      <c r="NV72">
+        <v>120</v>
+      </c>
+      <c r="NW72">
+        <v>112</v>
+      </c>
+      <c r="SD72" s="1"/>
+      <c r="UH72" t="s">
+        <v>1906</v>
+      </c>
+      <c r="ZL72" s="1"/>
+      <c r="ADO72" s="1"/>
+      <c r="ADW72" s="1"/>
+      <c r="AEA72" s="1"/>
+      <c r="AEY72">
+        <v>891959733</v>
+      </c>
+      <c r="AEZ72" t="s">
+        <v>1907</v>
+      </c>
+      <c r="AFA72" s="1">
+        <v>46307.696469907409</v>
+      </c>
+      <c r="AFC72" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE72" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AFF72" t="s">
+        <v>1908</v>
+      </c>
+      <c r="AFG72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B73" t="s">
+        <v>706</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D73" t="s">
+        <v>596</v>
+      </c>
+      <c r="E73" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K73" t="s">
+        <v>1019</v>
+      </c>
+      <c r="NX73" t="s">
+        <v>1911</v>
+      </c>
+      <c r="NY73" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ73" t="s">
+        <v>1913</v>
+      </c>
+      <c r="OA73" t="s">
+        <v>711</v>
+      </c>
+      <c r="OB73" t="s">
+        <v>1914</v>
+      </c>
+      <c r="OC73">
+        <v>1</v>
+      </c>
+      <c r="OD73">
+        <v>1</v>
+      </c>
+      <c r="OE73">
+        <v>0</v>
+      </c>
+      <c r="OF73">
+        <v>0</v>
+      </c>
+      <c r="OG73">
+        <v>0</v>
+      </c>
+      <c r="OI73" t="s">
+        <v>1915</v>
+      </c>
+      <c r="OJ73">
+        <v>1</v>
+      </c>
+      <c r="OK73">
+        <v>1</v>
+      </c>
+      <c r="OL73">
+        <v>0</v>
+      </c>
+      <c r="OM73">
+        <v>0</v>
+      </c>
+      <c r="OS73">
+        <v>0</v>
+      </c>
+      <c r="OT73" t="s">
+        <v>863</v>
+      </c>
+      <c r="OV73">
+        <v>7</v>
+      </c>
+      <c r="OW73" t="s">
+        <v>807</v>
+      </c>
+      <c r="OY73">
+        <v>10</v>
+      </c>
+      <c r="OZ73" t="s">
+        <v>1916</v>
+      </c>
+      <c r="PB73">
+        <v>0</v>
+      </c>
+      <c r="PC73" t="s">
+        <v>1917</v>
+      </c>
+      <c r="PE73">
+        <v>0</v>
+      </c>
+      <c r="PF73" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH73">
+        <v>0</v>
+      </c>
+      <c r="PI73" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ73" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL73" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM73" t="s">
+        <v>1919</v>
+      </c>
+      <c r="PN73" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO73" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ73" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PW73" t="s">
+        <v>1922</v>
+      </c>
+      <c r="PX73">
+        <v>1</v>
+      </c>
+      <c r="PY73">
+        <v>0</v>
+      </c>
+      <c r="PZ73">
+        <v>0</v>
+      </c>
+      <c r="QA73">
+        <v>0</v>
+      </c>
+      <c r="QJ73" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK73" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL73" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM73" t="s">
+        <v>1926</v>
+      </c>
+      <c r="QN73" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP73" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ73" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR73" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QS73" t="s">
+        <v>1930</v>
+      </c>
+      <c r="QT73" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV73" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QW73" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX73" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY73" t="s">
+        <v>1931</v>
+      </c>
+      <c r="QZ73" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA73" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB73" t="s">
+        <v>711</v>
+      </c>
+      <c r="RO73" t="s">
+        <v>1932</v>
+      </c>
+      <c r="RP73" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ73" t="s">
+        <v>1933</v>
+      </c>
+      <c r="RR73" t="s">
+        <v>1934</v>
+      </c>
+      <c r="RY73" t="s">
+        <v>1935</v>
+      </c>
+      <c r="RZ73" t="s">
+        <v>1568</v>
+      </c>
+      <c r="SA73" t="s">
+        <v>1936</v>
+      </c>
+      <c r="SB73" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD73" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH73" t="s">
+        <v>1937</v>
+      </c>
+      <c r="ZL73" s="1"/>
+      <c r="ADO73" s="1"/>
+      <c r="ADW73" s="1"/>
+      <c r="AEA73" s="1"/>
+      <c r="AEV73" t="s">
+        <v>711</v>
+      </c>
+      <c r="AEY73">
+        <v>891979475</v>
+      </c>
+      <c r="AEZ73" t="s">
+        <v>1938</v>
+      </c>
+      <c r="AFA73" s="1">
+        <v>46307.717777777783</v>
+      </c>
+      <c r="AFC73" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE73" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AFF73" t="s">
+        <v>1939</v>
+      </c>
+      <c r="AFG73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B74" t="s">
+        <v>706</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D74" t="s">
+        <v>596</v>
+      </c>
+      <c r="E74" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K74" t="s">
+        <v>1881</v>
+      </c>
+      <c r="NX74" t="s">
+        <v>1940</v>
+      </c>
+      <c r="NY74" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ74" t="s">
+        <v>1941</v>
+      </c>
+      <c r="OA74" t="s">
+        <v>711</v>
+      </c>
+      <c r="OB74" t="s">
+        <v>1914</v>
+      </c>
+      <c r="OC74">
+        <v>1</v>
+      </c>
+      <c r="OD74">
+        <v>1</v>
+      </c>
+      <c r="OE74">
+        <v>0</v>
+      </c>
+      <c r="OF74">
+        <v>0</v>
+      </c>
+      <c r="OG74">
+        <v>0</v>
+      </c>
+      <c r="OI74" t="s">
+        <v>1915</v>
+      </c>
+      <c r="OJ74">
+        <v>1</v>
+      </c>
+      <c r="OK74">
+        <v>1</v>
+      </c>
+      <c r="OL74">
+        <v>0</v>
+      </c>
+      <c r="OM74">
+        <v>0</v>
+      </c>
+      <c r="OS74">
+        <v>0</v>
+      </c>
+      <c r="OT74" t="s">
+        <v>1942</v>
+      </c>
+      <c r="OV74">
+        <v>17</v>
+      </c>
+      <c r="OW74" t="s">
+        <v>819</v>
+      </c>
+      <c r="OY74">
+        <v>38</v>
+      </c>
+      <c r="OZ74" t="s">
+        <v>819</v>
+      </c>
+      <c r="PB74">
+        <v>41</v>
+      </c>
+      <c r="PC74" t="s">
+        <v>819</v>
+      </c>
+      <c r="PE74">
+        <v>1</v>
+      </c>
+      <c r="PF74" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH74">
+        <v>0</v>
+      </c>
+      <c r="PI74" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ74" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PK74" t="s">
+        <v>1943</v>
+      </c>
+      <c r="PL74" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM74" t="s">
+        <v>1944</v>
+      </c>
+      <c r="PN74" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO74" t="s">
+        <v>706</v>
+      </c>
+      <c r="PQ74" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PW74" t="s">
+        <v>1945</v>
+      </c>
+      <c r="PX74">
+        <v>0</v>
+      </c>
+      <c r="PY74">
+        <v>1</v>
+      </c>
+      <c r="PZ74">
+        <v>0</v>
+      </c>
+      <c r="QA74">
+        <v>0</v>
+      </c>
+      <c r="QJ74" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QK74" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QL74" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM74" t="s">
+        <v>1948</v>
+      </c>
+      <c r="QN74" t="s">
+        <v>720</v>
+      </c>
+      <c r="QP74" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ74" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR74" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS74" t="s">
+        <v>1949</v>
+      </c>
+      <c r="QT74" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV74" t="s">
+        <v>1950</v>
+      </c>
+      <c r="QW74" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QX74" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY74" t="s">
+        <v>1952</v>
+      </c>
+      <c r="QZ74" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA74" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB74" t="s">
+        <v>711</v>
+      </c>
+      <c r="RO74" t="s">
+        <v>1953</v>
+      </c>
+      <c r="RP74" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ74" t="s">
+        <v>1954</v>
+      </c>
+      <c r="RR74" t="s">
+        <v>1955</v>
+      </c>
+      <c r="RY74" t="s">
+        <v>1956</v>
+      </c>
+      <c r="RZ74" t="s">
+        <v>1957</v>
+      </c>
+      <c r="SA74" t="s">
+        <v>1958</v>
+      </c>
+      <c r="SB74" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD74" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH74" t="s">
+        <v>842</v>
+      </c>
+      <c r="ZL74" s="1"/>
+      <c r="ADO74" s="1"/>
+      <c r="ADW74" s="1"/>
+      <c r="AEA74" s="1"/>
+      <c r="AEV74" t="s">
+        <v>711</v>
+      </c>
+      <c r="AEY74">
+        <v>891988321</v>
+      </c>
+      <c r="AEZ74" t="s">
+        <v>1959</v>
+      </c>
+      <c r="AFA74" s="1">
+        <v>46307.728344907409</v>
+      </c>
+      <c r="AFC74" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE74" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AFF74" t="s">
+        <v>1960</v>
+      </c>
+      <c r="AFG74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B75" t="s">
+        <v>706</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D75" t="s">
+        <v>596</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K75" t="s">
+        <v>1961</v>
+      </c>
+      <c r="NX75" t="s">
+        <v>1962</v>
+      </c>
+      <c r="NY75" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ75" t="s">
+        <v>1963</v>
+      </c>
+      <c r="OA75" t="s">
+        <v>711</v>
+      </c>
+      <c r="OB75" t="s">
+        <v>1964</v>
+      </c>
+      <c r="OC75">
+        <v>0</v>
+      </c>
+      <c r="OD75">
+        <v>0</v>
+      </c>
+      <c r="OE75">
+        <v>0</v>
+      </c>
+      <c r="OF75">
+        <v>1</v>
+      </c>
+      <c r="OG75">
+        <v>0</v>
+      </c>
+      <c r="OH75" t="s">
+        <v>1965</v>
+      </c>
+      <c r="OI75" t="s">
+        <v>1966</v>
+      </c>
+      <c r="OJ75">
+        <v>0</v>
+      </c>
+      <c r="OK75">
+        <v>0</v>
+      </c>
+      <c r="OL75">
+        <v>0</v>
+      </c>
+      <c r="OM75">
+        <v>1</v>
+      </c>
+      <c r="ON75" t="s">
+        <v>1967</v>
+      </c>
+      <c r="OS75">
+        <v>19</v>
+      </c>
+      <c r="OT75" t="s">
+        <v>819</v>
+      </c>
+      <c r="OV75">
+        <v>35</v>
+      </c>
+      <c r="OW75" t="s">
+        <v>819</v>
+      </c>
+      <c r="OY75">
+        <v>0</v>
+      </c>
+      <c r="OZ75" t="s">
+        <v>819</v>
+      </c>
+      <c r="PB75">
+        <v>0</v>
+      </c>
+      <c r="PC75" t="s">
+        <v>819</v>
+      </c>
+      <c r="PE75">
+        <v>0</v>
+      </c>
+      <c r="PF75" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH75">
+        <v>0</v>
+      </c>
+      <c r="PI75" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ75" t="s">
+        <v>706</v>
+      </c>
+      <c r="PL75" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN75" t="s">
+        <v>732</v>
+      </c>
+      <c r="PO75" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ75" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PW75" t="s">
+        <v>1922</v>
+      </c>
+      <c r="PX75">
+        <v>1</v>
+      </c>
+      <c r="PY75">
+        <v>0</v>
+      </c>
+      <c r="PZ75">
+        <v>0</v>
+      </c>
+      <c r="QA75">
+        <v>0</v>
+      </c>
+      <c r="QJ75" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK75" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL75" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM75" t="s">
+        <v>1969</v>
+      </c>
+      <c r="QN75" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP75" t="s">
+        <v>1950</v>
+      </c>
+      <c r="QQ75" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR75" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS75" t="s">
+        <v>1970</v>
+      </c>
+      <c r="QT75" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV75" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QW75" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX75" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY75" t="s">
+        <v>1971</v>
+      </c>
+      <c r="QZ75" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA75" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB75" t="s">
+        <v>711</v>
+      </c>
+      <c r="RO75" t="s">
+        <v>1953</v>
+      </c>
+      <c r="RP75" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ75" t="s">
+        <v>1972</v>
+      </c>
+      <c r="RR75" t="s">
+        <v>1954</v>
+      </c>
+      <c r="RY75" t="s">
+        <v>1973</v>
+      </c>
+      <c r="RZ75" t="s">
+        <v>1957</v>
+      </c>
+      <c r="SA75" t="s">
+        <v>1974</v>
+      </c>
+      <c r="SB75" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD75" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH75" t="s">
+        <v>1123</v>
+      </c>
+      <c r="ZL75" s="1"/>
+      <c r="ADO75" s="1"/>
+      <c r="ADW75" s="1"/>
+      <c r="AEA75" s="1"/>
+      <c r="AEV75" t="s">
+        <v>732</v>
+      </c>
+      <c r="AEY75">
+        <v>891998717</v>
+      </c>
+      <c r="AEZ75" t="s">
+        <v>1975</v>
+      </c>
+      <c r="AFA75" s="1">
+        <v>46307.741666666669</v>
+      </c>
+      <c r="AFC75" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE75" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AFF75" t="s">
+        <v>1976</v>
+      </c>
+      <c r="AFG75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B76" t="s">
+        <v>706</v>
+      </c>
+      <c r="C76" t="s">
+        <v>858</v>
+      </c>
+      <c r="D76" t="s">
+        <v>597</v>
+      </c>
+      <c r="E76" t="s">
+        <v>752</v>
+      </c>
+      <c r="M76" t="s">
+        <v>899</v>
+      </c>
+      <c r="EN76" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO76">
+        <v>909</v>
+      </c>
+      <c r="EP76">
+        <v>729</v>
+      </c>
+      <c r="EQ76" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER76" t="s">
+        <v>1702</v>
+      </c>
+      <c r="ES76">
+        <v>1</v>
+      </c>
+      <c r="ET76">
+        <v>0</v>
+      </c>
+      <c r="EU76">
+        <v>0</v>
+      </c>
+      <c r="EV76">
+        <v>1</v>
+      </c>
+      <c r="EW76">
+        <v>0</v>
+      </c>
+      <c r="EX76">
+        <v>0</v>
+      </c>
+      <c r="EZ76" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA76">
+        <v>40</v>
+      </c>
+      <c r="FB76" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC76">
+        <v>1</v>
+      </c>
+      <c r="FD76">
+        <v>1</v>
+      </c>
+      <c r="FE76">
+        <v>1</v>
+      </c>
+      <c r="FF76" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG76" t="s">
+        <v>1977</v>
+      </c>
+      <c r="FH76" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP76">
+        <v>267</v>
+      </c>
+      <c r="NQ76">
+        <v>278</v>
+      </c>
+      <c r="NS76">
+        <v>207</v>
+      </c>
+      <c r="NT76">
+        <v>181</v>
+      </c>
+      <c r="NV76">
+        <v>162</v>
+      </c>
+      <c r="NW76">
+        <v>99</v>
+      </c>
+      <c r="SD76" s="1"/>
+      <c r="UH76" t="s">
+        <v>1978</v>
+      </c>
+      <c r="ZL76" s="1"/>
+      <c r="ADO76" s="1"/>
+      <c r="ADW76" s="1"/>
+      <c r="AEA76" s="1"/>
+      <c r="AEY76">
+        <v>892038081</v>
+      </c>
+      <c r="AEZ76" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AFA76" s="1">
+        <v>46307.79760416667</v>
+      </c>
+      <c r="AFC76" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF76" t="s">
+        <v>1980</v>
+      </c>
+      <c r="AFG76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B77" t="s">
+        <v>706</v>
+      </c>
+      <c r="C77" t="s">
+        <v>858</v>
+      </c>
+      <c r="D77" t="s">
+        <v>597</v>
+      </c>
+      <c r="E77" t="s">
+        <v>752</v>
+      </c>
+      <c r="M77" t="s">
+        <v>899</v>
+      </c>
+      <c r="EN77" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT77">
+        <v>109</v>
+      </c>
+      <c r="FU77">
+        <v>94</v>
+      </c>
+      <c r="FV77">
+        <v>1</v>
+      </c>
+      <c r="FW77">
+        <v>0</v>
+      </c>
+      <c r="FY77">
+        <v>130</v>
+      </c>
+      <c r="FZ77">
+        <v>109</v>
+      </c>
+      <c r="GA77">
+        <v>2</v>
+      </c>
+      <c r="GB77">
+        <v>1</v>
+      </c>
+      <c r="GD77">
+        <v>75</v>
+      </c>
+      <c r="GE77">
+        <v>55</v>
+      </c>
+      <c r="GF77">
+        <v>0</v>
+      </c>
+      <c r="GG77">
+        <v>0</v>
+      </c>
+      <c r="GI77">
+        <v>8</v>
+      </c>
+      <c r="GJ77">
+        <v>4</v>
+      </c>
+      <c r="GK77">
+        <v>0</v>
+      </c>
+      <c r="GL77">
+        <v>0</v>
+      </c>
+      <c r="GN77">
+        <v>2</v>
+      </c>
+      <c r="GO77">
+        <v>1</v>
+      </c>
+      <c r="GP77">
+        <v>0</v>
+      </c>
+      <c r="GQ77">
+        <v>0</v>
+      </c>
+      <c r="GR77" t="s">
+        <v>871</v>
+      </c>
+      <c r="GS77">
+        <v>1</v>
+      </c>
+      <c r="GT77">
+        <v>0</v>
+      </c>
+      <c r="GU77">
+        <v>0</v>
+      </c>
+      <c r="GV77">
+        <v>1</v>
+      </c>
+      <c r="GW77">
+        <v>0</v>
+      </c>
+      <c r="GX77">
+        <v>0</v>
+      </c>
+      <c r="GY77">
+        <v>1</v>
+      </c>
+      <c r="GZ77" t="s">
+        <v>1578</v>
+      </c>
+      <c r="HA77">
+        <v>1</v>
+      </c>
+      <c r="HB77">
+        <v>1</v>
+      </c>
+      <c r="HC77">
+        <v>1</v>
+      </c>
+      <c r="HD77">
+        <v>1</v>
+      </c>
+      <c r="HE77">
+        <v>1</v>
+      </c>
+      <c r="HF77" t="s">
+        <v>1981</v>
+      </c>
+      <c r="HG77" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH77" t="s">
+        <v>1982</v>
+      </c>
+      <c r="HI77" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ77" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL77" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM77" t="s">
+        <v>1983</v>
+      </c>
+      <c r="HT77" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU77">
+        <v>360</v>
+      </c>
+      <c r="HV77" t="s">
+        <v>1984</v>
+      </c>
+      <c r="HX77" t="s">
+        <v>766</v>
+      </c>
+      <c r="HY77">
+        <v>380</v>
+      </c>
+      <c r="HZ77" t="s">
+        <v>1985</v>
+      </c>
+      <c r="IB77" t="s">
+        <v>765</v>
+      </c>
+      <c r="IC77">
+        <v>400</v>
+      </c>
+      <c r="ID77" t="s">
+        <v>1986</v>
+      </c>
+      <c r="IF77" t="s">
+        <v>765</v>
+      </c>
+      <c r="IG77">
+        <v>405</v>
+      </c>
+      <c r="IH77" t="s">
+        <v>1987</v>
+      </c>
+      <c r="IJ77" t="s">
+        <v>765</v>
+      </c>
+      <c r="IK77">
+        <v>401</v>
+      </c>
+      <c r="IL77" t="s">
+        <v>1988</v>
+      </c>
+      <c r="IV77" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW77" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX77" t="s">
+        <v>1989</v>
+      </c>
+      <c r="IY77" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ77" t="s">
+        <v>1990</v>
+      </c>
+      <c r="JA77" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC77" t="s">
+        <v>835</v>
+      </c>
+      <c r="JD77" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JE77" t="s">
+        <v>1991</v>
+      </c>
+      <c r="JF77" t="s">
+        <v>839</v>
+      </c>
+      <c r="JG77" t="s">
+        <v>1991</v>
+      </c>
+      <c r="JH77" t="s">
+        <v>716</v>
+      </c>
+      <c r="JJ77" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK77" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL77" t="s">
+        <v>1992</v>
+      </c>
+      <c r="JM77" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN77" t="s">
+        <v>1993</v>
+      </c>
+      <c r="JO77" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ77" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR77" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS77" t="s">
+        <v>1994</v>
+      </c>
+      <c r="JT77" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU77" t="s">
+        <v>1995</v>
+      </c>
+      <c r="JV77" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX77" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY77" t="s">
+        <v>879</v>
+      </c>
+      <c r="JZ77" t="s">
+        <v>1996</v>
+      </c>
+      <c r="KA77" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB77" t="s">
+        <v>1997</v>
+      </c>
+      <c r="KC77" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE77" t="s">
+        <v>835</v>
+      </c>
+      <c r="KF77" t="s">
+        <v>1143</v>
+      </c>
+      <c r="KG77" t="s">
+        <v>1998</v>
+      </c>
+      <c r="KH77" t="s">
+        <v>839</v>
+      </c>
+      <c r="KI77" t="s">
+        <v>1991</v>
+      </c>
+      <c r="KJ77" t="s">
+        <v>720</v>
+      </c>
+      <c r="KK77" t="s">
+        <v>1999</v>
+      </c>
+      <c r="KL77">
+        <v>0</v>
+      </c>
+      <c r="KM77">
+        <v>1</v>
+      </c>
+      <c r="KN77">
+        <v>0</v>
+      </c>
+      <c r="KO77">
+        <v>0</v>
+      </c>
+      <c r="KP77">
+        <v>1</v>
+      </c>
+      <c r="KR77" t="s">
+        <v>2000</v>
+      </c>
+      <c r="KS77" t="s">
+        <v>2001</v>
+      </c>
+      <c r="KT77" t="s">
+        <v>2002</v>
+      </c>
+      <c r="KU77" t="s">
+        <v>2003</v>
+      </c>
+      <c r="NP77">
+        <v>267</v>
+      </c>
+      <c r="NQ77">
+        <v>278</v>
+      </c>
+      <c r="NS77">
+        <v>207</v>
+      </c>
+      <c r="NT77">
+        <v>181</v>
+      </c>
+      <c r="NV77">
+        <v>162</v>
+      </c>
+      <c r="NW77">
+        <v>99</v>
+      </c>
+      <c r="SD77" s="1"/>
+      <c r="UH77" t="s">
+        <v>2004</v>
+      </c>
+      <c r="ZL77" s="1"/>
+      <c r="ADO77" s="1"/>
+      <c r="ADW77" s="1"/>
+      <c r="AEA77" s="1"/>
+      <c r="AEY77">
+        <v>892061737</v>
+      </c>
+      <c r="AEZ77" t="s">
+        <v>2005</v>
+      </c>
+      <c r="AFA77" s="1">
+        <v>46307.835381944453</v>
+      </c>
+      <c r="AFC77" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE77" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF77" t="s">
+        <v>2006</v>
+      </c>
+      <c r="AFG77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B78" t="s">
+        <v>773</v>
+      </c>
+      <c r="D78" t="s">
+        <v>593</v>
+      </c>
+      <c r="E78" t="s">
+        <v>738</v>
+      </c>
+      <c r="H78" t="s">
+        <v>1032</v>
+      </c>
+      <c r="SD78" s="1"/>
+      <c r="SV78" t="s">
+        <v>2007</v>
+      </c>
+      <c r="SW78">
+        <v>0</v>
+      </c>
+      <c r="SX78">
+        <v>1</v>
+      </c>
+      <c r="TQ78" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TR78" t="s">
+        <v>743</v>
+      </c>
+      <c r="TS78" t="s">
+        <v>2008</v>
+      </c>
+      <c r="TT78">
+        <v>104</v>
+      </c>
+      <c r="TU78">
+        <v>57</v>
+      </c>
+      <c r="TV78">
+        <v>1</v>
+      </c>
+      <c r="TW78">
+        <v>0</v>
+      </c>
+      <c r="TX78" t="s">
+        <v>2009</v>
+      </c>
+      <c r="TY78">
+        <v>0</v>
+      </c>
+      <c r="TZ78">
+        <v>0</v>
+      </c>
+      <c r="UA78">
+        <v>1</v>
+      </c>
+      <c r="UB78">
+        <v>1</v>
+      </c>
+      <c r="UC78">
+        <v>1</v>
+      </c>
+      <c r="UD78" t="s">
+        <v>2010</v>
+      </c>
+      <c r="UE78" s="1">
+        <v>46303</v>
+      </c>
+      <c r="UF78" t="s">
+        <v>2011</v>
+      </c>
+      <c r="UG78" t="s">
+        <v>2012</v>
+      </c>
+      <c r="UH78" t="s">
+        <v>2013</v>
+      </c>
+      <c r="ZL78" s="1"/>
+      <c r="ADO78" s="1"/>
+      <c r="ADW78" s="1"/>
+      <c r="AEA78" s="1"/>
+      <c r="AEY78">
+        <v>892138361</v>
+      </c>
+      <c r="AEZ78" t="s">
+        <v>2014</v>
+      </c>
+      <c r="AFA78" s="1">
+        <v>46308.07099537037</v>
+      </c>
+      <c r="AFC78" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE78" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AFF78" t="s">
+        <v>2015</v>
+      </c>
+      <c r="AFG78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B79" t="s">
+        <v>773</v>
+      </c>
+      <c r="D79" t="s">
+        <v>593</v>
+      </c>
+      <c r="E79" t="s">
+        <v>738</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1060</v>
+      </c>
+      <c r="SD79" s="1"/>
+      <c r="SV79" t="s">
+        <v>2007</v>
+      </c>
+      <c r="SW79">
+        <v>0</v>
+      </c>
+      <c r="SX79">
+        <v>1</v>
+      </c>
+      <c r="TQ79" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TR79" t="s">
+        <v>2016</v>
+      </c>
+      <c r="TS79" t="s">
+        <v>1036</v>
+      </c>
+      <c r="TT79">
+        <v>114</v>
+      </c>
+      <c r="TU79">
+        <v>91</v>
+      </c>
+      <c r="TV79">
+        <v>1</v>
+      </c>
+      <c r="TW79">
+        <v>2</v>
+      </c>
+      <c r="TX79" t="s">
+        <v>1037</v>
+      </c>
+      <c r="TY79">
+        <v>1</v>
+      </c>
+      <c r="TZ79">
+        <v>1</v>
+      </c>
+      <c r="UA79">
+        <v>1</v>
+      </c>
+      <c r="UB79">
+        <v>1</v>
+      </c>
+      <c r="UC79">
+        <v>1</v>
+      </c>
+      <c r="UD79" t="s">
+        <v>2010</v>
+      </c>
+      <c r="UE79" s="1">
+        <v>46303</v>
+      </c>
+      <c r="UF79" t="s">
+        <v>2017</v>
+      </c>
+      <c r="UG79" t="s">
+        <v>2018</v>
+      </c>
+      <c r="UH79" t="s">
+        <v>2019</v>
+      </c>
+      <c r="ZL79" s="1"/>
+      <c r="ADO79" s="1"/>
+      <c r="ADW79" s="1"/>
+      <c r="AEA79" s="1"/>
+      <c r="AEY79">
+        <v>892140218</v>
+      </c>
+      <c r="AEZ79" t="s">
+        <v>2020</v>
+      </c>
+      <c r="AFA79" s="1">
+        <v>46308.077997685177</v>
+      </c>
+      <c r="AFC79" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE79" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF79" t="s">
+        <v>2021</v>
+      </c>
+      <c r="AFG79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B80" t="s">
+        <v>773</v>
+      </c>
+      <c r="D80" t="s">
+        <v>593</v>
+      </c>
+      <c r="E80" t="s">
+        <v>738</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1078</v>
+      </c>
+      <c r="SD80" s="1"/>
+      <c r="SV80" t="s">
+        <v>2007</v>
+      </c>
+      <c r="SW80">
+        <v>0</v>
+      </c>
+      <c r="SX80">
+        <v>1</v>
+      </c>
+      <c r="TQ80" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TR80" t="s">
+        <v>2022</v>
+      </c>
+      <c r="TS80" t="s">
+        <v>1036</v>
+      </c>
+      <c r="TT80">
+        <v>31</v>
+      </c>
+      <c r="TU80">
+        <v>29</v>
+      </c>
+      <c r="TV80">
+        <v>3</v>
+      </c>
+      <c r="TW80">
+        <v>1</v>
+      </c>
+      <c r="TX80" t="s">
+        <v>1037</v>
+      </c>
+      <c r="TY80">
+        <v>1</v>
+      </c>
+      <c r="TZ80">
+        <v>1</v>
+      </c>
+      <c r="UA80">
+        <v>1</v>
+      </c>
+      <c r="UB80">
+        <v>1</v>
+      </c>
+      <c r="UC80">
+        <v>1</v>
+      </c>
+      <c r="UD80" t="s">
+        <v>2010</v>
+      </c>
+      <c r="UE80" s="1">
+        <v>46303</v>
+      </c>
+      <c r="UF80" t="s">
+        <v>2023</v>
+      </c>
+      <c r="UG80" t="s">
+        <v>2018</v>
+      </c>
+      <c r="UH80" t="s">
+        <v>2024</v>
+      </c>
+      <c r="ZL80" s="1"/>
+      <c r="ADO80" s="1"/>
+      <c r="ADW80" s="1"/>
+      <c r="AEA80" s="1"/>
+      <c r="AEY80">
+        <v>892141499</v>
+      </c>
+      <c r="AEZ80" t="s">
+        <v>2025</v>
+      </c>
+      <c r="AFA80" s="1">
+        <v>46308.081863425927</v>
+      </c>
+      <c r="AFC80" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE80" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF80" t="s">
+        <v>2026</v>
+      </c>
+      <c r="AFG80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B81" t="s">
+        <v>773</v>
+      </c>
+      <c r="D81" t="s">
+        <v>593</v>
+      </c>
+      <c r="E81" t="s">
+        <v>738</v>
+      </c>
+      <c r="H81" t="s">
+        <v>774</v>
+      </c>
+      <c r="SD81" s="1"/>
+      <c r="SV81" t="s">
+        <v>2007</v>
+      </c>
+      <c r="SW81">
+        <v>0</v>
+      </c>
+      <c r="SX81">
+        <v>1</v>
+      </c>
+      <c r="TQ81" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TR81" t="s">
+        <v>2027</v>
+      </c>
+      <c r="TS81" t="s">
+        <v>998</v>
+      </c>
+      <c r="TT81">
+        <v>312</v>
+      </c>
+      <c r="TU81">
+        <v>143</v>
+      </c>
+      <c r="TV81">
+        <v>2</v>
+      </c>
+      <c r="TW81">
+        <v>3</v>
+      </c>
+      <c r="TX81" t="s">
+        <v>1037</v>
+      </c>
+      <c r="TY81">
+        <v>1</v>
+      </c>
+      <c r="TZ81">
+        <v>1</v>
+      </c>
+      <c r="UA81">
+        <v>1</v>
+      </c>
+      <c r="UB81">
+        <v>1</v>
+      </c>
+      <c r="UC81">
+        <v>1</v>
+      </c>
+      <c r="UD81" t="s">
+        <v>2010</v>
+      </c>
+      <c r="UE81" s="1">
+        <v>46303</v>
+      </c>
+      <c r="UF81" t="s">
+        <v>2028</v>
+      </c>
+      <c r="UG81" t="s">
+        <v>2018</v>
+      </c>
+      <c r="UH81" t="s">
+        <v>2029</v>
+      </c>
+      <c r="ZL81" s="1"/>
+      <c r="ADO81" s="1"/>
+      <c r="ADW81" s="1"/>
+      <c r="AEA81" s="1"/>
+      <c r="AEY81">
+        <v>892143661</v>
+      </c>
+      <c r="AEZ81" t="s">
+        <v>2030</v>
+      </c>
+      <c r="AFA81" s="1">
+        <v>46308.088587962957</v>
+      </c>
+      <c r="AFC81" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE81" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF81" t="s">
+        <v>2031</v>
+      </c>
+      <c r="AFG81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B82" t="s">
+        <v>773</v>
+      </c>
+      <c r="D82" t="s">
+        <v>593</v>
+      </c>
+      <c r="E82" t="s">
+        <v>738</v>
+      </c>
+      <c r="H82" t="s">
+        <v>981</v>
+      </c>
+      <c r="SD82" s="1"/>
+      <c r="SV82" t="s">
+        <v>2007</v>
+      </c>
+      <c r="SW82">
+        <v>0</v>
+      </c>
+      <c r="SX82">
+        <v>1</v>
+      </c>
+      <c r="TQ82" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TR82" t="s">
+        <v>2032</v>
+      </c>
+      <c r="TS82" t="s">
+        <v>2033</v>
+      </c>
+      <c r="TT82">
+        <v>212</v>
+      </c>
+      <c r="TU82">
+        <v>146</v>
+      </c>
+      <c r="TV82">
+        <v>2</v>
+      </c>
+      <c r="TW82">
+        <v>3</v>
+      </c>
+      <c r="TX82" t="s">
+        <v>2034</v>
+      </c>
+      <c r="TY82">
+        <v>1</v>
+      </c>
+      <c r="TZ82">
+        <v>0</v>
+      </c>
+      <c r="UA82">
+        <v>1</v>
+      </c>
+      <c r="UB82">
+        <v>1</v>
+      </c>
+      <c r="UC82">
+        <v>0</v>
+      </c>
+      <c r="UD82" t="s">
+        <v>2010</v>
+      </c>
+      <c r="UE82" s="1">
+        <v>46303</v>
+      </c>
+      <c r="UF82" t="s">
+        <v>2035</v>
+      </c>
+      <c r="UG82" t="s">
+        <v>2012</v>
+      </c>
+      <c r="UH82" t="s">
+        <v>2036</v>
+      </c>
+      <c r="ZL82" s="1"/>
+      <c r="ADO82" s="1"/>
+      <c r="ADW82" s="1"/>
+      <c r="AEA82" s="1"/>
+      <c r="AEY82">
+        <v>892145084</v>
+      </c>
+      <c r="AEZ82" t="s">
+        <v>2037</v>
+      </c>
+      <c r="AFA82" s="1">
+        <v>46308.092847222222</v>
+      </c>
+      <c r="AFC82" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE82" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF82" t="s">
+        <v>2038</v>
+      </c>
+      <c r="AFG82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B83" t="s">
+        <v>773</v>
+      </c>
+      <c r="D83" t="s">
+        <v>593</v>
+      </c>
+      <c r="E83" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H83" t="s">
+        <v>774</v>
+      </c>
+      <c r="NX83" t="s">
+        <v>2039</v>
+      </c>
+      <c r="NY83" t="s">
+        <v>2040</v>
+      </c>
+      <c r="OA83" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS83">
+        <v>21</v>
+      </c>
+      <c r="OT83" t="s">
+        <v>2041</v>
+      </c>
+      <c r="OV83">
+        <v>17</v>
+      </c>
+      <c r="OW83" t="s">
+        <v>762</v>
+      </c>
+      <c r="OY83">
+        <v>6</v>
+      </c>
+      <c r="OZ83" t="s">
+        <v>831</v>
+      </c>
+      <c r="PB83">
+        <v>2</v>
+      </c>
+      <c r="PC83" t="s">
+        <v>819</v>
+      </c>
+      <c r="PE83">
+        <v>0</v>
+      </c>
+      <c r="PF83" t="s">
+        <v>807</v>
+      </c>
+      <c r="PH83">
+        <v>0</v>
+      </c>
+      <c r="PI83" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ83" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL83" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM83" t="s">
+        <v>2042</v>
+      </c>
+      <c r="PN83" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO83" t="s">
+        <v>2043</v>
+      </c>
+      <c r="PQ83" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR83" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS83">
+        <v>0</v>
+      </c>
+      <c r="PT83">
+        <v>0</v>
+      </c>
+      <c r="PU83">
+        <v>1</v>
+      </c>
+      <c r="PV83" t="s">
+        <v>2045</v>
+      </c>
+      <c r="PW83" t="s">
+        <v>2046</v>
+      </c>
+      <c r="PX83">
+        <v>0</v>
+      </c>
+      <c r="PY83">
+        <v>0</v>
+      </c>
+      <c r="PZ83">
+        <v>0</v>
+      </c>
+      <c r="QA83">
+        <v>1</v>
+      </c>
+      <c r="QJ83" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK83" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QL83" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM83" t="s">
+        <v>2047</v>
+      </c>
+      <c r="QN83" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP83" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ83" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR83" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS83" t="s">
+        <v>2048</v>
+      </c>
+      <c r="QT83" t="s">
+        <v>720</v>
+      </c>
+      <c r="QV83" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW83" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX83" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QY83" t="s">
+        <v>2049</v>
+      </c>
+      <c r="QZ83" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA83" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB83" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC83" t="s">
+        <v>2050</v>
+      </c>
+      <c r="RD83">
+        <v>0</v>
+      </c>
+      <c r="RE83">
+        <v>1</v>
+      </c>
+      <c r="RF83">
+        <v>0</v>
+      </c>
+      <c r="RG83">
+        <v>0</v>
+      </c>
+      <c r="RH83">
+        <v>0</v>
+      </c>
+      <c r="RJ83" t="s">
+        <v>2051</v>
+      </c>
+      <c r="RK83">
+        <v>1</v>
+      </c>
+      <c r="RL83">
+        <v>0</v>
+      </c>
+      <c r="RM83">
+        <v>0</v>
+      </c>
+      <c r="RO83" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP83" t="s">
+        <v>732</v>
+      </c>
+      <c r="RQ83" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR83" t="s">
+        <v>2054</v>
+      </c>
+      <c r="RS83" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT83" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY83" t="s">
+        <v>2055</v>
+      </c>
+      <c r="RZ83" t="s">
+        <v>1957</v>
+      </c>
+      <c r="SA83" t="s">
+        <v>2056</v>
+      </c>
+      <c r="SB83" t="s">
+        <v>711</v>
+      </c>
+      <c r="SC83" t="s">
+        <v>2057</v>
+      </c>
+      <c r="SD83" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH83" t="s">
+        <v>2058</v>
+      </c>
+      <c r="ZL83" s="1"/>
+      <c r="ADO83" s="1"/>
+      <c r="ADW83" s="1"/>
+      <c r="AEA83" s="1"/>
+      <c r="AEY83">
+        <v>892151728</v>
+      </c>
+      <c r="AEZ83" t="s">
+        <v>2059</v>
+      </c>
+      <c r="AFA83" s="1">
+        <v>46308.109895833331</v>
+      </c>
+      <c r="AFC83" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE83" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF83" t="s">
+        <v>2060</v>
+      </c>
+      <c r="AFG83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B84" t="s">
+        <v>773</v>
+      </c>
+      <c r="D84" t="s">
+        <v>593</v>
+      </c>
+      <c r="E84" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H84" t="s">
+        <v>774</v>
+      </c>
+      <c r="NX84" t="s">
+        <v>2061</v>
+      </c>
+      <c r="NY84" t="s">
+        <v>2040</v>
+      </c>
+      <c r="OA84" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS84">
+        <v>27</v>
+      </c>
+      <c r="OT84" t="s">
+        <v>2062</v>
+      </c>
+      <c r="OV84">
+        <v>17</v>
+      </c>
+      <c r="OW84" t="s">
+        <v>760</v>
+      </c>
+      <c r="OY84">
+        <v>14</v>
+      </c>
+      <c r="OZ84" t="s">
+        <v>812</v>
+      </c>
+      <c r="PB84">
+        <v>2</v>
+      </c>
+      <c r="PC84" t="s">
+        <v>822</v>
+      </c>
+      <c r="PE84">
+        <v>0</v>
+      </c>
+      <c r="PF84" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH84">
+        <v>0</v>
+      </c>
+      <c r="PI84" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ84" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL84" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM84" t="s">
+        <v>2063</v>
+      </c>
+      <c r="PN84" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO84" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ84" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR84" t="s">
+        <v>2064</v>
+      </c>
+      <c r="PS84">
+        <v>1</v>
+      </c>
+      <c r="PT84">
+        <v>1</v>
+      </c>
+      <c r="PU84">
+        <v>0</v>
+      </c>
+      <c r="PW84" t="s">
+        <v>2065</v>
+      </c>
+      <c r="PX84">
+        <v>1</v>
+      </c>
+      <c r="PY84">
+        <v>1</v>
+      </c>
+      <c r="PZ84">
+        <v>0</v>
+      </c>
+      <c r="QA84">
+        <v>1</v>
+      </c>
+      <c r="QJ84" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK84" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL84" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM84" t="s">
+        <v>2066</v>
+      </c>
+      <c r="QN84" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP84" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QQ84" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QR84" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QS84" t="s">
+        <v>2067</v>
+      </c>
+      <c r="QT84" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV84" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW84" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QX84" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY84" t="s">
+        <v>2068</v>
+      </c>
+      <c r="QZ84" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA84" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB84" t="s">
+        <v>732</v>
+      </c>
+      <c r="RC84" t="s">
+        <v>2069</v>
+      </c>
+      <c r="RD84">
+        <v>0</v>
+      </c>
+      <c r="RE84">
+        <v>1</v>
+      </c>
+      <c r="RF84">
+        <v>1</v>
+      </c>
+      <c r="RG84">
+        <v>1</v>
+      </c>
+      <c r="RH84">
+        <v>0</v>
+      </c>
+      <c r="RJ84" t="s">
+        <v>2070</v>
+      </c>
+      <c r="RK84">
+        <v>1</v>
+      </c>
+      <c r="RL84">
+        <v>1</v>
+      </c>
+      <c r="RM84">
+        <v>0</v>
+      </c>
+      <c r="RO84" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP84" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ84" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR84" t="s">
+        <v>2071</v>
+      </c>
+      <c r="RS84" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT84" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY84" t="s">
+        <v>2072</v>
+      </c>
+      <c r="RZ84" t="s">
+        <v>1912</v>
+      </c>
+      <c r="SA84" t="s">
+        <v>2073</v>
+      </c>
+      <c r="SB84" t="s">
+        <v>711</v>
+      </c>
+      <c r="SC84" t="s">
+        <v>2074</v>
+      </c>
+      <c r="SD84" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH84" t="s">
+        <v>2075</v>
+      </c>
+      <c r="ZL84" s="1"/>
+      <c r="ADO84" s="1"/>
+      <c r="ADW84" s="1"/>
+      <c r="AEA84" s="1"/>
+      <c r="AEY84">
+        <v>892154562</v>
+      </c>
+      <c r="AEZ84" t="s">
+        <v>2076</v>
+      </c>
+      <c r="AFA84" s="1">
+        <v>46308.119733796288</v>
+      </c>
+      <c r="AFC84" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE84" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF84" t="s">
+        <v>2077</v>
+      </c>
+      <c r="AFG84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B85" t="s">
+        <v>773</v>
+      </c>
+      <c r="D85" t="s">
+        <v>593</v>
+      </c>
+      <c r="E85" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H85" t="s">
+        <v>774</v>
+      </c>
+      <c r="NX85" t="s">
+        <v>2078</v>
+      </c>
+      <c r="NY85" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ85" t="s">
+        <v>2079</v>
+      </c>
+      <c r="OA85" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS85">
+        <v>27</v>
+      </c>
+      <c r="OT85" t="s">
+        <v>2080</v>
+      </c>
+      <c r="OV85">
+        <v>16</v>
+      </c>
+      <c r="OW85" t="s">
+        <v>767</v>
+      </c>
+      <c r="OY85">
+        <v>3</v>
+      </c>
+      <c r="OZ85" t="s">
+        <v>2081</v>
+      </c>
+      <c r="PB85">
+        <v>1</v>
+      </c>
+      <c r="PC85" t="s">
+        <v>807</v>
+      </c>
+      <c r="PE85">
+        <v>1</v>
+      </c>
+      <c r="PF85" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH85">
+        <v>0</v>
+      </c>
+      <c r="PI85" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ85" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL85" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM85" t="s">
+        <v>2082</v>
+      </c>
+      <c r="PN85" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO85" t="s">
+        <v>2043</v>
+      </c>
+      <c r="PQ85" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR85" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS85">
+        <v>0</v>
+      </c>
+      <c r="PT85">
+        <v>0</v>
+      </c>
+      <c r="PU85">
+        <v>1</v>
+      </c>
+      <c r="PV85" t="s">
+        <v>2083</v>
+      </c>
+      <c r="PW85" t="s">
+        <v>2084</v>
+      </c>
+      <c r="PX85">
+        <v>0</v>
+      </c>
+      <c r="PY85">
+        <v>1</v>
+      </c>
+      <c r="PZ85">
+        <v>1</v>
+      </c>
+      <c r="QA85">
+        <v>1</v>
+      </c>
+      <c r="QJ85" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK85" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QL85" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM85" t="s">
+        <v>2085</v>
+      </c>
+      <c r="QN85" t="s">
+        <v>720</v>
+      </c>
+      <c r="QP85" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ85" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QR85" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS85" t="s">
+        <v>2086</v>
+      </c>
+      <c r="QT85" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV85" t="s">
+        <v>2087</v>
+      </c>
+      <c r="QW85" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QX85" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QY85" t="s">
+        <v>2088</v>
+      </c>
+      <c r="QZ85" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA85" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB85" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC85" t="s">
+        <v>2069</v>
+      </c>
+      <c r="RD85">
+        <v>0</v>
+      </c>
+      <c r="RE85">
+        <v>1</v>
+      </c>
+      <c r="RF85">
+        <v>1</v>
+      </c>
+      <c r="RG85">
+        <v>1</v>
+      </c>
+      <c r="RH85">
+        <v>0</v>
+      </c>
+      <c r="RJ85" t="s">
+        <v>2089</v>
+      </c>
+      <c r="RK85">
+        <v>1</v>
+      </c>
+      <c r="RL85">
+        <v>1</v>
+      </c>
+      <c r="RM85">
+        <v>1</v>
+      </c>
+      <c r="RN85" t="s">
+        <v>2090</v>
+      </c>
+      <c r="RO85" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP85" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ85" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR85" t="s">
+        <v>2091</v>
+      </c>
+      <c r="RS85" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT85" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY85" t="s">
+        <v>2092</v>
+      </c>
+      <c r="RZ85" t="s">
+        <v>2093</v>
+      </c>
+      <c r="SA85" t="s">
+        <v>2094</v>
+      </c>
+      <c r="SB85" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD85" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH85" t="s">
+        <v>2095</v>
+      </c>
+      <c r="ZL85" s="1"/>
+      <c r="ADO85" s="1"/>
+      <c r="ADW85" s="1"/>
+      <c r="AEA85" s="1"/>
+      <c r="AEY85">
+        <v>892160242</v>
+      </c>
+      <c r="AEZ85" t="s">
+        <v>2096</v>
+      </c>
+      <c r="AFA85" s="1">
+        <v>46308.136921296304</v>
+      </c>
+      <c r="AFC85" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE85" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF85" t="s">
+        <v>2097</v>
+      </c>
+      <c r="AFG85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B86" t="s">
+        <v>773</v>
+      </c>
+      <c r="D86" t="s">
+        <v>593</v>
+      </c>
+      <c r="E86" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H86" t="s">
+        <v>981</v>
+      </c>
+      <c r="NX86" t="s">
+        <v>2098</v>
+      </c>
+      <c r="NY86" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ86" t="s">
+        <v>2099</v>
+      </c>
+      <c r="OA86" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS86">
+        <v>42</v>
+      </c>
+      <c r="OT86" t="s">
+        <v>2100</v>
+      </c>
+      <c r="OV86">
+        <v>14</v>
+      </c>
+      <c r="OW86" t="s">
+        <v>767</v>
+      </c>
+      <c r="OY86">
+        <v>18</v>
+      </c>
+      <c r="OZ86" t="s">
+        <v>838</v>
+      </c>
+      <c r="PB86">
+        <v>11</v>
+      </c>
+      <c r="PC86" t="s">
+        <v>810</v>
+      </c>
+      <c r="PE86">
+        <v>1</v>
+      </c>
+      <c r="PF86" t="s">
+        <v>840</v>
+      </c>
+      <c r="PH86">
+        <v>1</v>
+      </c>
+      <c r="PI86" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ86" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL86" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM86" t="s">
+        <v>2101</v>
+      </c>
+      <c r="PN86" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO86" t="s">
+        <v>2043</v>
+      </c>
+      <c r="PQ86" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR86" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS86">
+        <v>0</v>
+      </c>
+      <c r="PT86">
+        <v>0</v>
+      </c>
+      <c r="PU86">
+        <v>1</v>
+      </c>
+      <c r="PV86" t="s">
+        <v>2102</v>
+      </c>
+      <c r="PW86" t="s">
+        <v>2103</v>
+      </c>
+      <c r="PX86">
+        <v>1</v>
+      </c>
+      <c r="PY86">
+        <v>1</v>
+      </c>
+      <c r="PZ86">
+        <v>0</v>
+      </c>
+      <c r="QA86">
+        <v>0</v>
+      </c>
+      <c r="QJ86" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK86" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL86" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QM86" t="s">
+        <v>2104</v>
+      </c>
+      <c r="QN86" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP86" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ86" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR86" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QS86" t="s">
+        <v>2105</v>
+      </c>
+      <c r="QT86" t="s">
+        <v>720</v>
+      </c>
+      <c r="QV86" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QW86" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QX86" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QY86" t="s">
+        <v>2106</v>
+      </c>
+      <c r="QZ86" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA86" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB86" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC86" t="s">
+        <v>2107</v>
+      </c>
+      <c r="RD86">
+        <v>0</v>
+      </c>
+      <c r="RE86">
+        <v>1</v>
+      </c>
+      <c r="RF86">
+        <v>1</v>
+      </c>
+      <c r="RG86">
+        <v>0</v>
+      </c>
+      <c r="RH86">
+        <v>0</v>
+      </c>
+      <c r="RJ86" t="s">
+        <v>2108</v>
+      </c>
+      <c r="RK86">
+        <v>1</v>
+      </c>
+      <c r="RL86">
+        <v>0</v>
+      </c>
+      <c r="RM86">
+        <v>1</v>
+      </c>
+      <c r="RN86" t="s">
+        <v>2109</v>
+      </c>
+      <c r="RO86" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP86" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ86" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR86" t="s">
+        <v>2110</v>
+      </c>
+      <c r="RS86" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT86" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY86" t="s">
+        <v>2111</v>
+      </c>
+      <c r="RZ86" t="s">
+        <v>2112</v>
+      </c>
+      <c r="SA86" t="s">
+        <v>2113</v>
+      </c>
+      <c r="SB86" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD86" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH86" t="s">
+        <v>2114</v>
+      </c>
+      <c r="ZL86" s="1"/>
+      <c r="ADO86" s="1"/>
+      <c r="ADW86" s="1"/>
+      <c r="AEA86" s="1"/>
+      <c r="AEY86">
+        <v>892163668</v>
+      </c>
+      <c r="AEZ86" t="s">
+        <v>2115</v>
+      </c>
+      <c r="AFA86" s="1">
+        <v>46308.148136574076</v>
+      </c>
+      <c r="AFC86" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE86" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF86" t="s">
+        <v>2116</v>
+      </c>
+      <c r="AFG86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B87" t="s">
+        <v>773</v>
+      </c>
+      <c r="D87" t="s">
+        <v>593</v>
+      </c>
+      <c r="E87" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H87" t="s">
+        <v>981</v>
+      </c>
+      <c r="NX87" t="s">
+        <v>2117</v>
+      </c>
+      <c r="NY87" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ87" t="s">
+        <v>2118</v>
+      </c>
+      <c r="OA87" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS87">
+        <v>21</v>
+      </c>
+      <c r="OT87" t="s">
+        <v>2119</v>
+      </c>
+      <c r="OV87">
+        <v>12</v>
+      </c>
+      <c r="OW87" t="s">
+        <v>2120</v>
+      </c>
+      <c r="OY87">
+        <v>14</v>
+      </c>
+      <c r="OZ87" t="s">
+        <v>759</v>
+      </c>
+      <c r="PB87">
+        <v>12</v>
+      </c>
+      <c r="PC87" t="s">
+        <v>812</v>
+      </c>
+      <c r="PE87">
+        <v>1</v>
+      </c>
+      <c r="PF87" t="s">
+        <v>840</v>
+      </c>
+      <c r="PH87">
+        <v>1</v>
+      </c>
+      <c r="PI87" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ87" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL87" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM87" t="s">
+        <v>2121</v>
+      </c>
+      <c r="PN87" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO87" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ87" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR87" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS87">
+        <v>0</v>
+      </c>
+      <c r="PT87">
+        <v>0</v>
+      </c>
+      <c r="PU87">
+        <v>1</v>
+      </c>
+      <c r="PV87" t="s">
+        <v>2122</v>
+      </c>
+      <c r="PW87" t="s">
+        <v>2123</v>
+      </c>
+      <c r="PX87">
+        <v>1</v>
+      </c>
+      <c r="PY87">
+        <v>1</v>
+      </c>
+      <c r="PZ87">
+        <v>1</v>
+      </c>
+      <c r="QA87">
+        <v>1</v>
+      </c>
+      <c r="QJ87" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK87" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QL87" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM87" t="s">
+        <v>2124</v>
+      </c>
+      <c r="QN87" t="s">
+        <v>720</v>
+      </c>
+      <c r="QP87" t="s">
+        <v>1950</v>
+      </c>
+      <c r="QQ87" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QR87" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS87" t="s">
+        <v>2125</v>
+      </c>
+      <c r="QT87" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV87" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW87" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX87" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY87" t="s">
+        <v>2126</v>
+      </c>
+      <c r="QZ87" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA87" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB87" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC87" t="s">
+        <v>2127</v>
+      </c>
+      <c r="RD87">
+        <v>1</v>
+      </c>
+      <c r="RE87">
+        <v>1</v>
+      </c>
+      <c r="RF87">
+        <v>1</v>
+      </c>
+      <c r="RG87">
+        <v>1</v>
+      </c>
+      <c r="RH87">
+        <v>0</v>
+      </c>
+      <c r="RJ87" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK87">
+        <v>0</v>
+      </c>
+      <c r="RL87">
+        <v>0</v>
+      </c>
+      <c r="RM87">
+        <v>1</v>
+      </c>
+      <c r="RN87" t="s">
+        <v>2128</v>
+      </c>
+      <c r="RO87" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP87" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ87" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR87" t="s">
+        <v>2129</v>
+      </c>
+      <c r="RS87" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT87" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY87" t="s">
+        <v>2130</v>
+      </c>
+      <c r="RZ87" t="s">
+        <v>1957</v>
+      </c>
+      <c r="SA87" t="s">
+        <v>2131</v>
+      </c>
+      <c r="SB87" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD87" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH87" t="s">
+        <v>2132</v>
+      </c>
+      <c r="ZL87" s="1"/>
+      <c r="ADO87" s="1"/>
+      <c r="ADW87" s="1"/>
+      <c r="AEA87" s="1"/>
+      <c r="AEY87">
+        <v>892168286</v>
+      </c>
+      <c r="AEZ87" t="s">
+        <v>2133</v>
+      </c>
+      <c r="AFA87" s="1">
+        <v>46308.159733796303</v>
+      </c>
+      <c r="AFC87" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE87" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF87" t="s">
+        <v>2134</v>
+      </c>
+      <c r="AFG87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B88" t="s">
+        <v>773</v>
+      </c>
+      <c r="D88" t="s">
+        <v>593</v>
+      </c>
+      <c r="E88" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H88" t="s">
+        <v>981</v>
+      </c>
+      <c r="NX88" t="s">
+        <v>2135</v>
+      </c>
+      <c r="NY88" t="s">
+        <v>2040</v>
+      </c>
+      <c r="OA88" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS88">
+        <v>27</v>
+      </c>
+      <c r="OT88" t="s">
+        <v>2119</v>
+      </c>
+      <c r="OV88">
+        <v>14</v>
+      </c>
+      <c r="OW88" t="s">
+        <v>2136</v>
+      </c>
+      <c r="OY88">
+        <v>11</v>
+      </c>
+      <c r="OZ88" t="s">
+        <v>2081</v>
+      </c>
+      <c r="PB88">
+        <v>14</v>
+      </c>
+      <c r="PC88" t="s">
+        <v>834</v>
+      </c>
+      <c r="PE88">
+        <v>2</v>
+      </c>
+      <c r="PF88" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH88">
+        <v>0</v>
+      </c>
+      <c r="PI88" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ88" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL88" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM88" t="s">
+        <v>2137</v>
+      </c>
+      <c r="PN88" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO88" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ88" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR88" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS88">
+        <v>0</v>
+      </c>
+      <c r="PT88">
+        <v>0</v>
+      </c>
+      <c r="PU88">
+        <v>1</v>
+      </c>
+      <c r="PV88" t="s">
+        <v>2138</v>
+      </c>
+      <c r="PW88" t="s">
+        <v>2139</v>
+      </c>
+      <c r="PX88">
+        <v>1</v>
+      </c>
+      <c r="PY88">
+        <v>0</v>
+      </c>
+      <c r="PZ88">
+        <v>1</v>
+      </c>
+      <c r="QA88">
+        <v>0</v>
+      </c>
+      <c r="QJ88" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK88" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QL88" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QM88" t="s">
+        <v>2140</v>
+      </c>
+      <c r="QN88" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP88" t="s">
+        <v>2141</v>
+      </c>
+      <c r="QQ88" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QR88" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS88" t="s">
+        <v>2142</v>
+      </c>
+      <c r="QT88" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV88" t="s">
+        <v>2143</v>
+      </c>
+      <c r="QW88" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QX88" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY88" t="s">
+        <v>2144</v>
+      </c>
+      <c r="QZ88" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA88" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB88" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC88" t="s">
+        <v>2145</v>
+      </c>
+      <c r="RD88">
+        <v>1</v>
+      </c>
+      <c r="RE88">
+        <v>1</v>
+      </c>
+      <c r="RF88">
+        <v>0</v>
+      </c>
+      <c r="RG88">
+        <v>0</v>
+      </c>
+      <c r="RH88">
+        <v>0</v>
+      </c>
+      <c r="RJ88" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK88">
+        <v>0</v>
+      </c>
+      <c r="RL88">
+        <v>0</v>
+      </c>
+      <c r="RM88">
+        <v>1</v>
+      </c>
+      <c r="RN88" t="s">
+        <v>2146</v>
+      </c>
+      <c r="RO88" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP88" t="s">
+        <v>732</v>
+      </c>
+      <c r="RQ88" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR88" t="s">
+        <v>2147</v>
+      </c>
+      <c r="RS88" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT88" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY88" t="s">
+        <v>2148</v>
+      </c>
+      <c r="RZ88" t="s">
+        <v>2093</v>
+      </c>
+      <c r="SA88" t="s">
+        <v>2149</v>
+      </c>
+      <c r="SB88" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD88" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH88" t="s">
+        <v>2114</v>
+      </c>
+      <c r="ZL88" s="1"/>
+      <c r="ADO88" s="1"/>
+      <c r="ADW88" s="1"/>
+      <c r="AEA88" s="1"/>
+      <c r="AEY88">
+        <v>892171713</v>
+      </c>
+      <c r="AEZ88" t="s">
+        <v>2150</v>
+      </c>
+      <c r="AFA88" s="1">
+        <v>46308.168229166673</v>
+      </c>
+      <c r="AFC88" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE88" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF88" t="s">
+        <v>2151</v>
+      </c>
+      <c r="AFG88">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBDC11F0-182E-B946-BEF9-F35D74F0E5B8}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CD06B12-8B4C-2344-9699-C6BF58B30092}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4060" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nutribus 2.0 Activity" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4384" uniqueCount="2152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4878" uniqueCount="2298">
   <si>
     <t>Date</t>
   </si>
@@ -6476,6 +6476,444 @@
   </si>
   <si>
     <t>uuid:1a772879-5100-4112-8ec5-9605c7ae3ce0</t>
+  </si>
+  <si>
+    <t>Opio John Fred</t>
+  </si>
+  <si>
+    <t>ROGOM P/S</t>
+  </si>
+  <si>
+    <t>The lower level class is difficult to truck since many of them show up during Meals time.</t>
+  </si>
+  <si>
+    <t>6148ef3a-0a74-47e0-9eab-87176f2a444f</t>
+  </si>
+  <si>
+    <t>uuid:6148ef3a-0a74-47e0-9eab-87176f2a444f</t>
+  </si>
+  <si>
+    <t>Opio John fred</t>
+  </si>
+  <si>
+    <t>Tyen Kworo Village</t>
+  </si>
+  <si>
+    <t>Atyang Santina</t>
+  </si>
+  <si>
+    <t>Many of the female caregivers participated in the highest numbers for learning on how to make nutrious food</t>
+  </si>
+  <si>
+    <t>Men were practically few but they promised to convey the information to there families</t>
+  </si>
+  <si>
+    <t>Most of the children were ins school</t>
+  </si>
+  <si>
+    <t>Some children were in school</t>
+  </si>
+  <si>
+    <t>Actively participated into the discussion on gender and shred roles</t>
+  </si>
+  <si>
+    <t>There was no female PWDs in the Demos</t>
+  </si>
+  <si>
+    <t>There were no cooking items. They used pictures to demonstrate how to cook nutrious food</t>
+  </si>
+  <si>
+    <t>Explained to community members to use locally available food</t>
+  </si>
+  <si>
+    <t>The caregivers now wants to try cooking nutrious food and will practice it at household level</t>
+  </si>
+  <si>
+    <t>The caregiver still need more guidance from the VHT</t>
+  </si>
+  <si>
+    <t>The caregiver want to understand more about</t>
+  </si>
+  <si>
+    <t>Children are served first and household eat last</t>
+  </si>
+  <si>
+    <t>Adults should understand that children can't be patient during Meals time</t>
+  </si>
+  <si>
+    <t>Community members agreed to share roles and responsibilities at home</t>
+  </si>
+  <si>
+    <t>The elders forum of 5</t>
+  </si>
+  <si>
+    <t>The main debate was men are always bigger in home</t>
+  </si>
+  <si>
+    <t>Most community members wanted to observe the real porridge being cooked other than VHT explaining using charts</t>
+  </si>
+  <si>
+    <t>e2a1fe16-b46d-45c9-a431-d272586fdfd3</t>
+  </si>
+  <si>
+    <t>vTcyb2xG9rhdM78xkzh3CJ</t>
+  </si>
+  <si>
+    <t>uuid:e2a1fe16-b46d-45c9-a431-d272586fdfd3</t>
+  </si>
+  <si>
+    <t>Loyoro</t>
+  </si>
+  <si>
+    <t>Ngiro peter</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>They promised to prepare it at home</t>
+  </si>
+  <si>
+    <t>Sorghum,maize</t>
+  </si>
+  <si>
+    <t>Improved cookstove consuming less firewood Traditional 3-stone fire used (Non-compliant)</t>
+  </si>
+  <si>
+    <t>VHTs help in making energy saving stoves</t>
+  </si>
+  <si>
+    <t>She said nothing</t>
+  </si>
+  <si>
+    <t>VHTs to help in making energy saving stoves</t>
+  </si>
+  <si>
+    <t>If the elderly child is sick he or she can be served first</t>
+  </si>
+  <si>
+    <t>They said they will call the number in case of inquiries</t>
+  </si>
+  <si>
+    <t>LC 1 and elders of the community</t>
+  </si>
+  <si>
+    <t>They asked is there any support WFP is offering during this hard time</t>
+  </si>
+  <si>
+    <t>It's a mother advising young girls to start respecting elders</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Community sessions on food management is needed this particular time</t>
+  </si>
+  <si>
+    <t>65f28149-1444-4eb1-8a7f-b42512ececfa</t>
+  </si>
+  <si>
+    <t>uuid:65f28149-1444-4eb1-8a7f-b42512ececfa</t>
+  </si>
+  <si>
+    <t>Libayia</t>
+  </si>
+  <si>
+    <t>Komol denis</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>The community needs continued teaching for sustainable health of the community</t>
+  </si>
+  <si>
+    <t>No, promoted unapproved/unattainable foods</t>
+  </si>
+  <si>
+    <t>Promote making cooking stoves</t>
+  </si>
+  <si>
+    <t>She says some elders are not respectful</t>
+  </si>
+  <si>
+    <t>Delays children from going to school</t>
+  </si>
+  <si>
+    <t>Young girls who are married are not respectful</t>
+  </si>
+  <si>
+    <t>Incase where children are at school</t>
+  </si>
+  <si>
+    <t>They said they will start calling since they have learnt</t>
+  </si>
+  <si>
+    <t>Continues community dialogues needed for more effective work</t>
+  </si>
+  <si>
+    <t>8d00f17f-1e24-4625-bbcf-80bb2fdc5085</t>
+  </si>
+  <si>
+    <t>uuid:8d00f17f-1e24-4625-bbcf-80bb2fdc5085</t>
+  </si>
+  <si>
+    <t>Itayia</t>
+  </si>
+  <si>
+    <t>Apeyo santa</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>People to be trained on making energy saving stoves</t>
+  </si>
+  <si>
+    <t>Used available sorghum and maize flour</t>
+  </si>
+  <si>
+    <t>Making energy saving stoves</t>
+  </si>
+  <si>
+    <t>Elders also now don't respect young only because of over drinking</t>
+  </si>
+  <si>
+    <t>Only making cooking stoves is the best option</t>
+  </si>
+  <si>
+    <t>Senior men Senior women VHTs</t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t>They will save the contacts to their phones</t>
+  </si>
+  <si>
+    <t>Is there any support WFP is offering during this year nutribus</t>
+  </si>
+  <si>
+    <t>Maybe some responses by the WFP for karamoja region per hunger issues</t>
+  </si>
+  <si>
+    <t>1f8b2148-b858-497c-9256-e5eb37ef98f9</t>
+  </si>
+  <si>
+    <t>uuid:1f8b2148-b858-497c-9256-e5eb37ef98f9</t>
+  </si>
+  <si>
+    <t>NAPONGAE P/S</t>
+  </si>
+  <si>
+    <t>Tuesday Saturday</t>
+  </si>
+  <si>
+    <t>The nutrition club is active and workplan expected to be implemented immediately</t>
+  </si>
+  <si>
+    <t>a59aa586-0a74-4f91-9670-73de4e101b38</t>
+  </si>
+  <si>
+    <t>uuid:a59aa586-0a74-4f91-9670-73de4e101b38</t>
+  </si>
+  <si>
+    <t>Naoyagumk</t>
+  </si>
+  <si>
+    <t>Logwee Alfred</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>One member said next time Cook enough samples for the community</t>
+  </si>
+  <si>
+    <t>Asking how possible is it to more energy saving stoves</t>
+  </si>
+  <si>
+    <t>Not possible</t>
+  </si>
+  <si>
+    <t>Teaching the community more of good eating practices</t>
+  </si>
+  <si>
+    <t>Water is far from the surrounding</t>
+  </si>
+  <si>
+    <t>Let the number continue being displayed</t>
+  </si>
+  <si>
+    <t>Youth and LC 1</t>
+  </si>
+  <si>
+    <t>Requesting WFP continue teaching people on this projects</t>
+  </si>
+  <si>
+    <t>Mother advising young girls to respect there parents and in laws</t>
+  </si>
+  <si>
+    <t>Continues community engagement</t>
+  </si>
+  <si>
+    <t>06619a44-b422-4398-a078-fa8b756273e6</t>
+  </si>
+  <si>
+    <t>uuid:06619a44-b422-4398-a078-fa8b756273e6</t>
+  </si>
+  <si>
+    <t>OTALABAR P/S</t>
+  </si>
+  <si>
+    <t>The school enrollment is not bad. There is a Nutri club in the school</t>
+  </si>
+  <si>
+    <t>295decb1-1b8c-43f7-b241-5bdf8b6a15a1</t>
+  </si>
+  <si>
+    <t>uuid:295decb1-1b8c-43f7-b241-5bdf8b6a15a1</t>
+  </si>
+  <si>
+    <t>Loperu</t>
+  </si>
+  <si>
+    <t>Akol winny</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>They said the porridge is nice and they want to continue preparing at home</t>
+  </si>
+  <si>
+    <t>None possible right now</t>
+  </si>
+  <si>
+    <t>He said he will try because is able since is civil servant</t>
+  </si>
+  <si>
+    <t>Advise her children to share work</t>
+  </si>
+  <si>
+    <t>Unless they are not present</t>
+  </si>
+  <si>
+    <t>They is now good they can talk to WFP directly</t>
+  </si>
+  <si>
+    <t>LC 1</t>
+  </si>
+  <si>
+    <t>They are asking is there refreshments for this meeting</t>
+  </si>
+  <si>
+    <t>Mother telling out the importance of WFP during all the past years</t>
+  </si>
+  <si>
+    <t>Continues community dialogues is key they get information</t>
+  </si>
+  <si>
+    <t>c2f9dc84-56d8-46c4-a9ab-8f79b7a08aca</t>
+  </si>
+  <si>
+    <t>uuid:c2f9dc84-56d8-46c4-a9ab-8f79b7a08aca</t>
+  </si>
+  <si>
+    <t>MORULEM BOYS P/S</t>
+  </si>
+  <si>
+    <t>Lower (ECD-P2) Middle (P3-P4)</t>
+  </si>
+  <si>
+    <t>The school enrollment is big. The school has Nutri club which is very functional</t>
+  </si>
+  <si>
+    <t>a843c95f-61df-46cb-867a-3307178a18b3</t>
+  </si>
+  <si>
+    <t>uuid:a843c95f-61df-46cb-867a-3307178a18b3</t>
+  </si>
+  <si>
+    <t>Kokoro</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>They appreciate the porridge is nice and pray to continue</t>
+  </si>
+  <si>
+    <t>Orange-fleshed sweet potato (OFSP)</t>
+  </si>
+  <si>
+    <t>Proper mobilization is key</t>
+  </si>
+  <si>
+    <t>Wild animals are risking life</t>
+  </si>
+  <si>
+    <t>Train the community on how to make energy saving stoves</t>
+  </si>
+  <si>
+    <t>Incase the children are not there</t>
+  </si>
+  <si>
+    <t>They will start calling since they have got and what they have learnt about it</t>
+  </si>
+  <si>
+    <t>What are things we are to call for in that number</t>
+  </si>
+  <si>
+    <t>Continues community engagement is key</t>
+  </si>
+  <si>
+    <t>f34ae6f9-764f-4205-9521-66466a03947d</t>
+  </si>
+  <si>
+    <t>uuid:f34ae6f9-764f-4205-9521-66466a03947d</t>
+  </si>
+  <si>
+    <t>ALEREK P/S</t>
+  </si>
+  <si>
+    <t>School sessions/teacher led is ongoing in school now</t>
+  </si>
+  <si>
+    <t>b21897a7-0e5c-402e-bca9-3406b70ef7b2</t>
+  </si>
+  <si>
+    <t>uuid:b21897a7-0e5c-402e-bca9-3406b70ef7b2</t>
   </si>
 </sst>
 </file>
@@ -6557,8 +6995,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG88" totalsRowShown="0">
-  <autoFilter ref="A1:AFG88" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG100" totalsRowShown="0">
+  <autoFilter ref="A1:AFG100" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -7691,7 +8129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFG88"/>
+  <dimension ref="A1:AFG100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -31656,6 +32094,2423 @@
         <v>87</v>
       </c>
     </row>
+    <row r="89" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B89" t="s">
+        <v>706</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D89" t="s">
+        <v>591</v>
+      </c>
+      <c r="E89" t="s">
+        <v>752</v>
+      </c>
+      <c r="F89" t="s">
+        <v>2153</v>
+      </c>
+      <c r="EN89" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO89">
+        <v>680</v>
+      </c>
+      <c r="EP89">
+        <v>523</v>
+      </c>
+      <c r="EQ89" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER89" t="s">
+        <v>1290</v>
+      </c>
+      <c r="ES89">
+        <v>0</v>
+      </c>
+      <c r="ET89">
+        <v>1</v>
+      </c>
+      <c r="EU89">
+        <v>0</v>
+      </c>
+      <c r="EV89">
+        <v>0</v>
+      </c>
+      <c r="EW89">
+        <v>0</v>
+      </c>
+      <c r="EX89">
+        <v>0</v>
+      </c>
+      <c r="EZ89" t="s">
+        <v>732</v>
+      </c>
+      <c r="FA89">
+        <v>6</v>
+      </c>
+      <c r="FB89" t="s">
+        <v>1099</v>
+      </c>
+      <c r="FC89">
+        <v>0</v>
+      </c>
+      <c r="FD89">
+        <v>1</v>
+      </c>
+      <c r="FE89">
+        <v>0</v>
+      </c>
+      <c r="FF89" t="s">
+        <v>732</v>
+      </c>
+      <c r="FH89" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP89">
+        <v>86</v>
+      </c>
+      <c r="NQ89">
+        <v>52</v>
+      </c>
+      <c r="NS89">
+        <v>78</v>
+      </c>
+      <c r="NT89">
+        <v>62</v>
+      </c>
+      <c r="NV89">
+        <v>56</v>
+      </c>
+      <c r="NW89">
+        <v>48</v>
+      </c>
+      <c r="SD89" s="1"/>
+      <c r="UH89" t="s">
+        <v>2154</v>
+      </c>
+      <c r="ZL89" s="1"/>
+      <c r="ADO89" s="1"/>
+      <c r="ADW89" s="1"/>
+      <c r="AEA89" s="1"/>
+      <c r="AEY89">
+        <v>892239069</v>
+      </c>
+      <c r="AEZ89" t="s">
+        <v>2155</v>
+      </c>
+      <c r="AFA89" s="1">
+        <v>46308.268611111111</v>
+      </c>
+      <c r="AFC89" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE89" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF89" t="s">
+        <v>2156</v>
+      </c>
+      <c r="AFG89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B90" t="s">
+        <v>706</v>
+      </c>
+      <c r="C90" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D90" t="s">
+        <v>591</v>
+      </c>
+      <c r="E90" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F90" t="s">
+        <v>2153</v>
+      </c>
+      <c r="NX90" t="s">
+        <v>2158</v>
+      </c>
+      <c r="NY90" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ90" t="s">
+        <v>2159</v>
+      </c>
+      <c r="OA90" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS90">
+        <v>54</v>
+      </c>
+      <c r="OT90" t="s">
+        <v>2160</v>
+      </c>
+      <c r="OV90">
+        <v>28</v>
+      </c>
+      <c r="OW90" t="s">
+        <v>2161</v>
+      </c>
+      <c r="OY90">
+        <v>3</v>
+      </c>
+      <c r="OZ90" t="s">
+        <v>2162</v>
+      </c>
+      <c r="PB90">
+        <v>2</v>
+      </c>
+      <c r="PC90" t="s">
+        <v>2163</v>
+      </c>
+      <c r="PE90">
+        <v>1</v>
+      </c>
+      <c r="PF90" t="s">
+        <v>2164</v>
+      </c>
+      <c r="PH90">
+        <v>0</v>
+      </c>
+      <c r="PI90" t="s">
+        <v>2165</v>
+      </c>
+      <c r="PJ90" t="s">
+        <v>706</v>
+      </c>
+      <c r="PK90" t="s">
+        <v>2166</v>
+      </c>
+      <c r="PL90" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN90" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO90" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ90" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR90" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS90">
+        <v>0</v>
+      </c>
+      <c r="PT90">
+        <v>0</v>
+      </c>
+      <c r="PU90">
+        <v>1</v>
+      </c>
+      <c r="PV90" t="s">
+        <v>2167</v>
+      </c>
+      <c r="PW90" t="s">
+        <v>1922</v>
+      </c>
+      <c r="PX90">
+        <v>1</v>
+      </c>
+      <c r="PY90">
+        <v>0</v>
+      </c>
+      <c r="PZ90">
+        <v>0</v>
+      </c>
+      <c r="QA90">
+        <v>0</v>
+      </c>
+      <c r="QJ90" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK90" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QL90" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QM90" t="s">
+        <v>2168</v>
+      </c>
+      <c r="QN90" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP90" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QQ90" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QR90" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QS90" t="s">
+        <v>2169</v>
+      </c>
+      <c r="QT90" t="s">
+        <v>720</v>
+      </c>
+      <c r="QV90" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW90" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QX90" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QY90" t="s">
+        <v>2170</v>
+      </c>
+      <c r="QZ90" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA90" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB90" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC90" t="s">
+        <v>2145</v>
+      </c>
+      <c r="RD90">
+        <v>1</v>
+      </c>
+      <c r="RE90">
+        <v>1</v>
+      </c>
+      <c r="RF90">
+        <v>0</v>
+      </c>
+      <c r="RG90">
+        <v>0</v>
+      </c>
+      <c r="RH90">
+        <v>0</v>
+      </c>
+      <c r="RJ90" t="s">
+        <v>2051</v>
+      </c>
+      <c r="RK90">
+        <v>1</v>
+      </c>
+      <c r="RL90">
+        <v>0</v>
+      </c>
+      <c r="RM90">
+        <v>0</v>
+      </c>
+      <c r="RO90" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP90" t="s">
+        <v>732</v>
+      </c>
+      <c r="RQ90" t="s">
+        <v>2171</v>
+      </c>
+      <c r="RR90" t="s">
+        <v>2172</v>
+      </c>
+      <c r="RS90" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT90" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY90" t="s">
+        <v>2173</v>
+      </c>
+      <c r="RZ90" t="s">
+        <v>2174</v>
+      </c>
+      <c r="SA90" t="s">
+        <v>2175</v>
+      </c>
+      <c r="SB90" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD90" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH90" t="s">
+        <v>2176</v>
+      </c>
+      <c r="ZL90" s="1"/>
+      <c r="ADO90" s="1"/>
+      <c r="ADW90" s="1"/>
+      <c r="AEA90" s="1"/>
+      <c r="AEY90">
+        <v>892295911</v>
+      </c>
+      <c r="AEZ90" t="s">
+        <v>2177</v>
+      </c>
+      <c r="AFA90" s="1">
+        <v>46308.319444444453</v>
+      </c>
+      <c r="AFC90" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE90" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF90" t="s">
+        <v>2179</v>
+      </c>
+      <c r="AFG90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B91" t="s">
+        <v>773</v>
+      </c>
+      <c r="D91" t="s">
+        <v>593</v>
+      </c>
+      <c r="E91" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H91" t="s">
+        <v>1060</v>
+      </c>
+      <c r="NX91" t="s">
+        <v>2180</v>
+      </c>
+      <c r="NY91" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ91" t="s">
+        <v>2181</v>
+      </c>
+      <c r="OA91" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS91">
+        <v>56</v>
+      </c>
+      <c r="OT91" t="s">
+        <v>2182</v>
+      </c>
+      <c r="OV91">
+        <v>23</v>
+      </c>
+      <c r="OW91" t="s">
+        <v>2136</v>
+      </c>
+      <c r="OY91">
+        <v>42</v>
+      </c>
+      <c r="OZ91" t="s">
+        <v>2183</v>
+      </c>
+      <c r="PB91">
+        <v>11</v>
+      </c>
+      <c r="PC91" t="s">
+        <v>2184</v>
+      </c>
+      <c r="PE91">
+        <v>2</v>
+      </c>
+      <c r="PF91" t="s">
+        <v>807</v>
+      </c>
+      <c r="PH91">
+        <v>1</v>
+      </c>
+      <c r="PI91" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ91" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL91" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM91" t="s">
+        <v>2185</v>
+      </c>
+      <c r="PN91" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO91" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ91" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR91" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS91">
+        <v>0</v>
+      </c>
+      <c r="PT91">
+        <v>0</v>
+      </c>
+      <c r="PU91">
+        <v>1</v>
+      </c>
+      <c r="PV91" t="s">
+        <v>2186</v>
+      </c>
+      <c r="PW91" t="s">
+        <v>2187</v>
+      </c>
+      <c r="PX91">
+        <v>1</v>
+      </c>
+      <c r="PY91">
+        <v>0</v>
+      </c>
+      <c r="PZ91">
+        <v>0</v>
+      </c>
+      <c r="QA91">
+        <v>1</v>
+      </c>
+      <c r="QJ91" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK91" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QL91" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM91" t="s">
+        <v>2188</v>
+      </c>
+      <c r="QN91" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP91" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ91" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR91" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS91" t="s">
+        <v>2189</v>
+      </c>
+      <c r="QT91" t="s">
+        <v>720</v>
+      </c>
+      <c r="QV91" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW91" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QX91" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY91" t="s">
+        <v>2190</v>
+      </c>
+      <c r="QZ91" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA91" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB91" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC91" t="s">
+        <v>2069</v>
+      </c>
+      <c r="RD91">
+        <v>0</v>
+      </c>
+      <c r="RE91">
+        <v>1</v>
+      </c>
+      <c r="RF91">
+        <v>1</v>
+      </c>
+      <c r="RG91">
+        <v>1</v>
+      </c>
+      <c r="RH91">
+        <v>0</v>
+      </c>
+      <c r="RJ91" t="s">
+        <v>2051</v>
+      </c>
+      <c r="RK91">
+        <v>1</v>
+      </c>
+      <c r="RL91">
+        <v>0</v>
+      </c>
+      <c r="RM91">
+        <v>0</v>
+      </c>
+      <c r="RO91" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP91" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ91" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR91" t="s">
+        <v>2191</v>
+      </c>
+      <c r="RS91" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT91" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY91" t="s">
+        <v>2192</v>
+      </c>
+      <c r="RZ91" t="s">
+        <v>2193</v>
+      </c>
+      <c r="SA91" t="s">
+        <v>2194</v>
+      </c>
+      <c r="SB91" t="s">
+        <v>711</v>
+      </c>
+      <c r="SC91" t="s">
+        <v>2195</v>
+      </c>
+      <c r="SD91" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="SE91">
+        <v>1</v>
+      </c>
+      <c r="SF91" t="s">
+        <v>2196</v>
+      </c>
+      <c r="UH91" t="s">
+        <v>2197</v>
+      </c>
+      <c r="ZL91" s="1"/>
+      <c r="ADO91" s="1"/>
+      <c r="ADW91" s="1"/>
+      <c r="AEA91" s="1"/>
+      <c r="AEY91">
+        <v>892335748</v>
+      </c>
+      <c r="AEZ91" t="s">
+        <v>2198</v>
+      </c>
+      <c r="AFA91" s="1">
+        <v>46308.348368055558</v>
+      </c>
+      <c r="AFC91" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE91" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF91" t="s">
+        <v>2199</v>
+      </c>
+      <c r="AFG91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B92" t="s">
+        <v>773</v>
+      </c>
+      <c r="D92" t="s">
+        <v>593</v>
+      </c>
+      <c r="E92" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H92" t="s">
+        <v>1060</v>
+      </c>
+      <c r="NX92" t="s">
+        <v>2200</v>
+      </c>
+      <c r="NY92" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ92" t="s">
+        <v>2201</v>
+      </c>
+      <c r="OA92" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS92">
+        <v>98</v>
+      </c>
+      <c r="OT92" t="s">
+        <v>2202</v>
+      </c>
+      <c r="OV92">
+        <v>71</v>
+      </c>
+      <c r="OW92" t="s">
+        <v>2203</v>
+      </c>
+      <c r="OY92">
+        <v>47</v>
+      </c>
+      <c r="OZ92" t="s">
+        <v>2204</v>
+      </c>
+      <c r="PB92">
+        <v>25</v>
+      </c>
+      <c r="PC92" t="s">
+        <v>2205</v>
+      </c>
+      <c r="PE92">
+        <v>0</v>
+      </c>
+      <c r="PF92" t="s">
+        <v>840</v>
+      </c>
+      <c r="PH92">
+        <v>2</v>
+      </c>
+      <c r="PI92" t="s">
+        <v>840</v>
+      </c>
+      <c r="PJ92" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL92" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM92" t="s">
+        <v>2206</v>
+      </c>
+      <c r="PN92" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO92" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ92" t="s">
+        <v>2207</v>
+      </c>
+      <c r="PR92" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS92">
+        <v>0</v>
+      </c>
+      <c r="PT92">
+        <v>0</v>
+      </c>
+      <c r="PU92">
+        <v>1</v>
+      </c>
+      <c r="PV92" t="s">
+        <v>2186</v>
+      </c>
+      <c r="PW92" t="s">
+        <v>2187</v>
+      </c>
+      <c r="PX92">
+        <v>1</v>
+      </c>
+      <c r="PY92">
+        <v>0</v>
+      </c>
+      <c r="PZ92">
+        <v>0</v>
+      </c>
+      <c r="QA92">
+        <v>1</v>
+      </c>
+      <c r="QJ92" t="s">
+        <v>1950</v>
+      </c>
+      <c r="QK92" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QL92" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QM92" t="s">
+        <v>2208</v>
+      </c>
+      <c r="QN92" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP92" t="s">
+        <v>2087</v>
+      </c>
+      <c r="QQ92" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QR92" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS92" t="s">
+        <v>2209</v>
+      </c>
+      <c r="QT92" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV92" t="s">
+        <v>2143</v>
+      </c>
+      <c r="QW92" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QX92" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY92" t="s">
+        <v>2210</v>
+      </c>
+      <c r="QZ92" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA92" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB92" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC92" t="s">
+        <v>2069</v>
+      </c>
+      <c r="RD92">
+        <v>0</v>
+      </c>
+      <c r="RE92">
+        <v>1</v>
+      </c>
+      <c r="RF92">
+        <v>1</v>
+      </c>
+      <c r="RG92">
+        <v>1</v>
+      </c>
+      <c r="RH92">
+        <v>0</v>
+      </c>
+      <c r="RJ92" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK92">
+        <v>0</v>
+      </c>
+      <c r="RL92">
+        <v>0</v>
+      </c>
+      <c r="RM92">
+        <v>1</v>
+      </c>
+      <c r="RN92" t="s">
+        <v>2211</v>
+      </c>
+      <c r="RO92" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP92" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ92" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR92" t="s">
+        <v>2212</v>
+      </c>
+      <c r="RS92" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT92" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY92" t="s">
+        <v>2213</v>
+      </c>
+      <c r="RZ92" t="s">
+        <v>2093</v>
+      </c>
+      <c r="SA92" t="s">
+        <v>2196</v>
+      </c>
+      <c r="SB92" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD92" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH92" t="s">
+        <v>2214</v>
+      </c>
+      <c r="ZL92" s="1"/>
+      <c r="ADO92" s="1"/>
+      <c r="ADW92" s="1"/>
+      <c r="AEA92" s="1"/>
+      <c r="AEY92">
+        <v>892353951</v>
+      </c>
+      <c r="AEZ92" t="s">
+        <v>2215</v>
+      </c>
+      <c r="AFA92" s="1">
+        <v>46308.362372685187</v>
+      </c>
+      <c r="AFC92" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE92" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF92" t="s">
+        <v>2216</v>
+      </c>
+      <c r="AFG92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B93" t="s">
+        <v>773</v>
+      </c>
+      <c r="D93" t="s">
+        <v>593</v>
+      </c>
+      <c r="E93" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H93" t="s">
+        <v>1060</v>
+      </c>
+      <c r="NX93" t="s">
+        <v>2217</v>
+      </c>
+      <c r="NY93" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ93" t="s">
+        <v>2218</v>
+      </c>
+      <c r="OA93" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS93">
+        <v>142</v>
+      </c>
+      <c r="OT93" t="s">
+        <v>2219</v>
+      </c>
+      <c r="OV93">
+        <v>81</v>
+      </c>
+      <c r="OW93" t="s">
+        <v>2204</v>
+      </c>
+      <c r="OY93">
+        <v>31</v>
+      </c>
+      <c r="OZ93" t="s">
+        <v>762</v>
+      </c>
+      <c r="PB93">
+        <v>11</v>
+      </c>
+      <c r="PC93" t="s">
+        <v>767</v>
+      </c>
+      <c r="PE93">
+        <v>0</v>
+      </c>
+      <c r="PF93" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH93">
+        <v>1</v>
+      </c>
+      <c r="PI93" t="s">
+        <v>840</v>
+      </c>
+      <c r="PJ93" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL93" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM93" t="s">
+        <v>2220</v>
+      </c>
+      <c r="PN93" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO93" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ93" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR93" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS93">
+        <v>0</v>
+      </c>
+      <c r="PT93">
+        <v>0</v>
+      </c>
+      <c r="PU93">
+        <v>1</v>
+      </c>
+      <c r="PV93" t="s">
+        <v>2221</v>
+      </c>
+      <c r="PW93" t="s">
+        <v>2103</v>
+      </c>
+      <c r="PX93">
+        <v>1</v>
+      </c>
+      <c r="PY93">
+        <v>1</v>
+      </c>
+      <c r="PZ93">
+        <v>0</v>
+      </c>
+      <c r="QA93">
+        <v>0</v>
+      </c>
+      <c r="QJ93" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK93" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL93" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QM93" t="s">
+        <v>2222</v>
+      </c>
+      <c r="QN93" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP93" t="s">
+        <v>2087</v>
+      </c>
+      <c r="QQ93" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QR93" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QS93" t="s">
+        <v>2223</v>
+      </c>
+      <c r="QT93" t="s">
+        <v>720</v>
+      </c>
+      <c r="QV93" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QW93" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QX93" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY93" t="s">
+        <v>2224</v>
+      </c>
+      <c r="QZ93" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA93" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB93" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC93" t="s">
+        <v>2225</v>
+      </c>
+      <c r="RD93">
+        <v>1</v>
+      </c>
+      <c r="RE93">
+        <v>1</v>
+      </c>
+      <c r="RF93">
+        <v>1</v>
+      </c>
+      <c r="RG93">
+        <v>0</v>
+      </c>
+      <c r="RH93">
+        <v>0</v>
+      </c>
+      <c r="RJ93" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK93">
+        <v>0</v>
+      </c>
+      <c r="RL93">
+        <v>0</v>
+      </c>
+      <c r="RM93">
+        <v>1</v>
+      </c>
+      <c r="RN93" t="s">
+        <v>2128</v>
+      </c>
+      <c r="RO93" t="s">
+        <v>1953</v>
+      </c>
+      <c r="RP93" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ93" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR93" t="s">
+        <v>2226</v>
+      </c>
+      <c r="RS93" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT93" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY93" t="s">
+        <v>2227</v>
+      </c>
+      <c r="RZ93" t="s">
+        <v>2112</v>
+      </c>
+      <c r="SA93" t="s">
+        <v>2228</v>
+      </c>
+      <c r="SB93" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD93" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH93" t="s">
+        <v>2229</v>
+      </c>
+      <c r="ZL93" s="1"/>
+      <c r="ADO93" s="1"/>
+      <c r="ADW93" s="1"/>
+      <c r="AEA93" s="1"/>
+      <c r="AEY93">
+        <v>892372994</v>
+      </c>
+      <c r="AEZ93" t="s">
+        <v>2230</v>
+      </c>
+      <c r="AFA93" s="1">
+        <v>46308.377650462957</v>
+      </c>
+      <c r="AFC93" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE93" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF93" t="s">
+        <v>2231</v>
+      </c>
+      <c r="AFG93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D94" t="s">
+        <v>590</v>
+      </c>
+      <c r="E94" t="s">
+        <v>752</v>
+      </c>
+      <c r="L94" t="s">
+        <v>2232</v>
+      </c>
+      <c r="EN94" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO94">
+        <v>515</v>
+      </c>
+      <c r="EP94">
+        <v>521</v>
+      </c>
+      <c r="EQ94" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER94" t="s">
+        <v>2233</v>
+      </c>
+      <c r="ES94">
+        <v>0</v>
+      </c>
+      <c r="ET94">
+        <v>1</v>
+      </c>
+      <c r="EU94">
+        <v>0</v>
+      </c>
+      <c r="EV94">
+        <v>0</v>
+      </c>
+      <c r="EW94">
+        <v>0</v>
+      </c>
+      <c r="EX94">
+        <v>1</v>
+      </c>
+      <c r="EZ94" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA94">
+        <v>60</v>
+      </c>
+      <c r="FB94" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC94">
+        <v>1</v>
+      </c>
+      <c r="FD94">
+        <v>1</v>
+      </c>
+      <c r="FE94">
+        <v>1</v>
+      </c>
+      <c r="FF94" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG94" t="s">
+        <v>996</v>
+      </c>
+      <c r="FH94" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP94">
+        <v>203</v>
+      </c>
+      <c r="NQ94">
+        <v>211</v>
+      </c>
+      <c r="NS94">
+        <v>222</v>
+      </c>
+      <c r="NT94">
+        <v>196</v>
+      </c>
+      <c r="NV94">
+        <v>90</v>
+      </c>
+      <c r="NW94">
+        <v>106</v>
+      </c>
+      <c r="SD94" s="1"/>
+      <c r="UH94" t="s">
+        <v>2234</v>
+      </c>
+      <c r="ZL94" s="1"/>
+      <c r="ADO94" s="1"/>
+      <c r="ADW94" s="1"/>
+      <c r="AEA94" s="1"/>
+      <c r="AEY94">
+        <v>892386090</v>
+      </c>
+      <c r="AEZ94" t="s">
+        <v>2235</v>
+      </c>
+      <c r="AFA94" s="1">
+        <v>46308.386817129627</v>
+      </c>
+      <c r="AFC94" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE94" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF94" t="s">
+        <v>2236</v>
+      </c>
+      <c r="AFG94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B95" t="s">
+        <v>773</v>
+      </c>
+      <c r="D95" t="s">
+        <v>593</v>
+      </c>
+      <c r="E95" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H95" t="s">
+        <v>1078</v>
+      </c>
+      <c r="NX95" t="s">
+        <v>2237</v>
+      </c>
+      <c r="NY95" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ95" t="s">
+        <v>2238</v>
+      </c>
+      <c r="OA95" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS95">
+        <v>124</v>
+      </c>
+      <c r="OT95" t="s">
+        <v>2239</v>
+      </c>
+      <c r="OV95">
+        <v>69</v>
+      </c>
+      <c r="OW95" t="s">
+        <v>2240</v>
+      </c>
+      <c r="OY95">
+        <v>23</v>
+      </c>
+      <c r="OZ95" t="s">
+        <v>2205</v>
+      </c>
+      <c r="PB95">
+        <v>11</v>
+      </c>
+      <c r="PC95" t="s">
+        <v>2241</v>
+      </c>
+      <c r="PE95">
+        <v>0</v>
+      </c>
+      <c r="PF95" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH95">
+        <v>0</v>
+      </c>
+      <c r="PI95" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ95" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL95" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM95" t="s">
+        <v>2242</v>
+      </c>
+      <c r="PN95" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO95" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ95" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR95" t="s">
+        <v>2064</v>
+      </c>
+      <c r="PS95">
+        <v>1</v>
+      </c>
+      <c r="PT95">
+        <v>1</v>
+      </c>
+      <c r="PU95">
+        <v>0</v>
+      </c>
+      <c r="PW95" t="s">
+        <v>2123</v>
+      </c>
+      <c r="PX95">
+        <v>1</v>
+      </c>
+      <c r="PY95">
+        <v>1</v>
+      </c>
+      <c r="PZ95">
+        <v>1</v>
+      </c>
+      <c r="QA95">
+        <v>1</v>
+      </c>
+      <c r="QJ95" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK95" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QL95" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM95" t="s">
+        <v>2243</v>
+      </c>
+      <c r="QN95" t="s">
+        <v>720</v>
+      </c>
+      <c r="QP95" t="s">
+        <v>2087</v>
+      </c>
+      <c r="QQ95" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QR95" t="s">
+        <v>2244</v>
+      </c>
+      <c r="QS95" t="s">
+        <v>2245</v>
+      </c>
+      <c r="QT95" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV95" t="s">
+        <v>1950</v>
+      </c>
+      <c r="QW95" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QX95" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY95" t="s">
+        <v>2246</v>
+      </c>
+      <c r="QZ95" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA95" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB95" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC95" t="s">
+        <v>2225</v>
+      </c>
+      <c r="RD95">
+        <v>1</v>
+      </c>
+      <c r="RE95">
+        <v>1</v>
+      </c>
+      <c r="RF95">
+        <v>1</v>
+      </c>
+      <c r="RG95">
+        <v>0</v>
+      </c>
+      <c r="RH95">
+        <v>0</v>
+      </c>
+      <c r="RJ95" t="s">
+        <v>2051</v>
+      </c>
+      <c r="RK95">
+        <v>1</v>
+      </c>
+      <c r="RL95">
+        <v>0</v>
+      </c>
+      <c r="RM95">
+        <v>0</v>
+      </c>
+      <c r="RO95" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP95" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ95" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR95" t="s">
+        <v>2226</v>
+      </c>
+      <c r="RS95" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT95" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY95" t="s">
+        <v>2247</v>
+      </c>
+      <c r="RZ95" t="s">
+        <v>2248</v>
+      </c>
+      <c r="SA95" t="s">
+        <v>2249</v>
+      </c>
+      <c r="SB95" t="s">
+        <v>711</v>
+      </c>
+      <c r="SC95" t="s">
+        <v>2250</v>
+      </c>
+      <c r="SD95" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH95" t="s">
+        <v>2251</v>
+      </c>
+      <c r="ZL95" s="1"/>
+      <c r="ADO95" s="1"/>
+      <c r="ADW95" s="1"/>
+      <c r="AEA95" s="1"/>
+      <c r="AEY95">
+        <v>892388494</v>
+      </c>
+      <c r="AEZ95" t="s">
+        <v>2252</v>
+      </c>
+      <c r="AFA95" s="1">
+        <v>46308.388611111113</v>
+      </c>
+      <c r="AFC95" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE95" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF95" t="s">
+        <v>2253</v>
+      </c>
+      <c r="AFG95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B96" t="s">
+        <v>706</v>
+      </c>
+      <c r="C96" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D96" t="s">
+        <v>591</v>
+      </c>
+      <c r="E96" t="s">
+        <v>752</v>
+      </c>
+      <c r="F96" t="s">
+        <v>2254</v>
+      </c>
+      <c r="EN96" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO96">
+        <v>526</v>
+      </c>
+      <c r="EP96">
+        <v>576</v>
+      </c>
+      <c r="EQ96" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER96" t="s">
+        <v>1237</v>
+      </c>
+      <c r="ES96">
+        <v>0</v>
+      </c>
+      <c r="ET96">
+        <v>0</v>
+      </c>
+      <c r="EU96">
+        <v>1</v>
+      </c>
+      <c r="EV96">
+        <v>0</v>
+      </c>
+      <c r="EW96">
+        <v>0</v>
+      </c>
+      <c r="EX96">
+        <v>0</v>
+      </c>
+      <c r="EZ96" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA96">
+        <v>8</v>
+      </c>
+      <c r="FB96" t="s">
+        <v>1069</v>
+      </c>
+      <c r="FC96">
+        <v>0</v>
+      </c>
+      <c r="FD96">
+        <v>1</v>
+      </c>
+      <c r="FE96">
+        <v>1</v>
+      </c>
+      <c r="FF96" t="s">
+        <v>732</v>
+      </c>
+      <c r="FH96" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP96">
+        <v>174</v>
+      </c>
+      <c r="NQ96">
+        <v>193</v>
+      </c>
+      <c r="NS96">
+        <v>175</v>
+      </c>
+      <c r="NT96">
+        <v>184</v>
+      </c>
+      <c r="NV96">
+        <v>177</v>
+      </c>
+      <c r="NW96">
+        <v>193</v>
+      </c>
+      <c r="SD96" s="1"/>
+      <c r="UH96" t="s">
+        <v>2255</v>
+      </c>
+      <c r="ZL96" s="1"/>
+      <c r="ADO96" s="1"/>
+      <c r="ADW96" s="1"/>
+      <c r="AEA96" s="1"/>
+      <c r="AEY96">
+        <v>892397447</v>
+      </c>
+      <c r="AEZ96" t="s">
+        <v>2256</v>
+      </c>
+      <c r="AFA96" s="1">
+        <v>46308.394386574073</v>
+      </c>
+      <c r="AFC96" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE96" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF96" t="s">
+        <v>2257</v>
+      </c>
+      <c r="AFG96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B97" t="s">
+        <v>773</v>
+      </c>
+      <c r="D97" t="s">
+        <v>593</v>
+      </c>
+      <c r="E97" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H97" t="s">
+        <v>1078</v>
+      </c>
+      <c r="NX97" t="s">
+        <v>2258</v>
+      </c>
+      <c r="NY97" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ97" t="s">
+        <v>2259</v>
+      </c>
+      <c r="OA97" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS97">
+        <v>152</v>
+      </c>
+      <c r="OT97" t="s">
+        <v>2260</v>
+      </c>
+      <c r="OV97">
+        <v>38</v>
+      </c>
+      <c r="OW97" t="s">
+        <v>2261</v>
+      </c>
+      <c r="OY97">
+        <v>13</v>
+      </c>
+      <c r="OZ97" t="s">
+        <v>2184</v>
+      </c>
+      <c r="PB97">
+        <v>12</v>
+      </c>
+      <c r="PC97" t="s">
+        <v>2241</v>
+      </c>
+      <c r="PE97">
+        <v>1</v>
+      </c>
+      <c r="PF97" t="s">
+        <v>840</v>
+      </c>
+      <c r="PH97">
+        <v>0</v>
+      </c>
+      <c r="PI97" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ97" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL97" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM97" t="s">
+        <v>2262</v>
+      </c>
+      <c r="PN97" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO97" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ97" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR97" t="s">
+        <v>2064</v>
+      </c>
+      <c r="PS97">
+        <v>1</v>
+      </c>
+      <c r="PT97">
+        <v>1</v>
+      </c>
+      <c r="PU97">
+        <v>0</v>
+      </c>
+      <c r="PW97" t="s">
+        <v>2123</v>
+      </c>
+      <c r="PX97">
+        <v>1</v>
+      </c>
+      <c r="PY97">
+        <v>1</v>
+      </c>
+      <c r="PZ97">
+        <v>1</v>
+      </c>
+      <c r="QA97">
+        <v>1</v>
+      </c>
+      <c r="QJ97" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QK97" t="s">
+        <v>2263</v>
+      </c>
+      <c r="QL97" t="s">
+        <v>2244</v>
+      </c>
+      <c r="QM97" t="s">
+        <v>2264</v>
+      </c>
+      <c r="QN97" t="s">
+        <v>720</v>
+      </c>
+      <c r="QP97" t="s">
+        <v>2143</v>
+      </c>
+      <c r="QQ97" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QR97" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS97" t="s">
+        <v>2210</v>
+      </c>
+      <c r="QT97" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV97" t="s">
+        <v>2087</v>
+      </c>
+      <c r="QW97" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QX97" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY97" t="s">
+        <v>2265</v>
+      </c>
+      <c r="QZ97" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA97" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB97" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC97" t="s">
+        <v>2107</v>
+      </c>
+      <c r="RD97">
+        <v>0</v>
+      </c>
+      <c r="RE97">
+        <v>1</v>
+      </c>
+      <c r="RF97">
+        <v>1</v>
+      </c>
+      <c r="RG97">
+        <v>0</v>
+      </c>
+      <c r="RH97">
+        <v>0</v>
+      </c>
+      <c r="RJ97" t="s">
+        <v>2051</v>
+      </c>
+      <c r="RK97">
+        <v>1</v>
+      </c>
+      <c r="RL97">
+        <v>0</v>
+      </c>
+      <c r="RM97">
+        <v>0</v>
+      </c>
+      <c r="RO97" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP97" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ97" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR97" t="s">
+        <v>2266</v>
+      </c>
+      <c r="RS97" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT97" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY97" t="s">
+        <v>2267</v>
+      </c>
+      <c r="RZ97" t="s">
+        <v>2268</v>
+      </c>
+      <c r="SA97" t="s">
+        <v>2269</v>
+      </c>
+      <c r="SB97" t="s">
+        <v>711</v>
+      </c>
+      <c r="SC97" t="s">
+        <v>2270</v>
+      </c>
+      <c r="SD97" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH97" t="s">
+        <v>2271</v>
+      </c>
+      <c r="ZL97" s="1"/>
+      <c r="ADO97" s="1"/>
+      <c r="ADW97" s="1"/>
+      <c r="AEA97" s="1"/>
+      <c r="AEY97">
+        <v>892404110</v>
+      </c>
+      <c r="AEZ97" t="s">
+        <v>2272</v>
+      </c>
+      <c r="AFA97" s="1">
+        <v>46308.399131944447</v>
+      </c>
+      <c r="AFC97" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE97" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF97" t="s">
+        <v>2273</v>
+      </c>
+      <c r="AFG97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B98" t="s">
+        <v>706</v>
+      </c>
+      <c r="C98" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D98" t="s">
+        <v>591</v>
+      </c>
+      <c r="E98" t="s">
+        <v>752</v>
+      </c>
+      <c r="F98" t="s">
+        <v>2274</v>
+      </c>
+      <c r="EN98" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO98">
+        <v>1514</v>
+      </c>
+      <c r="EP98">
+        <v>351</v>
+      </c>
+      <c r="EQ98" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER98" t="s">
+        <v>1098</v>
+      </c>
+      <c r="ES98">
+        <v>0</v>
+      </c>
+      <c r="ET98">
+        <v>0</v>
+      </c>
+      <c r="EU98">
+        <v>0</v>
+      </c>
+      <c r="EV98">
+        <v>1</v>
+      </c>
+      <c r="EW98">
+        <v>0</v>
+      </c>
+      <c r="EX98">
+        <v>0</v>
+      </c>
+      <c r="EZ98" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA98">
+        <v>12</v>
+      </c>
+      <c r="FB98" t="s">
+        <v>2275</v>
+      </c>
+      <c r="FC98">
+        <v>1</v>
+      </c>
+      <c r="FD98">
+        <v>1</v>
+      </c>
+      <c r="FE98">
+        <v>0</v>
+      </c>
+      <c r="FF98" t="s">
+        <v>732</v>
+      </c>
+      <c r="FH98" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP98">
+        <v>298</v>
+      </c>
+      <c r="NQ98">
+        <v>49</v>
+      </c>
+      <c r="NS98">
+        <v>344</v>
+      </c>
+      <c r="NT98">
+        <v>76</v>
+      </c>
+      <c r="NV98">
+        <v>270</v>
+      </c>
+      <c r="NW98">
+        <v>126</v>
+      </c>
+      <c r="SD98" s="1"/>
+      <c r="UH98" t="s">
+        <v>2276</v>
+      </c>
+      <c r="ZL98" s="1"/>
+      <c r="ADO98" s="1"/>
+      <c r="ADW98" s="1"/>
+      <c r="AEA98" s="1"/>
+      <c r="AEY98">
+        <v>892405246</v>
+      </c>
+      <c r="AEZ98" t="s">
+        <v>2277</v>
+      </c>
+      <c r="AFA98" s="1">
+        <v>46308.399988425917</v>
+      </c>
+      <c r="AFC98" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE98" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF98" t="s">
+        <v>2278</v>
+      </c>
+      <c r="AFG98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B99" t="s">
+        <v>773</v>
+      </c>
+      <c r="D99" t="s">
+        <v>593</v>
+      </c>
+      <c r="E99" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1078</v>
+      </c>
+      <c r="NX99" t="s">
+        <v>2279</v>
+      </c>
+      <c r="NY99" t="s">
+        <v>2040</v>
+      </c>
+      <c r="OA99" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS99">
+        <v>142</v>
+      </c>
+      <c r="OT99" t="s">
+        <v>2280</v>
+      </c>
+      <c r="OV99">
+        <v>54</v>
+      </c>
+      <c r="OW99" t="s">
+        <v>2261</v>
+      </c>
+      <c r="OY99">
+        <v>12</v>
+      </c>
+      <c r="OZ99" t="s">
+        <v>2281</v>
+      </c>
+      <c r="PB99">
+        <v>31</v>
+      </c>
+      <c r="PC99" t="s">
+        <v>2282</v>
+      </c>
+      <c r="PE99">
+        <v>0</v>
+      </c>
+      <c r="PF99" t="s">
+        <v>840</v>
+      </c>
+      <c r="PH99">
+        <v>1</v>
+      </c>
+      <c r="PI99" t="s">
+        <v>840</v>
+      </c>
+      <c r="PJ99" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL99" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM99" t="s">
+        <v>2283</v>
+      </c>
+      <c r="PN99" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO99" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ99" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR99" t="s">
+        <v>2284</v>
+      </c>
+      <c r="PS99">
+        <v>1</v>
+      </c>
+      <c r="PT99">
+        <v>0</v>
+      </c>
+      <c r="PU99">
+        <v>0</v>
+      </c>
+      <c r="PW99" t="s">
+        <v>2123</v>
+      </c>
+      <c r="PX99">
+        <v>1</v>
+      </c>
+      <c r="PY99">
+        <v>1</v>
+      </c>
+      <c r="PZ99">
+        <v>1</v>
+      </c>
+      <c r="QA99">
+        <v>1</v>
+      </c>
+      <c r="QJ99" t="s">
+        <v>2143</v>
+      </c>
+      <c r="QK99" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QL99" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM99" t="s">
+        <v>2285</v>
+      </c>
+      <c r="QN99" t="s">
+        <v>720</v>
+      </c>
+      <c r="QP99" t="s">
+        <v>2141</v>
+      </c>
+      <c r="QQ99" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QR99" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS99" t="s">
+        <v>2286</v>
+      </c>
+      <c r="QT99" t="s">
+        <v>720</v>
+      </c>
+      <c r="QV99" t="s">
+        <v>2143</v>
+      </c>
+      <c r="QW99" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QX99" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY99" t="s">
+        <v>2287</v>
+      </c>
+      <c r="QZ99" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA99" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB99" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC99" t="s">
+        <v>2127</v>
+      </c>
+      <c r="RD99">
+        <v>1</v>
+      </c>
+      <c r="RE99">
+        <v>1</v>
+      </c>
+      <c r="RF99">
+        <v>1</v>
+      </c>
+      <c r="RG99">
+        <v>1</v>
+      </c>
+      <c r="RH99">
+        <v>0</v>
+      </c>
+      <c r="RJ99" t="s">
+        <v>2051</v>
+      </c>
+      <c r="RK99">
+        <v>1</v>
+      </c>
+      <c r="RL99">
+        <v>0</v>
+      </c>
+      <c r="RM99">
+        <v>0</v>
+      </c>
+      <c r="RO99" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP99" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ99" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR99" t="s">
+        <v>2288</v>
+      </c>
+      <c r="RS99" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT99" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY99" t="s">
+        <v>2289</v>
+      </c>
+      <c r="RZ99" t="s">
+        <v>1957</v>
+      </c>
+      <c r="SA99" t="s">
+        <v>2290</v>
+      </c>
+      <c r="SB99" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD99" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH99" t="s">
+        <v>2291</v>
+      </c>
+      <c r="ZL99" s="1"/>
+      <c r="ADO99" s="1"/>
+      <c r="ADW99" s="1"/>
+      <c r="AEA99" s="1"/>
+      <c r="AEY99">
+        <v>892415570</v>
+      </c>
+      <c r="AEZ99" t="s">
+        <v>2292</v>
+      </c>
+      <c r="AFA99" s="1">
+        <v>46308.408263888887</v>
+      </c>
+      <c r="AFC99" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE99" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF99" t="s">
+        <v>2293</v>
+      </c>
+      <c r="AFG99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B100" t="s">
+        <v>706</v>
+      </c>
+      <c r="C100" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D100" t="s">
+        <v>591</v>
+      </c>
+      <c r="E100" t="s">
+        <v>752</v>
+      </c>
+      <c r="F100" t="s">
+        <v>2294</v>
+      </c>
+      <c r="EN100" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO100">
+        <v>672</v>
+      </c>
+      <c r="EP100">
+        <v>413</v>
+      </c>
+      <c r="EQ100" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER100" t="s">
+        <v>1237</v>
+      </c>
+      <c r="ES100">
+        <v>0</v>
+      </c>
+      <c r="ET100">
+        <v>0</v>
+      </c>
+      <c r="EU100">
+        <v>1</v>
+      </c>
+      <c r="EV100">
+        <v>0</v>
+      </c>
+      <c r="EW100">
+        <v>0</v>
+      </c>
+      <c r="EX100">
+        <v>0</v>
+      </c>
+      <c r="EZ100" t="s">
+        <v>732</v>
+      </c>
+      <c r="FA100">
+        <v>10</v>
+      </c>
+      <c r="FB100" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC100">
+        <v>1</v>
+      </c>
+      <c r="FD100">
+        <v>1</v>
+      </c>
+      <c r="FE100">
+        <v>1</v>
+      </c>
+      <c r="FF100" t="s">
+        <v>732</v>
+      </c>
+      <c r="FH100" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP100">
+        <v>186</v>
+      </c>
+      <c r="NQ100">
+        <v>86</v>
+      </c>
+      <c r="NS100">
+        <v>126</v>
+      </c>
+      <c r="NT100">
+        <v>72</v>
+      </c>
+      <c r="NV100">
+        <v>122</v>
+      </c>
+      <c r="NW100">
+        <v>79</v>
+      </c>
+      <c r="SD100" s="1"/>
+      <c r="UH100" t="s">
+        <v>2295</v>
+      </c>
+      <c r="ZL100" s="1"/>
+      <c r="ADO100" s="1"/>
+      <c r="ADW100" s="1"/>
+      <c r="AEA100" s="1"/>
+      <c r="AEY100">
+        <v>892481608</v>
+      </c>
+      <c r="AEZ100" t="s">
+        <v>2296</v>
+      </c>
+      <c r="AFA100" s="1">
+        <v>46308.459282407413</v>
+      </c>
+      <c r="AFC100" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE100" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF100" t="s">
+        <v>2297</v>
+      </c>
+      <c r="AFG100">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CD06B12-8B4C-2344-9699-C6BF58B30092}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{361511B8-2F72-9546-B182-6379A393CEBA}"/>
   <bookViews>
     <workbookView xWindow="4060" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4878" uniqueCount="2298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5479" uniqueCount="2458">
   <si>
     <t>Date</t>
   </si>
@@ -6914,6 +6914,486 @@
   </si>
   <si>
     <t>uuid:b21897a7-0e5c-402e-bca9-3406b70ef7b2</t>
+  </si>
+  <si>
+    <t>Okello Daniel NImaro</t>
+  </si>
+  <si>
+    <t>AWACH P/S</t>
+  </si>
+  <si>
+    <t>Within the compound</t>
+  </si>
+  <si>
+    <t>Teachers/patrons actively monitor the pupils to ascertain their feeding culture. The school is ready and willing to support WFP in it's nutribus campaign</t>
+  </si>
+  <si>
+    <t>75625e51-9c51-4778-99bd-d7a56dfe948c</t>
+  </si>
+  <si>
+    <t>uuid:75625e51-9c51-4778-99bd-d7a56dfe948c</t>
+  </si>
+  <si>
+    <t>KAPUAT P/S</t>
+  </si>
+  <si>
+    <t>infront of admin block</t>
+  </si>
+  <si>
+    <t>d4468ad6-91d9-44dc-be03-3c383d890d78</t>
+  </si>
+  <si>
+    <t>uuid:d4468ad6-91d9-44dc-be03-3c383d890d78</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Food sorting &amp; matching game Fair food portions for all genders Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>in games</t>
+  </si>
+  <si>
+    <t>learning through practice</t>
+  </si>
+  <si>
+    <t>it ois good to support girls at work</t>
+  </si>
+  <si>
+    <t>attend to school together</t>
+  </si>
+  <si>
+    <t>easy work</t>
+  </si>
+  <si>
+    <t>easy to fetch water</t>
+  </si>
+  <si>
+    <t>difficult to rare animals for girls</t>
+  </si>
+  <si>
+    <t>doubts aboiut green putting in porriage</t>
+  </si>
+  <si>
+    <t>hurry up</t>
+  </si>
+  <si>
+    <t>not know</t>
+  </si>
+  <si>
+    <t>both boys and girls should work</t>
+  </si>
+  <si>
+    <t>work together os good</t>
+  </si>
+  <si>
+    <t>helping each other</t>
+  </si>
+  <si>
+    <t>heavy rains</t>
+  </si>
+  <si>
+    <t>learners interested in learning through games</t>
+  </si>
+  <si>
+    <t>session for differnt age groups</t>
+  </si>
+  <si>
+    <t>to encourage meeting of the nutrition club and request WFP to support their school kitchen</t>
+  </si>
+  <si>
+    <t>590135c7-76f9-4559-9952-eeff5afb4260</t>
+  </si>
+  <si>
+    <t>uuid:590135c7-76f9-4559-9952-eeff5afb4260</t>
+  </si>
+  <si>
+    <t>4fb7472d-38ea-4927-a5ba-903d5611091f</t>
+  </si>
+  <si>
+    <t>uuid:4fb7472d-38ea-4927-a5ba-903d5611091f</t>
+  </si>
+  <si>
+    <t>Nutri Club patron Nutri Club member District cordinator Other</t>
+  </si>
+  <si>
+    <t>Headteacher</t>
+  </si>
+  <si>
+    <t>Reading story books</t>
+  </si>
+  <si>
+    <t>to avoid crowd</t>
+  </si>
+  <si>
+    <t>support our sister</t>
+  </si>
+  <si>
+    <t>sharing rtesponsibilities</t>
+  </si>
+  <si>
+    <t>working to gether and show love and corpartion</t>
+  </si>
+  <si>
+    <t>to corparate</t>
+  </si>
+  <si>
+    <t>i will report any abuse of girls</t>
+  </si>
+  <si>
+    <t>i will learn if i am taught</t>
+  </si>
+  <si>
+    <t>i came late</t>
+  </si>
+  <si>
+    <t>we help each other at home work</t>
+  </si>
+  <si>
+    <t>nutri bus for school</t>
+  </si>
+  <si>
+    <t>we wake up early together</t>
+  </si>
+  <si>
+    <t>Nutri bus</t>
+  </si>
+  <si>
+    <t>we learn together</t>
+  </si>
+  <si>
+    <t>the bus school</t>
+  </si>
+  <si>
+    <t>i share roles with my sisters</t>
+  </si>
+  <si>
+    <t>nutri schoolbus</t>
+  </si>
+  <si>
+    <t>learners expect another bus visit</t>
+  </si>
+  <si>
+    <t>enage all learners in differnt sessions</t>
+  </si>
+  <si>
+    <t>we commit to feed school children with food supported by WFP without misuse</t>
+  </si>
+  <si>
+    <t>7d536a41-901d-4ecc-b890-6245817dc310</t>
+  </si>
+  <si>
+    <t>uuid:7d536a41-901d-4ecc-b890-6245817dc310</t>
+  </si>
+  <si>
+    <t>Go down A village</t>
+  </si>
+  <si>
+    <t>Longora Margret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co-facilitating clean cooking/gender dialogue Other </t>
+  </si>
+  <si>
+    <t>Metu porriage</t>
+  </si>
+  <si>
+    <t>we have no food this year</t>
+  </si>
+  <si>
+    <t>I will look for money and buy some of the foods</t>
+  </si>
+  <si>
+    <t>if rain continues, we shall get some greens</t>
+  </si>
+  <si>
+    <t>to use gas</t>
+  </si>
+  <si>
+    <t>gender roles at home</t>
+  </si>
+  <si>
+    <t>increase the portion of food for children</t>
+  </si>
+  <si>
+    <t>how to get nutrition food in this drought</t>
+  </si>
+  <si>
+    <t>c7eb34b7-fe1c-4ad7-806e-f47f9b1057ed</t>
+  </si>
+  <si>
+    <t>uuid:c7eb34b7-fe1c-4ad7-806e-f47f9b1057ed</t>
+  </si>
+  <si>
+    <t>Okello Daniel Nimaro</t>
+  </si>
+  <si>
+    <t>PUPUKAMUYA P/S</t>
+  </si>
+  <si>
+    <t>At the Administrative block</t>
+  </si>
+  <si>
+    <t>Simple irrigation system to help the school plant vegetables especially during off seasons and when theirs a dry spell. The school appreciates WFP for the initiative. The school administration is extremely happy for what WFP is doing and requested that they shiuld continue supporting them</t>
+  </si>
+  <si>
+    <t>86a4a697-0f82-4ea0-a7d0-ddcaa2eaffe4</t>
+  </si>
+  <si>
+    <t>uuid:86a4a697-0f82-4ea0-a7d0-ddcaa2eaffe4</t>
+  </si>
+  <si>
+    <t>Lorengechora village</t>
+  </si>
+  <si>
+    <t>Stood and watched passively</t>
+  </si>
+  <si>
+    <t>it is easy to cook Metu but there are no ingridients available right now</t>
+  </si>
+  <si>
+    <t>Iron-rich beans other</t>
+  </si>
+  <si>
+    <t>Beans</t>
+  </si>
+  <si>
+    <t>Retained heat cooking and pot covering to conserve fuel</t>
+  </si>
+  <si>
+    <t>I can waste oil in porriage</t>
+  </si>
+  <si>
+    <t>If food was available, I would feed children well</t>
+  </si>
+  <si>
+    <t>I will try at home when i have money to buy</t>
+  </si>
+  <si>
+    <t>men and children</t>
+  </si>
+  <si>
+    <t>to try cooking metu porriage</t>
+  </si>
+  <si>
+    <t>sharing food portions equally</t>
+  </si>
+  <si>
+    <t>bfb34e35-a90e-4efa-9d78-252b541a9daa</t>
+  </si>
+  <si>
+    <t>uuid:bfb34e35-a90e-4efa-9d78-252b541a9daa</t>
+  </si>
+  <si>
+    <t>OBOLOKOME P/S</t>
+  </si>
+  <si>
+    <t>At the administration block</t>
+  </si>
+  <si>
+    <t>The school is willing to work together with WFP. The kitchen is very clean. The matron of nutri club is very active</t>
+  </si>
+  <si>
+    <t>c53a12c1-5868-4371-b79b-0d6962786b5c</t>
+  </si>
+  <si>
+    <t>uuid:c53a12c1-5868-4371-b79b-0d6962786b5c</t>
+  </si>
+  <si>
+    <t>Lokilala village</t>
+  </si>
+  <si>
+    <t>metu porriage demostration using metu flip charts</t>
+  </si>
+  <si>
+    <t>But where do we get money to buy some of this items for porriage</t>
+  </si>
+  <si>
+    <t>Iron-rich beans</t>
+  </si>
+  <si>
+    <t>when food is available, we all eat equally</t>
+  </si>
+  <si>
+    <t>i will discuss this with my friends and neibors</t>
+  </si>
+  <si>
+    <t>some items are expensive like gnuts</t>
+  </si>
+  <si>
+    <t>school attendance, enrolment and participation for children in Nawanatau primary school</t>
+  </si>
+  <si>
+    <t>children are served first</t>
+  </si>
+  <si>
+    <t>when food is available</t>
+  </si>
+  <si>
+    <t>to try out cooking metu if we get money to buy some ingredients</t>
+  </si>
+  <si>
+    <t>VHTs and lead mothers</t>
+  </si>
+  <si>
+    <t>teaching boys to share roles at home and at school</t>
+  </si>
+  <si>
+    <t>have some food demonstarted</t>
+  </si>
+  <si>
+    <t>bc3c1d11-8a2a-4b9c-9bfb-d5f15c1ceaac</t>
+  </si>
+  <si>
+    <t>uuid:bc3c1d11-8a2a-4b9c-9bfb-d5f15c1ceaac</t>
+  </si>
+  <si>
+    <t>Within the school compound</t>
+  </si>
+  <si>
+    <t>The headteacher was very happy having received the nutrition bus T shirt and the gifts for the pupils on bus day. The pupils are served well during lunch time</t>
+  </si>
+  <si>
+    <t>9699f1db-6c99-4140-8878-c0071ae1c6e8</t>
+  </si>
+  <si>
+    <t>uuid:9699f1db-6c99-4140-8878-c0071ae1c6e8</t>
+  </si>
+  <si>
+    <t>Kamera village</t>
+  </si>
+  <si>
+    <t>AFI</t>
+  </si>
+  <si>
+    <t>Mentoring local VHTs/Elders</t>
+  </si>
+  <si>
+    <t>Orange-fleshed sweet potato (OFSP) Iron-rich beans other</t>
+  </si>
+  <si>
+    <t>I can help with caring fpr children when my wife is busy cooking</t>
+  </si>
+  <si>
+    <t>Iwill try and use milk on porriage</t>
+  </si>
+  <si>
+    <t>I feed my children eqaully if i have food</t>
+  </si>
+  <si>
+    <t>Available local food which we can grow and harvest early</t>
+  </si>
+  <si>
+    <t>children and old people</t>
+  </si>
+  <si>
+    <t>always remember children first</t>
+  </si>
+  <si>
+    <t>we shall share this messages with other neigbors especially on feeding children equal portion of food</t>
+  </si>
+  <si>
+    <t>Boys are always served little food at home and at school</t>
+  </si>
+  <si>
+    <t>Actual food can be demonstrated</t>
+  </si>
+  <si>
+    <t>8310300d-9018-45e6-9b30-79098f953a42</t>
+  </si>
+  <si>
+    <t>uuid:8310300d-9018-45e6-9b30-79098f953a42</t>
+  </si>
+  <si>
+    <t>MORULEM GIRLS' P/S</t>
+  </si>
+  <si>
+    <t>Near the administration block</t>
+  </si>
+  <si>
+    <t>I got only girls since it is a girls school. Other posters are pinned at the compound with educational messages</t>
+  </si>
+  <si>
+    <t>f45e4abc-6c22-463c-bb54-428e177f5191</t>
+  </si>
+  <si>
+    <t>uuid:f45e4abc-6c22-463c-bb54-428e177f5191</t>
+  </si>
+  <si>
+    <t>Okisa Alex</t>
+  </si>
+  <si>
+    <t>school compound tree</t>
+  </si>
+  <si>
+    <t>Gender Chore Rebalancing: Boys sharing morning water/firewood chores</t>
+  </si>
+  <si>
+    <t>sharing of roles of house hold chores by both girls and boys like fetching water and cooking, fetching firewood</t>
+  </si>
+  <si>
+    <t>e19c3e6b-4a3c-4796-af13-46d18067d639</t>
+  </si>
+  <si>
+    <t>uuid:e19c3e6b-4a3c-4796-af13-46d18067d639</t>
+  </si>
+  <si>
+    <t>16:15:00.000+03:00</t>
+  </si>
+  <si>
+    <t>17:15:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Most tried it successfully</t>
+  </si>
+  <si>
+    <t>sharing roles at home and at school to support each other to learn and attend classes on time. sharing and serving food portions equally for both boys and girls</t>
+  </si>
+  <si>
+    <t>The two patrons conducted sessions differently in two days.</t>
+  </si>
+  <si>
+    <t>d8ad475f-4b66-4304-86a9-1e103f94ef35</t>
+  </si>
+  <si>
+    <t>uuid:d8ad475f-4b66-4304-86a9-1e103f94ef35</t>
+  </si>
+  <si>
+    <t>Obangangeo Village</t>
+  </si>
+  <si>
+    <t>Zadok okello</t>
+  </si>
+  <si>
+    <t>My family lacks money to be able to buy nutritious food items</t>
+  </si>
+  <si>
+    <t>Money is always a challenge. Sometimes we would want to eat food diet but we limited</t>
+  </si>
+  <si>
+    <t>Am a window. My husband used to be the main source of money for the family. We are struggling because he is not more</t>
+  </si>
+  <si>
+    <t>Sanitation at home</t>
+  </si>
+  <si>
+    <t>Children served first and adults eat last</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>They will try their best to eat well at homes, they will support their children to go to school especially the girls. They will protect their environment</t>
+  </si>
+  <si>
+    <t>The.cooking demos should have been practical so that they learn well</t>
+  </si>
+  <si>
+    <t>Community members turned up thinking the demos were real practical. Most of them went back home not very satisfied</t>
+  </si>
+  <si>
+    <t>4964b72e-d6cb-49d4-81cc-e9468dc04607</t>
+  </si>
+  <si>
+    <t>uuid:4964b72e-d6cb-49d4-81cc-e9468dc04607</t>
   </si>
 </sst>
 </file>
@@ -6995,8 +7475,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG100" totalsRowShown="0">
-  <autoFilter ref="A1:AFG100" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG116" totalsRowShown="0">
+  <autoFilter ref="A1:AFG116" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -8129,7 +8609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFG100"/>
+  <dimension ref="A1:AFG116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -34511,6 +34991,3269 @@
         <v>99</v>
       </c>
     </row>
+    <row r="101" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B101" t="s">
+        <v>706</v>
+      </c>
+      <c r="C101" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D101" t="s">
+        <v>591</v>
+      </c>
+      <c r="E101" t="s">
+        <v>752</v>
+      </c>
+      <c r="F101" t="s">
+        <v>2299</v>
+      </c>
+      <c r="EN101" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO101">
+        <v>920</v>
+      </c>
+      <c r="EP101">
+        <v>928</v>
+      </c>
+      <c r="EQ101" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER101" t="s">
+        <v>1157</v>
+      </c>
+      <c r="ES101">
+        <v>0</v>
+      </c>
+      <c r="ET101">
+        <v>1</v>
+      </c>
+      <c r="EU101">
+        <v>0</v>
+      </c>
+      <c r="EV101">
+        <v>1</v>
+      </c>
+      <c r="EW101">
+        <v>0</v>
+      </c>
+      <c r="EX101">
+        <v>0</v>
+      </c>
+      <c r="EZ101" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA101">
+        <v>50</v>
+      </c>
+      <c r="FB101" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC101">
+        <v>1</v>
+      </c>
+      <c r="FD101">
+        <v>1</v>
+      </c>
+      <c r="FE101">
+        <v>1</v>
+      </c>
+      <c r="FF101" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG101" t="s">
+        <v>2300</v>
+      </c>
+      <c r="FH101" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP101">
+        <v>690</v>
+      </c>
+      <c r="NQ101">
+        <v>690</v>
+      </c>
+      <c r="NS101">
+        <v>581</v>
+      </c>
+      <c r="NT101">
+        <v>581</v>
+      </c>
+      <c r="NV101">
+        <v>572</v>
+      </c>
+      <c r="NW101">
+        <v>572</v>
+      </c>
+      <c r="SD101" s="1"/>
+      <c r="UH101" t="s">
+        <v>2301</v>
+      </c>
+      <c r="ZL101" s="1"/>
+      <c r="ADO101" s="1"/>
+      <c r="ADW101" s="1"/>
+      <c r="AEA101" s="1"/>
+      <c r="AEY101">
+        <v>892615656</v>
+      </c>
+      <c r="AEZ101" t="s">
+        <v>2302</v>
+      </c>
+      <c r="AFA101" s="1">
+        <v>46308.563425925917</v>
+      </c>
+      <c r="AFC101" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE101" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF101" t="s">
+        <v>2303</v>
+      </c>
+      <c r="AFG101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B102" t="s">
+        <v>706</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D102" t="s">
+        <v>596</v>
+      </c>
+      <c r="E102" t="s">
+        <v>752</v>
+      </c>
+      <c r="K102" t="s">
+        <v>2304</v>
+      </c>
+      <c r="EN102" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO102">
+        <v>586</v>
+      </c>
+      <c r="EP102">
+        <v>596</v>
+      </c>
+      <c r="EQ102" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER102" t="s">
+        <v>1098</v>
+      </c>
+      <c r="ES102">
+        <v>0</v>
+      </c>
+      <c r="ET102">
+        <v>0</v>
+      </c>
+      <c r="EU102">
+        <v>0</v>
+      </c>
+      <c r="EV102">
+        <v>1</v>
+      </c>
+      <c r="EW102">
+        <v>0</v>
+      </c>
+      <c r="EX102">
+        <v>0</v>
+      </c>
+      <c r="EZ102" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA102">
+        <v>30</v>
+      </c>
+      <c r="FB102" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC102">
+        <v>1</v>
+      </c>
+      <c r="FD102">
+        <v>1</v>
+      </c>
+      <c r="FE102">
+        <v>1</v>
+      </c>
+      <c r="FF102" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG102" t="s">
+        <v>2305</v>
+      </c>
+      <c r="FH102" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP102">
+        <v>299</v>
+      </c>
+      <c r="NQ102">
+        <v>344</v>
+      </c>
+      <c r="NS102">
+        <v>171</v>
+      </c>
+      <c r="NT102">
+        <v>171</v>
+      </c>
+      <c r="NV102">
+        <v>113</v>
+      </c>
+      <c r="NW102">
+        <v>114</v>
+      </c>
+      <c r="SD102" s="1"/>
+      <c r="UH102" t="s">
+        <v>1123</v>
+      </c>
+      <c r="ZL102" s="1"/>
+      <c r="ADO102" s="1"/>
+      <c r="ADW102" s="1"/>
+      <c r="AEA102" s="1"/>
+      <c r="AEY102">
+        <v>892681046</v>
+      </c>
+      <c r="AEZ102" t="s">
+        <v>2306</v>
+      </c>
+      <c r="AFA102" s="1">
+        <v>46308.613842592589</v>
+      </c>
+      <c r="AFC102" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE102" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF102" t="s">
+        <v>2307</v>
+      </c>
+      <c r="AFG102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B103" t="s">
+        <v>706</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D103" t="s">
+        <v>596</v>
+      </c>
+      <c r="E103" t="s">
+        <v>752</v>
+      </c>
+      <c r="K103" t="s">
+        <v>2304</v>
+      </c>
+      <c r="EN103" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT103">
+        <v>89</v>
+      </c>
+      <c r="FU103">
+        <v>105</v>
+      </c>
+      <c r="FV103">
+        <v>1</v>
+      </c>
+      <c r="FW103">
+        <v>1</v>
+      </c>
+      <c r="FY103">
+        <v>79</v>
+      </c>
+      <c r="FZ103">
+        <v>98</v>
+      </c>
+      <c r="GA103">
+        <v>0</v>
+      </c>
+      <c r="GB103">
+        <v>0</v>
+      </c>
+      <c r="GD103">
+        <v>50</v>
+      </c>
+      <c r="GE103">
+        <v>88</v>
+      </c>
+      <c r="GF103">
+        <v>0</v>
+      </c>
+      <c r="GG103">
+        <v>1</v>
+      </c>
+      <c r="GI103">
+        <v>3</v>
+      </c>
+      <c r="GJ103">
+        <v>2</v>
+      </c>
+      <c r="GK103">
+        <v>0</v>
+      </c>
+      <c r="GL103">
+        <v>0</v>
+      </c>
+      <c r="GN103">
+        <v>1</v>
+      </c>
+      <c r="GO103">
+        <v>3</v>
+      </c>
+      <c r="GP103">
+        <v>0</v>
+      </c>
+      <c r="GQ103">
+        <v>0</v>
+      </c>
+      <c r="GR103" t="s">
+        <v>2308</v>
+      </c>
+      <c r="GS103">
+        <v>1</v>
+      </c>
+      <c r="GT103">
+        <v>1</v>
+      </c>
+      <c r="GU103">
+        <v>0</v>
+      </c>
+      <c r="GV103">
+        <v>0</v>
+      </c>
+      <c r="GW103">
+        <v>1</v>
+      </c>
+      <c r="GX103">
+        <v>0</v>
+      </c>
+      <c r="GY103">
+        <v>1</v>
+      </c>
+      <c r="GZ103" t="s">
+        <v>1294</v>
+      </c>
+      <c r="HA103">
+        <v>1</v>
+      </c>
+      <c r="HB103">
+        <v>0</v>
+      </c>
+      <c r="HC103">
+        <v>1</v>
+      </c>
+      <c r="HD103">
+        <v>1</v>
+      </c>
+      <c r="HE103">
+        <v>0</v>
+      </c>
+      <c r="HG103" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH103" t="s">
+        <v>2309</v>
+      </c>
+      <c r="HI103" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ103" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL103" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM103" t="s">
+        <v>2310</v>
+      </c>
+      <c r="HT103" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU103">
+        <v>1</v>
+      </c>
+      <c r="HV103" t="s">
+        <v>2311</v>
+      </c>
+      <c r="HX103" t="s">
+        <v>766</v>
+      </c>
+      <c r="HY103">
+        <v>3</v>
+      </c>
+      <c r="HZ103" t="s">
+        <v>2312</v>
+      </c>
+      <c r="IB103" t="s">
+        <v>766</v>
+      </c>
+      <c r="IC103">
+        <v>2</v>
+      </c>
+      <c r="ID103" t="s">
+        <v>2313</v>
+      </c>
+      <c r="IF103" t="s">
+        <v>766</v>
+      </c>
+      <c r="IG103">
+        <v>3</v>
+      </c>
+      <c r="IH103" t="s">
+        <v>2314</v>
+      </c>
+      <c r="IJ103" t="s">
+        <v>830</v>
+      </c>
+      <c r="IK103">
+        <v>2</v>
+      </c>
+      <c r="IL103" t="s">
+        <v>2315</v>
+      </c>
+      <c r="IV103" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW103" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX103" t="s">
+        <v>2316</v>
+      </c>
+      <c r="IY103" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ103" t="s">
+        <v>1363</v>
+      </c>
+      <c r="JA103" t="s">
+        <v>716</v>
+      </c>
+      <c r="JC103" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD103" t="s">
+        <v>879</v>
+      </c>
+      <c r="JE103" t="s">
+        <v>2317</v>
+      </c>
+      <c r="JF103" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG103" t="s">
+        <v>1256</v>
+      </c>
+      <c r="JH103" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ103" t="s">
+        <v>837</v>
+      </c>
+      <c r="JK103" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JL103" t="s">
+        <v>2318</v>
+      </c>
+      <c r="JM103" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JN103" t="s">
+        <v>1361</v>
+      </c>
+      <c r="JO103" t="s">
+        <v>720</v>
+      </c>
+      <c r="JQ103" t="s">
+        <v>835</v>
+      </c>
+      <c r="JR103" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS103" t="s">
+        <v>2319</v>
+      </c>
+      <c r="JT103" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU103" t="s">
+        <v>1252</v>
+      </c>
+      <c r="JV103" t="s">
+        <v>716</v>
+      </c>
+      <c r="JX103" t="s">
+        <v>835</v>
+      </c>
+      <c r="JY103" t="s">
+        <v>879</v>
+      </c>
+      <c r="JZ103" t="s">
+        <v>2320</v>
+      </c>
+      <c r="KA103" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB103" t="s">
+        <v>1252</v>
+      </c>
+      <c r="KC103" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE103" t="s">
+        <v>835</v>
+      </c>
+      <c r="KF103" t="s">
+        <v>879</v>
+      </c>
+      <c r="KG103" t="s">
+        <v>2321</v>
+      </c>
+      <c r="KH103" t="s">
+        <v>839</v>
+      </c>
+      <c r="KI103" t="s">
+        <v>1211</v>
+      </c>
+      <c r="KJ103" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK103" t="s">
+        <v>1901</v>
+      </c>
+      <c r="KL103">
+        <v>0</v>
+      </c>
+      <c r="KM103">
+        <v>1</v>
+      </c>
+      <c r="KN103">
+        <v>0</v>
+      </c>
+      <c r="KO103">
+        <v>0</v>
+      </c>
+      <c r="KP103">
+        <v>0</v>
+      </c>
+      <c r="KR103" t="s">
+        <v>2322</v>
+      </c>
+      <c r="KS103" t="s">
+        <v>2323</v>
+      </c>
+      <c r="KT103" t="s">
+        <v>2324</v>
+      </c>
+      <c r="KU103" t="s">
+        <v>2325</v>
+      </c>
+      <c r="NP103">
+        <v>299</v>
+      </c>
+      <c r="NQ103">
+        <v>344</v>
+      </c>
+      <c r="NS103">
+        <v>171</v>
+      </c>
+      <c r="NT103">
+        <v>171</v>
+      </c>
+      <c r="NV103">
+        <v>113</v>
+      </c>
+      <c r="NW103">
+        <v>114</v>
+      </c>
+      <c r="SD103" s="1"/>
+      <c r="UH103" t="s">
+        <v>1123</v>
+      </c>
+      <c r="ZL103" s="1"/>
+      <c r="ADO103" s="1"/>
+      <c r="ADW103" s="1"/>
+      <c r="AEA103" s="1"/>
+      <c r="AEY103">
+        <v>892694516</v>
+      </c>
+      <c r="AEZ103" t="s">
+        <v>2326</v>
+      </c>
+      <c r="AFA103" s="1">
+        <v>46308.624328703707</v>
+      </c>
+      <c r="AFC103" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE103" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF103" t="s">
+        <v>2327</v>
+      </c>
+      <c r="AFG103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B104" t="s">
+        <v>706</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D104" t="s">
+        <v>596</v>
+      </c>
+      <c r="E104" t="s">
+        <v>752</v>
+      </c>
+      <c r="K104" t="s">
+        <v>1961</v>
+      </c>
+      <c r="EN104" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO104">
+        <v>641</v>
+      </c>
+      <c r="EP104">
+        <v>580</v>
+      </c>
+      <c r="EQ104" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER104" t="s">
+        <v>1157</v>
+      </c>
+      <c r="ES104">
+        <v>0</v>
+      </c>
+      <c r="ET104">
+        <v>1</v>
+      </c>
+      <c r="EU104">
+        <v>0</v>
+      </c>
+      <c r="EV104">
+        <v>1</v>
+      </c>
+      <c r="EW104">
+        <v>0</v>
+      </c>
+      <c r="EX104">
+        <v>0</v>
+      </c>
+      <c r="EZ104" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA104">
+        <v>35</v>
+      </c>
+      <c r="FB104" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC104">
+        <v>1</v>
+      </c>
+      <c r="FD104">
+        <v>1</v>
+      </c>
+      <c r="FE104">
+        <v>1</v>
+      </c>
+      <c r="FF104" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG104" t="s">
+        <v>1882</v>
+      </c>
+      <c r="FH104" t="s">
+        <v>711</v>
+      </c>
+      <c r="FI104">
+        <v>0</v>
+      </c>
+      <c r="FJ104" t="s">
+        <v>706</v>
+      </c>
+      <c r="FK104">
+        <v>0</v>
+      </c>
+      <c r="FL104">
+        <v>1</v>
+      </c>
+      <c r="NP104">
+        <v>197</v>
+      </c>
+      <c r="NQ104">
+        <v>237</v>
+      </c>
+      <c r="NS104">
+        <v>264</v>
+      </c>
+      <c r="NT104">
+        <v>193</v>
+      </c>
+      <c r="NV104">
+        <v>177</v>
+      </c>
+      <c r="NW104">
+        <v>150</v>
+      </c>
+      <c r="SD104" s="1"/>
+      <c r="UH104" t="s">
+        <v>1123</v>
+      </c>
+      <c r="ZL104" s="1"/>
+      <c r="ADO104" s="1"/>
+      <c r="ADW104" s="1"/>
+      <c r="AEA104" s="1"/>
+      <c r="AEY104">
+        <v>892697079</v>
+      </c>
+      <c r="AEZ104" t="s">
+        <v>2328</v>
+      </c>
+      <c r="AFA104" s="1">
+        <v>46308.626585648148</v>
+      </c>
+      <c r="AFC104" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE104" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF104" t="s">
+        <v>2329</v>
+      </c>
+      <c r="AFG104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B105" t="s">
+        <v>706</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D105" t="s">
+        <v>596</v>
+      </c>
+      <c r="E105" t="s">
+        <v>752</v>
+      </c>
+      <c r="K105" t="s">
+        <v>1961</v>
+      </c>
+      <c r="EN105" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT105">
+        <v>60</v>
+      </c>
+      <c r="FU105">
+        <v>89</v>
+      </c>
+      <c r="FV105">
+        <v>0</v>
+      </c>
+      <c r="FW105">
+        <v>2</v>
+      </c>
+      <c r="FY105">
+        <v>77</v>
+      </c>
+      <c r="FZ105">
+        <v>51</v>
+      </c>
+      <c r="GA105">
+        <v>0</v>
+      </c>
+      <c r="GB105">
+        <v>0</v>
+      </c>
+      <c r="GD105">
+        <v>68</v>
+      </c>
+      <c r="GE105">
+        <v>70</v>
+      </c>
+      <c r="GF105">
+        <v>1</v>
+      </c>
+      <c r="GG105">
+        <v>0</v>
+      </c>
+      <c r="GI105">
+        <v>2</v>
+      </c>
+      <c r="GJ105">
+        <v>2</v>
+      </c>
+      <c r="GK105">
+        <v>0</v>
+      </c>
+      <c r="GL105">
+        <v>0</v>
+      </c>
+      <c r="GN105">
+        <v>0</v>
+      </c>
+      <c r="GO105">
+        <v>0</v>
+      </c>
+      <c r="GP105">
+        <v>0</v>
+      </c>
+      <c r="GQ105">
+        <v>0</v>
+      </c>
+      <c r="GR105" t="s">
+        <v>2308</v>
+      </c>
+      <c r="GS105">
+        <v>1</v>
+      </c>
+      <c r="GT105">
+        <v>1</v>
+      </c>
+      <c r="GU105">
+        <v>0</v>
+      </c>
+      <c r="GV105">
+        <v>0</v>
+      </c>
+      <c r="GW105">
+        <v>1</v>
+      </c>
+      <c r="GX105">
+        <v>0</v>
+      </c>
+      <c r="GY105">
+        <v>1</v>
+      </c>
+      <c r="GZ105" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HA105">
+        <v>1</v>
+      </c>
+      <c r="HB105">
+        <v>0</v>
+      </c>
+      <c r="HC105">
+        <v>1</v>
+      </c>
+      <c r="HD105">
+        <v>1</v>
+      </c>
+      <c r="HE105">
+        <v>1</v>
+      </c>
+      <c r="HF105" t="s">
+        <v>2331</v>
+      </c>
+      <c r="HG105" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH105" t="s">
+        <v>2332</v>
+      </c>
+      <c r="HI105" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ105" t="s">
+        <v>711</v>
+      </c>
+      <c r="HK105" t="s">
+        <v>2333</v>
+      </c>
+      <c r="HL105" t="s">
+        <v>732</v>
+      </c>
+      <c r="HT105" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU105">
+        <v>3</v>
+      </c>
+      <c r="HV105" t="s">
+        <v>2334</v>
+      </c>
+      <c r="HX105" t="s">
+        <v>766</v>
+      </c>
+      <c r="HY105">
+        <v>3</v>
+      </c>
+      <c r="HZ105" t="s">
+        <v>2335</v>
+      </c>
+      <c r="IB105" t="s">
+        <v>766</v>
+      </c>
+      <c r="IC105">
+        <v>3</v>
+      </c>
+      <c r="ID105" t="s">
+        <v>2336</v>
+      </c>
+      <c r="IF105" t="s">
+        <v>766</v>
+      </c>
+      <c r="IG105">
+        <v>3</v>
+      </c>
+      <c r="IH105" t="s">
+        <v>2337</v>
+      </c>
+      <c r="IJ105" t="s">
+        <v>766</v>
+      </c>
+      <c r="IK105">
+        <v>2</v>
+      </c>
+      <c r="IL105" t="s">
+        <v>2338</v>
+      </c>
+      <c r="IV105" t="s">
+        <v>835</v>
+      </c>
+      <c r="IW105" t="s">
+        <v>879</v>
+      </c>
+      <c r="IX105" t="s">
+        <v>2339</v>
+      </c>
+      <c r="IY105" t="s">
+        <v>839</v>
+      </c>
+      <c r="IZ105" t="s">
+        <v>1337</v>
+      </c>
+      <c r="JA105" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC105" t="s">
+        <v>837</v>
+      </c>
+      <c r="JD105" t="s">
+        <v>879</v>
+      </c>
+      <c r="JE105" t="s">
+        <v>2340</v>
+      </c>
+      <c r="JF105" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG105" t="s">
+        <v>1252</v>
+      </c>
+      <c r="JH105" t="s">
+        <v>716</v>
+      </c>
+      <c r="JJ105" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK105" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL105" t="s">
+        <v>2341</v>
+      </c>
+      <c r="JM105" t="s">
+        <v>839</v>
+      </c>
+      <c r="JN105" t="s">
+        <v>2342</v>
+      </c>
+      <c r="JO105" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ105" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR105" t="s">
+        <v>879</v>
+      </c>
+      <c r="JS105" t="s">
+        <v>2343</v>
+      </c>
+      <c r="JT105" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU105" t="s">
+        <v>2344</v>
+      </c>
+      <c r="JV105" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX105" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY105" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ105" t="s">
+        <v>2345</v>
+      </c>
+      <c r="KA105" t="s">
+        <v>839</v>
+      </c>
+      <c r="KB105" t="s">
+        <v>2346</v>
+      </c>
+      <c r="KC105" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE105" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF105" t="s">
+        <v>769</v>
+      </c>
+      <c r="KG105" t="s">
+        <v>2347</v>
+      </c>
+      <c r="KH105" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI105" t="s">
+        <v>2348</v>
+      </c>
+      <c r="KJ105" t="s">
+        <v>720</v>
+      </c>
+      <c r="KK105" t="s">
+        <v>706</v>
+      </c>
+      <c r="KL105">
+        <v>0</v>
+      </c>
+      <c r="KM105">
+        <v>0</v>
+      </c>
+      <c r="KN105">
+        <v>0</v>
+      </c>
+      <c r="KO105">
+        <v>1</v>
+      </c>
+      <c r="KP105">
+        <v>0</v>
+      </c>
+      <c r="KR105" t="s">
+        <v>1149</v>
+      </c>
+      <c r="KS105" t="s">
+        <v>2349</v>
+      </c>
+      <c r="KT105" t="s">
+        <v>2350</v>
+      </c>
+      <c r="KU105" t="s">
+        <v>2351</v>
+      </c>
+      <c r="NP105">
+        <v>197</v>
+      </c>
+      <c r="NQ105">
+        <v>235</v>
+      </c>
+      <c r="NS105">
+        <v>245</v>
+      </c>
+      <c r="NT105">
+        <v>194</v>
+      </c>
+      <c r="NV105">
+        <v>177</v>
+      </c>
+      <c r="NW105">
+        <v>145</v>
+      </c>
+      <c r="SD105" s="1"/>
+      <c r="UH105" t="s">
+        <v>1123</v>
+      </c>
+      <c r="ZL105" s="1"/>
+      <c r="ADO105" s="1"/>
+      <c r="ADW105" s="1"/>
+      <c r="AEA105" s="1"/>
+      <c r="AEY105">
+        <v>892707241</v>
+      </c>
+      <c r="AEZ105" t="s">
+        <v>2352</v>
+      </c>
+      <c r="AFA105" s="1">
+        <v>46308.634236111109</v>
+      </c>
+      <c r="AFC105" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE105" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF105" t="s">
+        <v>2353</v>
+      </c>
+      <c r="AFG105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B106" t="s">
+        <v>706</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D106" t="s">
+        <v>596</v>
+      </c>
+      <c r="E106" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K106" t="s">
+        <v>2304</v>
+      </c>
+      <c r="NX106" t="s">
+        <v>2354</v>
+      </c>
+      <c r="NY106" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ106" t="s">
+        <v>2355</v>
+      </c>
+      <c r="OA106" t="s">
+        <v>711</v>
+      </c>
+      <c r="OB106" t="s">
+        <v>1914</v>
+      </c>
+      <c r="OC106">
+        <v>1</v>
+      </c>
+      <c r="OD106">
+        <v>1</v>
+      </c>
+      <c r="OE106">
+        <v>0</v>
+      </c>
+      <c r="OF106">
+        <v>0</v>
+      </c>
+      <c r="OG106">
+        <v>0</v>
+      </c>
+      <c r="OI106" t="s">
+        <v>2356</v>
+      </c>
+      <c r="OJ106">
+        <v>1</v>
+      </c>
+      <c r="OK106">
+        <v>0</v>
+      </c>
+      <c r="OL106">
+        <v>0</v>
+      </c>
+      <c r="OM106">
+        <v>1</v>
+      </c>
+      <c r="ON106" t="s">
+        <v>2357</v>
+      </c>
+      <c r="OS106">
+        <v>34</v>
+      </c>
+      <c r="OT106" t="s">
+        <v>819</v>
+      </c>
+      <c r="OV106">
+        <v>17</v>
+      </c>
+      <c r="OW106" t="s">
+        <v>819</v>
+      </c>
+      <c r="OY106">
+        <v>4</v>
+      </c>
+      <c r="OZ106" t="s">
+        <v>819</v>
+      </c>
+      <c r="PB106">
+        <v>11</v>
+      </c>
+      <c r="PC106" t="s">
+        <v>819</v>
+      </c>
+      <c r="PE106">
+        <v>0</v>
+      </c>
+      <c r="PF106" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH106">
+        <v>1</v>
+      </c>
+      <c r="PI106" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ106" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL106" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM106" t="s">
+        <v>2358</v>
+      </c>
+      <c r="PN106" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO106" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ106" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR106" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS106">
+        <v>0</v>
+      </c>
+      <c r="PT106">
+        <v>0</v>
+      </c>
+      <c r="PU106">
+        <v>1</v>
+      </c>
+      <c r="PV106" t="s">
+        <v>2357</v>
+      </c>
+      <c r="PW106" t="s">
+        <v>1922</v>
+      </c>
+      <c r="PX106">
+        <v>1</v>
+      </c>
+      <c r="PY106">
+        <v>0</v>
+      </c>
+      <c r="PZ106">
+        <v>0</v>
+      </c>
+      <c r="QA106">
+        <v>0</v>
+      </c>
+      <c r="QJ106" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QK106" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL106" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM106" t="s">
+        <v>2359</v>
+      </c>
+      <c r="QN106" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP106" t="s">
+        <v>2141</v>
+      </c>
+      <c r="QQ106" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR106" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS106" t="s">
+        <v>2360</v>
+      </c>
+      <c r="QT106" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV106" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW106" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QX106" t="s">
+        <v>2244</v>
+      </c>
+      <c r="QY106" t="s">
+        <v>2361</v>
+      </c>
+      <c r="QZ106" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA106" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB106" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC106" t="s">
+        <v>1957</v>
+      </c>
+      <c r="RD106">
+        <v>0</v>
+      </c>
+      <c r="RE106">
+        <v>0</v>
+      </c>
+      <c r="RF106">
+        <v>1</v>
+      </c>
+      <c r="RG106">
+        <v>0</v>
+      </c>
+      <c r="RH106">
+        <v>0</v>
+      </c>
+      <c r="RJ106" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK106">
+        <v>0</v>
+      </c>
+      <c r="RL106">
+        <v>0</v>
+      </c>
+      <c r="RM106">
+        <v>1</v>
+      </c>
+      <c r="RN106" t="s">
+        <v>2362</v>
+      </c>
+      <c r="RO106" t="s">
+        <v>1953</v>
+      </c>
+      <c r="RP106" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ106" t="s">
+        <v>1972</v>
+      </c>
+      <c r="RR106" t="s">
+        <v>2363</v>
+      </c>
+      <c r="RS106" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT106" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY106" t="s">
+        <v>1956</v>
+      </c>
+      <c r="RZ106" t="s">
+        <v>1568</v>
+      </c>
+      <c r="SA106" t="s">
+        <v>2364</v>
+      </c>
+      <c r="SB106" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD106" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH106" t="s">
+        <v>1123</v>
+      </c>
+      <c r="ZL106" s="1"/>
+      <c r="ADO106" s="1"/>
+      <c r="ADW106" s="1"/>
+      <c r="AEA106" s="1"/>
+      <c r="AEY106">
+        <v>892715494</v>
+      </c>
+      <c r="AEZ106" t="s">
+        <v>2365</v>
+      </c>
+      <c r="AFA106" s="1">
+        <v>46308.641412037039</v>
+      </c>
+      <c r="AFC106" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE106" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF106" t="s">
+        <v>2366</v>
+      </c>
+      <c r="AFG106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B107" t="s">
+        <v>706</v>
+      </c>
+      <c r="C107" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D107" t="s">
+        <v>591</v>
+      </c>
+      <c r="E107" t="s">
+        <v>752</v>
+      </c>
+      <c r="F107" t="s">
+        <v>2368</v>
+      </c>
+      <c r="EN107" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO107">
+        <v>670</v>
+      </c>
+      <c r="EP107">
+        <v>692</v>
+      </c>
+      <c r="EQ107" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER107" t="s">
+        <v>970</v>
+      </c>
+      <c r="ES107">
+        <v>0</v>
+      </c>
+      <c r="ET107">
+        <v>0</v>
+      </c>
+      <c r="EU107">
+        <v>1</v>
+      </c>
+      <c r="EV107">
+        <v>0</v>
+      </c>
+      <c r="EW107">
+        <v>1</v>
+      </c>
+      <c r="EX107">
+        <v>0</v>
+      </c>
+      <c r="EZ107" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA107">
+        <v>50</v>
+      </c>
+      <c r="FB107" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC107">
+        <v>1</v>
+      </c>
+      <c r="FD107">
+        <v>1</v>
+      </c>
+      <c r="FE107">
+        <v>1</v>
+      </c>
+      <c r="FF107" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG107" t="s">
+        <v>2369</v>
+      </c>
+      <c r="FH107" t="s">
+        <v>711</v>
+      </c>
+      <c r="FI107">
+        <v>5</v>
+      </c>
+      <c r="FJ107" t="s">
+        <v>706</v>
+      </c>
+      <c r="FK107">
+        <v>0</v>
+      </c>
+      <c r="FL107">
+        <v>1</v>
+      </c>
+      <c r="NP107">
+        <v>587</v>
+      </c>
+      <c r="NQ107">
+        <v>587</v>
+      </c>
+      <c r="NS107">
+        <v>476</v>
+      </c>
+      <c r="NT107">
+        <v>476</v>
+      </c>
+      <c r="NV107">
+        <v>297</v>
+      </c>
+      <c r="NW107">
+        <v>297</v>
+      </c>
+      <c r="SD107" s="1"/>
+      <c r="UH107" t="s">
+        <v>2370</v>
+      </c>
+      <c r="ZL107" s="1"/>
+      <c r="ADO107" s="1"/>
+      <c r="ADW107" s="1"/>
+      <c r="AEA107" s="1"/>
+      <c r="AEY107">
+        <v>892716941</v>
+      </c>
+      <c r="AEZ107" t="s">
+        <v>2371</v>
+      </c>
+      <c r="AFA107" s="1">
+        <v>46308.642777777779</v>
+      </c>
+      <c r="AFC107" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE107" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF107" t="s">
+        <v>2372</v>
+      </c>
+      <c r="AFG107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B108" t="s">
+        <v>706</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D108" t="s">
+        <v>596</v>
+      </c>
+      <c r="E108" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K108" t="s">
+        <v>1961</v>
+      </c>
+      <c r="NX108" t="s">
+        <v>2373</v>
+      </c>
+      <c r="NY108" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ108" t="s">
+        <v>1963</v>
+      </c>
+      <c r="OA108" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS108">
+        <v>0</v>
+      </c>
+      <c r="OT108" t="s">
+        <v>2041</v>
+      </c>
+      <c r="OV108">
+        <v>15</v>
+      </c>
+      <c r="OW108" t="s">
+        <v>819</v>
+      </c>
+      <c r="OY108">
+        <v>9</v>
+      </c>
+      <c r="OZ108" t="s">
+        <v>819</v>
+      </c>
+      <c r="PB108">
+        <v>0</v>
+      </c>
+      <c r="PC108" t="s">
+        <v>767</v>
+      </c>
+      <c r="PE108">
+        <v>0</v>
+      </c>
+      <c r="PF108" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH108">
+        <v>0</v>
+      </c>
+      <c r="PI108" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ108" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL108" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM108" t="s">
+        <v>2375</v>
+      </c>
+      <c r="PN108" t="s">
+        <v>732</v>
+      </c>
+      <c r="PO108" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ108" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR108" t="s">
+        <v>2376</v>
+      </c>
+      <c r="PS108">
+        <v>0</v>
+      </c>
+      <c r="PT108">
+        <v>1</v>
+      </c>
+      <c r="PU108">
+        <v>1</v>
+      </c>
+      <c r="PV108" t="s">
+        <v>2377</v>
+      </c>
+      <c r="PW108" t="s">
+        <v>2378</v>
+      </c>
+      <c r="PX108">
+        <v>0</v>
+      </c>
+      <c r="PY108">
+        <v>0</v>
+      </c>
+      <c r="PZ108">
+        <v>1</v>
+      </c>
+      <c r="QA108">
+        <v>0</v>
+      </c>
+      <c r="QJ108" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK108" t="s">
+        <v>2263</v>
+      </c>
+      <c r="QL108" t="s">
+        <v>2244</v>
+      </c>
+      <c r="QM108" t="s">
+        <v>2379</v>
+      </c>
+      <c r="QN108" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP108" t="s">
+        <v>2141</v>
+      </c>
+      <c r="QQ108" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QR108" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS108" t="s">
+        <v>2380</v>
+      </c>
+      <c r="QT108" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV108" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QW108" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX108" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY108" t="s">
+        <v>2381</v>
+      </c>
+      <c r="QZ108" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA108" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB108" t="s">
+        <v>732</v>
+      </c>
+      <c r="RC108" t="s">
+        <v>1957</v>
+      </c>
+      <c r="RD108">
+        <v>0</v>
+      </c>
+      <c r="RE108">
+        <v>0</v>
+      </c>
+      <c r="RF108">
+        <v>1</v>
+      </c>
+      <c r="RG108">
+        <v>0</v>
+      </c>
+      <c r="RH108">
+        <v>0</v>
+      </c>
+      <c r="RJ108" t="s">
+        <v>2051</v>
+      </c>
+      <c r="RK108">
+        <v>1</v>
+      </c>
+      <c r="RL108">
+        <v>0</v>
+      </c>
+      <c r="RM108">
+        <v>0</v>
+      </c>
+      <c r="RO108" t="s">
+        <v>1953</v>
+      </c>
+      <c r="RP108" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ108" t="s">
+        <v>2382</v>
+      </c>
+      <c r="RR108" t="s">
+        <v>1972</v>
+      </c>
+      <c r="RS108" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT108" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY108" t="s">
+        <v>2383</v>
+      </c>
+      <c r="RZ108" t="s">
+        <v>1957</v>
+      </c>
+      <c r="SA108" t="s">
+        <v>2384</v>
+      </c>
+      <c r="SB108" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD108" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH108" t="s">
+        <v>1123</v>
+      </c>
+      <c r="ZL108" s="1"/>
+      <c r="ADO108" s="1"/>
+      <c r="ADW108" s="1"/>
+      <c r="AEA108" s="1"/>
+      <c r="AEY108">
+        <v>892721675</v>
+      </c>
+      <c r="AEZ108" t="s">
+        <v>2385</v>
+      </c>
+      <c r="AFA108" s="1">
+        <v>46308.646956018521</v>
+      </c>
+      <c r="AFC108" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE108" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF108" t="s">
+        <v>2386</v>
+      </c>
+      <c r="AFG108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B109" t="s">
+        <v>706</v>
+      </c>
+      <c r="C109" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D109" t="s">
+        <v>591</v>
+      </c>
+      <c r="E109" t="s">
+        <v>752</v>
+      </c>
+      <c r="F109" t="s">
+        <v>2387</v>
+      </c>
+      <c r="EN109" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO109">
+        <v>620</v>
+      </c>
+      <c r="EP109">
+        <v>530</v>
+      </c>
+      <c r="EQ109" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER109" t="s">
+        <v>970</v>
+      </c>
+      <c r="ES109">
+        <v>0</v>
+      </c>
+      <c r="ET109">
+        <v>0</v>
+      </c>
+      <c r="EU109">
+        <v>1</v>
+      </c>
+      <c r="EV109">
+        <v>0</v>
+      </c>
+      <c r="EW109">
+        <v>1</v>
+      </c>
+      <c r="EX109">
+        <v>0</v>
+      </c>
+      <c r="EZ109" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA109">
+        <v>50</v>
+      </c>
+      <c r="FB109" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC109">
+        <v>1</v>
+      </c>
+      <c r="FD109">
+        <v>1</v>
+      </c>
+      <c r="FE109">
+        <v>1</v>
+      </c>
+      <c r="FF109" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG109" t="s">
+        <v>2388</v>
+      </c>
+      <c r="FH109" t="s">
+        <v>711</v>
+      </c>
+      <c r="FI109">
+        <v>10</v>
+      </c>
+      <c r="FJ109" t="s">
+        <v>706</v>
+      </c>
+      <c r="FK109">
+        <v>0</v>
+      </c>
+      <c r="FL109">
+        <v>1</v>
+      </c>
+      <c r="NP109">
+        <v>487</v>
+      </c>
+      <c r="NQ109">
+        <v>487</v>
+      </c>
+      <c r="NS109">
+        <v>404</v>
+      </c>
+      <c r="NT109">
+        <v>404</v>
+      </c>
+      <c r="NV109">
+        <v>251</v>
+      </c>
+      <c r="NW109">
+        <v>251</v>
+      </c>
+      <c r="SD109" s="1"/>
+      <c r="UH109" t="s">
+        <v>2389</v>
+      </c>
+      <c r="ZL109" s="1"/>
+      <c r="ADO109" s="1"/>
+      <c r="ADW109" s="1"/>
+      <c r="AEA109" s="1"/>
+      <c r="AEY109">
+        <v>892724421</v>
+      </c>
+      <c r="AEZ109" t="s">
+        <v>2390</v>
+      </c>
+      <c r="AFA109" s="1">
+        <v>46308.649375000001</v>
+      </c>
+      <c r="AFC109" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE109" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF109" t="s">
+        <v>2391</v>
+      </c>
+      <c r="AFG109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B110" t="s">
+        <v>817</v>
+      </c>
+      <c r="D110" t="s">
+        <v>595</v>
+      </c>
+      <c r="E110" t="s">
+        <v>1910</v>
+      </c>
+      <c r="J110" t="s">
+        <v>1319</v>
+      </c>
+      <c r="NX110" t="s">
+        <v>2392</v>
+      </c>
+      <c r="NY110" t="s">
+        <v>2040</v>
+      </c>
+      <c r="OA110" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS110">
+        <v>0</v>
+      </c>
+      <c r="OT110" t="s">
+        <v>2080</v>
+      </c>
+      <c r="OV110">
+        <v>19</v>
+      </c>
+      <c r="OW110" t="s">
+        <v>819</v>
+      </c>
+      <c r="OY110">
+        <v>2</v>
+      </c>
+      <c r="OZ110" t="s">
+        <v>819</v>
+      </c>
+      <c r="PB110">
+        <v>21</v>
+      </c>
+      <c r="PC110" t="s">
+        <v>819</v>
+      </c>
+      <c r="PE110">
+        <v>1</v>
+      </c>
+      <c r="PF110" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH110">
+        <v>0</v>
+      </c>
+      <c r="PI110" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ110" t="s">
+        <v>706</v>
+      </c>
+      <c r="PK110" t="s">
+        <v>2393</v>
+      </c>
+      <c r="PL110" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM110" t="s">
+        <v>2394</v>
+      </c>
+      <c r="PN110" t="s">
+        <v>732</v>
+      </c>
+      <c r="PO110" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ110" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR110" t="s">
+        <v>2395</v>
+      </c>
+      <c r="PS110">
+        <v>0</v>
+      </c>
+      <c r="PT110">
+        <v>1</v>
+      </c>
+      <c r="PU110">
+        <v>0</v>
+      </c>
+      <c r="PW110" t="s">
+        <v>1922</v>
+      </c>
+      <c r="PX110">
+        <v>1</v>
+      </c>
+      <c r="PY110">
+        <v>0</v>
+      </c>
+      <c r="PZ110">
+        <v>0</v>
+      </c>
+      <c r="QA110">
+        <v>0</v>
+      </c>
+      <c r="QJ110" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK110" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL110" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM110" t="s">
+        <v>2396</v>
+      </c>
+      <c r="QN110" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP110" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QQ110" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QR110" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS110" t="s">
+        <v>2397</v>
+      </c>
+      <c r="QT110" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV110" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QW110" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QX110" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QY110" t="s">
+        <v>2398</v>
+      </c>
+      <c r="QZ110" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA110" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB110" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC110" t="s">
+        <v>2050</v>
+      </c>
+      <c r="RD110">
+        <v>0</v>
+      </c>
+      <c r="RE110">
+        <v>1</v>
+      </c>
+      <c r="RF110">
+        <v>0</v>
+      </c>
+      <c r="RG110">
+        <v>0</v>
+      </c>
+      <c r="RH110">
+        <v>0</v>
+      </c>
+      <c r="RJ110" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK110">
+        <v>0</v>
+      </c>
+      <c r="RL110">
+        <v>0</v>
+      </c>
+      <c r="RM110">
+        <v>1</v>
+      </c>
+      <c r="RN110" t="s">
+        <v>2399</v>
+      </c>
+      <c r="RO110" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP110" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ110" t="s">
+        <v>2400</v>
+      </c>
+      <c r="RR110" t="s">
+        <v>2401</v>
+      </c>
+      <c r="RS110" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT110" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY110" t="s">
+        <v>2402</v>
+      </c>
+      <c r="RZ110" t="s">
+        <v>2403</v>
+      </c>
+      <c r="SA110" t="s">
+        <v>2404</v>
+      </c>
+      <c r="SB110" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD110" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH110" t="s">
+        <v>2405</v>
+      </c>
+      <c r="ZL110" s="1"/>
+      <c r="ADO110" s="1"/>
+      <c r="ADW110" s="1"/>
+      <c r="AEA110" s="1"/>
+      <c r="AEY110">
+        <v>892728870</v>
+      </c>
+      <c r="AEZ110" t="s">
+        <v>2406</v>
+      </c>
+      <c r="AFA110" s="1">
+        <v>46308.653483796297</v>
+      </c>
+      <c r="AFC110" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE110" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF110" t="s">
+        <v>2407</v>
+      </c>
+      <c r="AFG110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B111" t="s">
+        <v>706</v>
+      </c>
+      <c r="C111" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D111" t="s">
+        <v>591</v>
+      </c>
+      <c r="E111" t="s">
+        <v>752</v>
+      </c>
+      <c r="F111" t="s">
+        <v>710</v>
+      </c>
+      <c r="EN111" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO111">
+        <v>969</v>
+      </c>
+      <c r="EP111">
+        <v>914</v>
+      </c>
+      <c r="EQ111" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER111" t="s">
+        <v>1702</v>
+      </c>
+      <c r="ES111">
+        <v>1</v>
+      </c>
+      <c r="ET111">
+        <v>0</v>
+      </c>
+      <c r="EU111">
+        <v>0</v>
+      </c>
+      <c r="EV111">
+        <v>1</v>
+      </c>
+      <c r="EW111">
+        <v>0</v>
+      </c>
+      <c r="EX111">
+        <v>0</v>
+      </c>
+      <c r="EZ111" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA111">
+        <v>50</v>
+      </c>
+      <c r="FB111" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC111">
+        <v>1</v>
+      </c>
+      <c r="FD111">
+        <v>1</v>
+      </c>
+      <c r="FE111">
+        <v>1</v>
+      </c>
+      <c r="FF111" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG111" t="s">
+        <v>2408</v>
+      </c>
+      <c r="FH111" t="s">
+        <v>711</v>
+      </c>
+      <c r="FI111">
+        <v>6</v>
+      </c>
+      <c r="FJ111" t="s">
+        <v>706</v>
+      </c>
+      <c r="FK111">
+        <v>0</v>
+      </c>
+      <c r="FL111">
+        <v>1</v>
+      </c>
+      <c r="NP111">
+        <v>582</v>
+      </c>
+      <c r="NQ111">
+        <v>582</v>
+      </c>
+      <c r="NS111">
+        <v>610</v>
+      </c>
+      <c r="NT111">
+        <v>610</v>
+      </c>
+      <c r="NV111">
+        <v>691</v>
+      </c>
+      <c r="NW111">
+        <v>691</v>
+      </c>
+      <c r="SD111" s="1"/>
+      <c r="UH111" t="s">
+        <v>2409</v>
+      </c>
+      <c r="ZL111" s="1"/>
+      <c r="ADO111" s="1"/>
+      <c r="ADW111" s="1"/>
+      <c r="AEA111" s="1"/>
+      <c r="AEY111">
+        <v>892732960</v>
+      </c>
+      <c r="AEZ111" t="s">
+        <v>2410</v>
+      </c>
+      <c r="AFA111" s="1">
+        <v>46308.656898148147</v>
+      </c>
+      <c r="AFC111" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE111" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF111" t="s">
+        <v>2411</v>
+      </c>
+      <c r="AFG111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B112" t="s">
+        <v>817</v>
+      </c>
+      <c r="D112" t="s">
+        <v>595</v>
+      </c>
+      <c r="E112" t="s">
+        <v>1910</v>
+      </c>
+      <c r="J112" t="s">
+        <v>1236</v>
+      </c>
+      <c r="NX112" t="s">
+        <v>2412</v>
+      </c>
+      <c r="NY112" t="s">
+        <v>2040</v>
+      </c>
+      <c r="OA112" t="s">
+        <v>711</v>
+      </c>
+      <c r="OB112" t="s">
+        <v>2413</v>
+      </c>
+      <c r="OC112">
+        <v>0</v>
+      </c>
+      <c r="OD112">
+        <v>1</v>
+      </c>
+      <c r="OE112">
+        <v>0</v>
+      </c>
+      <c r="OF112">
+        <v>0</v>
+      </c>
+      <c r="OG112">
+        <v>0</v>
+      </c>
+      <c r="OI112" t="s">
+        <v>2414</v>
+      </c>
+      <c r="OJ112">
+        <v>0</v>
+      </c>
+      <c r="OK112">
+        <v>1</v>
+      </c>
+      <c r="OL112">
+        <v>0</v>
+      </c>
+      <c r="OM112">
+        <v>0</v>
+      </c>
+      <c r="OS112">
+        <v>41</v>
+      </c>
+      <c r="OT112" t="s">
+        <v>819</v>
+      </c>
+      <c r="OV112">
+        <v>9</v>
+      </c>
+      <c r="OW112" t="s">
+        <v>819</v>
+      </c>
+      <c r="OY112">
+        <v>0</v>
+      </c>
+      <c r="OZ112" t="s">
+        <v>819</v>
+      </c>
+      <c r="PB112">
+        <v>0</v>
+      </c>
+      <c r="PC112" t="s">
+        <v>767</v>
+      </c>
+      <c r="PE112">
+        <v>0</v>
+      </c>
+      <c r="PF112" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH112">
+        <v>0</v>
+      </c>
+      <c r="PI112" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ112" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL112" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN112" t="s">
+        <v>732</v>
+      </c>
+      <c r="PO112" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ112" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR112" t="s">
+        <v>2415</v>
+      </c>
+      <c r="PS112">
+        <v>1</v>
+      </c>
+      <c r="PT112">
+        <v>1</v>
+      </c>
+      <c r="PU112">
+        <v>1</v>
+      </c>
+      <c r="PV112" t="s">
+        <v>2357</v>
+      </c>
+      <c r="PW112" t="s">
+        <v>1922</v>
+      </c>
+      <c r="PX112">
+        <v>1</v>
+      </c>
+      <c r="PY112">
+        <v>0</v>
+      </c>
+      <c r="PZ112">
+        <v>0</v>
+      </c>
+      <c r="QA112">
+        <v>0</v>
+      </c>
+      <c r="QJ112" t="s">
+        <v>2087</v>
+      </c>
+      <c r="QK112" t="s">
+        <v>1951</v>
+      </c>
+      <c r="QL112" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM112" t="s">
+        <v>2416</v>
+      </c>
+      <c r="QN112" t="s">
+        <v>720</v>
+      </c>
+      <c r="QP112" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ112" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR112" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS112" t="s">
+        <v>2417</v>
+      </c>
+      <c r="QT112" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV112" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QW112" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX112" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY112" t="s">
+        <v>2418</v>
+      </c>
+      <c r="QZ112" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA112" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB112" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC112" t="s">
+        <v>1957</v>
+      </c>
+      <c r="RD112">
+        <v>0</v>
+      </c>
+      <c r="RE112">
+        <v>0</v>
+      </c>
+      <c r="RF112">
+        <v>1</v>
+      </c>
+      <c r="RG112">
+        <v>0</v>
+      </c>
+      <c r="RH112">
+        <v>0</v>
+      </c>
+      <c r="RJ112" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK112">
+        <v>0</v>
+      </c>
+      <c r="RL112">
+        <v>0</v>
+      </c>
+      <c r="RM112">
+        <v>1</v>
+      </c>
+      <c r="RN112" t="s">
+        <v>2419</v>
+      </c>
+      <c r="RO112" t="s">
+        <v>1953</v>
+      </c>
+      <c r="RP112" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ112" t="s">
+        <v>2420</v>
+      </c>
+      <c r="RR112" t="s">
+        <v>2421</v>
+      </c>
+      <c r="RS112" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT112" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY112" t="s">
+        <v>2422</v>
+      </c>
+      <c r="RZ112" t="s">
+        <v>2403</v>
+      </c>
+      <c r="SA112" t="s">
+        <v>2423</v>
+      </c>
+      <c r="SB112" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD112" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH112" t="s">
+        <v>2424</v>
+      </c>
+      <c r="ZL112" s="1"/>
+      <c r="ADO112" s="1"/>
+      <c r="ADW112" s="1"/>
+      <c r="AEA112" s="1"/>
+      <c r="AEY112">
+        <v>892735954</v>
+      </c>
+      <c r="AEZ112" t="s">
+        <v>2425</v>
+      </c>
+      <c r="AFA112" s="1">
+        <v>46308.659351851849</v>
+      </c>
+      <c r="AFC112" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE112" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF112" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFG112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B113" t="s">
+        <v>706</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D113" t="s">
+        <v>591</v>
+      </c>
+      <c r="E113" t="s">
+        <v>752</v>
+      </c>
+      <c r="F113" t="s">
+        <v>2427</v>
+      </c>
+      <c r="EN113" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO113">
+        <v>0</v>
+      </c>
+      <c r="EP113">
+        <v>1364</v>
+      </c>
+      <c r="EQ113" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER113" t="s">
+        <v>1157</v>
+      </c>
+      <c r="ES113">
+        <v>0</v>
+      </c>
+      <c r="ET113">
+        <v>1</v>
+      </c>
+      <c r="EU113">
+        <v>0</v>
+      </c>
+      <c r="EV113">
+        <v>1</v>
+      </c>
+      <c r="EW113">
+        <v>0</v>
+      </c>
+      <c r="EX113">
+        <v>0</v>
+      </c>
+      <c r="EZ113" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA113">
+        <v>50</v>
+      </c>
+      <c r="FB113" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC113">
+        <v>1</v>
+      </c>
+      <c r="FD113">
+        <v>1</v>
+      </c>
+      <c r="FE113">
+        <v>1</v>
+      </c>
+      <c r="FF113" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG113" t="s">
+        <v>2428</v>
+      </c>
+      <c r="FH113" t="s">
+        <v>711</v>
+      </c>
+      <c r="FI113">
+        <v>2</v>
+      </c>
+      <c r="FJ113" t="s">
+        <v>706</v>
+      </c>
+      <c r="FK113">
+        <v>0</v>
+      </c>
+      <c r="FL113">
+        <v>1</v>
+      </c>
+      <c r="NP113">
+        <v>500</v>
+      </c>
+      <c r="NQ113">
+        <v>500</v>
+      </c>
+      <c r="NS113">
+        <v>405</v>
+      </c>
+      <c r="NT113">
+        <v>405</v>
+      </c>
+      <c r="NV113">
+        <v>451</v>
+      </c>
+      <c r="NW113">
+        <v>451</v>
+      </c>
+      <c r="SD113" s="1"/>
+      <c r="UH113" t="s">
+        <v>2429</v>
+      </c>
+      <c r="ZL113" s="1"/>
+      <c r="ADO113" s="1"/>
+      <c r="ADW113" s="1"/>
+      <c r="AEA113" s="1"/>
+      <c r="AEY113">
+        <v>892741776</v>
+      </c>
+      <c r="AEZ113" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AFA113" s="1">
+        <v>46308.664895833332</v>
+      </c>
+      <c r="AFC113" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE113" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF113" t="s">
+        <v>2431</v>
+      </c>
+      <c r="AFG113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B114" t="s">
+        <v>817</v>
+      </c>
+      <c r="D114" t="s">
+        <v>595</v>
+      </c>
+      <c r="E114" t="s">
+        <v>738</v>
+      </c>
+      <c r="J114" t="s">
+        <v>1097</v>
+      </c>
+      <c r="SD114" s="1"/>
+      <c r="SV114" t="s">
+        <v>740</v>
+      </c>
+      <c r="SW114">
+        <v>1</v>
+      </c>
+      <c r="SX114">
+        <v>0</v>
+      </c>
+      <c r="SY114" t="s">
+        <v>2432</v>
+      </c>
+      <c r="SZ114">
+        <v>13</v>
+      </c>
+      <c r="TA114">
+        <v>17</v>
+      </c>
+      <c r="TB114" t="s">
+        <v>2433</v>
+      </c>
+      <c r="TC114" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TD114" t="s">
+        <v>744</v>
+      </c>
+      <c r="TE114" t="s">
+        <v>2022</v>
+      </c>
+      <c r="TF114">
+        <v>13</v>
+      </c>
+      <c r="TG114">
+        <v>17</v>
+      </c>
+      <c r="TH114">
+        <v>0</v>
+      </c>
+      <c r="TI114">
+        <v>1</v>
+      </c>
+      <c r="TJ114" t="s">
+        <v>2434</v>
+      </c>
+      <c r="TK114">
+        <v>0</v>
+      </c>
+      <c r="TL114">
+        <v>0</v>
+      </c>
+      <c r="TM114">
+        <v>0</v>
+      </c>
+      <c r="TN114">
+        <v>1</v>
+      </c>
+      <c r="TO114">
+        <v>0</v>
+      </c>
+      <c r="TP114" t="s">
+        <v>2435</v>
+      </c>
+      <c r="UH114" t="s">
+        <v>1149</v>
+      </c>
+      <c r="ZL114" s="1"/>
+      <c r="ADO114" s="1"/>
+      <c r="ADW114" s="1"/>
+      <c r="AEA114" s="1"/>
+      <c r="AEY114">
+        <v>892744326</v>
+      </c>
+      <c r="AEZ114" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AFA114" s="1">
+        <v>46308.667187500003</v>
+      </c>
+      <c r="AFC114" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE114" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF114" t="s">
+        <v>2437</v>
+      </c>
+      <c r="AFG114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B115" t="s">
+        <v>817</v>
+      </c>
+      <c r="D115" t="s">
+        <v>595</v>
+      </c>
+      <c r="E115" t="s">
+        <v>738</v>
+      </c>
+      <c r="J115" t="s">
+        <v>1097</v>
+      </c>
+      <c r="SD115" s="1"/>
+      <c r="SV115" t="s">
+        <v>2007</v>
+      </c>
+      <c r="SW115">
+        <v>0</v>
+      </c>
+      <c r="SX115">
+        <v>1</v>
+      </c>
+      <c r="TQ115" s="1">
+        <v>46304</v>
+      </c>
+      <c r="TR115" t="s">
+        <v>2438</v>
+      </c>
+      <c r="TS115" t="s">
+        <v>2439</v>
+      </c>
+      <c r="TT115">
+        <v>21</v>
+      </c>
+      <c r="TU115">
+        <v>19</v>
+      </c>
+      <c r="TV115">
+        <v>1</v>
+      </c>
+      <c r="TW115">
+        <v>0</v>
+      </c>
+      <c r="TX115" t="s">
+        <v>745</v>
+      </c>
+      <c r="TY115">
+        <v>0</v>
+      </c>
+      <c r="TZ115">
+        <v>0</v>
+      </c>
+      <c r="UA115">
+        <v>1</v>
+      </c>
+      <c r="UB115">
+        <v>1</v>
+      </c>
+      <c r="UC115">
+        <v>0</v>
+      </c>
+      <c r="UD115" t="s">
+        <v>2440</v>
+      </c>
+      <c r="UE115" s="1">
+        <v>46304</v>
+      </c>
+      <c r="UF115" t="s">
+        <v>2441</v>
+      </c>
+      <c r="UG115" t="s">
+        <v>2018</v>
+      </c>
+      <c r="UH115" t="s">
+        <v>2442</v>
+      </c>
+      <c r="ZL115" s="1"/>
+      <c r="ADO115" s="1"/>
+      <c r="ADW115" s="1"/>
+      <c r="AEA115" s="1"/>
+      <c r="AEY115">
+        <v>892749181</v>
+      </c>
+      <c r="AEZ115" t="s">
+        <v>2443</v>
+      </c>
+      <c r="AFA115" s="1">
+        <v>46308.671273148153</v>
+      </c>
+      <c r="AFC115" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE115" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF115" t="s">
+        <v>2444</v>
+      </c>
+      <c r="AFG115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B116" t="s">
+        <v>706</v>
+      </c>
+      <c r="C116" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D116" t="s">
+        <v>591</v>
+      </c>
+      <c r="E116" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F116" t="s">
+        <v>2299</v>
+      </c>
+      <c r="NX116" t="s">
+        <v>2445</v>
+      </c>
+      <c r="NY116" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ116" t="s">
+        <v>2446</v>
+      </c>
+      <c r="OA116" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS116">
+        <v>48</v>
+      </c>
+      <c r="OT116" t="s">
+        <v>2183</v>
+      </c>
+      <c r="OV116">
+        <v>18</v>
+      </c>
+      <c r="OW116" t="s">
+        <v>827</v>
+      </c>
+      <c r="OY116">
+        <v>2</v>
+      </c>
+      <c r="OZ116" t="s">
+        <v>807</v>
+      </c>
+      <c r="PB116">
+        <v>6</v>
+      </c>
+      <c r="PC116" t="s">
+        <v>810</v>
+      </c>
+      <c r="PE116">
+        <v>0</v>
+      </c>
+      <c r="PF116" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH116">
+        <v>2</v>
+      </c>
+      <c r="PI116" t="s">
+        <v>807</v>
+      </c>
+      <c r="PJ116" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL116" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN116" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO116" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ116" t="s">
+        <v>2207</v>
+      </c>
+      <c r="PR116" t="s">
+        <v>2284</v>
+      </c>
+      <c r="PS116">
+        <v>1</v>
+      </c>
+      <c r="PT116">
+        <v>0</v>
+      </c>
+      <c r="PU116">
+        <v>0</v>
+      </c>
+      <c r="PW116" t="s">
+        <v>1922</v>
+      </c>
+      <c r="PX116">
+        <v>1</v>
+      </c>
+      <c r="PY116">
+        <v>0</v>
+      </c>
+      <c r="PZ116">
+        <v>0</v>
+      </c>
+      <c r="QA116">
+        <v>0</v>
+      </c>
+      <c r="QJ116" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK116" t="s">
+        <v>2263</v>
+      </c>
+      <c r="QL116" t="s">
+        <v>2244</v>
+      </c>
+      <c r="QM116" t="s">
+        <v>2447</v>
+      </c>
+      <c r="QN116" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP116" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ116" t="s">
+        <v>2263</v>
+      </c>
+      <c r="QR116" t="s">
+        <v>2244</v>
+      </c>
+      <c r="QS116" t="s">
+        <v>2448</v>
+      </c>
+      <c r="QT116" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV116" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW116" t="s">
+        <v>2263</v>
+      </c>
+      <c r="QX116" t="s">
+        <v>2244</v>
+      </c>
+      <c r="QY116" t="s">
+        <v>2449</v>
+      </c>
+      <c r="QZ116" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA116" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB116" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC116" t="s">
+        <v>2145</v>
+      </c>
+      <c r="RD116">
+        <v>1</v>
+      </c>
+      <c r="RE116">
+        <v>1</v>
+      </c>
+      <c r="RF116">
+        <v>0</v>
+      </c>
+      <c r="RG116">
+        <v>0</v>
+      </c>
+      <c r="RH116">
+        <v>0</v>
+      </c>
+      <c r="RJ116" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK116">
+        <v>0</v>
+      </c>
+      <c r="RL116">
+        <v>0</v>
+      </c>
+      <c r="RM116">
+        <v>1</v>
+      </c>
+      <c r="RN116" t="s">
+        <v>2450</v>
+      </c>
+      <c r="RO116" t="s">
+        <v>1953</v>
+      </c>
+      <c r="RP116" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ116" t="s">
+        <v>2451</v>
+      </c>
+      <c r="RR116" t="s">
+        <v>2452</v>
+      </c>
+      <c r="RS116" t="s">
+        <v>732</v>
+      </c>
+      <c r="RT116" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY116" t="s">
+        <v>2453</v>
+      </c>
+      <c r="RZ116" t="s">
+        <v>2446</v>
+      </c>
+      <c r="SA116" t="s">
+        <v>2454</v>
+      </c>
+      <c r="SB116" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD116" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH116" t="s">
+        <v>2455</v>
+      </c>
+      <c r="ZL116" s="1"/>
+      <c r="ADO116" s="1"/>
+      <c r="ADW116" s="1"/>
+      <c r="AEA116" s="1"/>
+      <c r="AEY116">
+        <v>892756736</v>
+      </c>
+      <c r="AEZ116" t="s">
+        <v>2456</v>
+      </c>
+      <c r="AFA116" s="1">
+        <v>46308.678402777783</v>
+      </c>
+      <c r="AFC116" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE116" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF116" t="s">
+        <v>2457</v>
+      </c>
+      <c r="AFG116">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{361511B8-2F72-9546-B182-6379A393CEBA}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87D03F8A-9DFB-764D-AAEA-B372DB43A4BE}"/>
   <bookViews>
     <workbookView xWindow="4060" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5479" uniqueCount="2458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5924" uniqueCount="2610">
   <si>
     <t>Date</t>
   </si>
@@ -7394,6 +7394,462 @@
   </si>
   <si>
     <t>uuid:4964b72e-d6cb-49d4-81cc-e9468dc04607</t>
+  </si>
+  <si>
+    <t>LOKIDING P/S</t>
+  </si>
+  <si>
+    <t>Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>Nutri Club patron</t>
+  </si>
+  <si>
+    <t>Free discussion</t>
+  </si>
+  <si>
+    <t>Yes clearly understood</t>
+  </si>
+  <si>
+    <t>They said all should attend classes equally</t>
+  </si>
+  <si>
+    <t>They will help girls to finish the work early</t>
+  </si>
+  <si>
+    <t>They said there is no problem in collecting firewood</t>
+  </si>
+  <si>
+    <t>They said it's fine to fetch water</t>
+  </si>
+  <si>
+    <t>They promised to ensure that girls attend classes daily</t>
+  </si>
+  <si>
+    <t>Explained it clearly</t>
+  </si>
+  <si>
+    <t>Sharing work together</t>
+  </si>
+  <si>
+    <t>Not sure of his answer</t>
+  </si>
+  <si>
+    <t>Sure</t>
+  </si>
+  <si>
+    <t>Not clear</t>
+  </si>
+  <si>
+    <t>Un sure</t>
+  </si>
+  <si>
+    <t>Accepted to help girls do home chores</t>
+  </si>
+  <si>
+    <t>Explained well</t>
+  </si>
+  <si>
+    <t>There is need to share work</t>
+  </si>
+  <si>
+    <t>Sharing</t>
+  </si>
+  <si>
+    <t>Nothing wrong in sharing house chores</t>
+  </si>
+  <si>
+    <t>Ingredients not prioritized at household level Limited access to the cooking materials</t>
+  </si>
+  <si>
+    <t>Not all that much</t>
+  </si>
+  <si>
+    <t>All children were happy and promised embrace education</t>
+  </si>
+  <si>
+    <t>They accepted to participate in school gardening</t>
+  </si>
+  <si>
+    <t>As on the pledge card</t>
+  </si>
+  <si>
+    <t>Some schools had no power that means we couldn't use the screen but resorted to laptop</t>
+  </si>
+  <si>
+    <t>64d47415-5496-4fa5-a5e5-c50c23bff57e</t>
+  </si>
+  <si>
+    <t>uuid:64d47415-5496-4fa5-a5e5-c50c23bff57e</t>
+  </si>
+  <si>
+    <t>LORENG P/S</t>
+  </si>
+  <si>
+    <t>Infront of the headteachers office and staff room</t>
+  </si>
+  <si>
+    <t>The patrons coopareted and they finished pinning the toll free number, school meal at the kitchen and the other talking compound charts. All leaners and teachers were all excited and were expecting the nurti bus visit in their school soon.</t>
+  </si>
+  <si>
+    <t>8215e880-7a57-4766-8dd8-8ab8228a8b17</t>
+  </si>
+  <si>
+    <t>uuid:8215e880-7a57-4766-8dd8-8ab8228a8b17</t>
+  </si>
+  <si>
+    <t>Reading books, playing round game, taking instant photos with instant camera</t>
+  </si>
+  <si>
+    <t>Common materials like books, ball and common round game played in school</t>
+  </si>
+  <si>
+    <t>Because she will be late for school, others will concentrate in class more than her, she will feel unloved</t>
+  </si>
+  <si>
+    <t>To finish work faster, to get to class on time together, to promote unity and love</t>
+  </si>
+  <si>
+    <t>To stop over working girls, it builds strong love and unity in the family</t>
+  </si>
+  <si>
+    <t>Show love to our sister, we be in school early together</t>
+  </si>
+  <si>
+    <t>Girls are not supposed to graze animals, they are denaying her rights</t>
+  </si>
+  <si>
+    <t>Eboo is the greens i will add, to simplify work</t>
+  </si>
+  <si>
+    <t>Bus unites us</t>
+  </si>
+  <si>
+    <t>Groundnuts, he said connects peace at home</t>
+  </si>
+  <si>
+    <t>Abus brings as together</t>
+  </si>
+  <si>
+    <t>Scummer week greens,  girls deserve equal rights</t>
+  </si>
+  <si>
+    <t>Abus connects as together</t>
+  </si>
+  <si>
+    <t>Kamalakwan greens, both of the children should work together to avoid laziness among family members</t>
+  </si>
+  <si>
+    <t>Abus that brings as together</t>
+  </si>
+  <si>
+    <t>Akewoo greens, girls and boys should be together</t>
+  </si>
+  <si>
+    <t>A bus that brings as together</t>
+  </si>
+  <si>
+    <t>Eboo greens, its important because shaing work promotes</t>
+  </si>
+  <si>
+    <t>Ingredients not prioritized at household level Limited access to the cooking materials Other</t>
+  </si>
+  <si>
+    <t>The name was complicated to know the meaning in the local names</t>
+  </si>
+  <si>
+    <t>Great attendence and participation</t>
+  </si>
+  <si>
+    <t>Carry out orientation and first visit</t>
+  </si>
+  <si>
+    <t>I the headteacher and patrons to pledged to support this club by giving every step it in</t>
+  </si>
+  <si>
+    <t>Loreng P/s were willing to participate in the activity,</t>
+  </si>
+  <si>
+    <t>9c581d2a-8ca3-4641-b6da-1679b37e0b8d</t>
+  </si>
+  <si>
+    <t>uuid:9c581d2a-8ca3-4641-b6da-1679b37e0b8d</t>
+  </si>
+  <si>
+    <t>kakomomgole P/S</t>
+  </si>
+  <si>
+    <t>At the administration block walls</t>
+  </si>
+  <si>
+    <t>The headteacher and all school was informed about the Nutri bus visit, patrons had already finished pinning the toll free number, school meal and other taliking charst and leaners were taking time to read, they had few trees to hug on the charts</t>
+  </si>
+  <si>
+    <t>936cc23f-e5e7-48f7-a0d3-897a224a77d9</t>
+  </si>
+  <si>
+    <t>vspxa9ShrDMSZMboWVwW7A</t>
+  </si>
+  <si>
+    <t>uuid:936cc23f-e5e7-48f7-a0d3-897a224a77d9</t>
+  </si>
+  <si>
+    <t>Answering questions, playing round game and reading nurtition books</t>
+  </si>
+  <si>
+    <t>Simple and common materials locally avaialble and familiar games and familiar qiestions</t>
+  </si>
+  <si>
+    <t>It is not good, denying her right to be in school to achieve her dream. She will be tired before sitting in class,</t>
+  </si>
+  <si>
+    <t>Promote unity, love  makes work easy</t>
+  </si>
+  <si>
+    <t>To make work easy, to give the other company to harrasment by starnagers</t>
+  </si>
+  <si>
+    <t>To show her love, to ease work, to do work better</t>
+  </si>
+  <si>
+    <t>It will be denying the girl equal right with boys</t>
+  </si>
+  <si>
+    <t>Boo greens</t>
+  </si>
+  <si>
+    <t>Kamalakwan</t>
+  </si>
+  <si>
+    <t>Abus that joints as together</t>
+  </si>
+  <si>
+    <t>Scummer week</t>
+  </si>
+  <si>
+    <t>A Bus that brings as together</t>
+  </si>
+  <si>
+    <t>Spinash</t>
+  </si>
+  <si>
+    <t>A bus that joints as together</t>
+  </si>
+  <si>
+    <t>Boo</t>
+  </si>
+  <si>
+    <t>Abus that brights as together</t>
+  </si>
+  <si>
+    <t>Over welming number which attracted all the classes</t>
+  </si>
+  <si>
+    <t>Good attendence, active participation with kids</t>
+  </si>
+  <si>
+    <t>More time needed to conduct more</t>
+  </si>
+  <si>
+    <t>We pledge to support the Nutri club and make it the best in school</t>
+  </si>
+  <si>
+    <t>Primary seven class is not yet in kakomongole primary school</t>
+  </si>
+  <si>
+    <t>a055722b-307e-4a60-93af-ae3673954321</t>
+  </si>
+  <si>
+    <t>uuid:a055722b-307e-4a60-93af-ae3673954321</t>
+  </si>
+  <si>
+    <t>TOROI P/S</t>
+  </si>
+  <si>
+    <t>Outside the headmasters office</t>
+  </si>
+  <si>
+    <t>The number of pupils that day was less compared to the school enrollment</t>
+  </si>
+  <si>
+    <t>f7861a54-d6e4-444e-be10-842492a2d0d5</t>
+  </si>
+  <si>
+    <t>uuid:f7861a54-d6e4-444e-be10-842492a2d0d5</t>
+  </si>
+  <si>
+    <t>LOTIM P/S</t>
+  </si>
+  <si>
+    <t>Infront of the p.7 class</t>
+  </si>
+  <si>
+    <t>ee7d3ba8-c9c0-4399-ba21-23bb1cf0009d</t>
+  </si>
+  <si>
+    <t>uuid:ee7d3ba8-c9c0-4399-ba21-23bb1cf0009d</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Food sorting &amp; matching game Metu porridge supplementation demonstrated Structured dialogue on rebalancing chores Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>One of the club members was able to explain how rebalancing chores at home was important, they also participated in the outdoor nutri game</t>
+  </si>
+  <si>
+    <t>Promotes equal distribution of work, promotes equal rights in families</t>
+  </si>
+  <si>
+    <t>Promotes good morals, promotes love within family members</t>
+  </si>
+  <si>
+    <t>To Avoid kidnap among girl child, avoid child labor</t>
+  </si>
+  <si>
+    <t>Promotes loves within siblings, brings unity among boys and girls</t>
+  </si>
+  <si>
+    <t>By advising the girl to go to school,  to encourage girl child education in the community</t>
+  </si>
+  <si>
+    <t>Milk, sugar, cooking oil</t>
+  </si>
+  <si>
+    <t>Abus ikimorikinit kaapei means doing work together</t>
+  </si>
+  <si>
+    <t>Waking up early morning to do work, sharing work together among siblings</t>
+  </si>
+  <si>
+    <t>Abus means understanding each other</t>
+  </si>
+  <si>
+    <t>Finishing work in time, by understanding each other at home so that work can easily get done</t>
+  </si>
+  <si>
+    <t>It means communicating together at work, being cooperative</t>
+  </si>
+  <si>
+    <t>Waking up early to do work, doing some other work in the evening</t>
+  </si>
+  <si>
+    <t>The bus is carrying us together,</t>
+  </si>
+  <si>
+    <t>Divide work within siblings, cooperating together</t>
+  </si>
+  <si>
+    <t>Honey, milk, odii</t>
+  </si>
+  <si>
+    <t>Taste preference barriers Ingredients not prioritized at household level Limited access to the cooking materials</t>
+  </si>
+  <si>
+    <t>The games started a little late due to the long journey of traveling from toroi to lotim which almost took us 2hours and 30mins</t>
+  </si>
+  <si>
+    <t>The children learnt different nutritious foods that help the body to grow, another success observation was that most of them committed to practically help their siblings in house and home chores</t>
+  </si>
+  <si>
+    <t>The school should be ready and organized</t>
+  </si>
+  <si>
+    <t>They committed to working together with WFP since WFP has been their main donar in food and also provided a very improved kitchen for them</t>
+  </si>
+  <si>
+    <t>db582131-81e1-496a-a62e-cc787162997b</t>
+  </si>
+  <si>
+    <t>uuid:db582131-81e1-496a-a62e-cc787162997b</t>
+  </si>
+  <si>
+    <t>In front of school headteachers office</t>
+  </si>
+  <si>
+    <t>The club has to start it's activities and reporting immediately for time data entry</t>
+  </si>
+  <si>
+    <t>0994d7fe-4ec8-43ce-89c7-03e10dc8e154</t>
+  </si>
+  <si>
+    <t>uuid:0994d7fe-4ec8-43ce-89c7-03e10dc8e154</t>
+  </si>
+  <si>
+    <t>ACEGERTOLIM P/S</t>
+  </si>
+  <si>
+    <t>In the compound tree</t>
+  </si>
+  <si>
+    <t>Club activities should start immediately and the teacher led session as well.</t>
+  </si>
+  <si>
+    <t>1c2d00c5-b326-43f0-9401-c256138518fc</t>
+  </si>
+  <si>
+    <t>uuid:1c2d00c5-b326-43f0-9401-c256138518fc</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Metu porridge supplementation demonstrated Structured dialogue on rebalancing chores Climate-smart cooking methods explained Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>They participated in the reading games, they also participated in the nutri games</t>
+  </si>
+  <si>
+    <t>To avoid early marriage, equal treatment for both boys and girls</t>
+  </si>
+  <si>
+    <t>To avoid kidnap, to prevent girls from going different direction instead of going to school</t>
+  </si>
+  <si>
+    <t>To avoid work load, making work easy, saves time for other work</t>
+  </si>
+  <si>
+    <t>To avoid child abuse, avoid rape on the way, avoid girl child mistreatment by parents</t>
+  </si>
+  <si>
+    <t>Promotes girl education, to avoid forced marriage, to prevent early marriage and early pregnancy</t>
+  </si>
+  <si>
+    <t>Doing some other work in the morning, divide chores within ourselves</t>
+  </si>
+  <si>
+    <t>A group of people doing work together</t>
+  </si>
+  <si>
+    <t>Doing work in the morning together, sharing work within ourselves</t>
+  </si>
+  <si>
+    <t>Milk, Honey, sugar</t>
+  </si>
+  <si>
+    <t>Waking up early to do housework, finishing work in time</t>
+  </si>
+  <si>
+    <t>Honey, blue band, tamarind</t>
+  </si>
+  <si>
+    <t>Milk, soya</t>
+  </si>
+  <si>
+    <t>Bus ikimorikinit kaapei means the bus puts everyone together</t>
+  </si>
+  <si>
+    <t>Most upper classes didn't attend especially p.7 because they were busy in class</t>
+  </si>
+  <si>
+    <t>They learnt how to over barriers both at home and at school during the round game</t>
+  </si>
+  <si>
+    <t>Organizing the pupils according to their age bracket to participate in the bus activation</t>
+  </si>
+  <si>
+    <t>They committed to planting vegetables both at school and at home and also encouraging their parents to make the nutritious porridge</t>
+  </si>
+  <si>
+    <t>f345c3a1-d0fc-45f2-a99d-b7dfc845275d</t>
+  </si>
+  <si>
+    <t>uuid:f345c3a1-d0fc-45f2-a99d-b7dfc845275d</t>
   </si>
 </sst>
 </file>
@@ -7475,8 +7931,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG116" totalsRowShown="0">
-  <autoFilter ref="A1:AFG116" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG127" totalsRowShown="0">
+  <autoFilter ref="A1:AFG127" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -8609,7 +9065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFG116"/>
+  <dimension ref="A1:AFG127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -38254,6 +38710,2594 @@
         <v>115</v>
       </c>
     </row>
+    <row r="117" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B117" t="s">
+        <v>751</v>
+      </c>
+      <c r="D117" t="s">
+        <v>594</v>
+      </c>
+      <c r="E117" t="s">
+        <v>752</v>
+      </c>
+      <c r="I117" t="s">
+        <v>2458</v>
+      </c>
+      <c r="EN117" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT117">
+        <v>297</v>
+      </c>
+      <c r="FU117">
+        <v>189</v>
+      </c>
+      <c r="FV117">
+        <v>8</v>
+      </c>
+      <c r="FW117">
+        <v>11</v>
+      </c>
+      <c r="FY117">
+        <v>186</v>
+      </c>
+      <c r="FZ117">
+        <v>184</v>
+      </c>
+      <c r="GA117">
+        <v>5</v>
+      </c>
+      <c r="GB117">
+        <v>2</v>
+      </c>
+      <c r="GD117">
+        <v>138</v>
+      </c>
+      <c r="GE117">
+        <v>87</v>
+      </c>
+      <c r="GF117">
+        <v>6</v>
+      </c>
+      <c r="GG117">
+        <v>2</v>
+      </c>
+      <c r="GI117">
+        <v>10</v>
+      </c>
+      <c r="GJ117">
+        <v>5</v>
+      </c>
+      <c r="GK117">
+        <v>5</v>
+      </c>
+      <c r="GL117">
+        <v>1</v>
+      </c>
+      <c r="GN117">
+        <v>18</v>
+      </c>
+      <c r="GO117">
+        <v>18</v>
+      </c>
+      <c r="GP117">
+        <v>5</v>
+      </c>
+      <c r="GQ117">
+        <v>2</v>
+      </c>
+      <c r="GR117" t="s">
+        <v>2459</v>
+      </c>
+      <c r="GS117">
+        <v>0</v>
+      </c>
+      <c r="GT117">
+        <v>0</v>
+      </c>
+      <c r="GU117">
+        <v>0</v>
+      </c>
+      <c r="GV117">
+        <v>0</v>
+      </c>
+      <c r="GW117">
+        <v>0</v>
+      </c>
+      <c r="GX117">
+        <v>0</v>
+      </c>
+      <c r="GY117">
+        <v>1</v>
+      </c>
+      <c r="GZ117" t="s">
+        <v>2460</v>
+      </c>
+      <c r="HA117">
+        <v>1</v>
+      </c>
+      <c r="HB117">
+        <v>0</v>
+      </c>
+      <c r="HC117">
+        <v>0</v>
+      </c>
+      <c r="HD117">
+        <v>0</v>
+      </c>
+      <c r="HE117">
+        <v>0</v>
+      </c>
+      <c r="HG117" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH117" t="s">
+        <v>2461</v>
+      </c>
+      <c r="HI117" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ117" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL117" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM117" t="s">
+        <v>2462</v>
+      </c>
+      <c r="HT117" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU117">
+        <v>159</v>
+      </c>
+      <c r="HV117" t="s">
+        <v>2463</v>
+      </c>
+      <c r="HX117" t="s">
+        <v>765</v>
+      </c>
+      <c r="HY117">
+        <v>158</v>
+      </c>
+      <c r="HZ117" t="s">
+        <v>2464</v>
+      </c>
+      <c r="IB117" t="s">
+        <v>766</v>
+      </c>
+      <c r="IC117">
+        <v>123</v>
+      </c>
+      <c r="ID117" t="s">
+        <v>2465</v>
+      </c>
+      <c r="IF117" t="s">
+        <v>766</v>
+      </c>
+      <c r="IG117">
+        <v>140</v>
+      </c>
+      <c r="IH117" t="s">
+        <v>2466</v>
+      </c>
+      <c r="IJ117" t="s">
+        <v>766</v>
+      </c>
+      <c r="IK117">
+        <v>280</v>
+      </c>
+      <c r="IL117" t="s">
+        <v>2467</v>
+      </c>
+      <c r="IV117" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW117" t="s">
+        <v>1143</v>
+      </c>
+      <c r="IX117" t="s">
+        <v>2468</v>
+      </c>
+      <c r="IY117" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ117" t="s">
+        <v>2469</v>
+      </c>
+      <c r="JA117" t="s">
+        <v>716</v>
+      </c>
+      <c r="JC117" t="s">
+        <v>837</v>
+      </c>
+      <c r="JD117" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JE117" t="s">
+        <v>2470</v>
+      </c>
+      <c r="JF117" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JG117" t="s">
+        <v>2471</v>
+      </c>
+      <c r="JH117" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ117" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK117" t="s">
+        <v>879</v>
+      </c>
+      <c r="JL117" t="s">
+        <v>2472</v>
+      </c>
+      <c r="JM117" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JN117" t="s">
+        <v>2473</v>
+      </c>
+      <c r="JO117" t="s">
+        <v>720</v>
+      </c>
+      <c r="JQ117" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR117" t="s">
+        <v>879</v>
+      </c>
+      <c r="JS117" t="s">
+        <v>2474</v>
+      </c>
+      <c r="JT117" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU117" t="s">
+        <v>2475</v>
+      </c>
+      <c r="JV117" t="s">
+        <v>716</v>
+      </c>
+      <c r="JX117" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY117" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ117" t="s">
+        <v>2476</v>
+      </c>
+      <c r="KA117" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB117" t="s">
+        <v>2477</v>
+      </c>
+      <c r="KC117" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE117" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF117" t="s">
+        <v>769</v>
+      </c>
+      <c r="KG117" t="s">
+        <v>2478</v>
+      </c>
+      <c r="KH117" t="s">
+        <v>1209</v>
+      </c>
+      <c r="KI117" t="s">
+        <v>1501</v>
+      </c>
+      <c r="KJ117" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK117" t="s">
+        <v>2479</v>
+      </c>
+      <c r="KL117">
+        <v>0</v>
+      </c>
+      <c r="KM117">
+        <v>0</v>
+      </c>
+      <c r="KN117">
+        <v>1</v>
+      </c>
+      <c r="KO117">
+        <v>0</v>
+      </c>
+      <c r="KP117">
+        <v>1</v>
+      </c>
+      <c r="KR117" t="s">
+        <v>2480</v>
+      </c>
+      <c r="KS117" t="s">
+        <v>2481</v>
+      </c>
+      <c r="KT117" t="s">
+        <v>2482</v>
+      </c>
+      <c r="KU117" t="s">
+        <v>2483</v>
+      </c>
+      <c r="NP117">
+        <v>352</v>
+      </c>
+      <c r="NQ117">
+        <v>175</v>
+      </c>
+      <c r="NS117">
+        <v>186</v>
+      </c>
+      <c r="NT117">
+        <v>128</v>
+      </c>
+      <c r="NV117">
+        <v>98</v>
+      </c>
+      <c r="NW117">
+        <v>59</v>
+      </c>
+      <c r="SD117" s="1"/>
+      <c r="UH117" t="s">
+        <v>2484</v>
+      </c>
+      <c r="ZL117" s="1"/>
+      <c r="ADO117" s="1"/>
+      <c r="ADW117" s="1"/>
+      <c r="AEA117" s="1"/>
+      <c r="AEY117">
+        <v>892811098</v>
+      </c>
+      <c r="AEZ117" t="s">
+        <v>2485</v>
+      </c>
+      <c r="AFA117" s="1">
+        <v>46308.734548611108</v>
+      </c>
+      <c r="AFC117" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE117" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF117" t="s">
+        <v>2486</v>
+      </c>
+      <c r="AFG117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B118" t="s">
+        <v>858</v>
+      </c>
+      <c r="D118" t="s">
+        <v>597</v>
+      </c>
+      <c r="E118" t="s">
+        <v>752</v>
+      </c>
+      <c r="M118" t="s">
+        <v>2487</v>
+      </c>
+      <c r="EN118" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO118">
+        <v>610</v>
+      </c>
+      <c r="EP118">
+        <v>568</v>
+      </c>
+      <c r="EQ118" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER118" t="s">
+        <v>1400</v>
+      </c>
+      <c r="ES118">
+        <v>1</v>
+      </c>
+      <c r="ET118">
+        <v>0</v>
+      </c>
+      <c r="EU118">
+        <v>0</v>
+      </c>
+      <c r="EV118">
+        <v>0</v>
+      </c>
+      <c r="EW118">
+        <v>1</v>
+      </c>
+      <c r="EX118">
+        <v>0</v>
+      </c>
+      <c r="EZ118" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA118">
+        <v>40</v>
+      </c>
+      <c r="FB118" t="s">
+        <v>2275</v>
+      </c>
+      <c r="FC118">
+        <v>1</v>
+      </c>
+      <c r="FD118">
+        <v>1</v>
+      </c>
+      <c r="FE118">
+        <v>0</v>
+      </c>
+      <c r="FF118" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG118" t="s">
+        <v>2488</v>
+      </c>
+      <c r="FH118" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP118">
+        <v>558</v>
+      </c>
+      <c r="NQ118">
+        <v>422</v>
+      </c>
+      <c r="NS118">
+        <v>192</v>
+      </c>
+      <c r="NT118">
+        <v>144</v>
+      </c>
+      <c r="NV118">
+        <v>161</v>
+      </c>
+      <c r="NW118">
+        <v>101</v>
+      </c>
+      <c r="SD118" s="1"/>
+      <c r="UH118" t="s">
+        <v>2489</v>
+      </c>
+      <c r="ZL118" s="1"/>
+      <c r="ADO118" s="1"/>
+      <c r="ADW118" s="1"/>
+      <c r="AEA118" s="1"/>
+      <c r="AEY118">
+        <v>892848510</v>
+      </c>
+      <c r="AEZ118" t="s">
+        <v>2490</v>
+      </c>
+      <c r="AFA118" s="1">
+        <v>46308.780358796299</v>
+      </c>
+      <c r="AFC118" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE118" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF118" t="s">
+        <v>2491</v>
+      </c>
+      <c r="AFG118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B119" t="s">
+        <v>858</v>
+      </c>
+      <c r="D119" t="s">
+        <v>597</v>
+      </c>
+      <c r="E119" t="s">
+        <v>752</v>
+      </c>
+      <c r="M119" t="s">
+        <v>2487</v>
+      </c>
+      <c r="EN119" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT119">
+        <v>608</v>
+      </c>
+      <c r="FU119">
+        <v>567</v>
+      </c>
+      <c r="FV119">
+        <v>2</v>
+      </c>
+      <c r="FW119">
+        <v>1</v>
+      </c>
+      <c r="FY119">
+        <v>196</v>
+      </c>
+      <c r="FZ119">
+        <v>144</v>
+      </c>
+      <c r="GA119">
+        <v>0</v>
+      </c>
+      <c r="GB119">
+        <v>0</v>
+      </c>
+      <c r="GD119">
+        <v>171</v>
+      </c>
+      <c r="GE119">
+        <v>112</v>
+      </c>
+      <c r="GF119">
+        <v>0</v>
+      </c>
+      <c r="GG119">
+        <v>0</v>
+      </c>
+      <c r="GI119">
+        <v>6</v>
+      </c>
+      <c r="GJ119">
+        <v>4</v>
+      </c>
+      <c r="GK119">
+        <v>0</v>
+      </c>
+      <c r="GL119">
+        <v>0</v>
+      </c>
+      <c r="GN119">
+        <v>2</v>
+      </c>
+      <c r="GO119">
+        <v>1</v>
+      </c>
+      <c r="GP119">
+        <v>0</v>
+      </c>
+      <c r="GQ119">
+        <v>0</v>
+      </c>
+      <c r="GR119" t="s">
+        <v>1196</v>
+      </c>
+      <c r="GS119">
+        <v>1</v>
+      </c>
+      <c r="GT119">
+        <v>0</v>
+      </c>
+      <c r="GU119">
+        <v>0</v>
+      </c>
+      <c r="GV119">
+        <v>1</v>
+      </c>
+      <c r="GW119">
+        <v>1</v>
+      </c>
+      <c r="GX119">
+        <v>0</v>
+      </c>
+      <c r="GY119">
+        <v>1</v>
+      </c>
+      <c r="GZ119" t="s">
+        <v>1294</v>
+      </c>
+      <c r="HA119">
+        <v>1</v>
+      </c>
+      <c r="HB119">
+        <v>0</v>
+      </c>
+      <c r="HC119">
+        <v>1</v>
+      </c>
+      <c r="HD119">
+        <v>1</v>
+      </c>
+      <c r="HE119">
+        <v>0</v>
+      </c>
+      <c r="HG119" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH119" t="s">
+        <v>2492</v>
+      </c>
+      <c r="HI119" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ119" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL119" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM119" t="s">
+        <v>2493</v>
+      </c>
+      <c r="HT119" t="s">
+        <v>765</v>
+      </c>
+      <c r="HU119">
+        <v>450</v>
+      </c>
+      <c r="HV119" t="s">
+        <v>2494</v>
+      </c>
+      <c r="HX119" t="s">
+        <v>766</v>
+      </c>
+      <c r="HY119">
+        <v>402</v>
+      </c>
+      <c r="HZ119" t="s">
+        <v>2495</v>
+      </c>
+      <c r="IB119" t="s">
+        <v>765</v>
+      </c>
+      <c r="IC119">
+        <v>447</v>
+      </c>
+      <c r="ID119" t="s">
+        <v>2496</v>
+      </c>
+      <c r="IF119" t="s">
+        <v>765</v>
+      </c>
+      <c r="IG119">
+        <v>450</v>
+      </c>
+      <c r="IH119" t="s">
+        <v>2497</v>
+      </c>
+      <c r="IJ119" t="s">
+        <v>766</v>
+      </c>
+      <c r="IK119">
+        <v>339</v>
+      </c>
+      <c r="IL119" t="s">
+        <v>2498</v>
+      </c>
+      <c r="IV119" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW119" t="s">
+        <v>879</v>
+      </c>
+      <c r="IX119" t="s">
+        <v>2499</v>
+      </c>
+      <c r="IY119" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ119" t="s">
+        <v>2500</v>
+      </c>
+      <c r="JA119" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC119" t="s">
+        <v>837</v>
+      </c>
+      <c r="JD119" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE119" t="s">
+        <v>2501</v>
+      </c>
+      <c r="JF119" t="s">
+        <v>839</v>
+      </c>
+      <c r="JG119" t="s">
+        <v>2502</v>
+      </c>
+      <c r="JH119" t="s">
+        <v>716</v>
+      </c>
+      <c r="JJ119" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK119" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL119" t="s">
+        <v>2503</v>
+      </c>
+      <c r="JM119" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN119" t="s">
+        <v>2504</v>
+      </c>
+      <c r="JO119" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ119" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR119" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS119" t="s">
+        <v>2505</v>
+      </c>
+      <c r="JT119" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JU119" t="s">
+        <v>2506</v>
+      </c>
+      <c r="JV119" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX119" t="s">
+        <v>837</v>
+      </c>
+      <c r="JY119" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ119" t="s">
+        <v>2507</v>
+      </c>
+      <c r="KA119" t="s">
+        <v>839</v>
+      </c>
+      <c r="KB119" t="s">
+        <v>2508</v>
+      </c>
+      <c r="KC119" t="s">
+        <v>720</v>
+      </c>
+      <c r="KE119" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF119" t="s">
+        <v>769</v>
+      </c>
+      <c r="KG119" t="s">
+        <v>2509</v>
+      </c>
+      <c r="KH119" t="s">
+        <v>839</v>
+      </c>
+      <c r="KI119" t="s">
+        <v>2508</v>
+      </c>
+      <c r="KJ119" t="s">
+        <v>720</v>
+      </c>
+      <c r="KK119" t="s">
+        <v>2510</v>
+      </c>
+      <c r="KL119">
+        <v>0</v>
+      </c>
+      <c r="KM119">
+        <v>0</v>
+      </c>
+      <c r="KN119">
+        <v>1</v>
+      </c>
+      <c r="KO119">
+        <v>1</v>
+      </c>
+      <c r="KP119">
+        <v>1</v>
+      </c>
+      <c r="KR119" t="s">
+        <v>2511</v>
+      </c>
+      <c r="KS119" t="s">
+        <v>2512</v>
+      </c>
+      <c r="KT119" t="s">
+        <v>2513</v>
+      </c>
+      <c r="KU119" t="s">
+        <v>2514</v>
+      </c>
+      <c r="NP119">
+        <v>558</v>
+      </c>
+      <c r="NQ119">
+        <v>422</v>
+      </c>
+      <c r="NS119">
+        <v>192</v>
+      </c>
+      <c r="NT119">
+        <v>144</v>
+      </c>
+      <c r="NV119">
+        <v>161</v>
+      </c>
+      <c r="NW119">
+        <v>101</v>
+      </c>
+      <c r="SD119" s="1"/>
+      <c r="UH119" t="s">
+        <v>2515</v>
+      </c>
+      <c r="ZL119" s="1"/>
+      <c r="ADO119" s="1"/>
+      <c r="ADW119" s="1"/>
+      <c r="AEA119" s="1"/>
+      <c r="AEY119">
+        <v>892870662</v>
+      </c>
+      <c r="AEZ119" t="s">
+        <v>2516</v>
+      </c>
+      <c r="AFA119" s="1">
+        <v>46308.812627314823</v>
+      </c>
+      <c r="AFC119" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE119" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF119" t="s">
+        <v>2517</v>
+      </c>
+      <c r="AFG119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B120" t="s">
+        <v>858</v>
+      </c>
+      <c r="D120" t="s">
+        <v>597</v>
+      </c>
+      <c r="E120" t="s">
+        <v>752</v>
+      </c>
+      <c r="M120" t="s">
+        <v>2518</v>
+      </c>
+      <c r="EN120" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO120">
+        <v>475</v>
+      </c>
+      <c r="EP120">
+        <v>439</v>
+      </c>
+      <c r="EQ120" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER120" t="s">
+        <v>1702</v>
+      </c>
+      <c r="ES120">
+        <v>1</v>
+      </c>
+      <c r="ET120">
+        <v>0</v>
+      </c>
+      <c r="EU120">
+        <v>0</v>
+      </c>
+      <c r="EV120">
+        <v>1</v>
+      </c>
+      <c r="EW120">
+        <v>0</v>
+      </c>
+      <c r="EX120">
+        <v>0</v>
+      </c>
+      <c r="EZ120" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA120">
+        <v>40</v>
+      </c>
+      <c r="FB120" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC120">
+        <v>1</v>
+      </c>
+      <c r="FD120">
+        <v>1</v>
+      </c>
+      <c r="FE120">
+        <v>1</v>
+      </c>
+      <c r="FF120" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG120" t="s">
+        <v>2519</v>
+      </c>
+      <c r="FH120" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP120">
+        <v>339</v>
+      </c>
+      <c r="NQ120">
+        <v>360</v>
+      </c>
+      <c r="NS120">
+        <v>89</v>
+      </c>
+      <c r="NT120">
+        <v>29</v>
+      </c>
+      <c r="NV120">
+        <v>29</v>
+      </c>
+      <c r="NW120">
+        <v>0</v>
+      </c>
+      <c r="SD120" s="1"/>
+      <c r="UH120" t="s">
+        <v>2520</v>
+      </c>
+      <c r="ZL120" s="1"/>
+      <c r="ADO120" s="1"/>
+      <c r="ADW120" s="1"/>
+      <c r="AEA120" s="1"/>
+      <c r="AEY120">
+        <v>892889334</v>
+      </c>
+      <c r="AEZ120" t="s">
+        <v>2521</v>
+      </c>
+      <c r="AFA120" s="1">
+        <v>46308.845127314817</v>
+      </c>
+      <c r="AFC120" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE120" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF120" t="s">
+        <v>2523</v>
+      </c>
+      <c r="AFG120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B121" t="s">
+        <v>858</v>
+      </c>
+      <c r="D121" t="s">
+        <v>597</v>
+      </c>
+      <c r="E121" t="s">
+        <v>752</v>
+      </c>
+      <c r="M121" t="s">
+        <v>2518</v>
+      </c>
+      <c r="EN121" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT121">
+        <v>449</v>
+      </c>
+      <c r="FU121">
+        <v>350</v>
+      </c>
+      <c r="FV121">
+        <v>1</v>
+      </c>
+      <c r="FW121">
+        <v>0</v>
+      </c>
+      <c r="FY121">
+        <v>85</v>
+      </c>
+      <c r="FZ121">
+        <v>20</v>
+      </c>
+      <c r="GA121">
+        <v>0</v>
+      </c>
+      <c r="GB121">
+        <v>0</v>
+      </c>
+      <c r="GD121">
+        <v>29</v>
+      </c>
+      <c r="GE121">
+        <v>0</v>
+      </c>
+      <c r="GF121">
+        <v>0</v>
+      </c>
+      <c r="GG121">
+        <v>0</v>
+      </c>
+      <c r="GI121">
+        <v>3</v>
+      </c>
+      <c r="GJ121">
+        <v>3</v>
+      </c>
+      <c r="GK121">
+        <v>0</v>
+      </c>
+      <c r="GL121">
+        <v>0</v>
+      </c>
+      <c r="GN121">
+        <v>3</v>
+      </c>
+      <c r="GO121">
+        <v>2</v>
+      </c>
+      <c r="GP121">
+        <v>0</v>
+      </c>
+      <c r="GQ121">
+        <v>0</v>
+      </c>
+      <c r="GR121" t="s">
+        <v>1196</v>
+      </c>
+      <c r="GS121">
+        <v>1</v>
+      </c>
+      <c r="GT121">
+        <v>0</v>
+      </c>
+      <c r="GU121">
+        <v>0</v>
+      </c>
+      <c r="GV121">
+        <v>1</v>
+      </c>
+      <c r="GW121">
+        <v>1</v>
+      </c>
+      <c r="GX121">
+        <v>0</v>
+      </c>
+      <c r="GY121">
+        <v>1</v>
+      </c>
+      <c r="GZ121" t="s">
+        <v>1294</v>
+      </c>
+      <c r="HA121">
+        <v>1</v>
+      </c>
+      <c r="HB121">
+        <v>0</v>
+      </c>
+      <c r="HC121">
+        <v>1</v>
+      </c>
+      <c r="HD121">
+        <v>1</v>
+      </c>
+      <c r="HE121">
+        <v>0</v>
+      </c>
+      <c r="HG121" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH121" t="s">
+        <v>2524</v>
+      </c>
+      <c r="HI121" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ121" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL121" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM121" t="s">
+        <v>2525</v>
+      </c>
+      <c r="HT121" t="s">
+        <v>765</v>
+      </c>
+      <c r="HU121">
+        <v>440</v>
+      </c>
+      <c r="HV121" t="s">
+        <v>2526</v>
+      </c>
+      <c r="HX121" t="s">
+        <v>765</v>
+      </c>
+      <c r="HY121">
+        <v>445</v>
+      </c>
+      <c r="HZ121" t="s">
+        <v>2527</v>
+      </c>
+      <c r="IB121" t="s">
+        <v>766</v>
+      </c>
+      <c r="IC121">
+        <v>400</v>
+      </c>
+      <c r="ID121" t="s">
+        <v>2528</v>
+      </c>
+      <c r="IF121" t="s">
+        <v>765</v>
+      </c>
+      <c r="IG121">
+        <v>358</v>
+      </c>
+      <c r="IH121" t="s">
+        <v>2529</v>
+      </c>
+      <c r="IJ121" t="s">
+        <v>766</v>
+      </c>
+      <c r="IK121">
+        <v>420</v>
+      </c>
+      <c r="IL121" t="s">
+        <v>2530</v>
+      </c>
+      <c r="IV121" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW121" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX121" t="s">
+        <v>2531</v>
+      </c>
+      <c r="IY121" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ121" t="s">
+        <v>2506</v>
+      </c>
+      <c r="JA121" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC121" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD121" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE121" t="s">
+        <v>2532</v>
+      </c>
+      <c r="JF121" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JG121" t="s">
+        <v>2533</v>
+      </c>
+      <c r="JH121" t="s">
+        <v>716</v>
+      </c>
+      <c r="JJ121" t="s">
+        <v>835</v>
+      </c>
+      <c r="JK121" t="s">
+        <v>769</v>
+      </c>
+      <c r="JL121" t="s">
+        <v>2534</v>
+      </c>
+      <c r="JM121" t="s">
+        <v>839</v>
+      </c>
+      <c r="JN121" t="s">
+        <v>2535</v>
+      </c>
+      <c r="JO121" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ121" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR121" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS121" t="s">
+        <v>2536</v>
+      </c>
+      <c r="JT121" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU121" t="s">
+        <v>2537</v>
+      </c>
+      <c r="JV121" t="s">
+        <v>716</v>
+      </c>
+      <c r="JX121" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY121" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ121" t="s">
+        <v>2538</v>
+      </c>
+      <c r="KA121" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB121" t="s">
+        <v>2508</v>
+      </c>
+      <c r="KC121" t="s">
+        <v>720</v>
+      </c>
+      <c r="KE121" t="s">
+        <v>837</v>
+      </c>
+      <c r="KF121" t="s">
+        <v>769</v>
+      </c>
+      <c r="KG121" t="s">
+        <v>2532</v>
+      </c>
+      <c r="KH121" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI121" t="s">
+        <v>2539</v>
+      </c>
+      <c r="KJ121" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK121" t="s">
+        <v>1901</v>
+      </c>
+      <c r="KL121">
+        <v>0</v>
+      </c>
+      <c r="KM121">
+        <v>1</v>
+      </c>
+      <c r="KN121">
+        <v>0</v>
+      </c>
+      <c r="KO121">
+        <v>0</v>
+      </c>
+      <c r="KP121">
+        <v>0</v>
+      </c>
+      <c r="KR121" t="s">
+        <v>2540</v>
+      </c>
+      <c r="KS121" t="s">
+        <v>2541</v>
+      </c>
+      <c r="KT121" t="s">
+        <v>2542</v>
+      </c>
+      <c r="KU121" t="s">
+        <v>2543</v>
+      </c>
+      <c r="NP121">
+        <v>300</v>
+      </c>
+      <c r="NQ121">
+        <v>310</v>
+      </c>
+      <c r="NS121">
+        <v>80</v>
+      </c>
+      <c r="NT121">
+        <v>20</v>
+      </c>
+      <c r="NV121">
+        <v>29</v>
+      </c>
+      <c r="NW121">
+        <v>0</v>
+      </c>
+      <c r="SD121" s="1"/>
+      <c r="UH121" t="s">
+        <v>2544</v>
+      </c>
+      <c r="ZL121" s="1"/>
+      <c r="ADO121" s="1"/>
+      <c r="ADW121" s="1"/>
+      <c r="AEA121" s="1"/>
+      <c r="AEY121">
+        <v>892901594</v>
+      </c>
+      <c r="AEZ121" t="s">
+        <v>2545</v>
+      </c>
+      <c r="AFA121" s="1">
+        <v>46308.868657407409</v>
+      </c>
+      <c r="AFC121" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE121" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF121" t="s">
+        <v>2546</v>
+      </c>
+      <c r="AFG121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B122" t="s">
+        <v>737</v>
+      </c>
+      <c r="D122" t="s">
+        <v>592</v>
+      </c>
+      <c r="E122" t="s">
+        <v>752</v>
+      </c>
+      <c r="G122" t="s">
+        <v>2547</v>
+      </c>
+      <c r="EN122" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO122">
+        <v>790</v>
+      </c>
+      <c r="EP122">
+        <v>698</v>
+      </c>
+      <c r="EQ122" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER122" t="s">
+        <v>1702</v>
+      </c>
+      <c r="ES122">
+        <v>1</v>
+      </c>
+      <c r="ET122">
+        <v>0</v>
+      </c>
+      <c r="EU122">
+        <v>0</v>
+      </c>
+      <c r="EV122">
+        <v>1</v>
+      </c>
+      <c r="EW122">
+        <v>0</v>
+      </c>
+      <c r="EX122">
+        <v>0</v>
+      </c>
+      <c r="EZ122" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA122">
+        <v>30</v>
+      </c>
+      <c r="FB122" t="s">
+        <v>1069</v>
+      </c>
+      <c r="FC122">
+        <v>0</v>
+      </c>
+      <c r="FD122">
+        <v>1</v>
+      </c>
+      <c r="FE122">
+        <v>1</v>
+      </c>
+      <c r="FF122" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG122" t="s">
+        <v>2548</v>
+      </c>
+      <c r="FH122" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP122">
+        <v>530</v>
+      </c>
+      <c r="NQ122">
+        <v>398</v>
+      </c>
+      <c r="NS122">
+        <v>125</v>
+      </c>
+      <c r="NT122">
+        <v>94</v>
+      </c>
+      <c r="NV122">
+        <v>56</v>
+      </c>
+      <c r="NW122">
+        <v>36</v>
+      </c>
+      <c r="SD122" s="1"/>
+      <c r="UH122" t="s">
+        <v>2549</v>
+      </c>
+      <c r="ZL122" s="1"/>
+      <c r="ADO122" s="1"/>
+      <c r="ADW122" s="1"/>
+      <c r="AEA122" s="1"/>
+      <c r="AEY122">
+        <v>892988302</v>
+      </c>
+      <c r="AEZ122" t="s">
+        <v>2550</v>
+      </c>
+      <c r="AFA122" s="1">
+        <v>46309.109305555547</v>
+      </c>
+      <c r="AFC122" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE122" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF122" t="s">
+        <v>2551</v>
+      </c>
+      <c r="AFG122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B123" t="s">
+        <v>737</v>
+      </c>
+      <c r="D123" t="s">
+        <v>592</v>
+      </c>
+      <c r="E123" t="s">
+        <v>752</v>
+      </c>
+      <c r="G123" t="s">
+        <v>2552</v>
+      </c>
+      <c r="EN123" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO123">
+        <v>928</v>
+      </c>
+      <c r="EP123">
+        <v>630</v>
+      </c>
+      <c r="EQ123" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER123" t="s">
+        <v>1400</v>
+      </c>
+      <c r="ES123">
+        <v>1</v>
+      </c>
+      <c r="ET123">
+        <v>0</v>
+      </c>
+      <c r="EU123">
+        <v>0</v>
+      </c>
+      <c r="EV123">
+        <v>0</v>
+      </c>
+      <c r="EW123">
+        <v>1</v>
+      </c>
+      <c r="EX123">
+        <v>0</v>
+      </c>
+      <c r="EZ123" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA123">
+        <v>30</v>
+      </c>
+      <c r="FB123" t="s">
+        <v>1069</v>
+      </c>
+      <c r="FC123">
+        <v>0</v>
+      </c>
+      <c r="FD123">
+        <v>1</v>
+      </c>
+      <c r="FE123">
+        <v>1</v>
+      </c>
+      <c r="FF123" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG123" t="s">
+        <v>2553</v>
+      </c>
+      <c r="FH123" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP123">
+        <v>145</v>
+      </c>
+      <c r="NQ123">
+        <v>100</v>
+      </c>
+      <c r="NS123">
+        <v>598</v>
+      </c>
+      <c r="NT123">
+        <v>396</v>
+      </c>
+      <c r="NV123">
+        <v>84</v>
+      </c>
+      <c r="NW123">
+        <v>34</v>
+      </c>
+      <c r="SD123" s="1"/>
+      <c r="UH123" t="s">
+        <v>842</v>
+      </c>
+      <c r="ZL123" s="1"/>
+      <c r="ADO123" s="1"/>
+      <c r="ADW123" s="1"/>
+      <c r="AEA123" s="1"/>
+      <c r="AEY123">
+        <v>892989127</v>
+      </c>
+      <c r="AEZ123" t="s">
+        <v>2554</v>
+      </c>
+      <c r="AFA123" s="1">
+        <v>46309.111759259264</v>
+      </c>
+      <c r="AFC123" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE123" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF123" t="s">
+        <v>2555</v>
+      </c>
+      <c r="AFG123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B124" t="s">
+        <v>737</v>
+      </c>
+      <c r="D124" t="s">
+        <v>592</v>
+      </c>
+      <c r="E124" t="s">
+        <v>752</v>
+      </c>
+      <c r="G124" t="s">
+        <v>2552</v>
+      </c>
+      <c r="EN124" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT124">
+        <v>95</v>
+      </c>
+      <c r="FU124">
+        <v>58</v>
+      </c>
+      <c r="FV124">
+        <v>2</v>
+      </c>
+      <c r="FW124">
+        <v>0</v>
+      </c>
+      <c r="FY124">
+        <v>378</v>
+      </c>
+      <c r="FZ124">
+        <v>196</v>
+      </c>
+      <c r="GA124">
+        <v>0</v>
+      </c>
+      <c r="GB124">
+        <v>4</v>
+      </c>
+      <c r="GD124">
+        <v>56</v>
+      </c>
+      <c r="GE124">
+        <v>34</v>
+      </c>
+      <c r="GF124">
+        <v>2</v>
+      </c>
+      <c r="GG124">
+        <v>0</v>
+      </c>
+      <c r="GI124">
+        <v>4</v>
+      </c>
+      <c r="GJ124">
+        <v>3</v>
+      </c>
+      <c r="GK124">
+        <v>0</v>
+      </c>
+      <c r="GL124">
+        <v>0</v>
+      </c>
+      <c r="GN124">
+        <v>2</v>
+      </c>
+      <c r="GO124">
+        <v>0</v>
+      </c>
+      <c r="GP124">
+        <v>0</v>
+      </c>
+      <c r="GQ124">
+        <v>0</v>
+      </c>
+      <c r="GR124" t="s">
+        <v>2556</v>
+      </c>
+      <c r="GS124">
+        <v>1</v>
+      </c>
+      <c r="GT124">
+        <v>1</v>
+      </c>
+      <c r="GU124">
+        <v>1</v>
+      </c>
+      <c r="GV124">
+        <v>1</v>
+      </c>
+      <c r="GW124">
+        <v>0</v>
+      </c>
+      <c r="GX124">
+        <v>0</v>
+      </c>
+      <c r="GY124">
+        <v>1</v>
+      </c>
+      <c r="GZ124" t="s">
+        <v>1323</v>
+      </c>
+      <c r="HA124">
+        <v>1</v>
+      </c>
+      <c r="HB124">
+        <v>1</v>
+      </c>
+      <c r="HC124">
+        <v>0</v>
+      </c>
+      <c r="HD124">
+        <v>1</v>
+      </c>
+      <c r="HE124">
+        <v>0</v>
+      </c>
+      <c r="HG124" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH124" t="s">
+        <v>2557</v>
+      </c>
+      <c r="HI124" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ124" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL124" t="s">
+        <v>732</v>
+      </c>
+      <c r="HT124" t="s">
+        <v>1375</v>
+      </c>
+      <c r="HU124">
+        <v>16</v>
+      </c>
+      <c r="HV124" t="s">
+        <v>2558</v>
+      </c>
+      <c r="HX124" t="s">
+        <v>1375</v>
+      </c>
+      <c r="HY124">
+        <v>16</v>
+      </c>
+      <c r="HZ124" t="s">
+        <v>2559</v>
+      </c>
+      <c r="IB124" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IC124">
+        <v>16</v>
+      </c>
+      <c r="ID124" t="s">
+        <v>2560</v>
+      </c>
+      <c r="IF124" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IG124">
+        <v>16</v>
+      </c>
+      <c r="IH124" t="s">
+        <v>2561</v>
+      </c>
+      <c r="IJ124" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IK124">
+        <v>16</v>
+      </c>
+      <c r="IL124" t="s">
+        <v>2562</v>
+      </c>
+      <c r="IV124" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW124" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX124" t="s">
+        <v>2563</v>
+      </c>
+      <c r="IY124" t="s">
+        <v>839</v>
+      </c>
+      <c r="IZ124" t="s">
+        <v>2564</v>
+      </c>
+      <c r="JA124" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC124" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD124" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE124" t="s">
+        <v>2565</v>
+      </c>
+      <c r="JF124" t="s">
+        <v>839</v>
+      </c>
+      <c r="JG124" t="s">
+        <v>2566</v>
+      </c>
+      <c r="JH124" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ124" t="s">
+        <v>837</v>
+      </c>
+      <c r="JK124" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JL124" t="s">
+        <v>842</v>
+      </c>
+      <c r="JM124" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JN124" t="s">
+        <v>842</v>
+      </c>
+      <c r="JO124" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ124" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR124" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS124" t="s">
+        <v>2567</v>
+      </c>
+      <c r="JT124" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU124" t="s">
+        <v>2568</v>
+      </c>
+      <c r="JV124" t="s">
+        <v>716</v>
+      </c>
+      <c r="JX124" t="s">
+        <v>835</v>
+      </c>
+      <c r="JY124" t="s">
+        <v>879</v>
+      </c>
+      <c r="JZ124" t="s">
+        <v>2569</v>
+      </c>
+      <c r="KA124" t="s">
+        <v>839</v>
+      </c>
+      <c r="KB124" t="s">
+        <v>2570</v>
+      </c>
+      <c r="KC124" t="s">
+        <v>720</v>
+      </c>
+      <c r="KE124" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF124" t="s">
+        <v>769</v>
+      </c>
+      <c r="KG124" t="s">
+        <v>2571</v>
+      </c>
+      <c r="KH124" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI124" t="s">
+        <v>2572</v>
+      </c>
+      <c r="KJ124" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK124" t="s">
+        <v>2573</v>
+      </c>
+      <c r="KL124">
+        <v>0</v>
+      </c>
+      <c r="KM124">
+        <v>1</v>
+      </c>
+      <c r="KN124">
+        <v>1</v>
+      </c>
+      <c r="KO124">
+        <v>0</v>
+      </c>
+      <c r="KP124">
+        <v>1</v>
+      </c>
+      <c r="KR124" t="s">
+        <v>2574</v>
+      </c>
+      <c r="KS124" t="s">
+        <v>2575</v>
+      </c>
+      <c r="KT124" t="s">
+        <v>2576</v>
+      </c>
+      <c r="KU124" t="s">
+        <v>2577</v>
+      </c>
+      <c r="NP124">
+        <v>145</v>
+      </c>
+      <c r="NQ124">
+        <v>100</v>
+      </c>
+      <c r="NS124">
+        <v>598</v>
+      </c>
+      <c r="NT124">
+        <v>396</v>
+      </c>
+      <c r="NV124">
+        <v>84</v>
+      </c>
+      <c r="NW124">
+        <v>34</v>
+      </c>
+      <c r="SD124" s="1"/>
+      <c r="UH124" t="s">
+        <v>842</v>
+      </c>
+      <c r="ZL124" s="1"/>
+      <c r="ADO124" s="1"/>
+      <c r="ADW124" s="1"/>
+      <c r="AEA124" s="1"/>
+      <c r="AEY124">
+        <v>892996493</v>
+      </c>
+      <c r="AEZ124" t="s">
+        <v>2578</v>
+      </c>
+      <c r="AFA124" s="1">
+        <v>46309.134004629632</v>
+      </c>
+      <c r="AFC124" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE124" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF124" t="s">
+        <v>2579</v>
+      </c>
+      <c r="AFG124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D125" t="s">
+        <v>590</v>
+      </c>
+      <c r="E125" t="s">
+        <v>752</v>
+      </c>
+      <c r="L125" t="s">
+        <v>791</v>
+      </c>
+      <c r="EN125" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO125">
+        <v>587</v>
+      </c>
+      <c r="EP125">
+        <v>530</v>
+      </c>
+      <c r="EQ125" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER125" t="s">
+        <v>1393</v>
+      </c>
+      <c r="ES125">
+        <v>0</v>
+      </c>
+      <c r="ET125">
+        <v>1</v>
+      </c>
+      <c r="EU125">
+        <v>0</v>
+      </c>
+      <c r="EV125">
+        <v>0</v>
+      </c>
+      <c r="EW125">
+        <v>1</v>
+      </c>
+      <c r="EX125">
+        <v>0</v>
+      </c>
+      <c r="EZ125" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA125">
+        <v>60</v>
+      </c>
+      <c r="FB125" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC125">
+        <v>1</v>
+      </c>
+      <c r="FD125">
+        <v>1</v>
+      </c>
+      <c r="FE125">
+        <v>1</v>
+      </c>
+      <c r="FF125" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG125" t="s">
+        <v>2580</v>
+      </c>
+      <c r="FH125" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP125">
+        <v>275</v>
+      </c>
+      <c r="NQ125">
+        <v>255</v>
+      </c>
+      <c r="NS125">
+        <v>160</v>
+      </c>
+      <c r="NT125">
+        <v>140</v>
+      </c>
+      <c r="NV125">
+        <v>152</v>
+      </c>
+      <c r="NW125">
+        <v>135</v>
+      </c>
+      <c r="SD125" s="1"/>
+      <c r="UH125" t="s">
+        <v>2581</v>
+      </c>
+      <c r="ZL125" s="1"/>
+      <c r="ADO125" s="1"/>
+      <c r="ADW125" s="1"/>
+      <c r="AEA125" s="1"/>
+      <c r="AEY125">
+        <v>893046540</v>
+      </c>
+      <c r="AEZ125" t="s">
+        <v>2582</v>
+      </c>
+      <c r="AFA125" s="1">
+        <v>46309.225474537037</v>
+      </c>
+      <c r="AFC125" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE125" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF125" t="s">
+        <v>2583</v>
+      </c>
+      <c r="AFG125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D126" t="s">
+        <v>590</v>
+      </c>
+      <c r="E126" t="s">
+        <v>752</v>
+      </c>
+      <c r="L126" t="s">
+        <v>2584</v>
+      </c>
+      <c r="EN126" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO126">
+        <v>332</v>
+      </c>
+      <c r="EP126">
+        <v>342</v>
+      </c>
+      <c r="EQ126" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER126" t="s">
+        <v>1157</v>
+      </c>
+      <c r="ES126">
+        <v>0</v>
+      </c>
+      <c r="ET126">
+        <v>1</v>
+      </c>
+      <c r="EU126">
+        <v>0</v>
+      </c>
+      <c r="EV126">
+        <v>1</v>
+      </c>
+      <c r="EW126">
+        <v>0</v>
+      </c>
+      <c r="EX126">
+        <v>0</v>
+      </c>
+      <c r="EZ126" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA126">
+        <v>60</v>
+      </c>
+      <c r="FB126" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC126">
+        <v>1</v>
+      </c>
+      <c r="FD126">
+        <v>1</v>
+      </c>
+      <c r="FE126">
+        <v>1</v>
+      </c>
+      <c r="FF126" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG126" t="s">
+        <v>2585</v>
+      </c>
+      <c r="FH126" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP126">
+        <v>103</v>
+      </c>
+      <c r="NQ126">
+        <v>120</v>
+      </c>
+      <c r="NS126">
+        <v>113</v>
+      </c>
+      <c r="NT126">
+        <v>97</v>
+      </c>
+      <c r="NV126">
+        <v>116</v>
+      </c>
+      <c r="NW126">
+        <v>125</v>
+      </c>
+      <c r="SD126" s="1"/>
+      <c r="UH126" t="s">
+        <v>2586</v>
+      </c>
+      <c r="ZL126" s="1"/>
+      <c r="ADO126" s="1"/>
+      <c r="ADW126" s="1"/>
+      <c r="AEA126" s="1"/>
+      <c r="AEY126">
+        <v>893048549</v>
+      </c>
+      <c r="AEZ126" t="s">
+        <v>2587</v>
+      </c>
+      <c r="AFA126" s="1">
+        <v>46309.228159722217</v>
+      </c>
+      <c r="AFC126" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE126" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF126" t="s">
+        <v>2588</v>
+      </c>
+      <c r="AFG126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B127" t="s">
+        <v>737</v>
+      </c>
+      <c r="D127" t="s">
+        <v>592</v>
+      </c>
+      <c r="E127" t="s">
+        <v>752</v>
+      </c>
+      <c r="G127" t="s">
+        <v>2547</v>
+      </c>
+      <c r="EN127" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT127">
+        <v>400</v>
+      </c>
+      <c r="FU127">
+        <v>201</v>
+      </c>
+      <c r="FV127">
+        <v>0</v>
+      </c>
+      <c r="FW127">
+        <v>0</v>
+      </c>
+      <c r="FY127">
+        <v>102</v>
+      </c>
+      <c r="FZ127">
+        <v>86</v>
+      </c>
+      <c r="GA127">
+        <v>0</v>
+      </c>
+      <c r="GB127">
+        <v>0</v>
+      </c>
+      <c r="GD127">
+        <v>46</v>
+      </c>
+      <c r="GE127">
+        <v>24</v>
+      </c>
+      <c r="GF127">
+        <v>1</v>
+      </c>
+      <c r="GG127">
+        <v>1</v>
+      </c>
+      <c r="GI127">
+        <v>3</v>
+      </c>
+      <c r="GJ127">
+        <v>1</v>
+      </c>
+      <c r="GK127">
+        <v>0</v>
+      </c>
+      <c r="GL127">
+        <v>0</v>
+      </c>
+      <c r="GN127">
+        <v>0</v>
+      </c>
+      <c r="GO127">
+        <v>0</v>
+      </c>
+      <c r="GP127">
+        <v>0</v>
+      </c>
+      <c r="GQ127">
+        <v>0</v>
+      </c>
+      <c r="GR127" t="s">
+        <v>2589</v>
+      </c>
+      <c r="GS127">
+        <v>1</v>
+      </c>
+      <c r="GT127">
+        <v>0</v>
+      </c>
+      <c r="GU127">
+        <v>1</v>
+      </c>
+      <c r="GV127">
+        <v>1</v>
+      </c>
+      <c r="GW127">
+        <v>0</v>
+      </c>
+      <c r="GX127">
+        <v>1</v>
+      </c>
+      <c r="GY127">
+        <v>1</v>
+      </c>
+      <c r="GZ127" t="s">
+        <v>1323</v>
+      </c>
+      <c r="HA127">
+        <v>1</v>
+      </c>
+      <c r="HB127">
+        <v>1</v>
+      </c>
+      <c r="HC127">
+        <v>0</v>
+      </c>
+      <c r="HD127">
+        <v>1</v>
+      </c>
+      <c r="HE127">
+        <v>0</v>
+      </c>
+      <c r="HG127" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH127" t="s">
+        <v>2590</v>
+      </c>
+      <c r="HI127" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ127" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL127" t="s">
+        <v>732</v>
+      </c>
+      <c r="HT127" t="s">
+        <v>1375</v>
+      </c>
+      <c r="HU127">
+        <v>18</v>
+      </c>
+      <c r="HV127" t="s">
+        <v>2591</v>
+      </c>
+      <c r="HX127" t="s">
+        <v>1375</v>
+      </c>
+      <c r="HY127">
+        <v>18</v>
+      </c>
+      <c r="HZ127" t="s">
+        <v>2592</v>
+      </c>
+      <c r="IB127" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IC127">
+        <v>18</v>
+      </c>
+      <c r="ID127" t="s">
+        <v>2593</v>
+      </c>
+      <c r="IF127" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IG127">
+        <v>18</v>
+      </c>
+      <c r="IH127" t="s">
+        <v>2594</v>
+      </c>
+      <c r="IJ127" t="s">
+        <v>1375</v>
+      </c>
+      <c r="IK127">
+        <v>18</v>
+      </c>
+      <c r="IL127" t="s">
+        <v>2595</v>
+      </c>
+      <c r="IV127" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW127" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX127" t="s">
+        <v>2596</v>
+      </c>
+      <c r="IY127" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ127" t="s">
+        <v>2597</v>
+      </c>
+      <c r="JA127" t="s">
+        <v>720</v>
+      </c>
+      <c r="JC127" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD127" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE127" t="s">
+        <v>2598</v>
+      </c>
+      <c r="JF127" t="s">
+        <v>839</v>
+      </c>
+      <c r="JG127" t="s">
+        <v>2599</v>
+      </c>
+      <c r="JH127" t="s">
+        <v>716</v>
+      </c>
+      <c r="JJ127" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK127" t="s">
+        <v>879</v>
+      </c>
+      <c r="JL127" t="s">
+        <v>2600</v>
+      </c>
+      <c r="JM127" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN127" t="s">
+        <v>2601</v>
+      </c>
+      <c r="JO127" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ127" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR127" t="s">
+        <v>879</v>
+      </c>
+      <c r="JS127" t="s">
+        <v>842</v>
+      </c>
+      <c r="JT127" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JU127" t="s">
+        <v>842</v>
+      </c>
+      <c r="JV127" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX127" t="s">
+        <v>837</v>
+      </c>
+      <c r="JY127" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JZ127" t="s">
+        <v>842</v>
+      </c>
+      <c r="KA127" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB127" t="s">
+        <v>842</v>
+      </c>
+      <c r="KC127" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE127" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF127" t="s">
+        <v>879</v>
+      </c>
+      <c r="KG127" t="s">
+        <v>2602</v>
+      </c>
+      <c r="KH127" t="s">
+        <v>839</v>
+      </c>
+      <c r="KI127" t="s">
+        <v>2603</v>
+      </c>
+      <c r="KJ127" t="s">
+        <v>720</v>
+      </c>
+      <c r="KK127" t="s">
+        <v>2573</v>
+      </c>
+      <c r="KL127">
+        <v>0</v>
+      </c>
+      <c r="KM127">
+        <v>1</v>
+      </c>
+      <c r="KN127">
+        <v>1</v>
+      </c>
+      <c r="KO127">
+        <v>0</v>
+      </c>
+      <c r="KP127">
+        <v>1</v>
+      </c>
+      <c r="KR127" t="s">
+        <v>2604</v>
+      </c>
+      <c r="KS127" t="s">
+        <v>2605</v>
+      </c>
+      <c r="KT127" t="s">
+        <v>2606</v>
+      </c>
+      <c r="KU127" t="s">
+        <v>2607</v>
+      </c>
+      <c r="NP127">
+        <v>530</v>
+      </c>
+      <c r="NQ127">
+        <v>398</v>
+      </c>
+      <c r="NS127">
+        <v>125</v>
+      </c>
+      <c r="NT127">
+        <v>94</v>
+      </c>
+      <c r="NV127">
+        <v>56</v>
+      </c>
+      <c r="NW127">
+        <v>36</v>
+      </c>
+      <c r="SD127" s="1"/>
+      <c r="UH127" t="s">
+        <v>842</v>
+      </c>
+      <c r="ZL127" s="1"/>
+      <c r="ADO127" s="1"/>
+      <c r="ADW127" s="1"/>
+      <c r="AEA127" s="1"/>
+      <c r="AEY127">
+        <v>893132036</v>
+      </c>
+      <c r="AEZ127" t="s">
+        <v>2608</v>
+      </c>
+      <c r="AFA127" s="1">
+        <v>46309.315798611111</v>
+      </c>
+      <c r="AFC127" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE127" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF127" t="s">
+        <v>2609</v>
+      </c>
+      <c r="AFG127">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87D03F8A-9DFB-764D-AAEA-B372DB43A4BE}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5D5348F-C574-D943-B5A3-0CD151B9C2F1}"/>
   <bookViews>
-    <workbookView xWindow="4060" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3500" yWindow="1300" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nutribus 2.0 Activity" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5924" uniqueCount="2610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6901" uniqueCount="2868">
   <si>
     <t>Date</t>
   </si>
@@ -7850,6 +7850,780 @@
   </si>
   <si>
     <t>uuid:f345c3a1-d0fc-45f2-a99d-b7dfc845275d</t>
+  </si>
+  <si>
+    <t>LOMODOCH P/S</t>
+  </si>
+  <si>
+    <t>The one displayed is the one we gave on the activation day but previously it wasn't there</t>
+  </si>
+  <si>
+    <t>b9059fdd-2cad-4e7f-be05-ffbb4e9554c8</t>
+  </si>
+  <si>
+    <t>uuid:b9059fdd-2cad-4e7f-be05-ffbb4e9554c8</t>
+  </si>
+  <si>
+    <t>LOKITELAEBU P/S</t>
+  </si>
+  <si>
+    <t>They were engaged in the green house management,open discussion</t>
+  </si>
+  <si>
+    <t>They said it's not good for girl to remain at home while boys Jo to school</t>
+  </si>
+  <si>
+    <t>They supported the idea of sharing house chores</t>
+  </si>
+  <si>
+    <t>Many agreed to firewood together with girls</t>
+  </si>
+  <si>
+    <t>Many accepted to start fetching water</t>
+  </si>
+  <si>
+    <t>Many accepted to report and ensure that she comes back to school</t>
+  </si>
+  <si>
+    <t>You can add dodo</t>
+  </si>
+  <si>
+    <t>Doing work together</t>
+  </si>
+  <si>
+    <t>Sharing work at home equally</t>
+  </si>
+  <si>
+    <t>Not sure about it</t>
+  </si>
+  <si>
+    <t>Sharing work</t>
+  </si>
+  <si>
+    <t>Sharing work in order to finish it faster</t>
+  </si>
+  <si>
+    <t>Confident</t>
+  </si>
+  <si>
+    <t>Boys and girls should share work</t>
+  </si>
+  <si>
+    <t>Few seating facilities in classes</t>
+  </si>
+  <si>
+    <t>Many learners showed signs of understanding and happiness about the gifts given</t>
+  </si>
+  <si>
+    <t>More utilization of the green house</t>
+  </si>
+  <si>
+    <t>Giving of gifts should continue because it encourages learners to actively participate</t>
+  </si>
+  <si>
+    <t>ab7f8a30-46c2-4982-9ec1-f53bb80eaf5a</t>
+  </si>
+  <si>
+    <t>uuid:ab7f8a30-46c2-4982-9ec1-f53bb80eaf5a</t>
+  </si>
+  <si>
+    <t>Obokoloth central</t>
+  </si>
+  <si>
+    <t>Zadok Okello</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Millet porridge mixed with simsim paste</t>
+  </si>
+  <si>
+    <t>The training was okay though not practical but the caregiver promised to go and try at home</t>
+  </si>
+  <si>
+    <t>After the training the caregiver was optimistic to go ans try at home</t>
+  </si>
+  <si>
+    <t>The caregiver promised to go and try the skills acquired at home</t>
+  </si>
+  <si>
+    <t>Menstrual hygiene management</t>
+  </si>
+  <si>
+    <t>Man</t>
+  </si>
+  <si>
+    <t>Mindset change</t>
+  </si>
+  <si>
+    <t>We didn't understand the toll free what it meant. We shall now start calling in case of any issues</t>
+  </si>
+  <si>
+    <t>2 elders, 1 elderly woman and VHT</t>
+  </si>
+  <si>
+    <t>Supporting Girl child education.</t>
+  </si>
+  <si>
+    <t>Most of the members present were women. Climate change affected the way community members are feeding. Dry spell has reduced crop yields drastically</t>
+  </si>
+  <si>
+    <t>356180d6-8687-477e-8cf7-8f8288f365ea</t>
+  </si>
+  <si>
+    <t>uuid:356180d6-8687-477e-8cf7-8f8288f365ea</t>
+  </si>
+  <si>
+    <t>KALOTOM P/S</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>ede9f64d-10eb-4f83-abd3-e9c01d1efadb</t>
+  </si>
+  <si>
+    <t>uuid:ede9f64d-10eb-4f83-abd3-e9c01d1efadb</t>
+  </si>
+  <si>
+    <t>Monday and Thursday</t>
+  </si>
+  <si>
+    <t>Adopt metu porridge</t>
+  </si>
+  <si>
+    <t>Preparing/enriching WFP Metu porridge with local wild greens/staples Rebalancing morning water/firewood chores so girls stay in school Establishing Nutri Clubs, Nutri-Moments, or using WFP 0800 Hotline</t>
+  </si>
+  <si>
+    <t>Resources are scarse</t>
+  </si>
+  <si>
+    <t>Sharing out house chores</t>
+  </si>
+  <si>
+    <t>Both boys to share work</t>
+  </si>
+  <si>
+    <t>Nutrition is good</t>
+  </si>
+  <si>
+    <t>Save energy</t>
+  </si>
+  <si>
+    <t>Printed Nutri Club Session forms Metu Nutrition Posters Game for the school WFP Toll-Free Feedback Display Board Nutri calendar Metu handbook Pledge / Commitment card</t>
+  </si>
+  <si>
+    <t>UNAC (Uganda National Action on Childhood Disability) District Education Offices DEO</t>
+  </si>
+  <si>
+    <t>Mentorship on tool rollout Sustainability planning</t>
+  </si>
+  <si>
+    <t>The droughts have affected most people</t>
+  </si>
+  <si>
+    <t>d2e4042f-1b32-4d37-8ce5-f6033e06285f</t>
+  </si>
+  <si>
+    <t>uuid:d2e4042f-1b32-4d37-8ce5-f6033e06285f</t>
+  </si>
+  <si>
+    <t>Lopiida market</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>UNAC</t>
+  </si>
+  <si>
+    <t>Co-facilitating clean cooking/gender dialogue</t>
+  </si>
+  <si>
+    <t>Will try</t>
+  </si>
+  <si>
+    <t>Senior men VHTs</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>They will try metu porridge</t>
+  </si>
+  <si>
+    <t>The droughts have affected the crops</t>
+  </si>
+  <si>
+    <t>Will support women with house chores</t>
+  </si>
+  <si>
+    <t>Nutrition</t>
+  </si>
+  <si>
+    <t>Wfp should give them vegetables seeds to try to plant.</t>
+  </si>
+  <si>
+    <t>33e85d37-dd6e-4bc3-9201-ba610a7cfa7e</t>
+  </si>
+  <si>
+    <t>uuid:33e85d37-dd6e-4bc3-9201-ba610a7cfa7e</t>
+  </si>
+  <si>
+    <t>Session one of the week Session two of the week</t>
+  </si>
+  <si>
+    <t>Akwii ochan</t>
+  </si>
+  <si>
+    <t>Classroom and big tree</t>
+  </si>
+  <si>
+    <t>Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat) Gender Chore Rebalancing: Boys sharing morning water/firewood chores Peer Attendance Tracing: Checking and following up chronically absent classmates</t>
+  </si>
+  <si>
+    <t>Plant vegetables</t>
+  </si>
+  <si>
+    <t>16:29:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat) Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing Peer Attendance Tracing: Checking and following up chronically absent classmates</t>
+  </si>
+  <si>
+    <t>Promote nutrition and home equal sharing</t>
+  </si>
+  <si>
+    <t>They need to be supported with seeds</t>
+  </si>
+  <si>
+    <t>e18da3e4-08a6-4127-82b6-852a4f4849fa</t>
+  </si>
+  <si>
+    <t>uuid:e18da3e4-08a6-4127-82b6-852a4f4849fa</t>
+  </si>
+  <si>
+    <t>14:10:00.000+03:00</t>
+  </si>
+  <si>
+    <t>16:20:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Working hard at school</t>
+  </si>
+  <si>
+    <t>Wfp to continue supporting the school feeding</t>
+  </si>
+  <si>
+    <t>5b2cc114-16e9-416f-8d00-6e3d96c33273</t>
+  </si>
+  <si>
+    <t>uuid:5b2cc114-16e9-416f-8d00-6e3d96c33273</t>
+  </si>
+  <si>
+    <t>Mission cell</t>
+  </si>
+  <si>
+    <t>Adong Agness Vicky</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>VHT used the chart given</t>
+  </si>
+  <si>
+    <t>A care giver promised to use the locally available greens and other food items to supplement diet for her family</t>
+  </si>
+  <si>
+    <t>The caregiver is does retail trade and she promised to use her profit to supplement diet for her family</t>
+  </si>
+  <si>
+    <t>The caregiver promised to work hard to generate more income to help in buying different kinds of food items to supplement the diet</t>
+  </si>
+  <si>
+    <t>Lead Mothers present</t>
+  </si>
+  <si>
+    <t>Supporting girl child education,  Sanitation and protection of young children from malaria</t>
+  </si>
+  <si>
+    <t>The community agreed to support any initiative brought by WFP as they have helped their children so much amids scarcity of food in our school.</t>
+  </si>
+  <si>
+    <t>2 Elderly mothers, 1 influential male elder and VHT</t>
+  </si>
+  <si>
+    <t>They expected real practical demonstrations so that they would learn better.</t>
+  </si>
+  <si>
+    <t>The cooking demo was well attended by the community members. Mothers were more active than fathers</t>
+  </si>
+  <si>
+    <t>6d97005a-b638-4c46-81ea-d129dfbc0c3e</t>
+  </si>
+  <si>
+    <t>uuid:6d97005a-b638-4c46-81ea-d129dfbc0c3e</t>
+  </si>
+  <si>
+    <t>Amonicek</t>
+  </si>
+  <si>
+    <t>Akun Silvia</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Metu porridge chart was used to demonstrate</t>
+  </si>
+  <si>
+    <t>Using local vegetables to supplement diet</t>
+  </si>
+  <si>
+    <t>Serving everyone equally at home so that the little food is shared by all family members</t>
+  </si>
+  <si>
+    <t>Vegetables are always available when rain is there. These are very good supplements as they can be got.freely or at a very low cost, especially during rainy season</t>
+  </si>
+  <si>
+    <t>Theft of chicken and goats from the area</t>
+  </si>
+  <si>
+    <t>We serve our children first so there's nothing we can change about it</t>
+  </si>
+  <si>
+    <t>The community agreed to work tirelessly to support their families eat well, take children to school give strong support to WFP</t>
+  </si>
+  <si>
+    <t>Climate change as a major cause of lack of food items to supplement diet at family levels</t>
+  </si>
+  <si>
+    <t>The community appreciates WFP for the support.</t>
+  </si>
+  <si>
+    <t>c89ffa60-da17-4deb-b4e3-7bacac547dcb</t>
+  </si>
+  <si>
+    <t>uuid:c89ffa60-da17-4deb-b4e3-7bacac547dcb</t>
+  </si>
+  <si>
+    <t>RENGEN P/S</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Fair food portions for all genders Climate-smart cooking methods explained Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>Senior education officer and district nutrition focal person</t>
+  </si>
+  <si>
+    <t>Active demonstration</t>
+  </si>
+  <si>
+    <t>Written in simple English</t>
+  </si>
+  <si>
+    <t>Not being fair</t>
+  </si>
+  <si>
+    <t>Work should be shared</t>
+  </si>
+  <si>
+    <t>No problem with boys collecting firewood</t>
+  </si>
+  <si>
+    <t>Many said it's normal for boys to fetch water</t>
+  </si>
+  <si>
+    <t>Many accepted to report such cases</t>
+  </si>
+  <si>
+    <t>Sharing work equally</t>
+  </si>
+  <si>
+    <t>Sharing responsibility at home</t>
+  </si>
+  <si>
+    <t>Girls and boys should share work in a home</t>
+  </si>
+  <si>
+    <t>Sharing responsibility at home.e or by helping girls</t>
+  </si>
+  <si>
+    <t>Not very sure about it</t>
+  </si>
+  <si>
+    <t>Sharing everything in a home</t>
+  </si>
+  <si>
+    <t>Shared responsibility</t>
+  </si>
+  <si>
+    <t>Active participation from learners</t>
+  </si>
+  <si>
+    <t>Many could talk about environmental protection</t>
+  </si>
+  <si>
+    <t>They agreed to make their work plan</t>
+  </si>
+  <si>
+    <t>More materials written in the local language</t>
+  </si>
+  <si>
+    <t>7a79eec9-05c6-4dfd-b0f6-5259fe3ead23</t>
+  </si>
+  <si>
+    <t>uuid:7a79eec9-05c6-4dfd-b0f6-5259fe3ead23</t>
+  </si>
+  <si>
+    <t>Lokeru</t>
+  </si>
+  <si>
+    <t>Vicky</t>
+  </si>
+  <si>
+    <t>They lack money to purchase</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>Respect</t>
+  </si>
+  <si>
+    <t>Will support each other with work</t>
+  </si>
+  <si>
+    <t>Relief food to help the community</t>
+  </si>
+  <si>
+    <t>Droughts have affected community</t>
+  </si>
+  <si>
+    <t>Mostly droughts have affected the food</t>
+  </si>
+  <si>
+    <t>3aec9e71-67cd-409f-9fa1-55fa4fbf219b</t>
+  </si>
+  <si>
+    <t>uuid:3aec9e71-67cd-409f-9fa1-55fa4fbf219b</t>
+  </si>
+  <si>
+    <t>Town council</t>
+  </si>
+  <si>
+    <t>It's very nutritious</t>
+  </si>
+  <si>
+    <t>Yy</t>
+  </si>
+  <si>
+    <t>Respect for each other</t>
+  </si>
+  <si>
+    <t>Nutrition is healthy</t>
+  </si>
+  <si>
+    <t>Government to support the people since hunger is too much</t>
+  </si>
+  <si>
+    <t>daadea90-9e7c-4eeb-8b67-cc6496c4f62f</t>
+  </si>
+  <si>
+    <t>uuid:daadea90-9e7c-4eeb-8b67-cc6496c4f62f</t>
+  </si>
+  <si>
+    <t>Tuesday and Thursday</t>
+  </si>
+  <si>
+    <t>all pupils should given food equally at</t>
+  </si>
+  <si>
+    <t>it promotes togetherness</t>
+  </si>
+  <si>
+    <t>it promote equality</t>
+  </si>
+  <si>
+    <t>helps children to know house chores generally</t>
+  </si>
+  <si>
+    <t>it promotes unity among learners</t>
+  </si>
+  <si>
+    <t>it promotes good friendship</t>
+  </si>
+  <si>
+    <t>the sessions went well</t>
+  </si>
+  <si>
+    <t>794f527e-7739-4837-873a-c13618bd9397</t>
+  </si>
+  <si>
+    <t>uuid:794f527e-7739-4837-873a-c13618bd9397</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Structured dialogue on rebalancing chores Fair food portions for all genders Climate-smart cooking methods explained Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>Nutri Club patron Another teacher Nutri Club member</t>
+  </si>
+  <si>
+    <t>They got invovled with exitment in the activities</t>
+  </si>
+  <si>
+    <t>Every thing was clearely explained</t>
+  </si>
+  <si>
+    <t>every child has to education</t>
+  </si>
+  <si>
+    <t>so as to reach school on time</t>
+  </si>
+  <si>
+    <t>all are equal</t>
+  </si>
+  <si>
+    <t>it saves time for the sister to go to school</t>
+  </si>
+  <si>
+    <t>girls wil be left behind and will not aquire education</t>
+  </si>
+  <si>
+    <t>it saves time for all</t>
+  </si>
+  <si>
+    <t>all children are the same</t>
+  </si>
+  <si>
+    <t>it promotes gender equality</t>
+  </si>
+  <si>
+    <t>all pupils should do house chores to complete on time</t>
+  </si>
+  <si>
+    <t>all learner need same treatment</t>
+  </si>
+  <si>
+    <t>we need knowledge practically</t>
+  </si>
+  <si>
+    <t>all have right to good food</t>
+  </si>
+  <si>
+    <t>girls should be allowed to go to school</t>
+  </si>
+  <si>
+    <t>unity is promoted among learners</t>
+  </si>
+  <si>
+    <t>it promotes good respect</t>
+  </si>
+  <si>
+    <t>all children needs education equally</t>
+  </si>
+  <si>
+    <t>both children are same</t>
+  </si>
+  <si>
+    <t>Smaller saucepan for cooking food for learners</t>
+  </si>
+  <si>
+    <t>all learners were very happy and active</t>
+  </si>
+  <si>
+    <t>Good kitchen should be built and bigger sausepans should be provided to ensure faeter food preparetio</t>
+  </si>
+  <si>
+    <t>We need you to continue to provide food and skills on nutrition</t>
+  </si>
+  <si>
+    <t>The school has an temporary and emergency ECD claaroom  which is risky for the learners during windy and rainy seasons</t>
+  </si>
+  <si>
+    <t>632c3bee-c7eb-4d80-a912-865001697070</t>
+  </si>
+  <si>
+    <t>uuid:632c3bee-c7eb-4d80-a912-865001697070</t>
+  </si>
+  <si>
+    <t>at office wall and in the compound</t>
+  </si>
+  <si>
+    <t>8868ef5a-543c-41c8-a743-b49967afe478</t>
+  </si>
+  <si>
+    <t>uuid:8868ef5a-543c-41c8-a743-b49967afe478</t>
+  </si>
+  <si>
+    <t>Apeikar village Namodo</t>
+  </si>
+  <si>
+    <t>Cheploke Magret</t>
+  </si>
+  <si>
+    <t>Maize porriagde</t>
+  </si>
+  <si>
+    <t>not all food is needed right now</t>
+  </si>
+  <si>
+    <t>no money to buy all food iterms</t>
+  </si>
+  <si>
+    <t>all children need same food</t>
+  </si>
+  <si>
+    <t>none all eat together</t>
+  </si>
+  <si>
+    <t>nothing</t>
+  </si>
+  <si>
+    <t>we thanks WFP for giving food to our children at school</t>
+  </si>
+  <si>
+    <t>Ngirongole Joshua Lc1</t>
+  </si>
+  <si>
+    <t>we dont know how to use improved cooking stove and food would pour if we try</t>
+  </si>
+  <si>
+    <t>its good to involve both men and women in our demos</t>
+  </si>
+  <si>
+    <t>we need more skills on safe cooking</t>
+  </si>
+  <si>
+    <t>98b4299d-fcaa-4d02-9fad-551a2b898a02</t>
+  </si>
+  <si>
+    <t>uuid:98b4299d-fcaa-4d02-9fad-551a2b898a02</t>
+  </si>
+  <si>
+    <t>Apeikar</t>
+  </si>
+  <si>
+    <t>l9</t>
+  </si>
+  <si>
+    <t>Mixed beans and maize</t>
+  </si>
+  <si>
+    <t>i will look for money and buy balanced food for my food</t>
+  </si>
+  <si>
+    <t>i will learn how to cook using acooking stove if am taught</t>
+  </si>
+  <si>
+    <t>i will buy food for my family</t>
+  </si>
+  <si>
+    <t>Senior men Senior women VHTs Lead Mothers present Other</t>
+  </si>
+  <si>
+    <t>coordinater</t>
+  </si>
+  <si>
+    <t>we would work together with WFP to support our children stay and complete schhool</t>
+  </si>
+  <si>
+    <t>Lc1</t>
+  </si>
+  <si>
+    <t>We would like to tell WFP to bring more projects to our communities</t>
+  </si>
+  <si>
+    <t>c1938381-ca7b-48ae-bbdf-ebe84c852220</t>
+  </si>
+  <si>
+    <t>uuid:c1938381-ca7b-48ae-bbdf-ebe84c852220</t>
+  </si>
+  <si>
+    <t>Go down B</t>
+  </si>
+  <si>
+    <t>Margy</t>
+  </si>
+  <si>
+    <t>They will try to make metu</t>
+  </si>
+  <si>
+    <t>Available food's</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>VHTs Lead Mothers present</t>
+  </si>
+  <si>
+    <t>Support the growth</t>
+  </si>
+  <si>
+    <t>If food was available, they will try</t>
+  </si>
+  <si>
+    <t>Support house hold to fight malnutrition</t>
+  </si>
+  <si>
+    <t>Droughts have affected the crops</t>
+  </si>
+  <si>
+    <t>More sensitisation of the community on nutrition</t>
+  </si>
+  <si>
+    <t>5cd8117a-ba1c-4eec-9909-4a2ad7d58d84</t>
+  </si>
+  <si>
+    <t>uuid:5cd8117a-ba1c-4eec-9909-4a2ad7d58d84</t>
+  </si>
+  <si>
+    <t>Go down A</t>
+  </si>
+  <si>
+    <t>Lack of money to buy those items</t>
+  </si>
+  <si>
+    <t>They need more sensitisation</t>
+  </si>
+  <si>
+    <t>Inorder to grow heather</t>
+  </si>
+  <si>
+    <t>Wfp is to continue supporting the school and community</t>
+  </si>
+  <si>
+    <t>Everyone else to practice nutrition</t>
+  </si>
+  <si>
+    <t>They will try to promote nutrition at home.</t>
+  </si>
+  <si>
+    <t>456af3d8-5c31-4e90-b65b-7cb61f2194c0</t>
+  </si>
+  <si>
+    <t>uuid:456af3d8-5c31-4e90-b65b-7cb61f2194c0</t>
+  </si>
+  <si>
+    <t>LEMUSUI P/S</t>
+  </si>
+  <si>
+    <t>Infront of staff room and headteachers office</t>
+  </si>
+  <si>
+    <t>The nutri bus visit excited the learners and attracted community attention</t>
+  </si>
+  <si>
+    <t>61e6dcb6-3895-4856-b24f-ac1fdd2c5d6f</t>
+  </si>
+  <si>
+    <t>uuid:61e6dcb6-3895-4856-b24f-ac1fdd2c5d6f</t>
   </si>
 </sst>
 </file>
@@ -7931,8 +8705,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG127" totalsRowShown="0">
-  <autoFilter ref="A1:AFG127" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG148" totalsRowShown="0">
+  <autoFilter ref="A1:AFG148" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
   <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -9065,7 +9839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFG127"/>
+  <dimension ref="A1:AFG148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -41298,6 +42072,5183 @@
         <v>126</v>
       </c>
     </row>
+    <row r="128" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B128" t="s">
+        <v>737</v>
+      </c>
+      <c r="D128" t="s">
+        <v>592</v>
+      </c>
+      <c r="E128" t="s">
+        <v>752</v>
+      </c>
+      <c r="G128" t="s">
+        <v>2610</v>
+      </c>
+      <c r="EN128" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO128">
+        <v>1002</v>
+      </c>
+      <c r="EP128">
+        <v>719</v>
+      </c>
+      <c r="EQ128" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER128" t="s">
+        <v>1702</v>
+      </c>
+      <c r="ES128">
+        <v>1</v>
+      </c>
+      <c r="ET128">
+        <v>0</v>
+      </c>
+      <c r="EU128">
+        <v>0</v>
+      </c>
+      <c r="EV128">
+        <v>1</v>
+      </c>
+      <c r="EW128">
+        <v>0</v>
+      </c>
+      <c r="EX128">
+        <v>0</v>
+      </c>
+      <c r="EZ128" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA128">
+        <v>25</v>
+      </c>
+      <c r="FB128" t="s">
+        <v>1069</v>
+      </c>
+      <c r="FC128">
+        <v>0</v>
+      </c>
+      <c r="FD128">
+        <v>1</v>
+      </c>
+      <c r="FE128">
+        <v>1</v>
+      </c>
+      <c r="FF128" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG128" t="s">
+        <v>2611</v>
+      </c>
+      <c r="FH128" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP128">
+        <v>1286</v>
+      </c>
+      <c r="NQ128">
+        <v>783</v>
+      </c>
+      <c r="NS128">
+        <v>540</v>
+      </c>
+      <c r="NT128">
+        <v>246</v>
+      </c>
+      <c r="NV128">
+        <v>409</v>
+      </c>
+      <c r="NW128">
+        <v>176</v>
+      </c>
+      <c r="SD128" s="1"/>
+      <c r="UH128" t="s">
+        <v>842</v>
+      </c>
+      <c r="ZL128" s="1"/>
+      <c r="ADO128" s="1"/>
+      <c r="ADW128" s="1"/>
+      <c r="AEA128" s="1"/>
+      <c r="AEY128">
+        <v>893332929</v>
+      </c>
+      <c r="AEZ128" t="s">
+        <v>2612</v>
+      </c>
+      <c r="AFA128" s="1">
+        <v>46309.475694444453</v>
+      </c>
+      <c r="AFC128" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE128" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF128" t="s">
+        <v>2613</v>
+      </c>
+      <c r="AFG128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B129" t="s">
+        <v>751</v>
+      </c>
+      <c r="D129" t="s">
+        <v>594</v>
+      </c>
+      <c r="E129" t="s">
+        <v>752</v>
+      </c>
+      <c r="I129" t="s">
+        <v>2614</v>
+      </c>
+      <c r="EN129" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT129">
+        <v>794</v>
+      </c>
+      <c r="FU129">
+        <v>584</v>
+      </c>
+      <c r="FV129">
+        <v>12</v>
+      </c>
+      <c r="FW129">
+        <v>10</v>
+      </c>
+      <c r="FY129">
+        <v>276</v>
+      </c>
+      <c r="FZ129">
+        <v>213</v>
+      </c>
+      <c r="GA129">
+        <v>8</v>
+      </c>
+      <c r="GB129">
+        <v>12</v>
+      </c>
+      <c r="GD129">
+        <v>114</v>
+      </c>
+      <c r="GE129">
+        <v>119</v>
+      </c>
+      <c r="GF129">
+        <v>2</v>
+      </c>
+      <c r="GG129">
+        <v>12</v>
+      </c>
+      <c r="GI129">
+        <v>8</v>
+      </c>
+      <c r="GJ129">
+        <v>4</v>
+      </c>
+      <c r="GK129">
+        <v>3</v>
+      </c>
+      <c r="GL129">
+        <v>8</v>
+      </c>
+      <c r="GN129">
+        <v>15</v>
+      </c>
+      <c r="GO129">
+        <v>21</v>
+      </c>
+      <c r="GP129">
+        <v>0</v>
+      </c>
+      <c r="GQ129">
+        <v>0</v>
+      </c>
+      <c r="GR129" t="s">
+        <v>764</v>
+      </c>
+      <c r="GS129">
+        <v>1</v>
+      </c>
+      <c r="GT129">
+        <v>0</v>
+      </c>
+      <c r="GU129">
+        <v>0</v>
+      </c>
+      <c r="GV129">
+        <v>0</v>
+      </c>
+      <c r="GW129">
+        <v>1</v>
+      </c>
+      <c r="GX129">
+        <v>0</v>
+      </c>
+      <c r="GY129">
+        <v>1</v>
+      </c>
+      <c r="GZ129" t="s">
+        <v>1294</v>
+      </c>
+      <c r="HA129">
+        <v>1</v>
+      </c>
+      <c r="HB129">
+        <v>0</v>
+      </c>
+      <c r="HC129">
+        <v>1</v>
+      </c>
+      <c r="HD129">
+        <v>1</v>
+      </c>
+      <c r="HE129">
+        <v>0</v>
+      </c>
+      <c r="HG129" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH129" t="s">
+        <v>2615</v>
+      </c>
+      <c r="HI129" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ129" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL129" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM129" t="s">
+        <v>872</v>
+      </c>
+      <c r="HT129" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU129">
+        <v>752</v>
+      </c>
+      <c r="HV129" t="s">
+        <v>2616</v>
+      </c>
+      <c r="HX129" t="s">
+        <v>766</v>
+      </c>
+      <c r="HY129">
+        <v>524</v>
+      </c>
+      <c r="HZ129" t="s">
+        <v>2617</v>
+      </c>
+      <c r="IB129" t="s">
+        <v>766</v>
+      </c>
+      <c r="IC129">
+        <v>672</v>
+      </c>
+      <c r="ID129" t="s">
+        <v>2618</v>
+      </c>
+      <c r="IF129" t="s">
+        <v>766</v>
+      </c>
+      <c r="IG129">
+        <v>715</v>
+      </c>
+      <c r="IH129" t="s">
+        <v>2619</v>
+      </c>
+      <c r="IJ129" t="s">
+        <v>766</v>
+      </c>
+      <c r="IK129">
+        <v>452</v>
+      </c>
+      <c r="IL129" t="s">
+        <v>2620</v>
+      </c>
+      <c r="IV129" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW129" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX129" t="s">
+        <v>2621</v>
+      </c>
+      <c r="IY129" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ129" t="s">
+        <v>2622</v>
+      </c>
+      <c r="JA129" t="s">
+        <v>716</v>
+      </c>
+      <c r="JC129" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD129" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE129" t="s">
+        <v>2476</v>
+      </c>
+      <c r="JF129" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG129" t="s">
+        <v>2623</v>
+      </c>
+      <c r="JH129" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ129" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK129" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JL129" t="s">
+        <v>2624</v>
+      </c>
+      <c r="JM129" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN129" t="s">
+        <v>2625</v>
+      </c>
+      <c r="JO129" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ129" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR129" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JS129" t="s">
+        <v>2626</v>
+      </c>
+      <c r="JT129" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU129" t="s">
+        <v>2469</v>
+      </c>
+      <c r="JV129" t="s">
+        <v>716</v>
+      </c>
+      <c r="JX129" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY129" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ129" t="s">
+        <v>2627</v>
+      </c>
+      <c r="KA129" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB129" t="s">
+        <v>1501</v>
+      </c>
+      <c r="KC129" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE129" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF129" t="s">
+        <v>1143</v>
+      </c>
+      <c r="KG129" t="s">
+        <v>2628</v>
+      </c>
+      <c r="KH129" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI129" t="s">
+        <v>2622</v>
+      </c>
+      <c r="KJ129" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK129" t="s">
+        <v>2510</v>
+      </c>
+      <c r="KL129">
+        <v>0</v>
+      </c>
+      <c r="KM129">
+        <v>0</v>
+      </c>
+      <c r="KN129">
+        <v>1</v>
+      </c>
+      <c r="KO129">
+        <v>1</v>
+      </c>
+      <c r="KP129">
+        <v>1</v>
+      </c>
+      <c r="KR129" t="s">
+        <v>2629</v>
+      </c>
+      <c r="KS129" t="s">
+        <v>2630</v>
+      </c>
+      <c r="KT129" t="s">
+        <v>2631</v>
+      </c>
+      <c r="KU129" t="s">
+        <v>2483</v>
+      </c>
+      <c r="NP129">
+        <v>286</v>
+      </c>
+      <c r="NQ129">
+        <v>218</v>
+      </c>
+      <c r="NS129">
+        <v>215</v>
+      </c>
+      <c r="NT129">
+        <v>216</v>
+      </c>
+      <c r="NV129">
+        <v>98</v>
+      </c>
+      <c r="NW129">
+        <v>47</v>
+      </c>
+      <c r="SD129" s="1"/>
+      <c r="UH129" t="s">
+        <v>2632</v>
+      </c>
+      <c r="ZL129" s="1"/>
+      <c r="ADO129" s="1"/>
+      <c r="ADW129" s="1"/>
+      <c r="AEA129" s="1"/>
+      <c r="AEY129">
+        <v>893360765</v>
+      </c>
+      <c r="AEZ129" t="s">
+        <v>2633</v>
+      </c>
+      <c r="AFA129" s="1">
+        <v>46309.497685185182</v>
+      </c>
+      <c r="AFC129" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE129" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF129" t="s">
+        <v>2634</v>
+      </c>
+      <c r="AFG129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B130" t="s">
+        <v>706</v>
+      </c>
+      <c r="C130" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D130" t="s">
+        <v>591</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F130" t="s">
+        <v>2299</v>
+      </c>
+      <c r="NX130" t="s">
+        <v>2635</v>
+      </c>
+      <c r="NY130" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ130" t="s">
+        <v>2636</v>
+      </c>
+      <c r="OA130" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS130">
+        <v>41</v>
+      </c>
+      <c r="OT130" t="s">
+        <v>2282</v>
+      </c>
+      <c r="OV130">
+        <v>23</v>
+      </c>
+      <c r="OW130" t="s">
+        <v>2204</v>
+      </c>
+      <c r="OY130">
+        <v>8</v>
+      </c>
+      <c r="OZ130" t="s">
+        <v>812</v>
+      </c>
+      <c r="PB130">
+        <v>13</v>
+      </c>
+      <c r="PC130" t="s">
+        <v>2637</v>
+      </c>
+      <c r="PE130">
+        <v>1</v>
+      </c>
+      <c r="PF130" t="s">
+        <v>840</v>
+      </c>
+      <c r="PH130">
+        <v>2</v>
+      </c>
+      <c r="PI130" t="s">
+        <v>807</v>
+      </c>
+      <c r="PJ130" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL130" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN130" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO130" t="s">
+        <v>2043</v>
+      </c>
+      <c r="PQ130" t="s">
+        <v>2207</v>
+      </c>
+      <c r="PR130" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS130">
+        <v>0</v>
+      </c>
+      <c r="PT130">
+        <v>0</v>
+      </c>
+      <c r="PU130">
+        <v>1</v>
+      </c>
+      <c r="PV130" t="s">
+        <v>2638</v>
+      </c>
+      <c r="PW130" t="s">
+        <v>2046</v>
+      </c>
+      <c r="PX130">
+        <v>0</v>
+      </c>
+      <c r="PY130">
+        <v>0</v>
+      </c>
+      <c r="PZ130">
+        <v>0</v>
+      </c>
+      <c r="QA130">
+        <v>1</v>
+      </c>
+      <c r="QJ130" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK130" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QL130" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM130" t="s">
+        <v>2639</v>
+      </c>
+      <c r="QN130" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP130" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ130" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QR130" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS130" t="s">
+        <v>2640</v>
+      </c>
+      <c r="QT130" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV130" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW130" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX130" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY130" t="s">
+        <v>2641</v>
+      </c>
+      <c r="QZ130" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA130" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB130" t="s">
+        <v>732</v>
+      </c>
+      <c r="RC130" t="s">
+        <v>1957</v>
+      </c>
+      <c r="RD130">
+        <v>0</v>
+      </c>
+      <c r="RE130">
+        <v>0</v>
+      </c>
+      <c r="RF130">
+        <v>1</v>
+      </c>
+      <c r="RG130">
+        <v>0</v>
+      </c>
+      <c r="RH130">
+        <v>0</v>
+      </c>
+      <c r="RJ130" t="s">
+        <v>2642</v>
+      </c>
+      <c r="RK130">
+        <v>0</v>
+      </c>
+      <c r="RL130">
+        <v>1</v>
+      </c>
+      <c r="RM130">
+        <v>0</v>
+      </c>
+      <c r="RO130" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP130" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ130" t="s">
+        <v>2643</v>
+      </c>
+      <c r="RR130" t="s">
+        <v>2644</v>
+      </c>
+      <c r="RS130" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT130" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY130" t="s">
+        <v>2645</v>
+      </c>
+      <c r="RZ130" t="s">
+        <v>2646</v>
+      </c>
+      <c r="SA130" t="s">
+        <v>2647</v>
+      </c>
+      <c r="SB130" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD130" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH130" t="s">
+        <v>2648</v>
+      </c>
+      <c r="ZL130" s="1"/>
+      <c r="ADO130" s="1"/>
+      <c r="ADW130" s="1"/>
+      <c r="AEA130" s="1"/>
+      <c r="AEY130">
+        <v>893398430</v>
+      </c>
+      <c r="AEZ130" t="s">
+        <v>2649</v>
+      </c>
+      <c r="AFA130" s="1">
+        <v>46309.526030092587</v>
+      </c>
+      <c r="AFC130" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE130" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AFF130" t="s">
+        <v>2650</v>
+      </c>
+      <c r="AFG130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B131" t="s">
+        <v>706</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D131" t="s">
+        <v>596</v>
+      </c>
+      <c r="E131" t="s">
+        <v>752</v>
+      </c>
+      <c r="K131" t="s">
+        <v>2651</v>
+      </c>
+      <c r="EN131" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO131">
+        <v>627</v>
+      </c>
+      <c r="EP131">
+        <v>632</v>
+      </c>
+      <c r="EQ131" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER131" t="s">
+        <v>1702</v>
+      </c>
+      <c r="ES131">
+        <v>1</v>
+      </c>
+      <c r="ET131">
+        <v>0</v>
+      </c>
+      <c r="EU131">
+        <v>0</v>
+      </c>
+      <c r="EV131">
+        <v>1</v>
+      </c>
+      <c r="EW131">
+        <v>0</v>
+      </c>
+      <c r="EX131">
+        <v>0</v>
+      </c>
+      <c r="EZ131" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA131">
+        <v>35</v>
+      </c>
+      <c r="FB131" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC131">
+        <v>1</v>
+      </c>
+      <c r="FD131">
+        <v>1</v>
+      </c>
+      <c r="FE131">
+        <v>1</v>
+      </c>
+      <c r="FF131" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG131" t="s">
+        <v>2652</v>
+      </c>
+      <c r="FH131" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP131">
+        <v>182</v>
+      </c>
+      <c r="NQ131">
+        <v>183</v>
+      </c>
+      <c r="NS131">
+        <v>190</v>
+      </c>
+      <c r="NT131">
+        <v>155</v>
+      </c>
+      <c r="NV131">
+        <v>253</v>
+      </c>
+      <c r="NW131">
+        <v>263</v>
+      </c>
+      <c r="SD131" s="1"/>
+      <c r="UH131" t="s">
+        <v>732</v>
+      </c>
+      <c r="ZL131" s="1"/>
+      <c r="ADO131" s="1"/>
+      <c r="ADW131" s="1"/>
+      <c r="AEA131" s="1"/>
+      <c r="AEY131">
+        <v>893425944</v>
+      </c>
+      <c r="AEZ131" t="s">
+        <v>2653</v>
+      </c>
+      <c r="AFA131" s="1">
+        <v>46309.543009259258</v>
+      </c>
+      <c r="AFC131" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE131" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AFF131" t="s">
+        <v>2654</v>
+      </c>
+      <c r="AFG131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D132" t="s">
+        <v>596</v>
+      </c>
+      <c r="E132" t="s">
+        <v>709</v>
+      </c>
+      <c r="K132" t="s">
+        <v>2651</v>
+      </c>
+      <c r="P132">
+        <v>15</v>
+      </c>
+      <c r="Q132">
+        <v>4</v>
+      </c>
+      <c r="R132" t="s">
+        <v>711</v>
+      </c>
+      <c r="S132">
+        <v>2</v>
+      </c>
+      <c r="T132">
+        <v>1</v>
+      </c>
+      <c r="U132">
+        <v>1</v>
+      </c>
+      <c r="V132">
+        <v>0</v>
+      </c>
+      <c r="W132">
+        <v>0</v>
+      </c>
+      <c r="X132" t="s">
+        <v>711</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>2655</v>
+      </c>
+      <c r="AG132" t="s">
+        <v>1226</v>
+      </c>
+      <c r="AH132">
+        <v>1</v>
+      </c>
+      <c r="AI132">
+        <v>0</v>
+      </c>
+      <c r="AJ132">
+        <v>1</v>
+      </c>
+      <c r="AK132">
+        <v>1</v>
+      </c>
+      <c r="AL132">
+        <v>1</v>
+      </c>
+      <c r="AM132" t="s">
+        <v>783</v>
+      </c>
+      <c r="AN132">
+        <v>1</v>
+      </c>
+      <c r="AO132">
+        <v>1</v>
+      </c>
+      <c r="AP132">
+        <v>1</v>
+      </c>
+      <c r="AQ132" t="s">
+        <v>2656</v>
+      </c>
+      <c r="AR132" t="s">
+        <v>716</v>
+      </c>
+      <c r="AT132" t="s">
+        <v>2657</v>
+      </c>
+      <c r="AU132">
+        <v>1</v>
+      </c>
+      <c r="AV132">
+        <v>0</v>
+      </c>
+      <c r="AW132">
+        <v>1</v>
+      </c>
+      <c r="AX132">
+        <v>1</v>
+      </c>
+      <c r="AY132">
+        <v>0</v>
+      </c>
+      <c r="AZ132" t="s">
+        <v>783</v>
+      </c>
+      <c r="BA132">
+        <v>1</v>
+      </c>
+      <c r="BB132">
+        <v>1</v>
+      </c>
+      <c r="BC132">
+        <v>1</v>
+      </c>
+      <c r="BD132" t="s">
+        <v>2658</v>
+      </c>
+      <c r="BE132" t="s">
+        <v>716</v>
+      </c>
+      <c r="BG132" t="s">
+        <v>1226</v>
+      </c>
+      <c r="BH132">
+        <v>1</v>
+      </c>
+      <c r="BI132">
+        <v>0</v>
+      </c>
+      <c r="BJ132">
+        <v>1</v>
+      </c>
+      <c r="BK132">
+        <v>1</v>
+      </c>
+      <c r="BL132">
+        <v>1</v>
+      </c>
+      <c r="BM132" t="s">
+        <v>783</v>
+      </c>
+      <c r="BN132">
+        <v>1</v>
+      </c>
+      <c r="BO132">
+        <v>1</v>
+      </c>
+      <c r="BP132">
+        <v>1</v>
+      </c>
+      <c r="BQ132" t="s">
+        <v>2659</v>
+      </c>
+      <c r="BR132" t="s">
+        <v>716</v>
+      </c>
+      <c r="BT132" t="s">
+        <v>782</v>
+      </c>
+      <c r="BU132">
+        <v>1</v>
+      </c>
+      <c r="BV132">
+        <v>1</v>
+      </c>
+      <c r="BW132">
+        <v>1</v>
+      </c>
+      <c r="BX132">
+        <v>1</v>
+      </c>
+      <c r="BY132">
+        <v>1</v>
+      </c>
+      <c r="BZ132" t="s">
+        <v>783</v>
+      </c>
+      <c r="CA132">
+        <v>1</v>
+      </c>
+      <c r="CB132">
+        <v>1</v>
+      </c>
+      <c r="CC132">
+        <v>1</v>
+      </c>
+      <c r="CD132" t="s">
+        <v>2660</v>
+      </c>
+      <c r="CE132" t="s">
+        <v>716</v>
+      </c>
+      <c r="CG132" t="s">
+        <v>782</v>
+      </c>
+      <c r="CH132">
+        <v>1</v>
+      </c>
+      <c r="CI132">
+        <v>1</v>
+      </c>
+      <c r="CJ132">
+        <v>1</v>
+      </c>
+      <c r="CK132">
+        <v>1</v>
+      </c>
+      <c r="CL132">
+        <v>1</v>
+      </c>
+      <c r="CM132" t="s">
+        <v>783</v>
+      </c>
+      <c r="CN132">
+        <v>1</v>
+      </c>
+      <c r="CO132">
+        <v>1</v>
+      </c>
+      <c r="CP132">
+        <v>1</v>
+      </c>
+      <c r="CQ132" t="s">
+        <v>2661</v>
+      </c>
+      <c r="CR132" t="s">
+        <v>716</v>
+      </c>
+      <c r="CT132" t="s">
+        <v>782</v>
+      </c>
+      <c r="CU132">
+        <v>1</v>
+      </c>
+      <c r="CV132">
+        <v>1</v>
+      </c>
+      <c r="CW132">
+        <v>1</v>
+      </c>
+      <c r="CX132">
+        <v>1</v>
+      </c>
+      <c r="CY132">
+        <v>1</v>
+      </c>
+      <c r="CZ132" t="s">
+        <v>783</v>
+      </c>
+      <c r="DA132">
+        <v>1</v>
+      </c>
+      <c r="DB132">
+        <v>1</v>
+      </c>
+      <c r="DC132">
+        <v>1</v>
+      </c>
+      <c r="DD132" t="s">
+        <v>2662</v>
+      </c>
+      <c r="DE132" t="s">
+        <v>716</v>
+      </c>
+      <c r="DF132" t="s">
+        <v>2663</v>
+      </c>
+      <c r="DG132">
+        <v>1</v>
+      </c>
+      <c r="DH132">
+        <v>1</v>
+      </c>
+      <c r="DI132">
+        <v>0</v>
+      </c>
+      <c r="DJ132">
+        <v>1</v>
+      </c>
+      <c r="DK132">
+        <v>1</v>
+      </c>
+      <c r="DL132">
+        <v>1</v>
+      </c>
+      <c r="DM132">
+        <v>1</v>
+      </c>
+      <c r="DN132">
+        <v>0</v>
+      </c>
+      <c r="DO132">
+        <v>1</v>
+      </c>
+      <c r="DP132" t="s">
+        <v>711</v>
+      </c>
+      <c r="DQ132" t="s">
+        <v>2664</v>
+      </c>
+      <c r="DR132">
+        <v>1</v>
+      </c>
+      <c r="DS132">
+        <v>0</v>
+      </c>
+      <c r="DT132">
+        <v>1</v>
+      </c>
+      <c r="DU132">
+        <v>0</v>
+      </c>
+      <c r="DV132">
+        <v>0</v>
+      </c>
+      <c r="DW132">
+        <v>1</v>
+      </c>
+      <c r="DX132">
+        <v>0</v>
+      </c>
+      <c r="DY132">
+        <v>0</v>
+      </c>
+      <c r="DZ132" t="s">
+        <v>2665</v>
+      </c>
+      <c r="EA132">
+        <v>0</v>
+      </c>
+      <c r="EB132">
+        <v>1</v>
+      </c>
+      <c r="EC132">
+        <v>1</v>
+      </c>
+      <c r="ED132">
+        <v>0</v>
+      </c>
+      <c r="EI132">
+        <v>2</v>
+      </c>
+      <c r="EK132">
+        <v>0</v>
+      </c>
+      <c r="EM132">
+        <v>1</v>
+      </c>
+      <c r="SD132" s="1"/>
+      <c r="UH132" t="s">
+        <v>2666</v>
+      </c>
+      <c r="ZL132" s="1"/>
+      <c r="ADO132" s="1"/>
+      <c r="ADW132" s="1"/>
+      <c r="AEA132" s="1"/>
+      <c r="AEY132">
+        <v>893443270</v>
+      </c>
+      <c r="AEZ132" t="s">
+        <v>2667</v>
+      </c>
+      <c r="AFA132" s="1">
+        <v>46309.552662037036</v>
+      </c>
+      <c r="AFC132" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE132" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF132" t="s">
+        <v>2668</v>
+      </c>
+      <c r="AFG132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D133" t="s">
+        <v>596</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K133" t="s">
+        <v>2651</v>
+      </c>
+      <c r="NX133" t="s">
+        <v>2669</v>
+      </c>
+      <c r="NY133" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ133" t="s">
+        <v>2670</v>
+      </c>
+      <c r="OA133" t="s">
+        <v>711</v>
+      </c>
+      <c r="OB133" t="s">
+        <v>2671</v>
+      </c>
+      <c r="OC133">
+        <v>1</v>
+      </c>
+      <c r="OD133">
+        <v>0</v>
+      </c>
+      <c r="OE133">
+        <v>0</v>
+      </c>
+      <c r="OF133">
+        <v>0</v>
+      </c>
+      <c r="OG133">
+        <v>0</v>
+      </c>
+      <c r="OI133" t="s">
+        <v>2672</v>
+      </c>
+      <c r="OJ133">
+        <v>1</v>
+      </c>
+      <c r="OK133">
+        <v>0</v>
+      </c>
+      <c r="OL133">
+        <v>0</v>
+      </c>
+      <c r="OM133">
+        <v>0</v>
+      </c>
+      <c r="OS133">
+        <v>50</v>
+      </c>
+      <c r="OT133" t="s">
+        <v>826</v>
+      </c>
+      <c r="OV133">
+        <v>3</v>
+      </c>
+      <c r="OW133" t="s">
+        <v>819</v>
+      </c>
+      <c r="OY133">
+        <v>2</v>
+      </c>
+      <c r="OZ133" t="s">
+        <v>819</v>
+      </c>
+      <c r="PB133">
+        <v>5</v>
+      </c>
+      <c r="PC133" t="s">
+        <v>819</v>
+      </c>
+      <c r="PE133">
+        <v>0</v>
+      </c>
+      <c r="PF133" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH133">
+        <v>0</v>
+      </c>
+      <c r="PI133" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ133" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL133" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN133" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO133" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ133" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR133" t="s">
+        <v>2064</v>
+      </c>
+      <c r="PS133">
+        <v>1</v>
+      </c>
+      <c r="PT133">
+        <v>1</v>
+      </c>
+      <c r="PU133">
+        <v>0</v>
+      </c>
+      <c r="PW133" t="s">
+        <v>1922</v>
+      </c>
+      <c r="PX133">
+        <v>1</v>
+      </c>
+      <c r="PY133">
+        <v>0</v>
+      </c>
+      <c r="PZ133">
+        <v>0</v>
+      </c>
+      <c r="QA133">
+        <v>0</v>
+      </c>
+      <c r="QJ133" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK133" t="s">
+        <v>2263</v>
+      </c>
+      <c r="QL133" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM133" t="s">
+        <v>2673</v>
+      </c>
+      <c r="QN133" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP133" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QQ133" t="s">
+        <v>2263</v>
+      </c>
+      <c r="QR133" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS133" t="s">
+        <v>2673</v>
+      </c>
+      <c r="QT133" t="s">
+        <v>720</v>
+      </c>
+      <c r="QV133" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QW133" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX133" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY133" t="s">
+        <v>2673</v>
+      </c>
+      <c r="QZ133" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA133" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB133" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC133" t="s">
+        <v>2674</v>
+      </c>
+      <c r="RD133">
+        <v>1</v>
+      </c>
+      <c r="RE133">
+        <v>0</v>
+      </c>
+      <c r="RF133">
+        <v>1</v>
+      </c>
+      <c r="RG133">
+        <v>0</v>
+      </c>
+      <c r="RH133">
+        <v>0</v>
+      </c>
+      <c r="RJ133" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK133">
+        <v>0</v>
+      </c>
+      <c r="RL133">
+        <v>0</v>
+      </c>
+      <c r="RM133">
+        <v>1</v>
+      </c>
+      <c r="RN133" t="s">
+        <v>2675</v>
+      </c>
+      <c r="RO133" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP133" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ133" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR133" t="s">
+        <v>711</v>
+      </c>
+      <c r="RS133" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT133" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY133" t="s">
+        <v>2676</v>
+      </c>
+      <c r="RZ133" t="s">
+        <v>2677</v>
+      </c>
+      <c r="SA133" t="s">
+        <v>2678</v>
+      </c>
+      <c r="SB133" t="s">
+        <v>711</v>
+      </c>
+      <c r="SC133" t="s">
+        <v>2679</v>
+      </c>
+      <c r="SD133" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH133" t="s">
+        <v>2680</v>
+      </c>
+      <c r="ZL133" s="1"/>
+      <c r="ADO133" s="1"/>
+      <c r="ADW133" s="1"/>
+      <c r="AEA133" s="1"/>
+      <c r="AEY133">
+        <v>893458451</v>
+      </c>
+      <c r="AEZ133" t="s">
+        <v>2681</v>
+      </c>
+      <c r="AFA133" s="1">
+        <v>46309.561388888891</v>
+      </c>
+      <c r="AFC133" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE133" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF133" t="s">
+        <v>2682</v>
+      </c>
+      <c r="AFG133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D134" t="s">
+        <v>596</v>
+      </c>
+      <c r="E134" t="s">
+        <v>738</v>
+      </c>
+      <c r="K134" t="s">
+        <v>1961</v>
+      </c>
+      <c r="SD134" s="1"/>
+      <c r="SV134" t="s">
+        <v>2683</v>
+      </c>
+      <c r="SW134">
+        <v>1</v>
+      </c>
+      <c r="SX134">
+        <v>1</v>
+      </c>
+      <c r="SY134" t="s">
+        <v>2684</v>
+      </c>
+      <c r="SZ134">
+        <v>20</v>
+      </c>
+      <c r="TA134">
+        <v>20</v>
+      </c>
+      <c r="TB134" t="s">
+        <v>2685</v>
+      </c>
+      <c r="TC134" s="1">
+        <v>46305</v>
+      </c>
+      <c r="TD134" t="s">
+        <v>1081</v>
+      </c>
+      <c r="TE134" t="s">
+        <v>2016</v>
+      </c>
+      <c r="TF134">
+        <v>20</v>
+      </c>
+      <c r="TG134">
+        <v>20</v>
+      </c>
+      <c r="TH134">
+        <v>0</v>
+      </c>
+      <c r="TI134">
+        <v>0</v>
+      </c>
+      <c r="TJ134" t="s">
+        <v>2686</v>
+      </c>
+      <c r="TK134">
+        <v>1</v>
+      </c>
+      <c r="TL134">
+        <v>0</v>
+      </c>
+      <c r="TM134">
+        <v>0</v>
+      </c>
+      <c r="TN134">
+        <v>1</v>
+      </c>
+      <c r="TO134">
+        <v>1</v>
+      </c>
+      <c r="TP134" t="s">
+        <v>2687</v>
+      </c>
+      <c r="TQ134" s="1">
+        <v>46309</v>
+      </c>
+      <c r="TR134" t="s">
+        <v>1081</v>
+      </c>
+      <c r="TS134" t="s">
+        <v>2688</v>
+      </c>
+      <c r="TT134">
+        <v>20</v>
+      </c>
+      <c r="TU134">
+        <v>20</v>
+      </c>
+      <c r="TV134">
+        <v>0</v>
+      </c>
+      <c r="TW134">
+        <v>0</v>
+      </c>
+      <c r="TX134" t="s">
+        <v>2689</v>
+      </c>
+      <c r="TY134">
+        <v>1</v>
+      </c>
+      <c r="TZ134">
+        <v>0</v>
+      </c>
+      <c r="UA134">
+        <v>1</v>
+      </c>
+      <c r="UB134">
+        <v>0</v>
+      </c>
+      <c r="UC134">
+        <v>1</v>
+      </c>
+      <c r="UD134" t="s">
+        <v>2010</v>
+      </c>
+      <c r="UE134" s="1">
+        <v>46308</v>
+      </c>
+      <c r="UF134" t="s">
+        <v>2690</v>
+      </c>
+      <c r="UG134" t="s">
+        <v>2018</v>
+      </c>
+      <c r="UH134" t="s">
+        <v>2691</v>
+      </c>
+      <c r="ZL134" s="1"/>
+      <c r="ADO134" s="1"/>
+      <c r="ADW134" s="1"/>
+      <c r="AEA134" s="1"/>
+      <c r="AEY134">
+        <v>893476057</v>
+      </c>
+      <c r="AEZ134" t="s">
+        <v>2692</v>
+      </c>
+      <c r="AFA134" s="1">
+        <v>46309.571516203701</v>
+      </c>
+      <c r="AFC134" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE134" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF134" t="s">
+        <v>2693</v>
+      </c>
+      <c r="AFG134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D135" t="s">
+        <v>596</v>
+      </c>
+      <c r="E135" t="s">
+        <v>738</v>
+      </c>
+      <c r="K135" t="s">
+        <v>1961</v>
+      </c>
+      <c r="SD135" s="1"/>
+      <c r="SV135" t="s">
+        <v>2007</v>
+      </c>
+      <c r="SW135">
+        <v>0</v>
+      </c>
+      <c r="SX135">
+        <v>1</v>
+      </c>
+      <c r="TQ135" s="1">
+        <v>46309</v>
+      </c>
+      <c r="TR135" t="s">
+        <v>2694</v>
+      </c>
+      <c r="TS135" t="s">
+        <v>2695</v>
+      </c>
+      <c r="TT135">
+        <v>20</v>
+      </c>
+      <c r="TU135">
+        <v>20</v>
+      </c>
+      <c r="TV135">
+        <v>0</v>
+      </c>
+      <c r="TW135">
+        <v>0</v>
+      </c>
+      <c r="TX135" t="s">
+        <v>2686</v>
+      </c>
+      <c r="TY135">
+        <v>1</v>
+      </c>
+      <c r="TZ135">
+        <v>0</v>
+      </c>
+      <c r="UA135">
+        <v>0</v>
+      </c>
+      <c r="UB135">
+        <v>1</v>
+      </c>
+      <c r="UC135">
+        <v>1</v>
+      </c>
+      <c r="UD135" t="s">
+        <v>2010</v>
+      </c>
+      <c r="UE135" s="1">
+        <v>46308</v>
+      </c>
+      <c r="UF135" t="s">
+        <v>2696</v>
+      </c>
+      <c r="UG135" t="s">
+        <v>2018</v>
+      </c>
+      <c r="UH135" t="s">
+        <v>2697</v>
+      </c>
+      <c r="ZL135" s="1"/>
+      <c r="ADO135" s="1"/>
+      <c r="ADW135" s="1"/>
+      <c r="AEA135" s="1"/>
+      <c r="AEY135">
+        <v>893480374</v>
+      </c>
+      <c r="AEZ135" t="s">
+        <v>2698</v>
+      </c>
+      <c r="AFA135" s="1">
+        <v>46309.574178240742</v>
+      </c>
+      <c r="AFC135" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE135" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF135" t="s">
+        <v>2699</v>
+      </c>
+      <c r="AFG135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B136" t="s">
+        <v>706</v>
+      </c>
+      <c r="C136" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D136" t="s">
+        <v>591</v>
+      </c>
+      <c r="E136" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F136" t="s">
+        <v>710</v>
+      </c>
+      <c r="NX136" t="s">
+        <v>2700</v>
+      </c>
+      <c r="NY136" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ136" t="s">
+        <v>2701</v>
+      </c>
+      <c r="OA136" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS136">
+        <v>49</v>
+      </c>
+      <c r="OT136" t="s">
+        <v>2702</v>
+      </c>
+      <c r="OV136">
+        <v>25</v>
+      </c>
+      <c r="OW136" t="s">
+        <v>864</v>
+      </c>
+      <c r="OY136">
+        <v>12</v>
+      </c>
+      <c r="OZ136" t="s">
+        <v>767</v>
+      </c>
+      <c r="PB136">
+        <v>23</v>
+      </c>
+      <c r="PC136" t="s">
+        <v>2204</v>
+      </c>
+      <c r="PE136">
+        <v>1</v>
+      </c>
+      <c r="PF136" t="s">
+        <v>840</v>
+      </c>
+      <c r="PH136">
+        <v>1</v>
+      </c>
+      <c r="PI136" t="s">
+        <v>840</v>
+      </c>
+      <c r="PJ136" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL136" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN136" t="s">
+        <v>732</v>
+      </c>
+      <c r="PO136" t="s">
+        <v>2043</v>
+      </c>
+      <c r="PQ136" t="s">
+        <v>2207</v>
+      </c>
+      <c r="PR136" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS136">
+        <v>0</v>
+      </c>
+      <c r="PT136">
+        <v>0</v>
+      </c>
+      <c r="PU136">
+        <v>1</v>
+      </c>
+      <c r="PV136" t="s">
+        <v>2703</v>
+      </c>
+      <c r="PW136" t="s">
+        <v>2046</v>
+      </c>
+      <c r="PX136">
+        <v>0</v>
+      </c>
+      <c r="PY136">
+        <v>0</v>
+      </c>
+      <c r="PZ136">
+        <v>0</v>
+      </c>
+      <c r="QA136">
+        <v>1</v>
+      </c>
+      <c r="QJ136" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK136" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QL136" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM136" t="s">
+        <v>2704</v>
+      </c>
+      <c r="QN136" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP136" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QQ136" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR136" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS136" t="s">
+        <v>2705</v>
+      </c>
+      <c r="QT136" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV136" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW136" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QX136" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY136" t="s">
+        <v>2706</v>
+      </c>
+      <c r="QZ136" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA136" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB136" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC136" t="s">
+        <v>2707</v>
+      </c>
+      <c r="RD136">
+        <v>0</v>
+      </c>
+      <c r="RE136">
+        <v>0</v>
+      </c>
+      <c r="RF136">
+        <v>0</v>
+      </c>
+      <c r="RG136">
+        <v>1</v>
+      </c>
+      <c r="RH136">
+        <v>0</v>
+      </c>
+      <c r="RJ136" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK136">
+        <v>0</v>
+      </c>
+      <c r="RL136">
+        <v>0</v>
+      </c>
+      <c r="RM136">
+        <v>1</v>
+      </c>
+      <c r="RN136" t="s">
+        <v>2708</v>
+      </c>
+      <c r="RO136" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP136" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ136" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR136" t="s">
+        <v>2226</v>
+      </c>
+      <c r="RS136" t="s">
+        <v>732</v>
+      </c>
+      <c r="RT136" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY136" t="s">
+        <v>2709</v>
+      </c>
+      <c r="RZ136" t="s">
+        <v>2710</v>
+      </c>
+      <c r="SA136" t="s">
+        <v>2711</v>
+      </c>
+      <c r="SB136" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD136" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH136" t="s">
+        <v>2712</v>
+      </c>
+      <c r="ZL136" s="1"/>
+      <c r="ADO136" s="1"/>
+      <c r="ADW136" s="1"/>
+      <c r="AEA136" s="1"/>
+      <c r="AEY136">
+        <v>893563038</v>
+      </c>
+      <c r="AEZ136" t="s">
+        <v>2713</v>
+      </c>
+      <c r="AFA136" s="1">
+        <v>46309.624351851853</v>
+      </c>
+      <c r="AFC136" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE136" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF136" t="s">
+        <v>2714</v>
+      </c>
+      <c r="AFG136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B137" t="s">
+        <v>706</v>
+      </c>
+      <c r="C137" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D137" t="s">
+        <v>591</v>
+      </c>
+      <c r="E137" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F137" t="s">
+        <v>2299</v>
+      </c>
+      <c r="NX137" t="s">
+        <v>2715</v>
+      </c>
+      <c r="NY137" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ137" t="s">
+        <v>2716</v>
+      </c>
+      <c r="OA137" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS137">
+        <v>37</v>
+      </c>
+      <c r="OT137" t="s">
+        <v>2717</v>
+      </c>
+      <c r="OV137">
+        <v>19</v>
+      </c>
+      <c r="OW137" t="s">
+        <v>832</v>
+      </c>
+      <c r="OY137">
+        <v>11</v>
+      </c>
+      <c r="OZ137" t="s">
+        <v>1917</v>
+      </c>
+      <c r="PB137">
+        <v>14</v>
+      </c>
+      <c r="PC137" t="s">
+        <v>762</v>
+      </c>
+      <c r="PE137">
+        <v>2</v>
+      </c>
+      <c r="PF137" t="s">
+        <v>807</v>
+      </c>
+      <c r="PH137">
+        <v>1</v>
+      </c>
+      <c r="PI137" t="s">
+        <v>840</v>
+      </c>
+      <c r="PJ137" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL137" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN137" t="s">
+        <v>732</v>
+      </c>
+      <c r="PO137" t="s">
+        <v>2043</v>
+      </c>
+      <c r="PQ137" t="s">
+        <v>2207</v>
+      </c>
+      <c r="PR137" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS137">
+        <v>0</v>
+      </c>
+      <c r="PT137">
+        <v>0</v>
+      </c>
+      <c r="PU137">
+        <v>1</v>
+      </c>
+      <c r="PV137" t="s">
+        <v>2718</v>
+      </c>
+      <c r="PW137" t="s">
+        <v>2046</v>
+      </c>
+      <c r="PX137">
+        <v>0</v>
+      </c>
+      <c r="PY137">
+        <v>0</v>
+      </c>
+      <c r="PZ137">
+        <v>0</v>
+      </c>
+      <c r="QA137">
+        <v>1</v>
+      </c>
+      <c r="QJ137" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK137" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QL137" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM137" t="s">
+        <v>2719</v>
+      </c>
+      <c r="QN137" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP137" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QQ137" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QR137" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS137" t="s">
+        <v>2720</v>
+      </c>
+      <c r="QT137" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV137" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QW137" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QX137" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY137" t="s">
+        <v>2721</v>
+      </c>
+      <c r="QZ137" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA137" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB137" t="s">
+        <v>732</v>
+      </c>
+      <c r="RC137" t="s">
+        <v>1957</v>
+      </c>
+      <c r="RD137">
+        <v>0</v>
+      </c>
+      <c r="RE137">
+        <v>0</v>
+      </c>
+      <c r="RF137">
+        <v>1</v>
+      </c>
+      <c r="RG137">
+        <v>0</v>
+      </c>
+      <c r="RH137">
+        <v>0</v>
+      </c>
+      <c r="RJ137" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK137">
+        <v>0</v>
+      </c>
+      <c r="RL137">
+        <v>0</v>
+      </c>
+      <c r="RM137">
+        <v>1</v>
+      </c>
+      <c r="RN137" t="s">
+        <v>2722</v>
+      </c>
+      <c r="RO137" t="s">
+        <v>1953</v>
+      </c>
+      <c r="RP137" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ137" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR137" t="s">
+        <v>2723</v>
+      </c>
+      <c r="RS137" t="s">
+        <v>732</v>
+      </c>
+      <c r="RT137" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY137" t="s">
+        <v>2724</v>
+      </c>
+      <c r="RZ137" t="s">
+        <v>1912</v>
+      </c>
+      <c r="SA137" t="s">
+        <v>2725</v>
+      </c>
+      <c r="SB137" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD137" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH137" t="s">
+        <v>2726</v>
+      </c>
+      <c r="ZL137" s="1"/>
+      <c r="ADO137" s="1"/>
+      <c r="ADW137" s="1"/>
+      <c r="AEA137" s="1"/>
+      <c r="AEY137">
+        <v>893605677</v>
+      </c>
+      <c r="AEZ137" t="s">
+        <v>2727</v>
+      </c>
+      <c r="AFA137" s="1">
+        <v>46309.649652777778</v>
+      </c>
+      <c r="AFC137" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE137" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF137" t="s">
+        <v>2728</v>
+      </c>
+      <c r="AFG137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B138" t="s">
+        <v>751</v>
+      </c>
+      <c r="D138" t="s">
+        <v>594</v>
+      </c>
+      <c r="E138" t="s">
+        <v>752</v>
+      </c>
+      <c r="I138" t="s">
+        <v>2729</v>
+      </c>
+      <c r="EN138" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT138">
+        <v>683</v>
+      </c>
+      <c r="FU138">
+        <v>549</v>
+      </c>
+      <c r="FV138">
+        <v>15</v>
+      </c>
+      <c r="FW138">
+        <v>11</v>
+      </c>
+      <c r="FY138">
+        <v>386</v>
+      </c>
+      <c r="FZ138">
+        <v>254</v>
+      </c>
+      <c r="GA138">
+        <v>12</v>
+      </c>
+      <c r="GB138">
+        <v>7</v>
+      </c>
+      <c r="GD138">
+        <v>215</v>
+      </c>
+      <c r="GE138">
+        <v>185</v>
+      </c>
+      <c r="GF138">
+        <v>9</v>
+      </c>
+      <c r="GG138">
+        <v>5</v>
+      </c>
+      <c r="GI138">
+        <v>9</v>
+      </c>
+      <c r="GJ138">
+        <v>6</v>
+      </c>
+      <c r="GK138">
+        <v>4</v>
+      </c>
+      <c r="GL138">
+        <v>6</v>
+      </c>
+      <c r="GN138">
+        <v>10</v>
+      </c>
+      <c r="GO138">
+        <v>45</v>
+      </c>
+      <c r="GP138">
+        <v>6</v>
+      </c>
+      <c r="GQ138">
+        <v>2</v>
+      </c>
+      <c r="GR138" t="s">
+        <v>2730</v>
+      </c>
+      <c r="GS138">
+        <v>1</v>
+      </c>
+      <c r="GT138">
+        <v>0</v>
+      </c>
+      <c r="GU138">
+        <v>0</v>
+      </c>
+      <c r="GV138">
+        <v>0</v>
+      </c>
+      <c r="GW138">
+        <v>1</v>
+      </c>
+      <c r="GX138">
+        <v>1</v>
+      </c>
+      <c r="GY138">
+        <v>1</v>
+      </c>
+      <c r="GZ138" t="s">
+        <v>1671</v>
+      </c>
+      <c r="HA138">
+        <v>1</v>
+      </c>
+      <c r="HB138">
+        <v>0</v>
+      </c>
+      <c r="HC138">
+        <v>0</v>
+      </c>
+      <c r="HD138">
+        <v>1</v>
+      </c>
+      <c r="HE138">
+        <v>1</v>
+      </c>
+      <c r="HF138" t="s">
+        <v>2731</v>
+      </c>
+      <c r="HG138" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH138" t="s">
+        <v>2732</v>
+      </c>
+      <c r="HI138" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ138" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL138" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM138" t="s">
+        <v>2733</v>
+      </c>
+      <c r="HT138" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU138">
+        <v>750</v>
+      </c>
+      <c r="HV138" t="s">
+        <v>2734</v>
+      </c>
+      <c r="HX138" t="s">
+        <v>766</v>
+      </c>
+      <c r="HY138">
+        <v>654</v>
+      </c>
+      <c r="HZ138" t="s">
+        <v>2735</v>
+      </c>
+      <c r="IB138" t="s">
+        <v>766</v>
+      </c>
+      <c r="IC138">
+        <v>579</v>
+      </c>
+      <c r="ID138" t="s">
+        <v>2736</v>
+      </c>
+      <c r="IF138" t="s">
+        <v>765</v>
+      </c>
+      <c r="IG138">
+        <v>984</v>
+      </c>
+      <c r="IH138" t="s">
+        <v>2737</v>
+      </c>
+      <c r="IJ138" t="s">
+        <v>766</v>
+      </c>
+      <c r="IK138">
+        <v>987</v>
+      </c>
+      <c r="IL138" t="s">
+        <v>2738</v>
+      </c>
+      <c r="IV138" t="s">
+        <v>768</v>
+      </c>
+      <c r="IW138" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX138" t="s">
+        <v>2739</v>
+      </c>
+      <c r="IY138" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ138" t="s">
+        <v>2740</v>
+      </c>
+      <c r="JA138" t="s">
+        <v>716</v>
+      </c>
+      <c r="JC138" t="s">
+        <v>768</v>
+      </c>
+      <c r="JD138" t="s">
+        <v>879</v>
+      </c>
+      <c r="JE138" t="s">
+        <v>1501</v>
+      </c>
+      <c r="JF138" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG138" t="s">
+        <v>1493</v>
+      </c>
+      <c r="JH138" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ138" t="s">
+        <v>768</v>
+      </c>
+      <c r="JK138" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JL138" t="s">
+        <v>2741</v>
+      </c>
+      <c r="JM138" t="s">
+        <v>1209</v>
+      </c>
+      <c r="JN138" t="s">
+        <v>1501</v>
+      </c>
+      <c r="JO138" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ138" t="s">
+        <v>768</v>
+      </c>
+      <c r="JR138" t="s">
+        <v>1143</v>
+      </c>
+      <c r="JS138" t="s">
+        <v>2742</v>
+      </c>
+      <c r="JT138" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU138" t="s">
+        <v>1493</v>
+      </c>
+      <c r="JV138" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX138" t="s">
+        <v>835</v>
+      </c>
+      <c r="JY138" t="s">
+        <v>879</v>
+      </c>
+      <c r="JZ138" t="s">
+        <v>2743</v>
+      </c>
+      <c r="KA138" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB138" t="s">
+        <v>2744</v>
+      </c>
+      <c r="KC138" t="s">
+        <v>716</v>
+      </c>
+      <c r="KE138" t="s">
+        <v>768</v>
+      </c>
+      <c r="KF138" t="s">
+        <v>1143</v>
+      </c>
+      <c r="KG138" t="s">
+        <v>2745</v>
+      </c>
+      <c r="KH138" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI138" t="s">
+        <v>1493</v>
+      </c>
+      <c r="KJ138" t="s">
+        <v>720</v>
+      </c>
+      <c r="KK138" t="s">
+        <v>2479</v>
+      </c>
+      <c r="KL138">
+        <v>0</v>
+      </c>
+      <c r="KM138">
+        <v>0</v>
+      </c>
+      <c r="KN138">
+        <v>1</v>
+      </c>
+      <c r="KO138">
+        <v>0</v>
+      </c>
+      <c r="KP138">
+        <v>1</v>
+      </c>
+      <c r="KR138" t="s">
+        <v>2746</v>
+      </c>
+      <c r="KS138" t="s">
+        <v>2747</v>
+      </c>
+      <c r="KT138" t="s">
+        <v>2748</v>
+      </c>
+      <c r="KU138" t="s">
+        <v>2483</v>
+      </c>
+      <c r="NP138">
+        <v>989</v>
+      </c>
+      <c r="NQ138">
+        <v>564</v>
+      </c>
+      <c r="NS138">
+        <v>465</v>
+      </c>
+      <c r="NT138">
+        <v>324</v>
+      </c>
+      <c r="NV138">
+        <v>264</v>
+      </c>
+      <c r="NW138">
+        <v>325</v>
+      </c>
+      <c r="SD138" s="1"/>
+      <c r="UH138" t="s">
+        <v>2749</v>
+      </c>
+      <c r="ZL138" s="1"/>
+      <c r="ADO138" s="1"/>
+      <c r="ADW138" s="1"/>
+      <c r="AEA138" s="1"/>
+      <c r="AEY138">
+        <v>893658886</v>
+      </c>
+      <c r="AEZ138" t="s">
+        <v>2750</v>
+      </c>
+      <c r="AFA138" s="1">
+        <v>46309.682581018518</v>
+      </c>
+      <c r="AFC138" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE138" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF138" t="s">
+        <v>2751</v>
+      </c>
+      <c r="AFG138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D139" t="s">
+        <v>596</v>
+      </c>
+      <c r="E139" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K139" t="s">
+        <v>1961</v>
+      </c>
+      <c r="NX139" t="s">
+        <v>2752</v>
+      </c>
+      <c r="NY139" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ139" t="s">
+        <v>2753</v>
+      </c>
+      <c r="OA139" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS139">
+        <v>45</v>
+      </c>
+      <c r="OT139" t="s">
+        <v>819</v>
+      </c>
+      <c r="OV139">
+        <v>28</v>
+      </c>
+      <c r="OW139" t="s">
+        <v>819</v>
+      </c>
+      <c r="OY139">
+        <v>12</v>
+      </c>
+      <c r="OZ139" t="s">
+        <v>819</v>
+      </c>
+      <c r="PB139">
+        <v>18</v>
+      </c>
+      <c r="PC139" t="s">
+        <v>819</v>
+      </c>
+      <c r="PE139">
+        <v>1</v>
+      </c>
+      <c r="PF139" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH139">
+        <v>0</v>
+      </c>
+      <c r="PI139" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ139" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL139" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM139" t="s">
+        <v>2754</v>
+      </c>
+      <c r="PN139" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO139" t="s">
+        <v>1920</v>
+      </c>
+      <c r="PQ139" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR139" t="s">
+        <v>2395</v>
+      </c>
+      <c r="PS139">
+        <v>0</v>
+      </c>
+      <c r="PT139">
+        <v>1</v>
+      </c>
+      <c r="PU139">
+        <v>0</v>
+      </c>
+      <c r="PW139" t="s">
+        <v>2139</v>
+      </c>
+      <c r="PX139">
+        <v>1</v>
+      </c>
+      <c r="PY139">
+        <v>0</v>
+      </c>
+      <c r="PZ139">
+        <v>1</v>
+      </c>
+      <c r="QA139">
+        <v>0</v>
+      </c>
+      <c r="QJ139" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK139" t="s">
+        <v>2263</v>
+      </c>
+      <c r="QL139" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM139" t="s">
+        <v>711</v>
+      </c>
+      <c r="QN139" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP139" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QQ139" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QR139" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS139" t="s">
+        <v>711</v>
+      </c>
+      <c r="QT139" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV139" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW139" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX139" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY139" t="s">
+        <v>711</v>
+      </c>
+      <c r="QZ139" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA139" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB139" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC139" t="s">
+        <v>2225</v>
+      </c>
+      <c r="RD139">
+        <v>1</v>
+      </c>
+      <c r="RE139">
+        <v>1</v>
+      </c>
+      <c r="RF139">
+        <v>1</v>
+      </c>
+      <c r="RG139">
+        <v>0</v>
+      </c>
+      <c r="RH139">
+        <v>0</v>
+      </c>
+      <c r="RJ139" t="s">
+        <v>706</v>
+      </c>
+      <c r="RK139">
+        <v>0</v>
+      </c>
+      <c r="RL139">
+        <v>0</v>
+      </c>
+      <c r="RM139">
+        <v>1</v>
+      </c>
+      <c r="RN139" t="s">
+        <v>2755</v>
+      </c>
+      <c r="RO139" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP139" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ139" t="s">
+        <v>2756</v>
+      </c>
+      <c r="RR139" t="s">
+        <v>2757</v>
+      </c>
+      <c r="RS139" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT139" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY139" t="s">
+        <v>2758</v>
+      </c>
+      <c r="RZ139" t="s">
+        <v>2759</v>
+      </c>
+      <c r="SA139" t="s">
+        <v>2760</v>
+      </c>
+      <c r="SB139" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD139" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH139" t="s">
+        <v>2761</v>
+      </c>
+      <c r="ZL139" s="1"/>
+      <c r="ADO139" s="1"/>
+      <c r="ADW139" s="1"/>
+      <c r="AEA139" s="1"/>
+      <c r="AEY139">
+        <v>893700667</v>
+      </c>
+      <c r="AEZ139" t="s">
+        <v>2762</v>
+      </c>
+      <c r="AFA139" s="1">
+        <v>46309.715196759258</v>
+      </c>
+      <c r="AFC139" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE139" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF139" t="s">
+        <v>2763</v>
+      </c>
+      <c r="AFG139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D140" t="s">
+        <v>596</v>
+      </c>
+      <c r="E140" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K140" t="s">
+        <v>1961</v>
+      </c>
+      <c r="NX140" t="s">
+        <v>2764</v>
+      </c>
+      <c r="NY140" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ140" t="s">
+        <v>2753</v>
+      </c>
+      <c r="OA140" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS140">
+        <v>55</v>
+      </c>
+      <c r="OT140" t="s">
+        <v>819</v>
+      </c>
+      <c r="OV140">
+        <v>10</v>
+      </c>
+      <c r="OW140" t="s">
+        <v>819</v>
+      </c>
+      <c r="OY140">
+        <v>0</v>
+      </c>
+      <c r="OZ140" t="s">
+        <v>819</v>
+      </c>
+      <c r="PB140">
+        <v>0</v>
+      </c>
+      <c r="PC140" t="s">
+        <v>819</v>
+      </c>
+      <c r="PE140">
+        <v>0</v>
+      </c>
+      <c r="PF140" t="s">
+        <v>819</v>
+      </c>
+      <c r="PH140">
+        <v>0</v>
+      </c>
+      <c r="PI140" t="s">
+        <v>819</v>
+      </c>
+      <c r="PJ140" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL140" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM140" t="s">
+        <v>2765</v>
+      </c>
+      <c r="PN140" t="s">
+        <v>732</v>
+      </c>
+      <c r="PO140" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ140" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR140" t="s">
+        <v>2064</v>
+      </c>
+      <c r="PS140">
+        <v>1</v>
+      </c>
+      <c r="PT140">
+        <v>1</v>
+      </c>
+      <c r="PU140">
+        <v>0</v>
+      </c>
+      <c r="PW140" t="s">
+        <v>2139</v>
+      </c>
+      <c r="PX140">
+        <v>1</v>
+      </c>
+      <c r="PY140">
+        <v>0</v>
+      </c>
+      <c r="PZ140">
+        <v>1</v>
+      </c>
+      <c r="QA140">
+        <v>0</v>
+      </c>
+      <c r="QJ140" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK140" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL140" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM140" t="s">
+        <v>711</v>
+      </c>
+      <c r="QN140" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP140" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ140" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QR140" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS140" t="s">
+        <v>2766</v>
+      </c>
+      <c r="QT140" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV140" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW140" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX140" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY140" t="s">
+        <v>711</v>
+      </c>
+      <c r="QZ140" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA140" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB140" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC140" t="s">
+        <v>2107</v>
+      </c>
+      <c r="RD140">
+        <v>0</v>
+      </c>
+      <c r="RE140">
+        <v>1</v>
+      </c>
+      <c r="RF140">
+        <v>1</v>
+      </c>
+      <c r="RG140">
+        <v>0</v>
+      </c>
+      <c r="RH140">
+        <v>0</v>
+      </c>
+      <c r="RJ140" t="s">
+        <v>2108</v>
+      </c>
+      <c r="RK140">
+        <v>1</v>
+      </c>
+      <c r="RL140">
+        <v>0</v>
+      </c>
+      <c r="RM140">
+        <v>1</v>
+      </c>
+      <c r="RN140" t="s">
+        <v>2755</v>
+      </c>
+      <c r="RO140" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP140" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ140" t="s">
+        <v>2053</v>
+      </c>
+      <c r="RR140" t="s">
+        <v>2675</v>
+      </c>
+      <c r="RS140" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT140" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY140" t="s">
+        <v>2767</v>
+      </c>
+      <c r="RZ140" t="s">
+        <v>2687</v>
+      </c>
+      <c r="SA140" t="s">
+        <v>2768</v>
+      </c>
+      <c r="SB140" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD140" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH140" t="s">
+        <v>2769</v>
+      </c>
+      <c r="ZL140" s="1"/>
+      <c r="ADO140" s="1"/>
+      <c r="ADW140" s="1"/>
+      <c r="AEA140" s="1"/>
+      <c r="AEY140">
+        <v>893707884</v>
+      </c>
+      <c r="AEZ140" t="s">
+        <v>2770</v>
+      </c>
+      <c r="AFA140" s="1">
+        <v>46309.721122685187</v>
+      </c>
+      <c r="AFC140" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE140" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF140" t="s">
+        <v>2771</v>
+      </c>
+      <c r="AFG140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B141" t="s">
+        <v>951</v>
+      </c>
+      <c r="D141" t="s">
+        <v>589</v>
+      </c>
+      <c r="E141" t="s">
+        <v>709</v>
+      </c>
+      <c r="N141" t="s">
+        <v>1160</v>
+      </c>
+      <c r="P141">
+        <v>8</v>
+      </c>
+      <c r="Q141">
+        <v>6</v>
+      </c>
+      <c r="R141" t="s">
+        <v>711</v>
+      </c>
+      <c r="S141">
+        <v>2</v>
+      </c>
+      <c r="T141">
+        <v>1</v>
+      </c>
+      <c r="U141">
+        <v>2</v>
+      </c>
+      <c r="V141">
+        <v>1</v>
+      </c>
+      <c r="W141">
+        <v>1</v>
+      </c>
+      <c r="X141" t="s">
+        <v>711</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>2772</v>
+      </c>
+      <c r="AG141" t="s">
+        <v>854</v>
+      </c>
+      <c r="AH141">
+        <v>1</v>
+      </c>
+      <c r="AI141">
+        <v>0</v>
+      </c>
+      <c r="AJ141">
+        <v>0</v>
+      </c>
+      <c r="AK141">
+        <v>1</v>
+      </c>
+      <c r="AL141">
+        <v>1</v>
+      </c>
+      <c r="AM141" t="s">
+        <v>783</v>
+      </c>
+      <c r="AN141">
+        <v>1</v>
+      </c>
+      <c r="AO141">
+        <v>1</v>
+      </c>
+      <c r="AP141">
+        <v>1</v>
+      </c>
+      <c r="AQ141" t="s">
+        <v>2773</v>
+      </c>
+      <c r="AR141" t="s">
+        <v>716</v>
+      </c>
+      <c r="AT141" t="s">
+        <v>782</v>
+      </c>
+      <c r="AU141">
+        <v>1</v>
+      </c>
+      <c r="AV141">
+        <v>1</v>
+      </c>
+      <c r="AW141">
+        <v>1</v>
+      </c>
+      <c r="AX141">
+        <v>1</v>
+      </c>
+      <c r="AY141">
+        <v>1</v>
+      </c>
+      <c r="AZ141" t="s">
+        <v>783</v>
+      </c>
+      <c r="BA141">
+        <v>1</v>
+      </c>
+      <c r="BB141">
+        <v>1</v>
+      </c>
+      <c r="BC141">
+        <v>1</v>
+      </c>
+      <c r="BD141" t="s">
+        <v>2774</v>
+      </c>
+      <c r="BE141" t="s">
+        <v>720</v>
+      </c>
+      <c r="BG141" t="s">
+        <v>811</v>
+      </c>
+      <c r="BH141">
+        <v>0</v>
+      </c>
+      <c r="BI141">
+        <v>1</v>
+      </c>
+      <c r="BJ141">
+        <v>1</v>
+      </c>
+      <c r="BK141">
+        <v>1</v>
+      </c>
+      <c r="BL141">
+        <v>1</v>
+      </c>
+      <c r="BM141" t="s">
+        <v>783</v>
+      </c>
+      <c r="BN141">
+        <v>1</v>
+      </c>
+      <c r="BO141">
+        <v>1</v>
+      </c>
+      <c r="BP141">
+        <v>1</v>
+      </c>
+      <c r="BQ141" t="s">
+        <v>2775</v>
+      </c>
+      <c r="BR141" t="s">
+        <v>716</v>
+      </c>
+      <c r="BT141" t="s">
+        <v>782</v>
+      </c>
+      <c r="BU141">
+        <v>1</v>
+      </c>
+      <c r="BV141">
+        <v>1</v>
+      </c>
+      <c r="BW141">
+        <v>1</v>
+      </c>
+      <c r="BX141">
+        <v>1</v>
+      </c>
+      <c r="BY141">
+        <v>1</v>
+      </c>
+      <c r="BZ141" t="s">
+        <v>783</v>
+      </c>
+      <c r="CA141">
+        <v>1</v>
+      </c>
+      <c r="CB141">
+        <v>1</v>
+      </c>
+      <c r="CC141">
+        <v>1</v>
+      </c>
+      <c r="CD141" t="s">
+        <v>2776</v>
+      </c>
+      <c r="CE141" t="s">
+        <v>716</v>
+      </c>
+      <c r="CG141" t="s">
+        <v>782</v>
+      </c>
+      <c r="CH141">
+        <v>1</v>
+      </c>
+      <c r="CI141">
+        <v>1</v>
+      </c>
+      <c r="CJ141">
+        <v>1</v>
+      </c>
+      <c r="CK141">
+        <v>1</v>
+      </c>
+      <c r="CL141">
+        <v>1</v>
+      </c>
+      <c r="CM141" t="s">
+        <v>783</v>
+      </c>
+      <c r="CN141">
+        <v>1</v>
+      </c>
+      <c r="CO141">
+        <v>1</v>
+      </c>
+      <c r="CP141">
+        <v>1</v>
+      </c>
+      <c r="CQ141" t="s">
+        <v>2777</v>
+      </c>
+      <c r="CR141" t="s">
+        <v>720</v>
+      </c>
+      <c r="CT141" t="s">
+        <v>782</v>
+      </c>
+      <c r="CU141">
+        <v>1</v>
+      </c>
+      <c r="CV141">
+        <v>1</v>
+      </c>
+      <c r="CW141">
+        <v>1</v>
+      </c>
+      <c r="CX141">
+        <v>1</v>
+      </c>
+      <c r="CY141">
+        <v>1</v>
+      </c>
+      <c r="CZ141" t="s">
+        <v>783</v>
+      </c>
+      <c r="DA141">
+        <v>1</v>
+      </c>
+      <c r="DB141">
+        <v>1</v>
+      </c>
+      <c r="DC141">
+        <v>1</v>
+      </c>
+      <c r="DD141" t="s">
+        <v>2778</v>
+      </c>
+      <c r="DE141" t="s">
+        <v>720</v>
+      </c>
+      <c r="DF141" t="s">
+        <v>1167</v>
+      </c>
+      <c r="DG141">
+        <v>1</v>
+      </c>
+      <c r="DH141">
+        <v>1</v>
+      </c>
+      <c r="DI141">
+        <v>1</v>
+      </c>
+      <c r="DJ141">
+        <v>1</v>
+      </c>
+      <c r="DK141">
+        <v>1</v>
+      </c>
+      <c r="DL141">
+        <v>1</v>
+      </c>
+      <c r="DM141">
+        <v>1</v>
+      </c>
+      <c r="DN141">
+        <v>1</v>
+      </c>
+      <c r="DO141">
+        <v>1</v>
+      </c>
+      <c r="DP141" t="s">
+        <v>732</v>
+      </c>
+      <c r="EI141">
+        <v>2</v>
+      </c>
+      <c r="EK141">
+        <v>2</v>
+      </c>
+      <c r="EM141">
+        <v>4</v>
+      </c>
+      <c r="SD141" s="1"/>
+      <c r="UH141" t="s">
+        <v>2779</v>
+      </c>
+      <c r="ZL141" s="1"/>
+      <c r="ADO141" s="1"/>
+      <c r="ADW141" s="1"/>
+      <c r="AEA141" s="1"/>
+      <c r="AEY141">
+        <v>893713519</v>
+      </c>
+      <c r="AEZ141" t="s">
+        <v>2780</v>
+      </c>
+      <c r="AFA141" s="1">
+        <v>46309.725949074083</v>
+      </c>
+      <c r="AFC141" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE141" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF141" t="s">
+        <v>2781</v>
+      </c>
+      <c r="AFG141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B142" t="s">
+        <v>951</v>
+      </c>
+      <c r="D142" t="s">
+        <v>589</v>
+      </c>
+      <c r="E142" t="s">
+        <v>752</v>
+      </c>
+      <c r="N142" t="s">
+        <v>1160</v>
+      </c>
+      <c r="EN142" t="s">
+        <v>754</v>
+      </c>
+      <c r="FT142">
+        <v>153</v>
+      </c>
+      <c r="FU142">
+        <v>178</v>
+      </c>
+      <c r="FV142">
+        <v>8</v>
+      </c>
+      <c r="FW142">
+        <v>7</v>
+      </c>
+      <c r="FY142">
+        <v>45</v>
+      </c>
+      <c r="FZ142">
+        <v>70</v>
+      </c>
+      <c r="GA142">
+        <v>2</v>
+      </c>
+      <c r="GB142">
+        <v>2</v>
+      </c>
+      <c r="GD142">
+        <v>54</v>
+      </c>
+      <c r="GE142">
+        <v>63</v>
+      </c>
+      <c r="GF142">
+        <v>2</v>
+      </c>
+      <c r="GG142">
+        <v>4</v>
+      </c>
+      <c r="GI142">
+        <v>8</v>
+      </c>
+      <c r="GJ142">
+        <v>6</v>
+      </c>
+      <c r="GK142">
+        <v>0</v>
+      </c>
+      <c r="GL142">
+        <v>0</v>
+      </c>
+      <c r="GN142">
+        <v>2</v>
+      </c>
+      <c r="GO142">
+        <v>4</v>
+      </c>
+      <c r="GP142">
+        <v>0</v>
+      </c>
+      <c r="GQ142">
+        <v>0</v>
+      </c>
+      <c r="GR142" t="s">
+        <v>2782</v>
+      </c>
+      <c r="GS142">
+        <v>1</v>
+      </c>
+      <c r="GT142">
+        <v>0</v>
+      </c>
+      <c r="GU142">
+        <v>0</v>
+      </c>
+      <c r="GV142">
+        <v>1</v>
+      </c>
+      <c r="GW142">
+        <v>1</v>
+      </c>
+      <c r="GX142">
+        <v>1</v>
+      </c>
+      <c r="GY142">
+        <v>1</v>
+      </c>
+      <c r="GZ142" t="s">
+        <v>2783</v>
+      </c>
+      <c r="HA142">
+        <v>1</v>
+      </c>
+      <c r="HB142">
+        <v>1</v>
+      </c>
+      <c r="HC142">
+        <v>1</v>
+      </c>
+      <c r="HD142">
+        <v>0</v>
+      </c>
+      <c r="HE142">
+        <v>0</v>
+      </c>
+      <c r="HG142" t="s">
+        <v>711</v>
+      </c>
+      <c r="HH142" t="s">
+        <v>2784</v>
+      </c>
+      <c r="HI142" t="s">
+        <v>711</v>
+      </c>
+      <c r="HJ142" t="s">
+        <v>732</v>
+      </c>
+      <c r="HL142" t="s">
+        <v>711</v>
+      </c>
+      <c r="HM142" t="s">
+        <v>2785</v>
+      </c>
+      <c r="HT142" t="s">
+        <v>766</v>
+      </c>
+      <c r="HU142">
+        <v>42</v>
+      </c>
+      <c r="HV142" t="s">
+        <v>2786</v>
+      </c>
+      <c r="HX142" t="s">
+        <v>766</v>
+      </c>
+      <c r="HY142">
+        <v>32</v>
+      </c>
+      <c r="HZ142" t="s">
+        <v>2787</v>
+      </c>
+      <c r="IB142" t="s">
+        <v>766</v>
+      </c>
+      <c r="IC142">
+        <v>53</v>
+      </c>
+      <c r="ID142" t="s">
+        <v>2788</v>
+      </c>
+      <c r="IF142" t="s">
+        <v>766</v>
+      </c>
+      <c r="IG142">
+        <v>68</v>
+      </c>
+      <c r="IH142" t="s">
+        <v>2789</v>
+      </c>
+      <c r="IJ142" t="s">
+        <v>766</v>
+      </c>
+      <c r="IK142">
+        <v>25</v>
+      </c>
+      <c r="IL142" t="s">
+        <v>2790</v>
+      </c>
+      <c r="IV142" t="s">
+        <v>835</v>
+      </c>
+      <c r="IW142" t="s">
+        <v>769</v>
+      </c>
+      <c r="IX142" t="s">
+        <v>2791</v>
+      </c>
+      <c r="IY142" t="s">
+        <v>836</v>
+      </c>
+      <c r="IZ142" t="s">
+        <v>2792</v>
+      </c>
+      <c r="JA142" t="s">
+        <v>716</v>
+      </c>
+      <c r="JC142" t="s">
+        <v>835</v>
+      </c>
+      <c r="JD142" t="s">
+        <v>769</v>
+      </c>
+      <c r="JE142" t="s">
+        <v>2793</v>
+      </c>
+      <c r="JF142" t="s">
+        <v>836</v>
+      </c>
+      <c r="JG142" t="s">
+        <v>2794</v>
+      </c>
+      <c r="JH142" t="s">
+        <v>720</v>
+      </c>
+      <c r="JJ142" t="s">
+        <v>835</v>
+      </c>
+      <c r="JK142" t="s">
+        <v>879</v>
+      </c>
+      <c r="JL142" t="s">
+        <v>2795</v>
+      </c>
+      <c r="JM142" t="s">
+        <v>836</v>
+      </c>
+      <c r="JN142" t="s">
+        <v>2796</v>
+      </c>
+      <c r="JO142" t="s">
+        <v>716</v>
+      </c>
+      <c r="JQ142" t="s">
+        <v>835</v>
+      </c>
+      <c r="JR142" t="s">
+        <v>769</v>
+      </c>
+      <c r="JS142" t="s">
+        <v>2797</v>
+      </c>
+      <c r="JT142" t="s">
+        <v>836</v>
+      </c>
+      <c r="JU142" t="s">
+        <v>2798</v>
+      </c>
+      <c r="JV142" t="s">
+        <v>720</v>
+      </c>
+      <c r="JX142" t="s">
+        <v>768</v>
+      </c>
+      <c r="JY142" t="s">
+        <v>769</v>
+      </c>
+      <c r="JZ142" t="s">
+        <v>2799</v>
+      </c>
+      <c r="KA142" t="s">
+        <v>836</v>
+      </c>
+      <c r="KB142" t="s">
+        <v>2800</v>
+      </c>
+      <c r="KC142" t="s">
+        <v>720</v>
+      </c>
+      <c r="KE142" t="s">
+        <v>835</v>
+      </c>
+      <c r="KF142" t="s">
+        <v>1143</v>
+      </c>
+      <c r="KG142" t="s">
+        <v>2801</v>
+      </c>
+      <c r="KH142" t="s">
+        <v>836</v>
+      </c>
+      <c r="KI142" t="s">
+        <v>2802</v>
+      </c>
+      <c r="KJ142" t="s">
+        <v>716</v>
+      </c>
+      <c r="KK142" t="s">
+        <v>706</v>
+      </c>
+      <c r="KL142">
+        <v>0</v>
+      </c>
+      <c r="KM142">
+        <v>0</v>
+      </c>
+      <c r="KN142">
+        <v>0</v>
+      </c>
+      <c r="KO142">
+        <v>1</v>
+      </c>
+      <c r="KP142">
+        <v>0</v>
+      </c>
+      <c r="KR142" t="s">
+        <v>2803</v>
+      </c>
+      <c r="KS142" t="s">
+        <v>2804</v>
+      </c>
+      <c r="KT142" t="s">
+        <v>2805</v>
+      </c>
+      <c r="KU142" t="s">
+        <v>2806</v>
+      </c>
+      <c r="NP142">
+        <v>153</v>
+      </c>
+      <c r="NQ142">
+        <v>178</v>
+      </c>
+      <c r="NS142">
+        <v>45</v>
+      </c>
+      <c r="NT142">
+        <v>70</v>
+      </c>
+      <c r="NV142">
+        <v>54</v>
+      </c>
+      <c r="NW142">
+        <v>63</v>
+      </c>
+      <c r="SD142" s="1"/>
+      <c r="UH142" t="s">
+        <v>2807</v>
+      </c>
+      <c r="ZL142" s="1"/>
+      <c r="ADO142" s="1"/>
+      <c r="ADW142" s="1"/>
+      <c r="AEA142" s="1"/>
+      <c r="AEY142">
+        <v>893713537</v>
+      </c>
+      <c r="AEZ142" t="s">
+        <v>2808</v>
+      </c>
+      <c r="AFA142" s="1">
+        <v>46309.725972222222</v>
+      </c>
+      <c r="AFC142" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE142" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF142" t="s">
+        <v>2809</v>
+      </c>
+      <c r="AFG142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B143" t="s">
+        <v>951</v>
+      </c>
+      <c r="D143" t="s">
+        <v>589</v>
+      </c>
+      <c r="E143" t="s">
+        <v>752</v>
+      </c>
+      <c r="N143" t="s">
+        <v>1160</v>
+      </c>
+      <c r="EN143" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO143">
+        <v>468</v>
+      </c>
+      <c r="EP143">
+        <v>474</v>
+      </c>
+      <c r="EQ143" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER143" t="s">
+        <v>1157</v>
+      </c>
+      <c r="ES143">
+        <v>0</v>
+      </c>
+      <c r="ET143">
+        <v>1</v>
+      </c>
+      <c r="EU143">
+        <v>0</v>
+      </c>
+      <c r="EV143">
+        <v>1</v>
+      </c>
+      <c r="EW143">
+        <v>0</v>
+      </c>
+      <c r="EX143">
+        <v>0</v>
+      </c>
+      <c r="EZ143" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA143">
+        <v>30</v>
+      </c>
+      <c r="FB143" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC143">
+        <v>1</v>
+      </c>
+      <c r="FD143">
+        <v>1</v>
+      </c>
+      <c r="FE143">
+        <v>1</v>
+      </c>
+      <c r="FF143" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG143" t="s">
+        <v>2810</v>
+      </c>
+      <c r="FH143" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP143">
+        <v>153</v>
+      </c>
+      <c r="NQ143">
+        <v>177</v>
+      </c>
+      <c r="NS143">
+        <v>46</v>
+      </c>
+      <c r="NT143">
+        <v>67</v>
+      </c>
+      <c r="NV143">
+        <v>54</v>
+      </c>
+      <c r="NW143">
+        <v>63</v>
+      </c>
+      <c r="SD143" s="1"/>
+      <c r="UH143" t="s">
+        <v>1149</v>
+      </c>
+      <c r="ZL143" s="1"/>
+      <c r="ADO143" s="1"/>
+      <c r="ADW143" s="1"/>
+      <c r="AEA143" s="1"/>
+      <c r="AEY143">
+        <v>893713547</v>
+      </c>
+      <c r="AEZ143" t="s">
+        <v>2811</v>
+      </c>
+      <c r="AFA143" s="1">
+        <v>46309.725983796299</v>
+      </c>
+      <c r="AFC143" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE143" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF143" t="s">
+        <v>2812</v>
+      </c>
+      <c r="AFG143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B144" t="s">
+        <v>951</v>
+      </c>
+      <c r="D144" t="s">
+        <v>589</v>
+      </c>
+      <c r="E144" t="s">
+        <v>1910</v>
+      </c>
+      <c r="N144" t="s">
+        <v>1160</v>
+      </c>
+      <c r="NX144" t="s">
+        <v>2813</v>
+      </c>
+      <c r="NY144" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ144" t="s">
+        <v>2814</v>
+      </c>
+      <c r="OA144" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS144">
+        <v>13</v>
+      </c>
+      <c r="OT144" t="s">
+        <v>860</v>
+      </c>
+      <c r="OV144">
+        <v>2</v>
+      </c>
+      <c r="OW144" t="s">
+        <v>2637</v>
+      </c>
+      <c r="OY144">
+        <v>20</v>
+      </c>
+      <c r="OZ144" t="s">
+        <v>827</v>
+      </c>
+      <c r="PB144">
+        <v>14</v>
+      </c>
+      <c r="PC144" t="s">
+        <v>760</v>
+      </c>
+      <c r="PE144">
+        <v>1</v>
+      </c>
+      <c r="PF144" t="s">
+        <v>831</v>
+      </c>
+      <c r="PH144">
+        <v>2</v>
+      </c>
+      <c r="PI144" t="s">
+        <v>822</v>
+      </c>
+      <c r="PJ144" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL144" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN144" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO144" t="s">
+        <v>2043</v>
+      </c>
+      <c r="PQ144" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR144" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS144">
+        <v>0</v>
+      </c>
+      <c r="PT144">
+        <v>0</v>
+      </c>
+      <c r="PU144">
+        <v>1</v>
+      </c>
+      <c r="PV144" t="s">
+        <v>2815</v>
+      </c>
+      <c r="PW144" t="s">
+        <v>2046</v>
+      </c>
+      <c r="PX144">
+        <v>0</v>
+      </c>
+      <c r="PY144">
+        <v>0</v>
+      </c>
+      <c r="PZ144">
+        <v>0</v>
+      </c>
+      <c r="QA144">
+        <v>1</v>
+      </c>
+      <c r="QJ144" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QK144" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QL144" t="s">
+        <v>1929</v>
+      </c>
+      <c r="QM144" t="s">
+        <v>2816</v>
+      </c>
+      <c r="QN144" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP144" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ144" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QR144" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS144" t="s">
+        <v>2817</v>
+      </c>
+      <c r="QT144" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV144" t="s">
+        <v>2141</v>
+      </c>
+      <c r="QW144" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX144" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY144" t="s">
+        <v>2818</v>
+      </c>
+      <c r="QZ144" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA144" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB144" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC144" t="s">
+        <v>2127</v>
+      </c>
+      <c r="RD144">
+        <v>1</v>
+      </c>
+      <c r="RE144">
+        <v>1</v>
+      </c>
+      <c r="RF144">
+        <v>1</v>
+      </c>
+      <c r="RG144">
+        <v>1</v>
+      </c>
+      <c r="RH144">
+        <v>0</v>
+      </c>
+      <c r="RJ144" t="s">
+        <v>2051</v>
+      </c>
+      <c r="RK144">
+        <v>1</v>
+      </c>
+      <c r="RL144">
+        <v>0</v>
+      </c>
+      <c r="RM144">
+        <v>0</v>
+      </c>
+      <c r="RO144" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP144" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ144" t="s">
+        <v>2819</v>
+      </c>
+      <c r="RR144" t="s">
+        <v>2820</v>
+      </c>
+      <c r="RS144" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT144" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY144" t="s">
+        <v>2821</v>
+      </c>
+      <c r="RZ144" t="s">
+        <v>2822</v>
+      </c>
+      <c r="SA144" t="s">
+        <v>2823</v>
+      </c>
+      <c r="SB144" t="s">
+        <v>711</v>
+      </c>
+      <c r="SC144" t="s">
+        <v>2824</v>
+      </c>
+      <c r="SD144" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH144" t="s">
+        <v>2825</v>
+      </c>
+      <c r="ZL144" s="1"/>
+      <c r="ADO144" s="1"/>
+      <c r="ADW144" s="1"/>
+      <c r="AEA144" s="1"/>
+      <c r="AEY144">
+        <v>893713559</v>
+      </c>
+      <c r="AEZ144" t="s">
+        <v>2826</v>
+      </c>
+      <c r="AFA144" s="1">
+        <v>46309.725983796299</v>
+      </c>
+      <c r="AFC144" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE144" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF144" t="s">
+        <v>2827</v>
+      </c>
+      <c r="AFG144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B145" t="s">
+        <v>951</v>
+      </c>
+      <c r="D145" t="s">
+        <v>589</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1910</v>
+      </c>
+      <c r="N145" t="s">
+        <v>1160</v>
+      </c>
+      <c r="NX145" t="s">
+        <v>2828</v>
+      </c>
+      <c r="NY145" t="s">
+        <v>2040</v>
+      </c>
+      <c r="OA145" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS145">
+        <v>26</v>
+      </c>
+      <c r="OT145" t="s">
+        <v>860</v>
+      </c>
+      <c r="OV145">
+        <v>6</v>
+      </c>
+      <c r="OW145" t="s">
+        <v>2241</v>
+      </c>
+      <c r="OY145">
+        <v>18</v>
+      </c>
+      <c r="OZ145" t="s">
+        <v>2829</v>
+      </c>
+      <c r="PB145">
+        <v>16</v>
+      </c>
+      <c r="PC145" t="s">
+        <v>2204</v>
+      </c>
+      <c r="PE145">
+        <v>2</v>
+      </c>
+      <c r="PF145" t="s">
+        <v>1916</v>
+      </c>
+      <c r="PH145">
+        <v>1</v>
+      </c>
+      <c r="PI145" t="s">
+        <v>834</v>
+      </c>
+      <c r="PJ145" t="s">
+        <v>1918</v>
+      </c>
+      <c r="PL145" t="s">
+        <v>732</v>
+      </c>
+      <c r="PN145" t="s">
+        <v>711</v>
+      </c>
+      <c r="PO145" t="s">
+        <v>2043</v>
+      </c>
+      <c r="PQ145" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR145" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS145">
+        <v>0</v>
+      </c>
+      <c r="PT145">
+        <v>0</v>
+      </c>
+      <c r="PU145">
+        <v>1</v>
+      </c>
+      <c r="PV145" t="s">
+        <v>2830</v>
+      </c>
+      <c r="PW145" t="s">
+        <v>2187</v>
+      </c>
+      <c r="PX145">
+        <v>1</v>
+      </c>
+      <c r="PY145">
+        <v>0</v>
+      </c>
+      <c r="PZ145">
+        <v>0</v>
+      </c>
+      <c r="QA145">
+        <v>1</v>
+      </c>
+      <c r="QJ145" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK145" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL145" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM145" t="s">
+        <v>2831</v>
+      </c>
+      <c r="QN145" t="s">
+        <v>716</v>
+      </c>
+      <c r="QP145" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ145" t="s">
+        <v>1947</v>
+      </c>
+      <c r="QR145" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS145" t="s">
+        <v>2832</v>
+      </c>
+      <c r="QT145" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV145" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW145" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QX145" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY145" t="s">
+        <v>2833</v>
+      </c>
+      <c r="QZ145" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA145" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB145" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC145" t="s">
+        <v>2834</v>
+      </c>
+      <c r="RD145">
+        <v>1</v>
+      </c>
+      <c r="RE145">
+        <v>1</v>
+      </c>
+      <c r="RF145">
+        <v>1</v>
+      </c>
+      <c r="RG145">
+        <v>1</v>
+      </c>
+      <c r="RH145">
+        <v>1</v>
+      </c>
+      <c r="RI145" t="s">
+        <v>2835</v>
+      </c>
+      <c r="RJ145" t="s">
+        <v>2051</v>
+      </c>
+      <c r="RK145">
+        <v>1</v>
+      </c>
+      <c r="RL145">
+        <v>0</v>
+      </c>
+      <c r="RM145">
+        <v>0</v>
+      </c>
+      <c r="RO145" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP145" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ145" t="s">
+        <v>1149</v>
+      </c>
+      <c r="RR145" t="s">
+        <v>2820</v>
+      </c>
+      <c r="RS145" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT145" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY145" t="s">
+        <v>2836</v>
+      </c>
+      <c r="RZ145" t="s">
+        <v>2837</v>
+      </c>
+      <c r="SA145" t="s">
+        <v>1149</v>
+      </c>
+      <c r="SB145" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD145" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH145" t="s">
+        <v>2838</v>
+      </c>
+      <c r="ZL145" s="1"/>
+      <c r="ADO145" s="1"/>
+      <c r="ADW145" s="1"/>
+      <c r="AEA145" s="1"/>
+      <c r="AEY145">
+        <v>893713568</v>
+      </c>
+      <c r="AEZ145" t="s">
+        <v>2839</v>
+      </c>
+      <c r="AFA145" s="1">
+        <v>46309.725995370369</v>
+      </c>
+      <c r="AFC145" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE145" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AFF145" t="s">
+        <v>2840</v>
+      </c>
+      <c r="AFG145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D146" t="s">
+        <v>596</v>
+      </c>
+      <c r="E146" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K146" t="s">
+        <v>2304</v>
+      </c>
+      <c r="NX146" t="s">
+        <v>2841</v>
+      </c>
+      <c r="NY146" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ146" t="s">
+        <v>2842</v>
+      </c>
+      <c r="OA146" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS146">
+        <v>36</v>
+      </c>
+      <c r="OT146" t="s">
+        <v>755</v>
+      </c>
+      <c r="OV146">
+        <v>35</v>
+      </c>
+      <c r="OW146" t="s">
+        <v>755</v>
+      </c>
+      <c r="OY146">
+        <v>8</v>
+      </c>
+      <c r="OZ146" t="s">
+        <v>755</v>
+      </c>
+      <c r="PB146">
+        <v>15</v>
+      </c>
+      <c r="PC146" t="s">
+        <v>755</v>
+      </c>
+      <c r="PE146">
+        <v>0</v>
+      </c>
+      <c r="PF146" t="s">
+        <v>755</v>
+      </c>
+      <c r="PH146">
+        <v>0</v>
+      </c>
+      <c r="PI146" t="s">
+        <v>755</v>
+      </c>
+      <c r="PJ146" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL146" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM146" t="s">
+        <v>2843</v>
+      </c>
+      <c r="PN146" t="s">
+        <v>732</v>
+      </c>
+      <c r="PO146" t="s">
+        <v>1968</v>
+      </c>
+      <c r="PQ146" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR146" t="s">
+        <v>2044</v>
+      </c>
+      <c r="PS146">
+        <v>0</v>
+      </c>
+      <c r="PT146">
+        <v>0</v>
+      </c>
+      <c r="PU146">
+        <v>1</v>
+      </c>
+      <c r="PV146" t="s">
+        <v>2844</v>
+      </c>
+      <c r="PW146" t="s">
+        <v>2378</v>
+      </c>
+      <c r="PX146">
+        <v>0</v>
+      </c>
+      <c r="PY146">
+        <v>0</v>
+      </c>
+      <c r="PZ146">
+        <v>1</v>
+      </c>
+      <c r="QA146">
+        <v>0</v>
+      </c>
+      <c r="QJ146" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QK146" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QL146" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM146" t="s">
+        <v>2845</v>
+      </c>
+      <c r="QN146" t="s">
+        <v>720</v>
+      </c>
+      <c r="QP146" t="s">
+        <v>1946</v>
+      </c>
+      <c r="QQ146" t="s">
+        <v>1928</v>
+      </c>
+      <c r="QR146" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS146" t="s">
+        <v>2845</v>
+      </c>
+      <c r="QT146" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV146" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QW146" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX146" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY146" t="s">
+        <v>2845</v>
+      </c>
+      <c r="QZ146" t="s">
+        <v>716</v>
+      </c>
+      <c r="RA146" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB146" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC146" t="s">
+        <v>2846</v>
+      </c>
+      <c r="RD146">
+        <v>0</v>
+      </c>
+      <c r="RE146">
+        <v>0</v>
+      </c>
+      <c r="RF146">
+        <v>1</v>
+      </c>
+      <c r="RG146">
+        <v>1</v>
+      </c>
+      <c r="RH146">
+        <v>0</v>
+      </c>
+      <c r="RJ146" t="s">
+        <v>2108</v>
+      </c>
+      <c r="RK146">
+        <v>1</v>
+      </c>
+      <c r="RL146">
+        <v>0</v>
+      </c>
+      <c r="RM146">
+        <v>1</v>
+      </c>
+      <c r="RN146" t="s">
+        <v>2755</v>
+      </c>
+      <c r="RO146" t="s">
+        <v>2052</v>
+      </c>
+      <c r="RP146" t="s">
+        <v>711</v>
+      </c>
+      <c r="RQ146" t="s">
+        <v>2756</v>
+      </c>
+      <c r="RR146" t="s">
+        <v>2847</v>
+      </c>
+      <c r="RS146" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT146" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY146" t="s">
+        <v>2848</v>
+      </c>
+      <c r="RZ146" t="s">
+        <v>2849</v>
+      </c>
+      <c r="SA146" t="s">
+        <v>2850</v>
+      </c>
+      <c r="SB146" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD146" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH146" t="s">
+        <v>2851</v>
+      </c>
+      <c r="ZL146" s="1"/>
+      <c r="ADO146" s="1"/>
+      <c r="ADW146" s="1"/>
+      <c r="AEA146" s="1"/>
+      <c r="AEY146">
+        <v>893717096</v>
+      </c>
+      <c r="AEZ146" t="s">
+        <v>2852</v>
+      </c>
+      <c r="AFA146" s="1">
+        <v>46309.728692129633</v>
+      </c>
+      <c r="AFC146" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE146" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF146" t="s">
+        <v>2853</v>
+      </c>
+      <c r="AFG146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D147" t="s">
+        <v>596</v>
+      </c>
+      <c r="E147" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K147" t="s">
+        <v>2304</v>
+      </c>
+      <c r="NX147" t="s">
+        <v>2854</v>
+      </c>
+      <c r="NY147" t="s">
+        <v>1912</v>
+      </c>
+      <c r="NZ147" t="s">
+        <v>2842</v>
+      </c>
+      <c r="OA147" t="s">
+        <v>732</v>
+      </c>
+      <c r="OS147">
+        <v>42</v>
+      </c>
+      <c r="OT147" t="s">
+        <v>755</v>
+      </c>
+      <c r="OV147">
+        <v>18</v>
+      </c>
+      <c r="OW147" t="s">
+        <v>755</v>
+      </c>
+      <c r="OY147">
+        <v>15</v>
+      </c>
+      <c r="OZ147" t="s">
+        <v>755</v>
+      </c>
+      <c r="PB147">
+        <v>20</v>
+      </c>
+      <c r="PC147" t="s">
+        <v>755</v>
+      </c>
+      <c r="PE147">
+        <v>0</v>
+      </c>
+      <c r="PF147" t="s">
+        <v>755</v>
+      </c>
+      <c r="PH147">
+        <v>2</v>
+      </c>
+      <c r="PI147" t="s">
+        <v>755</v>
+      </c>
+      <c r="PJ147" t="s">
+        <v>2374</v>
+      </c>
+      <c r="PL147" t="s">
+        <v>711</v>
+      </c>
+      <c r="PM147" t="s">
+        <v>2855</v>
+      </c>
+      <c r="PN147" t="s">
+        <v>732</v>
+      </c>
+      <c r="PO147" t="s">
+        <v>706</v>
+      </c>
+      <c r="PP147" t="s">
+        <v>2856</v>
+      </c>
+      <c r="PQ147" t="s">
+        <v>1921</v>
+      </c>
+      <c r="PR147" t="s">
+        <v>2064</v>
+      </c>
+      <c r="PS147">
+        <v>1</v>
+      </c>
+      <c r="PT147">
+        <v>1</v>
+      </c>
+      <c r="PU147">
+        <v>0</v>
+      </c>
+      <c r="PW147" t="s">
+        <v>1922</v>
+      </c>
+      <c r="PX147">
+        <v>1</v>
+      </c>
+      <c r="PY147">
+        <v>0</v>
+      </c>
+      <c r="PZ147">
+        <v>0</v>
+      </c>
+      <c r="QA147">
+        <v>0</v>
+      </c>
+      <c r="QJ147" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QK147" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QL147" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QM147" t="s">
+        <v>711</v>
+      </c>
+      <c r="QN147" t="s">
+        <v>720</v>
+      </c>
+      <c r="QP147" t="s">
+        <v>1927</v>
+      </c>
+      <c r="QQ147" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QR147" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QS147" t="s">
+        <v>711</v>
+      </c>
+      <c r="QT147" t="s">
+        <v>716</v>
+      </c>
+      <c r="QV147" t="s">
+        <v>1923</v>
+      </c>
+      <c r="QW147" t="s">
+        <v>1924</v>
+      </c>
+      <c r="QX147" t="s">
+        <v>1925</v>
+      </c>
+      <c r="QY147" t="s">
+        <v>711</v>
+      </c>
+      <c r="QZ147" t="s">
+        <v>720</v>
+      </c>
+      <c r="RA147" t="s">
+        <v>711</v>
+      </c>
+      <c r="RB147" t="s">
+        <v>711</v>
+      </c>
+      <c r="RC147" t="s">
+        <v>2846</v>
+      </c>
+      <c r="RD147">
+        <v>0</v>
+      </c>
+      <c r="RE147">
+        <v>0</v>
+      </c>
+      <c r="RF147">
+        <v>1</v>
+      </c>
+      <c r="RG147">
+        <v>1</v>
+      </c>
+      <c r="RH147">
+        <v>0</v>
+      </c>
+      <c r="RJ147" t="s">
+        <v>2070</v>
+      </c>
+      <c r="RK147">
+        <v>1</v>
+      </c>
+      <c r="RL147">
+        <v>1</v>
+      </c>
+      <c r="RM147">
+        <v>0</v>
+      </c>
+      <c r="RO147" t="s">
+        <v>1932</v>
+      </c>
+      <c r="RP147" t="s">
+        <v>732</v>
+      </c>
+      <c r="RQ147" t="s">
+        <v>2756</v>
+      </c>
+      <c r="RR147" t="s">
+        <v>2857</v>
+      </c>
+      <c r="RS147" t="s">
+        <v>711</v>
+      </c>
+      <c r="RT147" t="s">
+        <v>732</v>
+      </c>
+      <c r="RY147" t="s">
+        <v>2858</v>
+      </c>
+      <c r="RZ147" t="s">
+        <v>2859</v>
+      </c>
+      <c r="SA147" t="s">
+        <v>2675</v>
+      </c>
+      <c r="SB147" t="s">
+        <v>732</v>
+      </c>
+      <c r="SD147" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="UH147" t="s">
+        <v>2860</v>
+      </c>
+      <c r="ZL147" s="1"/>
+      <c r="ADO147" s="1"/>
+      <c r="ADW147" s="1"/>
+      <c r="AEA147" s="1"/>
+      <c r="AEY147">
+        <v>893725481</v>
+      </c>
+      <c r="AEZ147" t="s">
+        <v>2861</v>
+      </c>
+      <c r="AFA147" s="1">
+        <v>46309.735300925917</v>
+      </c>
+      <c r="AFC147" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE147" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF147" t="s">
+        <v>2862</v>
+      </c>
+      <c r="AFG147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B148" t="s">
+        <v>858</v>
+      </c>
+      <c r="D148" t="s">
+        <v>597</v>
+      </c>
+      <c r="E148" t="s">
+        <v>752</v>
+      </c>
+      <c r="M148" t="s">
+        <v>2863</v>
+      </c>
+      <c r="EN148" t="s">
+        <v>966</v>
+      </c>
+      <c r="EO148">
+        <v>777</v>
+      </c>
+      <c r="EP148">
+        <v>589</v>
+      </c>
+      <c r="EQ148" t="s">
+        <v>711</v>
+      </c>
+      <c r="ER148" t="s">
+        <v>1400</v>
+      </c>
+      <c r="ES148">
+        <v>1</v>
+      </c>
+      <c r="ET148">
+        <v>0</v>
+      </c>
+      <c r="EU148">
+        <v>0</v>
+      </c>
+      <c r="EV148">
+        <v>0</v>
+      </c>
+      <c r="EW148">
+        <v>1</v>
+      </c>
+      <c r="EX148">
+        <v>0</v>
+      </c>
+      <c r="EZ148" t="s">
+        <v>711</v>
+      </c>
+      <c r="FA148">
+        <v>50</v>
+      </c>
+      <c r="FB148" t="s">
+        <v>967</v>
+      </c>
+      <c r="FC148">
+        <v>1</v>
+      </c>
+      <c r="FD148">
+        <v>1</v>
+      </c>
+      <c r="FE148">
+        <v>1</v>
+      </c>
+      <c r="FF148" t="s">
+        <v>711</v>
+      </c>
+      <c r="FG148" t="s">
+        <v>2864</v>
+      </c>
+      <c r="FH148" t="s">
+        <v>732</v>
+      </c>
+      <c r="NP148">
+        <v>317</v>
+      </c>
+      <c r="NQ148">
+        <v>241</v>
+      </c>
+      <c r="NS148">
+        <v>296</v>
+      </c>
+      <c r="NT148">
+        <v>274</v>
+      </c>
+      <c r="NV148">
+        <v>259</v>
+      </c>
+      <c r="NW148">
+        <v>193</v>
+      </c>
+      <c r="SD148" s="1"/>
+      <c r="UH148" t="s">
+        <v>2865</v>
+      </c>
+      <c r="ZL148" s="1"/>
+      <c r="ADO148" s="1"/>
+      <c r="ADW148" s="1"/>
+      <c r="AEA148" s="1"/>
+      <c r="AEY148">
+        <v>893731574</v>
+      </c>
+      <c r="AEZ148" t="s">
+        <v>2866</v>
+      </c>
+      <c r="AFA148" s="1">
+        <v>46309.739849537043</v>
+      </c>
+      <c r="AFC148" t="s">
+        <v>734</v>
+      </c>
+      <c r="AFE148" t="s">
+        <v>2522</v>
+      </c>
+      <c r="AFF148" t="s">
+        <v>2867</v>
+      </c>
+      <c r="AFG148">
+        <v>147</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5D5348F-C574-D943-B5A3-0CD151B9C2F1}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="11_38172402C256EF51DEA7AD90F45CC233B0A94B26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C304482-B3F4-D44D-8812-598A95A5E5C1}"/>
   <bookViews>
-    <workbookView xWindow="3500" yWindow="1300" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3500" yWindow="660" windowWidth="22640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nutribus 2.0 Activity" sheetId="1" r:id="rId1"/>
@@ -8706,7 +8706,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}" name="Table1" displayName="Table1" ref="A1:AFG148" totalsRowShown="0">
-  <autoFilter ref="A1:AFG148" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}"/>
+  <autoFilter ref="A1:AFG148" xr:uid="{654188A1-E11E-0A4B-B8C6-775AEDEA3813}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Kotido"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{F730B1FF-9535-D845-A274-5847CF805C90}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{D1FFB7C4-D1E3-6049-AAA1-7A61F668AF9D}" name="Coordinator Name"/>
@@ -12936,7 +12942,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="2" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>46297</v>
       </c>
@@ -13268,7 +13274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>46297</v>
       </c>
@@ -13569,7 +13575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>46298</v>
       </c>
@@ -13904,7 +13910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>46298</v>
       </c>
@@ -14607,7 +14613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>46295</v>
       </c>
@@ -14975,7 +14981,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>46298</v>
       </c>
@@ -15307,7 +15313,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46296</v>
       </c>
@@ -15657,7 +15663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46298</v>
       </c>
@@ -15992,7 +15998,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46298</v>
       </c>
@@ -16327,7 +16333,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46298</v>
       </c>
@@ -16476,7 +16482,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>46301</v>
       </c>
@@ -16586,7 +16592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>46301</v>
       </c>
@@ -16693,7 +16699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>46183</v>
       </c>
@@ -17025,7 +17031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>46301</v>
       </c>
@@ -17349,7 +17355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>46302</v>
       </c>
@@ -17456,7 +17462,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>46302</v>
       </c>
@@ -17602,7 +17608,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>46302</v>
       </c>
@@ -17816,7 +17822,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>46296</v>
       </c>
@@ -17935,7 +17941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>46303</v>
       </c>
@@ -18300,7 +18306,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>46299</v>
       </c>
@@ -18665,7 +18671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>46305</v>
       </c>
@@ -18811,7 +18817,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>46297</v>
       </c>
@@ -19143,7 +19149,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>46326</v>
       </c>
@@ -19508,7 +19514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>46297</v>
       </c>
@@ -19867,7 +19873,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>46302</v>
       </c>
@@ -20244,7 +20250,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>46296</v>
       </c>
@@ -20363,7 +20369,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>46297</v>
       </c>
@@ -20722,7 +20728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>46302</v>
       </c>
@@ -21090,7 +21096,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>46297</v>
       </c>
@@ -21209,7 +21215,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>46301</v>
       </c>
@@ -21574,7 +21580,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>46301</v>
       </c>
@@ -21693,7 +21699,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>46301</v>
       </c>
@@ -22055,7 +22061,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>46295</v>
       </c>
@@ -22420,7 +22426,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>46302</v>
       </c>
@@ -22782,7 +22788,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>46302</v>
       </c>
@@ -22910,7 +22916,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>46301</v>
       </c>
@@ -23035,7 +23041,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>46301</v>
       </c>
@@ -23400,7 +23406,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>46301</v>
       </c>
@@ -23522,7 +23528,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>46301</v>
       </c>
@@ -24252,7 +24258,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46302</v>
       </c>
@@ -24589,7 +24595,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46303</v>
       </c>
@@ -24959,7 +24965,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>46303</v>
       </c>
@@ -25083,7 +25089,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46301</v>
       </c>
@@ -25210,7 +25216,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>46301</v>
       </c>
@@ -25337,7 +25343,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>46303</v>
       </c>
@@ -25707,7 +25713,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>46303</v>
       </c>
@@ -26049,7 +26055,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>46303</v>
       </c>
@@ -26425,7 +26431,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>46307</v>
       </c>
@@ -26561,7 +26567,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>46307</v>
       </c>
@@ -26895,7 +26901,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>46303</v>
       </c>
@@ -27265,7 +27271,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>46303</v>
       </c>
@@ -27629,7 +27635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>46307</v>
       </c>
@@ -27765,7 +27771,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>46307</v>
       </c>
@@ -28129,7 +28135,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>46307</v>
       </c>
@@ -28253,7 +28259,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>46307</v>
       </c>
@@ -28587,7 +28593,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>46307</v>
       </c>
@@ -28954,7 +28960,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>46307</v>
       </c>
@@ -29503,7 +29509,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>46303</v>
       </c>
@@ -29630,7 +29636,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>46307</v>
       </c>
@@ -30003,7 +30009,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>46303</v>
       </c>
@@ -30130,7 +30136,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>46307</v>
       </c>
@@ -30500,7 +30506,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>46307</v>
       </c>
@@ -30743,7 +30749,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>46307</v>
       </c>
@@ -30989,7 +30995,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>46307</v>
       </c>
@@ -31235,7 +31241,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>46303</v>
       </c>
@@ -31362,7 +31368,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>46307</v>
       </c>
@@ -31738,7 +31744,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>46307</v>
       </c>
@@ -31844,7 +31850,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>46308</v>
       </c>
@@ -31950,7 +31956,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>46308</v>
       </c>
@@ -32056,7 +32062,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>46308</v>
       </c>
@@ -32162,7 +32168,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>46308</v>
       </c>
@@ -32268,7 +32274,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>46308</v>
       </c>
@@ -32523,7 +32529,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>46308</v>
       </c>
@@ -32775,7 +32781,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>46308</v>
       </c>
@@ -33033,7 +33039,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>46308</v>
       </c>
@@ -33291,7 +33297,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>46308</v>
       </c>
@@ -33549,7 +33555,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>46308</v>
       </c>
@@ -33804,7 +33810,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>46307</v>
       </c>
@@ -33928,7 +33934,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>46307</v>
       </c>
@@ -34186,7 +34192,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>46308</v>
       </c>
@@ -34450,7 +34456,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>46308</v>
       </c>
@@ -34708,7 +34714,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>46308</v>
       </c>
@@ -34966,7 +34972,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>46307</v>
       </c>
@@ -35090,7 +35096,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>46308</v>
       </c>
@@ -35345,7 +35351,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>46308</v>
       </c>
@@ -35469,7 +35475,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>46308</v>
       </c>
@@ -35724,7 +35730,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>46307</v>
       </c>
@@ -35848,7 +35854,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>46315</v>
       </c>
@@ -36097,7 +36103,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>46308</v>
       </c>
@@ -36221,7 +36227,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>46308</v>
       </c>
@@ -36348,7 +36354,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>46302</v>
       </c>
@@ -36475,7 +36481,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>46308</v>
       </c>
@@ -36848,7 +36854,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>46302</v>
       </c>
@@ -36987,7 +36993,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>46308</v>
       </c>
@@ -37363,7 +37369,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>46308</v>
       </c>
@@ -37660,7 +37666,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>46307</v>
       </c>
@@ -37799,7 +37805,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>46308</v>
       </c>
@@ -38057,7 +38063,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>46307</v>
       </c>
@@ -38196,7 +38202,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>46308</v>
       </c>
@@ -38451,7 +38457,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>46307</v>
       </c>
@@ -38590,7 +38596,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>46308</v>
       </c>
@@ -38875,7 +38881,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>46307</v>
       </c>
@@ -39014,7 +39020,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>46303</v>
       </c>
@@ -39123,7 +39129,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>46304</v>
       </c>
@@ -39229,7 +39235,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>46307</v>
       </c>
@@ -39854,7 +39860,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>46302</v>
       </c>
@@ -39978,7 +39984,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>46308</v>
       </c>
@@ -40348,7 +40354,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>46302</v>
       </c>
@@ -40472,7 +40478,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>46308</v>
       </c>
@@ -40842,7 +40848,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>46309</v>
       </c>
@@ -40966,7 +40972,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>46309</v>
       </c>
@@ -41090,7 +41096,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>46309</v>
       </c>
@@ -41457,7 +41463,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>46301</v>
       </c>
@@ -41581,7 +41587,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>46302</v>
       </c>
@@ -41705,7 +41711,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>46309</v>
       </c>
@@ -42072,7 +42078,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>46309</v>
       </c>
@@ -42566,7 +42572,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>46308</v>
       </c>
@@ -42821,7 +42827,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>46302</v>
       </c>
@@ -42948,7 +42954,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>46309</v>
       </c>
@@ -43324,7 +43330,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>46309</v>
       </c>
@@ -43612,7 +43618,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>46303</v>
       </c>
@@ -43772,7 +43778,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>46309</v>
       </c>
@@ -43878,7 +43884,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>46309</v>
       </c>
@@ -44136,7 +44142,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>46309</v>
       </c>
@@ -44767,7 +44773,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>46309</v>
       </c>
@@ -45022,7 +45028,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>46309</v>
       </c>
@@ -45277,7 +45283,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>46302</v>
       </c>
@@ -45611,7 +45617,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>46302</v>
       </c>
@@ -45981,7 +45987,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>46309</v>
       </c>
@@ -46105,7 +46111,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>46309</v>
       </c>
@@ -46360,7 +46366,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>46309</v>
       </c>
@@ -46612,7 +46618,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>46309</v>
       </c>
@@ -46870,7 +46876,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>46309</v>
       </c>
@@ -47125,7 +47131,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:839" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:839" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>46301</v>
       </c>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_875741B50482FB89CC18BFA3AD4603C54E6094F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9C9FE38-A2B5-024A-AB59-D72034B713E6}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_875741B50482FB89CC18BFA3AD4603C54E6094F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D1CC9B7-7033-D148-A013-7FF9E28617F6}"/>
   <bookViews>
     <workbookView xWindow="3340" yWindow="660" windowWidth="24340" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10849" uniqueCount="3899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11324" uniqueCount="4018">
   <si>
     <t>Date</t>
   </si>
@@ -11717,6 +11717,363 @@
   </si>
   <si>
     <t>uuid:112a6c7d-c1f6-461d-954e-75a81e22e5bc</t>
+  </si>
+  <si>
+    <t>Market place</t>
+  </si>
+  <si>
+    <t>Aleper pius and Nakiru luja</t>
+  </si>
+  <si>
+    <t>Some items are expensive and can not be afforded by all for example honey/sugar</t>
+  </si>
+  <si>
+    <t>Lack of enough money can hinder me to afford this some ingredence</t>
+  </si>
+  <si>
+    <t>Sometimes when the father divtates to not use money for buying what he has not accepted to spend on</t>
+  </si>
+  <si>
+    <t>I will also tell all my women to give egual ratio of food to both children</t>
+  </si>
+  <si>
+    <t>They say the father who provided will first be served then children and later mother</t>
+  </si>
+  <si>
+    <t>Understanding love, from father</t>
+  </si>
+  <si>
+    <t>We will also go and try in our homes,</t>
+  </si>
+  <si>
+    <t>VHTs and LC1</t>
+  </si>
+  <si>
+    <t>The current dry spell has affected the production of this ingredience</t>
+  </si>
+  <si>
+    <t>0284e227-da0c-4065-b872-918e1c47617a</t>
+  </si>
+  <si>
+    <t>uuid:0284e227-da0c-4065-b872-918e1c47617a</t>
+  </si>
+  <si>
+    <t>In front of the headmaster office</t>
+  </si>
+  <si>
+    <t>This went on well</t>
+  </si>
+  <si>
+    <t>c3781d50-afb4-4184-99c4-24e981b317c4</t>
+  </si>
+  <si>
+    <t>uuid:c3781d50-afb4-4184-99c4-24e981b317c4</t>
+  </si>
+  <si>
+    <t>Lokilala</t>
+  </si>
+  <si>
+    <t>Lotipo Rosa</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>why do you add cooking oil in the porriage</t>
+  </si>
+  <si>
+    <t>Vegetables and fruits</t>
+  </si>
+  <si>
+    <t>if monmey was there, I wopul feed mychildren well</t>
+  </si>
+  <si>
+    <t>I will try and add cooking oil if porriage will tase well</t>
+  </si>
+  <si>
+    <t>other sources of energy are scarce</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>chikldren and men are served first</t>
+  </si>
+  <si>
+    <t>some spoecial food for children</t>
+  </si>
+  <si>
+    <t>we shall try and water some vegetables in our homes tosupport feeding.</t>
+  </si>
+  <si>
+    <t>gender rolkes and decision making of feeding children and other people at homes</t>
+  </si>
+  <si>
+    <t>aae798ab-73b3-4cd0-99d7-1e3aa1aaf895</t>
+  </si>
+  <si>
+    <t>uuid:aae798ab-73b3-4cd0-99d7-1e3aa1aaf895</t>
+  </si>
+  <si>
+    <t>Lolain village</t>
+  </si>
+  <si>
+    <t>Nakut Angellina</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>good porriage but it may not be enough for many family members</t>
+  </si>
+  <si>
+    <t>buying all ingreidents may be difficult</t>
+  </si>
+  <si>
+    <t>sharing household work with my wife to support</t>
+  </si>
+  <si>
+    <t>iother stives are expensive</t>
+  </si>
+  <si>
+    <t>education for children</t>
+  </si>
+  <si>
+    <t>children and elder</t>
+  </si>
+  <si>
+    <t>eavailabilty of food</t>
+  </si>
+  <si>
+    <t>to  encourage all children to go to school</t>
+  </si>
+  <si>
+    <t>vhts and elder</t>
+  </si>
+  <si>
+    <t>children feeding well at home</t>
+  </si>
+  <si>
+    <t>1ed50827-c38c-4a64-9901-bdf4027a3650</t>
+  </si>
+  <si>
+    <t>uuid:1ed50827-c38c-4a64-9901-bdf4027a3650</t>
+  </si>
+  <si>
+    <t>Nakapelimen modern village</t>
+  </si>
+  <si>
+    <t>simon Peter</t>
+  </si>
+  <si>
+    <t>if money was available, I will try and buy nutritious food for my children</t>
+  </si>
+  <si>
+    <t>men always want to be treated well than children esepailly when food is served</t>
+  </si>
+  <si>
+    <t>i will support my children</t>
+  </si>
+  <si>
+    <t>children and old</t>
+  </si>
+  <si>
+    <t>to share roles and make decisions together</t>
+  </si>
+  <si>
+    <t>household chores and decision making</t>
+  </si>
+  <si>
+    <t>follow up on their commitments and conduct a dialogue</t>
+  </si>
+  <si>
+    <t>88c814fa-e84e-48e6-b365-fbc5b4d5b266</t>
+  </si>
+  <si>
+    <t>uuid:88c814fa-e84e-48e6-b365-fbc5b4d5b266</t>
+  </si>
+  <si>
+    <t>loputiput</t>
+  </si>
+  <si>
+    <t>Longole John Bosco</t>
+  </si>
+  <si>
+    <t>that is sorghum porriage</t>
+  </si>
+  <si>
+    <t>i will try and cook for my famiulky especially children</t>
+  </si>
+  <si>
+    <t>i will add milk if possible beacuse gnuts is difficult to buy</t>
+  </si>
+  <si>
+    <t>i will use clean eneregy</t>
+  </si>
+  <si>
+    <t>when food is served to children first</t>
+  </si>
+  <si>
+    <t>food protions for school children</t>
+  </si>
+  <si>
+    <t>debate and dialogue with elders</t>
+  </si>
+  <si>
+    <t>e05b673a-b97d-4dc4-88f3-56e320f264b3</t>
+  </si>
+  <si>
+    <t>uuid:e05b673a-b97d-4dc4-88f3-56e320f264b3</t>
+  </si>
+  <si>
+    <t>singila</t>
+  </si>
+  <si>
+    <t>Mary Goretti</t>
+  </si>
+  <si>
+    <t>Co-facilitating clean cooking/gender dialogue Observing for sustainability tracking</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>interesting to listen to how to cook porriage</t>
+  </si>
+  <si>
+    <t>when food is much, it can be distributed equally</t>
+  </si>
+  <si>
+    <t>I can support my wife with looking for food for household</t>
+  </si>
+  <si>
+    <t>education</t>
+  </si>
+  <si>
+    <t>availbility of food</t>
+  </si>
+  <si>
+    <t>to share roles</t>
+  </si>
+  <si>
+    <t>ef517446-874c-4f5d-bfd6-2616f6307e1f</t>
+  </si>
+  <si>
+    <t>uuid:ef517446-874c-4f5d-bfd6-2616f6307e1f</t>
+  </si>
+  <si>
+    <t>Reading games</t>
+  </si>
+  <si>
+    <t>Equal treatment for both boys and girls</t>
+  </si>
+  <si>
+    <t>Promotes good moral, love within family members</t>
+  </si>
+  <si>
+    <t>Avoids kidnapping among girls</t>
+  </si>
+  <si>
+    <t>To avoid going to school late.reduce workload</t>
+  </si>
+  <si>
+    <t>Promotes girl child education and reduces early marriages</t>
+  </si>
+  <si>
+    <t>Put in millet and paste to the porridge</t>
+  </si>
+  <si>
+    <t>It's good to share household chores</t>
+  </si>
+  <si>
+    <t>Put tarmarin to the porridge</t>
+  </si>
+  <si>
+    <t>Mixing posho with pounded soya</t>
+  </si>
+  <si>
+    <t>It is good to share work together at home</t>
+  </si>
+  <si>
+    <t>All this can be achieved through doing work together</t>
+  </si>
+  <si>
+    <t>Put in flour , sugar and paste</t>
+  </si>
+  <si>
+    <t>Put in flour , sugar and paste including tarmarin</t>
+  </si>
+  <si>
+    <t>Blueband and sugar are important</t>
+  </si>
+  <si>
+    <t>Paste and blue band are too good</t>
+  </si>
+  <si>
+    <t>Put sugar and enough paste</t>
+  </si>
+  <si>
+    <t>Put in enough blue band</t>
+  </si>
+  <si>
+    <t>The type of foods to be mixed.</t>
+  </si>
+  <si>
+    <t>There was another activity going on leading to late start of the activity after long hours of waiting</t>
+  </si>
+  <si>
+    <t>The activity was successfully implemented</t>
+  </si>
+  <si>
+    <t>Proper coordination with trachers</t>
+  </si>
+  <si>
+    <t>Committed to follow the actions agreed.</t>
+  </si>
+  <si>
+    <t>The activity went on well</t>
+  </si>
+  <si>
+    <t>cca8ac00-460d-4538-b6ab-160445a9ee16</t>
+  </si>
+  <si>
+    <t>uuid:cca8ac00-460d-4538-b6ab-160445a9ee16</t>
+  </si>
+  <si>
+    <t>NACHAKUNET P/S</t>
+  </si>
+  <si>
+    <t>In front of the classroom block</t>
+  </si>
+  <si>
+    <t>Proper and timely coordination</t>
+  </si>
+  <si>
+    <t>3c877e5d-4f35-4358-b498-f4af28abf317</t>
+  </si>
+  <si>
+    <t>uuid:3c877e5d-4f35-4358-b498-f4af28abf317</t>
+  </si>
+  <si>
+    <t>OKIROR MOSES</t>
+  </si>
+  <si>
+    <t>Under the big tree in the school</t>
+  </si>
+  <si>
+    <t>10:00:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Metu Porridge Plus: Enriched emergency rations with local wild greens         (Eboo, Lokaka) or cowpeas (Strictly zero unapproved foods/meat) Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing</t>
+  </si>
+  <si>
+    <t>They were tasked to prepare metu porridge with locally available foods at home</t>
+  </si>
+  <si>
+    <t>f46c4fcd-11e6-49c0-bfb4-27679bff6905</t>
+  </si>
+  <si>
+    <t>uuid:f46c4fcd-11e6-49c0-bfb4-27679bff6905</t>
   </si>
 </sst>
 </file>
@@ -11798,8 +12155,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AFG255" totalsRowShown="0">
-  <autoFilter ref="A1:AFG255" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AFG265" totalsRowShown="0">
+  <autoFilter ref="A1:AFG265" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Coordinator Name"/>
@@ -12932,7 +13289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFG255"/>
+  <dimension ref="A1:AFG265"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -70505,6 +70862,2404 @@
         <v>259</v>
       </c>
     </row>
+    <row r="256" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A256" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B256" t="s">
+        <v>960</v>
+      </c>
+      <c r="D256" t="s">
+        <v>12</v>
+      </c>
+      <c r="E256" t="s">
+        <v>1804</v>
+      </c>
+      <c r="M256" t="s">
+        <v>1006</v>
+      </c>
+      <c r="NX256" t="s">
+        <v>3899</v>
+      </c>
+      <c r="NY256" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ256" t="s">
+        <v>3900</v>
+      </c>
+      <c r="OA256" t="s">
+        <v>864</v>
+      </c>
+      <c r="OS256">
+        <v>52</v>
+      </c>
+      <c r="OT256" t="s">
+        <v>2099</v>
+      </c>
+      <c r="OV256">
+        <v>25</v>
+      </c>
+      <c r="OW256" t="s">
+        <v>2099</v>
+      </c>
+      <c r="OY256">
+        <v>15</v>
+      </c>
+      <c r="OZ256" t="s">
+        <v>2099</v>
+      </c>
+      <c r="PB256">
+        <v>19</v>
+      </c>
+      <c r="PC256" t="s">
+        <v>2099</v>
+      </c>
+      <c r="PE256">
+        <v>0</v>
+      </c>
+      <c r="PF256" t="s">
+        <v>2099</v>
+      </c>
+      <c r="PH256">
+        <v>0</v>
+      </c>
+      <c r="PI256" t="s">
+        <v>2099</v>
+      </c>
+      <c r="PJ256" t="s">
+        <v>2277</v>
+      </c>
+      <c r="PL256" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM256" t="s">
+        <v>3901</v>
+      </c>
+      <c r="PN256" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO256" t="s">
+        <v>1815</v>
+      </c>
+      <c r="PQ256" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR256" t="s">
+        <v>2298</v>
+      </c>
+      <c r="PS256">
+        <v>0</v>
+      </c>
+      <c r="PT256">
+        <v>1</v>
+      </c>
+      <c r="PU256">
+        <v>0</v>
+      </c>
+      <c r="PW256" t="s">
+        <v>1817</v>
+      </c>
+      <c r="PX256">
+        <v>1</v>
+      </c>
+      <c r="PY256">
+        <v>0</v>
+      </c>
+      <c r="PZ256">
+        <v>0</v>
+      </c>
+      <c r="QA256">
+        <v>0</v>
+      </c>
+      <c r="QJ256" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QK256" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QL256" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM256" t="s">
+        <v>3902</v>
+      </c>
+      <c r="QN256" t="s">
+        <v>848</v>
+      </c>
+      <c r="QP256" t="s">
+        <v>1986</v>
+      </c>
+      <c r="QQ256" t="s">
+        <v>1842</v>
+      </c>
+      <c r="QR256" t="s">
+        <v>1824</v>
+      </c>
+      <c r="QS256" t="s">
+        <v>3903</v>
+      </c>
+      <c r="QT256" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV256" t="s">
+        <v>1841</v>
+      </c>
+      <c r="QW256" t="s">
+        <v>1842</v>
+      </c>
+      <c r="QX256" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY256" t="s">
+        <v>3904</v>
+      </c>
+      <c r="QZ256" t="s">
+        <v>852</v>
+      </c>
+      <c r="RA256" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB256" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC256" t="s">
+        <v>2009</v>
+      </c>
+      <c r="RD256">
+        <v>0</v>
+      </c>
+      <c r="RE256">
+        <v>1</v>
+      </c>
+      <c r="RF256">
+        <v>1</v>
+      </c>
+      <c r="RG256">
+        <v>0</v>
+      </c>
+      <c r="RH256">
+        <v>0</v>
+      </c>
+      <c r="RJ256" t="s">
+        <v>1948</v>
+      </c>
+      <c r="RK256">
+        <v>1</v>
+      </c>
+      <c r="RL256">
+        <v>0</v>
+      </c>
+      <c r="RM256">
+        <v>0</v>
+      </c>
+      <c r="RO256" t="s">
+        <v>1827</v>
+      </c>
+      <c r="RP256" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ256" t="s">
+        <v>3905</v>
+      </c>
+      <c r="RR256" t="s">
+        <v>3906</v>
+      </c>
+      <c r="RS256" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT256" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY256" t="s">
+        <v>3907</v>
+      </c>
+      <c r="RZ256" t="s">
+        <v>3908</v>
+      </c>
+      <c r="SA256" t="s">
+        <v>2099</v>
+      </c>
+      <c r="SB256" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD256" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH256" t="s">
+        <v>3909</v>
+      </c>
+      <c r="ZL256" s="1"/>
+      <c r="ADO256" s="1"/>
+      <c r="ADW256" s="1"/>
+      <c r="AEA256" s="1"/>
+      <c r="AEY256">
+        <v>894899133</v>
+      </c>
+      <c r="AEZ256" t="s">
+        <v>3910</v>
+      </c>
+      <c r="AFA256" s="1">
+        <v>46311.247314814813</v>
+      </c>
+      <c r="AFC256" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE256" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF256" t="s">
+        <v>3911</v>
+      </c>
+      <c r="AFG256">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A257" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B257" t="s">
+        <v>870</v>
+      </c>
+      <c r="D257" t="s">
+        <v>6</v>
+      </c>
+      <c r="E257" t="s">
+        <v>885</v>
+      </c>
+      <c r="G257" t="s">
+        <v>872</v>
+      </c>
+      <c r="EN257" t="s">
+        <v>1038</v>
+      </c>
+      <c r="EO257">
+        <v>576</v>
+      </c>
+      <c r="EP257">
+        <v>478</v>
+      </c>
+      <c r="EQ257" t="s">
+        <v>843</v>
+      </c>
+      <c r="ER257" t="s">
+        <v>1042</v>
+      </c>
+      <c r="ES257">
+        <v>0</v>
+      </c>
+      <c r="ET257">
+        <v>0</v>
+      </c>
+      <c r="EU257">
+        <v>1</v>
+      </c>
+      <c r="EV257">
+        <v>0</v>
+      </c>
+      <c r="EW257">
+        <v>1</v>
+      </c>
+      <c r="EX257">
+        <v>0</v>
+      </c>
+      <c r="EZ257" t="s">
+        <v>843</v>
+      </c>
+      <c r="FA257">
+        <v>20</v>
+      </c>
+      <c r="FB257" t="s">
+        <v>1039</v>
+      </c>
+      <c r="FC257">
+        <v>1</v>
+      </c>
+      <c r="FD257">
+        <v>1</v>
+      </c>
+      <c r="FE257">
+        <v>1</v>
+      </c>
+      <c r="FF257" t="s">
+        <v>843</v>
+      </c>
+      <c r="FG257" t="s">
+        <v>3912</v>
+      </c>
+      <c r="FH257" t="s">
+        <v>864</v>
+      </c>
+      <c r="NP257">
+        <v>423</v>
+      </c>
+      <c r="NQ257">
+        <v>418</v>
+      </c>
+      <c r="NS257">
+        <v>171</v>
+      </c>
+      <c r="NT257">
+        <v>116</v>
+      </c>
+      <c r="NV257">
+        <v>108</v>
+      </c>
+      <c r="NW257">
+        <v>102</v>
+      </c>
+      <c r="SD257" s="1"/>
+      <c r="UH257" t="s">
+        <v>3913</v>
+      </c>
+      <c r="ZL257" s="1"/>
+      <c r="ADO257" s="1"/>
+      <c r="ADW257" s="1"/>
+      <c r="AEA257" s="1"/>
+      <c r="AEY257">
+        <v>894899251</v>
+      </c>
+      <c r="AEZ257" t="s">
+        <v>3914</v>
+      </c>
+      <c r="AFA257" s="1">
+        <v>46311.247499999998</v>
+      </c>
+      <c r="AFC257" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE257" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF257" t="s">
+        <v>3915</v>
+      </c>
+      <c r="AFG257">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A258" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D258" t="s">
+        <v>9</v>
+      </c>
+      <c r="E258" t="s">
+        <v>1804</v>
+      </c>
+      <c r="J258" t="s">
+        <v>1318</v>
+      </c>
+      <c r="NX258" t="s">
+        <v>3916</v>
+      </c>
+      <c r="NY258" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ258" t="s">
+        <v>3917</v>
+      </c>
+      <c r="OA258" t="s">
+        <v>864</v>
+      </c>
+      <c r="OS258">
+        <v>0</v>
+      </c>
+      <c r="OT258" t="s">
+        <v>3918</v>
+      </c>
+      <c r="OV258">
+        <v>14</v>
+      </c>
+      <c r="OW258" t="s">
+        <v>1243</v>
+      </c>
+      <c r="OY258">
+        <v>6</v>
+      </c>
+      <c r="OZ258" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PB258">
+        <v>0</v>
+      </c>
+      <c r="PC258" t="s">
+        <v>1812</v>
+      </c>
+      <c r="PE258">
+        <v>0</v>
+      </c>
+      <c r="PF258" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PH258">
+        <v>0</v>
+      </c>
+      <c r="PI258" t="s">
+        <v>2002</v>
+      </c>
+      <c r="PJ258" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL258" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM258" t="s">
+        <v>3919</v>
+      </c>
+      <c r="PN258" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO258" t="s">
+        <v>1863</v>
+      </c>
+      <c r="PQ258" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR258" t="s">
+        <v>1941</v>
+      </c>
+      <c r="PS258">
+        <v>0</v>
+      </c>
+      <c r="PT258">
+        <v>0</v>
+      </c>
+      <c r="PU258">
+        <v>1</v>
+      </c>
+      <c r="PV258" t="s">
+        <v>3920</v>
+      </c>
+      <c r="PW258" t="s">
+        <v>1817</v>
+      </c>
+      <c r="PX258">
+        <v>1</v>
+      </c>
+      <c r="PY258">
+        <v>0</v>
+      </c>
+      <c r="PZ258">
+        <v>0</v>
+      </c>
+      <c r="QA258">
+        <v>0</v>
+      </c>
+      <c r="QJ258" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QK258" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QL258" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM258" t="s">
+        <v>3921</v>
+      </c>
+      <c r="QN258" t="s">
+        <v>848</v>
+      </c>
+      <c r="QP258" t="s">
+        <v>1841</v>
+      </c>
+      <c r="QQ258" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QR258" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QS258" t="s">
+        <v>3922</v>
+      </c>
+      <c r="QT258" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV258" t="s">
+        <v>2044</v>
+      </c>
+      <c r="QW258" t="s">
+        <v>1842</v>
+      </c>
+      <c r="QX258" t="s">
+        <v>2147</v>
+      </c>
+      <c r="QY258" t="s">
+        <v>3923</v>
+      </c>
+      <c r="QZ258" t="s">
+        <v>848</v>
+      </c>
+      <c r="RA258" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB258" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC258" t="s">
+        <v>1852</v>
+      </c>
+      <c r="RD258">
+        <v>0</v>
+      </c>
+      <c r="RE258">
+        <v>0</v>
+      </c>
+      <c r="RF258">
+        <v>1</v>
+      </c>
+      <c r="RG258">
+        <v>0</v>
+      </c>
+      <c r="RH258">
+        <v>0</v>
+      </c>
+      <c r="RJ258" t="s">
+        <v>839</v>
+      </c>
+      <c r="RK258">
+        <v>0</v>
+      </c>
+      <c r="RL258">
+        <v>0</v>
+      </c>
+      <c r="RM258">
+        <v>1</v>
+      </c>
+      <c r="RN258" t="s">
+        <v>3924</v>
+      </c>
+      <c r="RO258" t="s">
+        <v>1848</v>
+      </c>
+      <c r="RP258" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ258" t="s">
+        <v>3925</v>
+      </c>
+      <c r="RR258" t="s">
+        <v>3926</v>
+      </c>
+      <c r="RS258" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT258" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY258" t="s">
+        <v>3927</v>
+      </c>
+      <c r="RZ258" t="s">
+        <v>1806</v>
+      </c>
+      <c r="SA258" t="s">
+        <v>3928</v>
+      </c>
+      <c r="SB258" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD258" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH258" t="s">
+        <v>1167</v>
+      </c>
+      <c r="ZL258" s="1"/>
+      <c r="ADO258" s="1"/>
+      <c r="ADW258" s="1"/>
+      <c r="AEA258" s="1"/>
+      <c r="AEY258">
+        <v>894909300</v>
+      </c>
+      <c r="AEZ258" t="s">
+        <v>3929</v>
+      </c>
+      <c r="AFA258" s="1">
+        <v>46311.264837962961</v>
+      </c>
+      <c r="AFC258" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE258" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF258" t="s">
+        <v>3930</v>
+      </c>
+      <c r="AFG258">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A259" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D259" t="s">
+        <v>9</v>
+      </c>
+      <c r="E259" t="s">
+        <v>1804</v>
+      </c>
+      <c r="J259" t="s">
+        <v>1318</v>
+      </c>
+      <c r="NX259" t="s">
+        <v>3931</v>
+      </c>
+      <c r="NY259" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ259" t="s">
+        <v>3932</v>
+      </c>
+      <c r="OA259" t="s">
+        <v>843</v>
+      </c>
+      <c r="OB259" t="s">
+        <v>1859</v>
+      </c>
+      <c r="OC259">
+        <v>0</v>
+      </c>
+      <c r="OD259">
+        <v>0</v>
+      </c>
+      <c r="OE259">
+        <v>0</v>
+      </c>
+      <c r="OF259">
+        <v>1</v>
+      </c>
+      <c r="OG259">
+        <v>0</v>
+      </c>
+      <c r="OI259" t="s">
+        <v>3724</v>
+      </c>
+      <c r="OJ259">
+        <v>0</v>
+      </c>
+      <c r="OK259">
+        <v>0</v>
+      </c>
+      <c r="OL259">
+        <v>1</v>
+      </c>
+      <c r="OM259">
+        <v>0</v>
+      </c>
+      <c r="OS259">
+        <v>0</v>
+      </c>
+      <c r="OT259" t="s">
+        <v>3933</v>
+      </c>
+      <c r="OV259">
+        <v>18</v>
+      </c>
+      <c r="OW259" t="s">
+        <v>1243</v>
+      </c>
+      <c r="OY259">
+        <v>3</v>
+      </c>
+      <c r="OZ259" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PB259">
+        <v>14</v>
+      </c>
+      <c r="PC259" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PE259">
+        <v>1</v>
+      </c>
+      <c r="PF259" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PH259">
+        <v>0</v>
+      </c>
+      <c r="PI259" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PJ259" t="s">
+        <v>2277</v>
+      </c>
+      <c r="PL259" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM259" t="s">
+        <v>3934</v>
+      </c>
+      <c r="PN259" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO259" t="s">
+        <v>1815</v>
+      </c>
+      <c r="PQ259" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR259" t="s">
+        <v>2279</v>
+      </c>
+      <c r="PS259">
+        <v>0</v>
+      </c>
+      <c r="PT259">
+        <v>1</v>
+      </c>
+      <c r="PU259">
+        <v>1</v>
+      </c>
+      <c r="PV259" t="s">
+        <v>2936</v>
+      </c>
+      <c r="PW259" t="s">
+        <v>1817</v>
+      </c>
+      <c r="PX259">
+        <v>1</v>
+      </c>
+      <c r="PY259">
+        <v>0</v>
+      </c>
+      <c r="PZ259">
+        <v>0</v>
+      </c>
+      <c r="QA259">
+        <v>0</v>
+      </c>
+      <c r="QJ259" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QK259" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QL259" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM259" t="s">
+        <v>3935</v>
+      </c>
+      <c r="QN259" t="s">
+        <v>848</v>
+      </c>
+      <c r="QP259" t="s">
+        <v>1986</v>
+      </c>
+      <c r="QQ259" t="s">
+        <v>1846</v>
+      </c>
+      <c r="QR259" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QS259" t="s">
+        <v>3936</v>
+      </c>
+      <c r="QT259" t="s">
+        <v>852</v>
+      </c>
+      <c r="QV259" t="s">
+        <v>2044</v>
+      </c>
+      <c r="QW259" t="s">
+        <v>1842</v>
+      </c>
+      <c r="QX259" t="s">
+        <v>2147</v>
+      </c>
+      <c r="QY259" t="s">
+        <v>3937</v>
+      </c>
+      <c r="QZ259" t="s">
+        <v>848</v>
+      </c>
+      <c r="RA259" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB259" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC259" t="s">
+        <v>2009</v>
+      </c>
+      <c r="RD259">
+        <v>0</v>
+      </c>
+      <c r="RE259">
+        <v>1</v>
+      </c>
+      <c r="RF259">
+        <v>1</v>
+      </c>
+      <c r="RG259">
+        <v>0</v>
+      </c>
+      <c r="RH259">
+        <v>0</v>
+      </c>
+      <c r="RJ259" t="s">
+        <v>2010</v>
+      </c>
+      <c r="RK259">
+        <v>1</v>
+      </c>
+      <c r="RL259">
+        <v>0</v>
+      </c>
+      <c r="RM259">
+        <v>1</v>
+      </c>
+      <c r="RN259" t="s">
+        <v>3938</v>
+      </c>
+      <c r="RO259" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP259" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ259" t="s">
+        <v>3939</v>
+      </c>
+      <c r="RR259" t="s">
+        <v>3940</v>
+      </c>
+      <c r="RS259" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT259" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY259" t="s">
+        <v>3941</v>
+      </c>
+      <c r="RZ259" t="s">
+        <v>3942</v>
+      </c>
+      <c r="SA259" t="s">
+        <v>3943</v>
+      </c>
+      <c r="SB259" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD259" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH259" t="s">
+        <v>1193</v>
+      </c>
+      <c r="ZL259" s="1"/>
+      <c r="ADO259" s="1"/>
+      <c r="ADW259" s="1"/>
+      <c r="AEA259" s="1"/>
+      <c r="AEY259">
+        <v>894909308</v>
+      </c>
+      <c r="AEZ259" t="s">
+        <v>3944</v>
+      </c>
+      <c r="AFA259" s="1">
+        <v>46311.264849537038</v>
+      </c>
+      <c r="AFC259" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE259" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF259" t="s">
+        <v>3945</v>
+      </c>
+      <c r="AFG259">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A260" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D260" t="s">
+        <v>9</v>
+      </c>
+      <c r="E260" t="s">
+        <v>1804</v>
+      </c>
+      <c r="J260" t="s">
+        <v>1318</v>
+      </c>
+      <c r="NX260" t="s">
+        <v>3946</v>
+      </c>
+      <c r="NY260" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ260" t="s">
+        <v>3947</v>
+      </c>
+      <c r="OA260" t="s">
+        <v>843</v>
+      </c>
+      <c r="OB260" t="s">
+        <v>1859</v>
+      </c>
+      <c r="OC260">
+        <v>0</v>
+      </c>
+      <c r="OD260">
+        <v>0</v>
+      </c>
+      <c r="OE260">
+        <v>0</v>
+      </c>
+      <c r="OF260">
+        <v>1</v>
+      </c>
+      <c r="OG260">
+        <v>0</v>
+      </c>
+      <c r="OI260" t="s">
+        <v>3724</v>
+      </c>
+      <c r="OJ260">
+        <v>0</v>
+      </c>
+      <c r="OK260">
+        <v>0</v>
+      </c>
+      <c r="OL260">
+        <v>1</v>
+      </c>
+      <c r="OM260">
+        <v>0</v>
+      </c>
+      <c r="OS260">
+        <v>0</v>
+      </c>
+      <c r="OT260" t="s">
+        <v>2185</v>
+      </c>
+      <c r="OV260">
+        <v>3</v>
+      </c>
+      <c r="OW260" t="s">
+        <v>1243</v>
+      </c>
+      <c r="OY260">
+        <v>6</v>
+      </c>
+      <c r="OZ260" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PB260">
+        <v>13</v>
+      </c>
+      <c r="PC260" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PE260">
+        <v>0</v>
+      </c>
+      <c r="PF260" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PH260">
+        <v>0</v>
+      </c>
+      <c r="PI260" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PJ260" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL260" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM260" t="s">
+        <v>1193</v>
+      </c>
+      <c r="PN260" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO260" t="s">
+        <v>1815</v>
+      </c>
+      <c r="PQ260" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR260" t="s">
+        <v>2279</v>
+      </c>
+      <c r="PS260">
+        <v>0</v>
+      </c>
+      <c r="PT260">
+        <v>1</v>
+      </c>
+      <c r="PU260">
+        <v>1</v>
+      </c>
+      <c r="PV260" t="s">
+        <v>2936</v>
+      </c>
+      <c r="PW260" t="s">
+        <v>1817</v>
+      </c>
+      <c r="PX260">
+        <v>1</v>
+      </c>
+      <c r="PY260">
+        <v>0</v>
+      </c>
+      <c r="PZ260">
+        <v>0</v>
+      </c>
+      <c r="QA260">
+        <v>0</v>
+      </c>
+      <c r="QJ260" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QK260" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QL260" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM260" t="s">
+        <v>3948</v>
+      </c>
+      <c r="QN260" t="s">
+        <v>848</v>
+      </c>
+      <c r="QP260" t="s">
+        <v>1986</v>
+      </c>
+      <c r="QQ260" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QR260" t="s">
+        <v>2147</v>
+      </c>
+      <c r="QS260" t="s">
+        <v>3949</v>
+      </c>
+      <c r="QT260" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV260" t="s">
+        <v>1818</v>
+      </c>
+      <c r="QW260" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QX260" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY260" t="s">
+        <v>3950</v>
+      </c>
+      <c r="QZ260" t="s">
+        <v>852</v>
+      </c>
+      <c r="RA260" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB260" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC260" t="s">
+        <v>2009</v>
+      </c>
+      <c r="RD260">
+        <v>0</v>
+      </c>
+      <c r="RE260">
+        <v>1</v>
+      </c>
+      <c r="RF260">
+        <v>1</v>
+      </c>
+      <c r="RG260">
+        <v>0</v>
+      </c>
+      <c r="RH260">
+        <v>0</v>
+      </c>
+      <c r="RJ260" t="s">
+        <v>1948</v>
+      </c>
+      <c r="RK260">
+        <v>1</v>
+      </c>
+      <c r="RL260">
+        <v>0</v>
+      </c>
+      <c r="RM260">
+        <v>0</v>
+      </c>
+      <c r="RO260" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP260" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ260" t="s">
+        <v>3951</v>
+      </c>
+      <c r="RR260" t="s">
+        <v>3695</v>
+      </c>
+      <c r="RS260" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT260" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY260" t="s">
+        <v>3952</v>
+      </c>
+      <c r="RZ260" t="s">
+        <v>1852</v>
+      </c>
+      <c r="SA260" t="s">
+        <v>3953</v>
+      </c>
+      <c r="SB260" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD260" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH260" t="s">
+        <v>3954</v>
+      </c>
+      <c r="ZL260" s="1"/>
+      <c r="ADO260" s="1"/>
+      <c r="ADW260" s="1"/>
+      <c r="AEA260" s="1"/>
+      <c r="AEY260">
+        <v>894909315</v>
+      </c>
+      <c r="AEZ260" t="s">
+        <v>3955</v>
+      </c>
+      <c r="AFA260" s="1">
+        <v>46311.264861111107</v>
+      </c>
+      <c r="AFC260" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE260" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF260" t="s">
+        <v>3956</v>
+      </c>
+      <c r="AFG260">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A261" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D261" t="s">
+        <v>9</v>
+      </c>
+      <c r="E261" t="s">
+        <v>1804</v>
+      </c>
+      <c r="J261" t="s">
+        <v>1318</v>
+      </c>
+      <c r="NX261" t="s">
+        <v>3957</v>
+      </c>
+      <c r="NY261" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ261" t="s">
+        <v>3958</v>
+      </c>
+      <c r="OA261" t="s">
+        <v>843</v>
+      </c>
+      <c r="OB261" t="s">
+        <v>1859</v>
+      </c>
+      <c r="OC261">
+        <v>0</v>
+      </c>
+      <c r="OD261">
+        <v>0</v>
+      </c>
+      <c r="OE261">
+        <v>0</v>
+      </c>
+      <c r="OF261">
+        <v>1</v>
+      </c>
+      <c r="OG261">
+        <v>0</v>
+      </c>
+      <c r="OI261" t="s">
+        <v>3537</v>
+      </c>
+      <c r="OJ261">
+        <v>0</v>
+      </c>
+      <c r="OK261">
+        <v>1</v>
+      </c>
+      <c r="OL261">
+        <v>1</v>
+      </c>
+      <c r="OM261">
+        <v>0</v>
+      </c>
+      <c r="OS261">
+        <v>0</v>
+      </c>
+      <c r="OT261" t="s">
+        <v>1937</v>
+      </c>
+      <c r="OV261">
+        <v>17</v>
+      </c>
+      <c r="OW261" t="s">
+        <v>1243</v>
+      </c>
+      <c r="OY261">
+        <v>12</v>
+      </c>
+      <c r="OZ261" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PB261">
+        <v>0</v>
+      </c>
+      <c r="PC261" t="s">
+        <v>1811</v>
+      </c>
+      <c r="PE261">
+        <v>0</v>
+      </c>
+      <c r="PF261" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PH261">
+        <v>2</v>
+      </c>
+      <c r="PI261" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PJ261" t="s">
+        <v>2277</v>
+      </c>
+      <c r="PL261" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM261" t="s">
+        <v>3959</v>
+      </c>
+      <c r="PN261" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO261" t="s">
+        <v>1815</v>
+      </c>
+      <c r="PQ261" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR261" t="s">
+        <v>2298</v>
+      </c>
+      <c r="PS261">
+        <v>0</v>
+      </c>
+      <c r="PT261">
+        <v>1</v>
+      </c>
+      <c r="PU261">
+        <v>0</v>
+      </c>
+      <c r="PW261" t="s">
+        <v>1817</v>
+      </c>
+      <c r="PX261">
+        <v>1</v>
+      </c>
+      <c r="PY261">
+        <v>0</v>
+      </c>
+      <c r="PZ261">
+        <v>0</v>
+      </c>
+      <c r="QA261">
+        <v>0</v>
+      </c>
+      <c r="QJ261" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QK261" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QL261" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM261" t="s">
+        <v>3960</v>
+      </c>
+      <c r="QN261" t="s">
+        <v>848</v>
+      </c>
+      <c r="QP261" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QQ261" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QR261" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QS261" t="s">
+        <v>3961</v>
+      </c>
+      <c r="QT261" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV261" t="s">
+        <v>2044</v>
+      </c>
+      <c r="QW261" t="s">
+        <v>1842</v>
+      </c>
+      <c r="QX261" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY261" t="s">
+        <v>3962</v>
+      </c>
+      <c r="QZ261" t="s">
+        <v>848</v>
+      </c>
+      <c r="RA261" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB261" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC261" t="s">
+        <v>1947</v>
+      </c>
+      <c r="RD261">
+        <v>0</v>
+      </c>
+      <c r="RE261">
+        <v>1</v>
+      </c>
+      <c r="RF261">
+        <v>0</v>
+      </c>
+      <c r="RG261">
+        <v>0</v>
+      </c>
+      <c r="RH261">
+        <v>0</v>
+      </c>
+      <c r="RJ261" t="s">
+        <v>1948</v>
+      </c>
+      <c r="RK261">
+        <v>1</v>
+      </c>
+      <c r="RL261">
+        <v>0</v>
+      </c>
+      <c r="RM261">
+        <v>0</v>
+      </c>
+      <c r="RO261" t="s">
+        <v>1848</v>
+      </c>
+      <c r="RP261" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ261" t="s">
+        <v>2941</v>
+      </c>
+      <c r="RR261" t="s">
+        <v>3963</v>
+      </c>
+      <c r="RS261" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT261" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY261" t="s">
+        <v>3732</v>
+      </c>
+      <c r="RZ261" t="s">
+        <v>1806</v>
+      </c>
+      <c r="SA261" t="s">
+        <v>3964</v>
+      </c>
+      <c r="SB261" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD261" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH261" t="s">
+        <v>3965</v>
+      </c>
+      <c r="ZL261" s="1"/>
+      <c r="ADO261" s="1"/>
+      <c r="ADW261" s="1"/>
+      <c r="AEA261" s="1"/>
+      <c r="AEY261">
+        <v>894909320</v>
+      </c>
+      <c r="AEZ261" t="s">
+        <v>3966</v>
+      </c>
+      <c r="AFA261" s="1">
+        <v>46311.264861111107</v>
+      </c>
+      <c r="AFC261" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE261" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF261" t="s">
+        <v>3967</v>
+      </c>
+      <c r="AFG261">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A262" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D262" t="s">
+        <v>9</v>
+      </c>
+      <c r="E262" t="s">
+        <v>1804</v>
+      </c>
+      <c r="J262" t="s">
+        <v>1288</v>
+      </c>
+      <c r="NX262" t="s">
+        <v>3968</v>
+      </c>
+      <c r="NY262" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ262" t="s">
+        <v>3969</v>
+      </c>
+      <c r="OA262" t="s">
+        <v>843</v>
+      </c>
+      <c r="OB262" t="s">
+        <v>2316</v>
+      </c>
+      <c r="OC262">
+        <v>0</v>
+      </c>
+      <c r="OD262">
+        <v>1</v>
+      </c>
+      <c r="OE262">
+        <v>0</v>
+      </c>
+      <c r="OF262">
+        <v>0</v>
+      </c>
+      <c r="OG262">
+        <v>0</v>
+      </c>
+      <c r="OI262" t="s">
+        <v>3970</v>
+      </c>
+      <c r="OJ262">
+        <v>1</v>
+      </c>
+      <c r="OK262">
+        <v>0</v>
+      </c>
+      <c r="OL262">
+        <v>1</v>
+      </c>
+      <c r="OM262">
+        <v>0</v>
+      </c>
+      <c r="OS262">
+        <v>0</v>
+      </c>
+      <c r="OT262" t="s">
+        <v>3971</v>
+      </c>
+      <c r="OV262">
+        <v>19</v>
+      </c>
+      <c r="OW262" t="s">
+        <v>1243</v>
+      </c>
+      <c r="OY262">
+        <v>0</v>
+      </c>
+      <c r="OZ262" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PB262">
+        <v>5</v>
+      </c>
+      <c r="PC262" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PE262">
+        <v>2</v>
+      </c>
+      <c r="PF262" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PH262">
+        <v>0</v>
+      </c>
+      <c r="PI262" t="s">
+        <v>2002</v>
+      </c>
+      <c r="PJ262" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL262" t="s">
+        <v>864</v>
+      </c>
+      <c r="PN262" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO262" t="s">
+        <v>1863</v>
+      </c>
+      <c r="PQ262" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR262" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS262">
+        <v>1</v>
+      </c>
+      <c r="PT262">
+        <v>1</v>
+      </c>
+      <c r="PU262">
+        <v>0</v>
+      </c>
+      <c r="PW262" t="s">
+        <v>1817</v>
+      </c>
+      <c r="PX262">
+        <v>1</v>
+      </c>
+      <c r="PY262">
+        <v>0</v>
+      </c>
+      <c r="PZ262">
+        <v>0</v>
+      </c>
+      <c r="QA262">
+        <v>0</v>
+      </c>
+      <c r="QJ262" t="s">
+        <v>1818</v>
+      </c>
+      <c r="QK262" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QL262" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM262" t="s">
+        <v>3972</v>
+      </c>
+      <c r="QN262" t="s">
+        <v>848</v>
+      </c>
+      <c r="QP262" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QQ262" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QR262" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QS262" t="s">
+        <v>3973</v>
+      </c>
+      <c r="QT262" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV262" t="s">
+        <v>1841</v>
+      </c>
+      <c r="QW262" t="s">
+        <v>1846</v>
+      </c>
+      <c r="QX262" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY262" t="s">
+        <v>3974</v>
+      </c>
+      <c r="QZ262" t="s">
+        <v>852</v>
+      </c>
+      <c r="RA262" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB262" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC262" t="s">
+        <v>1852</v>
+      </c>
+      <c r="RD262">
+        <v>0</v>
+      </c>
+      <c r="RE262">
+        <v>0</v>
+      </c>
+      <c r="RF262">
+        <v>1</v>
+      </c>
+      <c r="RG262">
+        <v>0</v>
+      </c>
+      <c r="RH262">
+        <v>0</v>
+      </c>
+      <c r="RJ262" t="s">
+        <v>2010</v>
+      </c>
+      <c r="RK262">
+        <v>1</v>
+      </c>
+      <c r="RL262">
+        <v>0</v>
+      </c>
+      <c r="RM262">
+        <v>1</v>
+      </c>
+      <c r="RN262" t="s">
+        <v>3975</v>
+      </c>
+      <c r="RO262" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP262" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ262" t="s">
+        <v>1867</v>
+      </c>
+      <c r="RR262" t="s">
+        <v>3976</v>
+      </c>
+      <c r="RS262" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT262" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY262" t="s">
+        <v>3977</v>
+      </c>
+      <c r="RZ262" t="s">
+        <v>1852</v>
+      </c>
+      <c r="SA262" t="s">
+        <v>1167</v>
+      </c>
+      <c r="SB262" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD262" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH262" t="s">
+        <v>1380</v>
+      </c>
+      <c r="ZL262" s="1"/>
+      <c r="ADO262" s="1"/>
+      <c r="ADW262" s="1"/>
+      <c r="AEA262" s="1"/>
+      <c r="AEY262">
+        <v>894909344</v>
+      </c>
+      <c r="AEZ262" t="s">
+        <v>3978</v>
+      </c>
+      <c r="AFA262" s="1">
+        <v>46311.264907407407</v>
+      </c>
+      <c r="AFC262" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE262" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF262" t="s">
+        <v>3979</v>
+      </c>
+      <c r="AFG262">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A263" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B263" t="s">
+        <v>870</v>
+      </c>
+      <c r="D263" t="s">
+        <v>6</v>
+      </c>
+      <c r="E263" t="s">
+        <v>885</v>
+      </c>
+      <c r="G263" t="s">
+        <v>872</v>
+      </c>
+      <c r="EN263" t="s">
+        <v>886</v>
+      </c>
+      <c r="FT263">
+        <v>185</v>
+      </c>
+      <c r="FU263">
+        <v>207</v>
+      </c>
+      <c r="FV263">
+        <v>0</v>
+      </c>
+      <c r="FW263">
+        <v>0</v>
+      </c>
+      <c r="FY263">
+        <v>98</v>
+      </c>
+      <c r="FZ263">
+        <v>100</v>
+      </c>
+      <c r="GA263">
+        <v>0</v>
+      </c>
+      <c r="GB263">
+        <v>0</v>
+      </c>
+      <c r="GD263">
+        <v>92</v>
+      </c>
+      <c r="GE263">
+        <v>65</v>
+      </c>
+      <c r="GF263">
+        <v>0</v>
+      </c>
+      <c r="GG263">
+        <v>0</v>
+      </c>
+      <c r="GI263">
+        <v>3</v>
+      </c>
+      <c r="GJ263">
+        <v>0</v>
+      </c>
+      <c r="GK263">
+        <v>0</v>
+      </c>
+      <c r="GL263">
+        <v>0</v>
+      </c>
+      <c r="GN263">
+        <v>0</v>
+      </c>
+      <c r="GO263">
+        <v>0</v>
+      </c>
+      <c r="GP263">
+        <v>0</v>
+      </c>
+      <c r="GQ263">
+        <v>0</v>
+      </c>
+      <c r="GR263" t="s">
+        <v>1565</v>
+      </c>
+      <c r="GS263">
+        <v>1</v>
+      </c>
+      <c r="GT263">
+        <v>0</v>
+      </c>
+      <c r="GU263">
+        <v>1</v>
+      </c>
+      <c r="GV263">
+        <v>1</v>
+      </c>
+      <c r="GW263">
+        <v>1</v>
+      </c>
+      <c r="GX263">
+        <v>0</v>
+      </c>
+      <c r="GY263">
+        <v>1</v>
+      </c>
+      <c r="GZ263" t="s">
+        <v>1261</v>
+      </c>
+      <c r="HA263">
+        <v>1</v>
+      </c>
+      <c r="HB263">
+        <v>0</v>
+      </c>
+      <c r="HC263">
+        <v>0</v>
+      </c>
+      <c r="HD263">
+        <v>1</v>
+      </c>
+      <c r="HE263">
+        <v>0</v>
+      </c>
+      <c r="HG263" t="s">
+        <v>843</v>
+      </c>
+      <c r="HH263" t="s">
+        <v>3980</v>
+      </c>
+      <c r="HI263" t="s">
+        <v>843</v>
+      </c>
+      <c r="HJ263" t="s">
+        <v>864</v>
+      </c>
+      <c r="HL263" t="s">
+        <v>864</v>
+      </c>
+      <c r="HT263" t="s">
+        <v>1374</v>
+      </c>
+      <c r="HU263">
+        <v>17</v>
+      </c>
+      <c r="HV263" t="s">
+        <v>3981</v>
+      </c>
+      <c r="HX263" t="s">
+        <v>892</v>
+      </c>
+      <c r="HY263">
+        <v>17</v>
+      </c>
+      <c r="HZ263" t="s">
+        <v>3982</v>
+      </c>
+      <c r="IB263" t="s">
+        <v>892</v>
+      </c>
+      <c r="IC263">
+        <v>17</v>
+      </c>
+      <c r="ID263" t="s">
+        <v>3983</v>
+      </c>
+      <c r="IF263" t="s">
+        <v>893</v>
+      </c>
+      <c r="IG263">
+        <v>17</v>
+      </c>
+      <c r="IH263" t="s">
+        <v>3984</v>
+      </c>
+      <c r="IJ263" t="s">
+        <v>893</v>
+      </c>
+      <c r="IK263">
+        <v>12</v>
+      </c>
+      <c r="IL263" t="s">
+        <v>3985</v>
+      </c>
+      <c r="IV263" t="s">
+        <v>895</v>
+      </c>
+      <c r="IW263" t="s">
+        <v>896</v>
+      </c>
+      <c r="IX263" t="s">
+        <v>3986</v>
+      </c>
+      <c r="IY263" t="s">
+        <v>982</v>
+      </c>
+      <c r="IZ263" t="s">
+        <v>3987</v>
+      </c>
+      <c r="JA263" t="s">
+        <v>852</v>
+      </c>
+      <c r="JC263" t="s">
+        <v>895</v>
+      </c>
+      <c r="JD263" t="s">
+        <v>896</v>
+      </c>
+      <c r="JE263" t="s">
+        <v>3988</v>
+      </c>
+      <c r="JF263" t="s">
+        <v>987</v>
+      </c>
+      <c r="JG263" t="s">
+        <v>3989</v>
+      </c>
+      <c r="JH263" t="s">
+        <v>848</v>
+      </c>
+      <c r="JJ263" t="s">
+        <v>895</v>
+      </c>
+      <c r="JK263" t="s">
+        <v>896</v>
+      </c>
+      <c r="JL263" t="s">
+        <v>3990</v>
+      </c>
+      <c r="JM263" t="s">
+        <v>982</v>
+      </c>
+      <c r="JN263" t="s">
+        <v>3991</v>
+      </c>
+      <c r="JO263" t="s">
+        <v>852</v>
+      </c>
+      <c r="JQ263" t="s">
+        <v>895</v>
+      </c>
+      <c r="JR263" t="s">
+        <v>896</v>
+      </c>
+      <c r="JS263" t="s">
+        <v>3992</v>
+      </c>
+      <c r="JT263" t="s">
+        <v>982</v>
+      </c>
+      <c r="JU263" t="s">
+        <v>3993</v>
+      </c>
+      <c r="JV263" t="s">
+        <v>848</v>
+      </c>
+      <c r="JX263" t="s">
+        <v>895</v>
+      </c>
+      <c r="JY263" t="s">
+        <v>1187</v>
+      </c>
+      <c r="JZ263" t="s">
+        <v>3994</v>
+      </c>
+      <c r="KA263" t="s">
+        <v>982</v>
+      </c>
+      <c r="KB263" t="s">
+        <v>3995</v>
+      </c>
+      <c r="KC263" t="s">
+        <v>848</v>
+      </c>
+      <c r="KE263" t="s">
+        <v>895</v>
+      </c>
+      <c r="KF263" t="s">
+        <v>1187</v>
+      </c>
+      <c r="KG263" t="s">
+        <v>3996</v>
+      </c>
+      <c r="KH263" t="s">
+        <v>982</v>
+      </c>
+      <c r="KI263" t="s">
+        <v>3997</v>
+      </c>
+      <c r="KJ263" t="s">
+        <v>848</v>
+      </c>
+      <c r="KK263" t="s">
+        <v>998</v>
+      </c>
+      <c r="KL263">
+        <v>1</v>
+      </c>
+      <c r="KM263">
+        <v>0</v>
+      </c>
+      <c r="KN263">
+        <v>0</v>
+      </c>
+      <c r="KO263">
+        <v>0</v>
+      </c>
+      <c r="KP263">
+        <v>0</v>
+      </c>
+      <c r="KQ263" t="s">
+        <v>3998</v>
+      </c>
+      <c r="KR263" t="s">
+        <v>3999</v>
+      </c>
+      <c r="KS263" t="s">
+        <v>4000</v>
+      </c>
+      <c r="KT263" t="s">
+        <v>4001</v>
+      </c>
+      <c r="KU263" t="s">
+        <v>4002</v>
+      </c>
+      <c r="NP263">
+        <v>423</v>
+      </c>
+      <c r="NQ263">
+        <v>418</v>
+      </c>
+      <c r="NS263">
+        <v>171</v>
+      </c>
+      <c r="NT263">
+        <v>116</v>
+      </c>
+      <c r="NV263">
+        <v>102</v>
+      </c>
+      <c r="NW263">
+        <v>108</v>
+      </c>
+      <c r="SD263" s="1"/>
+      <c r="UH263" t="s">
+        <v>4003</v>
+      </c>
+      <c r="ZL263" s="1"/>
+      <c r="ADO263" s="1"/>
+      <c r="ADW263" s="1"/>
+      <c r="AEA263" s="1"/>
+      <c r="AEY263">
+        <v>894915124</v>
+      </c>
+      <c r="AEZ263" t="s">
+        <v>4004</v>
+      </c>
+      <c r="AFA263" s="1">
+        <v>46311.273773148147</v>
+      </c>
+      <c r="AFC263" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE263" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF263" t="s">
+        <v>4005</v>
+      </c>
+      <c r="AFG263">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A264" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B264" t="s">
+        <v>870</v>
+      </c>
+      <c r="D264" t="s">
+        <v>6</v>
+      </c>
+      <c r="E264" t="s">
+        <v>885</v>
+      </c>
+      <c r="G264" t="s">
+        <v>4006</v>
+      </c>
+      <c r="EN264" t="s">
+        <v>1038</v>
+      </c>
+      <c r="EO264">
+        <v>440</v>
+      </c>
+      <c r="EP264">
+        <v>411</v>
+      </c>
+      <c r="EQ264" t="s">
+        <v>843</v>
+      </c>
+      <c r="ER264" t="s">
+        <v>1400</v>
+      </c>
+      <c r="ES264">
+        <v>1</v>
+      </c>
+      <c r="ET264">
+        <v>0</v>
+      </c>
+      <c r="EU264">
+        <v>0</v>
+      </c>
+      <c r="EV264">
+        <v>0</v>
+      </c>
+      <c r="EW264">
+        <v>1</v>
+      </c>
+      <c r="EX264">
+        <v>0</v>
+      </c>
+      <c r="EZ264" t="s">
+        <v>843</v>
+      </c>
+      <c r="FA264">
+        <v>20</v>
+      </c>
+      <c r="FB264" t="s">
+        <v>1039</v>
+      </c>
+      <c r="FC264">
+        <v>1</v>
+      </c>
+      <c r="FD264">
+        <v>1</v>
+      </c>
+      <c r="FE264">
+        <v>1</v>
+      </c>
+      <c r="FF264" t="s">
+        <v>843</v>
+      </c>
+      <c r="FG264" t="s">
+        <v>4007</v>
+      </c>
+      <c r="FH264" t="s">
+        <v>843</v>
+      </c>
+      <c r="FI264">
+        <v>1</v>
+      </c>
+      <c r="FJ264" t="s">
+        <v>839</v>
+      </c>
+      <c r="FK264">
+        <v>0</v>
+      </c>
+      <c r="FL264">
+        <v>1</v>
+      </c>
+      <c r="NP264">
+        <v>709</v>
+      </c>
+      <c r="NQ264">
+        <v>636</v>
+      </c>
+      <c r="NS264">
+        <v>224</v>
+      </c>
+      <c r="NT264">
+        <v>157</v>
+      </c>
+      <c r="NV264">
+        <v>177</v>
+      </c>
+      <c r="NW264">
+        <v>123</v>
+      </c>
+      <c r="SD264" s="1"/>
+      <c r="UH264" t="s">
+        <v>4008</v>
+      </c>
+      <c r="ZL264" s="1"/>
+      <c r="ADO264" s="1"/>
+      <c r="ADW264" s="1"/>
+      <c r="AEA264" s="1"/>
+      <c r="AEY264">
+        <v>894979495</v>
+      </c>
+      <c r="AEZ264" t="s">
+        <v>4009</v>
+      </c>
+      <c r="AFA264" s="1">
+        <v>46311.355682870373</v>
+      </c>
+      <c r="AFC264" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE264" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF264" t="s">
+        <v>4010</v>
+      </c>
+      <c r="AFG264">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A265" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B265" t="s">
+        <v>870</v>
+      </c>
+      <c r="D265" t="s">
+        <v>6</v>
+      </c>
+      <c r="E265" t="s">
+        <v>871</v>
+      </c>
+      <c r="G265" t="s">
+        <v>1392</v>
+      </c>
+      <c r="SD265" s="1"/>
+      <c r="SV265" t="s">
+        <v>873</v>
+      </c>
+      <c r="SW265">
+        <v>1</v>
+      </c>
+      <c r="SX265">
+        <v>0</v>
+      </c>
+      <c r="SY265" t="s">
+        <v>4011</v>
+      </c>
+      <c r="SZ265">
+        <v>12</v>
+      </c>
+      <c r="TA265">
+        <v>18</v>
+      </c>
+      <c r="TB265" t="s">
+        <v>4012</v>
+      </c>
+      <c r="TC265" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TD265" t="s">
+        <v>4013</v>
+      </c>
+      <c r="TE265" t="s">
+        <v>1049</v>
+      </c>
+      <c r="TF265">
+        <v>24</v>
+      </c>
+      <c r="TG265">
+        <v>11</v>
+      </c>
+      <c r="TH265">
+        <v>1</v>
+      </c>
+      <c r="TI265">
+        <v>1</v>
+      </c>
+      <c r="TJ265" t="s">
+        <v>4014</v>
+      </c>
+      <c r="TK265">
+        <v>1</v>
+      </c>
+      <c r="TL265">
+        <v>0</v>
+      </c>
+      <c r="TM265">
+        <v>1</v>
+      </c>
+      <c r="TN265">
+        <v>0</v>
+      </c>
+      <c r="TO265">
+        <v>0</v>
+      </c>
+      <c r="TP265" t="s">
+        <v>4015</v>
+      </c>
+      <c r="UH265" t="s">
+        <v>1380</v>
+      </c>
+      <c r="ZL265" s="1"/>
+      <c r="ADO265" s="1"/>
+      <c r="ADW265" s="1"/>
+      <c r="AEA265" s="1"/>
+      <c r="AEY265">
+        <v>894984010</v>
+      </c>
+      <c r="AEZ265" t="s">
+        <v>4016</v>
+      </c>
+      <c r="AFA265" s="1">
+        <v>46311.360567129632</v>
+      </c>
+      <c r="AFC265" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE265" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF265" t="s">
+        <v>4017</v>
+      </c>
+      <c r="AFG265">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_875741B50482FB89CC18BFA3AD4603C54E6094F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D1CC9B7-7033-D148-A013-7FF9E28617F6}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_875741B50482FB89CC18BFA3AD4603C54E6094F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F53B6809-FC64-874A-98A1-C11E7BD82805}"/>
   <bookViews>
-    <workbookView xWindow="3340" yWindow="660" windowWidth="24340" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="660" windowWidth="24340" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nutribus 2.0 Activity" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11324" uniqueCount="4018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12290" uniqueCount="4192">
   <si>
     <t>Date</t>
   </si>
@@ -12074,6 +12074,528 @@
   </si>
   <si>
     <t>uuid:f46c4fcd-11e6-49c0-bfb4-27679bff6905</t>
+  </si>
+  <si>
+    <t>The club patron informed the school about the currently running campaign of the NUTRI- BUS SCHOOL CAMPAIGN, he also passed a message of the importance of having children at school</t>
+  </si>
+  <si>
+    <t>They changed their meeting days from the previous one scheduled</t>
+  </si>
+  <si>
+    <t>92d2a0a1-c34d-43be-912f-186f2c94dc6a</t>
+  </si>
+  <si>
+    <t>uuid:92d2a0a1-c34d-43be-912f-186f2c94dc6a</t>
+  </si>
+  <si>
+    <t>They understand importance of school</t>
+  </si>
+  <si>
+    <t>Practiced firewood-saving cooking methods (covered pot, smaller wood)</t>
+  </si>
+  <si>
+    <t>Moderate impact</t>
+  </si>
+  <si>
+    <t>Children and caregivers have learnt some of the things about nutrition.gender</t>
+  </si>
+  <si>
+    <t>f24221b8-2914-40de-a28f-7ebff26e25ef</t>
+  </si>
+  <si>
+    <t>uuid:f24221b8-2914-40de-a28f-7ebff26e25ef</t>
+  </si>
+  <si>
+    <t>There is great improvement in the school.</t>
+  </si>
+  <si>
+    <t>8d04024a-ec9e-45cf-aedd-a6bf2963b955</t>
+  </si>
+  <si>
+    <t>uuid:8d04024a-ec9e-45cf-aedd-a6bf2963b955</t>
+  </si>
+  <si>
+    <t>Logolosimet</t>
+  </si>
+  <si>
+    <t>Jacinta</t>
+  </si>
+  <si>
+    <t>Retained heat cooking and pot covering to conserve fuel Traditional 3-stone fire used (Non-compliant)</t>
+  </si>
+  <si>
+    <t>Will try to practice metu porridge</t>
+  </si>
+  <si>
+    <t>They lack food due to drought</t>
+  </si>
+  <si>
+    <t>They will try again but the droughts have affected them</t>
+  </si>
+  <si>
+    <t>5665212f-8e26-460b-b884-7105e583bdbb</t>
+  </si>
+  <si>
+    <t>uuid:5665212f-8e26-460b-b884-7105e583bdbb</t>
+  </si>
+  <si>
+    <t>Lokarukoi</t>
+  </si>
+  <si>
+    <t>They were excited to learn</t>
+  </si>
+  <si>
+    <t>They are willing but hunger is much</t>
+  </si>
+  <si>
+    <t>They need support from other partners</t>
+  </si>
+  <si>
+    <t>The community needs to be supported with food.</t>
+  </si>
+  <si>
+    <t>28e482fc-8fd7-4682-98f4-3a8cf8ed2f59</t>
+  </si>
+  <si>
+    <t>uuid:28e482fc-8fd7-4682-98f4-3a8cf8ed2f59</t>
+  </si>
+  <si>
+    <t>Lopeei trading center</t>
+  </si>
+  <si>
+    <t>They will try metu porridge recipe but they can't afford some ingredients</t>
+  </si>
+  <si>
+    <t>Hunger is much in the region</t>
+  </si>
+  <si>
+    <t>Community is willing to practice nutrition facts but unable due to drought</t>
+  </si>
+  <si>
+    <t>dc35e5ea-75de-401e-85d5-bcad745f5fd9</t>
+  </si>
+  <si>
+    <t>uuid:dc35e5ea-75de-401e-85d5-bcad745f5fd9</t>
+  </si>
+  <si>
+    <t>Natirae primary school catchment area</t>
+  </si>
+  <si>
+    <t>Peter Achia, Michael Lochuge and Raphael longole</t>
+  </si>
+  <si>
+    <t>UNAC AFI Local Council</t>
+  </si>
+  <si>
+    <t>The ingredients for preparation look expensive but they are willing to try cook it.</t>
+  </si>
+  <si>
+    <t>I will try with local available materials</t>
+  </si>
+  <si>
+    <t>Incase I get materials I will try</t>
+  </si>
+  <si>
+    <t>Lacking ability to do that now</t>
+  </si>
+  <si>
+    <t>Importance of finishing school and why food is good while at school</t>
+  </si>
+  <si>
+    <t>Children followed the father</t>
+  </si>
+  <si>
+    <t>Availability of enough food</t>
+  </si>
+  <si>
+    <t>Make sure children at home share house choress, the last child be served food first in the household, try preparation of metu porridge with available materials</t>
+  </si>
+  <si>
+    <t>Local leaders, VHTs, District coordinator, partners</t>
+  </si>
+  <si>
+    <t>Materials availability for cooking METU poorridge</t>
+  </si>
+  <si>
+    <t>Capturing demos, gender and. Elders dialogue</t>
+  </si>
+  <si>
+    <t>More follow ups by the VHTs should be done, more Sensitization on nutrition, gender and education. Campaigns should be done</t>
+  </si>
+  <si>
+    <t>73fabe95-adc9-4fe6-99dd-281bd5995aa9</t>
+  </si>
+  <si>
+    <t>uuid:73fabe95-adc9-4fe6-99dd-281bd5995aa9</t>
+  </si>
+  <si>
+    <t>Lakateyak</t>
+  </si>
+  <si>
+    <t>They will try but drought has been too long</t>
+  </si>
+  <si>
+    <t>The community wants to be supported with seeds and water</t>
+  </si>
+  <si>
+    <t>Support the community with seeds and water and food to improve nutrition</t>
+  </si>
+  <si>
+    <t>d41ea114-ac5e-4556-8e7b-c93f9d224224</t>
+  </si>
+  <si>
+    <t>uuid:d41ea114-ac5e-4556-8e7b-c93f9d224224</t>
+  </si>
+  <si>
+    <t>Lotede</t>
+  </si>
+  <si>
+    <t>Very excited to see</t>
+  </si>
+  <si>
+    <t>It's drought which is a great problem to them</t>
+  </si>
+  <si>
+    <t>There high drought which is affected most families</t>
+  </si>
+  <si>
+    <t>dcb1f962-6f44-4309-9a2f-1b7db21ef8e3</t>
+  </si>
+  <si>
+    <t>uuid:dcb1f962-6f44-4309-9a2f-1b7db21ef8e3</t>
+  </si>
+  <si>
+    <t>Peter achia, Michael Lochuge and Raphael Longole</t>
+  </si>
+  <si>
+    <t>The porridge is good but some materials are unavailable.</t>
+  </si>
+  <si>
+    <t>It can be tried is materials available.</t>
+  </si>
+  <si>
+    <t>I do not know some steps</t>
+  </si>
+  <si>
+    <t>I will try setting up a traditional firewood saving stove</t>
+  </si>
+  <si>
+    <t>Local leaders.</t>
+  </si>
+  <si>
+    <t>In some of our households husbands are served first</t>
+  </si>
+  <si>
+    <t>We shall mobilize materials and try cook metu porridge,</t>
+  </si>
+  <si>
+    <t>Local leaders, VHTs, partners like AFI</t>
+  </si>
+  <si>
+    <t>The main debate was the gender responsibility sharing</t>
+  </si>
+  <si>
+    <t>Demonstrations pictures, gender lessons.</t>
+  </si>
+  <si>
+    <t>Mobilization of community members for demonstrations and household follow ups</t>
+  </si>
+  <si>
+    <t>e1b15e9e-7535-4c14-84c9-a35d86fdb5dd</t>
+  </si>
+  <si>
+    <t>uuid:e1b15e9e-7535-4c14-84c9-a35d86fdb5dd</t>
+  </si>
+  <si>
+    <t>Arengpuwa</t>
+  </si>
+  <si>
+    <t>Interested</t>
+  </si>
+  <si>
+    <t>It's lack of money affecting them</t>
+  </si>
+  <si>
+    <t>Poverty caused by drought has been too much effect on the nutrition</t>
+  </si>
+  <si>
+    <t>They need to be strengthen and supported inorder to reduce malnutrition</t>
+  </si>
+  <si>
+    <t>de5ebd3c-abfc-4a4e-9171-d113d21d1a42</t>
+  </si>
+  <si>
+    <t>uuid:de5ebd3c-abfc-4a4e-9171-d113d21d1a42</t>
+  </si>
+  <si>
+    <t>Lotop</t>
+  </si>
+  <si>
+    <t>Happy and ready to practice</t>
+  </si>
+  <si>
+    <t>They will try to plant vegetables in</t>
+  </si>
+  <si>
+    <t>They lack money</t>
+  </si>
+  <si>
+    <t>Poverty caused by drought has been too much but they will try to practice nutrition</t>
+  </si>
+  <si>
+    <t>9d159713-093a-4cbe-874a-cc4eb0ff8318</t>
+  </si>
+  <si>
+    <t>uuid:9d159713-093a-4cbe-874a-cc4eb0ff8318</t>
+  </si>
+  <si>
+    <t>LOMONYANG SIMON PETER AND ASEKENYE MARRIAM</t>
+  </si>
+  <si>
+    <t>Climate-Smart Living: Firewood-saving cooking methods &amp; moving from 3-stone fires Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing</t>
+  </si>
+  <si>
+    <t>Eating different types of foods</t>
+  </si>
+  <si>
+    <t>Clearly drawn charts would help the verbal talking</t>
+  </si>
+  <si>
+    <t>3589c305-de79-45f4-a9d2-d5ede8e77473</t>
+  </si>
+  <si>
+    <t>uuid:3589c305-de79-45f4-a9d2-d5ede8e77473</t>
+  </si>
+  <si>
+    <t>Sharing gender roles</t>
+  </si>
+  <si>
+    <t>More materials in Ngakarimojong</t>
+  </si>
+  <si>
+    <t>b531d196-acfd-4b35-9812-a504360b1f69</t>
+  </si>
+  <si>
+    <t>uuid:b531d196-acfd-4b35-9812-a504360b1f69</t>
+  </si>
+  <si>
+    <t>Need for more charts</t>
+  </si>
+  <si>
+    <t>1ff26af3-a90d-451f-ab73-2df466146fd6</t>
+  </si>
+  <si>
+    <t>uuid:1ff26af3-a90d-451f-ab73-2df466146fd6</t>
+  </si>
+  <si>
+    <t>Lomonyang Simon Peter and ASEKENYE MARRIAM</t>
+  </si>
+  <si>
+    <t>Within the school</t>
+  </si>
+  <si>
+    <t>16:50:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Boys and girls fetching firewood together</t>
+  </si>
+  <si>
+    <t>More playing materials to actively engage learners</t>
+  </si>
+  <si>
+    <t>cdd0a1bd-9ef2-4fe6-80a5-d92203c61965</t>
+  </si>
+  <si>
+    <t>uuid:cdd0a1bd-9ef2-4fe6-80a5-d92203c61965</t>
+  </si>
+  <si>
+    <t>07:30:00.000+03:00</t>
+  </si>
+  <si>
+    <t>08:35:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Smart cooking and gender roles in our homes</t>
+  </si>
+  <si>
+    <t>Children were looking satisfied with the messages</t>
+  </si>
+  <si>
+    <t>4a85d363-747d-474e-b1d8-9635ac350e47</t>
+  </si>
+  <si>
+    <t>uuid:4a85d363-747d-474e-b1d8-9635ac350e47</t>
+  </si>
+  <si>
+    <t>Aca Filex</t>
+  </si>
+  <si>
+    <t>cooking beans sukuma,posho</t>
+  </si>
+  <si>
+    <t>10563446-22d9-47f4-bd18-d236c79186ef</t>
+  </si>
+  <si>
+    <t>uuid:10563446-22d9-47f4-bd18-d236c79186ef</t>
+  </si>
+  <si>
+    <t>Demonstrating sharing of activities</t>
+  </si>
+  <si>
+    <t>Because explanation was simple to learners level</t>
+  </si>
+  <si>
+    <t>They do together</t>
+  </si>
+  <si>
+    <t>Agree to do as equal</t>
+  </si>
+  <si>
+    <t>Accepted</t>
+  </si>
+  <si>
+    <t>Agreed</t>
+  </si>
+  <si>
+    <t>Happening</t>
+  </si>
+  <si>
+    <t>They do</t>
+  </si>
+  <si>
+    <t>Many parents were not informed</t>
+  </si>
+  <si>
+    <t>School community welcomed the programme</t>
+  </si>
+  <si>
+    <t>Time schedule to be observed</t>
+  </si>
+  <si>
+    <t>Willing to fulfil the pledge</t>
+  </si>
+  <si>
+    <t>Need more community sensitization</t>
+  </si>
+  <si>
+    <t>6041ff22-5ecf-4e16-9ff6-664d075ca46e</t>
+  </si>
+  <si>
+    <t>uuid:6041ff22-5ecf-4e16-9ff6-664d075ca46e</t>
+  </si>
+  <si>
+    <t>Aca Filex And Atang</t>
+  </si>
+  <si>
+    <t>Millet porridge,</t>
+  </si>
+  <si>
+    <t>Lack of metu porridge Materials</t>
+  </si>
+  <si>
+    <t>e25477bf-6b26-4978-bbcd-ff5cfd54d4a3</t>
+  </si>
+  <si>
+    <t>uuid:e25477bf-6b26-4978-bbcd-ff5cfd54d4a3</t>
+  </si>
+  <si>
+    <t>Chore sharing promotes responsility and hardwork for all children</t>
+  </si>
+  <si>
+    <t>55b00b6e-97cb-4ab3-b604-499c5db6c88f</t>
+  </si>
+  <si>
+    <t>uuid:55b00b6e-97cb-4ab3-b604-499c5db6c88f</t>
+  </si>
+  <si>
+    <t>Near the kitchen</t>
+  </si>
+  <si>
+    <t>Continuous conducting of sessions</t>
+  </si>
+  <si>
+    <t>f2f147ca-b92e-47a7-9bc2-da2483889571</t>
+  </si>
+  <si>
+    <t>uuid:f2f147ca-b92e-47a7-9bc2-da2483889571</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Infront of the staffroom</t>
+  </si>
+  <si>
+    <t>Programme to be maintained</t>
+  </si>
+  <si>
+    <t>71cc2218-f81d-446e-9579-361cdcfda483</t>
+  </si>
+  <si>
+    <t>uuid:71cc2218-f81d-446e-9579-361cdcfda483</t>
+  </si>
+  <si>
+    <t>More materials needed</t>
+  </si>
+  <si>
+    <t>5cd7889b-c612-4d7f-8057-2f98af07f58b</t>
+  </si>
+  <si>
+    <t>uuid:5cd7889b-c612-4d7f-8057-2f98af07f58b</t>
+  </si>
+  <si>
+    <t>1078d6d7-7acc-4cfc-95bc-9650046e86cd</t>
+  </si>
+  <si>
+    <t>uuid:1078d6d7-7acc-4cfc-95bc-9650046e86cd</t>
+  </si>
+  <si>
+    <t>Olweny Richard and Lodou Patrick Ayella</t>
+  </si>
+  <si>
+    <t>Climate-Smart Living: Firewood-saving cooking methods &amp; moving from 3-stone fires Adere Calabash Dialogue: Collective responsibility, resilience &amp; fair food sharing Gender Chore Rebalancing: Boys sharing morning water/firewood chores</t>
+  </si>
+  <si>
+    <t>Smart cooking energy stove</t>
+  </si>
+  <si>
+    <t>They complain on the available local materials</t>
+  </si>
+  <si>
+    <t>b865c144-16b8-45a4-a54b-51dc3624e67c</t>
+  </si>
+  <si>
+    <t>uuid:b865c144-16b8-45a4-a54b-51dc3624e67c</t>
+  </si>
+  <si>
+    <t>07:00:00.000+03:00</t>
+  </si>
+  <si>
+    <t>How to follow the drop outs and sharing work at home</t>
+  </si>
+  <si>
+    <t>Empathise was put on sharing house chores</t>
+  </si>
+  <si>
+    <t>a935bc0e-bf91-45b4-a6cf-a5c8a131ec84</t>
+  </si>
+  <si>
+    <t>uuid:a935bc0e-bf91-45b4-a6cf-a5c8a131ec84</t>
+  </si>
+  <si>
+    <t>17:40:00.000+03:00</t>
+  </si>
+  <si>
+    <t>Tracing for drop out learners</t>
+  </si>
+  <si>
+    <t>Follow ups on learners who dropped out of school</t>
+  </si>
+  <si>
+    <t>142ba58d-72ab-422d-9bb1-2933e7ae9b51</t>
+  </si>
+  <si>
+    <t>uuid:142ba58d-72ab-422d-9bb1-2933e7ae9b51</t>
   </si>
 </sst>
 </file>
@@ -12155,8 +12677,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AFG265" totalsRowShown="0">
-  <autoFilter ref="A1:AFG265" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AFG293" totalsRowShown="0">
+  <autoFilter ref="A1:AFG293" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Coordinator Name"/>
@@ -13289,7 +13811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFG265"/>
+  <dimension ref="A1:AFG293"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -73260,6 +73782,4999 @@
         <v>269</v>
       </c>
     </row>
+    <row r="266" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A266" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B266" t="s">
+        <v>870</v>
+      </c>
+      <c r="D266" t="s">
+        <v>6</v>
+      </c>
+      <c r="E266" t="s">
+        <v>871</v>
+      </c>
+      <c r="G266" t="s">
+        <v>1392</v>
+      </c>
+      <c r="SD266" s="1"/>
+      <c r="SV266" t="s">
+        <v>1903</v>
+      </c>
+      <c r="SW266">
+        <v>0</v>
+      </c>
+      <c r="SX266">
+        <v>1</v>
+      </c>
+      <c r="TQ266" s="1">
+        <v>46307</v>
+      </c>
+      <c r="TR266" t="s">
+        <v>3030</v>
+      </c>
+      <c r="TS266" t="s">
+        <v>3665</v>
+      </c>
+      <c r="TT266">
+        <v>519</v>
+      </c>
+      <c r="TU266">
+        <v>325</v>
+      </c>
+      <c r="TV266">
+        <v>3</v>
+      </c>
+      <c r="TW266">
+        <v>2</v>
+      </c>
+      <c r="TX266" t="s">
+        <v>1905</v>
+      </c>
+      <c r="TY266">
+        <v>0</v>
+      </c>
+      <c r="TZ266">
+        <v>0</v>
+      </c>
+      <c r="UA266">
+        <v>1</v>
+      </c>
+      <c r="UB266">
+        <v>1</v>
+      </c>
+      <c r="UC266">
+        <v>1</v>
+      </c>
+      <c r="UD266" t="s">
+        <v>2343</v>
+      </c>
+      <c r="UE266" s="1">
+        <v>46307</v>
+      </c>
+      <c r="UF266" t="s">
+        <v>4018</v>
+      </c>
+      <c r="UG266" t="s">
+        <v>1914</v>
+      </c>
+      <c r="UH266" t="s">
+        <v>4019</v>
+      </c>
+      <c r="ZL266" s="1"/>
+      <c r="ADO266" s="1"/>
+      <c r="ADW266" s="1"/>
+      <c r="AEA266" s="1"/>
+      <c r="AEY266">
+        <v>894988237</v>
+      </c>
+      <c r="AEZ266" t="s">
+        <v>4020</v>
+      </c>
+      <c r="AFA266" s="1">
+        <v>46311.365023148152</v>
+      </c>
+      <c r="AFC266" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE266" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF266" t="s">
+        <v>4021</v>
+      </c>
+      <c r="AFG266">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A267" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B267" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D267" t="s">
+        <v>10</v>
+      </c>
+      <c r="E267" t="s">
+        <v>885</v>
+      </c>
+      <c r="K267" t="s">
+        <v>1775</v>
+      </c>
+      <c r="EN267" t="s">
+        <v>3573</v>
+      </c>
+      <c r="KV267">
+        <v>30</v>
+      </c>
+      <c r="KW267">
+        <v>15</v>
+      </c>
+      <c r="KX267">
+        <v>15</v>
+      </c>
+      <c r="KY267" t="s">
+        <v>3574</v>
+      </c>
+      <c r="LC267" t="s">
+        <v>3575</v>
+      </c>
+      <c r="LE267" t="s">
+        <v>843</v>
+      </c>
+      <c r="LF267" t="s">
+        <v>4022</v>
+      </c>
+      <c r="LG267" t="s">
+        <v>3598</v>
+      </c>
+      <c r="LH267" t="s">
+        <v>864</v>
+      </c>
+      <c r="LJ267" t="s">
+        <v>864</v>
+      </c>
+      <c r="LU267" t="s">
+        <v>852</v>
+      </c>
+      <c r="LV267" t="s">
+        <v>4023</v>
+      </c>
+      <c r="LW267" t="s">
+        <v>843</v>
+      </c>
+      <c r="LX267" t="s">
+        <v>843</v>
+      </c>
+      <c r="LY267" t="s">
+        <v>843</v>
+      </c>
+      <c r="LZ267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MB267" t="s">
+        <v>848</v>
+      </c>
+      <c r="MC267" t="s">
+        <v>3588</v>
+      </c>
+      <c r="MD267" t="s">
+        <v>843</v>
+      </c>
+      <c r="ME267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MF267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MG267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MI267" t="s">
+        <v>848</v>
+      </c>
+      <c r="MJ267" t="s">
+        <v>3579</v>
+      </c>
+      <c r="MK267" t="s">
+        <v>843</v>
+      </c>
+      <c r="ML267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MM267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MN267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MP267" t="s">
+        <v>848</v>
+      </c>
+      <c r="MQ267" t="s">
+        <v>2166</v>
+      </c>
+      <c r="MR267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MS267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MT267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MU267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MW267" t="s">
+        <v>852</v>
+      </c>
+      <c r="MX267" t="s">
+        <v>3579</v>
+      </c>
+      <c r="MY267" t="s">
+        <v>843</v>
+      </c>
+      <c r="MZ267" t="s">
+        <v>843</v>
+      </c>
+      <c r="NA267" t="s">
+        <v>843</v>
+      </c>
+      <c r="NB267" t="s">
+        <v>843</v>
+      </c>
+      <c r="ND267" t="s">
+        <v>848</v>
+      </c>
+      <c r="NE267" t="s">
+        <v>3579</v>
+      </c>
+      <c r="NF267" t="s">
+        <v>843</v>
+      </c>
+      <c r="NG267" t="s">
+        <v>843</v>
+      </c>
+      <c r="NH267" t="s">
+        <v>843</v>
+      </c>
+      <c r="NI267" t="s">
+        <v>843</v>
+      </c>
+      <c r="NJ267" t="s">
+        <v>3592</v>
+      </c>
+      <c r="NK267" t="s">
+        <v>4024</v>
+      </c>
+      <c r="NP267">
+        <v>302</v>
+      </c>
+      <c r="NQ267">
+        <v>285</v>
+      </c>
+      <c r="NS267">
+        <v>150</v>
+      </c>
+      <c r="NT267">
+        <v>180</v>
+      </c>
+      <c r="NV267">
+        <v>147</v>
+      </c>
+      <c r="NW267">
+        <v>147</v>
+      </c>
+      <c r="SD267" s="1"/>
+      <c r="UH267" t="s">
+        <v>4025</v>
+      </c>
+      <c r="ZL267" s="1"/>
+      <c r="ADO267" s="1"/>
+      <c r="ADW267" s="1"/>
+      <c r="AEA267" s="1"/>
+      <c r="AEY267">
+        <v>895015533</v>
+      </c>
+      <c r="AEZ267" t="s">
+        <v>4026</v>
+      </c>
+      <c r="AFA267" s="1">
+        <v>46311.394490740742</v>
+      </c>
+      <c r="AFC267" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE267" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF267" t="s">
+        <v>4027</v>
+      </c>
+      <c r="AFG267">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A268" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B268" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D268" t="s">
+        <v>10</v>
+      </c>
+      <c r="E268" t="s">
+        <v>885</v>
+      </c>
+      <c r="K268" t="s">
+        <v>2555</v>
+      </c>
+      <c r="EN268" t="s">
+        <v>3573</v>
+      </c>
+      <c r="KV268">
+        <v>30</v>
+      </c>
+      <c r="KW268">
+        <v>15</v>
+      </c>
+      <c r="KX268">
+        <v>15</v>
+      </c>
+      <c r="KY268" t="s">
+        <v>3574</v>
+      </c>
+      <c r="LC268" t="s">
+        <v>3575</v>
+      </c>
+      <c r="LE268" t="s">
+        <v>843</v>
+      </c>
+      <c r="LF268" t="s">
+        <v>3584</v>
+      </c>
+      <c r="LG268" t="s">
+        <v>3598</v>
+      </c>
+      <c r="LH268" t="s">
+        <v>864</v>
+      </c>
+      <c r="LJ268" t="s">
+        <v>864</v>
+      </c>
+      <c r="LU268" t="s">
+        <v>848</v>
+      </c>
+      <c r="LV268" t="s">
+        <v>3588</v>
+      </c>
+      <c r="LW268" t="s">
+        <v>843</v>
+      </c>
+      <c r="LX268" t="s">
+        <v>843</v>
+      </c>
+      <c r="LY268" t="s">
+        <v>843</v>
+      </c>
+      <c r="LZ268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MB268" t="s">
+        <v>852</v>
+      </c>
+      <c r="MC268" t="s">
+        <v>3579</v>
+      </c>
+      <c r="MD268" t="s">
+        <v>843</v>
+      </c>
+      <c r="ME268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MF268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MG268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MI268" t="s">
+        <v>852</v>
+      </c>
+      <c r="MJ268" t="s">
+        <v>3582</v>
+      </c>
+      <c r="MK268" t="s">
+        <v>843</v>
+      </c>
+      <c r="ML268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MM268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MN268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MP268" t="s">
+        <v>848</v>
+      </c>
+      <c r="MQ268" t="s">
+        <v>3588</v>
+      </c>
+      <c r="MR268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MS268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MT268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MU268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MW268" t="s">
+        <v>852</v>
+      </c>
+      <c r="MX268" t="s">
+        <v>3579</v>
+      </c>
+      <c r="MY268" t="s">
+        <v>843</v>
+      </c>
+      <c r="MZ268" t="s">
+        <v>843</v>
+      </c>
+      <c r="NA268" t="s">
+        <v>843</v>
+      </c>
+      <c r="NB268" t="s">
+        <v>843</v>
+      </c>
+      <c r="ND268" t="s">
+        <v>848</v>
+      </c>
+      <c r="NE268" t="s">
+        <v>3582</v>
+      </c>
+      <c r="NF268" t="s">
+        <v>843</v>
+      </c>
+      <c r="NG268" t="s">
+        <v>843</v>
+      </c>
+      <c r="NH268" t="s">
+        <v>843</v>
+      </c>
+      <c r="NI268" t="s">
+        <v>843</v>
+      </c>
+      <c r="NJ268" t="s">
+        <v>3592</v>
+      </c>
+      <c r="NK268" t="s">
+        <v>4024</v>
+      </c>
+      <c r="NP268">
+        <v>183</v>
+      </c>
+      <c r="NQ268">
+        <v>182</v>
+      </c>
+      <c r="NS268">
+        <v>190</v>
+      </c>
+      <c r="NT268">
+        <v>187263</v>
+      </c>
+      <c r="NV268">
+        <v>263</v>
+      </c>
+      <c r="NW268">
+        <v>263</v>
+      </c>
+      <c r="SD268" s="1"/>
+      <c r="UH268" t="s">
+        <v>4028</v>
+      </c>
+      <c r="ZL268" s="1"/>
+      <c r="ADO268" s="1"/>
+      <c r="ADW268" s="1"/>
+      <c r="AEA268" s="1"/>
+      <c r="AEY268">
+        <v>895019329</v>
+      </c>
+      <c r="AEZ268" t="s">
+        <v>4029</v>
+      </c>
+      <c r="AFA268" s="1">
+        <v>46311.398576388892</v>
+      </c>
+      <c r="AFC268" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE268" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF268" t="s">
+        <v>4030</v>
+      </c>
+      <c r="AFG268">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A269" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B269" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D269" t="s">
+        <v>10</v>
+      </c>
+      <c r="E269" t="s">
+        <v>1804</v>
+      </c>
+      <c r="K269" t="s">
+        <v>1775</v>
+      </c>
+      <c r="NX269" t="s">
+        <v>4031</v>
+      </c>
+      <c r="NY269" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ269" t="s">
+        <v>4032</v>
+      </c>
+      <c r="OA269" t="s">
+        <v>864</v>
+      </c>
+      <c r="OS269">
+        <v>45</v>
+      </c>
+      <c r="OT269" t="s">
+        <v>887</v>
+      </c>
+      <c r="OV269">
+        <v>30</v>
+      </c>
+      <c r="OW269" t="s">
+        <v>887</v>
+      </c>
+      <c r="OY269">
+        <v>15</v>
+      </c>
+      <c r="OZ269" t="s">
+        <v>887</v>
+      </c>
+      <c r="PB269">
+        <v>18</v>
+      </c>
+      <c r="PC269" t="s">
+        <v>887</v>
+      </c>
+      <c r="PE269">
+        <v>0</v>
+      </c>
+      <c r="PF269" t="s">
+        <v>887</v>
+      </c>
+      <c r="PH269">
+        <v>0</v>
+      </c>
+      <c r="PI269" t="s">
+        <v>887</v>
+      </c>
+      <c r="PJ269" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL269" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM269" t="s">
+        <v>3321</v>
+      </c>
+      <c r="PN269" t="s">
+        <v>864</v>
+      </c>
+      <c r="PO269" t="s">
+        <v>1940</v>
+      </c>
+      <c r="PQ269" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR269" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS269">
+        <v>1</v>
+      </c>
+      <c r="PT269">
+        <v>1</v>
+      </c>
+      <c r="PU269">
+        <v>0</v>
+      </c>
+      <c r="PW269" t="s">
+        <v>4033</v>
+      </c>
+      <c r="PX269">
+        <v>0</v>
+      </c>
+      <c r="PY269">
+        <v>0</v>
+      </c>
+      <c r="PZ269">
+        <v>1</v>
+      </c>
+      <c r="QA269">
+        <v>1</v>
+      </c>
+      <c r="QJ269" t="s">
+        <v>1818</v>
+      </c>
+      <c r="QK269" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QL269" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM269" t="s">
+        <v>843</v>
+      </c>
+      <c r="QN269" t="s">
+        <v>852</v>
+      </c>
+      <c r="QP269" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QQ269" t="s">
+        <v>2166</v>
+      </c>
+      <c r="QR269" t="s">
+        <v>2147</v>
+      </c>
+      <c r="QS269" t="s">
+        <v>843</v>
+      </c>
+      <c r="QT269" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV269" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QW269" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QX269" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY269" t="s">
+        <v>843</v>
+      </c>
+      <c r="QZ269" t="s">
+        <v>848</v>
+      </c>
+      <c r="RA269" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB269" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC269" t="s">
+        <v>2751</v>
+      </c>
+      <c r="RD269">
+        <v>0</v>
+      </c>
+      <c r="RE269">
+        <v>0</v>
+      </c>
+      <c r="RF269">
+        <v>1</v>
+      </c>
+      <c r="RG269">
+        <v>1</v>
+      </c>
+      <c r="RH269">
+        <v>0</v>
+      </c>
+      <c r="RJ269" t="s">
+        <v>1969</v>
+      </c>
+      <c r="RK269">
+        <v>1</v>
+      </c>
+      <c r="RL269">
+        <v>1</v>
+      </c>
+      <c r="RM269">
+        <v>0</v>
+      </c>
+      <c r="RO269" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP269" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ269" t="s">
+        <v>2661</v>
+      </c>
+      <c r="RR269" t="s">
+        <v>3416</v>
+      </c>
+      <c r="RS269" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT269" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY269" t="s">
+        <v>4034</v>
+      </c>
+      <c r="RZ269" t="s">
+        <v>3330</v>
+      </c>
+      <c r="SA269" t="s">
+        <v>4035</v>
+      </c>
+      <c r="SB269" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD269" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH269" t="s">
+        <v>4036</v>
+      </c>
+      <c r="ZL269" s="1"/>
+      <c r="ADO269" s="1"/>
+      <c r="ADW269" s="1"/>
+      <c r="AEA269" s="1"/>
+      <c r="AEY269">
+        <v>895024993</v>
+      </c>
+      <c r="AEZ269" t="s">
+        <v>4037</v>
+      </c>
+      <c r="AFA269" s="1">
+        <v>46311.404618055552</v>
+      </c>
+      <c r="AFC269" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE269" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF269" t="s">
+        <v>4038</v>
+      </c>
+      <c r="AFG269">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A270" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B270" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D270" t="s">
+        <v>10</v>
+      </c>
+      <c r="E270" t="s">
+        <v>1804</v>
+      </c>
+      <c r="K270" t="s">
+        <v>1775</v>
+      </c>
+      <c r="NX270" t="s">
+        <v>4039</v>
+      </c>
+      <c r="NY270" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ270" t="s">
+        <v>4032</v>
+      </c>
+      <c r="OA270" t="s">
+        <v>864</v>
+      </c>
+      <c r="OS270">
+        <v>48</v>
+      </c>
+      <c r="OT270" t="s">
+        <v>887</v>
+      </c>
+      <c r="OV270">
+        <v>36</v>
+      </c>
+      <c r="OW270" t="s">
+        <v>887</v>
+      </c>
+      <c r="OY270">
+        <v>12</v>
+      </c>
+      <c r="OZ270" t="s">
+        <v>887</v>
+      </c>
+      <c r="PB270">
+        <v>18</v>
+      </c>
+      <c r="PC270" t="s">
+        <v>887</v>
+      </c>
+      <c r="PE270">
+        <v>2</v>
+      </c>
+      <c r="PF270" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PH270">
+        <v>0</v>
+      </c>
+      <c r="PI270" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PJ270" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL270" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM270" t="s">
+        <v>4040</v>
+      </c>
+      <c r="PN270" t="s">
+        <v>864</v>
+      </c>
+      <c r="PO270" t="s">
+        <v>1940</v>
+      </c>
+      <c r="PQ270" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR270" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS270">
+        <v>1</v>
+      </c>
+      <c r="PT270">
+        <v>1</v>
+      </c>
+      <c r="PU270">
+        <v>0</v>
+      </c>
+      <c r="PW270" t="s">
+        <v>2090</v>
+      </c>
+      <c r="PX270">
+        <v>1</v>
+      </c>
+      <c r="PY270">
+        <v>0</v>
+      </c>
+      <c r="PZ270">
+        <v>0</v>
+      </c>
+      <c r="QA270">
+        <v>1</v>
+      </c>
+      <c r="QJ270" t="s">
+        <v>1818</v>
+      </c>
+      <c r="QK270" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QL270" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM270" t="s">
+        <v>843</v>
+      </c>
+      <c r="QN270" t="s">
+        <v>852</v>
+      </c>
+      <c r="QP270" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QQ270" t="s">
+        <v>2166</v>
+      </c>
+      <c r="QR270" t="s">
+        <v>2147</v>
+      </c>
+      <c r="QS270" t="s">
+        <v>843</v>
+      </c>
+      <c r="QT270" t="s">
+        <v>852</v>
+      </c>
+      <c r="QV270" t="s">
+        <v>1818</v>
+      </c>
+      <c r="QW270" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QX270" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY270" t="s">
+        <v>843</v>
+      </c>
+      <c r="QZ270" t="s">
+        <v>848</v>
+      </c>
+      <c r="RA270" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB270" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC270" t="s">
+        <v>2751</v>
+      </c>
+      <c r="RD270">
+        <v>0</v>
+      </c>
+      <c r="RE270">
+        <v>0</v>
+      </c>
+      <c r="RF270">
+        <v>1</v>
+      </c>
+      <c r="RG270">
+        <v>1</v>
+      </c>
+      <c r="RH270">
+        <v>0</v>
+      </c>
+      <c r="RJ270" t="s">
+        <v>1969</v>
+      </c>
+      <c r="RK270">
+        <v>1</v>
+      </c>
+      <c r="RL270">
+        <v>1</v>
+      </c>
+      <c r="RM270">
+        <v>0</v>
+      </c>
+      <c r="RO270" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP270" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ270" t="s">
+        <v>2661</v>
+      </c>
+      <c r="RR270" t="s">
+        <v>3416</v>
+      </c>
+      <c r="RS270" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT270" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY270" t="s">
+        <v>4041</v>
+      </c>
+      <c r="RZ270" t="s">
+        <v>3330</v>
+      </c>
+      <c r="SA270" t="s">
+        <v>4042</v>
+      </c>
+      <c r="SB270" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD270" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH270" t="s">
+        <v>4043</v>
+      </c>
+      <c r="ZL270" s="1"/>
+      <c r="ADO270" s="1"/>
+      <c r="ADW270" s="1"/>
+      <c r="AEA270" s="1"/>
+      <c r="AEY270">
+        <v>895031516</v>
+      </c>
+      <c r="AEZ270" t="s">
+        <v>4044</v>
+      </c>
+      <c r="AFA270" s="1">
+        <v>46311.411504629628</v>
+      </c>
+      <c r="AFC270" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE270" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF270" t="s">
+        <v>4045</v>
+      </c>
+      <c r="AFG270">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A271" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B271" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D271" t="s">
+        <v>10</v>
+      </c>
+      <c r="E271" t="s">
+        <v>1804</v>
+      </c>
+      <c r="K271" t="s">
+        <v>1775</v>
+      </c>
+      <c r="NX271" t="s">
+        <v>4046</v>
+      </c>
+      <c r="NY271" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ271" t="s">
+        <v>4032</v>
+      </c>
+      <c r="OA271" t="s">
+        <v>864</v>
+      </c>
+      <c r="OS271">
+        <v>44</v>
+      </c>
+      <c r="OT271" t="s">
+        <v>887</v>
+      </c>
+      <c r="OV271">
+        <v>35</v>
+      </c>
+      <c r="OW271" t="s">
+        <v>887</v>
+      </c>
+      <c r="OY271">
+        <v>10</v>
+      </c>
+      <c r="OZ271" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PB271">
+        <v>22</v>
+      </c>
+      <c r="PC271" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PE271">
+        <v>0</v>
+      </c>
+      <c r="PF271" t="s">
+        <v>887</v>
+      </c>
+      <c r="PH271">
+        <v>1</v>
+      </c>
+      <c r="PI271" t="s">
+        <v>887</v>
+      </c>
+      <c r="PJ271" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL271" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM271" t="s">
+        <v>3305</v>
+      </c>
+      <c r="PN271" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO271" t="s">
+        <v>1940</v>
+      </c>
+      <c r="PQ271" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR271" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS271">
+        <v>1</v>
+      </c>
+      <c r="PT271">
+        <v>1</v>
+      </c>
+      <c r="PU271">
+        <v>0</v>
+      </c>
+      <c r="PW271" t="s">
+        <v>2090</v>
+      </c>
+      <c r="PX271">
+        <v>1</v>
+      </c>
+      <c r="PY271">
+        <v>0</v>
+      </c>
+      <c r="PZ271">
+        <v>0</v>
+      </c>
+      <c r="QA271">
+        <v>1</v>
+      </c>
+      <c r="QJ271" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QK271" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QL271" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM271" t="s">
+        <v>843</v>
+      </c>
+      <c r="QN271" t="s">
+        <v>852</v>
+      </c>
+      <c r="QP271" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QQ271" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QR271" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QS271" t="s">
+        <v>843</v>
+      </c>
+      <c r="QT271" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV271" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QW271" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QX271" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY271" t="s">
+        <v>843</v>
+      </c>
+      <c r="QZ271" t="s">
+        <v>852</v>
+      </c>
+      <c r="RA271" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB271" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC271" t="s">
+        <v>1968</v>
+      </c>
+      <c r="RD271">
+        <v>0</v>
+      </c>
+      <c r="RE271">
+        <v>1</v>
+      </c>
+      <c r="RF271">
+        <v>1</v>
+      </c>
+      <c r="RG271">
+        <v>1</v>
+      </c>
+      <c r="RH271">
+        <v>0</v>
+      </c>
+      <c r="RJ271" t="s">
+        <v>1969</v>
+      </c>
+      <c r="RK271">
+        <v>1</v>
+      </c>
+      <c r="RL271">
+        <v>1</v>
+      </c>
+      <c r="RM271">
+        <v>0</v>
+      </c>
+      <c r="RO271" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP271" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ271" t="s">
+        <v>2661</v>
+      </c>
+      <c r="RR271" t="s">
+        <v>3416</v>
+      </c>
+      <c r="RS271" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT271" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY271" t="s">
+        <v>4047</v>
+      </c>
+      <c r="RZ271" t="s">
+        <v>3442</v>
+      </c>
+      <c r="SA271" t="s">
+        <v>4048</v>
+      </c>
+      <c r="SB271" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD271" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH271" t="s">
+        <v>4049</v>
+      </c>
+      <c r="ZL271" s="1"/>
+      <c r="ADO271" s="1"/>
+      <c r="ADW271" s="1"/>
+      <c r="AEA271" s="1"/>
+      <c r="AEY271">
+        <v>895035011</v>
+      </c>
+      <c r="AEZ271" t="s">
+        <v>4050</v>
+      </c>
+      <c r="AFA271" s="1">
+        <v>46311.41510416667</v>
+      </c>
+      <c r="AFC271" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE271" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF271" t="s">
+        <v>4051</v>
+      </c>
+      <c r="AFG271">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A272" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B272" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D272" t="s">
+        <v>11</v>
+      </c>
+      <c r="E272" t="s">
+        <v>1804</v>
+      </c>
+      <c r="L272" t="s">
+        <v>1509</v>
+      </c>
+      <c r="NX272" t="s">
+        <v>4052</v>
+      </c>
+      <c r="NY272" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ272" t="s">
+        <v>4053</v>
+      </c>
+      <c r="OA272" t="s">
+        <v>843</v>
+      </c>
+      <c r="OB272" t="s">
+        <v>4054</v>
+      </c>
+      <c r="OC272">
+        <v>1</v>
+      </c>
+      <c r="OD272">
+        <v>1</v>
+      </c>
+      <c r="OE272">
+        <v>0</v>
+      </c>
+      <c r="OF272">
+        <v>1</v>
+      </c>
+      <c r="OG272">
+        <v>0</v>
+      </c>
+      <c r="OI272" t="s">
+        <v>3233</v>
+      </c>
+      <c r="OJ272">
+        <v>1</v>
+      </c>
+      <c r="OK272">
+        <v>1</v>
+      </c>
+      <c r="OL272">
+        <v>1</v>
+      </c>
+      <c r="OM272">
+        <v>0</v>
+      </c>
+      <c r="OS272">
+        <v>54</v>
+      </c>
+      <c r="OT272" t="s">
+        <v>3213</v>
+      </c>
+      <c r="OV272">
+        <v>7</v>
+      </c>
+      <c r="OW272" t="s">
+        <v>3213</v>
+      </c>
+      <c r="OY272">
+        <v>15</v>
+      </c>
+      <c r="OZ272" t="s">
+        <v>3213</v>
+      </c>
+      <c r="PB272">
+        <v>18</v>
+      </c>
+      <c r="PC272" t="s">
+        <v>3213</v>
+      </c>
+      <c r="PE272">
+        <v>4</v>
+      </c>
+      <c r="PF272" t="s">
+        <v>3213</v>
+      </c>
+      <c r="PH272">
+        <v>7</v>
+      </c>
+      <c r="PI272" t="s">
+        <v>3213</v>
+      </c>
+      <c r="PJ272" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL272" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM272" t="s">
+        <v>4055</v>
+      </c>
+      <c r="PN272" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO272" t="s">
+        <v>1863</v>
+      </c>
+      <c r="PQ272" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR272" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS272">
+        <v>1</v>
+      </c>
+      <c r="PT272">
+        <v>1</v>
+      </c>
+      <c r="PU272">
+        <v>0</v>
+      </c>
+      <c r="PW272" t="s">
+        <v>2025</v>
+      </c>
+      <c r="PX272">
+        <v>1</v>
+      </c>
+      <c r="PY272">
+        <v>1</v>
+      </c>
+      <c r="PZ272">
+        <v>1</v>
+      </c>
+      <c r="QA272">
+        <v>1</v>
+      </c>
+      <c r="QJ272" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QK272" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QL272" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM272" t="s">
+        <v>4056</v>
+      </c>
+      <c r="QN272" t="s">
+        <v>848</v>
+      </c>
+      <c r="QP272" t="s">
+        <v>1818</v>
+      </c>
+      <c r="QQ272" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QR272" t="s">
+        <v>1824</v>
+      </c>
+      <c r="QS272" t="s">
+        <v>4057</v>
+      </c>
+      <c r="QT272" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV272" t="s">
+        <v>1986</v>
+      </c>
+      <c r="QW272" t="s">
+        <v>2166</v>
+      </c>
+      <c r="QX272" t="s">
+        <v>2147</v>
+      </c>
+      <c r="QY272" t="s">
+        <v>4058</v>
+      </c>
+      <c r="QZ272" t="s">
+        <v>852</v>
+      </c>
+      <c r="RA272" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB272" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC272" t="s">
+        <v>2739</v>
+      </c>
+      <c r="RD272">
+        <v>1</v>
+      </c>
+      <c r="RE272">
+        <v>1</v>
+      </c>
+      <c r="RF272">
+        <v>1</v>
+      </c>
+      <c r="RG272">
+        <v>1</v>
+      </c>
+      <c r="RH272">
+        <v>1</v>
+      </c>
+      <c r="RI272" t="s">
+        <v>3218</v>
+      </c>
+      <c r="RJ272" t="s">
+        <v>1988</v>
+      </c>
+      <c r="RK272">
+        <v>1</v>
+      </c>
+      <c r="RL272">
+        <v>1</v>
+      </c>
+      <c r="RM272">
+        <v>1</v>
+      </c>
+      <c r="RN272" t="s">
+        <v>4059</v>
+      </c>
+      <c r="RO272" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP272" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ272" t="s">
+        <v>4060</v>
+      </c>
+      <c r="RR272" t="s">
+        <v>4061</v>
+      </c>
+      <c r="RS272" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT272" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY272" t="s">
+        <v>4062</v>
+      </c>
+      <c r="RZ272" t="s">
+        <v>4063</v>
+      </c>
+      <c r="SA272" t="s">
+        <v>4064</v>
+      </c>
+      <c r="SB272" t="s">
+        <v>843</v>
+      </c>
+      <c r="SC272" t="s">
+        <v>4065</v>
+      </c>
+      <c r="SD272" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH272" t="s">
+        <v>4066</v>
+      </c>
+      <c r="ZL272" s="1"/>
+      <c r="ADO272" s="1"/>
+      <c r="ADW272" s="1"/>
+      <c r="AEA272" s="1"/>
+      <c r="AEY272">
+        <v>895037210</v>
+      </c>
+      <c r="AEZ272" t="s">
+        <v>4067</v>
+      </c>
+      <c r="AFA272" s="1">
+        <v>46311.417326388888</v>
+      </c>
+      <c r="AFC272" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE272" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF272" t="s">
+        <v>4068</v>
+      </c>
+      <c r="AFG272">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A273" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B273" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D273" t="s">
+        <v>10</v>
+      </c>
+      <c r="E273" t="s">
+        <v>1804</v>
+      </c>
+      <c r="K273" t="s">
+        <v>1775</v>
+      </c>
+      <c r="NX273" t="s">
+        <v>4069</v>
+      </c>
+      <c r="NY273" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ273" t="s">
+        <v>4032</v>
+      </c>
+      <c r="OA273" t="s">
+        <v>864</v>
+      </c>
+      <c r="OS273">
+        <v>50</v>
+      </c>
+      <c r="OT273" t="s">
+        <v>887</v>
+      </c>
+      <c r="OV273">
+        <v>32</v>
+      </c>
+      <c r="OW273" t="s">
+        <v>887</v>
+      </c>
+      <c r="OY273">
+        <v>8</v>
+      </c>
+      <c r="OZ273" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PB273">
+        <v>12</v>
+      </c>
+      <c r="PC273" t="s">
+        <v>887</v>
+      </c>
+      <c r="PE273">
+        <v>0</v>
+      </c>
+      <c r="PF273" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PH273">
+        <v>0</v>
+      </c>
+      <c r="PI273" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PJ273" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL273" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM273" t="s">
+        <v>3321</v>
+      </c>
+      <c r="PN273" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO273" t="s">
+        <v>1940</v>
+      </c>
+      <c r="PQ273" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR273" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS273">
+        <v>1</v>
+      </c>
+      <c r="PT273">
+        <v>1</v>
+      </c>
+      <c r="PU273">
+        <v>0</v>
+      </c>
+      <c r="PW273" t="s">
+        <v>2090</v>
+      </c>
+      <c r="PX273">
+        <v>1</v>
+      </c>
+      <c r="PY273">
+        <v>0</v>
+      </c>
+      <c r="PZ273">
+        <v>0</v>
+      </c>
+      <c r="QA273">
+        <v>1</v>
+      </c>
+      <c r="QJ273" t="s">
+        <v>1841</v>
+      </c>
+      <c r="QK273" t="s">
+        <v>1842</v>
+      </c>
+      <c r="QL273" t="s">
+        <v>1824</v>
+      </c>
+      <c r="QM273" t="s">
+        <v>843</v>
+      </c>
+      <c r="QN273" t="s">
+        <v>852</v>
+      </c>
+      <c r="QP273" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QQ273" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QR273" t="s">
+        <v>1824</v>
+      </c>
+      <c r="QS273" t="s">
+        <v>843</v>
+      </c>
+      <c r="QT273" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV273" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QW273" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QX273" t="s">
+        <v>1824</v>
+      </c>
+      <c r="QY273" t="s">
+        <v>843</v>
+      </c>
+      <c r="QZ273" t="s">
+        <v>852</v>
+      </c>
+      <c r="RA273" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB273" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC273" t="s">
+        <v>2029</v>
+      </c>
+      <c r="RD273">
+        <v>1</v>
+      </c>
+      <c r="RE273">
+        <v>1</v>
+      </c>
+      <c r="RF273">
+        <v>1</v>
+      </c>
+      <c r="RG273">
+        <v>1</v>
+      </c>
+      <c r="RH273">
+        <v>0</v>
+      </c>
+      <c r="RJ273" t="s">
+        <v>1969</v>
+      </c>
+      <c r="RK273">
+        <v>1</v>
+      </c>
+      <c r="RL273">
+        <v>1</v>
+      </c>
+      <c r="RM273">
+        <v>0</v>
+      </c>
+      <c r="RO273" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP273" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ273" t="s">
+        <v>2661</v>
+      </c>
+      <c r="RR273" t="s">
+        <v>3416</v>
+      </c>
+      <c r="RS273" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT273" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY273" t="s">
+        <v>4070</v>
+      </c>
+      <c r="RZ273" t="s">
+        <v>3442</v>
+      </c>
+      <c r="SA273" t="s">
+        <v>4071</v>
+      </c>
+      <c r="SB273" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD273" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH273" t="s">
+        <v>4072</v>
+      </c>
+      <c r="ZL273" s="1"/>
+      <c r="ADO273" s="1"/>
+      <c r="ADW273" s="1"/>
+      <c r="AEA273" s="1"/>
+      <c r="AEY273">
+        <v>895039862</v>
+      </c>
+      <c r="AEZ273" t="s">
+        <v>4073</v>
+      </c>
+      <c r="AFA273" s="1">
+        <v>46311.420138888891</v>
+      </c>
+      <c r="AFC273" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE273" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF273" t="s">
+        <v>4074</v>
+      </c>
+      <c r="AFG273">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A274" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B274" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D274" t="s">
+        <v>10</v>
+      </c>
+      <c r="E274" t="s">
+        <v>1804</v>
+      </c>
+      <c r="K274" t="s">
+        <v>1775</v>
+      </c>
+      <c r="NX274" t="s">
+        <v>4075</v>
+      </c>
+      <c r="NY274" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ274" t="s">
+        <v>4032</v>
+      </c>
+      <c r="OA274" t="s">
+        <v>864</v>
+      </c>
+      <c r="OS274">
+        <v>47</v>
+      </c>
+      <c r="OT274" t="s">
+        <v>887</v>
+      </c>
+      <c r="OV274">
+        <v>39</v>
+      </c>
+      <c r="OW274" t="s">
+        <v>1243</v>
+      </c>
+      <c r="OY274">
+        <v>7</v>
+      </c>
+      <c r="OZ274" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PB274">
+        <v>14</v>
+      </c>
+      <c r="PC274" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PE274">
+        <v>2</v>
+      </c>
+      <c r="PF274" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PH274">
+        <v>1</v>
+      </c>
+      <c r="PI274" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PJ274" t="s">
+        <v>2277</v>
+      </c>
+      <c r="PL274" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM274" t="s">
+        <v>4076</v>
+      </c>
+      <c r="PN274" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO274" t="s">
+        <v>1940</v>
+      </c>
+      <c r="PQ274" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR274" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS274">
+        <v>1</v>
+      </c>
+      <c r="PT274">
+        <v>1</v>
+      </c>
+      <c r="PU274">
+        <v>0</v>
+      </c>
+      <c r="PW274" t="s">
+        <v>2090</v>
+      </c>
+      <c r="PX274">
+        <v>1</v>
+      </c>
+      <c r="PY274">
+        <v>0</v>
+      </c>
+      <c r="PZ274">
+        <v>0</v>
+      </c>
+      <c r="QA274">
+        <v>1</v>
+      </c>
+      <c r="QJ274" t="s">
+        <v>1818</v>
+      </c>
+      <c r="QK274" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QL274" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM274" t="s">
+        <v>843</v>
+      </c>
+      <c r="QN274" t="s">
+        <v>848</v>
+      </c>
+      <c r="QP274" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QQ274" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QR274" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QS274" t="s">
+        <v>843</v>
+      </c>
+      <c r="QT274" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV274" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QW274" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QX274" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY274" t="s">
+        <v>843</v>
+      </c>
+      <c r="QZ274" t="s">
+        <v>852</v>
+      </c>
+      <c r="RA274" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB274" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC274" t="s">
+        <v>1968</v>
+      </c>
+      <c r="RD274">
+        <v>0</v>
+      </c>
+      <c r="RE274">
+        <v>1</v>
+      </c>
+      <c r="RF274">
+        <v>1</v>
+      </c>
+      <c r="RG274">
+        <v>1</v>
+      </c>
+      <c r="RH274">
+        <v>0</v>
+      </c>
+      <c r="RJ274" t="s">
+        <v>1969</v>
+      </c>
+      <c r="RK274">
+        <v>1</v>
+      </c>
+      <c r="RL274">
+        <v>1</v>
+      </c>
+      <c r="RM274">
+        <v>0</v>
+      </c>
+      <c r="RO274" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP274" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ274" t="s">
+        <v>2661</v>
+      </c>
+      <c r="RR274" t="s">
+        <v>3416</v>
+      </c>
+      <c r="RS274" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT274" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY274" t="s">
+        <v>3630</v>
+      </c>
+      <c r="RZ274" t="s">
+        <v>3330</v>
+      </c>
+      <c r="SA274" t="s">
+        <v>4077</v>
+      </c>
+      <c r="SB274" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD274" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH274" t="s">
+        <v>4078</v>
+      </c>
+      <c r="ZL274" s="1"/>
+      <c r="ADO274" s="1"/>
+      <c r="ADW274" s="1"/>
+      <c r="AEA274" s="1"/>
+      <c r="AEY274">
+        <v>895043244</v>
+      </c>
+      <c r="AEZ274" t="s">
+        <v>4079</v>
+      </c>
+      <c r="AFA274" s="1">
+        <v>46311.423645833333</v>
+      </c>
+      <c r="AFC274" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE274" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF274" t="s">
+        <v>4080</v>
+      </c>
+      <c r="AFG274">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A275" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B275" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D275" t="s">
+        <v>11</v>
+      </c>
+      <c r="E275" t="s">
+        <v>1804</v>
+      </c>
+      <c r="L275" t="s">
+        <v>1509</v>
+      </c>
+      <c r="NX275" t="s">
+        <v>4052</v>
+      </c>
+      <c r="NY275" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ275" t="s">
+        <v>4081</v>
+      </c>
+      <c r="OA275" t="s">
+        <v>843</v>
+      </c>
+      <c r="OB275" t="s">
+        <v>3232</v>
+      </c>
+      <c r="OC275">
+        <v>0</v>
+      </c>
+      <c r="OD275">
+        <v>1</v>
+      </c>
+      <c r="OE275">
+        <v>0</v>
+      </c>
+      <c r="OF275">
+        <v>1</v>
+      </c>
+      <c r="OG275">
+        <v>0</v>
+      </c>
+      <c r="OI275" t="s">
+        <v>3233</v>
+      </c>
+      <c r="OJ275">
+        <v>1</v>
+      </c>
+      <c r="OK275">
+        <v>1</v>
+      </c>
+      <c r="OL275">
+        <v>1</v>
+      </c>
+      <c r="OM275">
+        <v>0</v>
+      </c>
+      <c r="OS275">
+        <v>48</v>
+      </c>
+      <c r="OT275" t="s">
+        <v>3213</v>
+      </c>
+      <c r="OV275">
+        <v>30</v>
+      </c>
+      <c r="OW275" t="s">
+        <v>3213</v>
+      </c>
+      <c r="OY275">
+        <v>8</v>
+      </c>
+      <c r="OZ275" t="s">
+        <v>3213</v>
+      </c>
+      <c r="PB275">
+        <v>10</v>
+      </c>
+      <c r="PC275" t="s">
+        <v>3213</v>
+      </c>
+      <c r="PE275">
+        <v>2</v>
+      </c>
+      <c r="PF275" t="s">
+        <v>3213</v>
+      </c>
+      <c r="PH275">
+        <v>7</v>
+      </c>
+      <c r="PI275" t="s">
+        <v>3213</v>
+      </c>
+      <c r="PJ275" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL275" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM275" t="s">
+        <v>4082</v>
+      </c>
+      <c r="PN275" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO275" t="s">
+        <v>1863</v>
+      </c>
+      <c r="PQ275" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR275" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS275">
+        <v>1</v>
+      </c>
+      <c r="PT275">
+        <v>1</v>
+      </c>
+      <c r="PU275">
+        <v>0</v>
+      </c>
+      <c r="PW275" t="s">
+        <v>1964</v>
+      </c>
+      <c r="PX275">
+        <v>1</v>
+      </c>
+      <c r="PY275">
+        <v>1</v>
+      </c>
+      <c r="PZ275">
+        <v>0</v>
+      </c>
+      <c r="QA275">
+        <v>1</v>
+      </c>
+      <c r="QJ275" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QK275" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QL275" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM275" t="s">
+        <v>4083</v>
+      </c>
+      <c r="QN275" t="s">
+        <v>848</v>
+      </c>
+      <c r="QP275" t="s">
+        <v>1818</v>
+      </c>
+      <c r="QQ275" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QR275" t="s">
+        <v>1824</v>
+      </c>
+      <c r="QS275" t="s">
+        <v>4084</v>
+      </c>
+      <c r="QT275" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV275" t="s">
+        <v>2044</v>
+      </c>
+      <c r="QW275" t="s">
+        <v>1842</v>
+      </c>
+      <c r="QX275" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY275" t="s">
+        <v>4085</v>
+      </c>
+      <c r="QZ275" t="s">
+        <v>848</v>
+      </c>
+      <c r="RA275" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB275" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC275" t="s">
+        <v>2739</v>
+      </c>
+      <c r="RD275">
+        <v>1</v>
+      </c>
+      <c r="RE275">
+        <v>1</v>
+      </c>
+      <c r="RF275">
+        <v>1</v>
+      </c>
+      <c r="RG275">
+        <v>1</v>
+      </c>
+      <c r="RH275">
+        <v>1</v>
+      </c>
+      <c r="RI275" t="s">
+        <v>4086</v>
+      </c>
+      <c r="RJ275" t="s">
+        <v>1969</v>
+      </c>
+      <c r="RK275">
+        <v>1</v>
+      </c>
+      <c r="RL275">
+        <v>1</v>
+      </c>
+      <c r="RM275">
+        <v>0</v>
+      </c>
+      <c r="RO275" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP275" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ275" t="s">
+        <v>4087</v>
+      </c>
+      <c r="RR275" t="s">
+        <v>3222</v>
+      </c>
+      <c r="RS275" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT275" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY275" t="s">
+        <v>4088</v>
+      </c>
+      <c r="RZ275" t="s">
+        <v>4089</v>
+      </c>
+      <c r="SA275" t="s">
+        <v>4090</v>
+      </c>
+      <c r="SB275" t="s">
+        <v>843</v>
+      </c>
+      <c r="SC275" t="s">
+        <v>4091</v>
+      </c>
+      <c r="SD275" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH275" t="s">
+        <v>4092</v>
+      </c>
+      <c r="ZL275" s="1"/>
+      <c r="ADO275" s="1"/>
+      <c r="ADW275" s="1"/>
+      <c r="AEA275" s="1"/>
+      <c r="AEY275">
+        <v>895048135</v>
+      </c>
+      <c r="AEZ275" t="s">
+        <v>4093</v>
+      </c>
+      <c r="AFA275" s="1">
+        <v>46311.429537037038</v>
+      </c>
+      <c r="AFC275" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE275" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF275" t="s">
+        <v>4094</v>
+      </c>
+      <c r="AFG275">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A276" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B276" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D276" t="s">
+        <v>10</v>
+      </c>
+      <c r="E276" t="s">
+        <v>1804</v>
+      </c>
+      <c r="K276" t="s">
+        <v>1775</v>
+      </c>
+      <c r="NX276" t="s">
+        <v>4095</v>
+      </c>
+      <c r="NY276" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ276" t="s">
+        <v>4032</v>
+      </c>
+      <c r="OA276" t="s">
+        <v>864</v>
+      </c>
+      <c r="OS276">
+        <v>44</v>
+      </c>
+      <c r="OT276" t="s">
+        <v>887</v>
+      </c>
+      <c r="OV276">
+        <v>39</v>
+      </c>
+      <c r="OW276" t="s">
+        <v>887</v>
+      </c>
+      <c r="OY276">
+        <v>7</v>
+      </c>
+      <c r="OZ276" t="s">
+        <v>887</v>
+      </c>
+      <c r="PB276">
+        <v>10</v>
+      </c>
+      <c r="PC276" t="s">
+        <v>887</v>
+      </c>
+      <c r="PE276">
+        <v>1</v>
+      </c>
+      <c r="PF276" t="s">
+        <v>887</v>
+      </c>
+      <c r="PH276">
+        <v>0</v>
+      </c>
+      <c r="PI276" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PJ276" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL276" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM276" t="s">
+        <v>4096</v>
+      </c>
+      <c r="PN276" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO276" t="s">
+        <v>1815</v>
+      </c>
+      <c r="PQ276" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR276" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS276">
+        <v>1</v>
+      </c>
+      <c r="PT276">
+        <v>1</v>
+      </c>
+      <c r="PU276">
+        <v>0</v>
+      </c>
+      <c r="PW276" t="s">
+        <v>2090</v>
+      </c>
+      <c r="PX276">
+        <v>1</v>
+      </c>
+      <c r="PY276">
+        <v>0</v>
+      </c>
+      <c r="PZ276">
+        <v>0</v>
+      </c>
+      <c r="QA276">
+        <v>1</v>
+      </c>
+      <c r="QJ276" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QK276" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QL276" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM276" t="s">
+        <v>843</v>
+      </c>
+      <c r="QN276" t="s">
+        <v>852</v>
+      </c>
+      <c r="QP276" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QQ276" t="s">
+        <v>1842</v>
+      </c>
+      <c r="QR276" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QS276" t="s">
+        <v>843</v>
+      </c>
+      <c r="QT276" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV276" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QW276" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QX276" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY276" t="s">
+        <v>843</v>
+      </c>
+      <c r="QZ276" t="s">
+        <v>848</v>
+      </c>
+      <c r="RA276" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB276" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC276" t="s">
+        <v>2751</v>
+      </c>
+      <c r="RD276">
+        <v>0</v>
+      </c>
+      <c r="RE276">
+        <v>0</v>
+      </c>
+      <c r="RF276">
+        <v>1</v>
+      </c>
+      <c r="RG276">
+        <v>1</v>
+      </c>
+      <c r="RH276">
+        <v>0</v>
+      </c>
+      <c r="RJ276" t="s">
+        <v>1969</v>
+      </c>
+      <c r="RK276">
+        <v>1</v>
+      </c>
+      <c r="RL276">
+        <v>1</v>
+      </c>
+      <c r="RM276">
+        <v>0</v>
+      </c>
+      <c r="RO276" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP276" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ276" t="s">
+        <v>2661</v>
+      </c>
+      <c r="RR276" t="s">
+        <v>3416</v>
+      </c>
+      <c r="RS276" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT276" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY276" t="s">
+        <v>4097</v>
+      </c>
+      <c r="RZ276" t="s">
+        <v>3442</v>
+      </c>
+      <c r="SA276" t="s">
+        <v>4098</v>
+      </c>
+      <c r="SB276" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD276" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH276" t="s">
+        <v>4099</v>
+      </c>
+      <c r="ZL276" s="1"/>
+      <c r="ADO276" s="1"/>
+      <c r="ADW276" s="1"/>
+      <c r="AEA276" s="1"/>
+      <c r="AEY276">
+        <v>895048437</v>
+      </c>
+      <c r="AEZ276" t="s">
+        <v>4100</v>
+      </c>
+      <c r="AFA276" s="1">
+        <v>46311.429907407408</v>
+      </c>
+      <c r="AFC276" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE276" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF276" t="s">
+        <v>4101</v>
+      </c>
+      <c r="AFG276">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A277" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B277" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D277" t="s">
+        <v>10</v>
+      </c>
+      <c r="E277" t="s">
+        <v>1804</v>
+      </c>
+      <c r="K277" t="s">
+        <v>1775</v>
+      </c>
+      <c r="NX277" t="s">
+        <v>4102</v>
+      </c>
+      <c r="NY277" t="s">
+        <v>1806</v>
+      </c>
+      <c r="NZ277" t="s">
+        <v>4032</v>
+      </c>
+      <c r="OA277" t="s">
+        <v>864</v>
+      </c>
+      <c r="OS277">
+        <v>45</v>
+      </c>
+      <c r="OT277" t="s">
+        <v>887</v>
+      </c>
+      <c r="OV277">
+        <v>36</v>
+      </c>
+      <c r="OW277" t="s">
+        <v>887</v>
+      </c>
+      <c r="OY277">
+        <v>2</v>
+      </c>
+      <c r="OZ277" t="s">
+        <v>887</v>
+      </c>
+      <c r="PB277">
+        <v>8</v>
+      </c>
+      <c r="PC277" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PE277">
+        <v>0</v>
+      </c>
+      <c r="PF277" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PH277">
+        <v>0</v>
+      </c>
+      <c r="PI277" t="s">
+        <v>1243</v>
+      </c>
+      <c r="PJ277" t="s">
+        <v>1813</v>
+      </c>
+      <c r="PL277" t="s">
+        <v>843</v>
+      </c>
+      <c r="PM277" t="s">
+        <v>4103</v>
+      </c>
+      <c r="PN277" t="s">
+        <v>843</v>
+      </c>
+      <c r="PO277" t="s">
+        <v>1815</v>
+      </c>
+      <c r="PQ277" t="s">
+        <v>1816</v>
+      </c>
+      <c r="PR277" t="s">
+        <v>1963</v>
+      </c>
+      <c r="PS277">
+        <v>1</v>
+      </c>
+      <c r="PT277">
+        <v>1</v>
+      </c>
+      <c r="PU277">
+        <v>0</v>
+      </c>
+      <c r="PW277" t="s">
+        <v>1817</v>
+      </c>
+      <c r="PX277">
+        <v>1</v>
+      </c>
+      <c r="PY277">
+        <v>0</v>
+      </c>
+      <c r="PZ277">
+        <v>0</v>
+      </c>
+      <c r="QA277">
+        <v>0</v>
+      </c>
+      <c r="QJ277" t="s">
+        <v>1818</v>
+      </c>
+      <c r="QK277" t="s">
+        <v>1823</v>
+      </c>
+      <c r="QL277" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QM277" t="s">
+        <v>843</v>
+      </c>
+      <c r="QN277" t="s">
+        <v>852</v>
+      </c>
+      <c r="QP277" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QQ277" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QR277" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QS277" t="s">
+        <v>843</v>
+      </c>
+      <c r="QT277" t="s">
+        <v>848</v>
+      </c>
+      <c r="QV277" t="s">
+        <v>1822</v>
+      </c>
+      <c r="QW277" t="s">
+        <v>1819</v>
+      </c>
+      <c r="QX277" t="s">
+        <v>1820</v>
+      </c>
+      <c r="QY277" t="s">
+        <v>843</v>
+      </c>
+      <c r="QZ277" t="s">
+        <v>848</v>
+      </c>
+      <c r="RA277" t="s">
+        <v>843</v>
+      </c>
+      <c r="RB277" t="s">
+        <v>843</v>
+      </c>
+      <c r="RC277" t="s">
+        <v>1968</v>
+      </c>
+      <c r="RD277">
+        <v>0</v>
+      </c>
+      <c r="RE277">
+        <v>1</v>
+      </c>
+      <c r="RF277">
+        <v>1</v>
+      </c>
+      <c r="RG277">
+        <v>1</v>
+      </c>
+      <c r="RH277">
+        <v>0</v>
+      </c>
+      <c r="RJ277" t="s">
+        <v>1969</v>
+      </c>
+      <c r="RK277">
+        <v>1</v>
+      </c>
+      <c r="RL277">
+        <v>1</v>
+      </c>
+      <c r="RM277">
+        <v>0</v>
+      </c>
+      <c r="RO277" t="s">
+        <v>1949</v>
+      </c>
+      <c r="RP277" t="s">
+        <v>843</v>
+      </c>
+      <c r="RQ277" t="s">
+        <v>2661</v>
+      </c>
+      <c r="RR277" t="s">
+        <v>3416</v>
+      </c>
+      <c r="RS277" t="s">
+        <v>843</v>
+      </c>
+      <c r="RT277" t="s">
+        <v>864</v>
+      </c>
+      <c r="RY277" t="s">
+        <v>4104</v>
+      </c>
+      <c r="RZ277" t="s">
+        <v>3442</v>
+      </c>
+      <c r="SA277" t="s">
+        <v>4105</v>
+      </c>
+      <c r="SB277" t="s">
+        <v>864</v>
+      </c>
+      <c r="SD277" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="UH277" t="s">
+        <v>4106</v>
+      </c>
+      <c r="ZL277" s="1"/>
+      <c r="ADO277" s="1"/>
+      <c r="ADW277" s="1"/>
+      <c r="AEA277" s="1"/>
+      <c r="AEY277">
+        <v>895051867</v>
+      </c>
+      <c r="AEZ277" t="s">
+        <v>4107</v>
+      </c>
+      <c r="AFA277" s="1">
+        <v>46311.433553240742</v>
+      </c>
+      <c r="AFC277" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE277" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF277" t="s">
+        <v>4108</v>
+      </c>
+      <c r="AFG277">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A278" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B278" t="s">
+        <v>884</v>
+      </c>
+      <c r="D278" t="s">
+        <v>8</v>
+      </c>
+      <c r="E278" t="s">
+        <v>871</v>
+      </c>
+      <c r="I278" t="s">
+        <v>2518</v>
+      </c>
+      <c r="SD278" s="1"/>
+      <c r="SV278" t="s">
+        <v>873</v>
+      </c>
+      <c r="SW278">
+        <v>1</v>
+      </c>
+      <c r="SX278">
+        <v>0</v>
+      </c>
+      <c r="SY278" t="s">
+        <v>4109</v>
+      </c>
+      <c r="SZ278">
+        <v>35</v>
+      </c>
+      <c r="TA278">
+        <v>27</v>
+      </c>
+      <c r="TB278" t="s">
+        <v>3166</v>
+      </c>
+      <c r="TC278" s="1">
+        <v>46301</v>
+      </c>
+      <c r="TD278" t="s">
+        <v>3364</v>
+      </c>
+      <c r="TE278" t="s">
+        <v>1912</v>
+      </c>
+      <c r="TF278">
+        <v>35</v>
+      </c>
+      <c r="TG278">
+        <v>27</v>
+      </c>
+      <c r="TH278">
+        <v>2</v>
+      </c>
+      <c r="TI278">
+        <v>1</v>
+      </c>
+      <c r="TJ278" t="s">
+        <v>4110</v>
+      </c>
+      <c r="TK278">
+        <v>0</v>
+      </c>
+      <c r="TL278">
+        <v>1</v>
+      </c>
+      <c r="TM278">
+        <v>1</v>
+      </c>
+      <c r="TN278">
+        <v>0</v>
+      </c>
+      <c r="TO278">
+        <v>0</v>
+      </c>
+      <c r="TP278" t="s">
+        <v>4111</v>
+      </c>
+      <c r="UH278" t="s">
+        <v>4112</v>
+      </c>
+      <c r="ZL278" s="1"/>
+      <c r="ADO278" s="1"/>
+      <c r="ADW278" s="1"/>
+      <c r="AEA278" s="1"/>
+      <c r="AEY278">
+        <v>895092347</v>
+      </c>
+      <c r="AEZ278" t="s">
+        <v>4113</v>
+      </c>
+      <c r="AFA278" s="1">
+        <v>46311.476805555547</v>
+      </c>
+      <c r="AFC278" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE278" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF278" t="s">
+        <v>4114</v>
+      </c>
+      <c r="AFG278">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A279" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B279" t="s">
+        <v>884</v>
+      </c>
+      <c r="D279" t="s">
+        <v>8</v>
+      </c>
+      <c r="E279" t="s">
+        <v>871</v>
+      </c>
+      <c r="I279" t="s">
+        <v>2518</v>
+      </c>
+      <c r="SD279" s="1"/>
+      <c r="SV279" t="s">
+        <v>1903</v>
+      </c>
+      <c r="SW279">
+        <v>0</v>
+      </c>
+      <c r="SX279">
+        <v>1</v>
+      </c>
+      <c r="TQ279" s="1">
+        <v>46304</v>
+      </c>
+      <c r="TR279" t="s">
+        <v>3364</v>
+      </c>
+      <c r="TS279" t="s">
+        <v>1912</v>
+      </c>
+      <c r="TT279">
+        <v>35</v>
+      </c>
+      <c r="TU279">
+        <v>27</v>
+      </c>
+      <c r="TV279">
+        <v>1</v>
+      </c>
+      <c r="TW279">
+        <v>2</v>
+      </c>
+      <c r="TX279" t="s">
+        <v>3091</v>
+      </c>
+      <c r="TY279">
+        <v>0</v>
+      </c>
+      <c r="TZ279">
+        <v>0</v>
+      </c>
+      <c r="UA279">
+        <v>0</v>
+      </c>
+      <c r="UB279">
+        <v>1</v>
+      </c>
+      <c r="UC279">
+        <v>1</v>
+      </c>
+      <c r="UD279" t="s">
+        <v>3531</v>
+      </c>
+      <c r="UE279" s="1">
+        <v>46311</v>
+      </c>
+      <c r="UF279" t="s">
+        <v>4115</v>
+      </c>
+      <c r="UG279" t="s">
+        <v>1908</v>
+      </c>
+      <c r="UH279" t="s">
+        <v>4116</v>
+      </c>
+      <c r="ZL279" s="1"/>
+      <c r="ADO279" s="1"/>
+      <c r="ADW279" s="1"/>
+      <c r="AEA279" s="1"/>
+      <c r="AEY279">
+        <v>895094680</v>
+      </c>
+      <c r="AEZ279" t="s">
+        <v>4117</v>
+      </c>
+      <c r="AFA279" s="1">
+        <v>46311.479583333326</v>
+      </c>
+      <c r="AFC279" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE279" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF279" t="s">
+        <v>4118</v>
+      </c>
+      <c r="AFG279">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A280" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B280" t="s">
+        <v>927</v>
+      </c>
+      <c r="D280" t="s">
+        <v>8</v>
+      </c>
+      <c r="E280" t="s">
+        <v>885</v>
+      </c>
+      <c r="I280" t="s">
+        <v>1556</v>
+      </c>
+      <c r="EN280" t="s">
+        <v>1038</v>
+      </c>
+      <c r="EO280">
+        <v>756</v>
+      </c>
+      <c r="EP280">
+        <v>602</v>
+      </c>
+      <c r="EQ280" t="s">
+        <v>843</v>
+      </c>
+      <c r="ER280" t="s">
+        <v>1258</v>
+      </c>
+      <c r="ES280">
+        <v>0</v>
+      </c>
+      <c r="ET280">
+        <v>0</v>
+      </c>
+      <c r="EU280">
+        <v>1</v>
+      </c>
+      <c r="EV280">
+        <v>0</v>
+      </c>
+      <c r="EW280">
+        <v>0</v>
+      </c>
+      <c r="EX280">
+        <v>0</v>
+      </c>
+      <c r="EZ280" t="s">
+        <v>843</v>
+      </c>
+      <c r="FA280">
+        <v>5</v>
+      </c>
+      <c r="FB280" t="s">
+        <v>1039</v>
+      </c>
+      <c r="FC280">
+        <v>1</v>
+      </c>
+      <c r="FD280">
+        <v>1</v>
+      </c>
+      <c r="FE280">
+        <v>1</v>
+      </c>
+      <c r="FF280" t="s">
+        <v>843</v>
+      </c>
+      <c r="FG280" t="s">
+        <v>3876</v>
+      </c>
+      <c r="FH280" t="s">
+        <v>864</v>
+      </c>
+      <c r="NP280">
+        <v>358</v>
+      </c>
+      <c r="NQ280">
+        <v>452</v>
+      </c>
+      <c r="NS280">
+        <v>231</v>
+      </c>
+      <c r="NT280">
+        <v>109</v>
+      </c>
+      <c r="NV280">
+        <v>65</v>
+      </c>
+      <c r="NW280">
+        <v>49</v>
+      </c>
+      <c r="SD280" s="1"/>
+      <c r="UH280" t="s">
+        <v>4119</v>
+      </c>
+      <c r="ZL280" s="1"/>
+      <c r="ADO280" s="1"/>
+      <c r="ADW280" s="1"/>
+      <c r="AEA280" s="1"/>
+      <c r="AEY280">
+        <v>895096824</v>
+      </c>
+      <c r="AEZ280" t="s">
+        <v>4120</v>
+      </c>
+      <c r="AFA280" s="1">
+        <v>46311.482048611113</v>
+      </c>
+      <c r="AFC280" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE280" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF280" t="s">
+        <v>4121</v>
+      </c>
+      <c r="AFG280">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A281" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B281" t="s">
+        <v>884</v>
+      </c>
+      <c r="D281" t="s">
+        <v>8</v>
+      </c>
+      <c r="E281" t="s">
+        <v>871</v>
+      </c>
+      <c r="I281" t="s">
+        <v>2518</v>
+      </c>
+      <c r="SD281" s="1"/>
+      <c r="SV281" t="s">
+        <v>873</v>
+      </c>
+      <c r="SW281">
+        <v>1</v>
+      </c>
+      <c r="SX281">
+        <v>0</v>
+      </c>
+      <c r="SY281" t="s">
+        <v>4122</v>
+      </c>
+      <c r="SZ281">
+        <v>37</v>
+      </c>
+      <c r="TA281">
+        <v>27</v>
+      </c>
+      <c r="TB281" t="s">
+        <v>4123</v>
+      </c>
+      <c r="TC281" s="1">
+        <v>46308</v>
+      </c>
+      <c r="TD281" t="s">
+        <v>3364</v>
+      </c>
+      <c r="TE281" t="s">
+        <v>4124</v>
+      </c>
+      <c r="TF281">
+        <v>37</v>
+      </c>
+      <c r="TG281">
+        <v>27</v>
+      </c>
+      <c r="TH281">
+        <v>2</v>
+      </c>
+      <c r="TI281">
+        <v>1</v>
+      </c>
+      <c r="TJ281" t="s">
+        <v>3486</v>
+      </c>
+      <c r="TK281">
+        <v>0</v>
+      </c>
+      <c r="TL281">
+        <v>1</v>
+      </c>
+      <c r="TM281">
+        <v>0</v>
+      </c>
+      <c r="TN281">
+        <v>1</v>
+      </c>
+      <c r="TO281">
+        <v>0</v>
+      </c>
+      <c r="TP281" t="s">
+        <v>4125</v>
+      </c>
+      <c r="UH281" t="s">
+        <v>4126</v>
+      </c>
+      <c r="ZL281" s="1"/>
+      <c r="ADO281" s="1"/>
+      <c r="ADW281" s="1"/>
+      <c r="AEA281" s="1"/>
+      <c r="AEY281">
+        <v>895097310</v>
+      </c>
+      <c r="AEZ281" t="s">
+        <v>4127</v>
+      </c>
+      <c r="AFA281" s="1">
+        <v>46311.482523148137</v>
+      </c>
+      <c r="AFC281" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE281" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF281" t="s">
+        <v>4128</v>
+      </c>
+      <c r="AFG281">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A282" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B282" t="s">
+        <v>884</v>
+      </c>
+      <c r="D282" t="s">
+        <v>8</v>
+      </c>
+      <c r="E282" t="s">
+        <v>871</v>
+      </c>
+      <c r="I282" t="s">
+        <v>2518</v>
+      </c>
+      <c r="SD282" s="1"/>
+      <c r="SV282" t="s">
+        <v>1903</v>
+      </c>
+      <c r="SW282">
+        <v>0</v>
+      </c>
+      <c r="SX282">
+        <v>1</v>
+      </c>
+      <c r="TQ282" s="1">
+        <v>46310</v>
+      </c>
+      <c r="TR282" t="s">
+        <v>4129</v>
+      </c>
+      <c r="TS282" t="s">
+        <v>4130</v>
+      </c>
+      <c r="TT282">
+        <v>985</v>
+      </c>
+      <c r="TU282">
+        <v>685</v>
+      </c>
+      <c r="TV282">
+        <v>12</v>
+      </c>
+      <c r="TW282">
+        <v>9</v>
+      </c>
+      <c r="TX282" t="s">
+        <v>3486</v>
+      </c>
+      <c r="TY282">
+        <v>0</v>
+      </c>
+      <c r="TZ282">
+        <v>1</v>
+      </c>
+      <c r="UA282">
+        <v>0</v>
+      </c>
+      <c r="UB282">
+        <v>1</v>
+      </c>
+      <c r="UC282">
+        <v>0</v>
+      </c>
+      <c r="UD282" t="s">
+        <v>1906</v>
+      </c>
+      <c r="UE282" s="1">
+        <v>46310</v>
+      </c>
+      <c r="UF282" t="s">
+        <v>4131</v>
+      </c>
+      <c r="UG282" t="s">
+        <v>1914</v>
+      </c>
+      <c r="UH282" t="s">
+        <v>4132</v>
+      </c>
+      <c r="ZL282" s="1"/>
+      <c r="ADO282" s="1"/>
+      <c r="ADW282" s="1"/>
+      <c r="AEA282" s="1"/>
+      <c r="AEY282">
+        <v>895100043</v>
+      </c>
+      <c r="AEZ282" t="s">
+        <v>4133</v>
+      </c>
+      <c r="AFA282" s="1">
+        <v>46311.485625000001</v>
+      </c>
+      <c r="AFC282" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE282" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF282" t="s">
+        <v>4134</v>
+      </c>
+      <c r="AFG282">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A283" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D283" t="s">
+        <v>13</v>
+      </c>
+      <c r="E283" t="s">
+        <v>871</v>
+      </c>
+      <c r="N283" t="s">
+        <v>1172</v>
+      </c>
+      <c r="SD283" s="1"/>
+      <c r="SV283" t="s">
+        <v>873</v>
+      </c>
+      <c r="SW283">
+        <v>1</v>
+      </c>
+      <c r="SX283">
+        <v>0</v>
+      </c>
+      <c r="SY283" t="s">
+        <v>4135</v>
+      </c>
+      <c r="SZ283">
+        <v>32</v>
+      </c>
+      <c r="TA283">
+        <v>32</v>
+      </c>
+      <c r="TB283" t="s">
+        <v>3519</v>
+      </c>
+      <c r="TC283" s="1">
+        <v>46303</v>
+      </c>
+      <c r="TD283" t="s">
+        <v>877</v>
+      </c>
+      <c r="TE283" t="s">
+        <v>1918</v>
+      </c>
+      <c r="TF283">
+        <v>32</v>
+      </c>
+      <c r="TG283">
+        <v>32</v>
+      </c>
+      <c r="TH283">
+        <v>2</v>
+      </c>
+      <c r="TI283">
+        <v>2</v>
+      </c>
+      <c r="TJ283" t="s">
+        <v>3065</v>
+      </c>
+      <c r="TK283">
+        <v>1</v>
+      </c>
+      <c r="TL283">
+        <v>0</v>
+      </c>
+      <c r="TM283">
+        <v>0</v>
+      </c>
+      <c r="TN283">
+        <v>0</v>
+      </c>
+      <c r="TO283">
+        <v>0</v>
+      </c>
+      <c r="TP283" t="s">
+        <v>4136</v>
+      </c>
+      <c r="UH283" t="s">
+        <v>1193</v>
+      </c>
+      <c r="ZL283" s="1"/>
+      <c r="ADO283" s="1"/>
+      <c r="ADW283" s="1"/>
+      <c r="AEA283" s="1"/>
+      <c r="AEY283">
+        <v>895105698</v>
+      </c>
+      <c r="AEZ283" t="s">
+        <v>4137</v>
+      </c>
+      <c r="AFA283" s="1">
+        <v>46311.491840277777</v>
+      </c>
+      <c r="AFC283" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE283" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF283" t="s">
+        <v>4138</v>
+      </c>
+      <c r="AFG283">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A284" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B284" t="s">
+        <v>927</v>
+      </c>
+      <c r="D284" t="s">
+        <v>8</v>
+      </c>
+      <c r="E284" t="s">
+        <v>885</v>
+      </c>
+      <c r="I284" t="s">
+        <v>1556</v>
+      </c>
+      <c r="EN284" t="s">
+        <v>886</v>
+      </c>
+      <c r="FT284">
+        <v>514</v>
+      </c>
+      <c r="FU284">
+        <v>251</v>
+      </c>
+      <c r="FV284">
+        <v>11</v>
+      </c>
+      <c r="FW284">
+        <v>9</v>
+      </c>
+      <c r="FY284">
+        <v>230</v>
+      </c>
+      <c r="FZ284">
+        <v>198</v>
+      </c>
+      <c r="GA284">
+        <v>7</v>
+      </c>
+      <c r="GB284">
+        <v>6</v>
+      </c>
+      <c r="GD284">
+        <v>235</v>
+      </c>
+      <c r="GE284">
+        <v>145</v>
+      </c>
+      <c r="GF284">
+        <v>3</v>
+      </c>
+      <c r="GG284">
+        <v>1</v>
+      </c>
+      <c r="GI284">
+        <v>6</v>
+      </c>
+      <c r="GJ284">
+        <v>5</v>
+      </c>
+      <c r="GK284">
+        <v>1</v>
+      </c>
+      <c r="GL284">
+        <v>0</v>
+      </c>
+      <c r="GN284">
+        <v>12</v>
+      </c>
+      <c r="GO284">
+        <v>37</v>
+      </c>
+      <c r="GP284">
+        <v>0</v>
+      </c>
+      <c r="GQ284">
+        <v>0</v>
+      </c>
+      <c r="GR284" t="s">
+        <v>975</v>
+      </c>
+      <c r="GS284">
+        <v>1</v>
+      </c>
+      <c r="GT284">
+        <v>0</v>
+      </c>
+      <c r="GU284">
+        <v>0</v>
+      </c>
+      <c r="GV284">
+        <v>1</v>
+      </c>
+      <c r="GW284">
+        <v>0</v>
+      </c>
+      <c r="GX284">
+        <v>0</v>
+      </c>
+      <c r="GY284">
+        <v>1</v>
+      </c>
+      <c r="GZ284" t="s">
+        <v>1348</v>
+      </c>
+      <c r="HA284">
+        <v>1</v>
+      </c>
+      <c r="HB284">
+        <v>1</v>
+      </c>
+      <c r="HC284">
+        <v>1</v>
+      </c>
+      <c r="HD284">
+        <v>1</v>
+      </c>
+      <c r="HE284">
+        <v>0</v>
+      </c>
+      <c r="HG284" t="s">
+        <v>843</v>
+      </c>
+      <c r="HH284" t="s">
+        <v>4139</v>
+      </c>
+      <c r="HI284" t="s">
+        <v>843</v>
+      </c>
+      <c r="HJ284" t="s">
+        <v>864</v>
+      </c>
+      <c r="HL284" t="s">
+        <v>843</v>
+      </c>
+      <c r="HM284" t="s">
+        <v>4140</v>
+      </c>
+      <c r="HT284" t="s">
+        <v>1219</v>
+      </c>
+      <c r="HU284">
+        <v>3</v>
+      </c>
+      <c r="HV284" t="s">
+        <v>4141</v>
+      </c>
+      <c r="HX284" t="s">
+        <v>893</v>
+      </c>
+      <c r="HY284">
+        <v>3</v>
+      </c>
+      <c r="HZ284" t="s">
+        <v>4142</v>
+      </c>
+      <c r="IB284" t="s">
+        <v>893</v>
+      </c>
+      <c r="IC284">
+        <v>3</v>
+      </c>
+      <c r="ID284" t="s">
+        <v>4143</v>
+      </c>
+      <c r="IF284" t="s">
+        <v>893</v>
+      </c>
+      <c r="IG284">
+        <v>3</v>
+      </c>
+      <c r="IH284" t="s">
+        <v>4143</v>
+      </c>
+      <c r="IJ284" t="s">
+        <v>892</v>
+      </c>
+      <c r="IK284">
+        <v>3</v>
+      </c>
+      <c r="IL284" t="s">
+        <v>4144</v>
+      </c>
+      <c r="IV284" t="s">
+        <v>895</v>
+      </c>
+      <c r="IW284" t="s">
+        <v>896</v>
+      </c>
+      <c r="IX284" t="s">
+        <v>4144</v>
+      </c>
+      <c r="IY284" t="s">
+        <v>982</v>
+      </c>
+      <c r="IZ284" t="s">
+        <v>4144</v>
+      </c>
+      <c r="JA284" t="s">
+        <v>852</v>
+      </c>
+      <c r="JC284" t="s">
+        <v>995</v>
+      </c>
+      <c r="JD284" t="s">
+        <v>1187</v>
+      </c>
+      <c r="JE284" t="s">
+        <v>4145</v>
+      </c>
+      <c r="JF284" t="s">
+        <v>982</v>
+      </c>
+      <c r="JG284" t="s">
+        <v>4144</v>
+      </c>
+      <c r="JH284" t="s">
+        <v>848</v>
+      </c>
+      <c r="JJ284" t="s">
+        <v>984</v>
+      </c>
+      <c r="JK284" t="s">
+        <v>896</v>
+      </c>
+      <c r="JL284" t="s">
+        <v>4144</v>
+      </c>
+      <c r="JM284" t="s">
+        <v>982</v>
+      </c>
+      <c r="JN284" t="s">
+        <v>4144</v>
+      </c>
+      <c r="JO284" t="s">
+        <v>848</v>
+      </c>
+      <c r="JQ284" t="s">
+        <v>984</v>
+      </c>
+      <c r="JR284" t="s">
+        <v>985</v>
+      </c>
+      <c r="JS284" t="s">
+        <v>1380</v>
+      </c>
+      <c r="JT284" t="s">
+        <v>982</v>
+      </c>
+      <c r="JU284" t="s">
+        <v>1380</v>
+      </c>
+      <c r="JV284" t="s">
+        <v>852</v>
+      </c>
+      <c r="JX284" t="s">
+        <v>995</v>
+      </c>
+      <c r="JY284" t="s">
+        <v>985</v>
+      </c>
+      <c r="JZ284" t="s">
+        <v>4146</v>
+      </c>
+      <c r="KA284" t="s">
+        <v>982</v>
+      </c>
+      <c r="KB284" t="s">
+        <v>1380</v>
+      </c>
+      <c r="KC284" t="s">
+        <v>848</v>
+      </c>
+      <c r="KE284" t="s">
+        <v>984</v>
+      </c>
+      <c r="KF284" t="s">
+        <v>985</v>
+      </c>
+      <c r="KG284" t="s">
+        <v>1380</v>
+      </c>
+      <c r="KH284" t="s">
+        <v>982</v>
+      </c>
+      <c r="KI284" t="s">
+        <v>1380</v>
+      </c>
+      <c r="KJ284" t="s">
+        <v>852</v>
+      </c>
+      <c r="KK284" t="s">
+        <v>1192</v>
+      </c>
+      <c r="KL284">
+        <v>0</v>
+      </c>
+      <c r="KM284">
+        <v>0</v>
+      </c>
+      <c r="KN284">
+        <v>1</v>
+      </c>
+      <c r="KO284">
+        <v>0</v>
+      </c>
+      <c r="KP284">
+        <v>0</v>
+      </c>
+      <c r="KR284" t="s">
+        <v>4147</v>
+      </c>
+      <c r="KS284" t="s">
+        <v>4148</v>
+      </c>
+      <c r="KT284" t="s">
+        <v>4149</v>
+      </c>
+      <c r="KU284" t="s">
+        <v>4150</v>
+      </c>
+      <c r="NP284">
+        <v>235</v>
+      </c>
+      <c r="NQ284">
+        <v>358</v>
+      </c>
+      <c r="NS284">
+        <v>245</v>
+      </c>
+      <c r="NT284">
+        <v>123</v>
+      </c>
+      <c r="NV284">
+        <v>201</v>
+      </c>
+      <c r="NW284">
+        <v>156</v>
+      </c>
+      <c r="SD284" s="1"/>
+      <c r="UH284" t="s">
+        <v>4151</v>
+      </c>
+      <c r="ZL284" s="1"/>
+      <c r="ADO284" s="1"/>
+      <c r="ADW284" s="1"/>
+      <c r="AEA284" s="1"/>
+      <c r="AEY284">
+        <v>895107911</v>
+      </c>
+      <c r="AEZ284" t="s">
+        <v>4152</v>
+      </c>
+      <c r="AFA284" s="1">
+        <v>46311.494166666656</v>
+      </c>
+      <c r="AFC284" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE284" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF284" t="s">
+        <v>4153</v>
+      </c>
+      <c r="AFG284">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A285" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D285" t="s">
+        <v>13</v>
+      </c>
+      <c r="E285" t="s">
+        <v>871</v>
+      </c>
+      <c r="N285" t="s">
+        <v>1172</v>
+      </c>
+      <c r="SD285" s="1"/>
+      <c r="SV285" t="s">
+        <v>873</v>
+      </c>
+      <c r="SW285">
+        <v>1</v>
+      </c>
+      <c r="SX285">
+        <v>0</v>
+      </c>
+      <c r="SY285" t="s">
+        <v>4154</v>
+      </c>
+      <c r="SZ285">
+        <v>30</v>
+      </c>
+      <c r="TA285">
+        <v>28</v>
+      </c>
+      <c r="TB285" t="s">
+        <v>3519</v>
+      </c>
+      <c r="TC285" s="1">
+        <v>46308</v>
+      </c>
+      <c r="TD285" t="s">
+        <v>877</v>
+      </c>
+      <c r="TE285" t="s">
+        <v>1918</v>
+      </c>
+      <c r="TF285">
+        <v>30</v>
+      </c>
+      <c r="TG285">
+        <v>28</v>
+      </c>
+      <c r="TH285">
+        <v>2</v>
+      </c>
+      <c r="TI285">
+        <v>2</v>
+      </c>
+      <c r="TJ285" t="s">
+        <v>3337</v>
+      </c>
+      <c r="TK285">
+        <v>1</v>
+      </c>
+      <c r="TL285">
+        <v>0</v>
+      </c>
+      <c r="TM285">
+        <v>0</v>
+      </c>
+      <c r="TN285">
+        <v>1</v>
+      </c>
+      <c r="TO285">
+        <v>0</v>
+      </c>
+      <c r="TP285" t="s">
+        <v>4155</v>
+      </c>
+      <c r="UH285" t="s">
+        <v>4156</v>
+      </c>
+      <c r="ZL285" s="1"/>
+      <c r="ADO285" s="1"/>
+      <c r="ADW285" s="1"/>
+      <c r="AEA285" s="1"/>
+      <c r="AEY285">
+        <v>895108445</v>
+      </c>
+      <c r="AEZ285" t="s">
+        <v>4157</v>
+      </c>
+      <c r="AFA285" s="1">
+        <v>46311.494652777779</v>
+      </c>
+      <c r="AFC285" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE285" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF285" t="s">
+        <v>4158</v>
+      </c>
+      <c r="AFG285">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A286" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D286" t="s">
+        <v>13</v>
+      </c>
+      <c r="E286" t="s">
+        <v>871</v>
+      </c>
+      <c r="N286" t="s">
+        <v>1172</v>
+      </c>
+      <c r="SD286" s="1"/>
+      <c r="SV286" t="s">
+        <v>1903</v>
+      </c>
+      <c r="SW286">
+        <v>0</v>
+      </c>
+      <c r="SX286">
+        <v>1</v>
+      </c>
+      <c r="TQ286" s="1">
+        <v>46310</v>
+      </c>
+      <c r="TR286" t="s">
+        <v>877</v>
+      </c>
+      <c r="TS286" t="s">
+        <v>1918</v>
+      </c>
+      <c r="TT286">
+        <v>32</v>
+      </c>
+      <c r="TU286">
+        <v>32</v>
+      </c>
+      <c r="TV286">
+        <v>2</v>
+      </c>
+      <c r="TW286">
+        <v>2</v>
+      </c>
+      <c r="TX286" t="s">
+        <v>1551</v>
+      </c>
+      <c r="TY286">
+        <v>0</v>
+      </c>
+      <c r="TZ286">
+        <v>0</v>
+      </c>
+      <c r="UA286">
+        <v>1</v>
+      </c>
+      <c r="UB286">
+        <v>0</v>
+      </c>
+      <c r="UC286">
+        <v>0</v>
+      </c>
+      <c r="UD286" t="s">
+        <v>2343</v>
+      </c>
+      <c r="UE286" s="1">
+        <v>46311</v>
+      </c>
+      <c r="UF286" t="s">
+        <v>4159</v>
+      </c>
+      <c r="UG286" t="s">
+        <v>1908</v>
+      </c>
+      <c r="UH286" t="s">
+        <v>1193</v>
+      </c>
+      <c r="ZL286" s="1"/>
+      <c r="ADO286" s="1"/>
+      <c r="ADW286" s="1"/>
+      <c r="AEA286" s="1"/>
+      <c r="AEY286">
+        <v>895110587</v>
+      </c>
+      <c r="AEZ286" t="s">
+        <v>4160</v>
+      </c>
+      <c r="AFA286" s="1">
+        <v>46311.49722222222</v>
+      </c>
+      <c r="AFC286" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE286" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF286" t="s">
+        <v>4161</v>
+      </c>
+      <c r="AFG286">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A287" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B287" t="s">
+        <v>927</v>
+      </c>
+      <c r="D287" t="s">
+        <v>8</v>
+      </c>
+      <c r="E287" t="s">
+        <v>885</v>
+      </c>
+      <c r="I287" t="s">
+        <v>1097</v>
+      </c>
+      <c r="EN287" t="s">
+        <v>1038</v>
+      </c>
+      <c r="EO287">
+        <v>956</v>
+      </c>
+      <c r="EP287">
+        <v>602</v>
+      </c>
+      <c r="EQ287" t="s">
+        <v>843</v>
+      </c>
+      <c r="ER287" t="s">
+        <v>1142</v>
+      </c>
+      <c r="ES287">
+        <v>0</v>
+      </c>
+      <c r="ET287">
+        <v>0</v>
+      </c>
+      <c r="EU287">
+        <v>0</v>
+      </c>
+      <c r="EV287">
+        <v>1</v>
+      </c>
+      <c r="EW287">
+        <v>0</v>
+      </c>
+      <c r="EX287">
+        <v>0</v>
+      </c>
+      <c r="EZ287" t="s">
+        <v>843</v>
+      </c>
+      <c r="FA287">
+        <v>5</v>
+      </c>
+      <c r="FB287" t="s">
+        <v>1039</v>
+      </c>
+      <c r="FC287">
+        <v>1</v>
+      </c>
+      <c r="FD287">
+        <v>1</v>
+      </c>
+      <c r="FE287">
+        <v>1</v>
+      </c>
+      <c r="FF287" t="s">
+        <v>843</v>
+      </c>
+      <c r="FG287" t="s">
+        <v>4162</v>
+      </c>
+      <c r="FH287" t="s">
+        <v>843</v>
+      </c>
+      <c r="FI287">
+        <v>0</v>
+      </c>
+      <c r="FJ287" t="s">
+        <v>839</v>
+      </c>
+      <c r="FK287">
+        <v>0</v>
+      </c>
+      <c r="FL287">
+        <v>1</v>
+      </c>
+      <c r="NP287">
+        <v>258</v>
+      </c>
+      <c r="NQ287">
+        <v>123</v>
+      </c>
+      <c r="NS287">
+        <v>365</v>
+      </c>
+      <c r="NT287">
+        <v>123</v>
+      </c>
+      <c r="NV287">
+        <v>369</v>
+      </c>
+      <c r="NW287">
+        <v>258</v>
+      </c>
+      <c r="SD287" s="1"/>
+      <c r="UH287" t="s">
+        <v>4163</v>
+      </c>
+      <c r="ZL287" s="1"/>
+      <c r="ADO287" s="1"/>
+      <c r="ADW287" s="1"/>
+      <c r="AEA287" s="1"/>
+      <c r="AEY287">
+        <v>895110821</v>
+      </c>
+      <c r="AEZ287" t="s">
+        <v>4164</v>
+      </c>
+      <c r="AFA287" s="1">
+        <v>46311.497511574067</v>
+      </c>
+      <c r="AFC287" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE287" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF287" t="s">
+        <v>4165</v>
+      </c>
+      <c r="AFG287">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A288" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B288" t="s">
+        <v>927</v>
+      </c>
+      <c r="D288" t="s">
+        <v>8</v>
+      </c>
+      <c r="E288" t="s">
+        <v>885</v>
+      </c>
+      <c r="I288" t="s">
+        <v>1732</v>
+      </c>
+      <c r="EN288" t="s">
+        <v>1038</v>
+      </c>
+      <c r="EO288">
+        <v>1012</v>
+      </c>
+      <c r="EP288">
+        <v>827</v>
+      </c>
+      <c r="EQ288" t="s">
+        <v>843</v>
+      </c>
+      <c r="ER288" t="s">
+        <v>4166</v>
+      </c>
+      <c r="ES288">
+        <v>1</v>
+      </c>
+      <c r="ET288">
+        <v>0</v>
+      </c>
+      <c r="EU288">
+        <v>0</v>
+      </c>
+      <c r="EV288">
+        <v>0</v>
+      </c>
+      <c r="EW288">
+        <v>0</v>
+      </c>
+      <c r="EX288">
+        <v>0</v>
+      </c>
+      <c r="EZ288" t="s">
+        <v>843</v>
+      </c>
+      <c r="FA288">
+        <v>5</v>
+      </c>
+      <c r="FB288" t="s">
+        <v>1039</v>
+      </c>
+      <c r="FC288">
+        <v>1</v>
+      </c>
+      <c r="FD288">
+        <v>1</v>
+      </c>
+      <c r="FE288">
+        <v>1</v>
+      </c>
+      <c r="FF288" t="s">
+        <v>843</v>
+      </c>
+      <c r="FG288" t="s">
+        <v>4167</v>
+      </c>
+      <c r="FH288" t="s">
+        <v>843</v>
+      </c>
+      <c r="FI288">
+        <v>0</v>
+      </c>
+      <c r="FJ288" t="s">
+        <v>839</v>
+      </c>
+      <c r="FK288">
+        <v>0</v>
+      </c>
+      <c r="FL288">
+        <v>1</v>
+      </c>
+      <c r="NP288">
+        <v>312</v>
+      </c>
+      <c r="NQ288">
+        <v>245</v>
+      </c>
+      <c r="NS288">
+        <v>234</v>
+      </c>
+      <c r="NT288">
+        <v>125</v>
+      </c>
+      <c r="NV288">
+        <v>201</v>
+      </c>
+      <c r="NW288">
+        <v>542</v>
+      </c>
+      <c r="SD288" s="1"/>
+      <c r="UH288" t="s">
+        <v>4168</v>
+      </c>
+      <c r="ZL288" s="1"/>
+      <c r="ADO288" s="1"/>
+      <c r="ADW288" s="1"/>
+      <c r="AEA288" s="1"/>
+      <c r="AEY288">
+        <v>895113578</v>
+      </c>
+      <c r="AEZ288" t="s">
+        <v>4169</v>
+      </c>
+      <c r="AFA288" s="1">
+        <v>46311.500462962962</v>
+      </c>
+      <c r="AFC288" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE288" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF288" t="s">
+        <v>4170</v>
+      </c>
+      <c r="AFG288">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A289" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B289" t="s">
+        <v>927</v>
+      </c>
+      <c r="D289" t="s">
+        <v>8</v>
+      </c>
+      <c r="E289" t="s">
+        <v>885</v>
+      </c>
+      <c r="I289" t="s">
+        <v>1740</v>
+      </c>
+      <c r="EN289" t="s">
+        <v>1038</v>
+      </c>
+      <c r="EO289">
+        <v>589</v>
+      </c>
+      <c r="EP289">
+        <v>427</v>
+      </c>
+      <c r="EQ289" t="s">
+        <v>843</v>
+      </c>
+      <c r="ER289" t="s">
+        <v>1258</v>
+      </c>
+      <c r="ES289">
+        <v>0</v>
+      </c>
+      <c r="ET289">
+        <v>0</v>
+      </c>
+      <c r="EU289">
+        <v>1</v>
+      </c>
+      <c r="EV289">
+        <v>0</v>
+      </c>
+      <c r="EW289">
+        <v>0</v>
+      </c>
+      <c r="EX289">
+        <v>0</v>
+      </c>
+      <c r="EZ289" t="s">
+        <v>843</v>
+      </c>
+      <c r="FA289">
+        <v>5</v>
+      </c>
+      <c r="FB289" t="s">
+        <v>1039</v>
+      </c>
+      <c r="FC289">
+        <v>1</v>
+      </c>
+      <c r="FD289">
+        <v>1</v>
+      </c>
+      <c r="FE289">
+        <v>1</v>
+      </c>
+      <c r="FF289" t="s">
+        <v>843</v>
+      </c>
+      <c r="FG289" t="s">
+        <v>3876</v>
+      </c>
+      <c r="FH289" t="s">
+        <v>843</v>
+      </c>
+      <c r="FI289">
+        <v>0</v>
+      </c>
+      <c r="FJ289" t="s">
+        <v>839</v>
+      </c>
+      <c r="FK289">
+        <v>0</v>
+      </c>
+      <c r="FL289">
+        <v>1</v>
+      </c>
+      <c r="NP289">
+        <v>231</v>
+      </c>
+      <c r="NQ289">
+        <v>189</v>
+      </c>
+      <c r="NS289">
+        <v>101</v>
+      </c>
+      <c r="NT289">
+        <v>256</v>
+      </c>
+      <c r="NV289">
+        <v>109</v>
+      </c>
+      <c r="NW289">
+        <v>98</v>
+      </c>
+      <c r="SD289" s="1"/>
+      <c r="UH289" t="s">
+        <v>4171</v>
+      </c>
+      <c r="ZL289" s="1"/>
+      <c r="ADO289" s="1"/>
+      <c r="ADW289" s="1"/>
+      <c r="AEA289" s="1"/>
+      <c r="AEY289">
+        <v>895116027</v>
+      </c>
+      <c r="AEZ289" t="s">
+        <v>4172</v>
+      </c>
+      <c r="AFA289" s="1">
+        <v>46311.503182870372</v>
+      </c>
+      <c r="AFC289" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE289" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF289" t="s">
+        <v>4173</v>
+      </c>
+      <c r="AFG289">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A290" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B290" t="s">
+        <v>927</v>
+      </c>
+      <c r="D290" t="s">
+        <v>8</v>
+      </c>
+      <c r="E290" t="s">
+        <v>885</v>
+      </c>
+      <c r="I290" t="s">
+        <v>1546</v>
+      </c>
+      <c r="EN290" t="s">
+        <v>1038</v>
+      </c>
+      <c r="EO290">
+        <v>1212</v>
+      </c>
+      <c r="EP290">
+        <v>927</v>
+      </c>
+      <c r="EQ290" t="s">
+        <v>843</v>
+      </c>
+      <c r="ER290" t="s">
+        <v>1142</v>
+      </c>
+      <c r="ES290">
+        <v>0</v>
+      </c>
+      <c r="ET290">
+        <v>0</v>
+      </c>
+      <c r="EU290">
+        <v>0</v>
+      </c>
+      <c r="EV290">
+        <v>1</v>
+      </c>
+      <c r="EW290">
+        <v>0</v>
+      </c>
+      <c r="EX290">
+        <v>0</v>
+      </c>
+      <c r="EZ290" t="s">
+        <v>843</v>
+      </c>
+      <c r="FA290">
+        <v>5</v>
+      </c>
+      <c r="FB290" t="s">
+        <v>1039</v>
+      </c>
+      <c r="FC290">
+        <v>1</v>
+      </c>
+      <c r="FD290">
+        <v>1</v>
+      </c>
+      <c r="FE290">
+        <v>1</v>
+      </c>
+      <c r="FF290" t="s">
+        <v>843</v>
+      </c>
+      <c r="FG290" t="s">
+        <v>3876</v>
+      </c>
+      <c r="FH290" t="s">
+        <v>843</v>
+      </c>
+      <c r="FI290">
+        <v>0</v>
+      </c>
+      <c r="FJ290" t="s">
+        <v>839</v>
+      </c>
+      <c r="FK290">
+        <v>0</v>
+      </c>
+      <c r="FL290">
+        <v>1</v>
+      </c>
+      <c r="NP290">
+        <v>324</v>
+      </c>
+      <c r="NQ290">
+        <v>501</v>
+      </c>
+      <c r="NS290">
+        <v>211</v>
+      </c>
+      <c r="NT290">
+        <v>207</v>
+      </c>
+      <c r="NV290">
+        <v>241</v>
+      </c>
+      <c r="NW290">
+        <v>117</v>
+      </c>
+      <c r="SD290" s="1"/>
+      <c r="UH290" t="s">
+        <v>4171</v>
+      </c>
+      <c r="ZL290" s="1"/>
+      <c r="ADO290" s="1"/>
+      <c r="ADW290" s="1"/>
+      <c r="AEA290" s="1"/>
+      <c r="AEY290">
+        <v>895117406</v>
+      </c>
+      <c r="AEZ290" t="s">
+        <v>4174</v>
+      </c>
+      <c r="AFA290" s="1">
+        <v>46311.504791666674</v>
+      </c>
+      <c r="AFC290" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE290" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF290" t="s">
+        <v>4175</v>
+      </c>
+      <c r="AFG290">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A291" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B291" t="s">
+        <v>884</v>
+      </c>
+      <c r="D291" t="s">
+        <v>8</v>
+      </c>
+      <c r="E291" t="s">
+        <v>871</v>
+      </c>
+      <c r="I291" t="s">
+        <v>928</v>
+      </c>
+      <c r="SD291" s="1"/>
+      <c r="SV291" t="s">
+        <v>873</v>
+      </c>
+      <c r="SW291">
+        <v>1</v>
+      </c>
+      <c r="SX291">
+        <v>0</v>
+      </c>
+      <c r="SY291" t="s">
+        <v>4176</v>
+      </c>
+      <c r="SZ291">
+        <v>38</v>
+      </c>
+      <c r="TA291">
+        <v>25</v>
+      </c>
+      <c r="TB291" t="s">
+        <v>3166</v>
+      </c>
+      <c r="TC291" s="1">
+        <v>46301</v>
+      </c>
+      <c r="TD291" t="s">
+        <v>3342</v>
+      </c>
+      <c r="TE291" t="s">
+        <v>3481</v>
+      </c>
+      <c r="TF291">
+        <v>38</v>
+      </c>
+      <c r="TG291">
+        <v>25</v>
+      </c>
+      <c r="TH291">
+        <v>13</v>
+      </c>
+      <c r="TI291">
+        <v>9</v>
+      </c>
+      <c r="TJ291" t="s">
+        <v>4177</v>
+      </c>
+      <c r="TK291">
+        <v>0</v>
+      </c>
+      <c r="TL291">
+        <v>1</v>
+      </c>
+      <c r="TM291">
+        <v>1</v>
+      </c>
+      <c r="TN291">
+        <v>1</v>
+      </c>
+      <c r="TO291">
+        <v>0</v>
+      </c>
+      <c r="TP291" t="s">
+        <v>4178</v>
+      </c>
+      <c r="UH291" t="s">
+        <v>4179</v>
+      </c>
+      <c r="ZL291" s="1"/>
+      <c r="ADO291" s="1"/>
+      <c r="ADW291" s="1"/>
+      <c r="AEA291" s="1"/>
+      <c r="AEY291">
+        <v>895119480</v>
+      </c>
+      <c r="AEZ291" t="s">
+        <v>4180</v>
+      </c>
+      <c r="AFA291" s="1">
+        <v>46311.506620370368</v>
+      </c>
+      <c r="AFC291" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE291" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF291" t="s">
+        <v>4181</v>
+      </c>
+      <c r="AFG291">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A292" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B292" t="s">
+        <v>884</v>
+      </c>
+      <c r="D292" t="s">
+        <v>8</v>
+      </c>
+      <c r="E292" t="s">
+        <v>871</v>
+      </c>
+      <c r="I292" t="s">
+        <v>928</v>
+      </c>
+      <c r="SD292" s="1"/>
+      <c r="SV292" t="s">
+        <v>1903</v>
+      </c>
+      <c r="SW292">
+        <v>0</v>
+      </c>
+      <c r="SX292">
+        <v>1</v>
+      </c>
+      <c r="TQ292" s="1">
+        <v>46304</v>
+      </c>
+      <c r="TR292" t="s">
+        <v>4182</v>
+      </c>
+      <c r="TS292" t="s">
+        <v>3030</v>
+      </c>
+      <c r="TT292">
+        <v>758</v>
+      </c>
+      <c r="TU292">
+        <v>568</v>
+      </c>
+      <c r="TV292">
+        <v>15</v>
+      </c>
+      <c r="TW292">
+        <v>10</v>
+      </c>
+      <c r="TX292" t="s">
+        <v>1905</v>
+      </c>
+      <c r="TY292">
+        <v>0</v>
+      </c>
+      <c r="TZ292">
+        <v>0</v>
+      </c>
+      <c r="UA292">
+        <v>1</v>
+      </c>
+      <c r="UB292">
+        <v>1</v>
+      </c>
+      <c r="UC292">
+        <v>1</v>
+      </c>
+      <c r="UD292" t="s">
+        <v>2343</v>
+      </c>
+      <c r="UE292" s="1">
+        <v>46304</v>
+      </c>
+      <c r="UF292" t="s">
+        <v>4183</v>
+      </c>
+      <c r="UG292" t="s">
+        <v>1914</v>
+      </c>
+      <c r="UH292" t="s">
+        <v>4184</v>
+      </c>
+      <c r="ZL292" s="1"/>
+      <c r="ADO292" s="1"/>
+      <c r="ADW292" s="1"/>
+      <c r="AEA292" s="1"/>
+      <c r="AEY292">
+        <v>895119488</v>
+      </c>
+      <c r="AEZ292" t="s">
+        <v>4185</v>
+      </c>
+      <c r="AFA292" s="1">
+        <v>46311.506631944438</v>
+      </c>
+      <c r="AFC292" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE292" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF292" t="s">
+        <v>4186</v>
+      </c>
+      <c r="AFG292">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A293" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B293" t="s">
+        <v>884</v>
+      </c>
+      <c r="D293" t="s">
+        <v>8</v>
+      </c>
+      <c r="E293" t="s">
+        <v>871</v>
+      </c>
+      <c r="I293" t="s">
+        <v>928</v>
+      </c>
+      <c r="SD293" s="1"/>
+      <c r="SV293" t="s">
+        <v>873</v>
+      </c>
+      <c r="SW293">
+        <v>1</v>
+      </c>
+      <c r="SX293">
+        <v>0</v>
+      </c>
+      <c r="SY293" t="s">
+        <v>4176</v>
+      </c>
+      <c r="SZ293">
+        <v>38</v>
+      </c>
+      <c r="TA293">
+        <v>25</v>
+      </c>
+      <c r="TB293" t="s">
+        <v>4123</v>
+      </c>
+      <c r="TC293" s="1">
+        <v>46308</v>
+      </c>
+      <c r="TD293" t="s">
+        <v>2341</v>
+      </c>
+      <c r="TE293" t="s">
+        <v>4187</v>
+      </c>
+      <c r="TF293">
+        <v>38</v>
+      </c>
+      <c r="TG293">
+        <v>25</v>
+      </c>
+      <c r="TH293">
+        <v>5</v>
+      </c>
+      <c r="TI293">
+        <v>4</v>
+      </c>
+      <c r="TJ293" t="s">
+        <v>3071</v>
+      </c>
+      <c r="TK293">
+        <v>0</v>
+      </c>
+      <c r="TL293">
+        <v>0</v>
+      </c>
+      <c r="TM293">
+        <v>0</v>
+      </c>
+      <c r="TN293">
+        <v>0</v>
+      </c>
+      <c r="TO293">
+        <v>1</v>
+      </c>
+      <c r="TP293" t="s">
+        <v>4188</v>
+      </c>
+      <c r="UH293" t="s">
+        <v>4189</v>
+      </c>
+      <c r="ZL293" s="1"/>
+      <c r="ADO293" s="1"/>
+      <c r="ADW293" s="1"/>
+      <c r="AEA293" s="1"/>
+      <c r="AEY293">
+        <v>895122645</v>
+      </c>
+      <c r="AEZ293" t="s">
+        <v>4190</v>
+      </c>
+      <c r="AFA293" s="1">
+        <v>46311.509513888886</v>
+      </c>
+      <c r="AFC293" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE293" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF293" t="s">
+        <v>4191</v>
+      </c>
+      <c r="AFG293">
+        <v>297</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_875741B50482FB89CC18BFA3AD4603C54E6094F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F53B6809-FC64-874A-98A1-C11E7BD82805}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_875741B50482FB89CC18BFA3AD4603C54E6094F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E1F597-288E-9C44-94CF-98A586ECE17D}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="660" windowWidth="24340" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12290" uniqueCount="4192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12375" uniqueCount="4211">
   <si>
     <t>Date</t>
   </si>
@@ -12596,6 +12596,63 @@
   </si>
   <si>
     <t>uuid:142ba58d-72ab-422d-9bb1-2933e7ae9b51</t>
+  </si>
+  <si>
+    <t>Sharing house chores and keeping our environment clean and safe</t>
+  </si>
+  <si>
+    <t>Need for more seedlings to be planted in schools</t>
+  </si>
+  <si>
+    <t>ed6ee815-24fc-43fd-9648-ed0290fbf565</t>
+  </si>
+  <si>
+    <t>uuid:ed6ee815-24fc-43fd-9648-ed0290fbf565</t>
+  </si>
+  <si>
+    <t>Energizer song &amp; movement Food sorting &amp; matching game Structured dialogue on rebalancing chores Learners actively handled materials and practiced (not passive observers)</t>
+  </si>
+  <si>
+    <t>Through games</t>
+  </si>
+  <si>
+    <t>Used of simple language</t>
+  </si>
+  <si>
+    <t>All said it's not happening</t>
+  </si>
+  <si>
+    <t>All agreed</t>
+  </si>
+  <si>
+    <t>That it's happening at home</t>
+  </si>
+  <si>
+    <t>That are taught and they are practically doing</t>
+  </si>
+  <si>
+    <t>That their parents are arrogant but two accepted</t>
+  </si>
+  <si>
+    <t>Do</t>
+  </si>
+  <si>
+    <t>Inadequate materials</t>
+  </si>
+  <si>
+    <t>New knowledge learnt</t>
+  </si>
+  <si>
+    <t>Incorporating food stuff</t>
+  </si>
+  <si>
+    <t>Fulfilling the pledge</t>
+  </si>
+  <si>
+    <t>78290f8b-eec4-4e89-b4cc-43151fd603c1</t>
+  </si>
+  <si>
+    <t>uuid:78290f8b-eec4-4e89-b4cc-43151fd603c1</t>
   </si>
 </sst>
 </file>
@@ -12677,8 +12734,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AFG293" totalsRowShown="0">
-  <autoFilter ref="A1:AFG293" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AFG295" totalsRowShown="0">
+  <autoFilter ref="A1:AFG295" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="839">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Coordinator Name"/>
@@ -13811,7 +13868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AFG293"/>
+  <dimension ref="A1:AFG295"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -22134,7 +22191,7 @@
         <v>843</v>
       </c>
       <c r="FI25">
-        <v>333</v>
+        <v>33</v>
       </c>
       <c r="NP25">
         <v>319</v>
@@ -78773,6 +78830,482 @@
       </c>
       <c r="AFG293">
         <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A294" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B294" t="s">
+        <v>884</v>
+      </c>
+      <c r="D294" t="s">
+        <v>8</v>
+      </c>
+      <c r="E294" t="s">
+        <v>871</v>
+      </c>
+      <c r="I294" t="s">
+        <v>928</v>
+      </c>
+      <c r="SD294" s="1"/>
+      <c r="SV294" t="s">
+        <v>1903</v>
+      </c>
+      <c r="SW294">
+        <v>0</v>
+      </c>
+      <c r="SX294">
+        <v>1</v>
+      </c>
+      <c r="TQ294" s="1">
+        <v>46311</v>
+      </c>
+      <c r="TR294" t="s">
+        <v>4129</v>
+      </c>
+      <c r="TS294" t="s">
+        <v>3030</v>
+      </c>
+      <c r="TT294">
+        <v>848</v>
+      </c>
+      <c r="TU294">
+        <v>687</v>
+      </c>
+      <c r="TV294">
+        <v>10</v>
+      </c>
+      <c r="TW294">
+        <v>16</v>
+      </c>
+      <c r="TX294" t="s">
+        <v>3486</v>
+      </c>
+      <c r="TY294">
+        <v>0</v>
+      </c>
+      <c r="TZ294">
+        <v>1</v>
+      </c>
+      <c r="UA294">
+        <v>0</v>
+      </c>
+      <c r="UB294">
+        <v>1</v>
+      </c>
+      <c r="UC294">
+        <v>0</v>
+      </c>
+      <c r="UD294" t="s">
+        <v>2343</v>
+      </c>
+      <c r="UE294" s="1">
+        <v>46311</v>
+      </c>
+      <c r="UF294" t="s">
+        <v>4192</v>
+      </c>
+      <c r="UG294" t="s">
+        <v>2234</v>
+      </c>
+      <c r="UH294" t="s">
+        <v>4193</v>
+      </c>
+      <c r="ZL294" s="1"/>
+      <c r="ADO294" s="1"/>
+      <c r="ADW294" s="1"/>
+      <c r="AEA294" s="1"/>
+      <c r="AEY294">
+        <v>895125716</v>
+      </c>
+      <c r="AEZ294" t="s">
+        <v>4194</v>
+      </c>
+      <c r="AFA294" s="1">
+        <v>46311.512650462973</v>
+      </c>
+      <c r="AFC294" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE294" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF294" t="s">
+        <v>4195</v>
+      </c>
+      <c r="AFG294">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:839" x14ac:dyDescent="0.2">
+      <c r="A295" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B295" t="s">
+        <v>927</v>
+      </c>
+      <c r="D295" t="s">
+        <v>8</v>
+      </c>
+      <c r="E295" t="s">
+        <v>885</v>
+      </c>
+      <c r="I295" t="s">
+        <v>1097</v>
+      </c>
+      <c r="EN295" t="s">
+        <v>886</v>
+      </c>
+      <c r="FT295">
+        <v>402</v>
+      </c>
+      <c r="FU295">
+        <v>517</v>
+      </c>
+      <c r="FV295">
+        <v>15</v>
+      </c>
+      <c r="FW295">
+        <v>9</v>
+      </c>
+      <c r="FY295">
+        <v>235</v>
+      </c>
+      <c r="FZ295">
+        <v>259</v>
+      </c>
+      <c r="GA295">
+        <v>9</v>
+      </c>
+      <c r="GB295">
+        <v>7</v>
+      </c>
+      <c r="GD295">
+        <v>354</v>
+      </c>
+      <c r="GE295">
+        <v>211</v>
+      </c>
+      <c r="GF295">
+        <v>5</v>
+      </c>
+      <c r="GG295">
+        <v>1</v>
+      </c>
+      <c r="GI295">
+        <v>6</v>
+      </c>
+      <c r="GJ295">
+        <v>5</v>
+      </c>
+      <c r="GK295">
+        <v>1</v>
+      </c>
+      <c r="GL295">
+        <v>0</v>
+      </c>
+      <c r="GN295">
+        <v>11</v>
+      </c>
+      <c r="GO295">
+        <v>29</v>
+      </c>
+      <c r="GP295">
+        <v>0</v>
+      </c>
+      <c r="GQ295">
+        <v>1</v>
+      </c>
+      <c r="GR295" t="s">
+        <v>4196</v>
+      </c>
+      <c r="GS295">
+        <v>1</v>
+      </c>
+      <c r="GT295">
+        <v>1</v>
+      </c>
+      <c r="GU295">
+        <v>0</v>
+      </c>
+      <c r="GV295">
+        <v>1</v>
+      </c>
+      <c r="GW295">
+        <v>0</v>
+      </c>
+      <c r="GX295">
+        <v>0</v>
+      </c>
+      <c r="GY295">
+        <v>1</v>
+      </c>
+      <c r="GZ295" t="s">
+        <v>1348</v>
+      </c>
+      <c r="HA295">
+        <v>1</v>
+      </c>
+      <c r="HB295">
+        <v>1</v>
+      </c>
+      <c r="HC295">
+        <v>1</v>
+      </c>
+      <c r="HD295">
+        <v>1</v>
+      </c>
+      <c r="HE295">
+        <v>0</v>
+      </c>
+      <c r="HG295" t="s">
+        <v>843</v>
+      </c>
+      <c r="HH295" t="s">
+        <v>4197</v>
+      </c>
+      <c r="HI295" t="s">
+        <v>843</v>
+      </c>
+      <c r="HJ295" t="s">
+        <v>864</v>
+      </c>
+      <c r="HL295" t="s">
+        <v>843</v>
+      </c>
+      <c r="HM295" t="s">
+        <v>4198</v>
+      </c>
+      <c r="HT295" t="s">
+        <v>1374</v>
+      </c>
+      <c r="HU295">
+        <v>3</v>
+      </c>
+      <c r="HV295" t="s">
+        <v>4199</v>
+      </c>
+      <c r="HX295" t="s">
+        <v>892</v>
+      </c>
+      <c r="HY295">
+        <v>3</v>
+      </c>
+      <c r="HZ295" t="s">
+        <v>4200</v>
+      </c>
+      <c r="IB295" t="s">
+        <v>892</v>
+      </c>
+      <c r="IC295">
+        <v>3</v>
+      </c>
+      <c r="ID295" t="s">
+        <v>4201</v>
+      </c>
+      <c r="IF295" t="s">
+        <v>893</v>
+      </c>
+      <c r="IG295">
+        <v>3</v>
+      </c>
+      <c r="IH295" t="s">
+        <v>4202</v>
+      </c>
+      <c r="IJ295" t="s">
+        <v>1219</v>
+      </c>
+      <c r="IK295">
+        <v>3</v>
+      </c>
+      <c r="IL295" t="s">
+        <v>4203</v>
+      </c>
+      <c r="IV295" t="s">
+        <v>895</v>
+      </c>
+      <c r="IW295" t="s">
+        <v>896</v>
+      </c>
+      <c r="IX295" t="s">
+        <v>4143</v>
+      </c>
+      <c r="IY295" t="s">
+        <v>987</v>
+      </c>
+      <c r="IZ295" t="s">
+        <v>4143</v>
+      </c>
+      <c r="JA295" t="s">
+        <v>848</v>
+      </c>
+      <c r="JC295" t="s">
+        <v>995</v>
+      </c>
+      <c r="JD295" t="s">
+        <v>896</v>
+      </c>
+      <c r="JE295" t="s">
+        <v>4143</v>
+      </c>
+      <c r="JF295" t="s">
+        <v>982</v>
+      </c>
+      <c r="JG295" t="s">
+        <v>1380</v>
+      </c>
+      <c r="JH295" t="s">
+        <v>852</v>
+      </c>
+      <c r="JJ295" t="s">
+        <v>995</v>
+      </c>
+      <c r="JK295" t="s">
+        <v>896</v>
+      </c>
+      <c r="JL295" t="s">
+        <v>4143</v>
+      </c>
+      <c r="JM295" t="s">
+        <v>987</v>
+      </c>
+      <c r="JN295" t="s">
+        <v>4143</v>
+      </c>
+      <c r="JO295" t="s">
+        <v>848</v>
+      </c>
+      <c r="JQ295" t="s">
+        <v>995</v>
+      </c>
+      <c r="JR295" t="s">
+        <v>896</v>
+      </c>
+      <c r="JS295" t="s">
+        <v>4146</v>
+      </c>
+      <c r="JT295" t="s">
+        <v>987</v>
+      </c>
+      <c r="JU295" t="s">
+        <v>4204</v>
+      </c>
+      <c r="JV295" t="s">
+        <v>852</v>
+      </c>
+      <c r="JX295" t="s">
+        <v>995</v>
+      </c>
+      <c r="JY295" t="s">
+        <v>896</v>
+      </c>
+      <c r="JZ295" t="s">
+        <v>4143</v>
+      </c>
+      <c r="KA295" t="s">
+        <v>982</v>
+      </c>
+      <c r="KB295" t="s">
+        <v>1380</v>
+      </c>
+      <c r="KC295" t="s">
+        <v>848</v>
+      </c>
+      <c r="KE295" t="s">
+        <v>895</v>
+      </c>
+      <c r="KF295" t="s">
+        <v>896</v>
+      </c>
+      <c r="KG295" t="s">
+        <v>1380</v>
+      </c>
+      <c r="KH295" t="s">
+        <v>987</v>
+      </c>
+      <c r="KI295" t="s">
+        <v>1380</v>
+      </c>
+      <c r="KJ295" t="s">
+        <v>848</v>
+      </c>
+      <c r="KK295" t="s">
+        <v>2477</v>
+      </c>
+      <c r="KL295">
+        <v>0</v>
+      </c>
+      <c r="KM295">
+        <v>1</v>
+      </c>
+      <c r="KN295">
+        <v>1</v>
+      </c>
+      <c r="KO295">
+        <v>0</v>
+      </c>
+      <c r="KP295">
+        <v>1</v>
+      </c>
+      <c r="KR295" t="s">
+        <v>4205</v>
+      </c>
+      <c r="KS295" t="s">
+        <v>4206</v>
+      </c>
+      <c r="KT295" t="s">
+        <v>4207</v>
+      </c>
+      <c r="KU295" t="s">
+        <v>4208</v>
+      </c>
+      <c r="NP295">
+        <v>345</v>
+      </c>
+      <c r="NQ295">
+        <v>925</v>
+      </c>
+      <c r="NS295">
+        <v>458</v>
+      </c>
+      <c r="NT295">
+        <v>365</v>
+      </c>
+      <c r="NV295">
+        <v>258</v>
+      </c>
+      <c r="NW295">
+        <v>425</v>
+      </c>
+      <c r="SD295" s="1"/>
+      <c r="UH295" t="s">
+        <v>4171</v>
+      </c>
+      <c r="ZL295" s="1"/>
+      <c r="ADO295" s="1"/>
+      <c r="ADW295" s="1"/>
+      <c r="AEA295" s="1"/>
+      <c r="AEY295">
+        <v>895130017</v>
+      </c>
+      <c r="AEZ295" t="s">
+        <v>4209</v>
+      </c>
+      <c r="AFA295" s="1">
+        <v>46311.516527777778</v>
+      </c>
+      <c r="AFC295" t="s">
+        <v>867</v>
+      </c>
+      <c r="AFE295" t="s">
+        <v>2426</v>
+      </c>
+      <c r="AFF295" t="s">
+        <v>4210</v>
+      </c>
+      <c r="AFG295">
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/Nutribus_2.0_Activity.xlsx
+++ b/Nutribus_2.0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/Nutri-Bus/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_875741B50482FB89CC18BFA3AD4603C54E6094F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E1F597-288E-9C44-94CF-98A586ECE17D}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_875741B50482FB89CC18BFA3AD4603C54E6094F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BF60A9F-344C-6245-8C6E-3A6A326656DB}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="660" windowWidth="24340" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74329,7 +74329,7 @@
         <v>190</v>
       </c>
       <c r="NT268">
-        <v>187263</v>
+        <v>187</v>
       </c>
       <c r="NV268">
         <v>263</v>
